--- a/PARENT_App/data/app_analysis_results.xlsx
+++ b/PARENT_App/data/app_analysis_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="376">
   <si>
     <t>APP_ID</t>
   </si>
@@ -148,6 +148,30 @@
     <t>com.snapchat.android</t>
   </si>
   <si>
+    <t>com.ubercab</t>
+  </si>
+  <si>
+    <t>com.afmobi.boomplayer</t>
+  </si>
+  <si>
+    <t>com.google.android.apps.youtube.kids</t>
+  </si>
+  <si>
+    <t>com.facebook.lite</t>
+  </si>
+  <si>
+    <t>com.whatsapp.w4b</t>
+  </si>
+  <si>
+    <t>com.whatsapp</t>
+  </si>
+  <si>
+    <t>com.google.android.youtube</t>
+  </si>
+  <si>
+    <t>com.giraffegames.carmechanic</t>
+  </si>
+  <si>
     <t>Bible Offline-KJV Holy Bible</t>
   </si>
   <si>
@@ -166,6 +190,30 @@
     <t>Snapchat</t>
   </si>
   <si>
+    <t>Uber - Request a ride</t>
+  </si>
+  <si>
+    <t>Boomplay: Music &amp; Live Stream</t>
+  </si>
+  <si>
+    <t>YouTube Kids</t>
+  </si>
+  <si>
+    <t>Facebook Lite</t>
+  </si>
+  <si>
+    <t>WhatsApp Business</t>
+  </si>
+  <si>
+    <t>WhatsApp Messenger</t>
+  </si>
+  <si>
+    <t>YouTube</t>
+  </si>
+  <si>
+    <t>Car Restore - Car Mechanic</t>
+  </si>
+  <si>
     <t>https://play-lh.googleusercontent.com/2vbob1Knz2piGnjL1hgY1P4xdsO092dYPHGLCLUql2gf9b7OnQbtkM7wNN_u0LQqF3eU</t>
   </si>
   <si>
@@ -184,6 +232,30 @@
     <t>https://play-lh.googleusercontent.com/KxeSAjPTKliCErbivNiXrd6cTwfbqUJcbSRPe_IBVK_YmwckfMRS1VIHz-5cgT09yMo</t>
   </si>
   <si>
+    <t>https://play-lh.googleusercontent.com/AQtSF5Sl18yp3mQ2tcbOrBLekb7cyP3kyg5BB1uUuc55zfcnbkCDLHFTBwZfYiu1aDI</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/UPOgWEbW41KCHeeKmkqH62u1kaWwIGEGSLHF1TCk2K1fHwxGIyYVm9yRro9Aoi2bfGQ</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/OxNGx8LU6gm8aLfJcwcJxunvj2a7zDgDyPOD4J9HRSIc6N_1O1iZ2dLr3xQMbuMy_wE</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/U202Yto9o6IT1ZA8bgigA5q4nIzvu0S9ztl2d0WQSj6Iw0hIw5W7SIAnH0U2-Kk3nao</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/K6L_Ixmw0J9oTktAoHyEHvzQIfxEF1CIQ5aE0WHhdUeOgfAmn7KLhe47Q5XxZaXQ0g</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/bYtqbOcTYOlgc6gqZ2rwb8lptHuwlNE75zYJu6Bn076-hTmvd96HH-6v7S0YUAAJXoJN</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/6am0i3walYwNLc08QOOhRJttQENNGkhlKajXSERf3JnPVRQczIyxw2w3DxeMRTOSdsY</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/eqia7ygIjeHnszHFPAITCvfUAhEeqMy5Qyl7i-oQ68qeJCtpid663wMwfDTABzTq8o0A</t>
+  </si>
+  <si>
     <t>BOOKS_AND_REFERENCE</t>
   </si>
   <si>
@@ -199,6 +271,18 @@
     <t>COMMUNICATION</t>
   </si>
   <si>
+    <t>MUSIC_AND_AUDIO</t>
+  </si>
+  <si>
+    <t>ENTERTAINMENT</t>
+  </si>
+  <si>
+    <t>VIDEO_PLAYERS</t>
+  </si>
+  <si>
+    <t>GAME_SIMULATION</t>
+  </si>
+  <si>
     <t>Everyone</t>
   </si>
   <si>
@@ -223,6 +307,30 @@
     <t>http://www.snapchat.com/privacy</t>
   </si>
   <si>
+    <t>https://www.uber.com/privacy</t>
+  </si>
+  <si>
+    <t>https://www.boomplay.com/privacyPolicy</t>
+  </si>
+  <si>
+    <t>http://www.google.com/intl/en/policies/privacy/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/about/privacy/</t>
+  </si>
+  <si>
+    <t>https://www.whatsapp.com/legal/business-app-privacy-policy</t>
+  </si>
+  <si>
+    <t>https://www.whatsapp.com/legal/privacy-policy</t>
+  </si>
+  <si>
+    <t>http://www.google.com/policies/privacy</t>
+  </si>
+  <si>
+    <t>http://giraffe-games.com/privacypolicy.html</t>
+  </si>
+  <si>
     <t>{'Identity': ['find accounts on the device'], 'Contacts': ['find accounts on the device'], 'Phone': ['read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['Google Play license check', 'control vibration', 'create accounts and set passwords', 'draw over other apps', 'full network access', 'prevent device from sleeping', 'read sync settings', 'run at startup', 'toggle sync on and off', 'view network connections'], 'Uncategorized': ['receive data from Internet']}</t>
   </si>
   <si>
@@ -241,6 +349,30 @@
     <t>{'Identity': ['find accounts on the device', 'read your own contact card'], 'Contacts': ['find accounts on the device', 'modify your contacts', 'read your contacts'], 'Location': ['precise location (GPS and network-based)'], 'Phone': ['read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['access Bluetooth settings', 'change network connectivity', 'change your audio settings', 'connect and disconnect from Wi-Fi', 'control flashlight', 'control vibration', 'create accounts and set passwords', 'full network access', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read sync settings', 'run at startup', 'toggle sync on and off', 'view network connections'], 'Uncategorized': ['read sync statistics', 'receive data from Internet']}</t>
   </si>
   <si>
+    <t>{'Identity': ['add or remove accounts', 'find accounts on the device'], 'Contacts': ['find accounts on the device', 'read your contacts'], 'Location': ['approximate location (network-based)', 'precise location (GPS and network-based)'], 'Phone': ['directly call phone numbers', 'read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['access Bluetooth settings', 'change network connectivity', 'change your audio settings', 'control vibration', 'draw over other apps', 'full network access', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read Google service configuration', 'run at startup', 'use accounts on the device', 'view network connections'], 'Uncategorized': ['receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Contacts': ['read your contacts'], 'Phone': ['read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['change network connectivity', 'change your audio settings', 'connect and disconnect from Wi-Fi', 'control flashlight', 'control vibration', 'disable your screen lock', 'expand/collapse status bar', 'full network access', 'install shortcuts', 'modify system settings', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read Google service configuration', 'view network connections'], 'Uncategorized': ['receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Identity': ['find accounts on the device'], 'Contacts': ['find accounts on the device'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Other': ['draw over other apps', 'full network access', 'measure app storage space', 'prevent device from sleeping', 'read Google service configuration', 'run at startup', 'view network connections']}</t>
+  </si>
+  <si>
+    <t>{'Device &amp; app history': ['retrieve running apps'], 'Identity': ['add or remove accounts', 'find accounts on the device', 'read your own contact card'], 'Calendar': ["add or modify calendar events and send email to guests without owners' knowledge", 'read calendar events plus confidential information'], 'Contacts': ['find accounts on the device', 'modify your contacts', 'read your contacts'], 'Location': ['approximate location (network-based)', 'precise location (GPS and network-based)'], 'SMS': ['read your text messages (SMS or MMS)'], 'Phone': ['directly call phone numbers', 'read call log', 'read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['change network connectivity', 'change your audio settings', 'connect and disconnect from Wi-Fi', 'control vibration', 'create accounts and set passwords', 'draw over other apps', 'full network access', 'install shortcuts', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read battery statistics', 'reorder running apps', 'run at startup', 'send sticky broadcast', 'uninstall shortcuts', 'view network connections'], 'Uncategorized': ['bind to a notification listener service', 'receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Device &amp; app history': ['retrieve running apps'], 'Identity': ['add or remove accounts', 'find accounts on the device', 'read your own contact card'], 'Contacts': ['find accounts on the device', 'modify your contacts', 'read your contacts'], 'Location': ['approximate location (network-based)', 'precise location (GPS and network-based)'], 'SMS': ['send SMS messages'], 'Phone': ['directly call phone numbers', 'read call log', 'read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['access Bluetooth settings', 'change network connectivity', 'change your audio settings', 'connect and disconnect from Wi-Fi', 'control Near Field Communication', 'control vibration', 'create accounts and set passwords', 'draw over other apps', 'full network access', 'install shortcuts', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read Google service configuration', 'read sync settings', 'run at startup', 'send sticky broadcast', 'toggle sync on and off', 'uninstall shortcuts', 'use accounts on the device', 'view network connections'], 'Uncategorized': ['read sync statistics', 'receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Device &amp; app history': ['retrieve running apps'], 'Identity': ['add or remove accounts', 'find accounts on the device', 'read your own contact card'], 'Contacts': ['find accounts on the device', 'modify your contacts', 'read your contacts'], 'Location': ['approximate location (network-based)', 'precise location (GPS and network-based)'], 'SMS': ['receive text messages (SMS)', 'send SMS messages'], 'Phone': ['directly call phone numbers', 'read call log', 'read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['access Bluetooth settings', 'change network connectivity', 'change your audio settings', 'connect and disconnect from Wi-Fi', 'control Near Field Communication', 'control vibration', 'create accounts and set passwords', 'draw over other apps', 'full network access', 'install shortcuts', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read Google service configuration', 'read sync settings', 'reorder running apps', 'run at startup', 'send sticky broadcast', 'toggle sync on and off', 'uninstall shortcuts', 'use accounts on the device', 'view network connections'], 'Uncategorized': ['read sync statistics', 'receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Identity': ['add or remove accounts', 'find accounts on the device'], 'Contacts': ['find accounts on the device', 'read your contacts'], 'Location': ['approximate location (network-based)', 'precise location (GPS and network-based)'], 'Phone': ['read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['change your audio settings', 'control Near Field Communication', 'control vibration', 'draw over other apps', 'full network access', 'measure app storage space', 'prevent device from sleeping', 'read Google service configuration', 'run at startup', 'use accounts on the device', 'view network connections'], 'Uncategorized': ['manage document storage', 'receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Other': ['allow Wi-Fi Multicast reception', 'full network access', 'view network connections']}</t>
+  </si>
+  <si>
     <t>['CONTACTS', 'PERSISTENTID', 'STORAGE', 'LOCATION']</t>
   </si>
   <si>
@@ -257,6 +389,18 @@
   </si>
   <si>
     <t>['CONTACTS', 'LOCATION', 'PERSISTENTID', 'STORAGE', 'CAMERA', 'MICROPHONE']</t>
+  </si>
+  <si>
+    <t>['CONTACTS', 'LOCATION', 'PHONE_CALL', 'PERSISTENTID', 'STORAGE', 'CAMERA', 'MICROPHONE']</t>
+  </si>
+  <si>
+    <t>['CONTACTS', 'PERSISTENTID', 'STORAGE', 'CAMERA', 'MICROPHONE', 'LOCATION']</t>
+  </si>
+  <si>
+    <t>['CONTACTS', 'STORAGE', 'MICROPHONE', 'LOCATION', 'PERSISTENTID']</t>
+  </si>
+  <si>
+    <t>['CONTACTS', 'LOCATION', 'SMS', 'PHONE_CALL', 'PERSISTENTID', 'STORAGE', 'CAMERA', 'MICROPHONE']</t>
   </si>
   <si>
     <t>👥 CONTACTS: Could share your child’s contacts with others.
@@ -296,6 +440,40 @@
   <si>
     <t>👥 CONTACTS: Could share your child’s contacts with others.
 📍 LOCATION: Can follow your child’s location.
+🆔 DEVICE ID: Could track your child across apps or over time.
+📁 STORAGE: Could save or read your child’s photos or downloads.
+🎥 CAMERA: Could record your child’s face or surroundings.
+🎙️ MICROPHONE: Could listen to your child talk or play.</t>
+  </si>
+  <si>
+    <t>👥 CONTACTS: Could share your child’s contacts with others.
+📍 LOCATION: Can follow your child’s location.
+📞 PHONE CALL: Could make calls without your permission.
+🆔 DEVICE ID: Could track your child across apps or over time.
+📁 STORAGE: Could save or read your child’s photos or downloads.
+🎥 CAMERA: Could record your child’s face or surroundings.
+🎙️ MICROPHONE: Could listen to your child talk or play.</t>
+  </si>
+  <si>
+    <t>👥 CONTACTS: Could share your child’s contacts with others.
+🆔 DEVICE ID: Could track your child across apps or over time.
+📁 STORAGE: Could save or read your child’s photos or downloads.
+🎥 CAMERA: Could record your child’s face or surroundings.
+🎙️ MICROPHONE: Could listen to your child talk or play.
+📍 LOCATION: Can follow your child’s location.</t>
+  </si>
+  <si>
+    <t>👥 CONTACTS: Could share your child’s contacts with others.
+📁 STORAGE: Could save or read your child’s photos or downloads.
+🎙️ MICROPHONE: Could listen to your child talk or play.
+📍 LOCATION: Can follow your child’s location.
+🆔 DEVICE ID: Could track your child across apps or over time.</t>
+  </si>
+  <si>
+    <t>👥 CONTACTS: Could share your child’s contacts with others.
+📍 LOCATION: Can follow your child’s location.
+💬 SMS: Could send or read text messages without your knowledge.
+📞 PHONE CALL: Could make calls without your permission.
 🆔 DEVICE ID: Could track your child across apps or over time.
 📁 STORAGE: Could save or read your child’s photos or downloads.
 🎥 CAMERA: Could record your child’s face or surroundings.
@@ -673,6 +851,1438 @@
 To do the things you expect from our Services and as we’ve described within this Privacy Policy. For example, we maintain your list of friends until you ask us to delete them since friends are key to expressing yourself. Similarly, we keep your shared list of contacts until you ask us to remove them in our app settings (note: updating your device permissions may not remove the contacts you’ve previously shared with Snapchat). Learn more. Conversely, Snaps and Chats sent in Snapchat will be deleted by default from our servers within 24 hours after we detect they’ve been opened by all recipients or have expired, unless you’ve changed your default set</t>
   </si>
   <si>
+    <t>Uber Privacy Notice: Riders &amp; Order Recipients
+Skip to main content
+UberRide
+Drive
+Business
+Uber Eats
+About
+About us
+Our offerings
+How Uber works
+Sustainability
+Newsroom
+Investor relations
+Autonomous
+Blog
+Careers
+More
+No results
+EN
+Help
+Log in
+Sign up
+UberLog in
+Sign up
+,
+Uber Privacy Notice: Riders and Order Recipients
+When you use Uber, you trust us with your personal data. We’re committed to keeping that trust. That starts with helping you understand our privacy practices.
+This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. We recommend that you read this along with our privacy overview, which highlights key points about our privacy practices.
+Uber Privacy Notice: Drivers and Delivery People
+Previous version of the Privacy Notice
+I. Overview
+II. Data collections and uses
+A. Data we collect
+B. How we use data
+C. Core automated processes
+D. Cookies and related technologies
+E. Data sharing and disclosure
+F. Data retention and deletion
+III. Choice and transparency
+IV. Legal information
+A. Data controllers and Data Protection Officer
+B. Our legal bases for using your data
+C. Legal framework for data transfers
+D. Updates to this Privacy Notice
+I. Overview
+A. Scope
+This notice applies when you use Uber’s apps or websites to request or receive products or services, including rides or deliveries.
+This notice describes how we collect and use your data if you request or receive products or services through Uber’s apps or websites, except when you use Uber Freight, Careem or Uber Taxi (South Korea).
+This notice specifically applies if you:
+Request or receive mobility services, including rides and package delivery and return services through Uber Connect, via your Uber account (a “Rider”).
+Request or receive food or other products and services for delivery or pickup, including via your Uber Eats or Postmates account, or through the guest checkout features that allow you to access delivery or pickup services without creating and/or signing into your account (an “Order Recipient”).
+Receive services through Uber’s apps or websites requested by other account owners (a “Guest User”), including if you receive ride or delivery services ordered by Uber Health, Central, Uber Direct or Uber for Business customers (collectively, “Enterprise Customers”); or by friends, family members or other individual account owners, including via Uber Connect; or receive a gift card.
+Rent a vehicle through Uber Car Rentals (a “Renter”).
+This notice does not describe Uber’s collection and use of your data if you use Uber to provide (instead of request or receive) services through Uber’s app or websites, including as a driver or delivery person. Uber’s notice describing our collection and use of such data is available here. Those who use Uber to either request, receive or provide services are referred to as “users” in this notice.
+Our privacy practices are subject to applicable laws in the places in which we operate. The types of data processing that such laws require, allow, or prohibit vary globally. Therefore, if you travel across national, state or other geographic borders, Uber's data processing practices described in this notice may differ from those in your home country or territory.
+In addition, please note the following if you use Uber in:
+ArgentinaDown Small
+The Agency of Access to Public Information, in its role of Regulating Body of Law 25.326, is responsible for receiving complaints and reports presented by any data subjects who believe their rights have been impacted by a violation of the local data protection regulation.
+AustraliaDown Small
+You may contact Uber here regarding our compliance with the Australian Privacy Principles. Such contacts will be addressed by Uber’s customer service and/or relevant privacy teams within a reasonable timeframe. You may also contact the Office of the Australian Information Commissioner here with concerns regarding such compliance.
+BrazilDown Small
+Please go here for information regarding Uber’s privacy practices as relates to Brazil’s General Data Protection Law (Lei Geral de Proteção de Dados - LGPD).
+Colombia, Honduras and JamaicaDown Small
+“Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.”
+European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small
+Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. Such data collections and uses are indicated with an asterisk (*). If you use Uber outside of these regions, your data may be collected and used for the purposes indicated with an asterisk.
+KenyaDown Small
+You may contact Uber here with questions regarding Uber’s compliance with, or to request exercise of your rights under, Kenya’s Data Protection Act of 2019. You may also contact the Office of the Data Protection Commissioner here with concerns regarding such compliance or exercise of your rights.
+MexicoDown Small
+Please go here for information regarding Uber’s privacy practices as relates to Mexico’s Personal Data Protection Law (Ley Federal de Protección de Datos Personales en Posesión de los Particulares), and here for information regarding Uber Money's processing of personal data.
+NigeriaDown Small
+You may contact Uber here regarding Uber’s compliance with, or to request exercise of your rights under, Nigeria’s Data Protection Act of 2023. You may also contact the Nigeria Data Protection Commission here with concerns regarding such compliance.
+Quebec, CanadaDown Small
+You may contact Uber here with questions about Uber’s use of your data for purposes of automated decision making, including regarding the factors considered in connection with such decision, to request correction of any personal data relating to such decisions, and to request review of any such decisions by Uber personnel.
+SwitzerlandDown Small
+Uber Switzerland GmbH (Stockerstrasse 33
+8002 Zürich, Switzerland) is Uber’s appointed representative for purposes of the Federal Act on Data Protection and may be contacted here or by mail as relates to that act.
+TaiwanDown Small
+Please see here for information on the measures adopted by Uber when conducting cross-border data transfers in accordance with Taiwan’s Personal Data Protection Act and its relevant regulations, as well as other related information.
+United StatesDown Small
+Please go here for information regarding Uber’s privacy practices as relates to US state privacy laws, including the California Consumer Privacy Act. If you use Uber in Nevada or Washington, please go here for information regarding Uber’s practices as relates to collection and use of consumer health data under those states’ privacy laws.
+Please contact us here with any questions regarding our practices in a particular country or region.
+II. Data collections and uses
+A. The data we collect
+Uber collects data:
+1. That you provide
+2. When you use our services
+3. From other sources
+Please go here for a summary of the data we collect and how we use it.
+Uber collects the following data:
+1. Data you provide: This includes:
+Data category
+Data types
+a. Account information. We collect data when you create or update your Uber account.
+Address
+Email
+First and last name
+Login name and password
+Phone number
+Payment method (including related payment verification information)
+Profile picture
+Settings (including accessibility settings) and preferences
+Uber partner loyalty program information
+b. Demographic data. We collect demographic data if necessary to enable certain features. For example:
+We collect your date of birth and/or age to verify your eligibility to use age-restricted products or services, such as Uber for teens, or if you purchase alcohol, tobacco or cannabis products.
+We collect or infer your gender to enable Women Rider Preference, and for marketing and advertising.
+We may also collect demographic data through user surveys.
+Age or date of birth
+Gender or inferred gender (using first name)
+c. Identity verification information. This refers to the data that we collect to verify your account or identity.
+Government-issued identification documents, such as driver’s licenses or passports (which may contain identification photos and numbers, expiration date, date of birth, and gender)
+User-submitted selfies
+d. User content. This refers to the data that we collect when you:
+Contact Uber for customer support or other inquiries.
+Use features that enable you to create Lists or reviews of restaurants or merchants
+Upload photos and recordings (including those submitted for purposes of customer support)
+Provide ratings or feedback for drivers, delivery people, restaurants or merchants, or they provide feedback regarding you.
+Please go here for more information about how ratings provided by other users are determined and used.
+Chat logs and call recordings
+Ratings or feedback
+User created Lists or reviews of restaurants or merchants
+Uploaded photos and recordings, including in-app audio recordings
+e. Travel information. We collect travel itinerary information if you book bus, train or flight travel through Uber's apps.
+Dates/times of travel
+2. Data collected when you use our services: This includes:
+Data category
+Data types
+a. Location data. If you request a ride, we track your driver’s location during your trip, and link that data to your account. This allows us to display where you are on your trip.
+We also determine your approximate location, and can determine your precise location if you allow us to do so through the settings on your phone. If you do, we will collect your precise location from the time you request a ride or order until the ride is finished or your order is delivered. We also collect such data when you have the Uber app open on your phone’s screen.
+You can use Uber without letting us collect your precise location. However, it may be less convenient for you, including because you will have to type your location into your phone instead of allowing us to detect it for you.
+See “Choice and transparency” section below for information on how to control whether Uber may collect your precise location data.
+Approximate location
+Precise location
+b. Trip/order information. This refers to the details we collect about your trip or order, including orders placed via guest checkout features.
+Payment information (including amount charged and payment method)
+Proof of delivery (including photo or signature)
+Special instructions, allergies or food preferences
+Statistics derived from past trip/order information, such as  Averages
+Cancellation rates
+Total trips/orders
+Trip or order details, including Date and time
+Requested pickup and dropoff addresses
+Distance traveled
+Restaurant or merchant name and location
+Items ordered
+c. Usage data. This refers to data about how you interact with Uber’s apps and websites.
+App crashes and other system activity
+Access dates and times
+App features or pages viewed
+Browser type
+d. Device data. This refers to data about the device(s) you use to access Uber.
+Advertising identifiers
+Device motion data
+Device IP address or other unique device identifiers
+Hardware models
+Mobile network data
+Operating systems and versions
+Preferred languages
+e. Communications data. This refers to the data we collect when you communicate with drivers and delivery people through Uber’s apps.
+Communication type (phone or text message)
+Content (including recordings of phone calls solely when users are notified of the recording in advance)
+Date and time
+3. Data from other sources: These include:
+Data category
+Data types
+a. Law enforcement officials, public health officials and other government authorities.
+Name and contact information
+Information relating to law enforcement, health or other investigations
+b. Marketing partners and service providers. This includes banks in connection with cash back programs,* and data resellers.*
+Activity information
+Name and contact information
+User or device identifiers
+c. Service providers who help us verify your identity or detect fraud.*
+Confirmation of whether your account information relates to known persons
+Name and contact information
+Information relating to the wireless carrier associated with your phone number
+Information from government-issued identification documents such as driver’s licenses or passports (such as identification numbers, expiration date, date of birth, and gender)
+d. Uber account owners. This refers to Uber account owners who request services for you (such as friends or family members), or who enable you to request services through their accounts (such as Enterprise Customers).
+Name and contact information
+Trip/order info
+Location
+e. Uber business partners (account creation and access, and APIs). Uber may receive your data from business partners through which you create or access your Uber account, such as payment providers, social media services, or apps or websites that use Uber’s APIs or whose APIs Uber uses.
+The information received from Uber business partners depends on which partners you use to create or access your Uber account, or the API used.
+f. Uber business partners (debit or credit cards). Uber may receive your data from business partners in connection with debit or credit cards issued by a financial institution in partnership with Uber to the extent disclosed in the terms and conditions for the card.
+Debit or credit card activity information
+g. Users or others providing information in connection with customer support issues, claims or disputes.
+Name
+Evidence relating to accidents, conflicts, claims or disputes (which may include photos or recordings of you)
+h. Users participating in Uber’s referral programs. For example, if you are referred to Uber by another user, we receive your data from that user.
+Name and contact information
+B. How we use data
+Uber uses data to enable reliable and convenient transportation, delivery, and other products and services. We also use data:
+To enhance the safety and security of our users and services, and to prevent and detect fraud
+For marketing and advertising
+To enable communications between users
+For customer support
+For research and development
+To send non-marketing communications to users
+In connection with legal proceedings
+1. To provide our services. Uber uses data to provide, personalize, maintain, and improve our services.
+Data uses
+Data used includes
+a. Creating and updating your account
+Account
+Demographics
+Location
+b. Enabling services and features. This includes:
+Enabling navigation to pickups and dropoffs, calculating ETAs and tracking the progress of rides or deliveries
+Matching you with available drivers or delivery people when you request transportation or deliveries
+Enabling features that involve data sharing, such as ETA sharing and fare splitting
+Enabling accessibility features
+Enabling features that involve account linking, such as linking with Uber partners’ loyalty programs
+Facilitating and optimizing rental car reservations, pickup and dropoff through Uber Rent
+Account
+Data from other sources
+Demographics
+Device
+Ratings
+Travel
+c. Calculating rider/recipient prices and driver/delivery person fares.
+Location
+Trip/order info
+d. Processing payments and enabling payment and e-money products such as Uber Money.
+Account
+Demographics
+Data from other sources
+Trip/order info
+e. Personalizing your account. For example, we may present you with personalized restaurant or food recommendations, or trip suggestions, based on your prior orders, trips and delivery location.
+Account
+Demographics
+Data from other sources
+Trip/order info
+f. Providing you with trip or delivery updates and generating receipts.
+Account
+Trip/order info
+g. Informing you of changes to our terms, services, or policies.
+Account
+Trip/order info
+h. Performing necessary operations to maintain our services, including to troubleshoot software bugs and operational problems.
+Account
+Device
+Usage
+2. For safety, security, and fraud prevention and detection. Uber uses data to help maintain the safety and security of our services and users.
+Data uses
+Data used includes
+a. Verifying your account, identity or compliance with safety requirements. This includes:
+Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases*
+Verifying that your account is being used by you and not someone else by:
+Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document*
+Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person*
+Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect
+Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology
+Verifying your eligibility to subscribe to an Uber One for Students membership
+Account
+Data from other sources (third-party databases)
+Identity verification info
+User content
+b. Preventing, detecting, and combating fraud, including by Guest Users.
+Account
+Communications between users
+Data from other sources (driver data)
+Device
+Identity verification info
+Location
+Trip/order info
+Usage
+c. Predicting and helping avoid pairings of users that may result in increased risk of conflict,* or where one user has previously given the other a low (for instance, one star) rating.
+Account
+Trip/order info (including cancellation rates)
+Usage
+User content (ratings and reported incidents)
+d. Providing live support from safety experts during trips or deliveries.
+Account (phone, user name, vehicle details)
+Location
+Trip/order info
+User content
+3. For marketing and advertising. Uber uses data (except Guest Users’ data) to market its services, and those of Uber partners.
+Data uses
+Data used includes
+a. Personalizing marketing communications and ads relating to Uber products and services, and those offered by other companies. For example, Uber may:
+Send push notifications suggesting your favorite destinations or merchants, or in-app messages offering discounts or promotions for products or merchants similar to those you’ve previously ordered
+Display personalized ads on Uber or other companies’ apps or websites
+Personalize sponsored listings, discounts or promotions for restaurants and merchants available on Uber
+Account
+Data from other sources
+Demographics (including inferred gender)
+Device
+Location
+Trip/order info
+Usage
+b. Displaying ads that are targeted based on data about your current trip or delivery request, including time of request and services requested. For example, if you request a trip to a supermarket, we may display in-app ads for third-party products that may be available at that supermarket.
+Account
+Data from other sources
+Demographics (including inferred gender)
+Device
+Location
+Trip/order info
+Usage
+c. Measuring the effectiveness of the marketing communications and ads described above.
+Account
+Device
+Usage
+4. To enable communications between users.
+Data uses
+Data used includes
+For example, a driver may message or call you to confirm a pickup location, you may call a driver to retrieve a lost item, or a restaurant or delivery person may contact you with information about your order.
+Account
+Device
+Usage
+5. For customer support.
+Data uses
+Data used includes
+This includes investigating and addressing user concerns, monitoring and improving our customer support responses and processes, and identifying potential participants in research studies relating to customer support issues.
+Account
+Communications
+Device
+Identity verification info
+Data from other sources
+Location
+Travel information
+Usage
+User content
+Trip/order info
+6. For research and development.
+Data uses
+Data used includes
+We use data for analysis, research and product development, including training machine learning models. This helps us make our services more convenient and easy-to-use, enhance the safety and security of our services, and develop new services and features.
+Account
+Communications
+Demographics
+Device
+Identity verification info
+Data from other sources
+Location
+Travel information
+Usage
+User content
+Trip/order info
+7. For non-marketing communications.
+Data uses
+Data used includes
+This includes surveys and communications regarding elections, ballots, referenda and other political processes that relate to our services. For example, we may notify you of ballot measures or pending legislation relating to Uber’s services where you live.
+Account
+Location
+8. For legal proceedings and requirements.
+Data uses
+Data used includes
+We use data to investigate or address claims or disputes relating to use of Uber’s services; to satisfy requirements under applicable laws, regulations, operating licenses or agreements, insurance policies; or pursuant to legal process or governmental request, including from law enforcement.
+Account
+Communications
+Demographics
+Device
+Identity verification info
+Data from other sources
+Location
+Travel information
+Usage
+User content
+Trip/order info
+C. Core automated processes
+Uber uses automated processes to enable certain parts of our services, including functions essential to our business such as matching, pricing and fraud prevention and detection.
+Uber relies on automated processes to enable essential parts of our services, including matching (pairing users requesting and providing transportation and/or delivery services), pricing (calculating the amount owed for such services) and fraud detection and prevention. These processes allow Uber to provide a seamless, and safe, experience to millions of users globally every day.
+This section describes how automated matching, pricing, and fraud prevention and detection processes work, including how they impact your Uber experience and the personal and non-personal data used to enable these processes.
+You may contact Uber here if you have questions or concerns regarding these processes.
+1. MatchingDown Small
+Uber uses algorithms to efficiently match Riders and drivers, or delivery people and Order Recipients. This helps us minimize wait times for you, and enable efficiency for drivers and delivery people.
+The matching process is triggered when you request transportation or deliveries through Uber. Our algorithms then evaluate various factors to determine the best match, including your location, requested destination, the proximity and availability of drivers or delivery people, traffic conditions, and historical data (including, in some markets, whether the specific Rider and driver have previously reported having negative experiences with each other).
+The trip or delivery request is then communicated to the driver/delivery person matched through this process. Once a trip or order is accepted, we send confirmation of the match to you and the driver/delivery person.
+We are constantly refining our matching process to provide the best experience to all users on our platform and may consider different factors depending on the location where you use Uber.
+Additional information on Uber’s matching process is available here.
+2. PricingDown Small
+When you request transportation or a delivery, Uber uses algorithms to determine the price you pay based on a variety of factors, including:
+The type of service you request (for instance, UberX, UberXL, Uber Black)
+Your location
+Estimated time and distance to destination
+Availability and proximity of drivers or delivery people
+Time of day
+Traffic conditions
+Historical data such as traffic patterns and seasonal trends.
+Your price may also vary depending on tolls or surcharges incurred, tips, discounts, promotions and subscriptions, and route-based adjustments.
+The price may also vary depending on surge pricing, which automatically goes into effect when there are more Riders in a given area than available drivers. This encourages more drivers to serve the busy area over time and shifts Rider demand, to maintain reliability and restore balance.
+Additional information on Uber’s pricing process is available here.
+3. Fraud prevention and detectionDown Small
+Uber uses algorithms and machine learning models to prevent and detect fraud against Uber or our users. This includes efforts to monitor for account takeovers, suspicious user behaviors, and unauthorized access attempts, including by third-party aggregators.
+These tools look for patterns that may indicate fraudulent behavior, such as those that vary significantly from typical user behavior. To do this, Uber performs real-time monitoring of information collected from or generated by users, including location data, payment information, and Uber usage. We also examine historical data and compare it against real-time data to help detect suspicious behavior.
+Uber may limit your access to its services, or require that you undertake a particular action such as verifying your identity before allowing such access, if it detects potential fraudulent activity.
+You may contact Uber customer support here if you have questions or concerns about these processes.
+D. Cookies and related technologies
+Uber and its partners use cookies and other identification technologies on our apps, websites, emails, and online ads for purposes described in this notice, and Uber’s Cookie Notice.
+Cookies are small text files that are stored on browsers or devices by websites, apps, online media, and ads. Uber uses cookies and similar technologies for purposes such as:
+Authenticating users
+Remembering user preferences and settings
+Determining the popularity of content
+Delivering and measuring the effectiveness of advertising campaigns
+Analyzing site traffic and trends, and generally understanding the online behaviors and interests of people who interact with our services.
+We may also allow others to provide audience measurement and analytics services for us, to serve ads on our behalf across the internet or for other companies’ products and services on our apps, and to track and report on the performance of those ads. These entities may use cookies, web beacons, SDKs and other technologies to identify the devices used by visitors to our websites, as well as when they visit other online sites and services.
+Please see our Cookie Notice for more information regarding the use of cookies and other technologies described in this section.
+E. Data sharing and disclosure
+We share your data with other users where necessary to provide our services or features, at your request, or with your consent. We also share data with our affiliates, subsidiaries, service providers and partners, for legal reasons, or in connection with claims or disputes.
+Uber may share data:
+1. With other users
+This may include sharing data with:
+Recipient
+Data shared
+Your driver
+Account First name
+Rating
+Pickup and/or dropoff locations
+Settings and preferences
+Other Riders during shared rides
+Account First name
+Restaurants/merchants you order from, and your delivery person
+AccountFirst name
+Order infoDelivery address (including with  restaurants/merchants that use their own delivery people to fulfill your order)
+Items ordered (which may include drug prescriptions)
+Special instructions, allergies or food preferences
+User content Feedback
+Ratings
+The owner of any Uber account you use. This includes if you use an account linked to a Family profile, or request or receive ride or delivery services as a Guest User of an Enterprise Customer’s account.
+In addition, if you create an account using an email address affiliated with an Uber for Business account owner (i.e., your employer), we may share your account data (such as name and email address) with such account owner, to help you expense trips or orders to that Uber for Business account.*
+We may also share information with that account owner about issues involving your trip, such as safety incidents or complaints.
+Account
+Trip/order info
+Other recipients in your group order
+Account First name
+Order info Special instructions or allergies information
+Items ordered
+People who refer you to Uber. We may share your data as necessary to determine their referral bonus
+Trip/order infoTrip count
+Other Uber Eats users. We share your data if you post a review of a restaurant or create a List of your favorite restaurants on Uber Eats, and set sharing of the List to “Public.”
+Account First name
+User contentLists
+Reviews
+2. Upon request or with your consent
+This may include sharing data with:
+Recipient
+Data shared
+Users with whom you use data-sharing features. This includes features that allow you to share your ETA and location, or split your fare.
+Depending on the feature used, may include:
+Account
+Location
+Trip/order info
+Uber business partners. We share data with companies whose apps or websites you access through Uber, including for purposes of promotions, contests or specialized services.
+Depending on the app or website you access through Uber, and for what purpose, may include:
+Account
+Device
+Trip/order info
+Emergency services. We enable you to share your data with police, fire, and ambulance services in the event of an emergency or after certain incidents.
+For more information, please go to the “Choice and transparency” and “Emergency data sharing” sections below.
+AccountName
+Phone number
+Location
+Trip/order infoRequested pickup/dropoff
+Insurance companies. If you are involved in an incident, or report or submit a claim to an insurance company relating to Uber’s services, Uber will share data with that insurance company for the purpose of adjusting or handling that claim.
+Data necessary to adjust or handle the claim, which may include:
+Account
+Communications between users
+Device
+Location
+Trip/order info
+Usage
+User content
+Merchants or restaurants. If you add a restaurant or merchant loyalty membership number to your user account, we share that data with the restaurant/merchant when you place an order with them.
+We also enable you to share your phone number, email and/or order info with restaurants or merchants to receive marketing communications from them.
+Account dataEmail
+Phone number
+Restaurant/merchant loyalty membership number
+Order info
+3. With Uber service providers and business partners
+These include the third parties, or categories of third parties, listed below. Where a third party is identified, please go to their linked privacy notices for information regarding their collection and use of personal data.
+Accountants, consultants, lawyers, and other professional service providers.
+Ad and marketing partners and providers, including ad and marketing publishers (such as social media platforms), ad networks and advertisers, third-party data providers, ad technology vendors, measurement and analytics providers, and other service providers. Uber uses these vendors to reach or better understand current and potential users of Uber services or of our advertising partners, and measure and improve ad effectiveness.
+Cloud storage providers.
+Customer support platform and service providers.
+Google, in connection with the use of Google Maps in Uber’s apps.
+Identity verification and risk solutions providers.
+Payment processors and facilitators, including PayPal and Hyperwallet.
+Providers of bikes and scooters that can be rented through Uber apps, such as Lime and Tembici.
+Research partners, including those performing surveys or research projects in partnership with Uber or on Uber’s behalf.
+Social media companies, including Meta and TikTok, in connection with Uber’s use of their tools in Uber’s apps and websites.
+Service providers that assist Uber to enhance the safety and security of Uber apps and services.
+Service providers that provide us with artificial intelligence and machine learning tools and services.
+Third-party vehicle suppliers, including fleet and rental partners.
+This also includes ad intermediaries, such as Criteo, Google,  Rokt, The Trade Desk,   TripleLift   and others. We share data including advertising or device identifier, hashed email address, approximate location, current trip or order information, and ad interaction data with these intermediaries to enable their services and for such other purposes as are disclosed in their privacy notices. You may opt out from ad personalization here. For more information regarding these interme</t>
+  </si>
+  <si>
+    <t>What's on Boomplay? | Boomplay Music
+Get APPGet APP
+What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player
+What’s Boomplay
+For Artists
+Advertising
+News
+Contact
+Go Web Player
+Privacy Policy
+EFFECTIVE AS OF OCTOBER 26, 2020
+Welcome to Boomplay.
+Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”)
+We are committed to protecting and respecting your privacy.
+This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. Please read the following carefully to understand our views and practices regarding your personal data and how we will treat it. By accessing or using our website, software, services, applications, products and content offered via Boomplay (collectively, the “ Services ”), you are accepting and consenting to the practices described in this Policy.
+The Types of Personal Data We Collect and Use
+We may collect and use the following information about you:
+• Information you share with us.  This is the information about you or relating to you that is voluntarily shared by you on Boomplay. Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. Information you share with us also includes information about you (including location data and log data) that others who are using Boomplay share about you. Information you share with us will remain publicly-available for so long as you or a user that has shared such information retains it.
+• Information you share from your social networks.  If you choose to link Boomplay to your social network or public forum account (including without limitation Facebook, Twitter or Google account), you may provide us or allow your social network to provide us with information from your social network or public forum accounts. This data may include your use of Boomplay on such public forums and/or social networks. For further information as to how and for what purpose the social network provider processes your data, please see their privacy policies.
+• Information on Your Device.  We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. Any automated decision-making, including profiling, based on the data automatically collected from you, will solely be used in optimizing the Services and tailoring it to your preferences.
+• Behavioral information we collect about you.  We also collect information regarding your use of the Services, e.g. your comments on Boomplay or any other content that you Posted on or through the Services, views and interactions on Boomplay. In addition, we link your contact or subscriber information with your activity on Boomplay across all your devices using your email or social media log-in details, engagement (including without limitation likes, shares, comments, repeated views) and relate users based on your behavior. Finally, we collect opt-ins and communication preferences.
+• Location data  We may collect and process information about your location, including location information based on your SIM card, IP address or mobile device location settings, and if activated on your mobile device, by use of a Global Positioning System (GPS). We may use such information to provide you with location-based services, such as features, notifications, marketing, or other content that is influenced by your location. If you do not wish to share your GPS location with us, you can switch off GPS functionality on your mobile device.
+• Metadata. When you Post content, including images, text and audio to Boomplay, you automatically upload certain metadata that is connected to the content. In essence, metadata describes other data and provides information about your content that will not always be evident to the viewer. In connection with your content the metadata can describe how, when and by whom the piece of content was collected and how that content is formatted. It further includes information such as your account name that enables other users to trace back the content to your user account. Metadata will further consist of additional data that you chose to provide with the content, e.g. any hashtags used to mark keywords to the comments.
+• Information from third parties.  We may receive information if you use any of the other websites we operate or other Services we provide. We may also receive information from third parties (such as advertising networks and analytics providers) and from other sources, including business directories and other commercially or publicly available sources.
+• Contact Information. We may collect contact information from your contact list, address book and your social network to help you and others find people you may know and enable you to link your Boomplay contact list with the contact lists on your device and/or in your account on third party services. We will ask for your consent to access your contact list and address book before doing so. You may at any time allow or disallow us to access your contact list and address book by changing your settings.
+• Third-party Services. If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list.
+Cookies
+We use cookies and other similar technologies (e.g. web beacons, Flash cookies, App cache, etc.) (“ Cookies ”) to enhance your experience using Boomplay. Cookies are small files which, when placed on your device, enable us to provide certain features and functionality.
+We use the following Cookies:
+• Strictly necessary Cookies.  These are Cookies that are required for the operation of Boomplay and to keep your account and data safe and secure. They include, for example, Cookies that enable you to log into secure areas of Boomplay.
+• Analytical/performance Cookies.  They allow us to recognize and count the number of visitors and to see how visitors move around Boomplay when they are using it. This helps us to improve the way Boomplay works, for example, by ensuring that users are able to find what they are looking for easily.
+• Functionality Cookies.  These are used to recognize you when you return to Boomplay. This enables us to personalize our content for you, greet you by name and remember your preferences (for example, your choice of language or region).
+• Targeting Cookies.  These Cookies record your visit to Boomplay, the pages you have visited and the links you have followed. We will use this information to make Boomplay and the advertising displayed on it more relevant to your interests. We may also share this information with third parties for this purpose.
+If for any reason you wish to not take advantage of Cookies, you may disable Cookies by changing the settings on your browser. However, if you do so, this will affect your enjoyment of Boomplay and we will no longer be able to offer to you personalized content. Unless you opt out of Cookies, we will assume you consent to the use of Cookies.
+"Do not track" signals are preferences that users can set on their web browser to limit how their activity is tracked across third-party websites or online services. Boomplay does not respond to "do not track" signals in your web browser.
+Analytics information
+On Boomplay, we use third-party analytics tools to help us measure traffic and usage trends for the Services. Traffic refers to the different data flows surrounding activities of the users on the Services. These tools, for example, collect information sent by your device or our Services, including the pages you visit, add-ons, and other information that assists us in improving the Service. The information will be used to report and evaluate your activities and patterns as a user of Boomplay to provide services in accordance with these activities.
+How We Use Your Personal Data
+We will use the information we collect about you in the following ways:
+• To administer Boomplay (i.e. to provide our Services to you) and for internal operations, including troubleshooting, data analysis, testing, research, statistical and survey purposes (i.e. to guarantee Boomplay’s stability and security) and to solicit your feedback;
+• To allow you to participate in interactive features of Boomplay, when you choose to do so;
+• To personalize the content you receive and provide you with tailored content that will be of interest to you;
+• To improve and develop Boomplay and conduct product development;
+• To measure and understand the effectiveness of our recommendation and service we offer to you and others;
+• To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings;
+• To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them;
+• To allow other users to identify you as a user of the Service and to support the socializing function of the Services;
+• To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users;
+• To make your information available to other users in accordance with the privacy settings you chose for the respective information;
+• To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow;
+• To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services;
+• To enable our messenger service to function;
+• To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay;
+• To notify you about changes to our Services;
+• To communicate with you;
+• To provide you with user support;
+• To enforce our terms, conditions and policies;
+• For any other specific reason provided to you at the time we collect your information.
+It is in our legitimate interest to promote the Services, and we may use information that you give to us, such as content that you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services.
+How We Share Your Personal Data
+We may share your personal data with selected third parties in or outside your country, including without limitation:
+• Our business partners so that we can make you special offers via Boomplay;
+• With respect to on-screen ads, advertisers and advertising networks that require the data to select and serve advertisements to you and others. Without your consent, we will not share your contact details to our business partners to avoid direct contact from them, but we may share other information so that they can make you offers tailored to your requirements;
+• Cloud storage providers to store the information you provide and for disaster recovery services, as well as for the performance of any contract we have entered into with you;
+• Analytics and search engine providers that assist us in the improvement and optimization of Boomplay.
+• IT service providers that help develop, maintain, secure and optimize the Boomplay framework;
+• Our data center and the servers of our host providers.
+We may share your information with any member or affiliate of our group, which includes our subsidiaries, our ultimate holding company and its subsidiaries, and companies that we control, are controlled by or under common control, and our service providers and strategic business partners, and their respective subsidiaries, in each case in or outside your country, for the purposes set out above (“ How We Use Your Personal Data ”).
+We may share your information with law enforcement agencies, public or tax authorities or other organizations if legally required to do so, or if we have a good faith belief that such use is reasonably necessary to:
+• Comply with a legal obligation, process or request (including tax and related reporting requirements);
+• Enforce our Terms of Service and other agreements, policies, and standards, including investigation of any potential violation thereof;
+• Detect, prevent or otherwise address security, fraud or technical issues;
+• Protect the rights, property or safety of us, our users, a third party or the public as required or permitted by law (including exchanging information with other companies and organizations for the purposes of fraud protection and credit risk reduction).
+We may also disclose your information to third parties:
+• In the event that we sell or buy any business or assets, in which case we may disclose your data to the prospective seller or buyer of such business or assets; or
+• If we sell, buy, merge or partner with other companies or businesses, or sell some or all of our assets. In such transactions, user information may be among the transferred assets. In any such cases, the third party company or business will adhere to the provisions of this Privacy Policy and where it will result in a change in any of the provisions herein, such changes will be communicated to you and you will be given the chance to consent or opt out at your discretion.
+The Security of Your Personal Data
+We take steps to ensure that your information is treated securely and in accordance with this policy. Unfortunately, the transmission of information via the internet is not completely secure. Although we will do our best to protect your information, for example, by encryption, we cannot guarantee the security of your information transmitted through Boomplay; thus, any transmission is at your own risk.
+We have put in place appropriate technical and organizational measures to ensure a level of security appropriate to the risk of varying likelihood and severity for the rights and freedoms of you and other users. We maintain these technical and organizational measures and will amend them from time to time to improve the overall security of our systems.
+We will, from time to time, include links to and from the websites of our partner networks, advertisers and affiliates. If you follow a link to any of these websites, please note that these websites have their own privacy policies and that we do not accept any responsibility or liability for these policies. Please check these policies before you submit any information to these websites.
+Data Retention
+We use the following criteria to determine the period for which we will keep your information:
+• Our contractual obligations and rights in relation to the information involved;
+• Legal obligation(s) under applicable law(s) and regulations to retain data for a certain period of time;
+• Statute of limitations under applicable law(s);
+• Our legitimate business purposes;
+• Disputes or potential disputes.
+After you have terminated your use of our Services, we can store your information in an aggregated and anonymized format. Notwithstanding the foregoing, we can also retain any personal information as reasonably necessary to comply with our legal obligations, allow us to resolve and litigate disputes, and to enforce our agreements.
+Information Relating to Children
+The Services are not offered to children whose age makes it illegal to process their personal data or requires parental consent for the processing of their personal data under any applicable laws.
+We do not knowingly collect personal data from children under 13 years or under the applicable age limit in your jurisdiction (the “Age Limit”). If you are under the Age Limit, please do not use the Services, and do not provide any personal data to us.
+If you are a parent of a child under the Age Limit and become aware that your child has provided personal data to us, please contact us at privacy.boomplay@transsnet.com to delete such data.
+If we are aware that we have collected the personal data of a child under the Age Limit, we will take reasonable steps to delete the personal data.
+Complaints
+In the event that you wish to make a complaint about how we process your personal data, please contact us in the first instance at privacy.boomplay@transsnet.com and we will endeavor to deal with your request as soon as possible. This is without prejudice to your right to launch a claim with your data protection authority or follow the dispute resolution process provided in the Terms of Service.
+Changes
+We may amend and update this Policy from time to time. You can access the latest version of this Policy on Boomplay. It is your responsibility to remain informed of any changes. Your continued access to or use of the Services after the date of the updated Policy constitutes your acceptance of the updated Policy. If you do not agree to the updated Policy, you must stop accessing or using the Services.
+Contact
+Questions, comments and requests regarding this policy are welcomed and should be addressed to privacy.boomplay@transsnet.com.
+Your rights
+You have the right to make a request to access and delete the personal data we hold about you, to rectify any personal data held about you that is inaccurate, the right to data portability and the right to request the suspension of the processing of your personal data. You can exercise your rights by contacting us at privacy.boomplay@transsnet.com.
+Explore
+Artists
+Trending Songs
+New Songs
+Charts
+Videos
+Podcast
+Buzz
+For Users
+Download
+Help Center
+Go Premuim
+Wordpress
+For Artists and Vendors
+Boomplay for Artists
+Get Verified
+Artists FAQ
+Artists Distributors
+Vendors Login
+Report Content Issue
+Company
+About
+Contact
+Advertising
+News
+Visual Identity
+© 2023 Boomplay All rights reserved. Privacy PolicyEULAPodcast T&amp;CSitemap
+Explore
+ArtistsTrending SongsNew SongsChartsVideosPodcastBuzz
+For Users
+DownloadHelp CenterGo PremuimWordpress
+For Artists and Vendors
+Boomplay for ArtistsGet VerifiedArtists FAQArtists DistributorsVendors LoginReport Content Issue
+Company
+AboutContactAdvertisingNewsVisual Identity
+© 2023 Boomplay All rights reserved. Privacy PolicyEULAPodcast T&amp;CSitemap</t>
+  </si>
+  <si>
+    <t>https://policies.google.com/privacy?hl=en&amp;gl=us</t>
+  </si>
+  <si>
+    <t>Meta Privacy Policy - How Meta collects and uses user data
+Privacy Policy
+Search
+Privacy topics
+More privacy resources
+Privacy Policy
+What is the Privacy Policy and what does it cover?
+What information do we collect?
+How do we use your information?
+How is your information shared on Meta Products or with integrated partners?
+How do we share information with third parties?
+How do the Meta Companies work together?
+How can you manage or delete your information and exercise your rights?
+How long do we keep your information?
+How do we transfer information?
+How do we respond to legal requests, comply with applicable law and prevent harm?
+How will you know the Policy has changed?
+Privacy notice for United States residents
+How to contact Meta with questions
+Why and how we process your information
+Other policies and articles
+Settings
+Privacy Policy
+What is the Privacy Policy and what does it cover?
+Effective June 16, 2025 | View printable version | See previous versions
+Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights.
+Highlights
+We at Meta want you to understand what information we collect, and how we use and share it. That’s why we encourage you to read our Privacy Policy. This helps you use Meta Products in the way that’s right for you.
+In the Privacy Policy, we explain how we collect, use, share, retain and transfer information. We also let you know your rights. Each section of this Policy includes helpful examples and simpler language to make our practices easier to understand. We’ve also added links to resources where you can learn more about the privacy topics that interest you.
+It's important to us that you know how to control your privacy, so we also show you where you can manage your information in the settings of the Meta Products you use. You can update these settings to shape your experience.
+Read the full Policy below.
+What Products does this Policy cover?
+Learn more in Privacy Center about managing your privacy
+What information do we collect?
+Highlights
+The information we collect and process about you depends on how you use our Products. For example, we collect different information if you sell furniture on Marketplace than if you post a reel on Instagram. When you use our Products, we collect some information about you even if you don't have an account.
+Here's the information we collect:
+Your activity and information you provide
+Friends, followers and other connections
+App, browser and device information
+Information from partners, vendors and other third parties
+What if you don’t let us collect certain information?
+Some information is required for our Products to work. Other information is optional, but without it, the quality of your experience might be affected.
+Learn more
+What if the information we collect doesn’t identify individuals?
+In some cases information is de-identified, aggregated, or anonymized by third parties so that it no longer identifies individuals before it’s made available to us. We use this information as described below without trying to re-identify individuals.
+Take control
+Manage the information we collect about you
+Privacy Center
+How do we use your information?
+Highlights
+We use information we collect to provide a personalized experience to you, including ads, along with the other purposes we explain in detail below.
+For some of these purposes, we use information across our Products and across your devices. The information we use for these purposes is automatically processed by our systems. But in some cases, we also use manual review to access and review your information.
+To use less information that’s connected to individual users, in some cases we de-identify or aggregate information or anonymize it so that it no longer identifies you. We use this information in the same ways we use your information as described in this section.
+Here are the ways we use your information:
+To provide, personalize and improve our Products
+We use information we have to provide and improve our Products. This includes personalizing features, content and recommendations, such as your Facebook Feed, Instagram Feed, Stories and ads. We use information with special protections you choose to provide for these purposes, but not to show you ads.
+Read more about how we use information to provide, personalize and improve our Products:
+How we show ads and other sponsored or commercial content
+How we use information to improve our Products
+How we use location-related information
+To promote safety, security and integrity
+We use information we collect to help protect people from harm and provide safe, secure Products.
+Learn more
+To provide measurement, analytics and business services
+Lots of people rely on our Products to run or promote their businesses or share content. We help them measure how well their ads and other content, products and services are working.
+Learn more
+To communicate with you
+We communicate with you using information you've given us, like contact information you've entered on your profile.
+Learn more
+To research and innovate for social good
+We use information we have, information from researchers and datasets from publicly available sources, professional groups and non-profit groups to conduct and support research.
+Learn more
+More in the Privacy Policy
+Why and how we process your information
+How is your information shared on Meta Products or with integrated partners?
+Highlights
+On Meta Products
+Learn more about the different cases when your information can be shared on our Products:
+People and accounts you share and communicate with
+Content others share or reshare about you
+Public content
+With integrated partners
+You can choose to connect with integrated partners who use our Products. If you do, these integrated partners receive information about you and your activity.
+These integrated partners can always access information that’s public on our Products. Learn more about other information they receive and how they handle your information:
+When you use an integrated partner’s product or service
+When you interact with someone else’s content on an integrated partner’s product or service
+How integrated partners handle your information
+Take control
+Learn more about audiences
+Privacy Center
+Manage apps and websites
+How do we share information with third parties?
+Highlights
+We don't sell any of your information to anyone, and we never will. We also require partners and other third parties to follow rules about how they can and cannot use and disclose the information we provide.
+Here’s more detail about who we share information with:
+Partners
+Advertisers and Audience Network publishers
+Partners who use our analytics services
+Partners who offer goods or services on our Products and commerce services platforms
+Integrated partners
+Vendors
+Measurement vendors
+Marketing vendors
+Service providers
+Service providers
+Third parties
+External researchers
+AI integrations
+Other third parties
+We also share information with other third parties in response to legal requests, to comply with applicable law or to prevent harm. Read the Policy.
+And if we sell or transfer all or part of our business to someone else, in some cases we’ll give the new owner your information as part of that transaction, but only as the law allows.
+How do the Meta Companies work together?
+Highlights
+We are part of the Meta Companies that provide Meta Company Products. Meta Company Products include all the Meta Products covered by this Policy, plus other products like WhatsApp and more.
+We share information we collect, infrastructure, systems and technology with the other Meta Companies. Learn more about how we transfer information to other countries.
+We also process information that we receive about you from other Meta Companies, according to their terms and policies and as permitted by applicable law. In some cases, Meta acts as a service provider for other Meta Companies. We act on their behalf and in accordance with their instructions and terms.
+Why we share across the Meta Companies
+Meta Products share information with other Meta Companies:
+To promote safety, security and integrity and comply with applicable laws
+To personalize offers, ads and other sponsored or commercial content
+To develop and provide features and integrations
+To understand how people use and interact with Meta Company Products
+See some examples of why we share.
+More resources
+Review the privacy policies of the other Meta Companies
+Facebook Help Center
+How can you manage or delete your information and exercise your rights?
+Highlights
+We offer you a variety of tools to view, manage, download and delete your information below. You can also manage your information by visiting the settings of the Products you use. You may also have other privacy rights under applicable laws.
+To exercise your rights, visit our Help Centers, your settings for Facebook and Instagram and your device-based settings.
+Take a privacy checkup
+Take a privacy checkup
+Be guided through Facebook privacy settings
+View and manage your information
+Access your information
+Off-Meta activity
+Ad preferences
+Manage your data
+Port, download or delete your information
+Port your information
+Download your information
+Delete your information or account
+You can learn more about how privacy works on Facebook and on Instagram, and in the Facebook Help Center. If you have questions about this policy, you can contact us as described below. In some countries, you may also be able to contact the Data Protection Officer for Meta Platforms, Inc., and depending on your jurisdiction, you may also contact your local Data Protection Authority (“DPA”) directly.
+How long do we keep your information?
+Highlights
+We keep information as long as we need it to provide our Products, comply with legal obligations or protect our or other’s interests. We decide how long we need information on a case-by-case basis. Here’s what we consider when we decide:
+If we need it to operate or provide our Products. For example, we need to keep some of your information to maintain your account. Learn more.
+The feature we use it for, and how that feature works. For example, messages sent using Messenger’s vanish mode are retained for less time than regular messages. Learn more.
+How long we need to retain the information to comply with certain legal obligations. See some examples.
+If we need it for other legitimate purposes, such as to prevent harm; investigate possible violations of our terms or policies; promote safety, security and integrity; or protect ourselves, including our rights, property or products
+In some instances and for specific reasons, we’ll keep information for an extended period of time. Read our Policy about when we may preserve your information.
+How do we transfer information?
+Highlights
+Why is information transferred to other countries?
+Where is information transferred?
+How do we safeguard your information?
+How do we respond to legal requests, comply with applicable law and prevent harm?
+Highlights
+We access, preserve, use and share your information:
+In response to legal requests, like search warrants, court orders, production orders or subpoenas. These requests come from third parties such as civil litigants, law enforcement and other government authorities. Learn more about when we respond to legal requests.
+In accordance with applicable law
+To promote the safety, security and integrity of Meta Products, users, employees, property and the public. Learn more.
+We may access or preserve your information for an extended amount of time. Learn more.
+How will you know the Policy has changed?
+We'll notify you before we make material changes to this Policy. You’ll have the opportunity to review the revised Policy before you choose to continue using our Products.
+Privacy notice for United States residents
+You can learn more about the consumer privacy rights that may be available to you by reviewing the United States Regional Privacy Notice.
+How to contact Meta with questions
+You can learn more about how privacy works on Facebook and on Instagram and in the Facebook Help Center. If you have questions about this Policy or have questions, complaints or requests regarding your information, you can contact us as described below.
+You can contact us online or by mail at:
+Meta Platforms, Inc.
+ATTN: Privacy Operations
+1601 Willow Road
+Menlo Park, CA 94025
+Why and how we process your information
+The categories of information we use, and why and how information is processed, are set out below:
+Why and how we process your information
+Information categories we use (see 'What Information do we collect?' for more information on each information category)
+The actual information we use depends on your factual circumstances, but could include any of the following:
+Personalizing the Meta Products (other than ads, see below): Our systems automatically process information we collect and store associated with you and others to assess and understand your interests and your preferences and provide you personalized experiences across the Meta Products in accordance with our terms. This is how we:
+Personalize features and content (such as your Facebook Feed, Instagram Feed and Stories);
+Make suggestions for you (such as people you may know, groups or events that you may be interested in or topics that you may want to follow) on and off our products.
+Learn more about how we use information about you to personalize your experience on and across Meta Products and how we choose the ads that you see.
+Your activity and information you provide:
+Content you create, like posts, comments or audio
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+Metadata about content
+Types of content you view or interact with, and how you interact with it
+Apps and features you use, and what actions you take in them
+Purchases or other transactions you make
+Hashtags you use
+The time, frequency and duration of your activities on our Products
+Friends, followers and other connections
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users’
+Device signals
+Information you’ve shared through your device settings (like GPS location)
+Location-related information
+Information about the network you connect your device to
+Reports about our products’ performance on your device
+Information from cookies and similar technologies
+Information from partners, vendors and third parties
+Providing ads on the Meta Company Products:
+Our ads system automatically processes information that we’ve collected and stored associated with you. Our ads system uses this information to understand your interests and your preferences and personalize your ads across the Meta Company Products.
+Our ads system prioritizes what ad to show you based on what audience advertisers want to reach. Then we match the ad to people who might be interested. Learn more about how our ads system works
+Your activity and information you provide:
+Age
+The gender you provide
+Information about ads we show you and how you engage with those ads
+App, browser and device information:
+Location information
+Device characteristics and device software
+If you decide to add a WhatsApp account to an Accounts Center with other accounts on Meta Company Products:
+To associate your accounts on Meta Company Products with your WhatsApp account in the same Accounts Center and share your information with WhatsApp.
+Note: the list below is about information from Meta. For information that WhatsApp shares with Meta see the WhatsApp Help Center article.
+Your activity and information you provide
+Friends, followers and other connections
+App, browser and device information
+Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to:
+Create and maintain your account and profile,
+Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information,
+Facilitate the sharing of content and status,
+Provide and curate features,
+Provide messaging services, the ability to make voice and video calls and connect with others,
+Provide advertising products,
+Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide,
+Undertake analytics, and
+Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences.
+We also use information to develop, research and test improvements to our Products. We use information we have to:
+See if a product is working correctly,
+Troubleshoot and fix it when it’s not,
+Test out new products and features to see if they work,
+Get feedback on our ideas for products or features, and
+Conduct surveys and other research about what you like about our Products and brands and what we can do better.
+Your activity and information you provide:
+Content you create, like posts, comments or audio
+Your public profile information (including your name, username and profile picture)
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+Messages you send and receive, including their content, subject to applicable law
+Metadata about content and messages, subject to applicable law
+Types of content you view or interact with, and how you interact with it
+Apps and features you use, and what actions you take in them
+Purchases or other transactions you make, including truncated credit card information
+Hashtags you use
+The time, frequency and duration of your activities on our Products
+Your photo or video selfie if you provide it when you contact us for account support
+Friends, followers and other connections
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users’
+Device signals
+Information you’ve shared through your device settings
+Location-related information
+Information about the network you connect your device to, including your IP address
+Information from cookies and similar technologies
+Information from partners, vendors and third parties
+Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. We process information we have associated with you and apply automated processing techniques and, in some instances, conduct manual (human) review to:
+Verify accounts and activity,
+Find and address violations of our terms or policies. In some cases, the decisions we make about violations are reviewed by the Oversight Board,
+Investigate suspicious activity,
+Detect, prevent and combat harmful or unlawful behavior, such as to review and, in some cases, remove content reported to us,
+Identify and combat disparities and racial bias against historically marginalized communities,
+Protect the life, physical or mental health, well-being or integrity of our users or others,
+Detect and prevent spam, other security matters and other bad experiences,
+Detect and stop threats to our personnel and property, and
+Maintain the integrity of our Products.
+For more information on safety, integrity and security generally on Meta Products, visit the Facebook Security Help Center and Instagram Security Tips.
+Your activity and information you provide::
+Content you create, like posts, comments or audio
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+Messages you send and receive, including their content, subject to applicable law
+Metadata about content and messages, subject to applicable law
+Types of content you view or interact with, and how you interact with it
+Apps and features you use, and what actions you take in them
+Purchases or other transactions you make, including truncated credit card information
+Hashtags you use
+The time, frequency and duration of your activities on our Products
+Your photo or video selfie if you provide it when you contact us for account support
+Friends, followers and other connections
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users’
+Device signals
+Information you’ve shared through your device settings
+Location-related information
+Information about the network you connect your device to, including your IP address
+Information from cookies and similar technologies
+Information from partners, vendors and third parties
+To communicate with you: We use information you’ve given us (like contact information on your profile) to send you a communication, like an e-mail or in-product notice, for example:
+We’ll contact you via email or in-product notifications in relation to the Meta Products, product-related issues, research or to let you know about our terms and policies.
+We also use contact information like your email address to respond when you contact us.
+Your activity and information you provide:
+Contact information on your profile and your communications with us
+Content you create, like posts, comments or audio
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users’
+Device signals
+Information you’ve shared through your device settings
+Location-related information
+Information about the network you connect your device to, including your IP address
+Information from cookies and similar technologies.
+Transferring, storing or processing your information across borders, including from and to the United States and other countries: We share information we collect globally, both internally across our offices and data centers and externally with our partners, third parties and service providers. Because Meta is global, with users, partners, vendors and employees around the world, transfers are necessary:
+To operate and provide the services described in the terms that apply to the Meta Product(s) you are using. This includes allowing you to share information and connect with your family and friends around the globe; and
+To fix, analyze and improve our Products.
+For more information, see the "How do we transfer information?" section of the Meta Privacy Policy.
+Your activity and information you provide:
+Content you create, like posts, comments or audio
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+Metadata about content and messages, subject to applicable law
+Types of content you view or interact with, and how you interact with it
+Apps and features you use, and what actions you take in them
+Purchases or other transactions you make, including truncated credit card information
+Hashtags you use
+The time, frequency and duration of your activities on our Products
+Your photo or video selfie if you provide it when you contact us for account support
+Friends, followers and other connections
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users’
+Device signals
+Information you’ve shared through your device settings
+Location-related information
+Information about the network you connect your device to, including your IP address
+Information from cookies and similar technologies
+Information from partners, vendors and third parties
+Processing information subject to special protections under applicable laws that you provide so we can share it with those you choose, to provide, personalize and improve our Products and to undertake analytics.  We’ll collect, store, publish and apply automated, or sometimes manual (human), processing for these purposes.
+Your activity and information you provide:
+Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent
+Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. We receive this information whether or not you’re logged in or have an account on our Products. See the Cookies Policy for more information.
+Your activity and information you provide:
+Information and content you provide, such as your name or email address
+Information from partners, vendors and third parties
+Sharing your contact, profile or other information with third parties upon your request: The type of third party and categories of information shared depend on the circumstances of what you ask us to share. For example:
+We share your email (or other contact information) or other information you might choose when you direct us to share it with an advertiser so they can contact you with additional information about a promoted product, and
+If you choose to integrate other apps, games or websites with Meta Products and log in, we’ll share your information with the app, game or website to log you in.
+Your activity and information you provide:
+Information such as your contact or profile information
+Content you create, like posts or comments
+Providing measurement, analytics and business services:
+Our systems automatically, as well as with some manual (human) processing, process information we have collected and stored about you and others. We use this information to:
+Provide insights and measurement reports to businesses, advertisers and other partners to help them measure the effectiveness and distribution of their or their clients’ ads, content and services, to understand the kinds of people who are seeing their content and ads, and how their content and ads are performing on and off Meta Products, and
+Provide aggregated user analytics and insights reports that help users, businesses, advertisers and other partners better understand the audiences with whom they may want to connect, as well as the types of people who use their services and how people interact with their content, websites, apps and services.
+Your activity and information you provide:
+Content you create, like posts, comments or audio
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+Types of content you view or interact with, and how you interact with it
+Apps and features you use, and what actions you take in them
+Purchases or other transactions you make
+Hashtags you use
+The time, frequency and duration of your activities on our Products
+Friends, followers and other connections
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users
+Device signals
+Information you’ve shared through your device settings
+Location-related information
+Information about the network you connect your device to, including your IP address
+Information from cookies and similar technologies
+Sharing of information across the Meta Companies:
+To provide a seamless, consistent and richer, innovative experience across the Meta Company Products to enable cross app interactions, sharing, viewing and engaging with content, including posts and videos.
+Your activity and information you provide:
+Content you create, like posts, comments or audio
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+Metadata about content
+Types of content you view or interact with, and how you interact with it
+Apps and features you use, and what actions you take in them
+Purchases or other transactions you make
+Hashtags you use
+The time, frequency and duration of your activities on our Products
+Friends, followers and other connections
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users'
+Device signals
+Information you’ve shared through your device settings
+Location-related information
+Information about the network you connect your device to, including your IP address
+Information from cookies and similar technologies
+Business intelligence and analytics:
+To understand, in aggregate, your usage of and across our Products, to accurately count people and businesses; and
+To validate metrics directly related to these, in order to inform and improve product direction and development and to adhere to (shareholder/earning) reporting obligations.
+Your activity and information you provide:
+Content you create, like posts, comments or audio
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+Metadata about content and messages, subject to applicable law
+Types of content you view or interact with, and how you interact with it
+Apps and features you use, and what actions you take in them
+Purchases or other transactions you make
+Hashtags you use
+The time, frequency and duration of your activities on our Products
+Friends, followers and other connections
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users'
+Device signals
+Information you’ve shared through your device settings
+Location-related information
+Information about the network you connect your device to, including your IP address
+Information from cookies and similar technologies
+Information from partners, vendors and third parties
+Identifying you as a Meta Product user and personalizing the ads we show you through Meta Audience Network when you visit other apps:
+When we show you ads through Meta Audience Network when you visit other apps, our systems automatically process the information we have collected and stored about you and others to identify you as a Meta Product user and tailor the ads you see.
+Your activity and information you provide:
+Information you provide
+Content you create, like posts, comments or audio
+Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features
+Metadata about content
+Types of content you view or interact with, and how you interact with it
+Apps and features you use, and what actions you take in them
+Purchases or other transactions you make
+Hashtags you use
+The time, frequency and duration of your activities on our Products
+Friends, followers and other connections
+App, browser and device information:
+Device characteristics and device software
+What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)
+Identifiers that tell your device apart from other users'
+Device signals
+Information you’ve shared through your device settings
+Information about the network you connect your device to, including your IP address
+Information from cookies and s</t>
+  </si>
+  <si>
+    <t>WhatsApp Business App Privacy Policy
+Skip to contentHome
+Features
+Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI
+Privacy
+Help Center
+Blog
+For Business
+Download
+Download
+Terms &amp; Privacy Policy2025 © WhatsApp LLC
+AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어
+FeaturesMessage privatelyEnd-to-end encryption and privacy controls.
+Stay connectedMessage and call for free* around the world.
+Connect in groupsGroup messaging made easy.
+Express yourselfSay it with stickers, voice, GIFs and more.
+Secure by designLayers of protection to help you stay safe.
+Share your everydayShare photos, videos, voice notes on Status.
+Follow channelsStay updated on topics you care about.
+Do More with
+Meta AIGet help with anything.
+Privacy
+Help Center
+Blog
+For Business
+Apps
+Log inDownload
+WhatsApp Business App Privacy Policy
+Effective July 14, 2025
+Table of Contents
+WhatsApp Legal Info
+Scope of This WhatsApp Business App Privacy Policy
+Information We Collect
+How We Use Information
+Information You and We Share
+How We Work With Other Meta Companies
+Region Specific Information
+Assignment, Change Of Control, And Transfer
+Managing Your Information
+Law, Our Rights, And Protection
+Our Global Operations
+Updates to Our Privacy Policy
+Contact Us
+If you are located in the UK, WhatsApp LLC provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy.
+If you are located in the European Region, WhatsApp Ireland Ltd. provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy.
+WhatsApp Legal Info
+If you are located in the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Business App to you under this Terms of Service and this WhatsApp Business App Privacy Policy. WhatsApp LLC is also the data controller for any processing of personal information about you and you can contact us using the details in the section Contact Us below.
+If you are located in the European Region, WhatsApp Ireland Limited ("WhatsApp," "our," "we," or "us") provides our Business App to you under this Terms of Service and this  WhatsApp Business App Privacy Policy. WhatsApp Ireland Limited is also the data controller for the processing of any personal information about you and you can contact us using the details in the section Contact Us below.
+Scope of This WhatsApp Business App Privacy Policy
+The WhatsApp Business App provides similar features and functionality to the WhatsApp Messenger App (“Main App Functionality”), but provides additional features and functionality tailored for business needs (“Business Functions”). Business Functions include things like catalog, and greeting and away messages. While the WhatsApp Business App includes various features available in the WhatsApp Messenger App, some features may not be available; and not all Business Functions are available everywhere. Business Functions may be offered by WhatsApp, third parties and/or Meta, via integrations into our Business App, and may be subject to the third parties’ own terms of service and privacy policies.
+This WhatsApp Business App Privacy Policy (“Business App Privacy Policy”) explains WhatsApp’s data practices with respect to the Business Functions, and applies only to the extent information relating to users of the WhatsApp Business App would be considered personal data and is processed by WhatsApp as a controller, each under applicable law. Users should refer to the WhatsApp Privacy Policy, incorporated herein by reference, to understand how their information is processed in Main App Functionality. Learn more about Business Functions and the Main App Functionality available on WhatsApp Business App here.
+Please also read the WhatsApp Business Terms of Service ("Business Terms"), which describe the terms under which you use and we provide the WhatsApp Business App.
+Information We Collect
+In addition to the information described in the applicable WhatsApp Privacy Policy, we collect the following information.
+Information You Provide
+Your Business Account Information.
+In addition to your phone number, you must provide basic information about your business to create a WhatsApp business account, including your business name and business category. If you don’t provide us with this information, you will not be able to create an account to use our WhatsApp Business App. You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience.
+Automatically Collected Information
+Usage and Log Information.
+We collect information about your use of the Business Functions. For example, we collect information about your business profile settings; how you use Business Functions like catalogs, labels and quick replies; purchases and transactions with your business; and metrics related to how customers interact with your business.
+Information Received From Others
+User Reports, Feedback, Preferences and Blocks.
+Users can report, submit feedback, set communication preferences, or block businesses on WhatsApp, which we associate with the business that is the subject of the report, feedback, preference, or block.
+How We Use Information
+We use the information we collect for the same purposes described in the WhatsApp Privacy Policy, and also to operate, provide, improve, understand, customize, support, and market our WhatsApp Business App and Business Functions.
+Our WhatsApp Business App.
+We use the information we have to operate and provide our WhatsApp Business App and Business Functions, including providing you with business support; providing onboarding tools; providing message creation and delivery tools; providing you new and premium Business Functions (some of which may be offered by third parties and/or Meta); and improving, fixing, and customizing our WhatsApp Business App. We also use information we have to understand how you use our WhatsApp Business App; evaluate and improve our WhatsApp Business App; research, develop, and test new services and features; and conduct troubleshooting activities. We also use your information to respond to you when you contact us.
+Safety, Security and Integrity.
+In addition to the safety, security and integrity purposes described in the WhatsApp Privacy Policy, we also use the information we have to maintain safety, security and integrity on our WhatsApp Business App, for example: to create quality and integrity inferences about businesses; secure WhatsApp systems and WhatsApp Business App users’ accounts; fight threats, abuse, or infringement activities; promote safety, security, and integrity on the WhatsApp Business App; and to ensure compliance with our terms and policies.
+Information You and We Share
+You and we share information as described in the WhatsApp Privacy Policy, plus additional sharing relevant to the Business Functions.
+Information About Your Business Profile.
+Business profile information is publicly available, including your business name, phone number, hours of operation, business category, address, email address, website(s), description, and Facebook and Instagram accounts (if added). We may provide ways for our users to find or reach you, like our Business Search or other search functionality.
+Other Integrations.
+We allow you to connect the WhatsApp Business App to products and services offered by third parties and/or Meta. These can include for example: cloud storage and hosting services; customer relationship management tools; ad and message creation, delivery and management services; business analytics services; and AI tools. When you use these products or services, their own terms and privacy policies will govern your use of those services and products.
+How We Work With Other Meta Companies
+Review the WhatsApp Privacy Policy to understand how we work with the other Meta Companies for the WhatsApp Business App.
+Region Specific Information
+Additional information for users located in the US
+You can learn more about the consumer privacy rights that may be available to you, by reviewing the WhatsApp Business App United States Regional Privacy Notice here.
+Assignment, Change Of Control, And Transfer
+In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws.
+Managing And Retaining Your Information
+The WhatsApp Business App follows the same information management, retention and deletion practices described in the WhatsApp Privacy Policy.
+Law, Our Rights, And Protection
+Review the WhatsApp Privacy Policy to understand how we access, preserve, and share your information in response to legal obligations.
+Our Global Operations
+Review the WhatsApp Privacy Policy to understand how our global operations impact how your information is processed.
+Updates to Our Privacy Policy
+We may amend or update our Business App Privacy Policy. We will provide you notice of amendments to this Business App Privacy Policy, as appropriate, and update the “Effective Date” at the top of this Business App Privacy Policy. Please review our Business App Privacy Policy from time to time.
+Contact Us
+If you have questions or issues about our Privacy Policy, please contact us.
+WhatsApp LLC
+Privacy Policy
+1601 Willow Road
+Menlo Park, California 94025
+United States of America
+Download
+Download
+What we do
+FeaturesBlogSecurityFor Business
+Who we are
+About usCareersBrand CenterPrivacy
+Use WhatsApp
+AndroidiPhoneMac/PCWhatsApp Web
+Need help?
+Contact UsHelp CenterAppsSecurity Advisories
+Download
+2025 © WhatsApp LLC
+Terms &amp; Privacy PolicySitemap
+AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어</t>
+  </si>
+  <si>
+    <t>Privacy Policy
+Skip to contentHome
+Features
+Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI
+Privacy
+Help Center
+Blog
+For Business
+Download
+Download
+Terms &amp; Privacy Policy2025 © WhatsApp LLC
+Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）
+FeaturesMessage privatelyEnd-to-end encryption and privacy controls.
+Stay connectedMessage and call for free* around the world.
+Connect in groupsGroup messaging made easy.
+Express yourselfSay it with stickers, voice, GIFs and more.
+Secure by designLayers of protection to help you stay safe.
+Share your everydayShare photos, videos, voice notes on Status.
+Follow channelsStay updated on topics you care about.
+Do More with
+Meta AIGet help with anything.
+Privacy
+Help Center
+Blog
+For Business
+Apps
+Log inDownload
+WhatsApp Privacy Policy
+Effective January 4, 2021archived versions
+If you live in the European Region, WhatsApp Ireland Limited provides the Services to you under this Terms of Service and Privacy Policy.
+If you live in the UK, WhatsApp LLC provides the Services to you under this Terms of Service  and Privacy Policy.
+WhatsApp Legal Info
+If you live outside the European Region or the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Services to you under this Terms of Service and Privacy Policy.
+Our Privacy Policy ("Privacy Policy") helps explain our data practices, including the information we process to provide our Services.
+For example, our Privacy Policy talks about what information we collect and how this affects you. It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services.
+We are one of the Meta Companies. You can learn more further below in this Privacy Policy about the ways in which we share information across this family of companies.
+This Privacy Policy applies to all of our Services unless specified otherwise.
+Please also read WhatsApp’s Terms of Service ("Terms"), which describe the terms under which you use and we provide our Services.
+Back to top
+Key Updates
+Respect for your privacy is coded into our DNA. Since we started WhatsApp, we’ve built our services with a set of strong privacy principles in mind. In our updated Terms of Service and Privacy Policy you’ll find:
+Additional Information On How We Handle Your Data. Our updated Terms and Privacy Policy provide more information on how we process your data, and our commitment to privacy. For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information.
+Better Communication With Businesses. Many businesses rely on WhatsApp to communicate with their customers and clients. We work with businesses that use Meta or third parties to help store and better manage their communications with you on WhatsApp.
+Making It Easier To Connect. As part of the Meta Companies, WhatsApp partners with Meta to offer experiences and integrations across Meta’s family of apps and products.
+Back to top
+Information We Collect
+WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services.
+The types of information we receive and collect depend on how you use our Services. We require certain information to deliver our Services and without this we will not be able to provide our Services to you. For example, you must provide your mobile phone number to create an account to use our Services.
+Our Services have optional features which, if used by you, require us to collect additional information to provide such features. You will be notified of such collection, as appropriate. If you choose not to provide the information needed to use a feature, you will be unable to use the feature. For example, you cannot share your location with your contacts if you do not permit us to collect your location data from your device. Permissions can be managed through your Settings menu on both Android and iOS devices.
+Information You Provide
+Your Account Information. You must provide your mobile phone number and basic information (including a profile name of your choice) to create a WhatsApp account. If you don’t provide us with this information, you will not be able to create an account to use our Services. You can add other information to your account, such as a profile picture and "about" information.
+Your Messages. We do not retain your messages in the ordinary course of providing our Services to you. Instead, your messages are stored on your device and not typically stored on our servers. Once your messages are delivered, they are deleted from our servers. The following scenarios describe circumstances where we may store your messages in the course of delivering them: Undelivered Messages. If a message cannot be delivered immediately (for example, if the recipient is offline), we keep it in encrypted form on our servers for up to 30 days as we try to deliver it. If a message is still undelivered after 30 days, we delete it.
+Media Forwarding. When a user forwards media within a message, we store that media temporarily in encrypted form on our servers to aid in more efficient delivery of additional forwards.
+We offer end-to-end encryption for our Services. End-to-end encryption means that your messages are encrypted to protect against us and third parties from reading them. Learn more about end-to-end encryption and how businesses communicate with you on WhatsApp.
+Your Connections. You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. If any of your contacts aren’t yet using our Services, we’ll manage this information for you in a way that ensures those contacts cannot be identified by us. Learn more about our contact upload feature here. You can create, join, or get added to groups and broadcast lists, and such groups and lists get associated with your account information. You give your groups a name. You can provide a group profile picture or description.
+Status Information. You may provide us your status if you choose to include one on your account. Learn how to use status on Android, iPhone, or KaiOS.
+Transactions And Payments Data. If you use our payments services, or use our Services meant for purchases or other financial transactions, we process additional information about you, including payment account and transaction information. Payment account and transaction information includes information needed to complete the transaction (for example, information about your payment method, shipping details and transaction amount). If you use our payments services available in your country or territory, our privacy practices are described in the applicable payments privacy policy.
+Customer Support And Other Communications. When you contact us for customer support or otherwise communicate with us, you may provide us with information related to your use of our Services, including copies of your messages, any other information you deem helpful, and how to contact you (e.g., an email address). For example, you may send us an email with information relating to app performance or other issues.
+Automatically Collected Information
+Usage And Log Information. We collect information about your activity on our Services, like service-related, diagnostic, and performance information. This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information.
+Device And Connection Information. We collect device and connection-specific information when you install, access, or use our Services. This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account).
+Location Information. We collect and use precise location information from your device with your permission when you choose to use location-related features, like when you decide to share your location with your contacts or view locations nearby or locations others have shared with you. There are certain settings relating to location-related information which you can find in your device settings or the in-app settings, such as location sharing. Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). We also use your location information for diagnostics and troubleshooting purposes.
+Cookies. We use cookies to operate and provide our Services, including to provide our Services that are web-based, improve your experiences, understand how our Services are being used, and customize them. For example, we use cookies to provide our Services for web and desktop and other web-based services. We may also use cookies to understand which of our Help Center articles are most popular and to show you relevant content related to our Services. Additionally, we may use cookies to remember your choices, like your language preferences, to provide a safer experience, and otherwise to customize our Services for you. Learn more about how we use cookies to provide you our Services.
+Back to top
+Third-Party Information
+Information Others Provide About You. We receive information about you from other users. For example, when other users you know use our Services, they may provide your phone number, name, and other information (like information from their mobile address book) just as you may provide theirs. They may also send you messages, send messages to groups to which you belong, or call you. We require each of these users to have lawful rights to collect, use, and share your information before providing any information to us.
+You should keep in mind that in general any user can capture screenshots of your chats or messages or make recordings of your calls with them and send them to WhatsApp or anyone else, or post them on another platform.
+User Reports. Just as you can report other users, other users or third parties may also choose to report to us your interactions and your messages with them or others on our Services; for example, to report possible violations of our Terms or policies. When a report is made, we collect information on both the reporting user and reported user. To find out more about what happens when a user report is made, please see Advanced Safety and Security Features.
+Businesses On WhatsApp. Businesses you interact with using our Services may provide us with information about their interactions with you. We require each of these businesses to act in accordance with applicable law when providing any information to us.
+When you message with a business on WhatsApp, keep in mind that the content you share may be visible to several people in that business. In addition, some businesses might be working with third-party service providers (which may include Meta) to help manage their communications with their customers. For example, a business may give such third-party service provider access to its communications to send, store, read, manage, or otherwise process them for the business. To understand how a business processes your information, including how it might share your information with third parties or Meta, you should review that business’ privacy policy or contact the business directly.
+Third-Party Service Providers. We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. For example, we work with them to distribute our apps; provide our technical and physical infrastructure, delivery, and other systems; provide engineering support, cybersecurity support, and operational support; supply location, map, and places information; process payments; help us understand how people use our Services; market our Services; help you connect with businesses using our Services; conduct surveys and research for us; ensure safety, security, and integrity; and help with customer service. These companies may provide us with information about you in certain circumstances; for example, app stores may provide us with reports to help us diagnose and fix service issues.
+The "How We Work With Other Meta Companies" section below provides more information about how WhatsApp collects and shares information with the other Meta Companies.
+Third-Party Services. We allow you to use our Services in connection with third-party services and Meta Company Products. If you use our Services with such third-party services or Meta Company Products, we may receive information about you from them; for example, if you use the WhatsApp share button on a news service to share a news article with your WhatsApp contacts, groups, or broadcast lists on our Services, or if you choose to access our Services through a mobile carrier’s or device provider’s promotion of our Services. Please note that when you use third-party services or Meta Company Products, their own terms and privacy policies will govern your use of those services and products.
+Back to top
+How We Use Information
+We use information we have (subject to choices you make and applicable law) to operate, provide, improve, understand, customize, support, and market our Services. Here's how:
+Our Services. We use information we have to operate and provide our Services, including providing customer support; completing purchases or transactions; improving, fixing, and customizing our Services; and connecting our Services with Meta Company Products that you may use. We also use information we have to understand how people use our Services; evaluate and improve our Services; research, develop, and test new services and features; and conduct troubleshooting activities. We also use your information to respond to you when you contact us.
+Safety, Security, And Integrity. Safety, security, and integrity are an integral part of our Services. We use information we have to verify accounts and activity; combat harmful conduct; protect users against bad experiences and spam; and promote safety, security, and integrity on and off our Services, such as by investigating suspicious activity or violations of our Terms and policies, and to ensure our Services are being used legally. Please see the Law, Our Rights and Protection section below for more information.
+Communications About Our Services And The Meta Companies. We use information we have to communicate with you about our Services and let you know about our terms, policies, and other important updates. We may provide you marketing for our Services and those of the Meta Companies.
+No Third-Party Banner Ads. We still do not allow third-party banner ads on our Services. We have no intention to introduce them, but you may see other types of ads in the Updates Tab, home of features like Channels and Status.
+Business Interactions. We enable you and third parties, like businesses, to communicate and interact with each other using our Services, such as Catalogs for businesses on WhatsApp through which you can browse products and services and place orders. Businesses may send you transaction, appointment, and shipping notifications; product and service updates; and marketing. For example, you may receive flight status information for upcoming travel, a receipt for something you purchased, or a notification when a delivery will be made. Messages you receive from a business could include an offer for something that might interest you. We do not want you to have a spammy experience; as with all of your messages, you can manage these communications, and we will honor the choices you make.
+Back to top
+Information You And We Share
+You share your information as you use and communicate through our Services, and we share your information to help us operate, provide, improve, understand, customize, support, and market our Services.
+Send Your Information To Those With Whom You Choose To Communicate. You share your information (including messages) as you use and communicate through our Services.
+Information Associated With Your Account. Your phone number, profile name and photo, "about" information, last seen information, and message receipts are available to anyone who uses our Services, although you can configure your Services settings to manage certain information available to other users, including businesses, with whom you communicate.
+Your Contacts And Others. Users, including businesses, with whom you communicate can store or reshare your information (including your phone number or messages) with others on and off our Services. You can use your Services settings and the “block” feature in our Services to manage who you communicate with on our Services and certain information you share.
+Businesses On WhatsApp. We offer specific services to businesses such as providing them with metrics regarding their use of our Services.
+Third-Party Service Providers. We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. We work with these companies to support our Services, such as to provide technical infrastructure, delivery and other systems; market our Services; conduct surveys and research for us; protect the safety, security, and integrity of users and others; and assist with customer service. When we share information with third-party service providers and other Meta Companies in this capacity, we require them to use your information on our behalf in accordance with our instructions and terms.
+Third-Party Services. When you or others use third-party services or other Meta Company Products that are integrated with our Services, those third-party services may receive information about what you or others share with them. For example, if you use a data backup service integrated with our Services (like iCloud or Google Account), they will receive information you share with them, such as your WhatsApp messages. If you interact with a third-party service or another Meta Company Product linked through our Services, such as when you use the in-app player to play content from a third-party platform, information about you, like your IP address and the fact that you are a WhatsApp user, may be provided to such third party or Meta Company Product. Please note that when you use third-party services or other Meta Company Products, their own terms and privacy policies will govern your use of those services and products.
+Back to top
+How We Work With Other Meta Companies
+As part of the Meta Companies, WhatsApp receives information from, and shares information (see here) with, the other Meta Companies. We may use the information we receive from them, and they may use the information we share with them, to help operate, provide, improve, understand, customize, support, and market our Services and their offerings, including the Meta Company Products. This includes:
+helping improve infrastructure and delivery systems;
+understanding how our Services or theirs are used;
+promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities;
+improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and
+providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. For example, allowing you to connect your Facebook Pay account to pay for things on WhatsApp or enabling you to chat with your friends on other Meta Company Products, such as Portal, by connecting your WhatsApp account.
+Learn more about the other Meta Companies and their privacy practices by reviewing their privacy policies.
+Back to top
+Assignment, Change Of Control, And Transfer
+In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws.
+Back to top
+Managing And Retaining Your Information
+You can access or port your information using our in-app Request Account Info feature (available under Settings &gt; Account). For iPhone users, you can learn how to access, manage, and delete your information through our iPhone Help Center articles. For Android users, you can learn how to access, manage, and delete your information through our Android Help Center articles.
+We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. The storage periods are determined on a case-by-case basis that depends on factors like the nature of the information, why it is collected and processed, relevant legal or operational retention needs, and legal obligations.
+If you would like to further manage, change, limit, or delete your information, you can do that through the following tools:
+Services Settings. You can change your Services settings to manage certain information available to other users. You can manage your contacts, groups, and broadcast lists, or use our “block” feature to manage the users with whom you communicate.
+Changing Your Mobile Phone Number, Profile Name And Picture, And “About” Information. If you change your mobile phone number, you must update it using our in-app change number feature and transfer your account to your new mobile phone number. You can also change your profile name, profile picture, and "about" information at any time.
+Deleting Your WhatsApp Account. You can delete your WhatsApp account at any time (including if you want to revoke your consent to our use of your information pursuant to applicable law) using our in-app delete my account feature. When you delete your WhatsApp account, your undelivered messages are deleted from our servers as well as any of your other information we no longer need to operate and provide our Services. Deleting your account will, for example, delete your account info and profile photo, delete you from all WhatsApp groups, and delete your WhatsApp message history. Be mindful that if you only delete WhatsApp from your device without using our in-app delete my account feature, your information will be stored with us for a longer period. Please remember that when you delete your account, it does not affect your information related to the groups you created or the information other users have relating to you, such as their copy of the messages you sent them.
+You can learn more here about our data deletion and retention practices and about how to delete your account.
+Back to top
+Law, Our Rights, And Protection
+We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm.
+Back to top
+Our Global Operations
+WhatsApp shares information globally, both internally within the Meta Companies and externally with our partners and service providers, and with those with whom you communicate around the world, in accordance with this Privacy Policy. Your information may, for example, be transferred or transmitted to, or stored and processed in, the United States; countries or territories where the Meta Companies’ affiliates and partners, or our service providers are located; or any other country or territory globally where our Services are provided outside of where you live for the purposes as described in this Privacy Policy. WhatsApp uses Meta’s global infrastructure and data centers, including in the United States. These transfers are necessary to provide the global Services set forth in our Terms. Please keep in mind that the countries or territories to which your information is transferred may have different privacy laws and protections than what you have in your home country or territory.
+Back to top
+Updates To Our Policy
+We may amend or update our Privacy Policy. We will provide you notice of amendments to this Privacy Policy, as appropriate, and update the “Effective Date” at the top of this Privacy Policy. Please review our Privacy Policy from time to time.
+Back to top
+Privacy Rights for United States Residents
+You can learn more about the consumer privacy rights that may be available to you, by reviewing the United States Regional Privacy Notice here.
+Back to top
+Contact Us
+If you have questions or issues about our Privacy Policy, please contact us.
+WhatsApp LLC
+Privacy Policy
+1601 Willow Road
+Menlo Park, California 94025
+United States of America
+Back to top
+Download
+Download
+What we do
+FeaturesBlogSecurityFor Business
+Who we are
+About usCareersBrand CenterPrivacy
+Use WhatsApp
+AndroidiPhoneMac/PCWhatsApp Web
+Need help?
+Contact UsHelp CenterAppsSecurity Advisories
+Download
+2025 © WhatsApp LLC
+Terms &amp; Privacy PolicySitemap
+Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）</t>
+  </si>
+  <si>
+    <t>Privacy Policy – Giraffe Games
+GIRAFFE GAMESâ PRIVACY POLICY
+Effective date : 25th May 2018
+About us
+We are a limited company (company number : 535897) and out registered office is:
+Giraffe Games Limited
+26 Upper Pembroke Street,
+Dublin 2
+Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. We are responsible for processing personal data in accordance with the General Data Protection Regulation (âGDPRâ), an EU wide Regulation for the protection of personal data.
+This Privacy Policy explains:
+– What personal data we collect from you and why
+– How we use your personal data, and
+– The options you have in relation to your personal data.
+Contact us
+Contact Information
+Giraffe Games Limited,
+26 Upper Pembroke Street,
+Dublin 2
+If you have any questions about this Policy, please contact us at contact@giraffe-games.com
+The Privacy Policy, together with any game license agreement are to be read as a whole and form an integral part of the Terms of Use.
+Giraffe Games Limited and its affiliates (âGiraffeâ, âusâ, âourâ or âweâ) are dedicated to protecting the privacy rights of our users (âusersâ or âyouâ). This Privacy Policy (the âPolicyâ) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the âSitesâ) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the âServiceâ). If you have questions or concerns about our privacy policy or practices, please contact us at contact@giraffe-games.com .
+AGE LIMITS
+We do not knowingly process personal data belonging to anyone under the age of 16 or knowingly allow such persons to use our Services. No one under the age of 16 may provide any personal data. If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. If it is discovered that we process personal data of any individual under 16, this data will be deleted.
+Facebook third party account login
+If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. Basic profile information (avatar, Facebook name, country) will be displayed to other users during game play and on public leader-boards. Signing in with Facebook allows us to offer other functionalities such as to invite and play with friends, create challenges for friends and see friendsâ game progress. This is also to allow you to log in on multiple devices and synchronise progress across multiple devices on multiple platforms. If you would like to be signed in with your Facebook account, but would not like to have your image displayed to other players, you may use our âHide meâ option in the Settings to have your personal profile replaced with a dummy profile.
+What data do we collect?
+Giraffe collects information as described below.  Giraffeâs primary goals in collecting and using information is to create your account, provide Services to you, improve our Service, contact you, conduct research and create reports for internal use.  We use third parties to store information on servers located in the European Union and may store information on servers and equipment in other jurisdictions from time to time. You are not required to provide personally identifiable information to visit the Site; however, in order to take advantage of certain features you may need to provide some personally identifiable information.
+– User Name and Password. In order to access your third party message accounts, you must enter your applicable user name(s) and password(s). To use the basic Services of the Site we do not store your password(s) on our server. If you wish to utilise advanced features of Site, such as automatic sign-in, storage of your and password(s) may be necessary.
+– Aggregate Usage Data. Giraffe may collect usage data and other information on all users, including data about their usage of the site and its various features, but it is not personally identifiable except as described below under the IP Addresses section.
+– Social Features. Whenever a social feature involves the disclosure of personally identifiable information about you to other people, Giraffe will either provide you with an opportunity to opt out of the disclosure or will seek your consent prior to making the disclosure.
+Our Sites
+While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically.  We may use this information to monitor, develop and analyse your use of the Service.
+Facebook Connect
+You need to be over 13 years old in order to use the Facebook Connect feature of the Services. Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. Should you give us such permission, we will store the information received based on your use of the Services. Please review Facebookâs terms and conditions and privacy policy (here: https://www.facebook.com/about/privacy/update) because these third-party services are governed by their terms. Please note that your email address and the access token are encrypted.
+Social Media (Features) and Widgets
+The Site may from time to time include Social Media Features, such as the Facebook Like button and Widgets, such as the Share this button or interactive mini programs that run on our site. These Features may collect your IP address, which page you are visiting on our site, and may set a cookie to enable the Feature to function properly. Social Media Features and Widgets are either hosted by a third party or hosted directly on the Site. Your interactions with these features are governed by the privacy policy of the company providing it.
+iOS, Android and Windows Phone Platforms
+When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address).  This information is useful to us for troubleshooting and helps us understand usage trends. We may collect and process your location data to provide location related Services and advertisements. We may use various technologies to determine location, such as GPS, Wi-Fi or other network-based data such as IP address. Your GPS geo-location is not accessed without your consent. We will not share your GPS geo-location with third parties without your consent. Please note that we may share your anonymous location data with partners in order to improve the Services. If you no longer wish to allow us to track or use this information, you may turn it off at the device level.  Please note, the application may not work properly if we are unable to tell where you are coming from (Country specific). In addition, we create a unique user ID to track your use of our Service.  This unique user ID is stored in connection with your profile information to track the Giraffe games you are playing.   Log in You can log in to the Site using sign-in services (âSN Serviceâ) including  Facebook Connect, Appleâs Game Center, Google+ and such other SN Service as may be available from time to time.  These services will authenticate your identity and provide you the option to share certain personal information with us such as your name, email address, and resume to pre-populate our sign up form.  Services like Facebook Connect give you the option to post information about your activities on this Web site to your profile page to share with others within your network. We may collect and record information through the SN Service in accordance with the policies and terms of that SN Service.  The information we collect when you connect your user account to an SN Service may include: (1) your name, (2) your SN Service user identification number and/or user name, (3) locale, city, state and country, (4) sex, (5) birth date, (6) email address, (7) profile picture or its URL, and (8) the SN Service user identification numbers for your friends that are also connected to Giraffeâs game(s). If you want us to delete the data we receive from the SN Service about you, please contact us at support@giraffe-games.com.
+Invite a Friend
+Giraffe may offer you the opportunity to invite your contacts from a SN Service (such as your Facebook friends) so that those contacts can be located in Giraffe games and/or you can invite them to join you in Giraffe games.  Such contact information will be used only for the purpose of sending communications to the addressee.  You or the third party may contact us at support@giraffe-games.com to request the removal of this information from our database to the extent Giraffe stores any of this information.
+Customer Service
+We may collect your email address when you contact our customer service group and we may use that email address to contact you about your gaming experience with Giraffe games and notify you about company news and promotions. If you no longer wish to receive certain email notifications you may opt-out at any time by following the unsubscribe link located at the bottom of each communication or by emailing us at support@giraffe-games.com.
+Push Notifications
+We may occasionally send you push notifications through our mobile applications to send you game updates, high scores and other service related notifications that may be of importance to you.  You may at any time opt-out from receiving these types of communications by turning them off at the device level through your settings.
+Game Data Collection
+Whenever you play our games, we collect anonymous data using the service of http://www.gameanalytics.com and sometimes use http://www.flurry.com/solutions/analytics(or such other service providers as we may deem appropriate).   The data thereby collected is presented to us in an anonymous form to include, for example, the percentage of users who complete a particular level.
+Other Collection
+We may also acquire information from you through (1) your access and participation in message boards on the Service, (2) your participation in surveys regarding the Service or (3) your participation in a sweepstakes or contest through the Service. We may provide you the opportunity to participate in a sweepstakes or contest through our Service. If you participate, we will request certain personal information from you.  Participation in these sweepstakes and contests are voluntary and you therefore have a choice whether or not to disclose this information.  The requested information typically includes contact information (such as name and shipping address), and demographic information (such as zip code). We use this information to notify winners and award prizes, to monitor traffic or personalise the Service.  We may use a third party service provider to conduct these sweepstakes or contests; that company is prohibited from using your usersâ personal information for any other purpose.
+Cookies
+A cookie is a small text file that we transfer to your computer and/or device, to identify a userâs computer/device and to ârememberâ things about your visit, such as your preferences or a user name and password.  Information contained in a cookie may be linked to your personal information, such as your user ID, for purposes such as improving the quality of our Service, tailoring recommendations to your interests, and making the Service easier to use.  You can disable cookies at any time, although you may not be able to access or use features of the Service. We may feature advertisements served by third parties that deliver cookies to your computer/device so the content you access and advertisements you see can be tracked.  Since the third party advertising companies associate your computer/device with a number, they will be able to recognise your computer/device each time they send you an advertisement.  These advertisers may use information about your visits to our Service and third party sites and applications in order to measure advertisement performance and to provide advertisements about goods and services of interest to you. This Policy does not apply to, and we are not responsible for the data collection practices of these third party advertisers, and we encourage you to check their privacy policies to learn more about their use of cookies and other technology. You cannot use the Sites without accepting the use of cookies.  The cookies are used to support analytics and logged in users on the Site.
+Clear Gifs (Web Beacons/Web Bugs)
+We employ or our third party tracking utility partner employs a software technology called clear gifs (a.k.a. Web Beacons/Web Bugs), that help us better manage content on our site by informing us what content is effective.  Clear gifs are tiny graphics with a unique identifier, similar in function to cookies, and are used to track the online movements of Web users.  In contrast to cookies, which are stored on a userâs computer hard drive, clear gifs are embedded invisibly on Web pages or e-mails and are about the size of the period at the end of this sentence. We may associate this information with your IP address or device identifier but do not tie the information gathered by clear gifs to our customersâ personal information.
+Mobile Analytics
+We use mobile analytics software to allow us to better understand the functionality of our Mobile Software on your device. This software may record information such as how often you use the application, the events that occur within the application, aggregated usage, performance data, and where the application was downloaded from. We do not link the information we store within the analytics software to any personal information you submit within the mobile application.
+Third Party Services
+Our services may contain third party tracking tools from Google Analytics, our service provider. Such third party may use cookies, APIs, and SDKs in our services to enable them to collect and analyse user information on our behalf. The third party may have access to information such as your device identifier, MAC address, IMEI, locale (specific location where a given language is spoken), geo-location information, and IP address for the purpose of providing their services under their respective privacy policies. This Policy does not cover the use of tracking tools from Google Analytics.  We do not have access or control over Google Analytics.
+Ad Networks
+We do not serve ads within the Sites, but we do serve ads within our games and the advertisers we use have their own terms of service which are compatible with the terms of services of the mobile platforms. The option to opt out of advertising is not available for all of our games.  When available, advertisement can be blocked by making an in app purchase.  The advertisers may collect and use information about you, such as your Service session activity, device identifier, MAC address, IMEI, geo-location information and IP address.  They may use this information to provide advertisements of interest to you. In addition, you may see our games advertised in other services.  After clicking on one of these advertisements and installing our game, you will become a user of our Service.  In order to verify the installs, a device identifier may be shared with the advertiser.
+Why do we need your personal data?
+We use information collected through our Service for purposes described in this Policy or disclosed to you in connection with our Service. For example, we may use your information to:
+– create game accounts and allow users to play our games;
+– identify and suggest connections with other Giraffe users;
+– operate and improve our Service;
+– understand you and your preferences to enhance your experience and enjoyment using our Service;
+– respond to your comments and questions and provide customer service;
+– provide and deliver products and services you request;
+– send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages;
+– communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners;
+– enable you to communicate with other users; and
+– link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services.
+Disclosure of Your information
+We do not share your personal information except as approved by you or as described below:
+– We may engage other companies and individuals to perform services on our behalf. An example of these services include analysing data and providing customer support. These agents and service providers may have access to your personal information in connection with the performance of services for Giraffe.
+– We may release your information as permitted by law, such as to comply with a court order, or when we believe that release is appropriate to comply with the law; investigate fraud, respond to a government request, enforce or apply our rights; or protect the rights, property, or safety of us or our users, or others.  This includes exchanging information with other companies and organizations for fraud protection.
+– Giraffe may share your information in connection with any merger, sale of our assets, or a financing or acquisition of all or a portion of our business to another company.  You will be notified via email and/or notice on our site of any change in ownership or users of your personal information.
+– We may share aggregate or anonymous information about you with advertisers, publishers, business partners, sponsors, and other third parties.
+Changes to the Policy
+We may update this privacy policy to reflect changes to our information practices. If we make any material changes we will notify you by means of a notice on this Site prior to the change becoming effective. We encourage you to periodically review this page for the latest information on our privacy practices.
+Security
+We take reasonable measures to protect your information from unauthorised access or against loss, misuse or alteration by third parties. Although we make good faith efforts to store the information collected on the Service in a secure operating environment that is not available to the public, we cannot guarantee the absolute security of that information during its transmission or its storage on our systems.  Further, while we attempt to ensure the integrity and security of our network and systems, we cannot guarantee that our security measures will prevent third-party âhackersâ from illegally obtaining access to this information.  We do not warrant or represent that your information will be protected against, loss, misuse, or alteration by third parties. No method of transmission over the Internet, or method of electronic storage, is 100% secure, however.  Therefore, we cannot guarantee its absolute security.
+Access to Personal Information
+If your personal information changes, or if you no longer desire our service, you may correct, update, or delete inaccuracies by making the change within your account settings or by contacting us at support@giraffe-games.com.  We will respond to your access request within 30 days.
+Data Retention
+We will retain your information for as long as your account is active or as needed to provide you services.  If you wish to cancel your account or request that we no longer use your information to provide you services, contact us at support@giraffe-games.com.  We will retain and use your information as necessary to comply with our legal obligations, resolve disputes, and enforce our agreements.
+What are your rights?
+You have many rights in relation to your data under the GDPR, if you would like to exercise one of these rights, please contact us at: contact@giraffe-games.com
+You have the right to ;
+Access. You have a right to know what information we hold about you and to have the information communicated to you. Please contact us letting us know that you wish to exercise your right of access and what information in particular you would like to receive. We are entitled to request reasonable evidence to verify your identity before we provide you with information. Please note that we may not be able to provide all the information you ask for, for instance if the information includes personal information about another person or the request would require disproportionate effort. If we are not able to provide you with information that you request we will communicate our reasons to you. We will always respond within 1 month of receipt of your request and verification of your identity.
+Correction of personal data. We try to keep the information that we hold about you accurate and up to date. Should you realise that any of the information that we hold about you is incorrect, please let us know (see our contact information in this policy) and we will correct it as soon as possible.
+Deletion of your personal data. In some circumstances you have the right for your personal information to be erased. Executing this request will depend on you deleting our games from your devices and clearing cookies from any device where you have accessed our Site. We may have an overriding reason for retaining data in this event, in which case we will communicate our reasons to you. In some instances, personal information about you that is visible through gameplay such as username, avatar, your high scores may be cached on other playersâ devices and we may not be able to remove or update that data from those devices.
+Data portability. You may have the right to request that data which you have provided to us is exported and provided to you, so you can transfer this to another data controller, or that we transfer this data directly to another data controller. (contact us if you would like more information)
+Restriction of processing. You may have the right to request a restriction of the processing of your personal data, for example as an intermediate measure if we are investigating your claim for inaccurate data held.
+Right to object. You have the right to object to the processing of personal data about you which is processed on the grounds of legitimate interests
+How long do we keep your data for?
+We will retain your information for as long as your account is active or as needed to provide you services.  If you wish to cancel your account or request that we no longer use your information to provide you services, contact us at support@giraffe-games.com.  We will retain and use your information as necessary to comply with our legal obligations, resolve disputes, and enforce our agreements.
+International Transfer
+Under EU data protection law, personal data transferred outside of the EU must have a legal mechanism for transfer (in order to ensure that the same protections are afforded to your personal data once it travels outside of the EU jurisdictions). Our hosted servers store your data in the EU. We take steps to ensure that there are adequate safeguards and mechanisms in place (including the use of EU model clauses and verifying the presence of agreements to privacy shield) to allow the transfer of your information across borders and outside of the EEA that might arise where data is processed by our third party service providers.
+This privacy policy was updated on May 23, 2018.
+Contact Information
+Giraffe Games Limited,
+26 Upper Pembroke Street,
+Dublin 2
+For queries about how we protect your personal data or about this Policy, please contact us at contact@giraffe-games.com
+Copyright Â© Giraffe Games 2016
+Copyright © Giraffe Games 2016</t>
+  </si>
+  <si>
     <t>['ï»¿', 'privacy policy', 'Privacy Policy', 'As noted in the policy above, the English language version of the Privacy Policy and Terms of Use will govern your relationship with Pandas Of Caribbean Limited. While the English version will govern, you can also use an automatic translation tool like Google Translate to view the documents in your language. Any further translation revisions will be posted on this page.']</t>
   </si>
   <si>
@@ -691,6 +2301,27 @@
     <t>['Privacy Policy | Snapchat Privacy', 'Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day.', 'Content GuidelinesAdditional standards for algorithmic recommendation beyond the creator’s friends or subscribers Creator Monetization Policy Content must adhere to the policies to be eligible for monetization.', 'Advertising PoliciesThese apply to all aspects of advertisements served by Snap.Commercial Content PolicyApplies to commercial content on the Snap platform other than ads served by Snap.', 'PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. Privacy PrinciplesAt Snap, we make your privacy a priority. We know your trust is earned every time you use Snapchat, or any of our other products and Services.', 'Privacy by ProductSaving Snaps was designed with privacy in mind. You control whether your Snaps can be saved within Snapchat.Privacy Through SecurityFeatures and recommendations to help secure your account.', 'Teens on SnapchatAdditional protections for teens on Snapchat.Snap and AdsHow we collect, use, and share your data with respect to ads.', 'Privacy CenterPrivacy policies tend to be pretty long — and pretty confusing. That’s why we did our best to make our Privacy Policy brief, clear, and easy-to-read!Learn More', 'SafetySafety CenterHere are some steps you can take to help stay safe!Safety PoliciesWe created these safety policies to help our community enhance their relationships with friends, family, and the world.Safety ResourcesWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters in need.', "Safety Advisory BoardMeet Snap's Safety Advisory Board membersCouncil for Digital Well-BeingMeet Snap's Council for Digital Well-BeingDigital Well-Being IndexSnap's Digital Well-Being Index highlights Gen Z's attitudes and perceptions about life online.", 'Information for Law EnforcementSnap is committed to assisting law enforcement while respecting the privacy and rights of our users.Financial SextortionWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Combating Illicit DrugsWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Report a Safety ConcernIf you ever experience harassment, bullying, or any other safety concern, you can always report it right to us.', 'Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More', 'TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. Previous ReportsTransparency Report archives', 'Regional InformationEuropean UnionEU specific informationCalifornia California specific informationAustralia Australia specific informationIndiaIndia specific information', 'ResourcesResearchersAccess for researchersAds GalleryFind European Union ads that delivered in the last 12 months and commercial content that’s live right now.', 'AboutIn our Transparency Report, we disclose data regarding our safety efforts across our platform. Here we provide additional context and insight into our safety principles, policies, and practices, as well as links to various safety and privacy resources.Learn More', 'News', 'PrivacyPrivacyPrivacy Center', 'Privacy Principles', 'Privacy by Product', 'Privacy Policy', 'Teens on Snapchat', 'Snap and Ads', 'Privacy Through Security', 'Privacy Policy', 'Effective: April 7, 2025', 'Welcome to Snap Inc.’s Privacy Policy. This Policy explains how we collect and use your data and how you can control your information. Looking for a quick summary on our privacy practices? Check out this page or this video. If you’re looking for specific product privacy information, for example, how we process your Chats and Snaps, take a look at our Privacy by Product page. In addition to these documents, we also show in-app notices that provide you more information about our products and services. And if you’re a Spectacles user you can learn more on how we collect and use your data in the Spectacles Supplemental Privacy Policy.', 'Transparency is one of our core values at Snap. We believe there shouldn’t be any surprises about the data we collect and how we use it — that’s why we’re upfront with how we process it. For example, we process your information to provide you a more personalized experience, including to show you content and information that is most relevant to your experience, as well as more relevant advertisements. Understanding your interests and preferences help us provide a better product experience.', 'Furthermore, we believe a personalized experience should not come at the expense of your privacy. Just like in real life, there are some moments you want to share privately with your close friends, and others that you want to share publicly. That’s why from day one our philosophy has been to delete content by default and to give Snapchatters control by providing the tools that allow them to decide what happens with their content, like who to share it with or when to save it.', 'This Policy covers our Snapchat app as well as our other products, services, and features, such as Bitmoji, Spectacles, and our advertising and commerce initiatives. When you read "Services" in this Policy, we’re talking about all of them. Also, if you see us refer to our "Terms," we mean the Terms of Service that you agree to when you sign up for our Services. Finally, if you see the term "Snapchatter" we are often using that as shorthand for any user of our Services.', 'Let’s get started with the controls you have over your information:', 'Control Over Your Information', 'Control over your information and settings is a core part of Snapchat experience. You can access, update, and delete your information, decide who can contact you, and download your data from within the Snapchat app. Below, we give you more details on the types of settings that are available, link out to our data download tool, and provide instructions on how to delete data or your account.', 'We want you to be in control of your information, so we provide you with a range of tools, including:', 'Access and update your information. You can access and edit most of your basic account information right in our Services. Just navigate to your settings and you will see the options available to you.', 'Delete your information. If you want to delete your account, learn how here. You can also delete some information within our Services, like content you’ve saved to Memories, content you’ve shared with My AI, Spotlight submissions, and more.', 'Control who can see your content. We’ve built a number of tools that let you choose who you share your content with. In some cases you may want to share content with your friends, and in other instances you may want to share it with the public. To learn more, go here.', 'Control who can contact you. Snapchat is intended for close friends and family, that’s why we’ve built controls that help you decide who can contact you. If you receive unwanted communications, you can always block and report that person. Go here to learn more.', 'Change your permissions. In most cases, you can change your permissions at any time. For example,  by default you are findable to others through your phone number and/or email address that you provided. If you no longer want to be findable, you can always change your settings. Or if you provided access to your phone or third party platform contacts to make friending easier, you can change that later on in your app settings. Of course, if you do that, certain features and Services, like finding friends in your contact book, won’t work.', 'Opt out of promotional messages. You have the option to opt out or unsubscribe from promotional emails and messages sent by SMS or other messaging platforms. To do so, just follow the instructions in the message like an unsubscribe link or similar functionality.', 'Download your data. You can make a request in our Download My Data tool to export a copy of your Snapchat information.', 'Object to processing. Depending on where you live and the particular data we are processing, you may have the right to object to our processing of that information. This gets a bit technical, so we’ve explained it in more detail here.', 'Set advertising preferences. We try to show you ads that we think will be relevant to your interests, but if you’d like to have a less personalized experience, you can change your advertising settings in the Snapchat app. Learn more here.', 'Tracking. If you use an iPhone with iOS 14.5 or above, some specific requirements apply, which we’ve specified here.', 'Information We Collect', 'This section provides you with details on what information we collect: what you provide to us, what we collect when you use Snapchat, and information we receive from other companies or apps you’ve connected to your Snapchat account. Sometimes, we may also collect additional information, with your permission.', 'When you use our Services, such as Snapchat, we collect information you provide to us, generate information when you use our Services, and in some cases receive data from others. Let’s break these down in more detail.', 'Information You Provide', 'Many of our Services require you to set up an account. To do this, we ask you to provide us with account details (information about you, like your name, username, email address, birthday, and phone number). When you set up your profile, you’ll also provide us with profile details (like your Bitmoji and profile picture). If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history).', 'Of course, you’ll also provide us with information you send through or save within our Services, including content and information about that content, and content you share and generate with our AI Features (content, or “Inputs,” including text, images, video, audio, precise location, and engagement, used to generate content and responses, or “Outputs”). We consider some of this information to be private content and communications (like Snaps and Chats with friends, voice and video calls, and content that is saved in My Eyes Only). Or content you share with a particular audience like private &amp; friend stories (My Story set to Friends, Private Stories). On the other end of the spectrum, some of the information you send through or save within our Services may be public content that is accessible to everyone (such as Public Story content, including My Story set to Everyone, Shared Stories, and Community Stories, Spotlight or Snap Map submissions, and Public Profile information). Keep in mind that Snapchatters who view your Snaps, Chats, and any other content, can always screenshot that content, save it, or copy it outside the Snapchat app. So please don’t send messages or share content that you wouldn’t want someone to save or share.', 'Lastly, when you contact Support (content and communications shared with Support) or our Safety team, or communicate with us in any other way, including through our research efforts (like responses to surveys, consumer panels, or other research questions) we’ll collect whatever information you provide or that we need to resolve your question.', 'Information We Generate When You Use Our Services', 'When you use our Services, we collect information about which of those Services you’ve used and how you’ve used them. This helps us better understand the way our community uses our Services so that we can make improvements.', 'This includes usage information (information about how you interact with our Services — for example, which Lenses you view and apply, your premium subscriptions, Stories you watch, and how often you interact with other Snapchatters) and content information (information about content you create or provide, your engagement with the camera and creative tools, your interactions with My AI, and metadata — for example, information about the content itself like the date and time it was posted and who viewed it). Content information includes information based on the content of the image, video, or audio — so if you post a Spotlight of a basketball game, we may use that information to show you more content on Spotlight about basketball.', 'This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies).', 'If you’ve explicitly granted device-level permissions, device information may also include information about your device phonebook (contacts and related information), images and other information from your device’s camera, photos, and microphone (like the ability to take photos, videos, view stored photos and videos, and access the microphone to record audio while recording video), and location information (precise location through methods like GPS signals).', 'Data We Receive From Others', 'The last category of data we collect is information about you that we may receive from others, such as other users, our affiliates, and third parties. This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines).', 'Other Information, With Your Permission', 'Additionally, there may be instances when you interact with our Services that we will ask your permission to collect additional information. For example, before accessing your device’s camera roll or your device or third party contact book.', 'How We Use Information', 'This section explains how we use the information we collect. Among other things, we use the information we collect to provide you with personalized products and Services that we work hard to build and improve. Below, we walk through each purpose for which we use information in detail. If you’d like to see a mapping of the data we collect with the purposes for which we collect it, we have a table here.', 'Keep Things Up &amp; Running (i.e., operate, deliver, and maintain our Services)', 'We use the information we collect in order to operate, deliver, and maintain our Services. For example, by delivering a Snap you want to send to a friend or, if you share your location on Snap Map, to show you suggestions like places you might like in your neighborhood, content others have posted to the Map, or your friends if they’re sharing their location with you. We also use some of your information to help keep our products up to date, for example to make sure that our Services work with the latest operating systems and devices.', 'Personalize Your Experience &amp; Give Context', "We offer personalized Services to Snapchatters. One of the ways we do this is by showing you content that is relevant to you or we think you may enjoy based on the information you share with us. To do so, we use information about you across different areas of the Services in order to add context to your Snapchat experience. For example, we automatically tag content with labels based on the content, your location, or the time of day. So if there's a dog in the photo, it may be searchable in Memories by the term “dog,” show up on the Map at the location where you created the Memory, and inform us that you’re into dogs so we can surface you fun dog videos and dog food ads in other parts of our Services, such as Spotlight.", 'Personalization can also help with suggesting friends or recommending a new friend to send a Snap to based on who you Snap with the most. We may show recommended places on the Snap Map, generate stickers, or even generate Snaps and other content using AI, infer your interests based on your content or activity, or customize the content we show you, including ads. For example, if you watch barista content on Spotlight, talk to My AI about your favorite espresso machine, or save a lot of coffee-related Snaps in your Memories, we may highlight coffee shops on the Snap Map when you visit a new city or show you content about coffee that you may find interesting or relevant. Or, if you interact with a lot of music venues we may use that to show you ads for upcoming shows in town. Personalization also includes tailoring your experience based on who you interact with most and what your friends are doing, including showing you content your friends create, like, or enjoy on Spotlight or Place recommendations that are popular with your friends.', 'Our goal is to continuously provide you with more relevant and interesting content.', 'For example, if you watch a lot of sports content, but skip content with hair and makeup tips, our recommendation algorithms will prioritize sports, but not those makeup tips. You can learn more about how we understand Snapchatter preferences and rank and moderate content here.', 'We believe it is critical to also balance the benefits of personalization with our Snapchatters’ expectations of privacy. For example, we may automatically tag the Snaps you save to Memories based on the content within it (e.g., the Snap contained a dog), and then use that tag to personalize your experience, make recommendations, or show you ads (such as showing you Spotlight Snaps containing dogs). We do not use the private content and communications you send to your friends to personalize your experience, make recommendations, or show you ads.', 'Provide Relevant Ads', 'Another way we provide a personalized Service is through the ads we show. We use your interests and preferences from the information we’ve collected to personalize, target, and measure ads. We think ads are best when they’re relevant. That’s why we try to select the right ads and show them to you at the right time. For example, if you’ve interacted with ads for video games, we will infer that you like video games, and show you similar ads, but those won’t be the only ads you see. Similar to our content strategy, we try to ensure you receive a variety of ads. We also use your information to avoid showing you ads you probably won’t be interested in. For example, if a ticketing site tells us you’ve previously bought tickets for a movie — we can stop showing you ads for it. You can learn about the different types of advertising and your choices about which ads you receive here.', 'You can learn more about how we collect, use, and share your information for advertising purposes here.', 'A note about information collected by cookies and other technologies: we may use these technologies to collect information when you interact with Services we offer through one of our partners. For example, we may use information collected on an advertiser’s website to show you more relevant ads. Most web browsers are set to accept cookies by default. If you prefer, you can usually remove or reject browser cookies through the settings on your browser or device. Keep in mind, though, that removing or rejecting cookies could affect the availability and functionality of our Services. To learn more about how we and our partners use cookies on our Services and your choices, please check out our Cookie Policy.', 'Develop &amp; Improve Features, Algorithms &amp; Machine Learning Models', 'Our teams are constantly coming up with new ideas for features and ways to improve our Services. In order to do this, we also develop and improve the algorithms and machine learning models (an expression of an algorithm that combs through significant amounts of data to find patterns or make predictions) that make our features and Services work, including through generative AI features (artificial intelligence capable of generating text, images, or other media, using generative models. Generative AI models learn the patterns and structure of their input training data and then generate new data that has similar characteristics). We use algorithms and machine learning models for personalization, advertising, safety and security, fairness and inclusivity, augmented reality, and to prevent abuse or other Terms of Service violations. For example, our algorithms and machine learning models take into account the conversations Snapchatters are having with My AI to improve the responses from My AI.', 'Your information can help us decide what kind of improvements we should make, but we are always focused on privacy — and we don’t want to use more of your personal information than necessary to develop our features and models.', 'Analytics', 'In order to understand what to build or how to improve our Services, we need to understand trends and demand for our features. For example, we monitor metadata and trends about Group Chat use to help decide whether we should change parts of the feature, like the maximum size of a Group. Studying data from Snapchatters can help us see trends in the ways that people use the Services. This helps inspire us to improve Snapchat on a larger scale. We perform analytics in order to identify, monitor, and analyze trends and usage. Based on this information, we will, among other things, create information about our users to help us understand demand.', 'Research', 'We conduct research to better understand general consumer interests, trends, and how our Services are used by you and others in our community. This information, along with analytics (as we described above), helps us understand more about our community and about how our Services fit into the lives of those in our community. We also engage in research and development to develop new techniques and technologies (e.g., new machine learning models or hardware, such as Spectacles). The results of our research are sometimes used in features on Snapchat, and we sometimes publish papers about things like overall behaviors and consumer trends (which will only have aggregated data across our user base, and not contain any private information about you specifically).', 'Enhance the Safety &amp; Security of Our Services', 'We use your information to enhance the safety and security of our Services, verify Snapchatter identity, and prevent fraud or other unauthorized or illegal activity. For example, we provide two-factor authentication to help protect your account and can send you email or text messages if we notice any suspicious activity. We also scan URLs sent on Snapchat to see if that webpage is potentially harmful, and can give you a warning about it.', 'Contacting You', 'Sometimes we’ll get in touch with you to promote new or existing features. This includes sending Snapchatters communications through Snapchat, email, SMS, or other messaging platforms, where permitted. For example, we may use the Snapchat app, email, SMS, or other messaging platforms to share information about our Services and promotional offers that we think may interest you.', 'Other times, we need to communicate with you to provide information, alerts, or to send messages our users ask us to deliver at their request. This may include sending communications through Snapchat, email, SMS, or other messaging platforms, where permitted, to deliver account status updates, security alerts, and Chat or friending reminders; it may also include fulfilling our user’s request to send invites or Snapchat content to non-Snapchatters.', 'Support', 'When you ask for help, we want to get you support as quickly as possible. In order to provide you, the Snapchatter community, and our business partners with the help needed to resolve issues with our Services, we often need to use the information we have collected to respond.', 'Enforce Our Terms &amp; Policies', 'We use the data we collect to enforce our Terms and the law. This includes enforcing, investigating, and reporting conduct that violates our Terms, policies, or the law, responding to requests from law enforcement, and complying with legal requirements. For example, when unlawful content is posted on our Services, we may need to enforce our Terms and other policies. In some cases, we may also use or share your information to cooperate with law enforcement requests, escalate safety issues to law enforcement, industry partners, or others, or comply with our legal obligations. Check out our Transparency Report to learn more.', 'Other Purposes, With Your Permission', 'Additionally, there may be instances when you interact with our Services that we will ask for your permission to use your information in a new, different, or otherwise specific way.', 'How We Share Information', 'This section explains who we share information with, what that information may include, and the reasons for sharing that information, including when we need to transfer it outside of the country it was collected from.', 'Recipients &amp; Reasons for Sharing', 'Snapchat. To provide our Services to you and our community, we may share your information with your friends on Snapchat or other Snapchatters. For example, the content you post to Stories, or your status as a premium subscriber, can be viewed by your Friends if you allow them. See the Control Over Your Information section and your Settings for the controls you have over who sees what and when.', 'Family Center Participants. When you have enabled Family Center, we share information about the connected teen account to the parent or guardian to provide insight about how the account is used, for example, who your Friends are on Snapchat or which friends you may be sharing your location with. We do not share message content. Learn more.', 'Public. Most of the features on Snapchat are private and for Friends only, but we also offer public features that allow you to opt in to showcase your best Snaps to the world, such as Spotlight, Snap Map, or your Public Profile. When you do this, those Snaps may also be discoverable outside of Snapchat, for example on the web. Some information, like your username and Bitmoji, are visible to the public. Learn more.', 'Third-Party Apps. Sometimes we provide features that allow you to connect with third-party apps. If you decide to connect your Snapchat account with a third-party app, we will share any additional information you direct us to.', 'Service Providers. We share your information with our service providers, who process that information on our behalf.\xa0For example, we rely on such Service Providers to facilitate payments, measure and optimize the performance of ads, or protect the services. We do not share private communications with them. We maintain a list of categories of service providers here.', 'Business and Integrated Partners. We share your information with business and integrated partners in order to provide the Services. For example, you can use OpenTable within Snapchat to reserve a table. This does not include private communications. We maintain a list of these partners here.', 'Anti-Fraud Partners. We share your information, such as device and usage information, with industry partners working to prevent fraud.', 'Legal, Safety, and Security Partners. We share your information as necessary for the following legal, safety, and security reasons:', 'comply with any valid legal process, governmental request, or applicable law, rule, or regulation.', 'investigate, remedy, or enforce potential Terms of Service and Community Guidelines violations.', 'protect the rights, property, or safety of us, our users, or others.', 'detect and resolve any fraud or security concerns.', 'Affiliates. Snap Inc. consists of different subsidiaries owned by us.\xa0We may share your information within those internal subsidiaries as needed to carry out our Services.', 'For the purposes of a Merger or Acquisition. If we were to sell or negotiate to sell our business to a buyer or possible buyer, we may transfer your information to a successor or affiliate as part of that transaction.', 'Integrated Partners', 'Our Services may contain content and integrations offered by our integrated partners. Examples include integrations in Lenses, Camera editing tools, to provide Scan results, and third-party developer integrations. Through these integrations, you may be providing information to the integrated partner as well as to Snap. We are not responsible for how those partners collect or use your information. As always, we encourage you to review the privacy policies of every third-party service that you visit or use, including those third parties you interact with through our Services. You can learn more about our integrations in Snapchat here.', 'On iOS we use Apple’s TrueDepth camera to improve the quality of Lenses. Note, however, that this information is used in real time — we don’t store this information on our servers or share it with third parties.', 'International Data Transfers', 'Our Services connect you with your friends around the world. To make that possible, we may collect your personal information from, transfer it to, and store and process it in the United States or other countries outside of where you live. Whenever we share information outside of where you live, we ensure safeguards are in place to protect the data as required by law where you live. If you want to learn more about this, see the Region Specific Information section for more details.', 'How Long We Keep Your Information', 'In this section we provide you with information on how long we keep your information, why we keep your information, and also highlight how we may need to keep your information to comply with laws, courts, and other obligations.', 'As a general rule, we keep information as long as you tell us to, and otherwise as long as we need it to provide our Services, or as required by law. For example, if you store something in Memories, we will keep it as long as you need it, but when you Chat with a friend, our systems are designed to delete Chats you send within 24 hours after your friend reads it (unless you’ve changed your default settings or decide to save it). Whether we retain your data depends on the specific feature, your settings, and how you’re using the Services. Here are some more factors we consider when we decide how long to keep your information:', 'If we need the information to operate or provide our Services. For example, we store your basic account details — like your name, phone number, and email address — to maintain your account.', 'To do the things you expect from our Services and as we’ve described within this Privacy Policy. For example, we maintain your list of friends until you ask us to delete them since friends are key to expressing yourself. Similarly, we keep your shared list of contacts until you ask us to remov</t>
   </si>
   <si>
+    <t>['Uber Privacy Notice: Riders &amp; Order Recipients', 'Skip to main content', 'UberRide', 'Drive', 'Business', 'Uber Eats', 'About', 'About us', 'Our offerings', 'How Uber works', 'Sustainability', 'Newsroom', 'Investor relations', 'Autonomous', 'Blog', 'Careers', 'More', 'No results', 'EN', 'Help', 'Log in', 'Sign up', 'UberLog in', 'Sign up', ',', 'Uber Privacy Notice: Riders and Order Recipients', 'When you use Uber, you trust us with your personal data. We’re committed to keeping that trust. That starts with helping you understand our privacy practices.', 'This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. We recommend that you read this along with our privacy overview, which highlights key points about our privacy practices.', 'Uber Privacy Notice: Drivers and Delivery People', 'Previous version of the Privacy Notice', 'I. Overview', 'II. Data collections and uses', 'A. Data we collect', 'B. How we use data', 'C. Core automated processes', 'D. Cookies and related technologies', 'E. Data sharing and disclosure', 'F. Data retention and deletion', 'III. Choice and transparency', 'IV. Legal information', 'A. Data controllers and Data Protection Officer', 'B. Our legal bases for using your data', 'C. Legal framework for data transfers', 'D. Updates to this Privacy Notice', 'I. Overview', 'A. Scope', 'This notice applies when you use Uber’s apps or websites to request or receive products or services, including rides or deliveries.', 'This notice describes how we collect and use your data if you request or receive products or services through Uber’s apps or websites, except when you use Uber Freight, Careem or Uber Taxi (South Korea).', 'This notice specifically applies if you:', 'Request or receive mobility services, including rides and package delivery and return services through Uber Connect, via your Uber account (a “Rider”).', 'Request or receive food or other products and services for delivery or pickup, including via your Uber Eats or Postmates account, or through the guest checkout features that allow you to access delivery or pickup services without creating and/or signing into your account (an “Order Recipient”).', 'Receive services through Uber’s apps or websites requested by other account owners (a “Guest User”), including if you receive ride or delivery services ordered by Uber Health, Central, Uber Direct or Uber for Business customers (collectively, “Enterprise Customers”); or by friends, family members or other individual account owners, including via Uber Connect; or receive a gift card.', 'Rent a vehicle through Uber Car Rentals (a “Renter”).', 'This notice does not describe Uber’s collection and use of your data if you use Uber to provide (instead of request or receive) services through Uber’s app or websites, including as a driver or delivery person. Uber’s notice describing our collection and use of such data is available here. Those who use Uber to either request, receive or provide services are referred to as “users” in this notice.', "Our privacy practices are subject to applicable laws in the places in which we operate. The types of data processing that such laws require, allow, or prohibit vary globally. Therefore, if you travel across national, state or other geographic borders, Uber's data processing practices described in this notice may differ from those in your home country or territory.", 'In addition, please note the following if you use Uber in:', 'ArgentinaDown Small', 'The Agency of Access to Public Information, in its role of Regulating Body of Law 25.326, is responsible for receiving complaints and reports presented by any data subjects who believe their rights have been impacted by a violation of the local data protection regulation.', 'AustraliaDown Small', 'You may contact Uber here regarding our compliance with the Australian Privacy Principles. Such contacts will be addressed by Uber’s customer service and/or relevant privacy teams within a reasonable timeframe. You may also contact the Office of the Australian Information Commissioner here with concerns regarding such compliance.', 'BrazilDown Small', 'Please go here for information regarding Uber’s privacy practices as relates to Brazil’s General Data Protection Law (Lei Geral de Proteção de Dados - LGPD).', 'Colombia, Honduras and JamaicaDown Small', '“Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.”', 'European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small', 'Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. Such data collections and uses are indicated with an asterisk (*). If you use Uber outside of these regions, your data may be collected and used for the purposes indicated with an asterisk.', 'KenyaDown Small', 'You may contact Uber here with questions regarding Uber’s compliance with, or to request exercise of your rights under, Kenya’s Data Protection Act of 2019. You may also contact the Office of the Data Protection Commissioner here with concerns regarding such compliance or exercise of your rights.', 'MexicoDown Small', "Please go here for information regarding Uber’s privacy practices as relates to Mexico’s Personal Data Protection Law (Ley Federal de Protección de Datos Personales en Posesión de los Particulares), and here for information regarding Uber Money's processing of personal data.", 'NigeriaDown Small', 'You may contact Uber here regarding Uber’s compliance with, or to request exercise of your rights under, Nigeria’s Data Protection Act of 2023. You may also contact the Nigeria Data Protection Commission here with concerns regarding such compliance.', 'Quebec, CanadaDown Small', 'You may contact Uber here with questions about Uber’s use of your data for purposes of automated decision making, including regarding the factors considered in connection with such decision, to request correction of any personal data relating to such decisions, and to request review of any such decisions by Uber personnel.', 'SwitzerlandDown Small', 'Uber Switzerland GmbH (Stockerstrasse 33', '8002 Zürich, Switzerland) is Uber’s appointed representative for purposes of the Federal Act on Data Protection and may be contacted here or by mail as relates to that act.', 'TaiwanDown Small', 'Please see here for information on the measures adopted by Uber when conducting cross-border data transfers in accordance with Taiwan’s Personal Data Protection Act and its relevant regulations, as well as other related information.', 'United StatesDown Small', 'Please go here for information regarding Uber’s privacy practices as relates to US state privacy laws, including the California Consumer Privacy Act. If you use Uber in Nevada or Washington, please go here for information regarding Uber’s practices as relates to collection and use of consumer health data under those states’ privacy laws.', 'Please contact us here with any questions regarding our practices in a particular country or region.', 'II. Data collections and uses', 'A. The data we collect', 'Uber collects data:', '1. That you provide', '2. When you use our services', '3. From other sources', 'Please go here for a summary of the data we collect and how we use it.', 'Uber collects the following data:', '1. Data you provide: This includes:', 'Data category', 'Data types', 'a. Account information. We collect data when you create or update your Uber account.', 'Address', 'Email', 'First and last name', 'Login name and password', 'Phone number', 'Payment method (including related payment verification information)', 'Profile picture', 'Settings (including accessibility settings) and preferences', 'Uber partner loyalty program information', 'b. Demographic data. We collect demographic data if necessary to enable certain features. For example:', 'We collect your date of birth and/or age to verify your eligibility to use age-restricted products or services, such as Uber for teens, or if you purchase alcohol, tobacco or cannabis products.', 'We collect or infer your gender to enable Women Rider Preference, and for marketing and advertising.', 'We may also collect demographic data through user surveys.', 'Age or date of birth', 'Gender or inferred gender (using first name)', 'c. Identity verification information. This refers to the data that we collect to verify your account or identity.', 'Government-issued identification documents, such as driver’s licenses or passports (which may contain identification photos and numbers, expiration date, date of birth, and gender)', 'User-submitted selfies', 'd. User content. This refers to the data that we collect when you:', 'Contact Uber for customer support or other inquiries.', 'Use features that enable you to create Lists or reviews of restaurants or merchants', 'Upload photos and recordings (including those submitted for purposes of customer support)', 'Provide ratings or feedback for drivers, delivery people, restaurants or merchants, or they provide feedback regarding you.', 'Please go here for more information about how ratings provided by other users are determined and used.', 'Chat logs and call recordings', 'Ratings or feedback', 'User created Lists or reviews of restaurants or merchants', 'Uploaded photos and recordings, including in-app audio recordings', "e. Travel information. We collect travel itinerary information if you book bus, train or flight travel through Uber's apps.", 'Dates/times of travel', '2. Data collected when you use our services: This includes:', 'Data category', 'Data types', 'a. Location data. If you request a ride, we track your driver’s location during your trip, and link that data to your account. This allows us to display where you are on your trip.', 'We also determine your approximate location, and can determine your precise location if you allow us to do so through the settings on your phone. If you do, we will collect your precise location from the time you request a ride or order until the ride is finished or your order is delivered. We also collect such data when you have the Uber app open on your phone’s screen.', 'You can use Uber without letting us collect your precise location. However, it may be less convenient for you, including because you will have to type your location into your phone instead of allowing us to detect it for you.', 'See “Choice and transparency” section below for information on how to control whether Uber may collect your precise location data.', 'Approximate location', 'Precise location', 'b. Trip/order information. This refers to the details we collect about your trip or order, including orders placed via guest checkout features.', 'Payment information (including amount charged and payment method)', 'Proof of delivery (including photo or signature)', 'Special instructions, allergies or food preferences', 'Statistics derived from past trip/order information, such as  Averages', 'Cancellation rates', 'Total trips/orders', 'Trip or order details, including Date and time', 'Requested pickup and dropoff addresses', 'Distance traveled', 'Restaurant or merchant name and location', 'Items ordered', 'c. Usage data. This refers to data about how you interact with Uber’s apps and websites.', 'App crashes and other system activity', 'Access dates and times', 'App features or pages viewed', 'Browser type', 'd. Device data. This refers to data about the device(s) you use to access Uber.', 'Advertising identifiers', 'Device motion data', 'Device IP address or other unique device identifiers', 'Hardware models', 'Mobile network data', 'Operating systems and versions', 'Preferred languages', 'e. Communications data. This refers to the data we collect when you communicate with drivers and delivery people through Uber’s apps.', 'Communication type (phone or text message)', 'Content (including recordings of phone calls solely when users are notified of the recording in advance)', 'Date and time', '3. Data from other sources: These include:', 'Data category', 'Data types', 'a. Law enforcement officials, public health officials and other government authorities.', 'Name and contact information', 'Information relating to law enforcement, health or other investigations', 'b. Marketing partners and service providers. This includes banks in connection with cash back programs,* and data resellers.*', 'Activity information', 'Name and contact information', 'User or device identifiers', 'c. Service providers who help us verify your identity or detect fraud.*', 'Confirmation of whether your account information relates to known persons', 'Name and contact information', 'Information relating to the wireless carrier associated with your phone number', 'Information from government-issued identification documents such as driver’s licenses or passports (such as identification numbers, expiration date, date of birth, and gender)', 'd. Uber account owners. This refers to Uber account owners who request services for you (such as friends or family members), or who enable you to request services through their accounts (such as Enterprise Customers).', 'Name and contact information', 'Trip/order info', 'Location', 'e. Uber business partners (account creation and access, and APIs). Uber may receive your data from business partners through which you create or access your Uber account, such as payment providers, social media services, or apps or websites that use Uber’s APIs or whose APIs Uber uses.', 'The information received from Uber business partners depends on which partners you use to create or access your Uber account, or the API used.', 'f. Uber business partners (debit or credit cards). Uber may receive your data from business partners in connection with debit or credit cards issued by a financial institution in partnership with Uber to the extent disclosed in the terms and conditions for the card.', 'Debit or credit card activity information', 'g. Users or others providing information in connection with customer support issues, claims or disputes.', 'Name', 'Evidence relating to accidents, conflicts, claims or disputes (which may include photos or recordings of you)', 'h. Users participating in Uber’s referral programs. For example, if you are referred to Uber by another user, we receive your data from that user.', 'Name and contact information', 'B. How we use data', 'Uber uses data to enable reliable and convenient transportation, delivery, and other products and services. We also use data:', 'To enhance the safety and security of our users and services, and to prevent and detect fraud', 'For marketing and advertising', 'To enable communications between users', 'For customer support', 'For research and development', 'To send non-marketing communications to users', 'In connection with legal proceedings', '1. To provide our services. Uber uses data to provide, personalize, maintain, and improve our services.', 'Data uses', 'Data used includes', 'a. Creating and updating your account', 'Account', 'Demographics', 'Location', 'b. Enabling services and features. This includes:', 'Enabling navigation to pickups and dropoffs, calculating ETAs and tracking the progress of rides or deliveries', 'Matching you with available drivers or delivery people when you request transportation or deliveries', 'Enabling features that involve data sharing, such as ETA sharing and fare splitting', 'Enabling accessibility features', 'Enabling features that involve account linking, such as linking with Uber partners’ loyalty programs', 'Facilitating and optimizing rental car reservations, pickup and dropoff through Uber Rent', 'Account', 'Data from other sources', 'Demographics', 'Device', 'Ratings', 'Travel', 'c. Calculating rider/recipient prices and driver/delivery person fares.', 'Location', 'Trip/order info', 'd. Processing payments and enabling payment and e-money products such as Uber Money.', 'Account', 'Demographics', 'Data from other sources', 'Trip/order info', 'e. Personalizing your account. For example, we may present you with personalized restaurant or food recommendations, or trip suggestions, based on your prior orders, trips and delivery location.', 'Account', 'Demographics', 'Data from other sources', 'Trip/order info', 'f. Providing you with trip or delivery updates and generating receipts.', 'Account', 'Trip/order info', 'g. Informing you of changes to our terms, services, or policies.', 'Account', 'Trip/order info', 'h. Performing necessary operations to maintain our services, including to troubleshoot software bugs and operational problems.', 'Account', 'Device', 'Usage', '2. For safety, security, and fraud prevention and detection. Uber uses data to help maintain the safety and security of our services and users.', 'Data uses', 'Data used includes', 'a. Verifying your account, identity or compliance with safety requirements. This includes:', 'Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases*', 'Verifying that your account is being used by you and not someone else by:', 'Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document*', 'Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person*', 'Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect', 'Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology', 'Verifying your eligibility to subscribe to an Uber One for Students membership', 'Account', 'Data from other sources (third-party databases)', 'Identity verification info', 'User content', 'b. Preventing, detecting, and combating fraud, including by Guest Users.', 'Account', 'Communications between users', 'Data from other sources (driver data)', 'Device', 'Identity verification info', 'Location', 'Trip/order info', 'Usage', 'c. Predicting and helping avoid pairings of users that may result in increased risk of conflict,* or where one user has previously given the other a low (for instance, one star) rating.', 'Account', 'Trip/order info (including cancellation rates)', 'Usage', 'User content (ratings and reported incidents)', 'd. Providing live support from safety experts during trips or deliveries.', 'Account (phone, user name, vehicle details)', 'Location', 'Trip/order info', 'User content', '3. For marketing and advertising. Uber uses data (except Guest Users’ data) to market its services, and those of Uber partners.', 'Data uses', 'Data used includes', 'a. Personalizing marketing communications and ads relating to Uber products and services, and those offered by other companies. For example, Uber may:', 'Send push notifications suggesting your favorite destinations or merchants, or in-app messages offering discounts or promotions for products or merchants similar to those you’ve previously ordered', 'Display personalized ads on Uber or other companies’ apps or websites', 'Personalize sponsored listings, discounts or promotions for restaurants and merchants available on Uber', 'Account', 'Data from other sources', 'Demographics (including inferred gender)', 'Device', 'Location', 'Trip/order info', 'Usage', 'b. Displaying ads that are targeted based on data about your current trip or delivery request, including time of request and services requested. For example, if you request a trip to a supermarket, we may display in-app ads for third-party products that may be available at that supermarket.', 'Account', 'Data from other sources', 'Demographics (including inferred gender)', 'Device', 'Location', 'Trip/order info', 'Usage', 'c. Measuring the effectiveness of the marketing communications and ads described above.', 'Account', 'Device', 'Usage', '4. To enable communications between users.', 'Data uses', 'Data used includes', 'For example, a driver may message or call you to confirm a pickup location, you may call a driver to retrieve a lost item, or a restaurant or delivery person may contact you with information about your order.', 'Account', 'Device', 'Usage', '5. For customer support.', 'Data uses', 'Data used includes', 'This includes investigating and addressing user concerns, monitoring and improving our customer support responses and processes, and identifying potential participants in research studies relating to customer support issues.', 'Account', 'Communications', 'Device', 'Identity verification info', 'Data from other sources', 'Location', 'Travel information', 'Usage', 'User content', 'Trip/order info', '6. For research and development.', 'Data uses', 'Data used includes', 'We use data for analysis, research and product development, including training machine learning models. This helps us make our services more convenient and easy-to-use, enhance the safety and security of our services, and develop new services and features.', 'Account', 'Communications', 'Demographics', 'Device', 'Identity verification info', 'Data from other sources', 'Location', 'Travel information', 'Usage', 'User content', 'Trip/order info', '7. For non-marketing communications.', 'Data uses', 'Data used includes', 'This includes surveys and communications regarding elections, ballots, referenda and other political processes that relate to our services. For example, we may notify you of ballot measures or pending legislation relating to Uber’s services where you live.', 'Account', 'Location', '8. For legal proceedings and requirements.', 'Data uses', 'Data used includes', 'We use data to investigate or address claims or disputes relating to use of Uber’s services; to satisfy requirements under applicable laws, regulations, operating licenses or agreements, insurance policies; or pursuant to legal process or governmental request, including from law enforcement.', 'Account', 'Communications', 'Demographics', 'Device', 'Identity verification info', 'Data from other sources', 'Location', 'Travel information', 'Usage', 'User content', 'Trip/order info', 'C. Core automated processes', 'Uber uses automated processes to enable certain parts of our services, including functions essential to our business such as matching, pricing and fraud prevention and detection.', 'Uber relies on automated processes to enable essential parts of our services, including matching (pairing users requesting and providing transportation and/or delivery services), pricing (calculating the amount owed for such services) and fraud detection and prevention. These processes allow Uber to provide a seamless, and safe, experience to millions of users globally every day.', 'This section describes how automated matching, pricing, and fraud prevention and detection processes work, including how they impact your Uber experience and the personal and non-personal data used to enable these processes.', 'You may contact Uber here if you have questions or concerns regarding these processes.', '1. MatchingDown Small', 'Uber uses algorithms to efficiently match Riders and drivers, or delivery people and Order Recipients. This helps us minimize wait times for you, and enable efficiency for drivers and delivery people.', 'The matching process is triggered when you request transportation or deliveries through Uber. Our algorithms then evaluate various factors to determine the best match, including your location, requested destination, the proximity and availability of drivers or delivery people, traffic conditions, and historical data (including, in some markets, whether the specific Rider and driver have previously reported having negative experiences with each other).', 'The trip or delivery request is then communicated to the driver/delivery person matched through this process. Once a trip or order is accepted, we send confirmation of the match to you and the driver/delivery person.', 'We are constantly refining our matching process to provide the best experience to all users on our platform and may consider different factors depending on the location where you use Uber.', 'Additional information on Uber’s matching process is available here.', '2. PricingDown Small', 'When you request transportation or a delivery, Uber uses algorithms to determine the price you pay based on a variety of factors, including:', 'The type of service you request (for instance, UberX, UberXL, Uber Black)', 'Your location', 'Estimated time and distance to destination', 'Availability and proximity of drivers or delivery people', 'Time of day', 'Traffic conditions', 'Historical data such as traffic patterns and seasonal trends.', 'Your price may also vary depending on tolls or surcharges incurred, tips, discounts, promotions and subscriptions, and route-based adjustments.', 'The price may also vary depending on surge pricing, which automatically goes into effect when there are more Riders in a given area than available drivers. This encourages more drivers to serve the busy area over time and shifts Rider demand, to maintain reliability and restore balance.', 'Additional information on Uber’s pricing process is available here.', '3. Fraud prevention and detectionDown Small', 'Uber uses algorithms and machine learning models to prevent and detect fraud against Uber or our users. This includes efforts to monitor for account takeovers, suspicious user behaviors, and unauthorized access attempts, including by third-party aggregators.', 'These tools look for patterns that may indicate fraudulent behavior, such as those that vary significantly from typical user behavior. To do this, Uber performs real-time monitoring of information collected from or generated by users, including location data, payment information, and Uber usage. We also examine historical data and compare it against real-time data to help detect suspicious behavior.', 'Uber may limit your access to its services, or require that you undertake a particular action such as verifying your identity before allowing such access, if it detects potential fraudulent activity.', 'You may contact Uber customer support here if you have questions or concerns about these processes.', 'D. Cookies and related technologies', 'Uber and its partners use cookies and other identification technologies on our apps, websites, emails, and online ads for purposes described in this notice, and Uber’s Cookie Notice.', 'Cookies are small text files that are stored on browsers or devices by websites, apps, online media, and ads. Uber uses cookies and similar technologies for purposes such as:', 'Authenticating users', 'Remembering user preferences and settings', 'Determining the popularity of content', 'Delivering and measuring the effectiveness of advertising campaigns', 'Analyzing site traffic and trends, and generally understanding the online behaviors and interests of people who interact with our services.', 'We may also allow others to provide audience measurement and analytics services for us, to serve ads on our behalf across the internet or for other companies’ products and services on our apps, and to track and report on the performance of those ads. These entities may use cookies, web beacons, SDKs and other technologies to identify the devices used by visitors to our websites, as well as when they visit other online sites and services.', 'Please see our Cookie Notice for more information regarding the use of cookies and other technologies described in this section.', 'E. Data sharing and disclosure', 'We share your data with other users where necessary to provide our services or features, at your request, or with your consent. We also share data with our affiliates, subsidiaries, service providers and partners, for legal reasons, or in connection with claims or disputes.', 'Uber may share data:', '1. With other users', 'This may include sharing data with:', 'Recipient', 'Data shared', 'Your driver', 'Account First name', 'Rating', 'Pickup and/or dropoff locations', 'Settings and preferences', 'Other Riders during shared rides', 'Account First name', 'Restaurants/merchants you order from, and your delivery person', 'AccountFirst name', 'Order infoDelivery address (including with  restaurants/merchants that use their own delivery people to fulfill your order)', 'Items ordered (which may include drug prescriptions)', 'Special instructions, allergies or food preferences', 'User content Feedback', 'Ratings', 'The owner of any Uber account you use. This includes if you use an account linked to a Family profile, or request or receive ride or delivery services as a Guest User of an Enterprise Customer’s account.', 'In addition, if you create an account using an email address affiliated with an Uber for Business account owner (i.e., your employer), we may share your account data (such as name and email address) with such account owner, to help you expense trips or orders to that Uber for Business account.*', 'We may also share information with that account owner about issues involving your trip, such as safety incidents or complaints.', 'Account', 'Trip/order info', 'Other recipients in your group order', 'Account First name', 'Order info Special instructions or allergies information', 'Items ordered', 'People who refer you to Uber. We may share your data as necessary to determine their referral bonus', 'Trip/order infoTrip count', 'Other Uber Eats users. We share your data if you post a review of a restaurant or create a List of your favorite restaurants on Uber Eats, and set sharing of the List to “Public.”', 'Account First name', 'User contentLists', 'Reviews', '2. Upon request or with your consent', 'This may include sharing data with:', 'Recipient', 'Data shared', 'Users with whom you use data-sharing features. This includes features that allow you to share your ETA and location, or split your fare.', 'Depending on the feature used, may include:', 'Account', 'Location', 'Trip/order info', 'Uber business partners. We share data with companies whose apps or websites you access through Uber, including for purposes of promotions, contests or specialized services.', 'Depending on the app or website you access through Uber, and for what purpose, may include:', 'Account', 'Device', 'Trip/order info', 'Emergency services. We enable you to share your data with police, fire, and ambulance services in the event of an emergency or after certain incidents.', 'For more information, please go to the “Choice and transparency” and “Emergency data sharing” sections below.', 'AccountName', 'Phone number', 'Location', 'Trip/order infoRequested pickup/dropoff', 'Insurance companies. If you are involved in an incident, or report or submit a claim to an insurance company relating to Uber’s services, Uber will share data with that insurance company for the purpose of adjusting or handling that claim.', 'Data necessary to adjust or handle the claim, which may include:', 'Account', 'Communications between users', 'Device', 'Location', 'Trip/order info', 'Usage', 'User content', 'Merchants or restaurants. If you add a restaurant or merchant loyalty membership number to your user account, we share that data with the restaurant/merchant when you place an order with them.', 'We also enable you to share your phone number, email and/or order info with restaurants or merchants to receive marketing communications from them.', 'Account dataEmail', 'Phone number', 'Restaurant/merchant loyalty membership number', 'Order info', '3. With Uber service providers and business partners', 'These include the third parties, or categories of third parties, listed below. Where a third party is identified, please go to their linked privacy notices for information regarding their collection and use of personal data.', 'Accountants, consultants, lawyers, and other professional service providers.', 'Ad and marketing partners and providers, including ad and marketing publishers (such as social media platforms), ad networks and advertisers, third-party data providers, ad technology vendors, measurement and analytics providers, and other service providers. Uber uses these vendors to reach or better understand current and potential users of Uber services or of our advertis</t>
+  </si>
+  <si>
+    <t>["What's on Boomplay? | Boomplay Music", 'Get APPGet APP', 'What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player', 'What’s Boomplay', 'For Artists', 'Advertising', 'News', 'Contact', 'Go Web Player', 'Privacy Policy', 'EFFECTIVE AS OF OCTOBER 26, 2020', 'Welcome to Boomplay.', 'Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”)', 'We are committed to protecting and respecting your privacy.', 'This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. Please read the following carefully to understand our views and practices regarding your personal data and how we will treat it. By accessing or using our website, software, services, applications, products and content offered via Boomplay (collectively, the “ Services ”), you are accepting and consenting to the practices described in this Policy.', 'The Types of Personal Data We Collect and Use', 'We may collect and use the following information about you:', '• Information you share with us.\xa0 This is the information about you or relating to you that is voluntarily shared by you on Boomplay. Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. Information you share with us also includes information about you (including location data and log data) that others who are using Boomplay share about you. Information you share with us will remain publicly-available for so long as you or a user that has shared such information retains it.', '• Information you share from your social networks. \xa0If you choose to link Boomplay to your social network or public forum account (including without limitation Facebook, Twitter or Google account), you may provide us or allow your social network to provide us with information from your social network or public forum accounts. This data may include your use of Boomplay on such public forums and/or social networks. For further information as to how and for what purpose the social network provider processes your data, please see their privacy policies.', '• Information on Your Device. \xa0We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID, \xa0Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. Any automated decision-making, including profiling, based on the data automatically collected from you, will solely be used in optimizing the Services and tailoring it to your preferences.', '• Behavioral information we collect about you.\xa0 We also collect information regarding your use of the Services, e.g. your comments on Boomplay or any other content that you Posted on or through the Services, views and interactions on Boomplay. In addition, we link your contact or subscriber information with your activity on Boomplay across all your devices using your email or social media log-in details, engagement (including without limitation likes, shares, comments, repeated views) and relate users based on your behavior. Finally, we collect opt-ins and communication preferences.', '• Location data \xa0We may collect and process information about your location, including location information based on your SIM card, IP address or mobile device location settings, and if activated on your mobile device, by use of a Global Positioning System (GPS). We may use such information to provide you with location-based services, such as features, notifications, marketing, or other content that is influenced by your location. If you do not wish to share your GPS location with us, you can switch off GPS functionality on your mobile device.', '• Metadata. When you Post content, including images, text and audio to Boomplay, you automatically upload certain metadata that is connected to the content. In essence, metadata describes other data and provides information about your content that will not always be evident to the viewer. In connection with your content the metadata can describe how, when and by whom the piece of content was collected and how that content is formatted. It further includes information such as your account name that enables other users to trace back the content to your user account. Metadata will further consist of additional data that you chose to provide with the content, e.g. any hashtags used to mark keywords to the comments.', '• Information from third parties. \xa0We may receive information if you use any of the other websites we operate or other Services we provide. We may also receive information from third parties (such as advertising networks and analytics providers) and from other sources, including business directories and other commercially or publicly available sources.', '• Contact Information. We may collect contact information from your contact list, address book and your social network to help you and others find people you may know and enable you to link your Boomplay contact list with the contact lists on your device and/or in your account on third party services. We will ask for your consent to access your contact list and address book before doing so. You may at any time allow or disallow us to access your contact list and address book by changing your settings.', '• Third-party Services. If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list.', 'Cookies', 'We use cookies and other similar technologies (e.g. web beacons, Flash cookies, App cache, etc.) (“ Cookies ”) to enhance your experience using Boomplay. Cookies are small files which, when placed on your device, enable us to provide certain features and functionality.', 'We use the following Cookies:', '• Strictly necessary Cookies.\xa0 These are Cookies that are required for the operation of Boomplay and to keep your account and data safe and secure. They include, for example, Cookies that enable you to log into secure areas of Boomplay.', '• Analytical/performance Cookies. \xa0They allow us to recognize and count the number of visitors and to see how visitors move around Boomplay when they are using it. This helps us to improve the way Boomplay works, for example, by ensuring that users are able to find what they are looking for easily.', '• Functionality Cookies. \xa0These are used to recognize you when you return to Boomplay. This enables us to personalize our content for you, greet you by name and remember your preferences (for example, your choice of language or region).', '• Targeting Cookies. \xa0These Cookies record your visit to Boomplay, the pages you have visited and the links you have followed. We will use this information to make Boomplay and the advertising displayed on it more relevant to your interests. We may also share this information with third parties for this purpose.', 'If for any reason you wish to not take advantage of Cookies, you may disable Cookies by changing the settings on your browser. However, if you do so, this will affect your enjoyment of Boomplay and we will no longer be able to offer to you personalized content. Unless you opt out of Cookies, we will assume you consent to the use of Cookies.', '"Do not track" signals are preferences that users can set on their web browser to limit how their activity is tracked across third-party websites or online services. Boomplay does not respond to "do not track" signals in your web browser.', 'Analytics information', 'On Boomplay, we use third-party analytics tools to help us measure traffic and usage trends for the Services. Traffic refers to the different data flows surrounding activities of the users on the Services. These tools, for example, collect information sent by your device or our Services, including the pages you visit, add-ons, and other information that assists us in improving the Service. The information will be used to report and evaluate your activities and patterns as a user of Boomplay to provide services in accordance with these activities.', 'How We Use Your Personal Data', 'We will use the information we collect about you in the following ways:', '• To administer Boomplay (i.e. to provide our Services to you) and for internal operations, including troubleshooting, data analysis, testing, research, statistical and survey purposes (i.e. to guarantee Boomplay’s stability and security) and to solicit your feedback;', '• To allow you to participate in interactive features of Boomplay, when you choose to do so;', '• To personalize the content you receive and provide you with tailored content that will be of interest to you;', '• To improve and develop Boomplay and conduct product development;', '• To measure and understand the effectiveness of our recommendation and service we offer to you and others;', '• To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings;', '• To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them;', '• To allow other users to identify you as a user of the Service and to support the socializing function of the Services;', '• To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users;', '• To make your information available to other users in accordance with the privacy settings you chose for the respective information;', '• To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow;', '• To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services;', '• To enable our messenger service to function;', '• To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay;', '• To notify you about changes to our Services;', '• To communicate with you;', '• To provide you with user support;', '• To enforce our terms, conditions and policies;', '• For any other specific reason provided to you at the time we collect your information.', 'It is in our legitimate interest to promote the Services, and we may use information that you give to us, such as content that you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services.', 'How We Share Your Personal Data', 'We may share your personal data with selected third parties in or outside your country, including without limitation:', '• Our business partners so that we can make you special offers via Boomplay;', '• With respect to on-screen ads, advertisers and advertising networks that require the data to select and serve advertisements to you and others. Without your consent, we will not share your contact details to our business partners to avoid direct contact from them, but we may share other information so that they can make you offers tailored to your requirements;', '• Cloud storage providers to store the information you provide and for disaster recovery services, as well as for the performance of any contract we have entered into with you;', '• Analytics and search engine providers that assist us in the improvement and optimization of Boomplay.', '• IT service providers that help develop, maintain, secure and optimize the Boomplay framework;', '• Our data center and the servers of our host providers.', 'We may share your information with any member or affiliate of our group, which includes our subsidiaries, our ultimate holding company and its subsidiaries, and companies that we control, are controlled by or under common control, and our service providers and strategic business partners, and their respective subsidiaries, in each case in or outside your country, for the purposes set out above (“ How We Use Your Personal Data ”).', 'We may share your information with law enforcement agencies, public or tax authorities or other organizations if legally required to do so, or if we have a good faith belief that such use is reasonably necessary to:', '• Comply with a legal obligation, process or request (including tax and related reporting requirements);', '• Enforce our Terms of Service and other agreements, policies, and standards, including investigation of any potential violation thereof;', '• Detect, prevent or otherwise address security, fraud or technical issues;', '• Protect the rights, property or safety of us, our users, a third party or the public as required or permitted by law (including exchanging information with other companies and organizations for the purposes of fraud protection and credit risk reduction).', 'We may also disclose your information to third parties:', '• In the event that we sell or buy any business or assets, in which case we may disclose your data to the prospective seller or buyer of such business or assets; or', '• If we sell, buy, merge or partner with other companies or businesses, or sell some or all of our assets. In such transactions, user information may be among the transferred assets. In any such cases, the third party company or business will adhere to the provisions of this Privacy Policy and where it will result in a change in any of the provisions herein, such changes will be communicated to you and you will be given the chance to consent or opt out at your discretion.', 'The Security of Your Personal Data', 'We take steps to ensure that your information is treated securely and in accordance with this policy. Unfortunately, the transmission of information via the internet is not completely secure. Although we will do our best to protect your information, for example, by encryption, we cannot guarantee the security of your information transmitted through Boomplay; thus, any transmission is at your own risk.', 'We have put in place appropriate technical and organizational measures to ensure a level of security appropriate to the risk of varying likelihood and severity for the rights and freedoms of you and other users. We maintain these technical and organizational measures and will amend them from time to time to improve the overall security of our systems.', 'We will, from time to time, include links to and from the websites of our partner networks, advertisers and affiliates. If you follow a link to any of these websites, please note that these websites have their own privacy policies and that we do not accept any responsibility or liability for these policies. Please check these policies before you submit any information to these websites.', 'Data Retention', 'We use the following criteria to determine the period for which we will keep your information:', '• Our contractual obligations and rights in relation to the information involved;', '• Legal obligation(s) under applicable law(s) and regulations to retain data for a certain period of time;', '• Statute of limitations under applicable law(s);', '• Our legitimate business purposes;', '• Disputes or potential disputes.', 'After you have terminated your use of our Services, we can store your information in an aggregated and anonymized format. Notwithstanding the foregoing, we can also retain any personal information as reasonably necessary to comply with our legal obligations, allow us to resolve and litigate disputes, and to enforce our agreements.', 'Information Relating to Children', 'The Services are not offered to children whose age makes it illegal to process their personal data or requires parental consent for the processing of their personal data under any applicable laws.', 'We do not knowingly collect personal data from children under 13 years or under the applicable age limit in your jurisdiction (the “Age Limit”). If you are under the Age Limit, please do not use the Services, and do not provide any personal data to us.', 'If you are a parent of a child under the Age Limit and become aware that your child has provided personal data to us, please contact us at privacy.boomplay@transsnet.com to delete such data.', 'If we are aware that we have collected the personal data of a child under the Age Limit, we will take reasonable steps to delete the personal data.', 'Complaints', 'In the event that you wish to make a complaint about how we process your personal data, please contact us in the first instance at privacy.boomplay@transsnet.com and we will endeavor to deal with your request as soon as possible. This is without prejudice to your right to launch a claim with your data protection authority or follow the dispute resolution process provided in the Terms of Service.', 'Changes', 'We may amend and update this Policy from time to time. You can access the latest version of this Policy on Boomplay. It is your responsibility to remain informed of any changes. Your continued access to or use of the Services after the date of the updated Policy constitutes your acceptance of the updated Policy. If you do not agree to the updated Policy, you must stop accessing or using the Services.', 'Contact', 'Questions, comments and requests regarding this policy are welcomed and should be addressed to privacy.boomplay@transsnet.com.', 'Your rights', 'You have the right to make a request to access and delete the personal data we hold about you, to rectify any personal data held about you that is inaccurate, the right to data portability and the right to request the suspension of the processing of your personal data. You can exercise your rights by contacting us at privacy.boomplay@transsnet.com.', 'Explore', 'Artists', 'Trending Songs', 'New Songs', 'Charts', 'Videos', 'Podcast', 'Buzz', 'For Users', 'Download', 'Help Center', 'Go Premuim', 'Wordpress', 'For Artists and Vendors', 'Boomplay for Artists', 'Get Verified', 'Artists FAQ', 'Artists Distributors', 'Vendors Login', 'Report Content Issue', 'Company', 'About', 'Contact', 'Advertising', 'News', 'Visual Identity', '© 2023 Boomplay All rights reserved. Privacy PolicyEULAPodcast T&amp;CSitemap', 'Explore', 'ArtistsTrending SongsNew SongsChartsVideosPodcastBuzz', 'For Users', 'DownloadHelp CenterGo PremuimWordpress', 'For Artists and Vendors', 'Boomplay for ArtistsGet VerifiedArtists FAQArtists DistributorsVendors LoginReport Content Issue', 'Company', 'AboutContactAdvertisingNewsVisual Identity', '© 2023 Boomplay All rights reserved. Privacy PolicyEULAPodcast T&amp;CSitemap']</t>
+  </si>
+  <si>
+    <t>['https://policies.google.com/privacy?hl=en&amp;gl=us']</t>
+  </si>
+  <si>
+    <t xml:space="preserve">['Meta Privacy Policy - How Meta collects and uses user data', 'Privacy Policy', 'Search', 'Privacy topics', 'More privacy resources', 'Privacy Policy', 'What is the Privacy Policy and what does it cover?', 'What information do we collect?', 'How do we use your information?', 'How is your information shared on Meta Products or with integrated partners?', 'How do we share information with third parties?', 'How do the Meta Companies work together?', 'How can you manage or delete your information and exercise your rights?', 'How long do we keep your information?', 'How do we transfer information?', 'How do we respond to legal requests, comply with applicable law and prevent harm?', 'How will you know the Policy has changed?', 'Privacy notice for United States residents', 'How to contact Meta with questions', 'Why and how we process your information', 'Other policies and articles', 'Settings', 'Privacy Policy', 'What is the Privacy Policy and what does it cover?', 'Effective June 16, 2025 | View printable version | See previous versions', 'Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights.', 'Highlights', 'We at Meta want you to understand what information we collect, and how we use and share it. That’s why we encourage you to read our Privacy Policy. This helps you use Meta Products in the way that’s right for you.', 'In the Privacy Policy, we explain how we collect, use, share, retain and transfer information. We also let you know your rights. Each section of this Policy includes helpful examples and simpler language to make our practices easier to understand. We’ve also added links to resources where you can learn more about the privacy topics that interest you.', "It's important to us that you know how to control your privacy, so we also show you where you can manage your information in the settings of the Meta Products you use. You can update these settings to shape your experience.", 'Read the full Policy below.', 'What Products does this Policy cover?', 'Learn more in Privacy Center about managing your privacy', 'What information do we collect?', 'Highlights', "The information we collect and process about you depends on how you use our Products. For example, we collect different information if you sell furniture on Marketplace than if you post a reel on Instagram. When you use our Products, we collect some information about you even if you don't have an account.", "Here's the information we collect:", 'Your activity and information you provide', 'Friends, followers and other connections', 'App, browser and device information', 'Information from partners, vendors and other third parties', 'What if you don’t let us collect certain information?', 'Some information is required for our Products to work. Other information is optional, but without it, the quality of your experience might be affected.', 'Learn more', 'What if the information we collect doesn’t identify individuals?', 'In some cases information is de-identified, aggregated, or anonymized by third parties so that it no longer identifies individuals before it’s made available to us. We use this information as described below without trying to re-identify individuals.', 'Take control', 'Manage the information we collect about you', 'Privacy Center', 'How do we use your information?', 'Highlights', 'We use information we collect to provide a personalized experience to you, including ads, along with the other purposes we explain in detail below.', 'For some of these purposes, we use information across our Products and across your devices. The information we use for these purposes is automatically processed by our systems. But in some cases, we also use manual review to access and review your information.', 'To use less information that’s connected to individual users, in some cases we de-identify or aggregate information or anonymize it so that it no longer identifies you. We use this information in the same ways we use your information as described in this section.', 'Here are the ways we use your information:', 'To provide, personalize and improve our Products', 'We use information we have to provide and improve our Products. This includes personalizing features, content and recommendations, such as your Facebook Feed, Instagram Feed, Stories and ads. We use information with special protections you choose to provide for these purposes, but not to show you ads.', 'Read more about how we use information to provide, personalize and improve our Products:', 'How we show ads and other sponsored or commercial content', 'How we use information to improve our Products', 'How we use location-related information', 'To promote safety, security and integrity', 'We use information we collect to help protect people from harm and provide safe, secure Products.', 'Learn more', 'To provide measurement, analytics and business services', 'Lots of people rely on our Products to run or promote their businesses or share content. We help them measure how well their ads and other content, products and services are working.', 'Learn more', 'To communicate with you', "We communicate with you using information you've given us, like contact information you've entered on your profile.", 'Learn more', 'To research and innovate for social good', 'We use information we have, information from researchers and datasets from publicly available sources, professional groups and non-profit groups to conduct and support research.', 'Learn more', 'More in the Privacy Policy', 'Why and how we process your information', 'How is your information shared on Meta Products or with integrated partners?', 'Highlights', 'On Meta Products', 'Learn more about the different cases when your information can be shared on our Products:', 'People and accounts you share and communicate with', 'Content others share or reshare about you', 'Public content', 'With integrated partners', 'You can choose to connect with integrated partners who use our Products. If you do, these integrated partners receive information about you and your activity.', 'These integrated partners can always access information that’s public on our Products. Learn more about other information they receive and how they handle your information:', 'When you use an integrated partner’s product or service', 'When you interact with someone else’s content on an integrated partner’s product or service', 'How integrated partners handle your information', 'Take control', 'Learn more about audiences', 'Privacy Center', 'Manage apps and websites', 'How do we share information with third parties?', 'Highlights', "We don't sell any of your information to anyone, and we never will. We also require partners and other third parties to follow rules about how they can and cannot use and disclose the information we provide.", 'Here’s more detail about who we share information with:', 'Partners', 'Advertisers and Audience Network publishers', 'Partners who use our analytics services', 'Partners who offer goods or services on our Products and commerce services platforms', 'Integrated partners', 'Vendors', 'Measurement vendors', 'Marketing vendors', 'Service providers', 'Service providers', 'Third parties', 'External researchers', 'AI integrations', 'Other third parties', 'We also share information with other third parties in response to legal requests, to comply with applicable law or to prevent harm. Read the Policy.', 'And if we sell or transfer all or part of our business to someone else, in some cases we’ll give the new owner your information as part of that transaction, but only as the law allows.', 'How do the Meta Companies work together?', 'Highlights', 'We are part of the Meta Companies that provide Meta Company Products. Meta Company Products include all the Meta Products covered by this Policy, plus other products like WhatsApp and more.', 'We share information we collect, infrastructure, systems and technology with the other Meta Companies. Learn more about how we transfer information to other countries.', 'We also process information that we receive about you from other Meta Companies, according to their terms and policies and as permitted by applicable law. In some cases, Meta acts as a service provider for other Meta Companies. We act on their behalf and in accordance with their instructions and terms.', 'Why we share across the Meta Companies', 'Meta Products share information with other Meta Companies:', 'To promote safety, security and integrity and comply with applicable laws', 'To personalize offers, ads and other sponsored or commercial content', 'To develop and provide features and integrations', 'To understand how people use and interact with Meta Company Products', 'See some examples of why we share.', 'More resources', 'Review the privacy policies of the other Meta Companies', 'Facebook Help Center', 'How can you manage or delete your information and exercise your rights?', 'Highlights', 'We offer you a variety of tools to view, manage, download and delete your information below. You can also manage your information by visiting the settings of the Products you use. You may also have other privacy rights under applicable laws.', 'To exercise your rights, visit our Help Centers, your settings for Facebook and Instagram and your device-based settings.', 'Take a privacy checkup', 'Take a privacy checkup', 'Be guided through Facebook privacy settings', 'View and manage your information', 'Access your information', 'Off-Meta activity', 'Ad preferences', 'Manage your data', 'Port, download or delete your information', 'Port your information', 'Download your information', 'Delete your information or account', 'You can learn more about how privacy works on Facebook and on Instagram, and in the Facebook Help Center. If you have questions about this policy, you can contact us as described below. In some countries, you may also be able to contact the Data Protection Officer for Meta Platforms, Inc., and depending on your jurisdiction, you may also contact your local Data Protection Authority (“DPA”) directly.', 'How long do we keep your information?', 'Highlights', 'We keep information as long as we need it to provide our Products, comply with legal obligations or protect our or other’s interests. We decide how long we need information on a case-by-case basis. Here’s what we consider when we decide:', 'If we need it to operate or provide our Products. For example, we need to keep some of your information to maintain your account. Learn more.', 'The feature we use it for, and how that feature works. For example, messages sent using Messenger’s vanish mode are retained for less time than regular messages. Learn more.', 'How long we need to retain the information to comply with certain legal obligations. See some examples.', 'If we need it for other legitimate purposes, such as to prevent harm; investigate possible violations of our terms or policies; promote safety, security and integrity; or protect ourselves, including our rights, property or products', 'In some instances and for specific reasons, we’ll keep information for an extended period of time. Read our Policy about when we may preserve your information.', 'How do we transfer information?', 'Highlights', 'Why is information transferred to other countries?', 'Where is information transferred?', 'How do we safeguard your information?', 'How do we respond to legal requests, comply with applicable law and prevent harm?', 'Highlights', 'We access, preserve, use and share your information:', 'In response to legal requests, like search warrants, court orders, production orders or subpoenas. These requests come from third parties such as civil litigants, law enforcement and other government authorities. Learn more about when we respond to legal requests.', 'In accordance with applicable law', 'To promote the safety, security and integrity of Meta Products, users, employees, property and the public. Learn more.', 'We may access or preserve your information for an extended amount of time. Learn more.', 'How will you know the Policy has changed?', "We'll notify you before we make material changes to this Policy. You’ll have the opportunity to review the revised Policy before you choose to continue using our Products.", 'Privacy notice for United States residents', 'You can learn more about the consumer privacy rights that may be available to you by reviewing the United States Regional Privacy Notice.', 'How to contact Meta with questions', 'You can learn more about how privacy works on Facebook and on Instagram and in the Facebook Help Center. If you have questions about this Policy or have questions, complaints or requests regarding your information, you can contact us as described below.', 'You can contact us online or by mail at:', 'Meta Platforms, Inc.', 'ATTN: Privacy Operations', '1601 Willow Road', 'Menlo Park, CA 94025', 'Why and how we process your information', 'The categories of information we use, and why and how information is processed, are set out below:', 'Why and how we process your information', "Information categories we use (see 'What Information do we collect?' for more information on each information category)", 'The actual information we use depends on your factual circumstances, but could include any of the following:', 'Personalizing the Meta Products (other than ads, see below): Our systems automatically process information we collect and store associated with you and others to assess and understand your interests and your preferences and provide you personalized experiences across the Meta Products in accordance with our terms. This is how we:', 'Personalize features and content (such as your Facebook Feed, Instagram Feed and Stories);', 'Make suggestions for you (such as people you may know, groups or events that you may be interested in or topics that you may want to follow) on and off our products.', 'Learn more about how we use information about you to personalize your experience on and across Meta Products and how we choose the ads that you see.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Metadata about content', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings (like GPS location)', 'Location-related information', 'Information about the network you connect your device to', 'Reports about our products’ performance on your device', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'Providing ads on the Meta Company Products:', 'Our ads system automatically processes information that we’ve collected and stored associated with you. Our ads system uses this information to understand your interests and your preferences and personalize your ads across the Meta Company Products.', 'Our ads system prioritizes what ad to show you based on what audience advertisers want to reach. Then we match the ad to people who might be interested. Learn more about how our ads system works', 'Your activity and information you provide:', 'Age', 'The gender you provide', 'Information about ads we show you and how you engage with those ads', 'App, browser and device information:', 'Location information', 'Device characteristics and device software', 'If you decide to add a WhatsApp account to an Accounts Center with other accounts on Meta Company Products:', 'To associate your accounts on Meta Company Products with your WhatsApp account in the same Accounts Center and share your information with WhatsApp.', 'Note: the list below is about information from Meta. For information that WhatsApp shares with Meta see the WhatsApp Help Center article.', 'Your activity and information you provide', 'Friends, followers and other connections', 'App, browser and device information', 'Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to:', 'Create and maintain your account and profile,', 'Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information,', 'Facilitate the sharing of content and status,', 'Provide and curate features,', 'Provide messaging services, the ability to make voice and video calls and connect with others,', 'Provide advertising products,', 'Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide,', 'Undertake analytics, and', 'Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences.', 'We also use information to develop, research and test improvements to our Products. We use information we have to:', 'See if a product is working correctly,', 'Troubleshoot and fix it when it’s not,', 'Test out new products and features to see if they work,', 'Get feedback on our ideas for products or features, and', 'Conduct surveys and other research about what you like about our Products and brands and what we can do better.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Your public profile information (including your name, username and profile picture)', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Messages you send and receive, including their content, subject to applicable law', 'Metadata about content and messages, subject to applicable law', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make, including truncated credit card information', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Your photo or video selfie if you provide it when you contact us for account support', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. We process information we have associated with you and apply automated processing techniques and, in some instances, conduct manual (human) review to:', 'Verify accounts and activity,', 'Find and address violations of our terms or policies. In some cases, the decisions we make about violations are reviewed by the Oversight Board,', 'Investigate suspicious activity,', 'Detect, prevent and combat harmful or unlawful behavior, such as to review and, in some cases, remove content reported to us,', 'Identify and combat disparities and racial bias against historically marginalized communities,', 'Protect the life, physical or mental health, well-being or integrity of our users or others,', 'Detect and prevent spam, other security matters and other bad experiences,', 'Detect and stop threats to our personnel and property, and', 'Maintain the integrity of our Products.', 'For more information on safety, integrity and security generally on Meta Products, visit the Facebook Security Help Center and Instagram Security Tips.', 'Your activity and information you provide::', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Messages you send and receive, including their content, subject to applicable law', 'Metadata about content and messages, subject to applicable law', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make, including truncated credit card information', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Your photo or video selfie if you provide it when you contact us for account support', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'To communicate with you: We use information you’ve given us (like contact information on your profile) to send you a communication, like an e-mail or in-product notice, for example:', 'We’ll contact you via email or in-product notifications in relation to the Meta Products, product-related issues, research or to let you know about our terms and policies.', 'We also use contact information like your email address to respond when you contact us.', 'Your activity and information you provide:', 'Contact information on your profile and your communications with us', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies.', 'Transferring, storing or processing your information across borders, including from and to the United States and other countries: We share information we collect globally, both internally across our offices and data centers and externally with our partners, third parties and service providers. Because Meta is global, with users, partners, vendors and employees around the world, transfers are necessary:', 'To operate and provide the services described in the terms that apply to the Meta Product(s) you are using. This includes allowing you to share information and connect with your family and friends around the globe; and', 'To fix, analyze and improve our Products.', 'For more information, see the "How do we transfer information?" section of the Meta Privacy Policy.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Metadata about content and messages, subject to applicable law', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make, including truncated credit card information', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Your photo or video selfie if you provide it when you contact us for account support', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'Processing information subject to special protections under applicable laws that you provide so we can share it with those you choose, to provide, personalize and improve our Products and to undertake analytics.  We’ll collect, store, publish and apply automated, or sometimes manual (human), processing for these purposes.', 'Your activity and information you provide:', 'Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent', 'Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. We receive this information whether or not you’re logged in or have an account on our Products. See the Cookies Policy for more information.', 'Your activity and information you provide:', 'Information and content you provide, such as your name or email address', 'Information from partners, vendors and third parties', 'Sharing your contact, profile or other information with third parties upon your request: The type of third party and categories of information shared depend on the circumstances of what you ask us to share. For example:', 'We share your email (or other contact information) or other information you might choose when you direct us to share it with an advertiser so they can contact you with additional information about a promoted product, and', 'If you choose to integrate other apps, games or websites with Meta Products and log in, we’ll share your information with the app, game or website to log you in.', 'Your activity and information you provide:', 'Information such as your contact or profile information', 'Content you create, like posts or comments', 'Providing measurement, analytics and business services:', 'Our systems automatically, as well as with some manual (human) processing, process information we have collected and stored about you and others. We use this information to:', 'Provide insights and measurement reports to businesses, advertisers and other partners to help them measure the effectiveness and distribution of their or their clients’ ads, content and services, to understand the kinds of people who are seeing their content and ads, and how their content and ads are performing on and off Meta Products, and', 'Provide aggregated user analytics and insights reports that help users, businesses, advertisers and other partners better understand the audiences with whom they may want to connect, as well as the types of people who use their services and how people interact with their content, websites, apps and services.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Sharing of information across the Meta Companies:', 'To provide a seamless, consistent and richer, innovative experience across the Meta Company Products to enable cross app interactions, sharing, viewing and engaging with content, including posts and videos.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Metadata about content', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', "Identifiers that tell your device apart from other users'", 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Business intelligence and analytics:', 'To understand, in aggregate, your usage of and across our Products, to accurately count people and businesses; and', 'To validate metrics directly related to these, in order to inform and improve product direction and development and to adhere to (shareholder/earning) reporting obligations.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Metadata about content and messages, subject to applicable law', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', "Identifiers that tell your device apart from other users'", 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'Identifying you as a Meta Product user and personalizing the ads we show you through Meta Audience Network when you visit other apps:', 'When we show you ads </t>
+  </si>
+  <si>
+    <t>['WhatsApp Business App Privacy Policy', 'Skip to contentHome', 'Features', 'Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI', 'Privacy', 'Help Center', 'Blog', 'For Business', 'Download', 'Download', 'Terms &amp; Privacy Policy2025 © WhatsApp LLC', 'AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어', 'FeaturesMessage privatelyEnd-to-end encryption and privacy controls.', 'Stay connectedMessage and call for free* around the world.', 'Connect in groupsGroup messaging made easy.', 'Express yourselfSay it with stickers, voice, GIFs and more.', 'Secure by designLayers of protection to help you stay safe.', 'Share your everydayShare photos, videos, voice notes on Status.', 'Follow channelsStay updated on topics you care about.', 'Do More with', 'Meta AIGet help with anything.', 'Privacy', 'Help Center', 'Blog', 'For Business', 'Apps', 'Log inDownload', 'WhatsApp Business App Privacy Policy', 'Effective July 14, 2025', 'Table of Contents', 'WhatsApp Legal Info', 'Scope of This WhatsApp Business App Privacy Policy', 'Information We Collect', 'How We Use Information', 'Information You and We Share', 'How We Work With Other Meta Companies', 'Region Specific Information', 'Assignment, Change Of Control, And Transfer', 'Managing Your Information', 'Law, Our Rights, And Protection', 'Our Global Operations', 'Updates to Our Privacy Policy', 'Contact Us', 'If you are located in the UK, WhatsApp LLC provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy.', 'If you are located in the European Region, WhatsApp Ireland Ltd. provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy.', 'WhatsApp Legal Info', 'If you are located in the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Business App to you under this Terms of Service and this WhatsApp Business App Privacy Policy. WhatsApp LLC is also the data controller for any processing of personal information about you and you can contact us using the details in the section Contact Us below.', 'If you are located in the European Region, WhatsApp Ireland Limited ("WhatsApp," "our," "we," or "us") provides our Business App to you under this Terms of Service and this  WhatsApp Business App Privacy Policy. WhatsApp Ireland Limited is also the data controller for the processing of any personal information about you and you can contact us using the details in the section Contact Us below.', 'Scope of This WhatsApp Business App Privacy Policy', 'The WhatsApp Business App provides similar features and functionality to the WhatsApp Messenger App (“Main App Functionality”), but provides additional features and functionality tailored for business needs (“Business Functions”). Business Functions include things like catalog, and greeting and away messages. While the WhatsApp Business App includes various features available in the WhatsApp Messenger App, some features may not be available; and not all Business Functions are available everywhere. Business Functions may be offered by WhatsApp, third parties and/or Meta, via integrations into our Business App, and may be subject to the third parties’ own terms of service and privacy policies.', 'This WhatsApp Business App Privacy Policy (“Business App Privacy Policy”) explains WhatsApp’s data practices with respect to the Business Functions, and applies only to the extent information relating to users of the WhatsApp Business App would be considered personal data and is processed by WhatsApp as a controller, each under applicable law. Users should refer to the WhatsApp Privacy Policy, incorporated herein by reference, to understand how their information is processed in Main App Functionality. Learn more about Business Functions and the Main App Functionality available on WhatsApp Business App here.', 'Please also read the WhatsApp Business Terms of Service ("Business Terms"), which describe the terms under which you use and we provide the WhatsApp Business App.', 'Information We Collect', 'In addition to the information described in the applicable WhatsApp Privacy Policy, we collect the following information.', 'Information You Provide', 'Your Business Account Information.', 'In addition to your phone number, you must provide basic information about your business to create a WhatsApp business account, including your business name and business category. If you don’t provide us with this information, you will not be able to create an account to use our WhatsApp Business App. You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience.', 'Automatically Collected Information', 'Usage and Log Information.', 'We collect information about your use of the Business Functions. For example, we collect information about your business profile settings; how you use Business Functions like catalogs, labels and quick replies; purchases and transactions with your business; and metrics related to how customers interact with your business.', 'Information Received From Others', 'User Reports, Feedback, Preferences and Blocks.', 'Users can report, submit feedback, set communication preferences, or block businesses on WhatsApp, which we associate with the business that is the subject of the report, feedback, preference, or block.', 'How We Use Information', 'We use the information we collect for the same purposes described in the WhatsApp Privacy Policy, and also to operate, provide, improve, understand, customize, support, and market our WhatsApp Business App and Business Functions.', 'Our WhatsApp Business App.', 'We use the information we have to operate and provide our WhatsApp Business App and Business Functions, including providing you with business support; providing onboarding tools; providing message creation and delivery tools; providing you new and premium Business Functions (some of which may be offered by third parties and/or Meta); and improving, fixing, and customizing our WhatsApp Business App. We also use information we have to understand how you use our WhatsApp Business App; evaluate and improve our WhatsApp Business App; research, develop, and test new services and features; and conduct troubleshooting activities. We also use your information to respond to you when you contact us.', 'Safety, Security and Integrity.', 'In addition to the safety, security and integrity purposes described in the WhatsApp Privacy Policy, we also use the information we have to maintain safety, security and integrity on our WhatsApp Business App, for example: to create quality and integrity inferences about businesses; secure WhatsApp systems and WhatsApp Business App users’ accounts; fight threats, abuse, or infringement activities; promote safety, security, and integrity on the WhatsApp Business App; and to ensure compliance with our terms and policies.', 'Information You and We Share', 'You and we share information as described in the WhatsApp Privacy Policy, plus additional sharing relevant to the Business Functions.', 'Information About Your Business Profile.', 'Business profile information is publicly available, including your business name, phone number, hours of operation, business category, address, email address, website(s), description, and Facebook and Instagram accounts (if added). We may provide ways for our users to find or reach you, like our Business Search or other search functionality.', 'Other Integrations.', 'We allow you to connect the WhatsApp Business App to products and services offered by third parties and/or Meta. These can include for example: cloud storage and hosting services; customer relationship management tools; ad and message creation, delivery and management services; business analytics services; and AI tools. When you use these products or services, their own terms and privacy policies will govern your use of those services and products.', 'How We Work With Other Meta Companies', 'Review the WhatsApp Privacy Policy to understand how we work with the other Meta Companies for the WhatsApp Business App.', 'Region Specific Information', 'Additional information for users located in the US', 'You can learn more about the consumer privacy rights that may be available to you, by reviewing the WhatsApp Business App United States Regional Privacy Notice here.', 'Assignment, Change Of Control, And Transfer', 'In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws.', 'Managing And Retaining Your Information', 'The WhatsApp Business App follows the same information management, retention and deletion practices described in the WhatsApp Privacy Policy.', 'Law, Our Rights, And Protection', 'Review the WhatsApp Privacy Policy to understand how we access, preserve, and share your information in response to legal obligations.', 'Our Global Operations', 'Review the WhatsApp Privacy Policy to understand how our global operations impact how your information is processed.', 'Updates to Our Privacy Policy', 'We may amend or update our Business App Privacy Policy. We will provide you notice of amendments to this Business App Privacy Policy, as appropriate, and update the “Effective Date” at the top of this Business App Privacy Policy. Please review our Business App Privacy Policy from time to time.', 'Contact Us', 'If you have questions or issues about our Privacy Policy, please contact us.', 'WhatsApp LLC', 'Privacy Policy', '1601 Willow Road', 'Menlo Park, California 94025', 'United States of America', 'Download', 'Download', 'What we do', 'FeaturesBlogSecurityFor Business', 'Who we are', 'About usCareersBrand CenterPrivacy', 'Use WhatsApp', 'AndroidiPhoneMac/PCWhatsApp Web', 'Need help?', 'Contact UsHelp CenterAppsSecurity Advisories', 'Download', '2025 © WhatsApp LLC', 'Terms &amp; Privacy PolicySitemap', 'AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어']</t>
+  </si>
+  <si>
+    <t>['Privacy Policy', 'Skip to contentHome', 'Features', 'Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI', 'Privacy', 'Help Center', 'Blog', 'For Business', 'Download', 'Download', 'Terms &amp; Privacy Policy2025 © WhatsApp LLC', 'Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）', 'FeaturesMessage privatelyEnd-to-end encryption and privacy controls.', 'Stay connectedMessage and call for free* around the world.', 'Connect in groupsGroup messaging made easy.', 'Express yourselfSay it with stickers, voice, GIFs and more.', 'Secure by designLayers of protection to help you stay safe.', 'Share your everydayShare photos, videos, voice notes on Status.', 'Follow channelsStay updated on topics you care about.', 'Do More with', 'Meta AIGet help with anything.', 'Privacy', 'Help Center', 'Blog', 'For Business', 'Apps', 'Log inDownload', 'WhatsApp Privacy Policy', 'Effective January 4, 2021archived versions', 'If you live in the European Region, WhatsApp Ireland Limited provides the Services to you under this Terms of Service and Privacy Policy.', 'If you live in the UK, WhatsApp LLC provides the Services to you under this Terms of Service  and Privacy Policy.', 'WhatsApp Legal Info', 'If you live outside the European Region or the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Services to you under this Terms of Service and Privacy Policy.', 'Our Privacy Policy ("Privacy Policy") helps explain our data practices, including the information we process to provide our Services.', 'For example, our Privacy Policy talks about what information we collect and how this affects you. It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services.', 'We are one of the Meta Companies. You can learn more further below in this Privacy Policy about the ways in which we share information across this family of companies.', 'This Privacy Policy applies to all of our Services unless specified otherwise.', 'Please also read WhatsApp’s Terms of Service ("Terms"), which describe the terms under which you use and we provide our Services.', 'Back to top', 'Key Updates', 'Respect for your privacy is coded into our DNA. Since we started WhatsApp, we’ve built our services with a set of strong privacy principles in mind. In our updated Terms of Service and Privacy Policy you’ll find:', 'Additional Information On How We Handle Your Data. Our updated Terms and Privacy Policy provide more information on how we process your data, and our commitment to privacy. For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information.', 'Better Communication With Businesses. Many businesses rely on WhatsApp to communicate with their customers and clients. We work with businesses that use Meta or third parties to help store and better manage their communications with you on WhatsApp.', 'Making It Easier To Connect. As part of the Meta Companies, WhatsApp partners with Meta to offer experiences and integrations across Meta’s family of apps and products.', 'Back to top', 'Information We Collect', 'WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services.', 'The types of information we receive and collect depend on how you use our Services. We require certain information to deliver our Services and without this we will not be able to provide our Services to you. For example, you must provide your mobile phone number to create an account to use our Services.', 'Our Services have optional features which, if used by you, require us to collect additional information to provide such features. You will be notified of such collection, as appropriate. If you choose not to provide the information needed to use a feature, you will be unable to use the feature. For example, you cannot share your location with your contacts if you do not permit us to collect your location data from your device. Permissions can be managed through your Settings menu on both Android and iOS devices.', 'Information You Provide', 'Your Account Information. You must provide your mobile phone number and basic information (including a profile name of your choice) to create a WhatsApp account. If you don’t provide us with this information, you will not be able to create an account to use our Services. You can add other information to your account, such as a profile picture and "about" information.', 'Your Messages. We do not retain your messages in the ordinary course of providing our Services to you. Instead, your messages are stored on your device and not typically stored on our servers. Once your messages are delivered, they are deleted from our servers. The following scenarios describe circumstances where we may store your messages in the course of delivering them: Undelivered Messages. If a message cannot be delivered immediately (for example, if the recipient is offline), we keep it in encrypted form on our servers for up to 30 days as we try to deliver it. If a message is still undelivered after 30 days, we delete it.', 'Media Forwarding. When a user forwards media within a message, we store that media temporarily in encrypted form on our servers to aid in more efficient delivery of additional forwards.', 'We offer end-to-end encryption for our Services. End-to-end encryption means that your messages are encrypted to protect against us and third parties from reading them. Learn more about end-to-end encryption and how businesses communicate with you on WhatsApp.', 'Your Connections. You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. If any of your contacts aren’t yet using our Services, we’ll manage this information for you in a way that ensures those contacts cannot be identified by us. Learn more about our contact upload feature here. You can create, join, or get added to groups and broadcast lists, and such groups and lists get associated with your account information. You give your groups a name. You can provide a group profile picture or description.', 'Status Information. You may provide us your status if you choose to include one on your account. Learn how to use status on Android, iPhone, or KaiOS.', 'Transactions And Payments Data. If you use our payments services, or use our Services meant for purchases or other financial transactions, we process additional information about you, including payment account and transaction information. Payment account and transaction information includes information needed to complete the transaction (for example, information about your payment method, shipping details and transaction amount). If you use our payments services available in your country or territory, our privacy practices are described in the applicable payments privacy policy.', 'Customer Support And Other Communications. When you contact us for customer support or otherwise communicate with us, you may provide us with information related to your use of our Services, including copies of your messages, any other information you deem helpful, and how to contact you (e.g., an email address). For example, you may send us an email with information relating to app performance or other issues.', 'Automatically Collected Information', 'Usage And Log Information. We collect information about your activity on our Services, like service-related, diagnostic, and performance information. This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information.', 'Device And Connection Information. We collect device and connection-specific information when you install, access, or use our Services. This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account).', 'Location Information. We collect and use precise location information from your device with your permission when you choose to use location-related features, like when you decide to share your location with your contacts or view locations nearby or locations others have shared with you. There are certain settings relating to location-related information which you can find in your device settings or the in-app settings, such as location sharing. Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). We also use your location information for diagnostics and troubleshooting purposes.', 'Cookies. We use cookies to operate and provide our Services, including to provide our Services that are web-based, improve your experiences, understand how our Services are being used, and customize them. For example, we use cookies to provide our Services for web and desktop and other web-based services. We may also use cookies to understand which of our Help Center articles are most popular and to show you relevant content related to our Services. Additionally, we may use cookies to remember your choices, like your language preferences, to provide a safer experience, and otherwise to customize our Services for you. Learn more about how we use cookies to provide you our Services.', 'Back to top', 'Third-Party Information', 'Information Others Provide About You. We receive information about you from other users. For example, when other users you know use our Services, they may provide your phone number, name, and other information (like information from their mobile address book) just as you may provide theirs. They may also send you messages, send messages to groups to which you belong, or call you. We require each of these users to have lawful rights to collect, use, and share your information before providing any information to us.', 'You should keep in mind that in general any user can capture screenshots of your chats or messages or make recordings of your calls with them and send them to WhatsApp or anyone else, or post them on another platform.', 'User Reports. Just as you can report other users, other users or third parties may also choose to report to us your interactions and your messages with them or others on our Services; for example, to report possible violations of our Terms or policies. When a report is made, we collect information on both the reporting user and reported user. To find out more about what happens when a user report is made, please see Advanced Safety and Security Features.', 'Businesses On WhatsApp. Businesses you interact with using our Services may provide us with information about their interactions with you. We require each of these businesses to act in accordance with applicable law when providing any information to us.', 'When you message with a business on WhatsApp, keep in mind that the content you share may be visible to several people in that business. In addition, some businesses might be working with third-party service providers (which may include Meta) to help manage their communications with their customers. For example, a business may give such third-party service provider access to its communications to send, store, read, manage, or otherwise process them for the business. To understand how a business processes your information, including how it might share your information with third parties or Meta, you should review that business’ privacy policy or contact the business directly.', 'Third-Party Service Providers. We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. For example, we work with them to distribute our apps; provide our technical and physical infrastructure, delivery, and other systems; provide engineering support, cybersecurity support, and operational support; supply location, map, and places information; process payments; help us understand how people use our Services; market our Services; help you connect with businesses using our Services; conduct surveys and research for us; ensure safety, security, and integrity; and help with customer service. These companies may provide us with information about you in certain circumstances; for example, app stores may provide us with reports to help us diagnose and fix service issues.', 'The "How We Work With Other Meta Companies" section below provides more information about how WhatsApp collects and shares information with the other Meta Companies.', 'Third-Party Services. We allow you to use our Services in connection with third-party services and Meta Company Products. If you use our Services with such third-party services or Meta Company Products, we may receive information about you from them; for example, if you use the WhatsApp share button on a news service to share a news article with your WhatsApp contacts, groups, or broadcast lists on our Services, or if you choose to access our Services through a mobile carrier’s or device provider’s promotion of our Services. Please note that when you use third-party services or Meta Company Products, their own terms and privacy policies will govern your use of those services and products.', 'Back to top', 'How We Use Information', "We use information we have (subject to choices you make and applicable law) to operate, provide, improve, understand, customize, support, and market our Services. Here's how:", 'Our Services. We use information we have to operate and provide our Services, including providing customer support; completing purchases or transactions; improving, fixing, and customizing our Services; and connecting our Services with Meta Company Products that you may use. We also use information we have to understand how people use our Services; evaluate and improve our Services; research, develop, and test new services and features; and conduct troubleshooting activities. We also use your information to respond to you when you contact us.', 'Safety, Security, And Integrity. Safety, security, and integrity are an integral part of our Services. We use information we have to verify accounts and activity; combat harmful conduct; protect users against bad experiences and spam; and promote safety, security, and integrity on and off our Services, such as by investigating suspicious activity or violations of our Terms and policies, and to ensure our Services are being used legally. Please see the Law, Our Rights and Protection section below for more information.', 'Communications About Our Services And The Meta Companies. We use information we have to communicate with you about our Services and let you know about our terms, policies, and other important updates. We may provide you marketing for our Services and those of the Meta Companies.', 'No Third-Party Banner Ads. We still do not allow third-party banner ads on our Services. We have no intention to introduce them, but you may see other types of ads in the Updates Tab, home of features like Channels and Status.', 'Business Interactions. We enable you and third parties, like businesses, to communicate and interact with each other using our Services, such as Catalogs for businesses on WhatsApp through which you can browse products and services and place orders. Businesses may send you transaction, appointment, and shipping notifications; product and service updates; and marketing. For example, you may receive flight status information for upcoming travel, a receipt for something you purchased, or a notification when a delivery will be made. Messages you receive from a business could include an offer for something that might interest you. We do not want you to have a spammy experience; as with all of your messages, you can manage these communications, and we will honor the choices you make.', 'Back to top', 'Information You And We Share', 'You share your information as you use and communicate through our Services, and we share your information to help us operate, provide, improve, understand, customize, support, and market our Services.', 'Send Your Information To Those With Whom You Choose To Communicate. You share your information (including messages) as you use and communicate through our Services.', 'Information Associated With Your Account. Your phone number, profile name and photo, "about" information, last seen information, and message receipts are available to anyone who uses our Services, although you can configure your Services settings to manage certain information available to other users, including businesses, with whom you communicate.', 'Your Contacts And Others. Users, including businesses, with whom you communicate can store or reshare your information (including your phone number or messages) with others on and off our Services. You can use your Services settings and the “block” feature in our Services to manage who you communicate with on our Services and certain information you share.', 'Businesses On WhatsApp. We offer specific services to businesses such as providing them with metrics regarding their use of our Services.', 'Third-Party Service Providers. We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. We work with these companies to support our Services, such as to provide technical infrastructure, delivery and other systems; market our Services; conduct surveys and research for us; protect the safety, security, and integrity of users and others; and assist with customer service. When we share information with third-party service providers and other Meta Companies in this capacity, we require them to use your information on our behalf in accordance with our instructions and terms.', 'Third-Party Services. When you or others use third-party services or other Meta Company Products that are integrated with our Services, those third-party services may receive information about what you or others share with them. For example, if you use a data backup service integrated with our Services (like iCloud or Google Account), they will receive information you share with them, such as your WhatsApp messages. If you interact with a third-party service or another Meta Company Product linked through our Services, such as when you use the in-app player to play content from a third-party platform, information about you, like your IP address and the fact that you are a WhatsApp user, may be provided to such third party or Meta Company Product. Please note that when you use third-party services or other Meta Company Products, their own terms and privacy policies will govern your use of those services and products.', 'Back to top', 'How We Work With Other Meta Companies', 'As part of the Meta Companies, WhatsApp receives information from, and shares information (see here) with, the other Meta Companies. We may use the information we receive from them, and they may use the information we share with them, to help operate, provide, improve, understand, customize, support, and market our Services and their offerings, including the Meta Company Products. This includes:', 'helping improve infrastructure and delivery systems;', 'understanding how our Services or theirs are used;', 'promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities;', 'improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and', 'providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. For example, allowing you to connect your Facebook Pay account to pay for things on WhatsApp or enabling you to chat with your friends on other Meta Company Products, such as Portal, by connecting your WhatsApp account.', 'Learn more about the other Meta Companies and their privacy practices by reviewing their privacy policies.', 'Back to top', 'Assignment, Change Of Control, And Transfer', 'In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws.', 'Back to top', 'Managing And Retaining Your Information', 'You can access or port your information using our in-app Request Account Info feature (available under Settings &gt; Account). For iPhone users, you can learn how to access, manage, and delete your information through our iPhone Help Center articles. For Android users, you can learn how to access, manage, and delete your information through our Android Help Center articles.', 'We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. The storage periods are determined on a case-by-case basis that depends on factors like the nature of the information, why it is collected and processed, relevant legal or operational retention needs, and legal obligations.', 'If you would like to further manage, change, limit, or delete your information, you can do that through the following tools:', 'Services Settings. You can change your Services settings to manage certain information available to other users. You can manage your contacts, groups, and broadcast lists, or use our “block” feature to manage the users with whom you communicate.', 'Changing Your Mobile Phone Number, Profile Name And Picture, And “About” Information. If you change your mobile phone number, you must update it using our in-app change number feature and transfer your account to your new mobile phone number. You can also change your profile name, profile picture, and "about" information at any time.', 'Deleting Your WhatsApp Account. You can delete your WhatsApp account at any time (including if you want to revoke your consent to our use of your information pursuant to applicable law) using our in-app delete my account feature. When you delete your WhatsApp account, your undelivered messages are deleted from our servers as well as any of your other information we no longer need to operate and provide our Services. Deleting your account will, for example, delete your account info and profile photo, delete you from all WhatsApp groups, and delete your WhatsApp message history. Be mindful that if you only delete WhatsApp from your device without using our in-app delete my account feature, your information will be stored with us for a longer period. Please remember that when you delete your account, it does not affect your information related to the groups you created or the information other users have relating to you, such as their copy of the messages you sent them.', 'You can learn more here about our data deletion and retention practices and about how to delete your account.', 'Back to top', 'Law, Our Rights, And Protection', 'We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm.', 'Back to top', 'Our Global Operations', 'WhatsApp shares information globally, both internally within the Meta Companies and externally with our partners and service providers, and with those with whom you communicate around the world, in accordance with this Privacy Policy. Your information may, for example, be transferred or transmitted to, or stored and processed in, the United States; countries or territories where the Meta Companies’ affiliates and partners, or our service providers are located; or any other country or territory globally where our Services are provided outside of where you live for the purposes as described in this Privacy Policy. WhatsApp uses Meta’s global infrastructure and data centers, including in the United States. These transfers are necessary to provide the global Services set forth in our Terms. Please keep in mind that the countries or territories to which your information is transferred may have different privacy laws and protections than what you have in your home country or territory.', 'Back to top', 'Updates To Our Policy', 'We may amend or update our Privacy Policy. We will provide you notice of amendments to this Privacy Policy, as appropriate, and update the “Effective Date” at the top of this Privacy Policy. Please review our Privacy Policy from time to time.', 'Back to top', 'Privacy Rights for United States Residents', 'You can learn more about the consumer privacy rights that may be available to you, by reviewing the United States Regional Privacy Notice here.', 'Back to top', 'Contact Us', 'If you have questions or issues about our Privacy Policy, please contact us.', 'WhatsApp LLC', 'Privacy Policy', '1601 Willow Road', 'Menlo Park, California 94025', 'United States of America', 'Back to top', 'Download', 'Download', 'What we do', 'FeaturesBlogSecurityFor Business', 'Who we are', 'About usCareersBrand CenterPrivacy', 'Use WhatsApp', 'AndroidiPhoneMac/PCWhatsApp Web', 'Need help?', 'Contact UsHelp CenterAppsSecurity Advisories', 'Download', '2025 © WhatsApp LLC', 'Terms &amp; Privacy PolicySitemap', 'Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）']</t>
+  </si>
+  <si>
+    <t>['Privacy Policy – Giraffe Games', 'GIRAFFE GAMESâ\x80\x99 PRIVACY POLICY', 'Effective date : 25th May 2018', 'About us', 'We are a limited company (company number : 535897) and out registered office is:', 'Giraffe Games Limited', '26 Upper Pembroke Street,', 'Dublin 2', 'Giraffe Games is the â\x80\x98data controllerâ\x80\x99 for the personal data provided to us via the Giraffe Games Site and through the use of its Services. We are responsible for processing personal data in accordance with the General Data Protection Regulation (â\x80\x98GDPRâ\x80\x99), an EU wide Regulation for the protection of personal data.', 'This Privacy Policy explains:', '– What personal data we collect from you and why', '– How we use your personal data, and', '– The options you have in relation to your personal data.', 'Contact us', 'Contact Information', 'Giraffe Games Limited,', '26 Upper Pembroke Street,', 'Dublin 2', 'If you have any questions about this Policy, please contact us at contact@giraffe-games.com', 'The Privacy Policy, together with any game license agreement are to be read as a whole and form an integral part of the Terms of Use.', 'Giraffe Games Limited and its affiliates (â\x80\x9cGiraffeâ\x80\x9d, â\x80\x9cusâ\x80\x9d, â\x80\x9courâ\x80\x9d or â\x80\x9cweâ\x80\x9d) are dedicated to protecting the privacy rights of our users (â\x80\x9cusersâ\x80\x9d or â\x80\x9cyouâ\x80\x9d). This Privacy Policy (the â\x80\x9cPolicyâ\x80\x9d) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the â\x80\x9cSitesâ\x80\x9d) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the â\x80\x9cServiceâ\x80\x9d). If you have questions or concerns about our privacy policy or practices, please contact us at contact@giraffe-games.com .', 'AGE LIMITS', 'We do not knowingly process personal data belonging to anyone under the age of 16 or knowingly allow such persons to use our Services. No one under the age of 16 may provide any personal data. If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. If it is discovered that we process personal data of any individual under 16, this data will be deleted.', 'Facebook third party account login', 'If you choose to login with your Facebook account or other third party account (if applicable â\x80\x93 for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. Basic profile information (avatar, Facebook name, country) will be displayed to other users during game play and on public leader-boards. Signing in with Facebook allows us to offer other functionalities such as to invite and play with friends, create challenges for friends and see friendsâ\x80\x99 game progress. This is also to allow you to log in on multiple devices and synchronise progress across multiple devices on multiple platforms. If you would like to be signed in with your Facebook account, but would not like to have your image displayed to other players, you may use our â\x80\x98Hide meâ\x80\x99 option in the Settings to have your personal profile replaced with a dummy profile.', 'What data do we collect?', 'Giraffe collects information as described below.  Giraffeâ\x80\x99s primary goals in collecting and using information is to create your account, provide Services to you, improve our Service, contact you, conduct research and create reports for internal use.  We use third parties to store information on servers located in the European Union and may store information on servers and equipment in other jurisdictions from time to time. You are not required to provide personally identifiable information to visit the Site; however, in order to take advantage of certain features you may need to provide some personally identifiable information.', '– User Name and Password. In order to access your third party message accounts, you must enter your applicable user name(s) and password(s). To use the basic Services of the Site we do not store your password(s) on our server. If you wish to utilise advanced features of Site, such as automatic sign-in, storage of your and password(s) may be necessary.', '– Aggregate Usage Data. Giraffe may collect usage data and other information on all users, including data about their usage of the site and its various features, but it is not personally identifiable except as described below under the IP Addresses section.', '– Social Features. Whenever a social feature involves the disclosure of personally identifiable information about you to other people, Giraffe will either provide you with an opportunity to opt out of the disclosure or will seek your consent prior to making the disclosure.', 'Our Sites', 'While you are browsing Giraffeâ\x80\x99s Sites, your computerâ\x80\x99s operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically.  We may use this information to monitor, develop and analyse your use of the Service.', 'Facebook Connect', 'You need to be over 13 years old in order to use the Facebook Connect feature of the Services. Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. Should you give us such permission, we will store the information received based on your use of the Services. Please review Facebookâ\x80\x99s terms and conditions and privacy policy (here: https://www.facebook.com/about/privacy/update) because these third-party services are governed by their terms. Please note that your email address and the access token are encrypted.', 'Social Media (Features) and Widgets', 'The Site may from time to time include Social Media Features, such as the Facebook Like button and Widgets, such as the Share this button or interactive mini programs that run on our site. These Features may collect your IP address, which page you are visiting on our site, and may set a cookie to enable the Feature to function properly. Social Media Features and Widgets are either hosted by a third party or hosted directly on the Site. Your interactions with these features are governed by the privacy policy of the company providing it.', 'iOS, Android and Windows Phone Platforms', 'When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (â\x80\x9cMACâ\x80\x9d) address, international mobile equipment identity (â\x80\x9cIMEIâ\x80\x9d), the version of your operating system (â\x80\x9cOSâ\x80\x9d), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address).  This information is useful to us for troubleshooting and helps us understand usage trends. We may collect and process your location data to provide location related Services and advertisements. We may use various technologies to determine location, such as GPS, Wi-Fi or other network-based data such as IP address. Your GPS geo-location is not accessed without your consent. We will not share your GPS geo-location with third parties without your consent. Please note that we may share your anonymous location data with partners in order to improve the Services. If you no longer wish to allow us to track or use this information, you may turn it off at the device level.  Please note, the application may not work properly if we are unable to tell where you are coming from (Country specific). In addition, we create a unique user ID to track your use of our Service.  This unique user ID is stored in connection with your profile information to track the Giraffe games you are playing.   Log in You can log in to the Site using sign-in services (â\x80\x9cSN Serviceâ\x80\x9d) including  Facebook Connect, Appleâ\x80\x99s Game Center, Google+ and such other SN Service as may be available from time to time.  These services will authenticate your identity and provide you the option to share certain personal information with us such as your name, email address, and resume to pre-populate our sign up form.  Services like Facebook Connect give you the option to post information about your activities on this Web site to your profile page to share with others within your network. We may collect and record information through the SN Service in accordance with the policies and terms of that SN Service.  The information we collect when you connect your user account to an SN Service may include: (1) your name, (2) your SN Service user identification number and/or user name, (3) locale, city, state and country, (4) sex, (5) birth date, (6) email address, (7) profile picture or its URL, and (8) the SN Service user identification numbers for your friends that are also connected to Giraffeâ\x80\x99s game(s). If you want us to delete the data we receive from the SN Service about you, please contact us at support@giraffe-games.com.', 'Invite a Friend', 'Giraffe may offer you the opportunity to invite your contacts from a SN Service (such as your Facebook friends) so that those contacts can be located in Giraffe games and/or you can invite them to join you in Giraffe games.  Such contact information will be used only for the purpose of sending communications to the addressee.  You or the third party may contact us at support@giraffe-games.com to request the removal of this information from our database to the extent Giraffe stores any of this information.', 'Customer Service', 'We may collect your email address when you contact our customer service group and we may use that email address to contact you about your gaming experience with Giraffe games and notify you about company news and promotions. If you no longer wish to receive certain email notifications you may opt-out at any time by following the unsubscribe link located at the bottom of each communication or by emailing us at support@giraffe-games.com.', 'Push Notifications', 'We may occasionally send you push notifications through our mobile applications to send you game updates, high scores and other service related notifications that may be of importance to you.  You may at any time opt-out from receiving these types of communications by turning them off at the device level through your settings.', 'Game Data Collection', 'Whenever you play our games, we collect anonymous data using the service of http://www.gameanalytics.com and sometimes use http://www.flurry.com/solutions/analytics(or such other service providers as we may deem appropriate).   The data thereby collected is presented to us in an anonymous form to include, for example, the percentage of users who complete a particular level.', 'Other Collection', 'We may also acquire information from you through (1) your access and participation in message boards on the Service, (2) your participation in surveys regarding the Service or (3) your participation in a sweepstakes or contest through the Service. We may provide you the opportunity to participate in a sweepstakes or contest through our Service. If you participate, we will request certain personal information from you.  Participation in these sweepstakes and contests are voluntary and you therefore have a choice whether or not to disclose this information.  The requested information typically includes contact information (such as name and shipping address), and demographic information (such as zip code). We use this information to notify winners and award prizes, to monitor traffic or personalise the Service.  We may use a third party service provider to conduct these sweepstakes or contests; that company is prohibited from using your usersâ\x80\x99 personal information for any other purpose.', 'Cookies', 'A cookie is a small text file that we transfer to your computer and/or device, to identify a userâ\x80\x99s computer/device and to â\x80\x9crememberâ\x80\x9d things about your visit, such as your preferences or a user name and password.  Information contained in a cookie may be linked to your personal information, such as your user ID, for purposes such as improving the quality of our Service, tailoring recommendations to your interests, and making the Service easier to use.  You can disable cookies at any time, although you may not be able to access or use features of the Service. We may feature advertisements served by third parties that deliver cookies to your computer/device so the content you access and advertisements you see can be tracked.  Since the third party advertising companies associate your computer/device with a number, they will be able to recognise your computer/device each time they send you an advertisement.  These advertisers may use information about your visits to our Service and third party sites and applications in order to measure advertisement performance and to provide advertisements about goods and services of interest to you. This Policy does not apply to, and we are not responsible for the data collection practices of these third party advertisers, and we encourage you to check their privacy policies to learn more about their use of cookies and other technology. You cannot use the Sites without accepting the use of cookies.  The cookies are used to support analytics and logged in users on the Site.', 'Clear Gifs (Web Beacons/Web Bugs)', 'We employ or our third party tracking utility partner employs a software technology called clear gifs (a.k.a. Web Beacons/Web Bugs), that help us better manage content on our site by informing us what content is effective.  Clear gifs are tiny graphics with a unique identifier, similar in function to cookies, and are used to track the online movements of Web users.  In contrast to cookies, which are stored on a userâ\x80\x99s computer hard drive, clear gifs are embedded invisibly on Web pages or e-mails and are about the size of the period at the end of this sentence. We may associate this information with your IP address or device identifier but do not tie the information gathered by clear gifs to our customersâ\x80\x99 personal information.', 'Mobile Analytics', 'We use mobile analytics software to allow us to better understand the functionality of our Mobile Software on your device. This software may record information such as how often you use the application, the events that occur within the application, aggregated usage, performance data, and where the application was downloaded from. We do not link the information we store within the analytics software to any personal information you submit within the mobile application.', 'Third Party Services', 'Our services may contain third party tracking tools from Google Analytics, our service provider. Such third party may use cookies, APIs, and SDKs in our services to enable them to collect and analyse user information on our behalf. The third party may have access to information such as your device identifier, MAC address, IMEI, locale (specific location where a given language is spoken), geo-location information, and IP address for the purpose of providing their services under their respective privacy policies. This Policy does not cover the use of tracking tools from Google Analytics.  We do not have access or control over Google Analytics.', 'Ad Networks', 'We do not serve ads within the Sites, but we do serve ads within our games and the advertisers we use have their own terms of service which are compatible with the terms of services of the mobile platforms. The option to opt out of advertising is not available for all of our games.  When available, advertisement can be blocked by making an in app purchase.  The advertisers may collect and use information about you, such as your Service session activity, device identifier, MAC address, IMEI, geo-location information and IP address.  They may use this information to provide advertisements of interest to you. In addition, you may see our games advertised in other services.  After clicking on one of these advertisements and installing our game, you will become a user of our Service.  In order to verify the installs, a device identifier may be shared with the advertiser.', 'Why do we need your personal data?', 'We use information collected through our Service for purposes described in this Policy or disclosed to you in connection with our Service. For example, we may use your information to:', '– create game accounts and allow users to play our games;', '– identify and suggest connections with other Giraffe users;', '– operate and improve our Service;', '– understand you and your preferences to enhance your experience and enjoyment using our Service;', '– respond to your comments and questions and provide customer service;', '– provide and deliver products and services you request;', '– send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages;', '– communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners;', '– enable you to communicate with other users; and', '– link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services.', 'Disclosure of Your information', 'We do not share your personal information except as approved by you or as described below:', '– We may engage other companies and individuals to perform services on our behalf. An example of these services include analysing data and providing customer support. These agents and service providers may have access to your personal information in connection with the performance of services for Giraffe.', '– We may release your information as permitted by law, such as to comply with a court order, or when we believe that release is appropriate to comply with the law; investigate fraud, respond to a government request, enforce or apply our rights; or protect the rights, property, or safety of us or our users, or others.  This includes exchanging information with other companies and organizations for fraud protection.', '– Giraffe may share your information in connection with any merger, sale of our assets, or a financing or acquisition of all or a portion of our business to another company.  You will be notified via email and/or notice on our site of any change in ownership or users of your personal information.', '– We may share aggregate or anonymous information about you with advertisers, publishers, business partners, sponsors, and other third parties.', 'Changes to the Policy', 'We may update this privacy policy to reflect changes to our information practices. If we make any material changes we will notify you by means of a notice on this Site prior to the change becoming effective. We encourage you to periodically review this page for the latest information on our privacy practices.', 'Security', 'We take reasonable measures to protect your information from unauthorised access or against loss, misuse or alteration by third parties. Although we make good faith efforts to store the information collected on the Service in a secure operating environment that is not available to the public, we cannot guarantee the absolute security of that information during its transmission or its storage on our systems.  Further, while we attempt to ensure the integrity and security of our network and systems, we cannot guarantee that our security measures will prevent third-party â\x80\x9chackersâ\x80\x9d from illegally obtaining access to this information.  We do not warrant or represent that your information will be protected against, loss, misuse, or alteration by third parties. No method of transmission over the Internet, or method of electronic storage, is 100% secure, however.  Therefore, we cannot guarantee its absolute security.', 'Access to Personal Information', 'If your personal information changes, or if you no longer desire our service, you may correct, update, or delete inaccuracies by making the change within your account settings or by contacting us at support@giraffe-games.com.  We will respond to your access request within 30 days.', 'Data Retention', 'We will retain your information for as long as your account is active or as needed to provide you services.  If you wish to cancel your account or request that we no longer use your information to provide you services, contact us at support@giraffe-games.com.  We will retain and use your information as necessary to comply with our legal obligations, resolve disputes, and enforce our agreements.', 'What are your rights?', 'You have many rights in relation to your data under the GDPR, if you would like to exercise one of these rights, please contact us at: contact@giraffe-games.com', 'You have the right to ;', 'Access. You have a right to know what information we hold about you and to have the information communicated to you. Please contact us letting us know that you wish to exercise your right of access and what information in particular you would like to receive. We are entitled to request reasonable evidence to verify your identity before we provide you with information. Please note that we may not be able to provide all the information you ask for, for instance if the information includes personal information about another person or the request would require disproportionate effort. If we are not able to provide you with information that you request we will communicate our reasons to you. We will always respond within 1 month of receipt of your request and verification of your identity.', 'Correction of personal data. We try to keep the information that we hold about you accurate and up to date. Should you realise that any of the information that we hold about you is incorrect, please let us know (see our contact information in this policy) and we will correct it as soon as possible.', 'Deletion of your personal data. In some circumstances you have the right for your personal information to be erased. Executing this request will depend on you deleting our games from your devices and clearing cookies from any device where you have accessed our Site. We may have an overriding reason for retaining data in this event, in which case we will communicate our reasons to you. In some instances, personal information about you that is visible through gameplay such as username, avatar, your high scores may be cached on other playersâ\x80\x99 devices and we may not be able to remove or update that data from those devices.', 'Data portability. You may have the right to request that data which you have provided to us is exported and provided to you, so you can transfer this to another data controller, or that we transfer this data directly to another data controller. (contact us if you would like more information)', 'Restriction of processing. You may have the right to request a restriction of the processing of your personal data, for example as an intermediate measure if we are investigating your claim for inaccurate data held.', 'Right to object. You have the right to object to the processing of personal data about you which is processed on the grounds of legitimate interests', 'How long do we keep your data for?', 'We will retain your information for as long as your account is active or as needed to provide you services.  If you wish to cancel your account or request that we no longer use your information to provide you services, contact us at support@giraffe-games.com.  We will retain and use your information as necessary to comply with our legal obligations, resolve disputes, and enforce our agreements.', 'International Transfer', 'Under EU data protection law, personal data transferred outside of the EU must have a legal mechanism for transfer (in order to ensure that the same protections are afforded to your personal data once it travels outside of the EU jurisdictions). Our hosted servers store your data in the EU. We take steps to ensure that there are adequate safeguards and mechanisms in place (including the use of EU model clauses and verifying the presence of agreements to privacy shield) to allow the transfer of your information across borders and outside of the EEA that might arise where data is processed by our third party service providers.', 'This privacy policy was updated on May 23, 2018.', 'Contact Information', 'Giraffe Games Limited,', '26 Upper Pembroke Street,', 'Dublin 2', 'For queries about how we protect your personal data or about this Policy, please contact us at contact@giraffe-games.com', 'Copyright Â© Giraffe Games 2016', 'Copyright © Giraffe Games 2016']</t>
+  </si>
+  <si>
     <t>privacy policy privacy policy noted policy english language version privacy policy term use govern relationship panda caribbean limited english version govern also use automatic translation tool like google translate view document language translation revision posted page</t>
   </si>
   <si>
@@ -709,6 +2340,27 @@
     <t>privacy policy snapchat privacy snap valuespolicypolicyyour resource understanding rule policy across snapchatcommunity guidelineswe created guideline encourage broadest range selfexpression striving make sure snapchatters use service safely every day content guidelinesadditional standard algorithmic recommendation beyond creator friend subscriber creator monetization policy content must adhere policy eligible monetization advertising policiesthese apply aspect advertisement served snapcommercial content policyapplies commercial content snap platform ad served snap privacyprivacy policythis policy explains collect use data control information privacy principlesat snap make privacy priority know trust earned every time use snapchat product service privacy productsaving snap designed privacy mind control whether snap saved within snapchatprivacy securityfeatures recommendation help secure account teen snapchatadditional protection teen snapchatsnap adshow collect use share data respect ad privacy centerprivacy policy tend pretty long pretty confusing thats best make privacy policy brief clear easytoreadlearn safetysafety centerhere step take help stay safesafety policieswe created safety policy help community enhance relationship friend family worldsafety resourceswe work industry expert nongovernmental agency provide resource support snapchatters need safety advisory boardmeet snap safety advisory board memberscouncil digital wellbeingmeet snap council digital wellbeingdigital wellbeing indexsnaps digital wellbeing index highlight gen z attitude perception life online information law enforcementsnap committed assisting law enforcement respecting privacy right usersfinancial sextortionwe work industry expert nongovernmental agency provide resource support snapchatterscombating illicit drugswe work industry expert nongovernmental agency provide resource support snapchattersreport safety concernif ever experience harassment bullying safety concern always report right u information parentsthe parent guide snapchat cover snapchat work key protection offer teen use parental control answer common questionslearn transparencytransparency reporttransparency reporttwice year publish transparency report provide insight visibility nature volume content account reported usglossarydefinitions commonly used term policy operational practice discussed transparency report previous reportstransparency report archive regional informationeuropean unioneu specific informationcalifornia california specific informationaustralia australia specific informationindiaindia specific information resourcesresearchersaccess researchersads galleryfind european union ad delivered last month commercial content thats live right aboutin transparency report disclose data regarding safety effort across platform provide additional context insight safety principle policy practice well link various safety privacy resourceslearn news privacyprivacyprivacy center privacy principle privacy product privacy policy teen snapchat snap ad privacy security privacy policy effective april welcome snap inc privacy policy policy explains collect use data control information looking quick summary privacy practice check page video youre looking specific product privacy information example process chat snap take look privacy product page addition document also show inapp notice provide information product service youre spectacle user learn collect use data spectacle supplemental privacy policy transparency one core value snap believe shouldnt surprise data collect use thats upfront process example process information provide personalized experience including show content information relevant experience well relevant advertisement understanding interest preference help u provide better product experience furthermore believe personalized experience come expense privacy like real life moment want share privately close friend others want share publicly thats day one philosophy delete content default give snapchatters control providing tool allow decide happens content like share save policy cover snapchat app well product service feature bitmoji spectacle advertising commerce initiative read service policy talking also see u refer term mean term service agree sign service finally see term snapchatter often using shorthand user service let get started control information control information control information setting core part snapchat experience access update delete information decide contact download data within snapchat app give detail type setting available link data download tool provide instruction delete data account want control information provide range tool including access update information access edit basic account information right service navigate setting see option available delete information want delete account learn also delete information within service like content youve saved memory content youve shared ai spotlight submission control see content weve built number tool let choose share content case may want share content friend instance may want share public learn go control contact snapchat intended close friend family thats weve built control help decide contact receive unwanted communication always block report person go learn change permission case change permission time example default findable others phone number andor email address provided longer want findable always change setting provided access phone third party platform contact make friending easier change later app setting course certain feature service like finding friend contact book wont work opt promotional message option opt unsubscribe promotional email message sent sm messaging platform follow instruction message like unsubscribe link similar functionality download data make request download data tool export copy snapchat information object processing depending live particular data processing may right object processing information get bit technical weve explained detail set advertising preference try show ad think relevant interest youd like less personalized experience change advertising setting snapchat app learn tracking use iphone io specific requirement apply weve specified information collect section provides detail information collect provide u collect use snapchat information receive company apps youve connected snapchat account sometimes may also collect additional information permission use service snapchat collect information provide u generate information use service case receive data others let break detail information provide many service require set account ask provide u account detail information like name username email address birthday phone number set profile youll also provide u profile detail like bitmoji profile picture use commerce product buy something like latest sneaker may ask payment related information like physical address ship product payment information process payment transaction history course youll also provide u information send save within service including content information content content share generate ai feature content input including text image video audio precise location engagement used generate content response output consider information private content communication like snap chat friend voice video call content saved eye content share particular audience like private friend story story set friend private story end spectrum information send save within service may public content accessible everyone public story content including story set everyone shared story community story spotlight snap map submission public profile information keep mind snapchatters view snap chat content always screenshot content save copy outside snapchat app please dont send message share content wouldnt want someone save share lastly contact support content communication shared support safety team communicate u way including research effort like response survey consumer panel research question well collect whatever information provide need resolve question information generate use service use service collect information service youve used youve used help u better understand way community us service make improvement includes usage information information interact service example lens view apply premium subscription story watch often interact snapchatters content information information content create provide engagement camera creative tool interaction ai metadata example information content like date time posted viewed content information includes information based content image video audio post spotlight basketball game may use information show content spotlight basketball also includes device information hardware software operating system device memory advertising identifier apps installed browser type information device sensor measure motion device compass microphone including whether headphone connected information wireless mobile connection location information ip address information collected cooky similar technology depending setting cooky pixel small graphic data recognize user activity often user visited website web storage unique advertising identifier log information detail youve used service access time page viewed ip address unique identifier like cooky youve explicitly granted devicelevel permission device information may also include information device phonebook contact related information image information device camera photo microphone like ability take photo video view stored photo video access microphone record audio recording video location information precise location method like gps signal data receive others last category data collect information may receive others user affiliate third party includes linked thirdparty service data information get link snapchat account another service data advertiser information advertiser app developer publisher third party help target measure performance ad contact info snapchatters third party another snapchatter uploads contact list includes information may combine information better understand may want communicate provide u contact information may use determine communicate way like sm email messaging service data relating potential violation term may receive information third party including website publisher social network provider law enforcement others potential violator term service community guideline information permission additionally may instance interact service ask permission collect additional information example accessing device camera roll device third party contact book use information section explains use information collect among thing use information collect provide personalized product service work hard build improve walk purpose use information detail youd like see mapping data collect purpose collect table keep thing running ie operate deliver maintain service use information collect order operate deliver maintain service example delivering snap want send friend share location snap map show suggestion like place might like neighborhood content others posted map friend theyre sharing location also use information help keep product date example make sure service work latest operating system device personalize experience give context offer personalized service snapchatters one way showing content relevant think may enjoy based information share u use information across different area service order add context snapchat experience example automatically tag content label based content location time day there dog photo may searchable memory term dog show map location created memory inform u youre dog surface fun dog video dog food ad part service spotlight personalization also help suggesting friend recommending new friend send snap based snap may show recommended place snap map generate sticker even generate snap content using ai infer interest based content activity customize content show including ad example watch barista content spotlight talk ai favorite espresso machine save lot coffeerelated snap memory may highlight coffee shop snap map visit new city show content coffee may find interesting relevant interact lot music venue may use show ad upcoming show town personalization also includes tailoring experience based interact friend including showing content friend create like enjoy spotlight place recommendation popular friend goal continuously provide relevant interesting content example watch lot sport content skip content hair makeup tip recommendation algorithm prioritize sport makeup tip learn understand snapchatter preference rank moderate content believe critical also balance benefit personalization snapchatters expectation privacy example may automatically tag snap save memory based content within eg snap contained dog use tag personalize experience make recommendation show ad showing spotlight snap containing dog use private content communication send friend personalize experience make recommendation show ad provide relevant ad another way provide personalized service ad show use interest preference information weve collected personalize target measure ad think ad best theyre relevant thats try select right ad show right time example youve interacted ad video game infer like video game show similar ad wont ad see similar content strategy try ensure receive variety ad also use information avoid showing ad probably wont interested example ticketing site tell u youve previously bought ticket movie stop showing ad learn different type advertising choice ad receive learn collect use share information advertising purpose note information collected cooky technology may use technology collect information interact service offer one partner example may use information collected advertiser website show relevant ad web browser set accept cooky default prefer usually remove reject browser cooky setting browser device keep mind though removing rejecting cooky could affect availability functionality service learn partner use cooky service choice please check cookie policy develop improve feature algorithm machine learning model team constantly coming new idea feature way improve service order also develop improve algorithm machine learning model expression algorithm comb significant amount data find pattern make prediction make feature service work including generative ai feature artificial intelligence capable generating text image medium using generative model generative ai model learn pattern structure input training data generate new data similar characteristic use algorithm machine learning model personalization advertising safety security fairness inclusivity augmented reality prevent abuse term service violation example algorithm machine learning model take account conversation snapchatters ai improve response ai information help u decide kind improvement make always focused privacy dont want use personal information necessary develop feature model analytics order understand build improve service need understand trend demand feature example monitor metadata trend group chat use help decide whether change part feature like maximum size group studying data snapchatters help u see trend way people use service help inspire u improve snapchat larger scale perform analytics order identify monitor analyze trend usage based information among thing create information user help u understand demand research conduct research better understand general consumer interest trend service used others community information along analytics described help u understand community service fit life community also engage research development develop new technique technology eg new machine learning model hardware spectacle result research sometimes used feature snapchat sometimes publish paper thing like overall behavior consumer trend aggregated data across user base contain private information specifically enhance safety security service use information enhance safety security service verify snapchatter identity prevent fraud unauthorized illegal activity example provide twofactor authentication help protect account send email text message notice suspicious activity also scan url sent snapchat see webpage potentially harmful give warning contacting sometimes well get touch promote new existing feature includes sending snapchatters communication snapchat email sm messaging platform permitted example may use snapchat app email sm messaging platform share information service promotional offer think may interest time need communicate provide information alert send message user ask u deliver request may include sending communication snapchat email sm messaging platform permitted deliver account status update security alert chat friending reminder may also include fulfilling user request send invite snapchat content nonsnapchatters support ask help want get support quickly possible order provide snapchatter community business partner help needed resolve issue service often need use information collected respond enforce term policy use data collect enforce term law includes enforcing investigating reporting conduct violates term policy law responding request law enforcement complying legal requirement example unlawful content posted service may need enforce term policy case may also use share information cooperate law enforcement request escalate safety issue law enforcement industry partner others comply legal obligation check transparency report learn purpose permission additionally may instance interact service ask permission use information new different otherwise specific way share information section explains share information information may include reason sharing information including need transfer outside country collected recipient reason sharing snapchat provide service community may share information friend snapchat snapchatters example content post story status premium subscriber viewed friend allow see control information section setting control see family center participant enabled family center share information connected teen account parent guardian provide insight account used example friend snapchat friend may sharing location share message content learn public feature snapchat private friend also offer public feature allow opt showcase best snap world spotlight snap map public profile snap may also discoverable outside snapchat example web information like username bitmoji visible public learn thirdparty apps sometimes provide feature allow connect thirdparty apps decide connect snapchat account thirdparty app share additional information direct u service provider share information service provider process information behalf example rely service provider facilitate payment measure optimize performance ad protect service share private communication maintain list category service provider business integrated partner share information business integrated partner order provide service example use opentable within snapchat reserve table include private communication maintain list partner antifraud partner share information device usage information industry partner working prevent fraud legal safety security partner share information necessary following legal safety security reason comply valid legal process governmental request applicable law rule regulation investigate remedy enforce potential term service community guideline violation protect right property safety u user others detect resolve fraud security concern affiliate snap inc consists different subsidiary owned u may share information within internal subsidiary needed carry service purpose merger acquisition sell negotiate sell business buyer possible buyer may transfer information successor affiliate part transaction integrated partner service may contain content integration offered integrated partner example include integration lens camera editing tool provide scan result thirdparty developer integration integration may providing information integrated partner well snap responsible partner collect use information always encourage review privacy policy every thirdparty service visit use including third party interact service learn integration snapchat io use apple truedepth camera improve quality lens note however information used real time dont store information server share third party international data transfer service connect friend around world make possible may collect personal information transfer store process united state country outside live whenever share information outside live ensure safeguard place protect data required law live want learn see region specific information section detail long keep information section provide information long keep information keep information also highlight may need keep information comply law court obligation general rule keep information long tell u otherwise long need provide service required law example store something memory keep long need chat friend system designed delete chat send within hour friend read unless youve changed default setting decide save whether retain data depends specific feature setting youre using service factor consider decide long keep information need information operate provide service example store basic account detail like name phone number email address maintain account thing expect service weve described within privacy policy example maintain list friend ask u delete since friend key expressing similarly keep shared list contact ask u remove app setting note updating device permission may remove contact youve previously shared snapchat learn conversely snap chat sent snapchat deleted default server within hour detect theyve opened recipient expired unless youve changed default setting decide save something case honor choice information example store location information different length time based precise service use location information associated snap like saved memory posted snap map spotlight well retain location long store snap pro tip see location data retain downloading data long need retain information comply certain legal obligation need legitimate purpose prevent harm investigate possible violation term service policy investigate report abuse protect others take look privacy product page support page detail specific retention period product although system designed delete information automatically promise deletion take place specific time case need comply legal requirement store data stop u deleting information example receive notice court asking u keep copy content reason may keep copy data get report abuse term policy violation account content created content created snapchatters flagged others system abuse term policy violation finally may also keep certain information backup limited period time required law latest information long store different type content check support site region specific information depending live may additional right section provides detail region specific information best keep policy simple possible depending live additional right may specific information aware please take look list see apply australia brazil canada europe mexico south korea turkey united state note u state privacy notice applies resident certain u state implemented statelevel privacy law jurisdiction require state legal basis processing data particular purpose find information audience service directed individual year older service directed child age must confirm year older order create account use service actual knowledge age minimum age person may use service state province country without parental consent greater stop providing service delete account data addition may also limit collect use store information snapchatters case mean unable provide certain functionality people age update privacy policy may update privacy policy time time give head make change think know may change privacy policy time time well let know one way another sometimes well let know revising date top privacy policy thats available website mobile application time may provide additional notice adding statement website homepage providing inapp notification contact u question information wish contact data protection officer dpo contact u company snap inc career news privacy safety community snapchat support spectacle support community guideline advertising snapchat ad advertising policy political ad library brand guideline promotion rule legal term policy law enforcement cookie policy cookie setting report infringement privacy policy term service languageenglish u</t>
   </si>
   <si>
+    <t>uber privacy notice rider order recipient skip main content uberride drive business uber eats u offering uber work sustainability newsroom investor relation autonomous blog career result en help log sign uberlog sign uber privacy notice rider order recipient use uber trust u personal data committed keeping trust start helping understand privacy practice notice describes personal data data collect used shared choice regarding data recommend read along privacy overview highlight key point privacy practice uber privacy notice driver delivery people previous version privacy notice overview ii data collection us data collect use data core automated process cooky related technology data sharing disclosure data retention deletion iii choice transparency iv legal information data controller data protection officer legal base using data legal framework data transfer update privacy notice overview scope notice applies use ubers apps website request receive product service including ride delivery notice describes collect use data request receive product service ubers apps website except use uber freight careem uber taxi south korea notice specifically applies request receive mobility service including ride package delivery return service uber connect via uber account rider request receive food product service delivery pickup including via uber eats postmates account guest checkout feature allow access delivery pickup service without creating andor signing account order recipient receive service ubers apps website requested account owner guest user including receive ride delivery service ordered uber health central uber direct uber business customer collectively enterprise customer friend family member individual account owner including via uber connect receive gift card rent vehicle uber car rental renter notice describe ubers collection use data use uber provide instead request receive service ubers app website including driver delivery person ubers notice describing collection use data available use uber either request receive provide service referred user notice privacy practice subject applicable law place operate type data processing law require allow prohibit vary globally therefore travel across national state geographic border ubers data processing practice described notice may differ home country territory addition please note following use uber argentinadown small agency access public information role regulating body law responsible receiving complaint report presented data subject believe right impacted violation local data protection regulation australiadown small may contact uber regarding compliance australian privacy principle contact addressed ubers customer service andor relevant privacy team within reasonable timeframe may also contact office australian information commissioner concern regarding compliance brazildown small please go information regarding ubers privacy practice relates brazil general data protection law lei geral de proteo de dado lgpd colombia honduras jamaicadown small rider driver used notice known respectively lessee lessor european economic area eea united kingdom uk switzerlanddown small due data protection law region including european union general data protection regulation gdpr uber perform data collection us described notice eea uk switzerland data collection us indicated asterisk use uber outside region data may collected used purpose indicated asterisk kenyadown small may contact uber question regarding ubers compliance request exercise right kenya data protection act may also contact office data protection commissioner concern regarding compliance exercise right mexicodown small please go information regarding ubers privacy practice relates mexico personal data protection law ley federal de proteccin de datos personales en posesin de los particulares information regarding uber money processing personal data nigeriadown small may contact uber regarding ubers compliance request exercise right nigeria data protection act may also contact nigeria data protection commission concern regarding compliance quebec canadadown small may contact uber question ubers use data purpose automated decision making including regarding factor considered connection decision request correction personal data relating decision request review decision uber personnel switzerlanddown small uber switzerland gmbh stockerstrasse zrich switzerland ubers appointed representative purpose federal act data protection may contacted mail relates act taiwandown small please see information measure adopted uber conducting crossborder data transfer accordance taiwan personal data protection act relevant regulation well related information united statesdown small please go information regarding ubers privacy practice relates u state privacy law including california consumer privacy act use uber nevada washington please go information regarding ubers practice relates collection use consumer health data state privacy law please contact u question regarding practice particular country region ii data collection us data collect uber collect data provide use service source please go summary data collect use uber collect following data data provide includes data category data type account information collect data create update uber account address email first last name login name password phone number payment method including related payment verification information profile picture setting including accessibility setting preference uber partner loyalty program information demographic data collect demographic data necessary enable certain feature example collect date birth andor age verify eligibility use agerestricted product service uber teen purchase alcohol tobacco cannabis product collect infer gender enable woman rider preference marketing advertising may also collect demographic data user survey age date birth gender inferred gender using first name identity verification information refers data collect verify account identity governmentissued identification document driver license passport may contain identification photo number expiration date date birth gender usersubmitted selfies user content refers data collect contact uber customer support inquiry use feature enable create list review restaurant merchant upload photo recording including submitted purpose customer support provide rating feedback driver delivery people restaurant merchant provide feedback regarding please go information rating provided user determined used chat log call recording rating feedback user created list review restaurant merchant uploaded photo recording including inapp audio recording travel information collect travel itinerary information book bus train flight travel ubers apps datestimes travel data collected use service includes data category data type location data request ride track driver location trip link data account allows u display trip also determine approximate location determine precise location allow u setting phone collect precise location time request ride order ride finished order delivered also collect data uber app open phone screen use uber without letting u collect precise location however may less convenient including type location phone instead allowing u detect see choice transparency section information control whether uber may collect precise location data approximate location precise location triporder information refers detail collect trip order including order placed via guest checkout feature payment information including amount charged payment method proof delivery including photo signature special instruction allergy food preference statistic derived past triporder information average cancellation rate total tripsorders trip order detail including date time requested pickup dropoff address distance traveled restaurant merchant name location item ordered usage data refers data interact ubers apps website app crash system activity access date time app feature page viewed browser type device data refers data device use access uber advertising identifier device motion data device ip address unique device identifier hardware model mobile network data operating system version preferred language communication data refers data collect communicate driver delivery people ubers apps communication type phone text message content including recording phone call solely user notified recording advance date time data source include data category data type law enforcement official public health official government authority name contact information information relating law enforcement health investigation marketing partner service provider includes bank connection cash back program data resellers activity information name contact information user device identifier service provider help u verify identity detect fraud confirmation whether account information relates known person name contact information information relating wireless carrier associated phone number information governmentissued identification document driver license passport identification number expiration date date birth gender uber account owner refers uber account owner request service friend family member enable request service account enterprise customer name contact information triporder info location uber business partner account creation access apis uber may receive data business partner create access uber account payment provider social medium service apps website use ubers apis whose apis uber us information received uber business partner depends partner use create access uber account api used uber business partner debit credit card uber may receive data business partner connection debit credit card issued financial institution partnership uber extent disclosed term condition card debit credit card activity information user others providing information connection customer support issue claim dispute name evidence relating accident conflict claim dispute may include photo recording user participating ubers referral program example referred uber another user receive data user name contact information use data uber us data enable reliable convenient transportation delivery product service also use data enhance safety security user service prevent detect fraud marketing advertising enable communication user customer support research development send nonmarketing communication user connection legal proceeding provide service uber us data provide personalize maintain improve service data us data used includes creating updating account account demographic location enabling service feature includes enabling navigation pickup dropoffs calculating eta tracking progress ride delivery matching available driver delivery people request transportation delivery enabling feature involve data sharing eta sharing fare splitting enabling accessibility feature enabling feature involve account linking linking uber partner loyalty program facilitating optimizing rental car reservation pickup dropoff uber rent account data source demographic device rating travel calculating riderrecipient price driverdelivery person fare location triporder info processing payment enabling payment emoney product uber money account demographic data source triporder info personalizing account example may present personalized restaurant food recommendation trip suggestion based prior order trip delivery location account demographic data source triporder info providing trip delivery update generating receipt account triporder info informing change term service policy account triporder info performing necessary operation maintain service including troubleshoot software bug operational problem account device usage safety security fraud prevention detection uber us data help maintain safety security service user data us data used includes verifying account identity compliance safety requirement includes verifying say crosschecking account information provide signup name email telephone number date birth payment information thirdparty database verifying account used someone else collecting id number andor photo id completing verification confirm id valid unaltered account associated document collecting realtime selfie compare photo id confirm person verifying identity andor age collecting photo id receive delivery agerestricted item like alcohol tobacco cannabis use product like uber rent uber connect verifying rent bike scooter uber wearing helmet mandatory safety gear collecting realtime selfie using object verification technology verifying eligibility subscribe uber one student membership account data source thirdparty database identity verification info user content preventing detecting combating fraud including guest user account communication user data source driver data device identity verification info location triporder info usage predicting helping avoid pairing user may result increased risk conflict one user previously given low instance one star rating account triporder info including cancellation rate usage user content rating reported incident providing live support safety expert trip delivery account phone user name vehicle detail location triporder info user content marketing advertising uber us data except guest user data market service uber partner data us data used includes personalizing marketing communication ad relating uber product service offered company example uber may send push notification suggesting favorite destination merchant inapp message offering discount promotion product merchant similar youve previously ordered display personalized ad uber company apps website personalize sponsored listing discount promotion restaurant merchant available uber account data source demographic including inferred gender device location triporder info usage displaying ad targeted based data current trip delivery request including time request service requested example request trip supermarket may display inapp ad thirdparty product may available supermarket account data source demographic including inferred gender device location triporder info usage measuring effectiveness marketing communication ad described account device usage enable communication user data us data used includes example driver may message call confirm pickup location may call driver retrieve lost item restaurant delivery person may contact information order account device usage customer support data us data used includes includes investigating addressing user concern monitoring improving customer support response process identifying potential participant research study relating customer support issue account communication device identity verification info data source location travel information usage user content triporder info research development data us data used includes use data analysis research product development including training machine learning model help u make service convenient easytouse enhance safety security service develop new service feature account communication demographic device identity verification info data source location travel information usage user content triporder info nonmarketing communication data us data used includes includes survey communication regarding election ballot referendum political process relate service example may notify ballot measure pending legislation relating ubers service live account location legal proceeding requirement data us data used includes use data investigate address claim dispute relating use ubers service satisfy requirement applicable law regulation operating license agreement insurance policy pursuant legal process governmental request including law enforcement account communication demographic device identity verification info data source location travel information usage user content triporder info core automated process uber us automated process enable certain part service including function essential business matching pricing fraud prevention detection uber relies automated process enable essential part service including matching pairing user requesting providing transportation andor delivery service pricing calculating amount owed service fraud detection prevention process allow uber provide seamless safe experience million user globally every day section describes automated matching pricing fraud prevention detection process work including impact uber experience personal nonpersonal data used enable process may contact uber question concern regarding process matchingdown small uber us algorithm efficiently match rider driver delivery people order recipient help u minimize wait time enable efficiency driver delivery people matching process triggered request transportation delivery uber algorithm evaluate various factor determine best match including location requested destination proximity availability driver delivery people traffic condition historical data including market whether specific rider driver previously reported negative experience trip delivery request communicated driverdelivery person matched process trip order accepted send confirmation match driverdelivery person constantly refining matching process provide best experience user platform may consider different factor depending location use uber additional information ubers matching process available pricingdown small request transportation delivery uber us algorithm determine price pay based variety factor including type service request instance uberx uberxl uber black location estimated time distance destination availability proximity driver delivery people time day traffic condition historical data traffic pattern seasonal trend price may also vary depending toll surcharge incurred tip discount promotion subscription routebased adjustment price may also vary depending surge pricing automatically go effect rider given area available driver encourages driver serve busy area time shift rider demand maintain reliability restore balance additional information ubers pricing process available fraud prevention detectiondown small uber us algorithm machine learning model prevent detect fraud uber user includes effort monitor account takeover suspicious user behavior unauthorized access attempt including thirdparty aggregator tool look pattern may indicate fraudulent behavior vary significantly typical user behavior uber performs realtime monitoring information collected generated user including location data payment information uber usage also examine historical data compare realtime data help detect suspicious behavior uber may limit access service require undertake particular action verifying identity allowing access detects potential fraudulent activity may contact uber customer support question concern process cooky related technology uber partner use cooky identification technology apps website email online ad purpose described notice ubers cookie notice cooky small text file stored browser device website apps online medium ad uber us cooky similar technology purpose authenticating user remembering user preference setting determining popularity content delivering measuring effectiveness advertising campaign analyzing site traffic trend generally understanding online behavior interest people interact service may also allow others provide audience measurement analytics service u serve ad behalf across internet company product service apps track report performance ad entity may use cooky web beacon sdks technology identify device used visitor website well visit online site service please see cookie notice information regarding use cooky technology described section data sharing disclosure share data user necessary provide service feature request consent also share data affiliate subsidiary service provider partner legal reason connection claim dispute uber may share data user may include sharing data recipient data shared driver account first name rating pickup andor dropoff location setting preference rider shared ride account first name restaurantsmerchants order delivery person accountfirst name order infodelivery address including restaurantsmerchants use delivery people fulfill order item ordered may include drug prescription special instruction allergy food preference user content feedback rating owner uber account use includes use account linked family profile request receive ride delivery service guest user enterprise customer account addition create account using email address affiliated uber business account owner ie employer may share account data name email address account owner help expense trip order uber business account may also share information account owner issue involving trip safety incident complaint account triporder info recipient group order account first name order info special instruction allergy information item ordered people refer uber may share data necessary determine referral bonus triporder infotrip count uber eats user share data post review restaurant create list favorite restaurant uber eats set sharing list public account first name user contentlists review upon request consent may include sharing data recipient data shared user use datasharing feature includes feature allow share eta location split fare depending feature used may include account location triporder info uber business partner share data company whose apps website access uber including purpose promotion contest specialized service depending app website access uber purpose may include account device triporder info emergency service enable share data police fire ambulance service event emergency certain incident information please go choice transparency emergency data sharing section accountname phone number location triporder inforequested pickupdropoff insurance company involved incident report submit claim insurance company relating ubers service uber share data insurance company purpose adjusting handling claim data necessary adjust handle claim may include account communication user device location triporder info usage user content merchant restaurant add restaurant merchant loyalty membership number user account share data restaurantmerchant place order also enable share phone number email andor order info restaurant merchant receive marketing communication account dataemail phone number restaurantmerchant loyalty membership number order info uber service provider business partner include third party category third party listed third party identified please go linked privacy notice information regarding collection use personal data accountant consultant lawyer professional service provider ad marketing partner provider including ad marketing publisher social medium platform ad network advertiser thirdparty data provider ad technology vendor measurement analytics provider service provider uber us vendor reach better understand current potential user uber service advertising partner measure improve ad effectiveness cloud storage provider customer support platform service provider google connection use google map ubers apps identity verification risk solution provider payment processor facilitator including paypal hyperwallet provider bike scooter rented uber apps lime tembici research partner including performing survey research project partnership uber ubers behalf social medium company including meta tiktok connection ubers use tool ubers apps website service provider assist uber enhance safety security uber apps service service provider provide u artificial intelligence machine learning tool service thirdparty vehicle supplier including fleet rental partner also includes ad intermediary criteo google rokt trade desk triplelift others share data including advertising device identifier hashed email address approximate location current trip order information ad interaction data intermediary enable service purpose disclosed privacy notice may opt ad personalization information regarding intermediary privacy practice including submit request relating handling personal data please go privacy notice linked uber subsidiary affiliate share data subsidiary affiliate help u provide service conduct data processing behalf legal reason event claim dispute uber may share data believe required applicable law regulation operating license agreement legal process governmental request insurance policy disclosure otherwise appropriate due safety similar concern includes sharing data law enforcement official public health official government authority insurance company third party necessary enforce term condition user agreement policy protect ubers right property right safety property others event claim dispute relating use service event dispute relating use another person credit card may required law share user data including trip order information owner credit card information please see ubers guideline united state law enforcement guideline law enforcement authority outside united state guideline third party data request service legal document may also share data others connection negotiation merger sale company asset consolidation restructuring financing acquisition portion business another company data retention deletion uber retains data long necessary purpose described user may request account deletion uber apps website uber retains data long necessary purpose described varies depending data type category user data relates purpose collected data whether data must retained account deletion request purpose described example retain data life account data necessary provide service account data defined period necessary including necessary meet tax insurance legal regulatory requirement example retain transaction information year may request delete account privacy menu uber app ubers website rider order recipient guest user following account deletion request delete account data except necessary purpose safety security fraud prevention compliance legal requirement issue relating account outstanding credit unresolved claim dispute generally delete data within day account deletion request except retention necessary reason iii choice transparency uber enables access andor control data uber collect including privacy setting device permission inapp rating page marketing advertising choice may also request access copy data make change update account request account deletion request uber restrict processing data privacy setting set update preference regarding location data collection sharing emergency data sharing notification ubers privacy center accessible via privacy menu uber apps location data collectiondown small enabledisable ubers collection mobile device location data device setting accessible via location sharing menu privacy center ubers apps share live locationdown small enabledisable ubers sharing mobile device realtime location data driver delivery people device setting accessible via account setting privacy location sharing menu ubers apps gender identitydown small update gender information account setting privacy ad data gender identity menu ubers apps emergency data sharingdown small may enable uber share data emergency police fire ambulance service necessary trip share data including name phone number approximate location time emergency call placed car make model color license plate information pickup dropoff location driver name enabledisable feature via location sharing menu privacy center ubers apps safety center notification discount newsdown small may enable uber send push notification discount news uber thirdparty app access small may authorize thirdparty application access uber account data enable additional feature reviewwithdraw access thirdparty application device permission mobile device platform io android defined certain type device data apps access without device owner permission platform different method permission obtained check available setting device check provider inapp rating page every trip driver rider rate scale average rating receive displayed driver find average rating account section uber app also access breakdown average rating ubers privacy center marketing advertising choice personalized marketing communication uberdown small choose whether uber may personalize marketing communication email push notification inapp message uber product service may also choose whether receive marketing email push notification uber data sharing trackingdown small choose whether uber may share data third party collect data regarding visit action thirdparty apps website purpose personalized ad personalized adsdown small choose whether uber us uber trip order search history personalize ad see uber uber eats postmates cooky related technologiesdown small information control ubers use cooky related technology including purpose displaying personalized ad please see cookie notice user data request uber provides variety way learn control submit question comment ubers handling data addition method indicated may also submit data request via privacy inquiry form data access portabilitydown small depending located may right access data portability data regardless location access data including profile data trip order history uber apps website also use explore data view summary certain information account rating trip order count reward status long youve using uber also use download data feature download copy requested data relating use uber including account usage communication device data changing updating datadown small edit name phone number email address payment method profile picture setting menu ubers apps deleting datadown small may request uber delete account ubers privacy center objection restriction complaintsdown small may request stop using data limit use data includes objecting use data based ubers legitimate interest uber may continue process data objection request extent necessary provide service required permitted law addition depending location may right file complaint relating ubers handling data data protection authority country iv legal information data controller data protection officer uber technology inc sole controller data processed uber use ubers service globally except joint controller uber affiliate uber technology inc uti controller data processed uber use ubers service globally except uti ubr pagos mexico sa de cv controller data user ubers payment emoney service mexico uti uber bv together uber payment bv joint controller data user ubers payment emoney service eea uber payment uk ltd user service uk uti uber bv joint controller data processed connection us ubers service eea uk switzerland may also contact ubers data protection officer ubercomprivacydpo mail uber bv burgerweeshuispad hr amsterdam netherlands regarding issue relating ubers processing personal data data protection right legal base using data depending use service purpose using data uber relies following legal base processing data necessity perform contract consent ubers legitimate interest legal obligation data protection law country area including eea uk switzerland brazil nigeria allow uber use data certain circumstance defined law apply called legal basis using data applicability legal base may depend location chart indicates legal base uber law apply us data purpose described notice legal basis description data us contract set uber account andor request ride delivery uber entering contract defined term condition provide service legal basis applies must use data order provide service request meet responsibility contract calculating riderrecipient price driverdelivery person fare creating updating account enabling service feature customer support enabling communication driver delivery person performing necessary operation maintain service personalizing account processing payment providing trip delivery update generating receipt informing change term service policy consent legal basis applies notify collect use data voluntarily agree use data case enabling collection use device uber setting rely consent right withdraw consent time case cease collection use data personalizing ad relating product service offered company processing health data sensitive data depending region live legitimate interest legal basis applies uber legitimate purpose using data purpose safety security fraud prevention detection processing data necessary purpose benefit purpose outweighed risk privacy would expect ubers use data would prevent exercising right displaying ad targeted based data current trip delivery request predicting helping avoid pairing user may result increased risk conflict preventing detecting combating fraud verifying account identity compliance safety requirement providing live support safety expert trip delivery</t>
+  </si>
+  <si>
+    <t>whats boomplay boomplay music get appget app whats boomplayfor artistsadvertisingnewscontactgo web player whats boomplay artist advertising news contact go web player privacy policy effective october welcome boomplay boomplay provided controlled transsnet music limited hereinafter tml u committed protecting respecting privacy privacy policy hereinafter policy set basis personal data collect provide u processed u please read following carefully understand view practice regarding personal data treat accessing using website software service application product content offered via boomplay collectively service accepting consenting practice described policy type personal data collect use may collect use following information information share u information relating voluntarily shared boomplay information share u may include without limitation posting make boomplay including public profile name identification number address email address social medium login detail telephone number information device browsing record comment make boomplay well account billing detail list create photo video voice recording accessed prior consent device setting turn posting others repost location data log data associated posting information share u also includes information including location data log data others using boomplay share information share u remain publiclyavailable long user shared information retains information share social network choose link boomplay social network public forum account including without limitation facebook twitter google account may provide u allow social network provide u information social network public forum account data may include use boomplay public forum andor social network information purpose social network provider process data please see privacy policy information device automatically collect certain data including ip address unique device identifier google advertising id android id identifier advertising cooky defined mobile carrier time zone locale setting operating system platform hardware software version battery level signal strength available storage space browser type app file name type bluetooth signal international mobile equipment identity international mobile subscriber identity data device setting information allow u receive device setting turn access gps location photo video voice recording information device automated decisionmaking including profiling based data automatically collected solely used optimizing service tailoring preference behavioral information collect also collect information regarding use service eg comment boomplay content posted service view interaction boomplay addition link contact subscriber information activity boomplay across device using email social medium login detail engagement including without limitation like share comment repeated view relate user based behavior finally collect optins communication preference location data may collect process information location including location information based sim card ip address mobile device location setting activated mobile device use global positioning system gps may use information provide locationbased service feature notification marketing content influenced location wish share gps location u switch gps functionality mobile device metadata post content including image text audio boomplay automatically upload certain metadata connected content essence metadata describes data provides information content always evident viewer connection content metadata describe piece content collected content formatted includes information account name enables user trace back content user account metadata consist additional data chose provide content eg hashtags used mark keywords comment information third party may receive information use website operate service provide may also receive information third party advertising network analytics provider source including business directory commercially publicly available source contact information may collect contact information contact list address book social network help others find people may know enable link boomplay contact list contact list device andor account third party service ask consent access contact list address book may time allow disallow u access contact list address book changing setting thirdparty service create boomplay account connecting thirdparty service facebook google instagram whatsapp email may collect information thirdparty service including without limitation thirdparty service user name gender profile image birthday thirdparty service contact list cooky use cooky similar technology eg web beacon flash cooky app cache etc cooky enhance experience using boomplay cooky small file placed device enable u provide certain feature functionality use following cooky strictly necessary cooky cooky required operation boomplay keep account data safe secure include example cooky enable log secure area boomplay analyticalperformance cooky allow u recognize count number visitor see visitor move around boomplay using help u improve way boomplay work example ensuring user able find looking easily functionality cooky used recognize return boomplay enables u personalize content greet name remember preference example choice language region targeting cooky cooky record visit boomplay page visited link followed use information make boomplay advertising displayed relevant interest may also share information third party purpose reason wish take advantage cooky may disable cooky changing setting browser however affect enjoyment boomplay longer able offer personalized content unless opt cooky assume consent use cooky track signal preference user set web browser limit activity tracked across thirdparty website online service boomplay respond track signal web browser analytics information boomplay use thirdparty analytics tool help u measure traffic usage trend service traffic refers different data flow surrounding activity user service tool example collect information sent device service including page visit addons information assist u improving service information used report evaluate activity pattern user boomplay provide service accordance activity use personal data use information collect following way administer boomplay ie provide service internal operation including troubleshooting data analysis testing research statistical survey purpose ie guarantee boomplays stability security solicit feedback allow participate interactive feature boomplay choose personalize content receive provide tailored content interest improve develop boomplay conduct product development measure understand effectiveness recommendation service offer others provide tailored service based country setting chosen recommendation content related country setting make suggestion recommendation user boomplay good service interest allow user identify user service support socializing function service provide profile information send anyone choose enable participate boomplay interact user make information available user accordance privacy setting chose respective information show content similar content liked interacted commenting andor watching content content region well content user follow promote service use information give u content choose post service part advertising marketing campaign promote service enable messenger service function verify account activity combat harmful conduct detect prevent spam bad experience maintain integrity boomplay promote safety security boomplay notify change service communicate provide user support enforce term condition policy specific reason provided time collect information legitimate interest promote service may use information give u content choose post service part advertising marketing campaign promote service share personal data may share personal data selected third party outside country including without limitation business partner make special offer via boomplay respect onscreen ad advertiser advertising network require data select serve advertisement others without consent share contact detail business partner avoid direct contact may share information make offer tailored requirement cloud storage provider store information provide disaster recovery service well performance contract entered analytics search engine provider assist u improvement optimization boomplay service provider help develop maintain secure optimize boomplay framework data center server host provider may share information member affiliate group includes subsidiary ultimate holding company subsidiary company control controlled common control service provider strategic business partner respective subsidiary case outside country purpose set use personal data may share information law enforcement agency public tax authority organization legally required good faith belief use reasonably necessary comply legal obligation process request including tax related reporting requirement enforce term service agreement policy standard including investigation potential violation thereof detect prevent otherwise address security fraud technical issue protect right property safety u user third party public required permitted law including exchanging information company organization purpose fraud protection credit risk reduction may also disclose information third party event sell buy business asset case may disclose data prospective seller buyer business asset sell buy merge partner company business sell asset transaction user information may among transferred asset case third party company business adhere provision privacy policy result change provision herein change communicated given chance consent opt discretion security personal data take step ensure information treated securely accordance policy unfortunately transmission information via internet completely secure although best protect information example encryption guarantee security information transmitted boomplay thus transmission risk put place appropriate technical organizational measure ensure level security appropriate risk varying likelihood severity right freedom user maintain technical organizational measure amend time time improve overall security system time time include link website partner network advertiser affiliate follow link website please note website privacy policy accept responsibility liability policy please check policy submit information website data retention use following criterion determine period keep information contractual obligation right relation information involved legal obligation applicable law regulation retain data certain period time statute limitation applicable law legitimate business purpose dispute potential dispute terminated use service store information aggregated anonymized format notwithstanding foregoing also retain personal information reasonably necessary comply legal obligation allow u resolve litigate dispute enforce agreement information relating child service offered child whose age make illegal process personal data requires parental consent processing personal data applicable law knowingly collect personal data child year applicable age limit jurisdiction age limit age limit please use service provide personal data u parent child age limit become aware child provided personal data u please contact u privacyboomplaytranssnetcom delete data aware collected personal data child age limit take reasonable step delete personal data complaint event wish make complaint process personal data please contact u first instance privacyboomplaytranssnetcom endeavor deal request soon possible without prejudice right launch claim data protection authority follow dispute resolution process provided term service change may amend update policy time time access latest version policy boomplay responsibility remain informed change continued access use service date updated policy constitutes acceptance updated policy agree updated policy must stop accessing using service contact question comment request regarding policy welcomed addressed privacyboomplaytranssnetcom right right make request access delete personal data hold rectify personal data held inaccurate right data portability right request suspension processing personal data exercise right contacting u privacyboomplaytranssnetcom explore artist trending song new song chart video podcast buzz user download help center go premuim wordpress artist vendor boomplay artist get verified artist faq artist distributor vendor login report content issue company contact advertising news visual identity boomplay right reserved privacy policyeulapodcast tcsitemap explore artiststrending songsnew songschartsvideospodcastbuzz user downloadhelp centergo premuimwordpress artist vendor boomplay artistsget verifiedartists faqartists distributorsvendors loginreport content issue company aboutcontactadvertisingnewsvisual identity boomplay right reserved privacy policyeulapodcast tcsitemap</t>
+  </si>
+  <si>
+    <t>httpspoliciesgooglecomprivacyhlenglus</t>
+  </si>
+  <si>
+    <t>meta privacy policy meta collect us user data privacy policy search privacy topic privacy resource privacy policy privacy policy cover information collect use information information shared meta product integrated partner share information third party meta company work together manage delete information exercise right long keep information transfer information respond legal request comply applicable law prevent harm know policy changed privacy notice united state resident contact meta question process information policy article setting privacy policy privacy policy cover effective june view printable version see previous version read united state regional privacy notice detail handle personal information exercise right highlight meta want understand information collect use share thats encourage read privacy policy help use meta product way thats right privacy policy explain collect use share retain transfer information also let know right section policy includes helpful example simpler language make practice easier understand weve also added link resource learn privacy topic interest important u know control privacy also show manage information setting meta product use update setting shape experience read full policy product policy cover learn privacy center managing privacy information collect highlight information collect process depends use product example collect different information sell furniture marketplace post reel instagram use product collect information even dont account here information collect activity information provide friend follower connection app browser device information information partner vendor third party dont let u collect certain information information required product work information optional without quality experience might affected learn information collect doesnt identify individual case information deidentified aggregated anonymized third party longer identifies individual made available u use information described without trying reidentify individual take control manage information collect privacy center use information highlight use information collect provide personalized experience including ad along purpose explain detail purpose use information across product across device information use purpose automatically processed system case also use manual review access review information use less information thats connected individual user case deidentify aggregate information anonymize longer identifies use information way use information described section way use information provide personalize improve product use information provide improve product includes personalizing feature content recommendation facebook feed instagram feed story ad use information special protection choose provide purpose show ad read use information provide personalize improve product show ad sponsored commercial content use information improve product use locationrelated information promote safety security integrity use information collect help protect people harm provide safe secure product learn provide measurement analytics business service lot people rely product run promote business share content help measure well ad content product service working learn communicate communicate using information youve given u like contact information youve entered profile learn research innovate social good use information information researcher datasets publicly available source professional group nonprofit group conduct support research learn privacy policy process information information shared meta product integrated partner highlight meta product learn different case information shared product people account share communicate content others share reshare public content integrated partner choose connect integrated partner use product integrated partner receive information activity integrated partner always access information thats public product learn information receive handle information use integrated partner product service interact someone elses content integrated partner product service integrated partner handle information take control learn audience privacy center manage apps website share information third party highlight dont sell information anyone never also require partner third party follow rule use disclose information provide here detail share information partner advertiser audience network publisher partner use analytics service partner offer good service product commerce service platform integrated partner vendor measurement vendor marketing vendor service provider service provider third party external researcher ai integration third party also share information third party response legal request comply applicable law prevent harm read policy sell transfer part business someone else case well give new owner information part transaction law allows meta company work together highlight part meta company provide meta company product meta company product include meta product covered policy plus product like whatsapp share information collect infrastructure system technology meta company learn transfer information country also process information receive meta company according term policy permitted applicable law case meta act service provider meta company act behalf accordance instruction term share across meta company meta product share information meta company promote safety security integrity comply applicable law personalize offer ad sponsored commercial content develop provide feature integration understand people use interact meta company product see example share resource review privacy policy meta company facebook help center manage delete information exercise right highlight offer variety tool view manage download delete information also manage information visiting setting product use may also privacy right applicable law exercise right visit help center setting facebook instagram devicebased setting take privacy checkup take privacy checkup guided facebook privacy setting view manage information access information offmeta activity ad preference manage data port download delete information port information download information delete information account learn privacy work facebook instagram facebook help center question policy contact u described country may also able contact data protection officer meta platform inc depending jurisdiction may also contact local data protection authority dpa directly long keep information highlight keep information long need provide product comply legal obligation protect others interest decide long need information casebycase basis here consider decide need operate provide product example need keep information maintain account learn feature use feature work example message sent using messenger vanish mode retained less time regular message learn long need retain information comply certain legal obligation see example need legitimate purpose prevent harm investigate possible violation term policy promote safety security integrity protect including right property product instance specific reason well keep information extended period time read policy may preserve information transfer information highlight information transferred country information transferred safeguard information respond legal request comply applicable law prevent harm highlight access preserve use share information response legal request like search warrant court order production order subpoena request come third party civil litigant law enforcement government authority learn respond legal request accordance applicable law promote safety security integrity meta product user employee property public learn may access preserve information extended amount time learn know policy changed well notify make material change policy youll opportunity review revised policy choose continue using product privacy notice united state resident learn consumer privacy right may available reviewing united state regional privacy notice contact meta question learn privacy work facebook instagram facebook help center question policy question complaint request regarding information contact u described contact u online mail meta platform inc attn privacy operation willow road menlo park ca process information category information use information processed set process information information category use see information collect information information category actual information use depends factual circumstance could include following personalizing meta product ad see system automatically process information collect store associated others assess understand interest preference provide personalized experience across meta product accordance term personalize feature content facebook feed instagram feed story make suggestion people may know group event may interested topic may want follow product learn use information personalize experience across meta product choose ad see activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting like gps location locationrelated information information network connect device report product performance device information cooky similar technology information partner vendor third party providing ad meta company product ad system automatically process information weve collected stored associated ad system us information understand interest preference personalize ad across meta company product ad system prioritizes ad show based audience advertiser want reach match ad people might interested learn ad system work activity information provide age gender provide information ad show engage ad app browser device information location information device characteristic device software decide add whatsapp account account center account meta company product associate account meta company product whatsapp account account center share information whatsapp note list information meta information whatsapp share meta see whatsapp help center article activity information provide friend follower connection app browser device information providing improving meta product provision meta product includes collecting storing relevant sharing profiling reviewing curating instance automated processing also manual human reviewing create maintain account profile connect meta product account including public profile information integrated partner sign share information facilitate sharing content status provide curate feature provide messaging service ability make voice video call connect others provide advertising product understand enable creation content like text audio image video including artificial intelligence technology provide undertake analytics facilitate purchase payment meta pay meta checkout experience also use information develop research test improvement product use information see product working correctly troubleshoot fix test new product feature see work get feedback idea product feature conduct survey research like product brand better activity information provide content create like post comment audio public profile information including name username profile picture content provide camera feature camera roll setting voiceenabled feature message send receive including content subject applicable law metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make including truncated credit card information hashtags use time frequency duration activity product photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party promoting safety integrity security across meta product meta product designed research help ensure safety integrity security service people enjoy meta product process information associated apply automated processing technique instance conduct manual human review verify account activity find address violation term policy case decision make violation reviewed oversight board investigate suspicious activity detect prevent combat harmful unlawful behavior review case remove content reported u identify combat disparity racial bias historically marginalized community protect life physical mental health wellbeing integrity user others detect prevent spam security matter bad experience detect stop threat personnel property maintain integrity product information safety integrity security generally meta product visit facebook security help center instagram security tip activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature message send receive including content subject applicable law metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make including truncated credit card information hashtags use time frequency duration activity product photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party communicate use information youve given u like contact information profile send communication like email inproduct notice example well contact via email inproduct notification relation meta product productrelated issue research let know term policy also use contact information like email address respond contact u activity information provide contact information profile communication u content create like post comment audio content provide camera feature camera roll setting voiceenabled feature app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology transferring storing processing information across border including united state country share information collect globally internally across office data center externally partner third party service provider meta global user partner vendor employee around world transfer necessary operate provide service described term apply meta product using includes allowing share information connect family friend around globe fix analyze improve product information see transfer information section meta privacy policy activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make including truncated credit card information hashtags use time frequency duration activity product photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party processing information subject special protection applicable law provide share choose provide personalize improve product undertake analytics well collect store publish apply automated sometimes manual human processing purpose activity information provide information special protection choose provide religious view sexual orientation political view health racial ethnic origin philosophical belief trade union membership part survey choose participate given explicit consent receiving using information third party tailor ad see well use information advertiser business partner provide u activity meta company product associated personalize ad show meta product website apps device use advertising service receive information whether youre logged account product see cooky policy information activity information provide information content provide name email address information partner vendor third party sharing contact profile information third party upon request type third party category information shared depend circumstance ask u share example share email contact information information might choose direct u share advertiser contact additional information promoted product choose integrate apps game website meta product log well share information app game website log activity information provide information contact profile information content create like post comment providing measurement analytics business service system automatically well manual human processing process information collected stored others use information provide insight measurement report business advertiser partner help measure effectiveness distribution client ad content service understand kind people seeing content ad content ad performing meta product provide aggregated user analytics insight report help user business advertiser partner better understand audience may want connect well type people use service people interact content website apps service activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology sharing information across meta company provide seamless consistent richer innovative experience across meta company product enable cross app interaction sharing viewing engaging content including post video activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology business intelligence analytics understand aggregate usage across product accurately count people business validate metric directly related order inform improve product direction development adhere shareholderearning reporting obligation activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party identifying meta product user personalizing ad show meta audience network visit apps show ad meta audience network visit apps system automatically process information collected stored others identify meta product user tailor ad see activity information provide information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting information network connect device including ip address information cooky similar technology providing marketing communication depending setting subject applicable law well share marketing communication well collect store information use send marketing communication like email subject applicable law activity information provide information content provide including contact information like email address app browser device information device identifier research innovate social good carry survey use information including researcher collaborate conduct support research innovation topic general social welfare technological advancement public interest health wellbeing example analyze information migration pattern crisis help relief organization get aid right place collect store combine analyze apply automatic processing technique like aggregation information well manual human review share information necessary research innovate social good way support research area like artificial intelligence machine learning learn research program activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party anonymizing information case anonymize information associated activity product use resulting information example provide improve meta product including ad activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party sharing information others including law enforcement respond legal request see respond legal request prevent harm promote safety integrity section meta privacy policy information share information law enforcement others category information access preserve use share depend specific circumstance example response legal request compelled law typically include limited information contact detail login information however information process depend purpose could include following response legal request third party civil litigant law enforcement government authority comply applicable law legitimate legal purpose promote safety security integrity meta company meta product user employee property public learn promote safety security integrity activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content subject applicable law type content view interact interact apps feature use action take purchase transaction make hashtags use photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party processing information law requires obligation disclose information example receive valid legal request certain information search warrant access preserve andor share information regulator law enforcement others way information processed depends specific circumstance see respond legal request prevent harm promote safety integrity section meta privacy policy information law enforcement authority provides information operational guideline law enforcement need follow category information depend specific circumstance mandatory request obligation information necessary comply relevant legal obligation shared otherwise processed example civil matter typically include limited information contact detail login information however depending circumstance could include following activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature message send receive including content subject applicable law metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make including truncated credit card information hashtags use time frequency duration activity product photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party</t>
+  </si>
+  <si>
+    <t>whatsapp business app privacy policy skip contenthome feature message privatelystay connectedconnect groupsexpress yourselfsecure designshare everydayfollow channel meta ai privacy help center blog business download download term privacy policy whatsapp llc azrbaycanafrikaansbahasa indonesiamelayucataletinadanskdeutscheestienglishespaolfranaisgaeilgehrvatskiitalianokiswahililatvieulietuvimagyarnederlandsnorsk bokmlozbekfilipinopolskiportugus brasilportugus portugalromnshqipsloveninasloveninasuomisvenskating vittrke azrbaycanafrikaansbahasa indonesiamelayucataletinadanskdeutscheestienglishespaolfranaisgaeilgehrvatskiitalianokiswahililatvieulietuvimagyarnederlandsnorsk bokmlozbekfilipinopolskiportugus brasilportugus portugalromnshqipsloveninasloveninasuomisvenskating vittrke featuresmessage privatelyendtoend encryption privacy control stay connectedmessage call free around world connect groupsgroup messaging made easy express yourselfsay sticker voice gifs secure designlayers protection help stay safe share everydayshare photo video voice note status follow channelsstay updated topic care meta aiget help anything privacy help center blog business apps log indownload whatsapp business app privacy policy effective july table content whatsapp legal info scope whatsapp business app privacy policy information collect use information information share work meta company region specific information assignment change control transfer managing information law right protection global operation update privacy policy contact u located uk whatsapp llc provides business app whatsapp business term service whatsapp business app privacy policy located european region whatsapp ireland ltd provides business app whatsapp business term service whatsapp business app privacy policy whatsapp legal info located uk whatsapp llc whatsapp u provides business app term service whatsapp business app privacy policy whatsapp llc also data controller processing personal information contact u using detail section contact u located european region whatsapp ireland limited whatsapp u provides business app term service whatsapp business app privacy policy whatsapp ireland limited also data controller processing personal information contact u using detail section contact u scope whatsapp business app privacy policy whatsapp business app provides similar feature functionality whatsapp messenger app main app functionality provides additional feature functionality tailored business need business function business function include thing like catalog greeting away message whatsapp business app includes various feature available whatsapp messenger app feature may available business function available everywhere business function may offered whatsapp third party andor meta via integration business app may subject third party term service privacy policy whatsapp business app privacy policy business app privacy policy explains whatsapps data practice respect business function applies extent information relating user whatsapp business app would considered personal data processed whatsapp controller applicable law user refer whatsapp privacy policy incorporated herein reference understand information processed main app functionality learn business function main app functionality available whatsapp business app please also read whatsapp business term service business term describe term use provide whatsapp business app information collect addition information described applicable whatsapp privacy policy collect following information information provide business account information addition phone number must provide basic information business create whatsapp business account including business name business category dont provide u information able create account use whatsapp business app add optional information business account profile picture cover photo contact information like business address business email website description business product service offer name description image video price related marketing material intended audience automatically collected information usage log information collect information use business function example collect information business profile setting use business function like catalog label quick reply purchase transaction business metric related customer interact business information received others user report feedback preference block user report submit feedback set communication preference block business whatsapp associate business subject report feedback preference block use information use information collect purpose described whatsapp privacy policy also operate provide improve understand customize support market whatsapp business app business function whatsapp business app use information operate provide whatsapp business app business function including providing business support providing onboarding tool providing message creation delivery tool providing new premium business function may offered third party andor meta improving fixing customizing whatsapp business app also use information understand use whatsapp business app evaluate improve whatsapp business app research develop test new service feature conduct troubleshooting activity also use information respond contact u safety security integrity addition safety security integrity purpose described whatsapp privacy policy also use information maintain safety security integrity whatsapp business app example create quality integrity inference business secure whatsapp system whatsapp business app user account fight threat abuse infringement activity promote safety security integrity whatsapp business app ensure compliance term policy information share share information described whatsapp privacy policy plus additional sharing relevant business function information business profile business profile information publicly available including business name phone number hour operation business category address email address website description facebook instagram account added may provide way user find reach like business search search functionality integration allow connect whatsapp business app product service offered third party andor meta include example cloud storage hosting service customer relationship management tool ad message creation delivery management service business analytics service ai tool use product service term privacy policy govern use service product work meta company review whatsapp privacy policy understand work meta company whatsapp business app region specific information additional information user located u learn consumer privacy right may available reviewing whatsapp business app united state regional privacy notice assignment change control transfer event involved merger acquisition restructuring bankruptcy sale asset share information successor entity new owner connection transaction accordance applicable data protection law managing retaining information whatsapp business app follows information management retention deletion practice described whatsapp privacy policy law right protection review whatsapp privacy policy understand access preserve share information response legal obligation global operation review whatsapp privacy policy understand global operation impact information processed update privacy policy may amend update business app privacy policy provide notice amendment business app privacy policy appropriate update effective date top business app privacy policy please review business app privacy policy time time contact u question issue privacy policy please contact u whatsapp llc privacy policy willow road menlo park california united state america download download featuresblogsecurityfor business uscareersbrand centerprivacy use whatsapp androidiphonemacpcwhatsapp web need help contact ushelp centerappssecurity advisory download whatsapp llc term privacy policysitemap azrbaycanafrikaansbahasa indonesiamelayucataletinadanskdeutscheestienglishespaolfranaisgaeilgehrvatskiitalianokiswahililatvieulietuvimagyarnederlandsnorsk bokmlozbekfilipinopolskiportugus brasilportugus portugalromnshqipsloveninasloveninasuomisvenskating vittrke azrbaycanafrikaansbahasa indonesiamelayucataletinadanskdeutscheestienglishespaolfranaisgaeilgehrvatskiitalianokiswahililatvieulietuvimagyarnederlandsnorsk bokmlozbekfilipinopolskiportugus brasilportugus portugalromnshqipsloveninasloveninasuomisvenskating vittrke</t>
+  </si>
+  <si>
+    <t>privacy policy skip contenthome feature message privatelystay connectedconnect groupsexpress yourselfsecure designshare everydayfollow channel meta ai privacy help center blog business download download term privacy policy whatsapp llc englishespaolfranaisbahasa indonesiaoriyaportugus brasilfilipinotrkeenglishespaolfranaisbahasa indonesiaoriyaportugus brasilfilipinotrke featuresmessage privatelyendtoend encryption privacy control stay connectedmessage call free around world connect groupsgroup messaging made easy express yourselfsay sticker voice gifs secure designlayers protection help stay safe share everydayshare photo video voice note status follow channelsstay updated topic care meta aiget help anything privacy help center blog business apps log indownload whatsapp privacy policy effective january archived version live european region whatsapp ireland limited provides service term service privacy policy live uk whatsapp llc provides service term service privacy policy whatsapp legal info live outside european region uk whatsapp llc whatsapp u provides service term service privacy policy privacy policy privacy policy help explain data practice including information process provide service example privacy policy talk information collect affect also explains step take protect privacy like building service delivered message arent stored u giving control communicate service one meta company learn privacy policy way share information across family company privacy policy applies service unless specified otherwise please also read whatsapps term service term describe term use provide service back top key update respect privacy coded dna since started whatsapp weve built service set strong privacy principle mind updated term service privacy policy youll find additional information handle data updated term privacy policy provide information process data commitment privacy example weve added information recent product feature functionality process data safety security integrity added direct link user setting help center article manage information better communication business many business rely whatsapp communicate customer client work business use meta third party help store better manage communication whatsapp making easier connect part meta company whatsapp partner meta offer experience integration across metas family apps product back top information collect whatsapp must receive collect information operate provide improve understand customize support market service including install access use service type information receive collect depend use service require certain information deliver service without able provide service example must provide mobile phone number create account use service service optional feature used require u collect additional information provide feature notified collection appropriate choose provide information needed use feature unable use feature example share location contact permit u collect location data device permission managed setting menu android io device information provide account information must provide mobile phone number basic information including profile name choice create whatsapp account dont provide u information able create account use service add information account profile picture information message retain message ordinary course providing service instead message stored device typically stored server message delivered deleted server following scenario describe circumstance may store message course delivering undelivered message message delivered immediately example recipient offline keep encrypted form server day try deliver message still undelivered day delete medium forwarding user forward medium within message store medium temporarily encrypted form server aid efficient delivery additional forward offer endtoend encryption service endtoend encryption mean message encrypted protect u third party reading learn endtoend encryption business communicate whatsapp connection use contact upload feature provide u permitted applicable law phone number address book regular basis including user service contact contact arent yet using service well manage information way ensures contact identified u learn contact upload feature create join get added group broadcast list group list get associated account information give group name provide group profile picture description status information may provide u status choose include one account learn use status android iphone kaios transaction payment data use payment service use service meant purchase financial transaction process additional information including payment account transaction information payment account transaction information includes information needed complete transaction example information payment method shipping detail transaction amount use payment service available country territory privacy practice described applicable payment privacy policy customer support communication contact u customer support otherwise communicate u may provide u information related use service including copy message information deem helpful contact eg email address example may send u email information relating app performance issue automatically collected information usage log information collect information activity service like servicerelated diagnostic performance information includes information activity including use service service setting interact others using service including interact business time frequency duration activity interaction log file diagnostic crash website performance log report also includes information registered use service feature use like messaging calling status group including group name group picture group description payment business feature profile photo information whether online last used service last seen last updated information device connection information collect device connectionspecific information install access use service includes information hardware model operating system information battery level signal strength app version browser information mobile network connection information including phone number mobile operator isp language time zone ip address device operation information identifier including identifier unique meta company product associated device account location information collect use precise location information device permission choose use locationrelated feature like decide share location contact view location nearby location others shared certain setting relating locationrelated information find device setting inapp setting location sharing even use locationrelated feature use ip address information like phone number area code estimate general location eg city country also use location information diagnostics troubleshooting purpose cooky use cooky operate provide service including provide service webbased improve experience understand service used customize example use cooky provide service web desktop webbased service may also use cooky understand help center article popular show relevant content related service additionally may use cooky remember choice like language preference provide safer experience otherwise customize service learn use cooky provide service back top thirdparty information information others provide receive information user example user know use service may provide phone number name information like information mobile address book may provide may also send message send message group belong call require user lawful right collect use share information providing information u keep mind general user capture screenshots chat message make recording call send whatsapp anyone else post another platform user report report user user third party may also choose report u interaction message others service example report possible violation term policy report made collect information reporting user reported user find happens user report made please see advanced safety security feature business whatsapp business interact using service may provide u information interaction require business act accordance applicable law providing information u message business whatsapp keep mind content share may visible several people business addition business might working thirdparty service provider may include meta help manage communication customer example business may give thirdparty service provider access communication send store read manage otherwise process business understand business process information including might share information third party meta review business privacy policy contact business directly thirdparty service provider work thirdparty service provider meta company help u operate provide improve understand customize support market service example work distribute apps provide technical physical infrastructure delivery system provide engineering support cybersecurity support operational support supply location map place information process payment help u understand people use service market service help connect business using service conduct survey research u ensure safety security integrity help customer service company may provide u information certain circumstance example app store may provide u report help u diagnose fix service issue work meta company section provides information whatsapp collect share information meta company thirdparty service allow use service connection thirdparty service meta company product use service thirdparty service meta company product may receive information example use whatsapp share button news service share news article whatsapp contact group broadcast list service choose access service mobile carrier device provider promotion service please note use thirdparty service meta company product term privacy policy govern use service product back top use information use information subject choice make applicable law operate provide improve understand customize support market service here service use information operate provide service including providing customer support completing purchase transaction improving fixing customizing service connecting service meta company product may use also use information understand people use service evaluate improve service research develop test new service feature conduct troubleshooting activity also use information respond contact u safety security integrity safety security integrity integral part service use information verify account activity combat harmful conduct protect user bad experience spam promote safety security integrity service investigating suspicious activity violation term policy ensure service used legally please see law right protection section information communication service meta company use information communicate service let know term policy important update may provide marketing service meta company thirdparty banner ad still allow thirdparty banner ad service intention introduce may see type ad update tab home feature like channel status business interaction enable third party like business communicate interact using service catalog business whatsapp browse product service place order business may send transaction appointment shipping notification product service update marketing example may receive flight status information upcoming travel receipt something purchased notification delivery made message receive business could include offer something might interest want spammy experience message manage communication honor choice make back top information share share information use communicate service share information help u operate provide improve understand customize support market service send information choose communicate share information including message use communicate service information associated account phone number profile name photo information last seen information message receipt available anyone us service although configure service setting manage certain information available user including business communicate contact others user including business communicate store reshare information including phone number message others service use service setting block feature service manage communicate service certain information share business whatsapp offer specific service business providing metric regarding use service thirdparty service provider work thirdparty service provider meta company help u operate provide improve understand customize support market service work company support service provide technical infrastructure delivery system market service conduct survey research u protect safety security integrity user others assist customer service share information thirdparty service provider meta company capacity require use information behalf accordance instruction term thirdparty service others use thirdparty service meta company product integrated service thirdparty service may receive information others share example use data backup service integrated service like icloud google account receive information share whatsapp message interact thirdparty service another meta company product linked service use inapp player play content thirdparty platform information like ip address fact whatsapp user may provided third party meta company product please note use thirdparty service meta company product term privacy policy govern use service product back top work meta company part meta company whatsapp receives information share information see meta company may use information receive may use information share help operate provide improve understand customize support market service offering including meta company product includes helping improve infrastructure delivery system understanding service used promoting safety security integrity across meta company product eg securing system fighting spam threat abuse infringement activity improving service experience using making suggestion example friend group connection interesting content personalizing feature content helping complete purchase transaction showing relevant offer ad across meta company product providing integration enable connect whatsapp experience meta company product example allowing connect facebook pay account pay thing whatsapp enabling chat friend meta company product portal connecting whatsapp account learn meta company privacy practice reviewing privacy policy back top assignment change control transfer event involved merger acquisition restructuring bankruptcy sale asset share information successor entity new owner connection transaction accordance applicable data protection law back top managing retaining information access port information using inapp request account info feature available setting account iphone user learn access manage delete information iphone help center article android user learn access manage delete information android help center article store information long necessary purpose identified privacy policy including provide service legitimate purpose complying legal obligation enforcing preventing violation term protecting defending right property user storage period determined casebycase basis depends factor like nature information collected processed relevant legal operational retention need legal obligation would like manage change limit delete information following tool service setting change service setting manage certain information available user manage contact group broadcast list use block feature manage user communicate changing mobile phone number profile name picture information change mobile phone number must update using inapp change number feature transfer account new mobile phone number also change profile name profile picture information time deleting whatsapp account delete whatsapp account time including want revoke consent use information pursuant applicable law using inapp delete account feature delete whatsapp account undelivered message deleted server well information longer need operate provide service deleting account example delete account info profile photo delete whatsapp group delete whatsapp message history mindful delete whatsapp device without using inapp delete account feature information stored u longer period please remember delete account affect information related group created information user relating copy message sent learn data deletion retention practice delete account back top law right protection access preserve share information described information collect section privacy policy goodfaith belief necessary respond pursuant applicable law regulation legal process government request enforce term applicable term policy including investigation potential violation detect investigate prevent address fraud illegal activity security technical issue protect right property safety user whatsapp meta company others including prevent death imminent bodily harm back top global operation whatsapp share information globally internally within meta company externally partner service provider communicate around world accordance privacy policy information may example transferred transmitted stored processed united state country territory meta company affiliate partner service provider located country territory globally service provided outside live purpose described privacy policy whatsapp us metas global infrastructure data center including united state transfer necessary provide global service set forth term please keep mind country territory information transferred may different privacy law protection home country territory back top update policy may amend update privacy policy provide notice amendment privacy policy appropriate update effective date top privacy policy please review privacy policy time time back top privacy right united state resident learn consumer privacy right may available reviewing united state regional privacy notice back top contact u question issue privacy policy please contact u whatsapp llc privacy policy willow road menlo park california united state america back top download download featuresblogsecurityfor business uscareersbrand centerprivacy use whatsapp androidiphonemacpcwhatsapp web need help contact ushelp centerappssecurity advisory download whatsapp llc term privacy policysitemap englishespaolfranaisbahasa indonesiaoriyaportugus brasilfilipinotrkeenglishespaolfranaisbahasa indonesiaoriyaportugus brasilfilipinotrke</t>
+  </si>
+  <si>
+    <t>privacy policy giraffe game giraffe game privacy policy effective date th may u limited company company number registered office giraffe game limited upper pembroke street dublin giraffe game data controller personal data provided u via giraffe game site use service responsible processing personal data accordance general data protection regulation gdpr eu wide regulation protection personal data privacy policy explains personal data collect use personal data option relation personal data contact u contact information giraffe game limited upper pembroke street dublin question policy please contact u contactgiraffegamescom privacy policy together game license agreement read whole form integral part term use giraffe game limited affiliate giraffe u dedicated protecting privacy right user user privacy policy policy describes way collect store use manage information including personal information provide collect connection website including wwwgiraffegamescom site giraffe game provided mobile platform example io android window phone collectively service question concern privacy policy practice please contact u contactgiraffegamescom age limit knowingly process personal data belonging anyone age knowingly allow person use service one age may provide personal data please send data u including name address telephone number email address discovered process personal data individual data deleted facebook third party account login choose login facebook account third party account applicable game maybe please aware depending setting receive facebook login account information basic profile information avatar facebook name country displayed user game play public leaderboards signing facebook allows u offer functionality invite play friend create challenge friend see friend game progress also allow log multiple device synchronise progress across multiple device multiple platform would like signed facebook account would like image displayed player may use hide option setting personal profile replaced dummy profile data collect giraffe collect information described giraffe primary goal collecting using information create account provide service improve service contact conduct research create report internal use use third party store information server located european union may store information server equipment jurisdiction time time required provide personally identifiable information visit site however order take advantage certain feature may need provide personally identifiable information user name password order access third party message account must enter applicable user name password use basic service site store password server wish utilise advanced feature site automatic signin storage password may necessary aggregate usage data giraffe may collect usage data information user including data usage site various feature personally identifiable except described ip address section social feature whenever social feature involves disclosure personally identifiable information people giraffe either provide opportunity opt disclosure seek consent prior making disclosure site browsing giraffe site computer operating system ip address access time browser type language referring web site address may logged automatically may use information monitor develop analyse use service facebook connect need year old order use facebook connect feature service facebook connect enables give permission may receive information facebook including limited name profile picture avatar gender location email address date birth give u permission store information received based use service please review facebooks term condition privacy policy httpswwwfacebookcomaboutprivacyupdate thirdparty service governed term please note email address access token encrypted social medium feature widget site may time time include social medium feature facebook like button widget share button interactive mini program run site feature may collect ip address page visiting site may set cookie enable feature function properly social medium feature widget either hosted third party hosted directly site interaction feature governed privacy policy company providing io android window phone platform use giraffe game application mobile platform may collect record certain information unique device id persistent nonpersistent hardware type medium access control mac address international mobile equipment identity imei version operating system o device name email address connected facebook google location based ip address information useful u troubleshooting help u understand usage trend may collect process location data provide location related service advertisement may use various technology determine location gps wifi networkbased data ip address gps geolocation accessed without consent share gps geolocation third party without consent please note may share anonymous location data partner order improve service longer wish allow u track use information may turn device level please note application may work properly unable tell coming country specific addition create unique user id track use service unique user id stored connection profile information track giraffe game playing log log site using signin service sn service including facebook connect apple game center google sn service may available time time service authenticate identity provide option share certain personal information u name email address resume prepopulate sign form service like facebook connect give option post information activity web site profile page share others within network may collect record information sn service accordance policy term sn service information collect connect user account sn service may include name sn service user identification number andor user name locale city state country sex birth date email address profile picture url sn service user identification number friend also connected giraffe game want u delete data receive sn service please contact u supportgiraffegamescom invite friend giraffe may offer opportunity invite contact sn service facebook friend contact located giraffe game andor invite join giraffe game contact information used purpose sending communication addressee third party may contact u supportgiraffegamescom request removal information database extent giraffe store information customer service may collect email address contact customer service group may use email address contact gaming experience giraffe game notify company news promotion longer wish receive certain email notification may optout time following unsubscribe link located bottom communication emailing u supportgiraffegamescom push notification may occasionally send push notification mobile application send game update high score service related notification may importance may time optout receiving type communication turning device level setting game data collection whenever play game collect anonymous data using service httpwwwgameanalyticscom sometimes use httpwwwflurrycomsolutionsanalyticsor service provider may deem appropriate data thereby collected presented u anonymous form include example percentage user complete particular level collection may also acquire information access participation message board service participation survey regarding service participation sweepstakes contest service may provide opportunity participate sweepstakes contest service participate request certain personal information participation sweepstakes contest voluntary therefore choice whether disclose information requested information typically includes contact information name shipping address demographic information zip code use information notify winner award prize monitor traffic personalise service may use third party service provider conduct sweepstakes contest company prohibited using user personal information purpose cooky cookie small text file transfer computer andor device identify user computerdevice remember thing visit preference user name password information contained cookie may linked personal information user id purpose improving quality service tailoring recommendation interest making service easier use disable cooky time although may able access use feature service may feature advertisement served third party deliver cooky computerdevice content access advertisement see tracked since third party advertising company associate computerdevice number able recognise computerdevice time send advertisement advertiser may use information visit service third party site application order measure advertisement performance provide advertisement good service interest policy apply responsible data collection practice third party advertiser encourage check privacy policy learn use cooky technology use site without accepting use cooky cooky used support analytics logged user site clear gifs web beaconsweb bug employ third party tracking utility partner employ software technology called clear gifs aka web beaconsweb bug help u better manage content site informing u content effective clear gifs tiny graphic unique identifier similar function cooky used track online movement web user contrast cooky stored user computer hard drive clear gifs embedded invisibly web page email size period end sentence may associate information ip address device identifier tie information gathered clear gifs customer personal information mobile analytics use mobile analytics software allow u better understand functionality mobile software device software may record information often use application event occur within application aggregated usage performance data application downloaded link information store within analytics software personal information submit within mobile application third party service service may contain third party tracking tool google analytics service provider third party may use cooky apis sdks service enable collect analyse user information behalf third party may access information device identifier mac address imei locale specific location given language spoken geolocation information ip address purpose providing service respective privacy policy policy cover use tracking tool google analytics access control google analytics ad network serve ad within site serve ad within game advertiser use term service compatible term service mobile platform option opt advertising available game available advertisement blocked making app purchase advertiser may collect use information service session activity device identifier mac address imei geolocation information ip address may use information provide advertisement interest addition may see game advertised service clicking one advertisement installing game become user service order verify installs device identifier may shared advertiser need personal data use information collected service purpose described policy disclosed connection service example may use information create game account allow user play game identify suggest connection giraffe user operate improve service understand preference enhance experience enjoyment using service respond comment question provide customer service provide deliver product service request send related information including confirmation invoice technical notice update security alert support administrative message communicate promotion reward upcoming event news product service offered giraffe selected partner enable communicate user link combine information get third party help understand preference provide better service disclosure information share personal information except approved described may engage company individual perform service behalf example service include analysing data providing customer support agent service provider may access personal information connection performance service giraffe may release information permitted law comply court order believe release appropriate comply law investigate fraud respond government request enforce apply right protect right property safety u user others includes exchanging information company organization fraud protection giraffe may share information connection merger sale asset financing acquisition portion business another company notified via email andor notice site change ownership user personal information may share aggregate anonymous information advertiser publisher business partner sponsor third party change policy may update privacy policy reflect change information practice make material change notify mean notice site prior change becoming effective encourage periodically review page latest information privacy practice security take reasonable measure protect information unauthorised access loss misuse alteration third party although make good faith effort store information collected service secure operating environment available public guarantee absolute security information transmission storage system attempt ensure integrity security network system guarantee security measure prevent thirdparty hacker illegally obtaining access information warrant represent information protected loss misuse alteration third party method transmission internet method electronic storage secure however therefore guarantee absolute security access personal information personal information change longer desire service may correct update delete inaccuracy making change within account setting contacting u supportgiraffegamescom respond access request within day data retention retain information long account active needed provide service wish cancel account request longer use information provide service contact u supportgiraffegamescom retain use information necessary comply legal obligation resolve dispute enforce agreement right many right relation data gdpr would like exercise one right please contact u contactgiraffegamescom right access right know information hold information communicated please contact u letting u know wish exercise right access information particular would like receive entitled request reasonable evidence verify identity provide information please note may able provide information ask instance information includes personal information another person request would require disproportionate effort able provide information request communicate reason always respond within month receipt request verification identity correction personal data try keep information hold accurate date realise information hold incorrect please let u know see contact information policy correct soon possible deletion personal data circumstance right personal information erased executing request depend deleting game device clearing cooky device accessed site may overriding reason retaining data event case communicate reason instance personal information visible gameplay username avatar high score may cached player device may able remove update data device data portability may right request data provided u exported provided transfer another data controller transfer data directly another data controller contact u would like information restriction processing may right request restriction processing personal data example intermediate measure investigating claim inaccurate data held right object right object processing personal data processed ground legitimate interest long keep data retain information long account active needed provide service wish cancel account request longer use information provide service contact u supportgiraffegamescom retain use information necessary comply legal obligation resolve dispute enforce agreement international transfer eu data protection law personal data transferred outside eu must legal mechanism transfer order ensure protection afforded personal data travel outside eu jurisdiction hosted server store data eu take step ensure adequate safeguard mechanism place including use eu model clause verifying presence agreement privacy shield allow transfer information across border outside eea might arise data processed third party service provider privacy policy updated may contact information giraffe game limited upper pembroke street dublin query protect personal data policy please contact u contactgiraffegamescom copyright giraffe game copyright giraffe game</t>
+  </si>
+  <si>
     <t>['LOCATION']</t>
   </si>
   <si>
@@ -739,6 +2391,30 @@
     <t>{'CONTACTS': 91, 'LOCATION': 64, 'PERSISTENTID': 123, 'STORAGE': 99, 'CAMERA': 128, 'MICROPHONE': 23}</t>
   </si>
   <si>
+    <t>{'CONTACTS': 162, 'LOCATION': 211, 'PHONE_CALL': 74, 'PERSISTENTID': 166, 'STORAGE': 148, 'CAMERA': 12, 'MICROPHONE': 4}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 83, 'PERSISTENTID': 69, 'STORAGE': 45, 'CAMERA': 12, 'MICROPHONE': 9, 'LOCATION': 48}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 0, 'STORAGE': 0, 'MICROPHONE': 0, 'LOCATION': 0, 'PERSISTENTID': 0}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 87, 'CALENDAR': 113, 'LOCATION': 88, 'SMS': 41, 'PHONE_CALL': 90, 'PERSISTENTID': 171, 'STORAGE': 97, 'CAMERA': 76, 'MICROPHONE': 42}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 18, 'LOCATION': 27, 'SMS': 15, 'PHONE_CALL': 18, 'PERSISTENTID': 28, 'STORAGE': 28, 'CAMERA': 6, 'MICROPHONE': 7}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 65, 'LOCATION': 70, 'SMS': 65, 'PHONE_CALL': 92, 'PERSISTENTID': 108, 'STORAGE': 84, 'CAMERA': 17, 'MICROPHONE': 8}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 0, 'LOCATION': 0, 'PERSISTENTID': 0, 'STORAGE': 0, 'CAMERA': 0, 'MICROPHONE': 0}</t>
+  </si>
+  <si>
+    <t>{'PERSISTENTID': 109}</t>
+  </si>
+  <si>
     <t>{'CONTACTS': {}, 'PERSISTENTID': {}, 'STORAGE': {}, 'LOCATION': {'ip': 1}}</t>
   </si>
   <si>
@@ -755,6 +2431,30 @@
   </si>
   <si>
     <t>{'CONTACTS': {'account': 20, 'contact': 17, 'contact list': 1, 'cooky': 8, 'friend': 29, 'list': 6, 'medium': 1, 'phonebook': 1, 'purpose': 7, 'social': 1}, 'LOCATION': {'gps': 1, 'identifier': 3, 'including': 13, 'ip': 16, 'ip address': 2, 'location': 13, 'location data': 1, 'location information': 4, 'map': 9, 'sensor': 1, 'track': 1}, 'PERSISTENTID': {'advertising id': 2, 'application': 1, 'browser': 4, 'id': 95, 'identifier': 3, 'information collect': 9, 'mobile': 2, 'phone number': 3, 'type setting': 1, 'unique': 2, 'unique identifier': 1}, 'STORAGE': {'account': 20, 'download': 5, 'file': 5, 'receive': 9, 'save': 13, 'share': 35, 'storage': 1, 'upload': 1, 'video': 10}, 'CAMERA': {'activity': 4, 'camera': 5, 'photo': 4, 'service like': 2, 'snap': 102, 'take photo': 1, 'video': 10}, 'MICROPHONE': {'audio': 3, 'information use': 3, 'microphone': 3, 'record audio': 1, 'talk': 2, 'video': 10, 'voice': 1}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {'account': 89, 'contact': 22, 'cooky': 9, 'friend': 2, 'list': 7, 'medium': 4, 'purpose': 23, 'social': 3, 'social medium': 3}, 'LOCATION': {'identifier': 4, 'including': 58, 'ip': 85, 'ip address': 1, 'locate': 3, 'location': 48, 'location data': 7, 'map': 1, 'track': 4}, 'PHONE_CALL': {'application': 2, 'browser': 2, 'call': 9, 'identifier': 4, 'information collect': 3, 'message': 4, 'mobile': 4, 'network': 2, 'phone': 14, 'phone number': 8, 'receive': 21, 'unique': 1}, 'PERSISTENTID': {'advertising id': 1, 'application': 2, 'browser': 2, 'device id': 7, 'id': 134, 'identifier': 4, 'information collect': 3, 'mobile': 4, 'phone number': 8, 'unique': 1}, 'STORAGE': {'account': 89, 'download': 2, 'file': 6, 'receive': 21, 'share': 27, 'storage': 1, 'upload': 2}, 'CAMERA': {'activity': 4, 'photo': 8}, 'MICROPHONE': {'audio': 1, 'information use': 3}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {'account': 10, 'address book': 3, 'contact': 19, 'contact list': 6, 'cooky': 18, 'list': 7, 'medium': 2, 'purpose': 6, 'social': 10, 'social medium': 2}, 'PERSISTENTID': {'advertising id': 1, 'android id': 1, 'application': 1, 'browser': 4, 'device id': 1, 'id': 49, 'identifier': 2, 'information collect': 2, 'mobile': 6, 'phone number': 1, 'unique': 1}, 'STORAGE': {'account': 10, 'download': 2, 'file': 5, 'receive': 4, 'share': 17, 'storage': 2, 'upload': 1, 'video': 4}, 'CAMERA': {'activity': 6, 'photo': 2, 'video': 4}, 'MICROPHONE': {'audio': 1, 'information use': 2, 'video': 4, 'voice': 2}, 'LOCATION': {'gps': 4, 'identifier': 2, 'including': 16, 'ip': 5, 'ip address': 2, 'location': 10, 'location data': 3, 'location information': 1, 'map': 2, 'track': 3}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {}, 'STORAGE': {}, 'MICROPHONE': {}, 'LOCATION': {}, 'PERSISTENTID': {}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {'account': 19, 'contact': 25, 'content service': 1, 'cooky': 14, 'friend': 15, 'list': 1, 'purpose': 8, 'social': 4}, 'CALENDAR': {'book': 10, 'contact': 25, 'event': 9, 'including': 30, 'search': 17, 'use information': 22}, 'LOCATION': {'gps': 1, 'identifier': 14, 'including': 30, 'ip': 15, 'ip address': 12, 'location': 15, 'location information': 1}, 'SMS': {'log': 21, 'message': 11, 'receive': 8, 'use service': 1}, 'PHONE_CALL': {'browser': 17, 'call': 9, 'identifier': 14, 'information collect': 15, 'message': 11, 'network': 16, 'receive': 8}, 'PERSISTENTID': {'browser': 17, 'device id': 1, 'id': 124, 'identifier': 14, 'information collect': 15}, 'STORAGE': {'account': 19, 'download': 3, 'file': 9, 'file communication': 1, 'receive': 8, 'share': 49, 'video': 8}, 'CAMERA': {'activity': 37, 'camera': 26, 'photo': 5, 'video': 8}, 'MICROPHONE': {'audio': 14, 'information use': 6, 'video': 8, 'voice': 14}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {'account': 6, 'contact': 10, 'purpose': 2}, 'LOCATION': {'including': 3, 'ip': 18, 'locate': 5, 'map': 1}, 'SMS': {'log': 7, 'message': 6, 'receive': 1, 'use service': 1}, 'PHONE_CALL': {'call': 2, 'information collect': 4, 'message': 6, 'phone': 3, 'phone number': 2, 'receive': 1}, 'PERSISTENTID': {'id': 22, 'information collect': 4, 'phone number': 2}, 'STORAGE': {'account': 6, 'download': 6, 'file': 4, 'receive': 1, 'share': 8, 'storage': 1, 'video': 2}, 'CAMERA': {'activity': 2, 'photo': 2, 'video': 2}, 'MICROPHONE': {'information use': 3, 'video': 2, 'voice': 2}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {'account': 27, 'address book': 2, 'contact': 17, 'cooky': 6, 'friend': 2, 'list': 4, 'medium': 3, 'purpose': 4}, 'LOCATION': {'identifier': 2, 'including': 24, 'ip': 20, 'ip address': 3, 'locate': 1, 'location': 14, 'location data': 1, 'location information': 3, 'map': 2}, 'SMS': {'log': 8, 'message': 29, 'receive': 10, 'use service': 18}, 'PHONE_CALL': {'browser': 1, 'call': 6, 'identifier': 2, 'information collect': 7, 'message': 29, 'mobile': 9, 'network': 1, 'phone': 15, 'phone number': 11, 'receive': 10, 'unique': 1}, 'PERSISTENTID': {'browser': 1, 'id': 77, 'identifier': 2, 'information collect': 7, 'mobile': 9, 'phone number': 11, 'unique': 1}, 'STORAGE': {'account': 27, 'download': 6, 'file': 10, 'receive': 10, 'share': 27, 'storage': 1, 'upload': 2, 'video': 1}, 'CAMERA': {'activity': 8, 'photo': 4, 'profile photo': 2, 'service like': 2, 'video': 1}, 'MICROPHONE': {'information use': 4, 'talk': 1, 'video': 1, 'voice': 2}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {}, 'LOCATION': {}, 'PERSISTENTID': {}, 'STORAGE': {}, 'CAMERA': {}, 'MICROPHONE': {}}</t>
+  </si>
+  <si>
+    <t>{'PERSISTENTID': {'application': 8, 'browser': 1, 'device id': 6, 'id': 68, 'identifier': 5, 'imei': 3, 'information collect': 3, 'mobile': 9, 'phone number': 1, 'unique': 4, 'unique identifier': 1}}</t>
   </si>
   <si>
     <t>❌ This app uses several permissions (like contacts, persistentid and storage), but doesn’t explain how or why.
@@ -817,6 +2517,24 @@
     <t>{'Purpose_Analytics or research': 0.8602398071024153, 'Purpose_Advertising or marketing': 0.8336667617162069, 'Purpose_Service operation and security': 0.9231236775716146, 'Purpose_Legal requirement': 0.7799467444419861, 'Information Type_Contact information': 0.878225576877594, 'Information Type_Location': 0.8768467009067535, 'Collection Process_Collected on first-party website/app': 0.8744916915893555, 'Purpose_Essential service or feature': 0.7798055211702982, 'Information Type_User online activities': 0.8891043596797519, 'Information Type_Computer information': 0.7992608845233917, 'Information Type_IP address and device IDs': 0.9943147301673889, 'Information Type_Generic personal information': 0.9237729907035828, 'Collection Process_Shared by first party with a third party': 0.726582258939743}</t>
   </si>
   <si>
+    <t>{'Information Type_Generic personal information': 0.7650425500339932, 'Collection Process_Collected on first-party website/app': 0.8029275894165039, 'Information Type_Contact information': 0.8144683904118009, 'Purpose_Essential service or feature': 0.7072132031122843, 'Purpose_Legal requirement': 0.916644016901652, 'Information Type_Health, genetic, or biometric data': 0.5331324934959412, 'Purpose_Advertising or marketing': 0.9740971326828003, 'Information Type_Personal identifier': 0.6192275484402975, 'Information Type_Location': 0.9761630594730377, 'Information Type_User online activities': 0.976525068283081, 'Information Type_Computer information': 0.9603303074836731, 'Information Type_IP address and device IDs': 0.9937660694122314, 'Purpose_Service operation and security': 0.8870320618152618, 'Collection Process_Shared by first party with a third party': 0.8634935021400452, 'Purpose_Analytics or research': 0.5697241425514221}</t>
+  </si>
+  <si>
+    <t>{'Purpose_Essential service or feature': 0.6741171641783281, 'Purpose_Analytics or research': 0.9077772796154022, 'Purpose_Service operation and security': 0.8977640966574351, 'Purpose_Legal requirement': 0.9155191020532087, 'Information Type_Generic personal information': 0.9331792460547553, 'Collection Process_Collected on first-party website/app': 0.8217605298215692, 'Information Type_Contact information': 0.8719618320465088, 'Information Type_Location': 0.8089659114678701, 'Information Type_Computer information': 0.9132554133733114, 'Information Type_User online activities': 0.9595974418852065, 'Collection Process_Shared by first party with a third party': 0.8841601610183716, 'Information Type_IP address and device IDs': 0.9946363866329193, 'Purpose_Advertising or marketing': 0.9298503498236338}</t>
+  </si>
+  <si>
+    <t>{'Information Type_Generic personal information': 0.6706074476242065, 'Collection Process_Shared by first party with a third party': 0.8011803179979324, 'Purpose_Service operation and security': 0.9169465228915215, 'Purpose_Legal requirement': 0.9616091582510207, 'Purpose_Essential service or feature': 0.7149259448051453, 'Purpose_Analytics or research': 0.7856379747390747, 'Collection Process_Collected on first-party website/app': 0.9814310073852539, 'Purpose_Advertising or marketing': 0.8579348444938659, 'Information Type_Contact information': 0.8510975241661072}</t>
+  </si>
+  <si>
+    <t>{'Information Type_Contact information': 0.8808202892541885, 'Purpose_Essential service or feature': 0.7031891494989395, 'Information Type_Generic personal information': 0.7893685599168142, 'Purpose_Analytics or research': 0.7504673429897853, 'Purpose_Service operation and security': 0.7721719486372811, 'Information Type_Health, genetic, or biometric data': 0.5165250301361084, 'Collection Process_Shared by first party with a third party': 0.7921234766642252, 'Collection Process_Collected on first-party website/app': 0.6308806737263998, 'Information Type_User online activities': 0.8586700856685638, 'Purpose_Advertising or marketing': 0.9710175395011902, 'Information Type_Location': 0.767689049243927, 'Purpose_Legal requirement': 0.8916712999343872}</t>
+  </si>
+  <si>
+    <t>{'Information Type_Contact information': 0.8854578658938408, 'Purpose_Essential service or feature': 0.7709387926494374, 'Purpose_Service operation and security': 0.9291250507036845, 'Information Type_Health, genetic, or biometric data': 0.516525149345398, 'Collection Process_Shared by first party with a third party': 0.7387300804257393, 'Purpose_Analytics or research': 0.887497807542483, 'Collection Process_Collected on first-party website/app': 0.8472914457321167, 'Purpose_Advertising or marketing': 0.9375910758972168, 'Information Type_Location': 0.9841348528862, 'Information Type_User online activities': 0.719200611114502, 'Information Type_Computer information': 0.8451553285121918, 'Information Type_IP address and device IDs': 0.9942948222160339, 'Purpose_Legal requirement': 0.9588719308376312, 'Information Type_Generic personal information': 0.5557473599910736}</t>
+  </si>
+  <si>
+    <t>{'Information Type_Contact information': 0.9161156614621481, 'Purpose_Essential service or feature': 0.7567308028539022, 'Information Type_Generic personal information': 0.8836749386787415, 'Information Type_Location': 0.982063102722168, 'Collection Process_Collected on first-party website/app': 0.8971645746912275, 'Purpose_Analytics or research': 0.9588536090321012, 'Information Type_IP address and device IDs': 0.9943044015339443, 'Information Type_User online activities': 0.9593718647956848, 'Information Type_Computer information': 0.8994356989860535, 'Purpose_Advertising or marketing': 0.8612423777580261, 'Collection Process_Shared by first party with a third party': 0.7864545087019602, 'Purpose_Service operation and security': 0.7593016624450684, 'Purpose_Legal requirement': 0.9847841262817383}</t>
+  </si>
+  <si>
     <t>User online activities (Freq: 10, MaxProb: 99%), Analytics or research (Freq: 10, MaxProb: 98%), Advertising or marketing (Freq: 9, MaxProb: 98%), Shared by first party with a third party (Freq: 9, MaxProb: 97%), Essential service or feature (Freq: 9, MaxProb: 88%), Contact information (Freq: 8, MaxProb: 98%), Service operation and security (Freq: 7, MaxProb: 99%), Collected on first-party website/app (Freq: 6, MaxProb: 99%), Legal requirement (Freq: 5, MaxProb: 99%), Generic personal information (Freq: 5, MaxProb: 93%), IP address and device IDs (Freq: 3, MaxProb: 99%), Location (Freq: 3, MaxProb: 99%), Computer information (Freq: 1, MaxProb: 99%), Health, genetic, or biometric data (Freq: 1, MaxProb: 91%)</t>
   </si>
   <si>
@@ -827,6 +2545,24 @@
   </si>
   <si>
     <t>Analytics or research (Freq: 14, MaxProb: 98%), Collected on first-party website/app (Freq: 11, MaxProb: 99%), User online activities (Freq: 9, MaxProb: 99%), Service operation and security (Freq: 9, MaxProb: 99%), Advertising or marketing (Freq: 7, MaxProb: 98%), Essential service or feature (Freq: 5, MaxProb: 87%), Contact information (Freq: 4, MaxProb: 98%), Location (Freq: 3, MaxProb: 99%), Computer information (Freq: 2, MaxProb: 99%), Legal requirement (Freq: 2, MaxProb: 99%), IP address and device IDs (Freq: 1, MaxProb: 99%), Generic personal information (Freq: 1, MaxProb: 92%), Shared by first party with a third party (Freq: 1, MaxProb: 86%)</t>
+  </si>
+  <si>
+    <t>Contact information (Freq: 6, MaxProb: 98%), Essential service or feature (Freq: 6, MaxProb: 80%), Generic personal information (Freq: 5, MaxProb: 93%), Location (Freq: 4, MaxProb: 99%), Collected on first-party website/app (Freq: 3, MaxProb: 99%), Legal requirement (Freq: 3, MaxProb: 96%), Service operation and security (Freq: 2, MaxProb: 92%), IP address and device IDs (Freq: 1, MaxProb: 99%), User online activities (Freq: 1, MaxProb: 98%), Advertising or marketing (Freq: 1, MaxProb: 97%), Computer information (Freq: 1, MaxProb: 96%), Shared by first party with a third party (Freq: 1, MaxProb: 86%), Personal identifier (Freq: 1, MaxProb: 78%)</t>
+  </si>
+  <si>
+    <t>Service operation and security (Freq: 10, MaxProb: 99%), User online activities (Freq: 9, MaxProb: 99%), Legal requirement (Freq: 9, MaxProb: 99%), Analytics or research (Freq: 9, MaxProb: 99%), Shared by first party with a third party (Freq: 9, MaxProb: 97%), Generic personal information (Freq: 9, MaxProb: 94%), Collected on first-party website/app (Freq: 7, MaxProb: 99%), Advertising or marketing (Freq: 6, MaxProb: 98%), Location (Freq: 4, MaxProb: 99%), Essential service or feature (Freq: 4, MaxProb: 86%), Computer information (Freq: 3, MaxProb: 99%), Contact information (Freq: 3, MaxProb: 98%), IP address and device IDs (Freq: 2, MaxProb: 99%)</t>
+  </si>
+  <si>
+    <t>Legal requirement (Freq: 9, MaxProb: 99%), Analytics or research (Freq: 8, MaxProb: 95%), Service operation and security (Freq: 7, MaxProb: 98%), Shared by first party with a third party (Freq: 6, MaxProb: 95%), Advertising or marketing (Freq: 5, MaxProb: 98%), Essential service or feature (Freq: 2, MaxProb: 87%), Collected on first-party website/app (Freq: 1, MaxProb: 98%), Generic personal information (Freq: 1, MaxProb: 94%), Contact information (Freq: 1, MaxProb: 85%)</t>
+  </si>
+  <si>
+    <t>Analytics or research (Freq: 5, MaxProb: 98%), Generic personal information (Freq: 4, MaxProb: 91%), Service operation and security (Freq: 3, MaxProb: 99%), Contact information (Freq: 3, MaxProb: 98%), Legal requirement (Freq: 2, MaxProb: 97%), Shared by first party with a third party (Freq: 2, MaxProb: 95%), User online activities (Freq: 2, MaxProb: 95%), Essential service or feature (Freq: 2, MaxProb: 88%), Advertising or marketing (Freq: 1, MaxProb: 97%), Collected on first-party website/app (Freq: 1, MaxProb: 79%), Location (Freq: 1, MaxProb: 77%)</t>
+  </si>
+  <si>
+    <t>Essential service or feature (Freq: 12, MaxProb: 88%), Service operation and security (Freq: 11, MaxProb: 99%), Analytics or research (Freq: 11, MaxProb: 98%), Advertising or marketing (Freq: 8, MaxProb: 98%), Contact information (Freq: 7, MaxProb: 98%), Shared by first party with a third party (Freq: 5, MaxProb: 95%), Collected on first-party website/app (Freq: 4, MaxProb: 96%), IP address and device IDs (Freq: 3, MaxProb: 99%), Location (Freq: 3, MaxProb: 99%), User online activities (Freq: 2, MaxProb: 99%), Legal requirement (Freq: 2, MaxProb: 98%), Computer information (Freq: 1, MaxProb: 99%)</t>
+  </si>
+  <si>
+    <t>Generic personal information (Freq: 23, MaxProb: 95%), Essential service or feature (Freq: 12, MaxProb: 88%), Contact information (Freq: 9, MaxProb: 98%), Analytics or research (Freq: 9, MaxProb: 98%), IP address and device IDs (Freq: 7, MaxProb: 99%), User online activities (Freq: 6, MaxProb: 99%), Collected on first-party website/app (Freq: 6, MaxProb: 99%), Location (Freq: 5, MaxProb: 99%), Advertising or marketing (Freq: 4, MaxProb: 98%), Shared by first party with a third party (Freq: 4, MaxProb: 97%), Legal requirement (Freq: 3, MaxProb: 99%), Computer information (Freq: 3, MaxProb: 98%), Service operation and security (Freq: 2, MaxProb: 98%)</t>
   </si>
   <si>
     <t>No specific data collection details were detected.</t>
@@ -850,6 +2586,22 @@
 Data collected is used for advertising, analytics or research, essential services, legal compliance and security or app functionality.</t>
   </si>
   <si>
+    <t>This app may collect information such as device/computer info, contact information, other personal information, device ID, location, personal ID and online activity, directly through the app and some of this data may be shared with third parties. 
+Data collected is used for advertising, essential services, legal compliance and security or app functionality.</t>
+  </si>
+  <si>
+    <t>This app may collect information such as contact information and other personal information, directly through the app and some of this data may be shared with third parties. 
+Data collected is used for advertising, analytics or research, essential services, legal compliance and security or app functionality.</t>
+  </si>
+  <si>
+    <t>This app may collect information such as contact information, other personal information, location and online activity, directly through the app and some of this data may be shared with third parties. 
+Data collected is used for advertising, analytics or research, essential services, legal compliance and security or app functionality.</t>
+  </si>
+  <si>
+    <t>This app may collect information such as device/computer info, contact information, device ID, location and online activity, directly through the app and some of this data may be shared with third parties. 
+Data collected is used for advertising, analytics or research, essential services, legal compliance and security or app functionality.</t>
+  </si>
+  <si>
     <t>[{'entity_group': 'DC', 'score': np.float32(0.99287295), 'word': 'Pan', 'start': 133, 'end': 136, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9775852), 'word': '##das Of Caribbean Limited.', 'start': 136, 'end': 161, 'label_readable': 'Data Controller'}]</t>
   </si>
   <si>
@@ -865,6 +2617,24 @@
     <t>[{'entity_group': 'DC', 'score': np.float32(0.9610852), 'word': 'we', 'start': 60, 'end': 62, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9963607), 'word': 'collect', 'start': 81, 'end': 88, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.97891116), 'word': 'use', 'start': 61, 'end': 64, 'label_readable': 'Processing'}, {'entity_group': 'DC', 'score': np.float32(0.99370354), 'word': 'We', 'start': 70, 'end': 72, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.82707036), 'word': 'saved', 'start': 104, 'end': 109, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9899949), 'word': 'share', 'start': 167, 'end': 172, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9796627), 'word': 'to help our community enhance their relationships with friends, family, and the world.', 'start': 118, 'end': 204, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.85248), 'word': 'non - governmental agencies', 'start': 317, 'end': 342, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.96275836), 'word': 'to', 'start': 96, 'end': 98, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7657949), 'word': 'provide resources and support to', 'start': 283, 'end': 315, 'label_readable': 'Required Purpose'}, {'entity_group': 'RI', 'score': np.float32(0.9229669), 'word': 'rights', 'start': 53, 'end': 59, 'label_readable': 'Right'}, {'entity_group': 'P', 'score': np.float32(0.86054456), 'word': 'publish', 'start': 67, 'end': 74, 'label_readable': 'Processing'}, {'entity_group': 'OM', 'score': np.float32(0.8677735), 'word': 'transparency reports', 'start': 75, 'end': 95, 'label_readable': 'Organisational Measure'}, {'entity_group': 'RP', 'score': np.float32(0.94810486), 'word': 'provide insight and visibility into the nature and volume of content and accounts reported to us.', 'start': 99, 'end': 196, 'label_readable': 'Required Purpose'}, {'entity_group': 'OM', 'score': np.float32(0.7197132), 'word': 'operational practices', 'start': 254, 'end': 275, 'label_readable': 'Organisational Measure'}, {'entity_group': 'P', 'score': np.float32(0.9866671), 'word': 'disc', 'start': 36, 'end': 40, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.97197074), 'word': '##lose', 'start': 40, 'end': 44, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.8655465), 'word': 'data', 'start': 192, 'end': 196, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.8663947), 'word': 'into our safety principles, policies, and practices, as well as links to various safety and privacy resources.', 'start': 147, 'end': 257, 'label_readable': 'Required Purpose'}, {'entity_group': 'DC', 'score': np.float32(0.70818216), 'word': '##nap', 'start': 43, 'end': 46, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9939214), 'word': 'process', 'start': 77, 'end': 84, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.84060574), 'word': '.', 'start': 378, 'end': 379, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9418446), 'word': 'your information', 'start': 211, 'end': 227, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.99769336), 'word': 'to provide you a more personalized experience, including to show you content and information that is most relevant to your experience, as well as more relevant advertisements.', 'start': 228, 'end': 403, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9108391), 'word': 'Understanding your interests and preferences help us provide a better product experience.', 'start': 404, 'end': 493, 'label_readable': 'Required Purpose'}, {'entity_group': 'DC', 'score': np.float32(0.94733995), 'word': 'us', 'start': 707, 'end': 709, 'label_readable': 'Data Controller'}, {'entity_group': 'CONS', 'score': np.float32(0.9522425), 'word': 'agree', 'start': 320, 'end': 325, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.8130123), 'word': 'Control', 'start': 0, 'end': 7, 'label_readable': 'Consent'}, {'entity_group': 'OM', 'score': np.float32(0.82023966), 'word': 'who can contact you', 'start': 142, 'end': 161, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.7845727), 'word': 'app.', 'start': 211, 'end': 215, 'label_readable': 'Organisational Measure'}, {'entity_group': 'CONS', 'score': np.float32(0.9035915), 'word': 'be in control of', 'start': 15, 'end': 31, 'label_readable': 'Consent'}, {'entity_group': 'DSR17', 'score': np.float32(0.8785453), 'word': 'Del', 'start': 0, 'end': 3, 'label_readable': 'Art. 17 Right to erasure (‘right to be forgotten’)'}, {'entity_group': 'DSR17', 'score': np.float32(0.91944444), 'word': '##ete your information.', 'start': 3, 'end': 24, 'label_readable': 'Art. 17 Right to erasure (‘right to be forgotten’)'}, {'entity_group': 'DSR17', 'score': np.float32(0.7500371), 'word': 'del', 'start': 40, 'end': 43, 'label_readable': 'Art. 17 Right to erasure (‘right to be forgotten’)'}, {'entity_group': 'DSR17', 'score': np.float32(0.7889591), 'word': '##ete your account', 'start': 43, 'end': 59, 'label_readable': 'Art. 17 Right to erasure (‘right to be forgotten’)'}, {'entity_group': 'P', 'score': np.float32(0.7969973), 'word': 'shared', 'start': 189, 'end': 195, 'label_readable': 'Processing'}, {'entity_group': 'OM', 'score': np.float32(0.8403072), 'word': 'who can see your content.', 'start': 8, 'end': 33, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.7166649), 'word': 'can contact you.', 'start': 12, 'end': 28, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.9110911), 'word': 'controls', 'start': 103, 'end': 111, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.9473556), 'word': 'help you decide who can contact you.', 'start': 117, 'end': 153, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.93922913), 'word': 'you can always block and report that person.', 'start': 194, 'end': 238, 'label_readable': 'Organisational Measure'}, {'entity_group': 'CONS', 'score': np.float32(0.98108304), 'word': 'Change your permissions.', 'start': 0, 'end': 24, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.9455348), 'word': 'you can change your permissions at any time.', 'start': 40, 'end': 84, 'label_readable': 'Consent'}, {'entity_group': 'PD', 'score': np.float32(0.96735), 'word': 'phone number', 'start': 150, 'end': 162, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.98967946), 'word': 'email address', 'start': 170, 'end': 183, 'label_readable': 'Personal Data'}, {'entity_group': 'OM', 'score': np.float32(0.79385674), 'word': 'contacts', 'start': 342, 'end': 350, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.7565916), 'word': 'you can change that later on in your app settings.', 'start': 377, 'end': 427, 'label_readable': 'Organisational Measure'}, {'entity_group': 'CONS', 'score': np.float32(0.8895525), 'word': 'Op', 'start': 0, 'end': 2, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.9274543), 'word': '##t out of', 'start': 2, 'end': 10, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.797515), 'word': 'option', 'start': 46, 'end': 52, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.78327084), 'word': '##t out or unsubscribe from', 'start': 58, 'end': 83, 'label_readable': 'Consent'}, {'entity_group': 'DSR21', 'score': np.float32(0.84886897), 'word': 'right to object to our processing of that', 'start': 110, 'end': 151, 'label_readable': 'Art. 21 Right to object'}, {'entity_group': 'DSR21', 'score': np.float32(0.7913798), 'word': '.', 'start': 163, 'end': 164, 'label_readable': 'Art. 21 Right to object'}, {'entity_group': 'RP', 'score': np.float32(0.7837871), 'word': 'Set advertising preferences.', 'start': 0, 'end': 28, 'label_readable': 'Required Purpose'}, {'entity_group': 'DSO', 'score': np.float32(0.9246801), 'word': 'you provide', 'start': 68, 'end': 79, 'label_readable': 'Data Source'}, {'entity_group': 'DS', 'score': np.float32(0.85255057), 'word': 'you', 'start': 718, 'end': 721, 'label_readable': 'Data Subject'}, {'entity_group': 'CONS', 'score': np.float32(0.72763544), 'word': 'permission', 'start': 298, 'end': 308, 'label_readable': 'Consent'}, {'entity_group': 'P', 'score': np.float32(0.9685947), 'word': 'generate', 'start': 87, 'end': 95, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9533375), 'word': 'receive', 'start': 153, 'end': 160, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9744134), 'word': 'provide', 'start': 699, 'end': 706, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.87883127), 'word': 'details', 'start': 105, 'end': 112, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.763988), 'word': 'name,', 'start': 147, 'end': 152, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9903348), 'word': 'user', 'start': 357, 'end': 361, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7684823), 'word': '##name,', 'start': 157, 'end': 162, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.839853), 'word': 'email address,', 'start': 163, 'end': 177, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7449133), 'word': 'birthday, and', 'start': 178, 'end': 191, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9254656), 'word': 'profile picture', 'start': 304, 'end': 319, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8797827), 'word': 'payment', 'start': 420, 'end': 427, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9358865), 'word': 'physical address', 'start': 463, 'end': 479, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.7702227), 'word': 'so', 'start': 481, 'end': 483, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8103376), 'word': 'can ship the product to you', 'start': 487, 'end': 514, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.97843236), 'word': 'payment information', 'start': 516, 'end': 535, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9503498), 'word': 'so we can process the payment', 'start': 537, 'end': 566, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7497009), 'word': 'transaction history', 'start': 572, 'end': 591, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.95880777), 'word': 'save', 'start': 738, 'end': 742, 'label_readable': 'Processing'}, {'entity_group': 'NPD', 'score': np.float32(0.8631547), 'word': 'which of those Services you ’ ve used', 'start': 56, 'end': 91, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8608531), 'word': 'how you ’ ve used them.', 'start': 96, 'end': 117, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9830011), 'word': 'better understand the way our community uses our Services so that we can make improvements.', 'start': 132, 'end': 223, 'label_readable': 'Required Purpose'}, {'entity_group': 'NPD', 'score': np.float32(0.75784636), 'word': 'how you interact with our Services', 'start': 51, 'end': 85, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.82961464), 'word': 'creative tools', 'start': 343, 'end': 357, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7402587), 'word': 'date and time it was posted', 'start': 463, 'end': 490, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.98951894), 'word': 'to show you more content on Spotlight about basketball.', 'start': 682, 'end': 737, 'label_readable': 'Required Purpose'}, {'entity_group': 'NPD', 'score': np.float32(0.9021148), 'word': 'your', 'start': 47, 'end': 51, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.739927), 'word': 'hardware or software,', 'start': 52, 'end': 73, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8334503), 'word': 'operating system,', 'start': 74, 'end': 91, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9689705), 'word': 'device memory', 'start': 92, 'end': 105, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9011502), 'word': 'advertising identifiers', 'start': 107, 'end': 130, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8981414), 'word': 'apps installed', 'start': 132, 'end': 146, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.89581597), 'word': 'browser type', 'start': 148, 'end': 160, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.80881757), 'word': 'the motion of your device', 'start': 207, 'end': 232, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.861084), 'word': 'whether you have headphones connected', 'start': 273, 'end': 310, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.83636045), 'word': 'information about your wireless and mobile connections )', 'start': 316, 'end': 371, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9900245), 'word': 'location information', 'start': 373, 'end': 393, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9955466), 'word': 'collected', 'start': 255, 'end': 264, 'label_readable': 'Processing'}, {'entity_group': 'TM', 'score': np.float32(0.98130167), 'word': 'cookies', 'start': 433, 'end': 440, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.85277677), 'word': 'similar technologies', 'start': 445, 'end': 465, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.90380204), 'word': 'p', 'start': 505, 'end': 506, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.90171844), 'word': '##ixel', 'start': 506, 'end': 510, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.8630502), 'word': '##s', 'start': 510, 'end': 511, 'label_readable': 'Technical Measure'}, {'entity_group': 'PD', 'score': np.float32(0.9344046), 'word': 'unique advertising identifiers', 'start': 631, 'end': 661, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9472964), 'word': 'log information', 'start': 668, 'end': 683, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8247598), 'word': 'how you ’ ve used our Services', 'start': 707, 'end': 735, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8625566), 'word': 'pages viewed', 'start': 751, 'end': 763, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9711865), 'word': 'IP address', 'start': 765, 'end': 775, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9642874), 'word': 'unique identifiers', 'start': 781, 'end': 799, 'label_readable': 'Personal Data'}, {'entity_group': 'CONS', 'score': np.float32(0.7225502), 'word': 've explicitly granted', 'start': 7, 'end': 28, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.85424596), 'word': '-', 'start': 35, 'end': 36, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.96830636), 'word': 'permissions', 'start': 42, 'end': 53, 'label_readable': 'Consent'}, {'entity_group': 'PD', 'score': np.float32(0.89705455), 'word': 'information about your device phonebook (', 'start': 91, 'end': 132, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.95758224), 'word': 'contacts and related information', 'start': 132, 'end': 164, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9909326), 'word': 'images', 'start': 167, 'end': 173, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.78972775), 'word': 'photos', 'start': 223, 'end': 229, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7664188), 'word': 'precise location', 'start': 411, 'end': 427, 'label_readable': 'Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.7933754), 'word': 'other users', 'start': 103, 'end': 114, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.81473655), 'word': 'affiliates', 'start': 120, 'end': 130, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9636367), 'word': 'third parties.', 'start': 197, 'end': 211, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.98535424), 'word': 'third - party service', 'start': 468, 'end': 487, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.83808047), 'word': 'ad', 'start': 314, 'end': 316, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.7565611), 'word': '##vert', 'start': 286, 'end': 290, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.91486144), 'word': '##isers', 'start': 320, 'end': 325, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.82065076), 'word': 'app developers,', 'start': 327, 'end': 342, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.92195404), 'word': 'publishers', 'start': 343, 'end': 353, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.98414373), 'word': 'third parties', 'start': 527, 'end': 540, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.76014894), 'word': 'to help', 'start': 379, 'end': 386, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9274862), 'word': 'or measure the performance of ads', 'start': 394, 'end': 427, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9901713), 'word': 'contact info', 'start': 430, 'end': 442, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9595644), 'word': 'list', 'start': 530, 'end': 534, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.98092777), 'word': 'combine', 'start': 575, 'end': 582, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9979463), 'word': 'to better understand who you may want to communicate with.', 'start': 629, 'end': 687, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9417643), 'word': 'contact information', 'start': 720, 'end': 739, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9932346), 'word': 'to determine if we can communicate with you in other ways', 'start': 757, 'end': 814, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.90899044), 'word': 'potential violations of our Terms', 'start': 884, 'end': 917, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.8686909), 'word': 'third parties,', 'start': 951, 'end': 965, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.95880437), 'word': 'website publishers', 'start': 976, 'end': 994, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9784315), 'word': 'social network providers', 'start': 996, 'end': 1020, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.8190646), 'word': 'law enforcement,', 'start': 1022, 'end': 1038, 'label_readable': 'Third Party'}, {'entity_group': 'CONS', 'score': np.float32(0.7720369), 'word': 'your permission', 'start': 90, 'end': 105, 'label_readable': 'Consent'}, {'entity_group': 'TP', 'score': np.float32(0.83578396), 'word': 'party', 'start': 221, 'end': 226, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.9772542), 'word': 'to provide you with personalized products and Services that we work hard to build and improve.', 'start': 115, 'end': 209, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8904326), 'word': 'operate', 'start': 32, 'end': 39, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.74202335), 'word': 'deliver', 'start': 41, 'end': 48, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.92413855), 'word': 'in', 'start': 256, 'end': 258, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7401408), 'word': 'order', 'start': 37, 'end': 42, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9893178), 'word': 'to operate, deliver, and maintain our Services.', 'start': 43, 'end': 90, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7140321), 'word': 'to the Map', 'start': 298, 'end': 308, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8970183), 'word': 'your friends', 'start': 313, 'end': 325, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7058351), 'word': 'they ’', 'start': 329, 'end': 334, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9975101), 'word': 'their location', 'start': 345, 'end': 359, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.74617875), 'word': 'you.', 'start': 365, 'end': 369, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9576075), 'word': 'to help keep our products up to date, for example', 'start': 407, 'end': 456, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9663066), 'word': 'to make sure that our Services work with the latest operating systems and devices.', 'start': 457, 'end': 539, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9295839), 'word': 'in order to add context to your Snapchat experience.', 'start': 273, 'end': 325, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.84427166), 'word': 'you', 'start': 642, 'end': 645, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.975465), 'word': 'Personal', 'start': 784, 'end': 792, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9634333), 'word': '##ization', 'start': 792, 'end': 799, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.83001804), 'word': 'suggesting friends', 'start': 35, 'end': 53, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8068991), 'word': '##ing a new friend to send a Snap to based on', 'start': 66, 'end': 109, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.71985954), 'word': 'you Snap with the most.', 'start': 114, 'end': 137, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.96104676), 'word': 'custom', 'start': 315, 'end': 321, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9567529), 'word': '##ize the content we show you, including ads.', 'start': 321, 'end': 364, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9747303), 'word': 'tail', 'start': 814, 'end': 818, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8487575), 'word': '##oring your experience based on who you interact with', 'start': 818, 'end': 870, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7620776), 'word': 'friends are doing', 'start': 890, 'end': 907, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7911408), 'word': 'provide you with more relevant and interesting content.', 'start': 28, 'end': 83, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.7125877), 'word': 'makeup', 'start': 163, 'end': 169, 'label_readable': 'Personal Data'}, {'entity_group': 'ADM', 'score': np.float32(0.93781877), 'word': 'automatically', 'start': 142, 'end': 155, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'RP', 'score': np.float32(0.9795661), 'word': 'to personalize, target, and measure ads.', 'start': 149, 'end': 189, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8502402), 'word': '’ re relevant.', 'start': 221, 'end': 234, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.72269046), 'word': 'choices', 'start': 845, 'end': 852, 'label_readable': 'Consent'}, {'entity_group': 'P', 'score': np.float32(0.8247972), 'word': 'collect, use, and share', 'start': 32, 'end': 55, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.93401134), 'word': 'advertising purposes', 'start': 77, 'end': 97, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.83942294), 'word': 'technologies', 'start': 87, 'end': 99, 'label_readable': 'Technical Measure'}, {'entity_group': 'TP', 'score': np.float32(0.7669269), 'word': 'partners.', 'start': 183, 'end': 192, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.80173016), 'word': '##iser ’ s', 'start': 251, 'end': 257, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.9851375), 'word': 'to show you more relevant ads.', 'start': 266, 'end': 296, 'label_readable': 'Required Purpose'}, {'entity_group': 'OM', 'score': np.float32(0.9475824), 'word': '.', 'start': 403, 'end': 404, 'label_readable': 'Organisational Measure'}, {'entity_group': 'RP', 'score': np.float32(0.80940527), 'word': 'and functionality of', 'start': 552, 'end': 572, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.95072585), 'word': 'partners', 'start': 358, 'end': 366, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.7137756), 'word': 'features', 'start': 54, 'end': 62, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8737505), 'word': 'ways to improve our Services.', 'start': 67, 'end': 96, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.9631997), 'word': 'machine', 'start': 657, 'end': 664, 'label_readable': 'Technical Measure'}, {'entity_group': 'P', 'score': np.float32(0.9094245), 'word': 'comb', 'start': 225, 'end': 229, 'label_readable': 'Processing'}, {'entity_group': 'TM', 'score': np.float32(0.7361562), 'word': 'genera', 'start': 365, 'end': 371, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.81734955), 'word': '##tive', 'start': 371, 'end': 375, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.75416005), 'word': 'artificial', 'start': 389, 'end': 399, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.9650038), 'word': 'algorithms', 'start': 642, 'end': 652, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.91460013), 'word': 'learning models', 'start': 665, 'end': 680, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.94569254), 'word': '##ization, advertising, safety and security, fairness and inclusivity, augmented', 'start': 693, 'end': 771, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9793221), 'word': 'to prevent abuse or other Terms of Service violations.', 'start': 785, 'end': 839, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.75245297), 'word': 'improvements', 'start': 49, 'end': 61, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.70982796), 'word': 'should make', 'start': 65, 'end': 76, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9907286), 'word': 'personal information', 'start': 104, 'end': 124, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.8148139), 'word': 'to develop our features and models.', 'start': 191, 'end': 226, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9182833), 'word': 'In order to understand what to build or how to improve our Services,', 'start': 0, 'end': 68, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.95695335), 'word': 'to understand trends and demand for our features.', 'start': 77, 'end': 126, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.9445014), 'word': 'monitor', 'start': 143, 'end': 150, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.7933675), 'word': 'and trends', 'start': 160, 'end': 170, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9892809), 'word': 'to help decide whether we should change parts of the feature, like the maximum size of a Group.', 'start': 192, 'end': 287, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.9604651), 'word': 'Study', 'start': 288, 'end': 293, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.95737034), 'word': '##ing', 'start': 293, 'end': 296, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9604785), 'word': 'can help us see trends in the ways that people use the Services.', 'start': 320, 'end': 384, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9690683), 'word': 'inspire us to improve Snapchat on a larger scale.', 'start': 396, 'end': 445, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9372219), 'word': '##s in order to identify, monitor, and analyze trends and usage.', 'start': 465, 'end': 527, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.96472853), 'word': 'create', 'start': 584, 'end': 590, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.74713874), 'word': 'information', 'start': 591, 'end': 602, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9946015), 'word': 'to help us understand demand.', 'start': 619, 'end': 648, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.986112), 'word': 'to better understand general consumer interests, trends, and how our Services are used by you and others in our community.', 'start': 20, 'end': 142, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.85195005), 'word': 'anal', 'start': 172, 'end': 176, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7845977), 'word': '##s', 'start': 74, 'end': 75, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9744797), 'word': 'helps us understand more about our community and about how our Services fit into the lives of those in our community.', 'start': 207, 'end': 324, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.83032686), 'word': 'S', 'start': 467, 'end': 468, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.86384624), 'word': '##acles', 'start': 472, 'end': 477, 'label_readable': 'Technical Measure'}, {'entity_group': 'P', 'score': np.float32(0.8666151), 'word': 'used', 'start': 113, 'end': 117, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.99338984), 'word': 'to enhance the safety and security of our Services, verify Snapchatter identity, and prevent fraud or other unauthorized or illegal activity.', 'start': 24, 'end': 165, 'label_re</t>
   </si>
   <si>
+    <t xml:space="preserve">[{'entity_group': 'DC', 'score': np.float32(0.9972355), 'word': 'U', 'start': 0, 'end': 1, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9976017), 'word': '##ber', 'start': 1, 'end': 4, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9103126), 'word': 'us', 'start': 114, 'end': 116, 'label_readable': 'Data Controller'}, {'entity_group': 'PD', 'score': np.float32(0.99183244), 'word': 'personal data.', 'start': 210, 'end': 224, 'label_readable': 'Personal Data'}, {'entity_group': 'DC', 'score': np.float32(0.9835069), 'word': 'We', 'start': 108, 'end': 110, 'label_readable': 'Data Controller'}, {'entity_group': 'PD', 'score': np.float32(0.9950203), 'word': 'personal data ( “ data ” )', 'start': 26, 'end': 48, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.993529), 'word': 'collect', 'start': 51, 'end': 58, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.7311219), 'word': 'data.', 'start': 119, 'end': 124, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9606676), 'word': 'use', 'start': 38, 'end': 41, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9492529), 'word': 'your data', 'start': 28, 'end': 37, 'label_readable': 'Personal Data'}, {'entity_group': 'LB', 'score': np.float32(0.91702247), 'word': 'applicable laws', 'start': 37, 'end': 52, 'label_readable': 'Legal Basis'}, {'entity_group': 'P', 'score': np.float32(0.99488705), 'word': 'processing', 'start': 69, 'end': 79, 'label_readable': 'Processing'}, {'entity_group': 'DS', 'score': np.float32(0.9361229), 'word': 'data subjects', 'start': 159, 'end': 172, 'label_readable': 'Data Subject'}, {'entity_group': 'LB', 'score': np.float32(0.90422916), 'word': 'the', 'start': 235, 'end': 238, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.9195533), 'word': 'local data protection regulation.', 'start': 239, 'end': 272, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.86092335), 'word': 'Australian Privacy Principles.', 'start': 60, 'end': 90, 'label_readable': 'Legal Basis'}, {'entity_group': 'A', 'score': np.float32(0.7811502), 'word': 'the Australian Information Commissioner', 'start': 246, 'end': 285, 'label_readable': 'Authority'}, {'entity_group': 'LB', 'score': np.float32(0.91199994), 'word': 'General Data Protection Law ( Lei Geral de Proteção de Dados - LGPD )', 'start': 89, 'end': 156, 'label_readable': 'Legal Basis'}, {'entity_group': 'SEU', 'score': np.float32(0.92052376), 'word': 'European Economic Area ( “ EEA ” )', 'start': 0, 'end': 30, 'label_readable': 'Scale EU'}, {'entity_group': 'SNEU', 'score': np.float32(0.9706348), 'word': 'United Kingdom', 'start': 32, 'end': 46, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'SNEU', 'score': np.float32(0.9438475), 'word': 'Switzerland', 'start': 59, 'end': 70, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'LB', 'score': np.float32(0.84403384), 'word': 'data protection and other laws', 'start': 7, 'end': 37, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.85255754), 'word': 'European Union ’ s General Data Protection Regulation ( “ GDPR ” )', 'start': 70, 'end': 130, 'label_readable': 'Legal Basis'}, {'entity_group': 'P', 'score': np.float32(0.7753945), 'word': 'collections', 'start': 258, 'end': 269, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9800086), 'word': 'collected', 'start': 8, 'end': 17, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9042108), 'word': 'used', 'start': 388, 'end': 392, 'label_readable': 'Processing'}, {'entity_group': 'RI', 'score': np.float32(0.76289034), 'word': 'your rights', 'start': 285, 'end': 296, 'label_readable': 'Right'}, {'entity_group': 'LB', 'score': np.float32(0.9130396), 'word': 'Kenya ’ s Data Protection Act of 2019.', 'start': 120, 'end': 156, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.97630745), 'word': 'Mexico ’ s Personal Data Protection Law ( Ley Federal de Protección de Datos Personales en Posesión de los Particulares )', 'start': 80, 'end': 197, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.94294244), 'word': 'Nigeria ’ s Data Protection Act of 2023.', 'start': 105, 'end': 143, 'label_readable': 'Legal Basis'}, {'entity_group': 'A', 'score': np.float32(0.90682197), 'word': 'Data Protection Commission', 'start': 177, 'end': 203, 'label_readable': 'Authority'}, {'entity_group': 'ADM', 'score': np.float32(0.92112947), 'word': 'automated decision making', 'start': 87, 'end': 112, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'PD', 'score': np.float32(0.9976274), 'word': 'personal data', 'start': 43, 'end': 56, 'label_readable': 'Personal Data'}, {'entity_group': 'LB', 'score': np.float32(0.8940907), 'word': 'Federal Act on', 'start': 81, 'end': 95, 'label_readable': 'Legal Basis'}, {'entity_group': 'P', 'score': np.float32(0.8408596), 'word': 'transfers', 'start': 98, 'end': 107, 'label_readable': 'Processing'}, {'entity_group': 'LB', 'score': np.float32(0.93537), 'word': 'Taiwan ’ s Personal Data Protection Act', 'start': 127, 'end': 164, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.85870373), 'word': 'relevant regulations', 'start': 173, 'end': 193, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.8656593), 'word': 'US', 'start': 80, 'end': 82, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.83198375), 'word': 'state privacy laws', 'start': 83, 'end': 101, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.95539284), 'word': 'California Consumer Privacy Act.', 'start': 117, 'end': 149, 'label_readable': 'Legal Basis'}, {'entity_group': 'SNEU', 'score': np.float32(0.86515725), 'word': 'Nevada', 'start': 169, 'end': 175, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'SNEU', 'score': np.float32(0.85075176), 'word': 'Washington', 'start': 179, 'end': 189, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'PD', 'score': np.float32(0.9531354), 'word': 'health data', 'start': 11, 'end': 22, 'label_readable': 'Personal Data'}, {'entity_group': 'LB', 'score': np.float32(0.97390974), 'word': 'states ’ privacy laws.', 'start': 318, 'end': 339, 'label_readable': 'Legal Basis'}, {'entity_group': 'RET', 'score': np.float32(0.75457484), 'word': 'create or update your', 'start': 49, 'end': 70, 'label_readable': 'Retention'}, {'entity_group': 'PD', 'score': np.float32(0.9927873), 'word': 'De', 'start': 3, 'end': 5, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9943627), 'word': '##mo', 'start': 5, 'end': 7, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.91960496), 'word': '##graphic data.', 'start': 7, 'end': 20, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9883326), 'word': 'demographic data', 'start': 32, 'end': 48, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9703442), 'word': 'to enable certain features.', 'start': 62, 'end': 89, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9437084), 'word': 'your', 'start': 173, 'end': 177, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8212899), 'word': 'date of birth and / or age', 'start': 16, 'end': 40, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9776234), 'word': 'to verify your eligibility to use age - restricted products or services', 'start': 41, 'end': 110, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.8768425), 'word': 'collect or', 'start': 3, 'end': 13, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9094199), 'word': 'in', 'start': 14, 'end': 16, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9482697), 'word': 'your gender', 'start': 20, 'end': 31, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9407064), 'word': 'to enable Women Rider Preference,', 'start': 32, 'end': 65, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9543928), 'word': 'for marketing and advertising.', 'start': 70, 'end': 100, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9899746), 'word': 'Identity verification information.', 'start': 3, 'end': 37, 'label_readable': 'Personal Data'}, {'entity_group': 'DC', 'score': np.float32(0.96821904), 'word': 'we', 'start': 129, 'end': 131, 'label_readable': 'Data Controller'}, {'entity_group': 'RP', 'score': np.float32(0.88268614), 'word': 'to verify your account or identity', 'start': 78, 'end': 112, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.8632415), 'word': 'Government - issued identification documents', 'start': 0, 'end': 42, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9887236), 'word': 'driver ’ s licenses', 'start': 68, 'end': 85, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9643476), 'word': 'passports', 'start': 89, 'end': 98, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9932524), 'word': 'identification photos', 'start': 102, 'end': 123, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9831724), 'word': 'ex', 'start': 137, 'end': 139, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.94881934), 'word': '##piration date', 'start': 139, 'end': 152, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9920147), 'word': 'date of birth', 'start': 149, 'end': 162, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.98906285), 'word': 'gender', 'start': 168, 'end': 174, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.75804687), 'word': 'Use', 'start': 3, 'end': 6, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.7963726), 'word': '##load', 'start': 2, 'end': 6, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.98452353), 'word': 'photos', 'start': 7, 'end': 13, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.82240736), 'word': 'recordings', 'start': 18, 'end': 28, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9896136), 'word': 'Pro', 'start': 0, 'end': 3, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.89134544), 'word': '##vide ratings or feedback', 'start': 3, 'end': 27, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.7129749), 'word': 'other users', 'start': 66, 'end': 77, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.9935177), 'word': 'Travel information.', 'start': 3, 'end': 22, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9960138), 'word': 'travel itinerary information', 'start': 34, 'end': 62, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9779821), 'word': 'Location data.', 'start': 3, 'end': 17, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9534464), 'word': 'track', 'start': 44, 'end': 49, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.725904), 'word': 'your driver ’ s location', 'start': 50, 'end': 72, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.861321), 'word': 'link', 'start': 95, 'end': 99, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.70872414), 'word': 'your', 'start': 113, 'end': 117, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.95200646), 'word': 'to display where you are on your trip.', 'start': 142, 'end': 180, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.7936977), 'word': 'approximate location', 'start': 192, 'end': 212, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.81804913), 'word': 'precise location', 'start': 178, 'end': 194, 'label_readable': 'Personal Data'}, {'entity_group': 'RET', 'score': np.float32(0.87977946), 'word': 'from the time you request a ride or order', 'start': 195, 'end': 236, 'label_readable': 'Retention'}, {'entity_group': 'RET', 'score': np.float32(0.97427213), 'word': 'until the ride is finished or your order is delivered.', 'start': 237, 'end': 291, 'label_readable': 'Retention'}, {'entity_group': 'PD', 'score': np.float32(0.964314), 'word': 'precise location.', 'start': 49, 'end': 66, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.7380739), 'word': 'type', 'start': 146, 'end': 150, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.96163774), 'word': 'your location', 'start': 151, 'end': 164, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.95590687), 'word': 'precise location data', 'start': 108, 'end': 129, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7410414), 'word': 'Trip /', 'start': 3, 'end': 8, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.74347425), 'word': 'information', 'start': 14, 'end': 25, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.89898163), 'word': 'Us', 'start': 3, 'end': 5, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.85794324), 'word': '##age data.', 'start': 5, 'end': 14, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.92060554), 'word': 'how you interact with', 'start': 41, 'end': 62, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9138685), 'word': 'apps', 'start': 70, 'end': 74, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.86792374), 'word': 'Devi', 'start': 3, 'end': 7, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.74415255), 'word': '##ce data', 'start': 7, 'end': 14, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8924153), 'word': 'about the device ( s ) you use to', 'start': 36, 'end': 66, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.97176105), 'word': 'Communications data.', 'start': 3, 'end': 23, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.85353285), 'word': 'Content', 'start': 0, 'end': 7, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9472999), 'word': 'recordings of phone calls', 'start': 19, 'end': 44, 'label_readable': 'Personal Data'}, {'entity_group': 'A', 'score': np.float32(0.82240885), 'word': 'Law enforcement officials', 'start': 3, 'end': 28, 'label_readable': 'Authority'}, {'entity_group': 'PD', 'score': np.float32(0.82444835), 'word': '- issued identification documents', 'start': 27, 'end': 59, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9872538), 'word': 'identification numbers', 'start': 108, 'end': 130, 'label_readable': 'Personal Data'}, {'entity_group': 'DS', 'score': np.float32(0.87884414), 'word': 'you', 'start': 141, 'end': 144, 'label_readable': 'Data Subject'}, {'entity_group': 'P', 'score': np.float32(0.8694262), 'word': 'receive', 'start': 76, 'end': 83, 'label_readable': 'Processing'}, {'entity_group': 'DSO', 'score': np.float32(0.7202594), 'word': 'business partners', 'start': 99, 'end': 116, 'label_readable': 'Data Source'}, {'entity_group': 'P', 'score': np.float32(0.95669925), 'word': 'received', 'start': 16, 'end': 24, 'label_readable': 'Processing'}, {'entity_group': 'TP', 'score': np.float32(0.92304593), 'word': 'partners', 'start': 13, 'end': 21, 'label_readable': 'Third Party'}, {'entity_group': 'R', 'score': np.float32(0.75723225), 'word': '##ber business partners', 'start': 4, 'end': 25, 'label_readable': 'Recipient'}, {'entity_group': 'PD', 'score': np.float32(0.7999055), 'word': 'recordings of', 'start': 91, 'end': 104, 'label_readable': 'Personal Data'}, {'entity_group': 'DS', 'score': np.float32(0.71074724), 'word': 'Users', 'start': 3, 'end': 8, 'label_readable': 'Data Subject'}, {'entity_group': 'DSO', 'score': np.float32(0.84364283), 'word': 'user', 'start': 141, 'end': 145, 'label_readable': 'Data Source'}, {'entity_group': 'P', 'score': np.float32(0.99281037), 'word': 'uses', 'start': 33, 'end': 37, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.94038135), 'word': 'data', 'start': 78, 'end': 82, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.99816513), 'word': 'to enable reliable and convenient transportation, delivery, and other products and services.', 'start': 15, 'end': 107, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.88560164), 'word': 'To', 'start': 0, 'end': 2, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.97262573), 'word': 'enhance the safety and security of our users and services', 'start': 3, 'end': 60, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9487292), 'word': 'to prevent and detect fraud', 'start': 66, 'end': 93, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9913044), 'word': 'To provide our services.', 'start': 3, 'end': 27, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.99538314), 'word': 'to provide, personalize, maintain, and improve our services.', 'start': 43, 'end': 103, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9502699), 'word': 'En', 'start': 0, 'end': 2, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9639025), 'word': '##ab', 'start': 2, 'end': 4, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9765064), 'word': '##ling navigation to pickups and dropoffs', 'start': 4, 'end': 43, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9554425), 'word': 'calculating ETAs', 'start': 45, 'end': 61, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9897268), 'word': 'tracking the progress of rides or deliveries', 'start': 66, 'end': 110, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.7269015), 'word': 'Match', 'start': 0, 'end': 5, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9826093), 'word': 'sharing', 'start': 14, 'end': 21, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.98093665), 'word': 'F', 'start': 0, 'end': 1, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.98544914), 'word': '##ac', 'start': 1, 'end': 3, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9435832), 'word': '##ilitating and optimizing rental car reservations, pickup and dropoff through', 'start': 3, 'end': 79, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8215503), 'word': 'Process', 'start': 3, 'end': 10, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.91254985), 'word': '##ing payments', 'start': 10, 'end': 22, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9275901), 'word': 'enabling payment and e - money products', 'start': 27, 'end': 64, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9934802), 'word': 'Personal', 'start': 3, 'end': 11, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.933041), 'word': '##izing your account.', 'start': 11, 'end': 30, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.991928), 'word': '##vid', 'start': 3, 'end': 6, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9964894), 'word': '##ing you with trip or delivery updates', 'start': 6, 'end': 43, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.94885254), 'word': 'generating receipts', 'start': 51, 'end': 70, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7571454), 'word': 'In', 'start': 3, 'end': 5, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7438643), 'word': '##form', 'start': 5, 'end': 9, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.90206486), 'word': '##ing you of changes to our terms, services, or policies', 'start': 9, 'end': 63, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9788815), 'word': 'For safety, security, and fraud prevention and detection.', 'start': 3, 'end': 60, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9970146), 'word': 'to help maintain the safety and security of our services and users.', 'start': 76, 'end': 143, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.97103405), 'word': 'V', 'start': 3, 'end': 4, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.95869327), 'word': '##eri', 'start': 4, 'end': 7, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9202443), 'word': '##fying your account, identity or compliance with safety requirements.', 'start': 7, 'end': 75, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.76182866), 'word': '##fying that you are who you say you are', 'start': 4, 'end': 42, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.8497557), 'word': 'checking', 'start': 52, 'end': 60, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.7602287), 'word': 'name,', 'start': 120, 'end': 125, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8045032), 'word': 'email,', 'start': 126, 'end': 132, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.91500336), 'word': 'telephone number', 'start': 133, 'end': 149, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9753742), 'word': 'payment information', 'start': 168, 'end': 187, 'label_readable': 'Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.98863345), 'word': 'third - party', 'start': 197, 'end': 208, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.75292957), 'word': 'Col', 'start': 0, 'end': 3, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9605525), 'word': '##lect', 'start': 3, 'end': 7, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.8992902), 'word': '##ing', 'start': 7, 'end': 10, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.8709578), 'word': 'your ID number', 'start': 11, 'end': 25, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9852365), 'word': 'a', 'start': 49, 'end': 50, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9719418), 'word': 'photo of your ID', 'start': 35, 'end': 51, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.98899496), 'word': 'real - time selfie', 'start': 13, 'end': 29, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.85751253), 'word': 'ID', 'start': 72, 'end': 74, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.8209721), 'word': '##fying', 'start': 4, 'end': 9, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.80495596), 'word': 'identity and / or age', 'start': 15, 'end': 34, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.97025216), 'word': 'collecting', 'start': 38, 'end': 48, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.7357139), 'word': 'Pre', 'start': 3, 'end': 6, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.72507286), 'word': '##ing, and combating fraud', 'start': 21, 'end': 45, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8795107), 'word': '##ing live support', 'start': 9, 'end': 25, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.91814786), 'word': 'to market', 'start': 76, 'end': 85, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8520972), 'word': 'services', 'start': 90, 'end': 98, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8875351), 'word': '##izing marketing communications and ads relating to', 'start': 11, 'end': 61, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8770907), 'word': 'products and services', 'start': 67, 'end': 88, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.82549286), 'word': '.', 'start': 110, 'end': 111, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.8678449), 'word': '##ize sponsored listings, discounts or promotions for', 'start': 8, 'end': 59, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.887378), 'word': 'investigating and', 'start': 14, 'end': 31, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.947817), 'word': 'addressing user concerns', 'start': 32, 'end': 56, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9620702), 'word': 'monitoring and', 'start': 58, 'end': 72, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.94980353), 'word': 'improving our customer support responses and processes', 'start': 73, 'end': 127, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.96627116), 'word': 'identifying potential participants in research studies relating to customer support issues.', 'start': 133, 'end': 224, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9237597), 'word': 'analysis, research and product development, including training machine learning models.', 'start': 16, 'end': 103, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.86966646), 'word': 'services more convenient and easy - to - use, enhance the safety and security of our services, and develop new services and features.', 'start': 127, 'end': 256, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.79350513), 'word': 'to investigate or address claims or disputes relating to use of', 'start': 12, 'end': 75, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.75182986), 'word': 'to satisfy requirements', 'start': 93, 'end': 116, 'label_readable': 'Required Purpose'}, {'entity_group': 'ADM', 'score': np.float32(0.93887705), 'word': 'automated processes', 'start': 10, 'end': 29, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'RP', 'score': np.float32(0.93493587), 'word': 'matching, pricing and fraud prevention and detection.', 'start': 125, 'end': 178, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9119851), 'word': 'fraud detection and prevention.', 'start': 239, 'end': 270, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.99086), 'word': 'personal', 'start': 162, 'end': 170, 'label_readable': 'Personal Data'}, {'entity_group': 'TM', 'score': np.float32(0.96064526), 'word': 'algorithms', 'start': 10, 'end': 20, 'label_readable': 'Technical Measure'}, {'entity_group': 'DS', 'score': np.float32(0.88393575), 'word': 'Riders', 'start': 30, 'end': 36, 'label_readable': 'Data Subject'}, {'entity_group': 'PD', 'score': np.float32(0.8926703), 'word': 'location', 'start': 183, 'end': 191, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.74139106), 'word': 'traffic conditions', 'start': 278, 'end': 296, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.98770946), 'word': 'historical data', 'start': 313, 'end': 328, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.77644515), 'word': 'communicated', 'start': 37, 'end': 49, 'label_readable': 'Processing'}, {'entity_group': 'OM', 'score': np.float32(0.76291126), 'word': 'refining our', 'start': 18, 'end': 30, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.70843583), 'word': 'process', 'start': 40, 'end': 47, 'label_readable': 'Organisational Measure'}, {'entity_group': 'RP', 'score': np.float32(0.774661), 'word': 'to', 'start': 48, 'end': 50, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7946281), 'word': 'provide the best experience to all', 'start': 51, 'end': 85, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7945996), 'word': 'to maintain reliability', 'start': 243, 'end': 266, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.90819836), 'word': 'restore balance.', 'start': 271, 'end': 287, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.9219234), 'word': 'machine', 'start': 25, 'end': 32, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.9612747), 'word': 'to prevent and detect fraud against', 'start': 49, 'end': 84, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7491429), 'word': 'or our users.', 'start': 90, 'end': 103, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.83984303), 'word': 'third - party aggregators.', 'start': 234, 'end': 258, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.933575), 'word': 'generated', 'start': 215, 'end': 224, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9906227), 'word': 'location data', 'start': 245, 'end': 258, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8665735), 'word': 'payment information,', 'start': 260, 'end': 280, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7530132), 'word': 'usage.', 'start': 290, 'end': 296, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.87236065), 'word': 'examine', 'start': 305, 'end': 312, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.95908505), 'word': 'to help detect suspicious behavior.', 'start': 367, 'end': 402, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.984092), 'word': 'cookies', 'start': 71, 'end': 78, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.961079), 'word': 'identification technologies', 'start': 44, 'end': 71, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.9658095), 'word': 'Cook', 'start': 0, 'end': 4, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.9012861), 'word': '##ies', 'start': 4, 'end': 7, 'label_readable': 'Technical Measure'}, {'entity_group': 'P', 'score': np.float32(0.92675537), 'word': 'stored', 'start': 38, 'end': 44, 'label_readable': 'Processing'}, {'entity_group': 'TM', 'score': np.float32(0.8789977), 'word': 'similar technologies', 'start': 132, 'end': 152, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.9570304), 'word': 'Ana', 'start': 0, 'end': 3, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9262181), 'word': '##ly', 'start': 3, 'end': 5, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.94663906), 'word': '##zing site traffic and trends', 'start': 5, 'end': 33, 'label_readable': 'Required </t>
+  </si>
+  <si>
+    <t>[{'entity_group': 'P', 'score': np.float32(0.89325094), 'word': 'provided', 'start': 88, 'end': 96, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.91252166), 'word': 'controlled', 'start': 24, 'end': 34, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.99597156), 'word': 'personal data', 'start': 97, 'end': 110, 'label_readable': 'Personal Data'}, {'entity_group': 'DC', 'score': np.float32(0.97133887), 'word': 'we', 'start': 95, 'end': 97, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9960861), 'word': 'collect', 'start': 98, 'end': 105, 'label_readable': 'Processing'}, {'entity_group': 'DSO', 'score': np.float32(0.7747374), 'word': 'provide', 'start': 128, 'end': 135, 'label_readable': 'Data Source'}, {'entity_group': 'DC', 'score': np.float32(0.99072266), 'word': 'us', 'start': 164, 'end': 166, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9939877), 'word': 'processed', 'start': 151, 'end': 160, 'label_readable': 'Processing'}, {'entity_group': 'CONS', 'score': np.float32(0.96091706), 'word': 'consent', 'start': 464, 'end': 471, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.8801986), 'word': '##ing', 'start': 471, 'end': 474, 'label_readable': 'Consent'}, {'entity_group': 'DC', 'score': np.float32(0.9746995), 'word': 'We', 'start': 0, 'end': 2, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.97206306), 'word': 'use', 'start': 271, 'end': 274, 'label_readable': 'Processing'}, {'entity_group': 'DS', 'score': np.float32(0.8842082), 'word': 'you', 'start': 45, 'end': 48, 'label_readable': 'Data Subject'}, {'entity_group': 'P', 'score': np.float32(0.9924994), 'word': 'share', 'start': 150, 'end': 155, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9836578), 'word': 'shared', 'start': 107, 'end': 113, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.8323638), 'word': 'public profile,', 'start': 246, 'end': 261, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8664609), 'word': 'name,', 'start': 262, 'end': 267, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8684339), 'word': 'identification number,', 'start': 268, 'end': 290, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.87061465), 'word': 'address,', 'start': 291, 'end': 299, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8429685), 'word': 'email address,', 'start': 300, 'end': 314, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8721902), 'word': 'social media login details,', 'start': 315, 'end': 342, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.80178237), 'word': 'telephone number,', 'start': 343, 'end': 360, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.73138463), 'word': '##ing records', 'start': 402, 'end': 413, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.78298235), 'word': 'billing details', 'start': 473, 'end': 488, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.97730017), 'word': 'photos', 'start': 516, 'end': 522, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9389016), 'word': 'videos', 'start': 524, 'end': 530, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9622493), 'word': 'voice recordings', 'start': 703, 'end': 719, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9535892), 'word': 're', 'start': 665, 'end': 667, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9783957), 'word': 'post', 'start': 668, 'end': 672, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9911982), 'word': 'location data', 'start': 812, 'end': 825, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8777633), 'word': 'log data', 'start': 695, 'end': 703, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.76648504), 'word': 'log data )', 'start': 830, 'end': 839, 'label_readable': 'Personal Data'}, {'entity_group': 'RET', 'score': np.float32(0.9218186), 'word': 'for so long as you or a user that has shared such information retains it.', 'start': 953, 'end': 1026, 'label_readable': 'Retention'}, {'entity_group': 'DSO', 'score': np.float32(0.8594757), 'word': 'you', 'start': 14, 'end': 17, 'label_readable': 'Data Source'}, {'entity_group': 'DSO', 'score': np.float32(0.84686977), 'word': 'from your social networks.', 'start': 24, 'end': 50, 'label_readable': 'Data Source'}, {'entity_group': 'CONS', 'score': np.float32(0.9373206), 'word': 'choose', 'start': 131, 'end': 137, 'label_readable': 'Consent'}, {'entity_group': 'P', 'score': np.float32(0.75165665), 'word': 'provide', 'start': 249, 'end': 256, 'label_readable': 'Processing'}, {'entity_group': 'DSO', 'score': np.float32(0.8029733), 'word': 'from', 'start': 277, 'end': 281, 'label_readable': 'Data Source'}, {'entity_group': 'DSO', 'score': np.float32(0.8284252), 'word': 'your social network', 'start': 282, 'end': 301, 'label_readable': 'Data Source'}, {'entity_group': 'DSO', 'score': np.float32(0.8753998), 'word': 'public forum accounts.', 'start': 305, 'end': 327, 'label_readable': 'Data Source'}, {'entity_group': 'TP', 'score': np.float32(0.8428116), 'word': 'social network provider', 'start': 476, 'end': 499, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.9910347), 'word': 'processes', 'start': 500, 'end': 509, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.95532215), 'word': 'IP address', 'start': 89, 'end': 99, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9468598), 'word': 'unique device identifiers', 'start': 109, 'end': 134, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9164859), 'word': 'Google advertising ID,', 'start': 143, 'end': 165, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7386685), 'word': 'Android ID,', 'start': 166, 'end': 177, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.97194314), 'word': 'I', 'start': 179, 'end': 180, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7290393), 'word': '##dentifier for Advertising,', 'start': 180, 'end': 206, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.87502563), 'word': 'mobile carrier', 'start': 235, 'end': 249, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7414583), 'word': 'time zone', 'start': 251, 'end': 260, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8419718), 'word': '##e setting', 'start': 270, 'end': 279, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.980343), 'word': 'operating system and platform', 'start': 281, 'end': 310, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.960645), 'word': 'hardware and software versions', 'start': 312, 'end': 342, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.90619487), 'word': 'battery level', 'start': 344, 'end': 357, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8722445), 'word': 'signal strength', 'start': 359, 'end': 374, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.880575), 'word': 'available storage space', 'start': 376, 'end': 399, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.88671243), 'word': 'browser type', 'start': 401, 'end': 413, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.84453607), 'word': 'app and file names and types', 'start': 415, 'end': 443, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.97698146), 'word': 'Blue', 'start': 445, 'end': 449, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.886907), 'word': '##tooth signals', 'start': 449, 'end': 462, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.96751547), 'word': 'International Mobile Equipment Identity', 'start': 464, 'end': 503, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.98175675), 'word': 'International Mobile Subscriber Identity', 'start': 505, 'end': 545, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.81355065), 'word': 'your GPS location', 'start': 665, 'end': 682, 'label_readable': 'Personal Data'}, {'entity_group': 'ADM', 'score': np.float32(0.7806544), 'word': 'automated decision - making, including profiling', 'start': 767, 'end': 813, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'RP', 'score': np.float32(0.8632938), 'word': 'op', 'start': 890, 'end': 892, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.86608076), 'word': '##ti', 'start': 892, 'end': 894, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.89897245), 'word': '##mizing the Services', 'start': 894, 'end': 913, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.90754455), 'word': '##oring it to your preferences.', 'start': 922, 'end': 951, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.7278217), 'word': 'interactions', 'start': 218, 'end': 230, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.96643806), 'word': 'link', 'start': 260, 'end': 264, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.94637924), 'word': 'contact or subscriber information', 'start': 270, 'end': 303, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8258917), 'word': 'email', 'start': 370, 'end': 375, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8697683), 'word': 'social media log - in details', 'start': 379, 'end': 406, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9832529), 'word': 'process', 'start': 36, 'end': 43, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.88918364), 'word': 'location information', 'start': 87, 'end': 107, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7169266), 'word': 'device location settings', 'start': 153, 'end': 177, 'label_readable': 'Personal Data'}, {'entity_group': 'TM', 'score': np.float32(0.8926318), 'word': 'Global Positioning System ( GPS ).', 'start': 231, 'end': 263, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.99762595), 'word': 'to provide you with location - based services, such as features, notifications, marketing, or other content that is influenced by your location.', 'start': 292, 'end': 434, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.76331574), 'word': 'GPS location', 'start': 468, 'end': 480, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9674605), 'word': 'Post', 'start': 21, 'end': 25, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.8676855), 'word': 'images', 'start': 45, 'end': 51, 'label_readable': 'Personal Data'}, {'entity_group': 'ADM', 'score': np.float32(0.7155083), 'word': 'automatically upload', 'start': 85, 'end': 105, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'P', 'score': np.float32(0.81755435), 'word': 'describes', 'start': 178, 'end': 187, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9867378), 'word': 'collected', 'start': 395, 'end': 404, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.76650447), 'word': 'format', 'start': 429, 'end': 435, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.78166324), 'word': 'your', 'start': 480, 'end': 484, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7769102), 'word': 'account name', 'start': 485, 'end': 497, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8876927), 'word': 'has', 'start': 673, 'end': 676, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.80198914), 'word': '##hta', 'start': 676, 'end': 679, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7256467), 'word': '##gs used to', 'start': 679, 'end': 689, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7567441), 'word': '##words', 'start': 698, 'end': 703, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.9529634), 'word': 'third parties.', 'start': 19, 'end': 33, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.93879086), 'word': 'receive', 'start': 42, 'end': 49, 'label_readable': 'Processing'}, {'entity_group': 'TP', 'score': np.float32(0.9564135), 'word': 'third parties', 'start': 177, 'end': 190, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.8807383), 'word': 'Contact Information.', 'start': 2, 'end': 22, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9937338), 'word': 'contact information', 'start': 38, 'end': 57, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.81313014), 'word': 'your contact list, address book', 'start': 63, 'end': 94, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9975091), 'word': 'to help you and others find people you may know and enable you to link your Boomplay contact list with the contact lists on your device and / or in your account on third party services.', 'start': 119, 'end': 302, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.74795943), 'word': 'your consent', 'start': 319, 'end': 331, 'label_readable': 'Consent'}, {'entity_group': 'PD', 'score': np.float32(0.7813866), 'word': 'contact list', 'start': 450, 'end': 462, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.79499644), 'word': 'address book', 'start': 364, 'end': 376, 'label_readable': 'Personal Data'}, {'entity_group': 'CONS', 'score': np.float32(0.79145896), 'word': '.', 'start': 392, 'end': 393, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.7365073), 'word': 'disal', 'start': 423, 'end': 428, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.81498873), 'word': '##low', 'start': 428, 'end': 431, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.81722605), 'word': 'changing your settings.', 'start': 483, 'end': 506, 'label_readable': 'Consent'}, {'entity_group': 'TP', 'score': np.float32(0.79238975), 'word': 'Third - party Services.', 'start': 2, 'end': 23, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.91541404), 'word': 'third - party service,', 'start': 78, 'end': 98, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9100794), 'word': 'Facebook', 'start': 107, 'end': 115, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.749493), 'word': 'Google,', 'start': 117, 'end': 124, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.73206925), 'word': '##sta', 'start': 127, 'end': 130, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9872655), 'word': 'third - party service', 'start': 192, 'end': 211, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.92134905), 'word': 'user name', 'start': 267, 'end': 276, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9947844), 'word': 'gender', 'start': 278, 'end': 284, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9787637), 'word': 'profile image', 'start': 286, 'end': 299, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9763115), 'word': 'birthday', 'start': 301, 'end': 309, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9582701), 'word': 'contact list.', 'start': 334, 'end': 347, 'label_readable': 'Personal Data'}, {'entity_group': 'TM', 'score': np.float32(0.9835127), 'word': 'cookies', 'start': 7, 'end': 14, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.72357243), 'word': 'similar technologies', 'start': 25, 'end': 45, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.86401355), 'word': 'web beacons,', 'start': 52, 'end': 64, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.84066963), 'word': 'Flash cookies,', 'start': 65, 'end': 79, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.8687354), 'word': 'A', 'start': 80, 'end': 81, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.7475928), 'word': '##pp cache', 'start': 81, 'end': 89, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.98258865), 'word': 'to enhance your experience using Boomplay.', 'start': 111, 'end': 153, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.99358726), 'word': 'Cook', 'start': 334, 'end': 338, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.9917814), 'word': '##ies', 'start': 338, 'end': 341, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.79885596), 'word': 'provide certain features and functionality.', 'start': 226, 'end': 269, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.93218786), 'word': 'to keep your account and data safe and secure.', 'start': 101, 'end': 147, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9468713), 'word': 'move around', 'start': 119, 'end': 130, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8987627), 'word': '##play', 'start': 135, 'end': 139, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7612669), 'word': 'using it.', 'start': 154, 'end': 163, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.84911805), 'word': 'to improve the way Boomplay works,', 'start': 178, 'end': 212, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9663171), 'word': 'ensuring that users are able to find what they are looking for easily.', 'start': 229, 'end': 299, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7353143), 'word': 'to', 'start': 41, 'end': 43, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.74674356), 'word': 'recognize', 'start': 44, 'end': 53, 'label_readable': 'Required Purpose'}, {'entity_group': 'RET', 'score': np.float32(0.7669222), 'word': 'when', 'start': 58, 'end': 62, 'label_readable': 'Retention'}, {'entity_group': 'RP', 'score': np.float32(0.7780188), 'word': 'to personalize our content for you', 'start': 103, 'end': 137, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7927625), 'word': 'greet you by name', 'start': 139, 'end': 156, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.83303636), 'word': 'remember your preferences', 'start': 161, 'end': 186, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.97723603), 'word': 'to make Boomplay and the advertising displayed on it more relevant to your interests.', 'start': 156, 'end': 241, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.75409025), 'word': 'for', 'start': 296, 'end': 299, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.80497116), 'word': 'this purpose.', 'start': 300, 'end': 313, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.95084137), 'word': 'op', 'start': 273, 'end': 275, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.9689706), 'word': '##t out', 'start': 275, 'end': 280, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.87414974), 'word': 'consent to the', 'start': 312, 'end': 326, 'label_readable': 'Consent'}, {'entity_group': 'TP', 'score': np.float32(0.99161935), 'word': 'third - party websites', 'start': 125, 'end': 145, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.90722245), 'word': 'online services.', 'start': 149, 'end': 165, 'label_readable': 'Third Party'}, {'entity_group': 'TM', 'score': np.float32(0.7676834), 'word': 'third - party analytics tools', 'start': 20, 'end': 47, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.94109756), 'word': 'to help us measure traffic and usage trends for the Services.', 'start': 48, 'end': 109, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8558491), 'word': 'that assists us in improving the Service.', 'start': 351, 'end': 392, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.85303724), 'word': 'used', 'start': 417, 'end': 421, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9739917), 'word': 'to report and evaluate your activities and patterns as', 'start': 422, 'end': 476, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.99474347), 'word': 'to provide services in accordance with these activities.', 'start': 496, 'end': 552, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8594585), 'word': 'To', 'start': 2, 'end': 4, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.89159393), 'word': 'administer Boomplay', 'start': 5, 'end': 24, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9821703), 'word': 'to provide our Services to you )', 'start': 31, 'end': 62, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.884482), 'word': 'for internal operations, including', 'start': 67, 'end': 101, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.75907326), 'word': 'troubles', 'start': 102, 'end': 110, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7233432), 'word': '##hoot', 'start': 110, 'end': 114, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9565419), 'word': '##ing, data analysis,', 'start': 114, 'end': 133, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9281915), 'word': 'testing, research, statistical and survey purposes', 'start': 134, 'end': 184, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.94179916), 'word': 'to guarantee Boomplay ’ s stability and security )', 'start': 191, 'end': 238, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8106238), 'word': 'to solicit your feedback', 'start': 243, 'end': 267, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.87954473), 'word': 'personal', 'start': 5, 'end': 13, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9607094), 'word': '##ize the content', 'start': 13, 'end': 28, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.94826007), 'word': 'receive', 'start': 33, 'end': 40, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8107623), 'word': 'provide you with tailored content that will be', 'start': 45, 'end': 91, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.95290166), 'word': 'To improve and develop Boomplay and conduct product development', 'start': 2, 'end': 65, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8442896), 'word': 'understand', 'start': 17, 'end': 27, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.87443006), 'word': 'provide you with tailored services', 'start': 5, 'end': 39, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.93578464), 'word': 'allow other users to identify you as a user of the Service', 'start': 5, 'end': 63, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.97160995), 'word': 'to support the socializing function of the Services', 'start': 68, 'end': 119, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.73489976), 'word': 'profile information', 'start': 27, 'end': 46, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.7422285), 'word': 'interact', 'start': 125, 'end': 133, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.94177675), 'word': 'your information', 'start': 13, 'end': 29, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.88986456), 'word': 'verify accounts and activity,', 'start': 5, 'end': 34, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9315846), 'word': 'combat harmful conduct, detect and prevent spam and other bad experiences', 'start': 35, 'end': 108, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9685771), 'word': 'maintain the integrity of Boomplay', 'start': 110, 'end': 144, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9502002), 'word': 'promote safety and security on and off of Boomplay', 'start': 150, 'end': 200, 'label_readable': 'Required Purpose'}, {'entity_group': 'LI', 'score': np.float32(0.9604954), 'word': 'legitimate interest to promote the Services', 'start': 13, 'end': 56, 'label_readable': 'Legitimate Interest'}, {'entity_group': 'DSO', 'score': np.float32(0.70122063), 'word': 'give', 'start': 94, 'end': 98, 'label_readable': 'Data Source'}, {'entity_group': 'TP', 'score': np.float32(0.7318404), 'word': 'business partners', 'start': 6, 'end': 23, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.88802487), 'word': '##isers', 'start': 98, 'end': 103, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.7440692), 'word': 'advertising networks', 'start': 49, 'end': 69, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.90360194), 'word': 'contact details', 'start': 191, 'end': 206, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.7889495), 'word': 'so', 'start': 302, 'end': 304, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8894419), 'word': 'they can make you offers tailored to your requirements', 'start': 310, 'end': 364, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.97389954), 'word': 'store', 'start': 29, 'end': 34, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.7070276), 'word': 'the improvement and optimization of', 'start': 58, 'end': 93, 'label_readable': 'Required Purpose'}, {'entity_group': 'A', 'score': np.float32(0.96453446), 'word': 'law enforcement agencies', 'start': 35, 'end': 59, 'label_readable': 'Authority'}, {'entity_group': 'A', 'score': np.float32(0.7098131), 'word': 'public', 'start': 61, 'end': 67, 'label_readable': 'Authority'}, {'entity_group': 'A', 'score': np.float32(0.7898286), 'word': 'tax authorities', 'start': 71, 'end': 86, 'label_readable': 'Authority'}, {'entity_group': 'LB', 'score': np.float32(0.7938262), 'word': 'legally required', 'start': 113, 'end': 129, 'label_readable': 'Legal Basis'}, {'entity_group': 'RP', 'score': np.float32(0.7108866), 'word': 'Co', 'start': 2, 'end': 4, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7726418), 'word': '##mp', 'start': 4, 'end': 6, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.80347383), 'word': '##ly', 'start': 6, 'end': 8, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7286269), 'word': '##force', 'start': 4, 'end': 9, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7170479), 'word': 'Det', 'start': 2, 'end': 5, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7722062), 'word': '##t', 'start': 7, 'end': 8, 'label_readable': 'Required Purpose'}, {'entity_group': 'LB', 'score': np.float32(0.7811084), 'word': 'by law', 'start': 112, 'end': 118, 'label_readable': 'Legal Basis'}, {'entity_group': 'P', 'score': np.float32(0.73529637), 'word': 'ex', 'start': 130, 'end': 132, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9593829), 'word': '##changing', 'start': 132, 'end': 140, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.7534754), 'word': 'risk reduction', 'start': 240, 'end': 254, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.93592024), 'word': 'disc', 'start': 80, 'end': 84, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.7648537), 'word': '##lose', 'start': 84, 'end': 88, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9690486), 'word': 'your data', 'start': 89, 'end': 98, 'label_readable': 'Personal Data'}, {'entity_group': 'R', 'score': np.float32(0.76958674), 'word': 'prospective seller or buyer', 'start': 106, 'end': 133, 'label_readable': 'Recipient'}, {'entity_group': 'TP', 'score': np.float32(0.79012406), 'word': 'companies', 'start': 47, 'end': 56, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.9827026), 'word': 'user information', 'start': 129, 'end': 145, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.73487973), 'word': 'transferred assets', 'start': 163, 'end': 181, 'label_readable': 'Processing'}, {'entity_group': 'TP', 'score': np.float32(0.96719885), 'word': 'third party company', 'start': 206, 'end': 225, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.7622117), 'word': 'business', 'start': 229, 'end': 237, 'label_readable': 'Third Party'}, {'entity_group': 'OM', 'score': np.float32(0.72561455), 'word': 'take steps to ensure that', 'start': 3, 'end': 28, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.70758146), 'word': 'and in accordance with this policy.', 'start': 66, 'end': 101, 'label_readable': 'Organisational Measure'}, {'entity_group': 'P', 'score': np.float32(0.9783785), 'word': 'transmission', 'start': 121, 'end': 133, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.93429583), 'word': 'transmitted', 'start': 331, 'end': 342, 'label_readable': 'Processing'}, {'entity_group': 'OM', 'score': np.float32(0.8419135), 'word': 'We have put in place appropriate technical and organizational measures to ensure a level of security appropriate to the risk', 'start': 0, 'end': 124, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.9279842), 'word': 'maintain these technical and organizational measures', 'start': 215, 'end': 267, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.864021), 'word': '.', 'start': 352, 'end': 353, 'label_readable': 'Organisational Measure'}, {'entity_group': 'TP', 'score': np.float32(0.741854), 'word': 'partner networks,', 'start': 74, 'end': 91, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9220216), 'word': 'ad', 'start': 92, 'end': 94, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.8816394), 'word': '##vert', 'start': 94, 'end': 98, 'label_rea</t>
+  </si>
+  <si>
+    <t>[{'entity_group': 'P', 'score': np.float32(0.99624676), 'word': 'collects', 'start': 31, 'end': 39, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.98338014), 'word': 'uses', 'start': 44, 'end': 48, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.90138113), 'word': 'user data', 'start': 49, 'end': 58, 'label_readable': 'Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.96304333), 'word': 'integrated partners', 'start': 31, 'end': 50, 'label_readable': 'Third Party'}, {'entity_group': 'DSR17', 'score': np.float32(0.79256254), 'word': 'del', 'start': 62, 'end': 65, 'label_readable': 'Art. 17 Right to erasure (‘right to be forgotten’)'}, {'entity_group': 'LB', 'score': np.float32(0.9759697), 'word': 'applicable law', 'start': 42, 'end': 56, 'label_readable': 'Legal Basis'}, {'entity_group': 'PD', 'score': np.float32(0.995623), 'word': 'Personal Information', 'start': 84, 'end': 104, 'label_readable': 'Personal Data'}, {'entity_group': 'RI', 'score': np.float32(0.7484471), 'word': 'your rights', 'start': 125, 'end': 136, 'label_readable': 'Right'}, {'entity_group': 'DC', 'score': np.float32(0.96283174), 'word': 'We', 'start': 130, 'end': 132, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.97994906), 'word': 'we', 'start': 19, 'end': 21, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.995769), 'word': 'collect', 'start': 22, 'end': 29, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.97352594), 'word': 'use', 'start': 33, 'end': 36, 'label_readable': 'Processing'}, {'entity_group': 'DC', 'score': np.float32(0.7515055), 'word': 'our', 'start': 128, 'end': 131, 'label_readable': 'Data Controller'}, {'entity_group': 'RI', 'score': np.float32(0.782248), 'word': 'your rights.', 'start': 116, 'end': 128, 'label_readable': 'Right'}, {'entity_group': 'DC', 'score': np.float32(0.75209403), 'word': 'We ’', 'start': 248, 'end': 251, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9918703), 'word': 'process', 'start': 28, 'end': 35, 'label_readable': 'Processing'}, {'entity_group': 'DS', 'score': np.float32(0.92892325), 'word': 'you', 'start': 45, 'end': 48, 'label_readable': 'Data Subject'}, {'entity_group': 'RP', 'score': np.float32(0.8599734), 'word': 'required for our Products to work.', 'start': 20, 'end': 54, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.70807636), 'word': 'quality of', 'start': 106, 'end': 116, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8923599), 'word': 'experience', 'start': 70, 'end': 80, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.724839), 'word': 'de - identified,', 'start': 29, 'end': 43, 'label_readable': 'Processing'}, {'entity_group': 'TP', 'score': np.float32(0.978039), 'word': 'third parties', 'start': 37, 'end': 50, 'label_readable': 'Third Party'}, {'entity_group': 'RET', 'score': np.float32(0.7322685), 'word': 'so that it no longer identifies individuals before it ’ s made', 'start': 87, 'end': 147, 'label_readable': 'Retention'}, {'entity_group': 'RET', 'score': np.float32(0.85075116), 'word': 'us.', 'start': 161, 'end': 164, 'label_readable': 'Retention'}, {'entity_group': 'RP', 'score': np.float32(0.97376984), 'word': 'to provide a personalized experience to you', 'start': 30, 'end': 73, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9191487), 'word': 'including ads', 'start': 75, 'end': 88, 'label_readable': 'Required Purpose'}, {'entity_group': 'ADM', 'score': np.float32(0.70720947), 'word': 'automatically processed', 'start': 137, 'end': 160, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'P', 'score': np.float32(0.97344697), 'word': 'access', 'start': 33, 'end': 39, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.82415575), 'word': 'review', 'start': 236, 'end': 242, 'label_readable': 'Processing'}, {'entity_group': 'NPD', 'score': np.float32(0.70352894), 'word': 'de - identify', 'start': 79, 'end': 90, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7287624), 'word': 'aggregate information', 'start': 94, 'end': 115, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.98867714), 'word': 'to provide and improve our Products.', 'start': 27, 'end': 63, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9198392), 'word': 'personal', 'start': 43, 'end': 51, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.78375846), 'word': '##izing features, content and recommendations, such as', 'start': 86, 'end': 138, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.74789506), 'word': 'and ads.', 'start': 183, 'end': 191, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9186751), 'word': 'to provide, personalize and improve our Products', 'start': 39, 'end': 87, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.97815675), 'word': 'to help protect people from harm and provide safe, secure Products.', 'start': 30, 'end': 97, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7238292), 'word': 'share content.', 'start': 74, 'end': 88, 'label_readable': 'Required Purpose'}, {'entity_group': 'DSO', 'score': np.float32(0.71507835), 'word': 've given us', 'start': 46, 'end': 57, 'label_readable': 'Data Source'}, {'entity_group': 'PD', 'score': np.float32(0.97961724), 'word': 'contact information', 'start': 64, 'end': 83, 'label_readable': 'Personal Data'}, {'entity_group': 'DSO', 'score': np.float32(0.7464635), 'word': 'from researchers and data', 'start': 40, 'end': 65, 'label_readable': 'Data Source'}, {'entity_group': 'DSO', 'score': np.float32(0.9189462), 'word': 'from publicly available sources', 'start': 70, 'end': 101, 'label_readable': 'Data Source'}, {'entity_group': 'TP', 'score': np.float32(0.7097825), 'word': 'professional groups', 'start': 103, 'end': 122, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.8398512), 'word': 'non - profit groups', 'start': 127, 'end': 144, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.8980618), 'word': 'to conduct and support research.', 'start': 145, 'end': 177, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.9950086), 'word': 'shared', 'start': 143, 'end': 149, 'label_readable': 'Processing'}, {'entity_group': 'TP', 'score': np.float32(0.8608096), 'word': '.', 'start': 71, 'end': 72, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.9790989), 'word': 'receive', 'start': 360, 'end': 367, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.77807677), 'word': 'activity.', 'start': 149, 'end': 158, 'label_readable': 'Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.94991475), 'word': 'partners', 'start': 84, 'end': 92, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9513013), 'word': 'other third parties', 'start': 97, 'end': 116, 'label_readable': 'Third Party'}, {'entity_group': 'OM', 'score': np.float32(0.7420436), 'word': 'follow rules about how they can and cannot use and disclose the information we', 'start': 120, 'end': 198, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.96970266), 'word': '.', 'start': 206, 'end': 207, 'label_readable': 'Organisational Measure'}, {'entity_group': 'P', 'score': np.float32(0.98548734), 'word': 'share', 'start': 165, 'end': 170, 'label_readable': 'Processing'}, {'entity_group': 'LI', 'score': np.float32(0.7202594), 'word': 'requests', 'start': 72, 'end': 80, 'label_readable': 'Legitimate Interest'}, {'entity_group': 'RP', 'score': np.float32(0.8661642), 'word': 'prevent harm.', 'start': 118, 'end': 131, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.9695914), 'word': 'transfer', 'start': 127, 'end': 135, 'label_readable': 'Processing'}, {'entity_group': 'LB', 'score': np.float32(0.9279121), 'word': 'the law', 'start': 169, 'end': 176, 'label_readable': 'Legal Basis'}, {'entity_group': 'DC', 'score': np.float32(0.9923207), 'word': '##pp', 'start': 80, 'end': 82, 'label_readable': 'Data Controller'}, {'entity_group': 'R', 'score': np.float32(0.832313), 'word': '##a Companies.', 'start': 90, 'end': 102, 'label_readable': 'Recipient'}, {'entity_group': 'DSO', 'score': np.float32(0.76768124), 'word': '##a Companies', 'start': 68, 'end': 79, 'label_readable': 'Data Source'}, {'entity_group': 'LB', 'score': np.float32(0.8864744), 'word': 'permitted by', 'start': 126, 'end': 138, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.9301679), 'word': 'applicable law.', 'start': 139, 'end': 154, 'label_readable': 'Legal Basis'}, {'entity_group': 'DC', 'score': np.float32(0.7051867), 'word': 'Met', 'start': 170, 'end': 173, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.87852424), 'word': '##a', 'start': 173, 'end': 174, 'label_readable': 'Data Controller'}, {'entity_group': 'RP', 'score': np.float32(0.8965489), 'word': 'promote safety, security and integrity and comply with', 'start': 3, 'end': 57, 'label_readable': 'Required Purpose'}, {'entity_group': 'LB', 'score': np.float32(0.93418556), 'word': 'applicable laws', 'start': 58, 'end': 73, 'label_readable': 'Legal Basis'}, {'entity_group': 'RP', 'score': np.float32(0.7402176), 'word': 'To personal', 'start': 0, 'end': 11, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.74359864), 'word': '##ize offers, ads and other sponsored or commercial content', 'start': 11, 'end': 68, 'label_readable': 'Required Purpose'}, {'entity_group': 'DSR17', 'score': np.float32(0.7669563), 'word': '##ete', 'start': 65, 'end': 68, 'label_readable': 'Art. 17 Right to erasure (‘right to be forgotten’)'}, {'entity_group': 'RI', 'score': np.float32(0.8113576), 'word': 'privacy rights', 'start': 204, 'end': 218, 'label_readable': 'Right'}, {'entity_group': 'LB', 'score': np.float32(0.9826574), 'word': 'applicable laws.', 'start': 119, 'end': 135, 'label_readable': 'Legal Basis'}, {'entity_group': 'DPO', 'score': np.float32(0.802359), 'word': 'the Data Protection Officer for', 'start': 237, 'end': 268, 'label_readable': 'Data Protection Officer'}, {'entity_group': 'A', 'score': np.float32(0.7993122), 'word': 'Data Protection Authority ( “ DPA ” )', 'start': 359, 'end': 392, 'label_readable': 'Authority'}, {'entity_group': 'P', 'score': np.float32(0.8141611), 'word': 'keep', 'start': 3, 'end': 7, 'label_readable': 'Processing'}, {'entity_group': 'RET', 'score': np.float32(0.9628091), 'word': 'as long as we need it', 'start': 20, 'end': 41, 'label_readable': 'Retention'}, {'entity_group': 'RET', 'score': np.float32(0.8992009), 'word': 'provide our', 'start': 45, 'end': 56, 'label_readable': 'Retention'}, {'entity_group': 'RP', 'score': np.float32(0.71799225), 'word': 'Products', 'start': 57, 'end': 65, 'label_readable': 'Required Purpose'}, {'entity_group': 'RET', 'score': np.float32(0.7408155), 'word': 'our', 'start': 108, 'end': 111, 'label_readable': 'Retention'}, {'entity_group': 'RET', 'score': np.float32(0.77452475), 'word': 'other', 'start': 115, 'end': 120, 'label_readable': 'Retention'}, {'entity_group': 'RET', 'score': np.float32(0.95431143), 'word': 'decide how long we need information on a case - by - case basis.', 'start': 137, 'end': 197, 'label_readable': 'Retention'}, {'entity_group': 'RP', 'score': np.float32(0.97402185), 'word': 'to operate or provide our Products.', 'start': 14, 'end': 49, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.86464834), 'word': 'your information', 'start': 36, 'end': 52, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9922066), 'word': 'to maintain your account.', 'start': 104, 'end': 129, 'label_readable': 'Required Purpose'}, {'entity_group': 'RET', 'score': np.float32(0.7317354), 'word': 'retained for less time than', 'start': 116, 'end': 143, 'label_readable': 'Retention'}, {'entity_group': 'RET', 'score': np.float32(0.7553364), 'word': 'messages.', 'start': 152, 'end': 161, 'label_readable': 'Retention'}, {'entity_group': 'RET', 'score': np.float32(0.9646318), 'word': 'How long we need to retain the information to comply with certain legal obligations.', 'start': 0, 'end': 84, 'label_readable': 'Retention'}, {'entity_group': 'LI', 'score': np.float32(0.83087957), 'word': 'legitimate purposes', 'start': 24, 'end': 43, 'label_readable': 'Legitimate Interest'}, {'entity_group': 'LI', 'score': np.float32(0.7466884), 'word': 'to prevent harm', 'start': 53, 'end': 68, 'label_readable': 'Legitimate Interest'}, {'entity_group': 'LI', 'score': np.float32(0.77616715), 'word': 'investigate possible violations of our terms or policies', 'start': 70, 'end': 126, 'label_readable': 'Legitimate Interest'}, {'entity_group': 'LI', 'score': np.float32(0.7860476), 'word': 'promote', 'start': 128, 'end': 135, 'label_readable': 'Legitimate Interest'}, {'entity_group': 'RP', 'score': np.float32(0.72016746), 'word': 'safety, security and integrity', 'start': 136, 'end': 166, 'label_readable': 'Required Purpose'}, {'entity_group': 'LI', 'score': np.float32(0.71576416), 'word': 'protect ourselves, including our rights, property or products', 'start': 171, 'end': 232, 'label_readable': 'Legitimate Interest'}, {'entity_group': 'RET', 'score': np.float32(0.8695799), 'word': 'information for an extended period of time.', 'start': 55, 'end': 98, 'label_readable': 'Retention'}, {'entity_group': 'P', 'score': np.float32(0.95731854), 'word': 'preserve', 'start': 133, 'end': 141, 'label_readable': 'Processing'}, {'entity_group': 'OM', 'score': np.float32(0.7297523), 'word': 'warrants', 'start': 43, 'end': 51, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.72759163), 'word': 'production orders', 'start': 67, 'end': 84, 'label_readable': 'Organisational Measure'}, {'entity_group': 'TP', 'score': np.float32(0.832751), 'word': 'third parties such', 'start': 124, 'end': 142, 'label_readable': 'Third Party'}, {'entity_group': 'A', 'score': np.float32(0.9516561), 'word': 'law enforcement', 'start': 290, 'end': 305, 'label_readable': 'Authority'}, {'entity_group': 'RP', 'score': np.float32(0.90316683), 'word': 'To', 'start': 0, 'end': 2, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9796148), 'word': 'promote the safety, security and integrity of Meta Products, users, employees, property and the public.', 'start': 3, 'end': 106, 'label_readable': 'Required Purpose'}, {'entity_group': 'RET', 'score': np.float32(0.93988854), 'word': 'for an extended amount of time.', 'start': 43, 'end': 74, 'label_readable': 'Retention'}, {'entity_group': 'OM', 'score': np.float32(0.9762282), 'word': "We ' ll notify you before we make material changes to this Policy.", 'start': 0, 'end': 64, 'label_readable': 'Organisational Measure'}, {'entity_group': 'CONS', 'score': np.float32(0.8327716), 'word': 'choose', 'start': 7, 'end': 13, 'label_readable': 'Consent'}, {'entity_group': 'SNEU', 'score': np.float32(0.7422136), 'word': 'United', 'start': 99, 'end': 105, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'DC', 'score': np.float32(0.76387006), 'word': 'us', 'start': 62, 'end': 64, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9918173), 'word': 'processed', 'start': 69, 'end': 78, 'label_readable': 'Processing'}, {'entity_group': 'ADM', 'score': np.float32(0.95114183), 'word': 'automatically', 'start': 73, 'end': 86, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'P', 'score': np.float32(0.7832078), 'word': 'store', 'start': 228, 'end': 233, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9940814), 'word': 'to assess and understand your interests and your preferences and provide you personalized experiences across the Meta Products in accordance with our terms.', 'start': 159, 'end': 315, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.96299255), 'word': 'Personal', 'start': 0, 'end': 8, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.864847), 'word': '##ize features and content', 'start': 8, 'end': 32, 'label_readable': 'Required Purpose'}, {'entity_group': 'NPD', 'score': np.float32(0.77722156), 'word': 'how', 'start': 48, 'end': 51, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.92787284), 'word': 'time', 'start': 4, 'end': 8, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.83913165), 'word': 'frequency', 'start': 10, 'end': 19, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.73789895), 'word': 'duration of your activities on', 'start': 24, 'end': 54, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.97389644), 'word': 'GPS location', 'start': 61, 'end': 73, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.75888866), 'word': 'processes', 'start': 29, 'end': 38, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9845206), 'word': 'collected', 'start': 136, 'end': 145, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9746525), 'word': 'stored', 'start': 150, 'end': 156, 'label_readable': 'Processing'}, {'entity_group': 'DSO', 'score': np.float32(0.8381555), 'word': '.', 'start': 102, 'end': 103, 'label_readable': 'Data Source'}, {'entity_group': 'RP', 'score': np.float32(0.98965454), 'word': 'to understand your interests and your preferences and personalize your ads across the Meta Company Products.', 'start': 141, 'end': 249, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.92700374), 'word': 'match', 'start': 105, 'end': 110, 'label_readable': 'Processing'}, {'entity_group': 'CONS', 'score': np.float32(0.8397684), 'word': 'decide', 'start': 7, 'end': 13, 'label_readable': 'Consent'}, {'entity_group': 'DC', 'score': np.float32(0.9456456), 'word': 'What', 'start': 74, 'end': 78, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.99065137), 'word': '##s', 'start': 78, 'end': 79, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9716754), 'word': '##A', 'start': 79, 'end': 80, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.97749853), 'word': 'shares', 'start': 83, 'end': 89, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9580432), 'word': 'Pro', 'start': 0, 'end': 3, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.94532365), 'word': '##vid', 'start': 3, 'end': 6, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.924643), 'word': '##ing and improving our Meta Products', 'start': 6, 'end': 41, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.857581), 'word': 'collecting,', 'start': 87, 'end': 98, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.7307503), 'word': 'storing,', 'start': 99, 'end': 107, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.7229949), 'word': 'sharing,', 'start': 129, 'end': 137, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.7516781), 'word': 'pro', 'start': 138, 'end': 141, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.737738), 'word': '##fi', 'start': 141, 'end': 143, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.8492457), 'word': '##ling,', 'start': 143, 'end': 148, 'label_readable': 'Processing'}, {'entity_group': 'ADM', 'score': np.float32(0.9096399), 'word': 'automated', 'start': 204, 'end': 213, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'RP', 'score': np.float32(0.8463187), 'word': '##stand', 'start': 5, 'end': 10, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.77800655), 'word': 'enable creation of content', 'start': 15, 'end': 41, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.9597239), 'word': 'artificial intelligence technology', 'start': 97, 'end': 131, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.9931421), 'word': 'F', 'start': 0, 'end': 1, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9932199), 'word': '##ac', 'start': 1, 'end': 3, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9948584), 'word': '##ili', 'start': 3, 'end': 6, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.97276497), 'word': '##tate your purchases and payments on Meta Pay or other Meta checkout experiences.', 'start': 6, 'end': 86, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9963833), 'word': 'to develop, research and test improvements to our Products.', 'start': 24, 'end': 83, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9449778), 'word': 'Test out new products and features to see if they work', 'start': 0, 'end': 54, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7399894), 'word': 'do better', 'start': 101, 'end': 110, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9544843), 'word': 'public profile information', 'start': 5, 'end': 31, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.710471), 'word': 'name,', 'start': 48, 'end': 53, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9812151), 'word': 'user', 'start': 54, 'end': 58, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.97998524), 'word': '##name', 'start': 58, 'end': 62, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9589824), 'word': 'profile picture', 'start': 67, 'end': 82, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8224839), 'word': '##s', 'start': 8, 'end': 9, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7158802), 'word': 'card information', 'start': 69, 'end': 85, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8401211), 'word': 'photo', 'start': 5, 'end': 10, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.905086), 'word': 'video selfie', 'start': 14, 'end': 26, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.91658795), 'word': 'IP address', 'start': 73, 'end': 83, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.8167997), 'word': '##mot', 'start': 3, 'end': 6, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8892045), 'word': '##ing safety, integrity and security', 'start': 6, 'end': 40, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.91611505), 'word': 'research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off', 'start': 108, 'end': 229, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8561344), 'word': '##a Products.', 'start': 233, 'end': 244, 'label_readable': 'Required Purpose'}, {'entity_group': 'ADM', 'score': np.float32(0.7966571), 'word': 'automated processing techniques', 'start': 306, 'end': 337, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'P', 'score': np.float32(0.7056042), 'word': 'remove', 'start': 95, 'end': 101, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.935418), 'word': '##dent', 'start': 1, 'end': 5, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7553058), 'word': '##ify', 'start': 5, 'end': 8, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.93210846), 'word': '##tec', 'start': 3, 'end': 6, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8770023), 'word': '##t the life, physical or mental health, well - being or integrity of our users or others', 'start': 6, 'end': 91, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9374002), 'word': 'Det', 'start': 0, 'end': 3, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.90619624), 'word': '##ec', 'start': 3, 'end': 5, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9279287), 'word': '##t', 'start': 5, 'end': 6, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.71155953), 'word': 'prevent spam', 'start': 11, 'end': 23, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.95001286), 'word': 'To communicate with you', 'start': 0, 'end': 23, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.71249944), 'word': '’ ve given us', 'start': 47, 'end': 59, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.763622), 'word': 'contact information on your profile', 'start': 66, 'end': 101, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.91267), 'word': 'to send you a communication', 'start': 103, 'end': 130, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.74789155), 'word': 'e -', 'start': 140, 'end': 142, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8005558), 'word': 'contact', 'start': 13, 'end': 20, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7833417), 'word': 'your email address', 'start': 37, 'end': 55, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.8005352), 'word': 'to respond when you contact us.', 'start': 56, 'end': 87, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.93989277), 'word': 'Contact information', 'start': 0, 'end': 19, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.82352215), 'word': 'Transfer', 'start': 0, 'end': 8, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9658019), 'word': '##ring, storing or processing', 'start': 8, 'end': 35, 'label_readable': 'Processing'}, {'entity_group': 'SNEU', 'score': np.float32(0.86312866), 'word': 'United States', 'start': 95, 'end': 108, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'SNEU', 'score': np.float32(0.8552384), 'word': 'countries', 'start': 119, 'end': 128, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'TP', 'score': np.float32(0.8641316), 'word': 'users', 'start': 324, 'end': 329, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.7748207), 'word': 'vendors', 'start': 341, 'end': 348, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.94201684), 'word': 'transfers', 'start': 381, 'end': 390, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.8764792), 'word': 'To operate and provide the services', 'start': 0, 'end': 35, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.76196474), 'word': 'in the terms that apply to the Meta Product ( s )', 'start': 46, 'end': 92, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.74485743), 'word': 'connect', 'start': 160, 'end': 167, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.97811913), 'word': 'Process', 'start': 0, 'end': 7, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9269223), 'word': '##ing', 'start': 7, 'end': 10, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.95604306), 'word': 'to provide, personalize and improve our Products and', 'start': 135, 'end': 187, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.95880467), 'word': 'to undertake analytics.', 'start': 188, 'end': 211, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.91146517), 'word': 'religious views', 'start': 82, 'end': 97, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9419519), 'word': 'sexual orientation', 'start': 104, 'end': 122, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9365921), 'word': 'political views', 'start': 124, 'end': 139, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8246262), 'word': 'health,', 'start': 141, 'end': 148, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9094337), 'word': 'racial or ethnic origin,', 'start': 149, 'end': 173, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7240847), 'word': 'philosophical beliefs or', 'start': 174, 'end': 198, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8612933), 'word': 'trade union membership', 'start': 199, 'end': 221, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9898679), 'word': 'Re', 'start': 0, 'end': 2, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9806984), 'word': '##ceiving', 'start': 2, 'end': 9, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9322657), 'word': 'using', 'start': 14, 'end': 19, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.96852154), 'word': 'to tailor the ads you see', 'start': 51, 'end': 76, 'label_readable': 'Required Purpose'}, {'entity_group': 'DC', 'score': np.float32(0.71421367), 'word': 'We ’ ll', 'start': 79, 'end': 84, 'label_readable': 'Data Controller'}, {'entity_group': 'TP', 'score': np.float32(0.9863679), 'word': 'ad', 'start': 106, 'end': 108, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.98738396), 'word': '##vert', 'start': 108, 'end': 112, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9863355), 'word': '##isers', 'start': 112, 'end': 117, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.98080575), 'word': 'businesses', 'start': 119, 'end': 129, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.90846914), 'word': 'other partners', 'start': 134, 'end': 148, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.86574346), 'word': 'provide', 'start': 149, 'end': 156, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.94148725), 'word': 'to personalize ads that we show you on Meta', 'start': 234, 'end': 277, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.71031636), 'word': ', and on websites, apps and devices that', 'start': 286, 'end': 326, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7406236), 'word': 'our advertising', 'start': 331, 'end': 346, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8320017), 'word': '.', 'start': 355, 'end': 356, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.7252305), 'word': 'name', 'start': 50, 'end': 54, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9805571), 'word': 'email address', 'start': 58, 'end': 71, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9870368), 'word': 'S', 'start': 0, 'end': 1, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9879659), 'word': '##hari', 'start': 1, 'end': 5, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.97920036), 'word': '##ng', 'start': 5, 'end': 7, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.8544311), 'word': 'your', 'start': 8, 'end': 1</t>
+  </si>
+  <si>
+    <t>[{'entity_group': 'SNEU', 'score': np.float32(0.75183576), 'word': 'UK', 'start': 26, 'end': 28, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'DC', 'score': np.float32(0.9970366), 'word': 'What', 'start': 186, 'end': 190, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9981199), 'word': '##s', 'start': 216, 'end': 217, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.99649566), 'word': '##A', 'start': 217, 'end': 218, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9959079), 'word': '##pp LLC', 'start': 192, 'end': 198, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9947373), 'word': '##pp', 'start': 299, 'end': 301, 'label_readable': 'Data Controller'}, {'entity_group': 'SEU', 'score': np.float32(0.81306314), 'word': 'European Region,', 'start': 26, 'end': 42, 'label_readable': 'Scale EU'}, {'entity_group': 'DC', 'score': np.float32(0.9859773), 'word': '##pp Ireland Ltd.', 'start': 49, 'end': 64, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.8692793), 'word': '##pp LLC ( " Whats', 'start': 36, 'end': 50, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.95488405), 'word': '##pp, " " our, " "', 'start': 76, 'end': 89, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.93544513), 'word': 'we, " or "', 'start': 89, 'end': 98, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.938687), 'word': 'us " )', 'start': 98, 'end': 102, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9610036), 'word': 'processing', 'start': 235, 'end': 245, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9923275), 'word': 'personal information', 'start': 291, 'end': 311, 'label_readable': 'Personal Data'}, {'entity_group': 'DS', 'score': np.float32(0.8205348), 'word': 'you', 'start': 318, 'end': 321, 'label_readable': 'Data Subject'}, {'entity_group': 'DC', 'score': np.float32(0.94123846), 'word': 'us', 'start': 300, 'end': 302, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9859232), 'word': '##pp Ireland Limited ( "', 'start': 49, 'end': 70, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9967358), 'word': '##pp Ireland Limited', 'start': 218, 'end': 236, 'label_readable': 'Data Controller'}, {'entity_group': 'TP', 'score': np.float32(0.9894389), 'word': 'third parties', 'start': 643, 'end': 656, 'label_readable': 'Third Party'}, {'entity_group': 'DC', 'score': np.float32(0.85804427), 'word': '##pp ’', 'start': 89, 'end': 92, 'label_readable': 'Data Controller'}, {'entity_group': 'DS', 'score': np.float32(0.8413975), 'word': 'users', 'start': 204, 'end': 209, 'label_readable': 'Data Subject'}, {'entity_group': 'PD', 'score': np.float32(0.98977625), 'word': 'personal data', 'start': 259, 'end': 272, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9955836), 'word': 'processed', 'start': 280, 'end': 289, 'label_readable': 'Processing'}, {'entity_group': 'LB', 'score': np.float32(0.9924321), 'word': 'applicable law.', 'start': 330, 'end': 345, 'label_readable': 'Legal Basis'}, {'entity_group': 'DC', 'score': np.float32(0.97971284), 'word': 'we', 'start': 8, 'end': 10, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9927099), 'word': 'collect', 'start': 3, 'end': 10, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9673737), 'word': 'phone number', 'start': 82, 'end': 94, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.95362985), 'word': 'provide', 'start': 43, 'end': 50, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.70930195), 'word': 'to create', 'start': 89, 'end': 98, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9762166), 'word': 'business name', 'start': 143, 'end': 156, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7423255), 'word': 'business category.', 'start': 161, 'end': 179, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8275631), 'word': 'profile picture', 'start': 378, 'end': 393, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8866817), 'word': 'cover photo', 'start': 398, 'end': 409, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9726363), 'word': 'contact information', 'start': 411, 'end': 430, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7316274), 'word': 'business address,', 'start': 441, 'end': 458, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.86190754), 'word': 'business email,', 'start': 459, 'end': 474, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8587679), 'word': 'website', 'start': 479, 'end': 486, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8544618), 'word': 'description of your business', 'start': 490, 'end': 518, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9109752), 'word': 'names', 'start': 573, 'end': 578, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7543654), 'word': 'descriptions', 'start': 580, 'end': 592, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.95234156), 'word': 'images', 'start': 594, 'end': 600, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.80595106), 'word': 'prices', 'start': 610, 'end': 616, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'DC', 'score': np.float32(0.93012536), 'word': 'We', 'start': 0, 'end': 2, 'label_readable': 'Data Controller'}, {'entity_group': 'PD', 'score': np.float32(0.8470815), 'word': 'purchases and transactions with your business ;', 'start': 211, 'end': 257, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.88470703), 'word': 'metric', 'start': 262, 'end': 268, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.844163), 'word': '##s related to how customers interact with your business', 'start': 268, 'end': 322, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9712657), 'word': 'use', 'start': 3, 'end': 6, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.83824426), 'word': 'Priva', 'start': 82, 'end': 87, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.83269125), 'word': 'also', 'start': 102, 'end': 106, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9914208), 'word': 'to operate, provide, improve, understand, customize, support, and market our WhatsApp Business App and Business Functions.', 'start': 107, 'end': 229, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.98769253), 'word': 'to operate and provide our WhatsApp Business App and Business Functions, including', 'start': 31, 'end': 113, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9554594), 'word': 'providing you with business support ;', 'start': 114, 'end': 150, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9251129), 'word': 'providing onboarding tools ;', 'start': 151, 'end': 178, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.94725615), 'word': 'providing message creation and delivery tools ; providing you new and premium Business Functions', 'start': 179, 'end': 274, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.82366484), 'word': '/', 'start': 325, 'end': 326, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.91659796), 'word': '; and', 'start': 334, 'end': 339, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.959296), 'word': 'improving, fixing, and customizing our WhatsApp Business App.', 'start': 340, 'end': 401, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.995072), 'word': 'to understand how you use our WhatsApp Business App ; evaluate and improve our WhatsApp Business App ; research, develop, and test new services and features ; and conduct troubleshooting activities.', 'start': 434, 'end': 629, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9622383), 'word': 'to respond to you when you contact us.', 'start': 659, 'end': 697, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9801425), 'word': 'to maintain safety, security and integrity on our', 'start': 137, 'end': 186, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8080913), 'word': '##sApp Business App,', 'start': 191, 'end': 209, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.98846537), 'word': 'to create quality and integrity inferences about businesses ; secure WhatsApp systems and WhatsApp Business App users ’ accounts ; fight threats, abuse, or infringement activities ;', 'start': 223, 'end': 400, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9677216), 'word': 'promote safety, security, and integrity on the WhatsApp Business App ; and to ensure compliance with our terms and policies.', 'start': 401, 'end': 524, 'label_readable': 'Required Purpose'}, {'entity_group': 'DS', 'score': np.float32(0.83564675), 'word': 'You', 'start': 0, 'end': 3, 'label_readable': 'Data Subject'}, {'entity_group': 'P', 'score': np.float32(0.9937302), 'word': 'share', 'start': 11, 'end': 16, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.8514888), 'word': 'sharing', 'start': 90, 'end': 97, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9496155), 'word': 'Business profile information', 'start': 0, 'end': 28, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.81641483), 'word': 'hours of operation', 'start': 96, 'end': 114, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9647014), 'word': 'business category', 'start': 116, 'end': 133, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9821805), 'word': 'address', 'start': 135, 'end': 142, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.96286505), 'word': 'email address', 'start': 144, 'end': 157, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9466803), 'word': 'website ( s )', 'start': 159, 'end': 169, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7996015), 'word': 'description', 'start': 171, 'end': 182, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.7759794), 'word': 'Met', 'start': 107, 'end': 110, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.7562119), 'word': '##a.', 'start': 110, 'end': 112, 'label_readable': 'Third Party'}, {'entity_group': 'RI', 'score': np.float32(0.73194957), 'word': 'rights', 'start': 46, 'end': 52, 'label_readable': 'Right'}, {'entity_group': 'PD', 'score': np.float32(0.89595014), 'word': 'your information', 'start': 139, 'end': 155, 'label_readable': 'Personal Data'}, {'entity_group': 'R', 'score': np.float32(0.7973046), 'word': 'successor entities or new owners', 'start': 165, 'end': 197, 'label_readable': 'Recipient'}, {'entity_group': 'LB', 'score': np.float32(0.96013486), 'word': 'applicable data protection laws.', 'start': 252, 'end': 284, 'label_readable': 'Legal Basis'}, {'entity_group': 'P', 'score': np.float32(0.9769984), 'word': 'access', 'start': 56, 'end': 62, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.97143596), 'word': 'preserve', 'start': 64, 'end': 72, 'label_readable': 'Processing'}, {'entity_group': 'LB', 'score': np.float32(0.7635927), 'word': 'legal', 'start': 116, 'end': 121, 'label_readable': 'Legal Basis'}]</t>
+  </si>
+  <si>
+    <t>[{'entity_group': 'SEU', 'score': np.float32(0.78394884), 'word': 'European Region,', 'start': 19, 'end': 35, 'label_readable': 'Scale EU'}, {'entity_group': 'DC', 'score': np.float32(0.9954757), 'word': 'What', 'start': 620, 'end': 624, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9980434), 'word': '##s', 'start': 4, 'end': 5, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9966293), 'word': '##A', 'start': 5, 'end': 6, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9921325), 'word': '##pp Ireland Limited', 'start': 42, 'end': 60, 'label_readable': 'Data Controller'}, {'entity_group': 'SNEU', 'score': np.float32(0.7430131), 'word': 'UK', 'start': 19, 'end': 21, 'label_readable': 'Scale Non-EU'}, {'entity_group': 'DC', 'score': np.float32(0.9927918), 'word': '##pp LLC', 'start': 29, 'end': 35, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9916755), 'word': '##pp LLC ( "', 'start': 57, 'end': 66, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.937388), 'word': '##pp, " " our, " " we, " or "', 'start': 72, 'end': 94, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.96343285), 'word': 'us " )', 'start': 94, 'end': 98, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9841791), 'word': 'we', 'start': 54, 'end': 56, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.9959537), 'word': 'process', 'start': 101, 'end': 108, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9954855), 'word': 'to provide our Services.', 'start': 109, 'end': 133, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.99385947), 'word': 'collect', 'start': 25, 'end': 32, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9156929), 'word': 'stored', 'start': 307, 'end': 313, 'label_readable': 'Processing'}, {'entity_group': 'DC', 'score': np.float32(0.95858556), 'word': 'us', 'start': 183, 'end': 185, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9794647), 'word': 'We', 'start': 133, 'end': 135, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.99646395), 'word': 'share', 'start': 352, 'end': 357, 'label_readable': 'Processing'}, {'entity_group': 'DS', 'score': np.float32(0.9751751), 'word': 'you', 'start': 348, 'end': 351, 'label_readable': 'Data Subject'}, {'entity_group': 'DC', 'score': np.float32(0.99851555), 'word': '##pp', 'start': 6, 'end': 8, 'label_readable': 'Data Controller'}, {'entity_group': 'OM', 'score': np.float32(0.7632338), 'word': 'privacy principles', 'start': 121, 'end': 139, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.8494288), 'word': '.', 'start': 147, 'end': 148, 'label_readable': 'Organisational Measure'}, {'entity_group': 'P', 'score': np.float32(0.9754513), 'word': 'Hand', 'start': 33, 'end': 37, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9629946), 'word': '##le', 'start': 37, 'end': 39, 'label_readable': 'Processing'}, {'entity_group': 'DC', 'score': np.float32(0.7170875), 'word': 'we ’', 'start': 186, 'end': 189, 'label_readable': 'Data Controller'}, {'entity_group': 'OM', 'score': np.float32(0.7598585), 'word': 'more recent product features and functionalities', 'start': 221, 'end': 269, 'label_readable': 'Organisational Measure'}, {'entity_group': 'TP', 'score': np.float32(0.92824095), 'word': 'businesses', 'start': 133, 'end': 143, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9871587), 'word': 'third parties', 'start': 41, 'end': 54, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.9932934), 'word': 'receive', 'start': 14, 'end': 21, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9969189), 'word': 'to operate, provide, improve, understand, customize, support, and market our Services,', 'start': 50, 'end': 136, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9885301), 'word': '.', 'start': 192, 'end': 193, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.9880888), 'word': 'use', 'start': 140, 'end': 143, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.8664508), 'word': 'require', 'start': 87, 'end': 94, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9928335), 'word': 'to deliver our Services and without this we will not be able to provide our Services to you.', 'start': 115, 'end': 207, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.9885528), 'word': 'provide', 'start': 76, 'end': 83, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9482365), 'word': 'mobile phone number', 'start': 48, 'end': 67, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.8940844), 'word': 'to create an account to use our Services.', 'start': 263, 'end': 304, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.9597666), 'word': 'used', 'start': 46, 'end': 50, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9796187), 'word': 'to provide such features.', 'start': 104, 'end': 129, 'label_readable': 'Required Purpose'}, {'entity_group': 'OM', 'score': np.float32(0.95019966), 'word': 'You will be notified of such collection', 'start': 130, 'end': 169, 'label_readable': 'Organisational Measure'}, {'entity_group': 'OM', 'score': np.float32(0.80059606), 'word': 'as appropriate.', 'start': 171, 'end': 186, 'label_readable': 'Organisational Measure'}, {'entity_group': 'CONS', 'score': np.float32(0.91449594), 'word': 'choose', 'start': 426, 'end': 432, 'label_readable': 'Consent'}, {'entity_group': 'PD', 'score': np.float32(0.9084072), 'word': 'your location', 'start': 326, 'end': 339, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8110092), 'word': 'your', 'start': 394, 'end': 398, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.85426646), 'word': 'location data', 'start': 399, 'end': 412, 'label_readable': 'Personal Data'}, {'entity_group': 'CONS', 'score': np.float32(0.9585621), 'word': 'Per', 'start': 431, 'end': 434, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.9614341), 'word': '##mission', 'start': 434, 'end': 441, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.9568432), 'word': '##s', 'start': 441, 'end': 442, 'label_readable': 'Consent'}, {'entity_group': 'PD', 'score': np.float32(0.7927397), 'word': 'A', 'start': 5, 'end': 6, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.77210736), 'word': '##cco', 'start': 6, 'end': 9, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7438918), 'word': '##unt Information.', 'start': 9, 'end': 25, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7010967), 'word': 'a profile name', 'start': 101, 'end': 115, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.7521664), 'word': 'add', 'start': 280, 'end': 283, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.89094514), 'word': 'profile picture', 'start': 329, 'end': 344, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.7954825), 'word': 'retain', 'start': 25, 'end': 31, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.98448527), 'word': 'store', 'start': 66, 'end': 71, 'label_readable': 'Processing'}, {'entity_group': 'RET', 'score': np.float32(0.90045476), 'word': 'for up to 30 days as we try to deliver it.', 'start': 531, 'end': 573, 'label_readable': 'Retention'}, {'entity_group': 'P', 'score': np.float32(0.9317955), 'word': '##ete', 'start': 464, 'end': 467, 'label_readable': 'Processing'}, {'entity_group': 'NPD', 'score': np.float32(0.85580003), 'word': 'media temporarily in encrypted form', 'start': 77, 'end': 112, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9881703), 'word': 'to aid in more efficient delivery of additional forwards.', 'start': 128, 'end': 185, 'label_readable': 'Required Purpose'}, {'entity_group': 'OM', 'score': np.float32(0.86672294), 'word': 'end - to - end encryption for our Services.', 'start': 9, 'end': 48, 'label_readable': 'Organisational Measure'}, {'entity_group': 'TM', 'score': np.float32(0.89671737), 'word': 'End - to - end encryption', 'start': 49, 'end': 70, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.9867207), 'word': 'to protect against us and third parties from reading them.', 'start': 110, 'end': 168, 'label_readable': 'Required Purpose'}, {'entity_group': 'LB', 'score': np.float32(0.8110915), 'word': 'permitted by', 'start': 76, 'end': 88, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.98288363), 'word': 'applicable laws', 'start': 89, 'end': 104, 'label_readable': 'Legal Basis'}, {'entity_group': 'PD', 'score': np.float32(0.8956461), 'word': 'phone numbers', 'start': 115, 'end': 128, 'label_readable': 'Personal Data'}, {'entity_group': 'DC', 'score': np.float32(0.77643466), 'word': 'our', 'start': 43, 'end': 46, 'label_readable': 'Data Controller'}, {'entity_group': 'PD', 'score': np.float32(0.8658824), 'word': 'payment account and transaction information.', 'start': 194, 'end': 238, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9434871), 'word': 'to complete the transaction', 'start': 311, 'end': 338, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.77850777), 'word': 'information about your payment method, shipping details and transaction amount ).', 'start': 353, 'end': 433, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9395776), 'word': 'copies of your messages', 'start': 201, 'end': 224, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8642825), 'word': 'email address', 'start': 299, 'end': 312, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.864333), 'word': 'performance', 'start': 386, 'end': 397, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9017348), 'word': 'service - related', 'start': 92, 'end': 107, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.85580564), 'word': 'performance information.', 'start': 125, 'end': 149, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8559055), 'word': 'how you use our Services,', 'start': 207, 'end': 232, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7068035), 'word': 'your Services settings', 'start': 233, 'end': 255, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.89466774), 'word': 'how you interact with others using our Services', 'start': 257, 'end': 304, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.85601026), 'word': 'time,', 'start': 360, 'end': 365, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.89193845), 'word': 'log files', 'start': 428, 'end': 437, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8650065), 'word': 'diagnostic, crash, website, and performance logs and reports.', 'start': 443, 'end': 504, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.77878153), 'word': 'when you registered to use our Services', 'start': 542, 'end': 581, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7786901), 'word': 'picture', 'start': 677, 'end': 684, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.79801935), 'word': 'profile photo,', 'start': 737, 'end': 751, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7965132), 'word': 'whether you', 'start': 773, 'end': 784, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7120815), 'word': 'when you last used our Services', 'start': 797, 'end': 828, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'RET', 'score': np.float32(0.7925071), 'word': 'when you install, access, or use our Services.', 'start': 89, 'end': 135, 'label_readable': 'Retention'}, {'entity_group': 'NPD', 'score': np.float32(0.8848049), 'word': 'hardware model,', 'start': 170, 'end': 185, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8650319), 'word': 'operating system information,', 'start': 186, 'end': 215, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.84632343), 'word': 'battery level,', 'start': 216, 'end': 230, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8496979), 'word': 'signal strength,', 'start': 231, 'end': 247, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.86479855), 'word': 'app version,', 'start': 248, 'end': 260, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.881972), 'word': 'browser information,', 'start': 261, 'end': 281, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.88017637), 'word': 'mobile network,', 'start': 282, 'end': 297, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.86829245), 'word': 'connection information', 'start': 298, 'end': 320, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.97998416), 'word': 'phone number', 'start': 168, 'end': 180, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.73077565), 'word': ',', 'start': 344, 'end': 345, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.84541625), 'word': 'mobile operator or ISP )', 'start': 346, 'end': 369, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9896629), 'word': 'IP address', 'start': 641, 'end': 651, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.82776123), 'word': 'device operations information', 'start': 407, 'end': 436, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8922567), 'word': 'id', 'start': 465, 'end': 467, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8293315), 'word': '##ent', 'start': 467, 'end': 470, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.77212006), 'word': '##ifier', 'start': 447, 'end': 452, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9043244), 'word': '##s', 'start': 452, 'end': 453, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.98993474), 'word': 'precise location information', 'start': 41, 'end': 69, 'label_readable': 'Personal Data'}, {'entity_group': 'DSO', 'score': np.float32(0.85502744), 'word': 'from your device', 'start': 70, 'end': 86, 'label_readable': 'Data Source'}, {'entity_group': 'P', 'score': np.float32(0.82510465), 'word': 'shared', 'start': 271, 'end': 277, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9052772), 'word': 'sharing', 'start': 440, 'end': 447, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9969385), 'word': 'IP addresses', 'start': 510, 'end': 522, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.99065375), 'word': 'phone number area codes', 'start': 550, 'end': 573, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.990773), 'word': 'to estimate your general location', 'start': 574, 'end': 607, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.7164664), 'word': 'city', 'start': 615, 'end': 619, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.98144233), 'word': 'location information', 'start': 651, 'end': 671, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.8944432), 'word': 'for', 'start': 672, 'end': 675, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.84567195), 'word': 'diagnostics and troubleshooting purposes.', 'start': 676, 'end': 717, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.977403), 'word': 'Cook', 'start': 0, 'end': 4, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.9591828), 'word': '##ies', 'start': 4, 'end': 7, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.9342279), 'word': 'cookies', 'start': 225, 'end': 232, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.9978642), 'word': 'to operate and provide our Services, including to provide our Services that are web - based, improve your experiences, understand how our Services are being used, and customize them.', 'start': 24, 'end': 204, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.99691856), 'word': 'to provide our Services for web and desktop and other web - based services.', 'start': 233, 'end': 306, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9861812), 'word': 'to understand which of our Help Center articles are most popular and to show you relevant content related to our Services. Additionally,', 'start': 331, 'end': 467, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.98693234), 'word': 'to remember your choices, like your language preferences, to provide a safer experience, and otherwise to customize our Services for you.', 'start': 487, 'end': 624, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7418425), 'word': 'more about how', 'start': 631, 'end': 645, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.97284824), 'word': 'to provide you our Services.', 'start': 661, 'end': 689, 'label_readable': 'Required Purpose'}, {'entity_group': 'DSO', 'score': np.float32(0.726413), 'word': 'from other users.', 'start': 71, 'end': 88, 'label_readable': 'Data Source'}, {'entity_group': 'PD', 'score': np.float32(0.98774135), 'word': 'name', 'start': 182, 'end': 186, 'label_readable': 'Personal Data'}, {'entity_group': 'RI', 'score': np.float32(0.757372), 'word': 'law', 'start': 422, 'end': 425, 'label_readable': 'Right'}, {'entity_group': 'RI', 'score': np.float32(0.7134522), 'word': '##ful rights', 'start': 425, 'end': 435, 'label_readable': 'Right'}, {'entity_group': 'P', 'score': np.float32(0.8822075), 'word': 'providing', 'start': 221, 'end': 230, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9864667), 'word': 'capture', 'start': 53, 'end': 60, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9126252), 'word': 'messages', 'start': 151, 'end': 159, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.72353125), 'word': 'recordings of your calls', 'start': 107, 'end': 131, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7837013), 'word': '##r Reports', 'start': 3, 'end': 12, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.99677175), 'word': 'to report possible violations of our Terms or policies.', 'start': 197, 'end': 252, 'label_readable': 'Required Purpose'}, {'entity_group': 'DS', 'score': np.float32(0.8934082), 'word': 'reporting user', 'start': 311, 'end': 325, 'label_readable': 'Data Subject'}, {'entity_group': 'DS', 'score': np.float32(0.8693113), 'word': 'reported user.', 'start': 330, 'end': 344, 'label_readable': 'Data Subject'}, {'entity_group': 'TP', 'score': np.float32(0.87574995), 'word': 'Business', 'start': 250, 'end': 258, 'label_readable': 'Third Party'}, {'entity_group': 'DSO', 'score': np.float32(0.7871989), 'word': 'interact', 'start': 39, 'end': 47, 'label_readable': 'Data Source'}, {'entity_group': 'LB', 'score': np.float32(0.9948826), 'word': 'applicable law', 'start': 201, 'end': 215, 'label_readable': 'Legal Basis'}, {'entity_group': 'TP', 'score': np.float32(0.89131296), 'word': 'business', 'start': 316, 'end': 324, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9293057), 'word': 'third - party service providers', 'start': 44, 'end': 73, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.9404064), 'word': 'to help manage their communications with their customers.', 'start': 243, 'end': 300, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.988972), 'word': 'third - party', 'start': 339, 'end': 350, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.71845156), 'word': 'service provider', 'start': 351, 'end': 367, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.8332007), 'word': 'send, store, read, manage, or otherwise process', 'start': 400, 'end': 447, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.920975), 'word': 'processes', 'start': 500, 'end': 509, 'label_readable': 'Processing'}, {'entity_group': 'TP', 'score': np.float32(0.8692226), 'word': 'Third - Party Service Providers.', 'start': 0, 'end': 30, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.91641486), 'word': 'Met', 'start': 84, 'end': 87, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9192909), 'word': '##a Companies', 'start': 87, 'end': 98, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.9988528), 'word': 'to help us operate, provide, improve, understand, customize, support, and market our Services.', 'start': 99, 'end': 193, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.99226373), 'word': 'to distribute our apps ; provide our technical and physical infrastructure, delivery, and other systems ; provide engineering support, cybersecurity support, and operational support ; supply location, map, and places information ; process payments ; help us understand how people use our Services ; market our Services ; help you connect with businesses using our Services ; conduct surveys and research for us ; ensure safety, security, and integrity ; and help with customer service.', 'start': 225, 'end': 700, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9927767), 'word': 'to help us diagnose and fix service issues.', 'start': 837, 'end': 880, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.99337316), 'word': 'collects', 'start': 103, 'end': 111, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9933727), 'word': 'shares', 'start': 9, 'end': 15, 'label_readable': 'Processing'}, {'entity_group': 'R', 'score': np.float32(0.82312137), 'word': '##a Companies.', 'start': 120, 'end': 132, 'label_readable': 'Recipient'}, {'entity_group': 'TP', 'score': np.float32(0.9840862), 'word': 'Third - Party Services.', 'start': 0, 'end': 21, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.99592644), 'word': 'third - party services', 'start': 45, 'end': 65, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.7467964), 'word': 'Company Products.', 'start': 104, 'end': 121, 'label_readable': 'Third Party'}, {'entity_group': 'CONS', 'score': np.float32(0.9611649), 'word': 'choices', 'start': 39, 'end': 46, 'label_readable': 'Consent'}, {'entity_group': 'LB', 'score': np.float32(0.95729333), 'word': 'applicable law )', 'start': 60, 'end': 75, 'label_readable': 'Legal Basis'}, {'entity_group': 'RP', 'score': np.float32(0.9968769), 'word': 'to operate, provide, improve, understand, customize, support, and market our Services.', 'start': 76, 'end': 162, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.99322057), 'word': 'Our Services.', 'start': 0, 'end': 13, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9972919), 'word': 'to operate and provide our Services, including providing customer support ; completing purchases or transactions ; improving, fixing, and customizing our Services ; and connecting our Services with Meta Company Products that you may use.', 'start': 41, 'end': 275, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.993952), 'word': 'to understand how people use our Services ; evaluate and improve our Services ; research, develop, and test new services and features ; and conduct troubleshooting activities.', 'start': 308, 'end': 480, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.99094516), 'word': 'to respond to you when you contact us.', 'start': 510, 'end': 548, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.78607875), 'word': 'integrity', 'start': 55, 'end': 64, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8236416), 'word': 'part of our Services.', 'start': 81, 'end': 102, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.98100704), 'word': 'to verify accounts and activity ;', 'start': 130, 'end': 162, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9219228), 'word': 'combat harmful conduct ;', 'start': 163, 'end': 186, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9856596), 'word': 'protect users against bad experiences and spam ; and promote safety, security, and integrity on and off our Services, such as by investigating suspicious activity or violations of our Terms and policies, and to ensure our Services are being used legally.', 'start': 187, 'end': 440, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9958505), 'word': 'to communicate with you about our Services and let you know about our terms, policies, and other important updates.', 'start': 85, 'end': 200, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.9313598), 'word': 'Third - Party', 'start': 3, 'end': 14, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.8823921), 'word': 'third - party banner ads', 'start': 49, 'end': 71, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.8615094), 'word': '##es', 'start': 258, 'end': 260, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.74017364), 'word': 'send', 'start': 265, 'end': 269, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.89576924), 'word': 'transaction, appointment, and shipping notifications ;', 'start': 274, 'end': 327, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.73754), 'word': 'flight status information', 'start': 401, 'end': 426, 'label_readable': 'Personal Data'}, {'entity_group': 'CONS', 'score': np.float32(0.7210565), 'word': 'make', 'start': 783, 'end': 787, 'label_readable': 'Consent'}, {'entity_group': 'P', 'score': np.float32(0.8704717), 'word': 'communicate', 'start': 42, 'end': 53, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.8113811), 'word': 'information', 'start': 94, 'end': 105, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.94102675), 'word': 'Cho', 'start': 45, 'end': 48, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.92606306), 'word': '##ose', 'start': 48, 'end': 51, 'label_readable': 'Consent'}, {'entity_group': 'DS', 'score': np.float32(0.89262), 'word': 'You', 'start': 68, 'end': 71, 'label_readable': 'Data Subject'}, {'entity_group': 'PD', 'score': np.float32(0.9630169), 'word': 'profile name', 'start': 61, 'end': 73, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9802715), 'word': 'last seen information', 'start': 106, 'end': 127, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.98583716), 'word': 'message receipts', 'start': 133, 'end': 149, 'label_readable': 'Personal Data'}, {'entity_group': 'CONS', 'score': np.float32(0.7335196), 'word': 'con', 'start': 214, 'end': 217, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.8144559), 'word': '##fi', 'start': 217, 'end': 219, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.85877997), 'word': '##gu', 'start': 219, 'end': 221, 'label_readable': 'Consent'}, {'entity_group': 'P', 'score': np.float32(0.9567126), 'word': 're', 'start': 94, 'end': 96, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.96004444), 'word': '##sha', 'start': 96, 'end': 99, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.8819908), 'word': '##re', 'start': 99, 'end': 101, 'label_readable': 'Processing'}, {'entity_group': 'R', 'score': np.float32(0.8202796), 'word': 'businesses', 'start': 54, 'end': 64, 'label_readable': 'Recipient'}, {'entity_group': 'NPD', 'score': np.float32(0.97498953), 'word': 'use of our Services.', 'start': 117, 'end': 137, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.99780124), 'word': 'to support our Services, such as to provide technical infrastructure, delivery and other systems ; market our Services ; conduct surveys and research for us ; protect the safety, security, and integrity of users and others ; and assist with customer service.', 'start': 223, 'end': 477, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9989685), 'word': 'share', 'start': 486, 'end': 491, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.79843736), 'word': 'terms.', 'start': 676, 'end': 682, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.9594504), 'word': '##a Company Products', 'start': 78, 'end': 96, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.74421704), 'word': '##A', 'start': 406, 'end': 407, 'label_readable': 'Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.98496854), 'word': 'third - party service', 'start': 443, 'end': 462, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.7955854), 'word': 'Company', 'start': 479, 'end': 486, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9863224), 'word': 'third - party platform', 'start': 586, 'end': 606, 'label_readable': 'Third Party'}, {'entity_group': 'DS', 'score': np.float32(0.7740212), 'word': 'user', 'start': 689, 'end': 693, 'label_readable': 'Data Subject'}, {'entity_group': 'P', 'score': np.float32(0.9562727), 'word': 'provided', 'start': 702, 'end': 710, 'label_readable': 'Processing'}, {'entity_group': 'TP', 'score': np.float32(0.9901312), 'word': 'third party', 'start': 719, 'end': 730, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.8325882), 'word': '##a Company Product.', 'start': 737, 'end': 755, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.99279433), 'word': 'receives', 'start': 40, 'end': 48, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9983555), 'word': 'to help operate, provide, improve, understand, customize, support, and market our Services and their offerings, including the Meta Company Products.', 'start': 235, 'end': 383, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8896782), 'word': 'promoting safety, security, and integrity across the Meta Company Products, e. g.,', 'start': 0, 'end': 81, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9516339), 'word': 'securing systems and fighting spam, threats, abuse, or infringement activities ;</t>
+  </si>
+  <si>
+    <t>[{'entity_group': 'DC', 'score': np.float32(0.98556596), 'word': 'We', 'start': 144, 'end': 146, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.97422487), 'word': 'G', 'start': 0, 'end': 1, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.91281885), 'word': '##ira', 'start': 1, 'end': 4, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9423792), 'word': '##ffe Games', 'start': 4, 'end': 13, 'label_readable': 'Data Controller'}, {'entity_group': 'PD', 'score': np.float32(0.99607414), 'word': 'personal data', 'start': 178, 'end': 191, 'label_readable': 'Personal Data'}, {'entity_group': 'DC', 'score': np.float32(0.9260748), 'word': 'us', 'start': 89, 'end': 91, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.96049315), 'word': 'processing', 'start': 167, 'end': 177, 'label_readable': 'Processing'}, {'entity_group': 'LB', 'score': np.float32(0.96290535), 'word': 'the General Data Protection Regulation ( âGDPRâ ),', 'start': 211, 'end': 263, 'label_readable': 'Legal Basis'}, {'entity_group': 'LB', 'score': np.float32(0.9211793), 'word': 'an EU wide Regulation for the', 'start': 264, 'end': 293, 'label_readable': 'Legal Basis'}, {'entity_group': 'PD', 'score': np.float32(0.9746621), 'word': 'personal data.', 'start': 308, 'end': 322, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9938059), 'word': 'collect', 'start': 83, 'end': 90, 'label_readable': 'Processing'}, {'entity_group': 'DC', 'score': np.float32(0.93268925), 'word': '##ffe Games Limited', 'start': 4, 'end': 21, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.6534327), 'word': ')', 'start': 88, 'end': 89, 'label_readable': 'Data Controller'}, {'entity_group': 'DC', 'score': np.float32(0.9785407), 'word': 'we', 'start': 367, 'end': 369, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.82970095), 'word': 'collect,', 'start': 239, 'end': 247, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.750534), 'word': 'store,', 'start': 248, 'end': 254, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.6555177), 'word': 'use, and manage', 'start': 255, 'end': 270, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.99708915), 'word': 'personal information', 'start': 298, 'end': 318, 'label_readable': 'Personal Data'}, {'entity_group': 'DS', 'score': np.float32(0.9454783), 'word': 'you', 'start': 79, 'end': 82, 'label_readable': 'Data Subject'}, {'entity_group': 'P', 'score': np.float32(0.97508675), 'word': 'provide', 'start': 329, 'end': 336, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9891248), 'word': 'process', 'start': 585, 'end': 592, 'label_readable': 'Processing'}, {'entity_group': 'OM', 'score': np.float32(0.7070179), 'word': '.', 'start': 694, 'end': 695, 'label_readable': 'Organisational Measure'}, {'entity_group': 'PD', 'score': np.float32(0.9937516), 'word': 'name', 'start': 1801, 'end': 1805, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.99309), 'word': 'address', 'start': 285, 'end': 292, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9935961), 'word': 'telephone number', 'start': 294, 'end': 310, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9899208), 'word': 'email address.', 'start': 315, 'end': 329, 'label_readable': 'Personal Data'}, {'entity_group': 'CONS', 'score': np.float32(0.6069132), 'word': 'choose', 'start': 7, 'end': 13, 'label_readable': 'Consent'}, {'entity_group': 'TP', 'score': np.float32(0.84083945), 'word': 'third party account', 'start': 59, 'end': 78, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.8250847), 'word': 'Facebook log', 'start': 200, 'end': 212, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8424162), 'word': '##in account information.', 'start': 212, 'end': 235, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9078861), 'word': 'a', 'start': 263, 'end': 264, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9310368), 'word': '##vat', 'start': 264, 'end': 267, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.95095986), 'word': '##ar', 'start': 267, 'end': 269, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8879874), 'word': 'Facebook name,', 'start': 271, 'end': 285, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.90036327), 'word': 'country', 'start': 286, 'end': 293, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.924056), 'word': 'displayed', 'start': 303, 'end': 312, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.77500635), 'word': 'to offer other functionalities such as to invite and play with friends', 'start': 409, 'end': 479, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9226345), 'word': 'create challenges for friends and see friendsâ game progress.', 'start': 481, 'end': 544, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.70463234), 'word': 'you', 'start': 567, 'end': 570, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.6691362), 'word': 'to log in on multiple devices', 'start': 571, 'end': 600, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8917275), 'word': 'synchronise progress across multiple devices on multiple platforms.', 'start': 605, 'end': 672, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.9155799), 'word': 'option', 'start': 211, 'end': 217, 'label_readable': 'Consent'}, {'entity_group': 'PD', 'score': np.float32(0.86223125), 'word': 'personal', 'start': 867, 'end': 875, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.99301153), 'word': 'collects', 'start': 8, 'end': 16, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9925655), 'word': 'collecting', 'start': 79, 'end': 89, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.9790948), 'word': 'using', 'start': 94, 'end': 99, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.98774046), 'word': 'to create your account, provide Services to you, improve our Service, contact you, conduct research and create reports for internal use.', 'start': 115, 'end': 251, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.9908853), 'word': 'use', 'start': 947, 'end': 950, 'label_readable': 'Processing'}, {'entity_group': 'TP', 'score': np.float32(0.98843), 'word': 'third parties', 'start': 611, 'end': 624, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.99281), 'word': 'store', 'start': 355, 'end': 360, 'label_readable': 'Processing'}, {'entity_group': 'SEU', 'score': np.float32(0.8312118), 'word': 'European Union', 'start': 321, 'end': 335, 'label_readable': 'Scale EU'}, {'entity_group': 'PD', 'score': np.float32(0.9954211), 'word': 'personally identifiable information', 'start': 72, 'end': 107, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.94806176), 'word': 'to', 'start': 1483, 'end': 1485, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.8562483), 'word': 'in order to take advantage of certain features', 'start': 525, 'end': 571, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.96566874), 'word': 'personally identifiable information.', 'start': 601, 'end': 637, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7944246), 'word': '–', 'start': 0, 'end': 1, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.95386744), 'word': 'Use', 'start': 2, 'end': 5, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9875648), 'word': '##r Name and Password.', 'start': 5, 'end': 25, 'label_readable': 'Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.84523535), 'word': 'third party message', 'start': 50, 'end': 69, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.95351076), 'word': 'user name ( s', 'start': 111, 'end': 122, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.99061406), 'word': 'password', 'start': 128, 'end': 136, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9185197), 'word': 's', 'start': 137, 'end': 138, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.89756167), 'word': '.', 'start': 139, 'end': 140, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.88681555), 'word': 'storage', 'start': 304, 'end': 311, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.61966884), 'word': 'your', 'start': 456, 'end': 460, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.60366756), 'word': '##gg', 'start': 3, 'end': 5, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.6080942), 'word': '##gate Usage Data', 'start': 7, 'end': 22, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8849326), 'word': 'usage data', 'start': 44, 'end': 54, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.6128287), 'word': 'information', 'start': 65, 'end': 76, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7420371), 'word': 'data', 'start': 101, 'end': 105, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.62125736), 'word': 'about', 'start': 106, 'end': 111, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.74668384), 'word': 'usage of the site', 'start': 118, 'end': 135, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.6452284), 'word': 'personally id', 'start': 176, 'end': 189, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.8715165), 'word': 'disclosure', 'start': 58, 'end': 68, 'label_readable': 'Processing'}, {'entity_group': 'DC', 'score': np.float32(0.8784719), 'word': '##ffe', 'start': 139, 'end': 142, 'label_readable': 'Data Controller'}, {'entity_group': 'CONS', 'score': np.float32(0.7289355), 'word': 'an opportunity to opt out of the', 'start': 172, 'end': 204, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.72268844), 'word': 'your consent', 'start': 229, 'end': 241, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.8671824), 'word': '.', 'start': 272, 'end': 273, 'label_readable': 'Consent'}, {'entity_group': 'NPD', 'score': np.float32(0.937669), 'word': 'operating system', 'start': 314, 'end': 330, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9897903), 'word': 'IP address', 'start': 613, 'end': 623, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.80219686), 'word': 'access times', 'start': 90, 'end': 102, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9458561), 'word': 'browser type', 'start': 104, 'end': 116, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.6534264), 'word': 'language and', 'start': 121, 'end': 133, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.66009974), 'word': 'referring Web site', 'start': 134, 'end': 152, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8195108), 'word': 'addresses', 'start': 153, 'end': 162, 'label_readable': 'Personal Data'}, {'entity_group': 'ADM', 'score': np.float32(0.624195), 'word': 'logged', 'start': 170, 'end': 176, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'ADM', 'score': np.float32(0.61171657), 'word': 'automatically.', 'start': 177, 'end': 191, 'label_readable': 'Automated Decision Making'}, {'entity_group': 'RP', 'score': np.float32(0.9636245), 'word': 'to monitor, develop and analyse your use of the Service.', 'start': 221, 'end': 277, 'label_readable': 'Required Purpose'}, {'entity_group': 'DC', 'score': np.float32(0.6576578), 'word': 'Facebook', 'start': 95, 'end': 103, 'label_readable': 'Data Controller'}, {'entity_group': 'P', 'score': np.float32(0.70480937), 'word': 'receive', 'start': 160, 'end': 167, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.8985921), 'word': 'name,', 'start': 228, 'end': 233, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9033627), 'word': 'profile picture /', 'start': 234, 'end': 251, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.77604234), 'word': '##vatar', 'start': 253, 'end': 258, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.73099273), 'word': ',', 'start': 258, 'end': 259, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9009783), 'word': 'gender,', 'start': 260, 'end': 267, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.90746295), 'word': 'location,', 'start': 268, 'end': 277, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.80720973), 'word': 'email address and', 'start': 278, 'end': 295, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.93839073), 'word': 'date of birth.', 'start': 296, 'end': 310, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.89608324), 'word': 'received', 'start': 377, 'end': 385, 'label_readable': 'Processing'}, {'entity_group': 'DSO', 'score': np.float32(0.8196096), 'word': '.', 'start': 419, 'end': 420, 'label_readable': 'Data Source'}, {'entity_group': 'TP', 'score': np.float32(0.98612756), 'word': 'third - party', 'start': 556, 'end': 567, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.99451554), 'word': 'email address', 'start': 1807, 'end': 1820, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.96468824), 'word': 'access token', 'start': 650, 'end': 662, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.93361354), 'word': 'en', 'start': 667, 'end': 669, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.80145794), 'word': '##ry', 'start': 670, 'end': 672, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.8647741), 'word': '##pted', 'start': 672, 'end': 676, 'label_readable': 'Processing'}, {'entity_group': 'TM', 'score': np.float32(0.968658), 'word': 'cookie', 'start': 288, 'end': 294, 'label_readable': 'Technical Measure'}, {'entity_group': 'TP', 'score': np.float32(0.99017835), 'word': 'third party', 'start': 1257, 'end': 1268, 'label_readable': 'Third Party'}, {'entity_group': 'P', 'score': np.float32(0.98540074), 'word': 'record', 'start': 141, 'end': 147, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.94814473), 'word': 'unique device ID', 'start': 135, 'end': 151, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.7037562), 'word': 'hardware type', 'start': 183, 'end': 196, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.6960211), 'word': 'media access control', 'start': 198, 'end': 218, 'label_readable': 'Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.8709836), 'word': 'version of your', 'start': 298, 'end': 313, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.8774448), 'word': 'device name', 'start': 348, 'end': 359, 'label_readable': 'Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.7583585), 'word': 'Google +', 'start': 418, 'end': 425, 'label_readable': 'Third Party'}, {'entity_group': 'PD', 'score': np.float32(0.98698634), 'word': 'location', 'start': 437, 'end': 445, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.78334135), 'word': 'for troubleshooting', 'start': 508, 'end': 527, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.6778455), 'word': 'helps', 'start': 532, 'end': 537, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.96847653), 'word': 'understand usage trends.', 'start': 541, 'end': 565, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.96953976), 'word': 'location data', 'start': 598, 'end': 611, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9754524), 'word': 'to provide location related Services and advertisements.', 'start': 612, 'end': 668, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.9028408), 'word': 'technologies', 'start': 688, 'end': 700, 'label_readable': 'Technical Measure'}, {'entity_group': 'PD', 'score': np.float32(0.6851776), 'word': 'GPS', 'start': 732, 'end': 735, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.744024), 'word': 'W', 'start': 737, 'end': 738, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.6891819), 'word': '##i -', 'start': 738, 'end': 740, 'label_readable': 'Personal Data'}, {'entity_group': 'TM', 'score': np.float32(0.66165596), 'word': 'Fi', 'start': 740, 'end': 742, 'label_readable': 'Technical Measure'}, {'entity_group': 'PD', 'score': np.float32(0.9884364), 'word': 'IP address.', 'start': 779, 'end': 790, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9777045), 'word': 'GPS g', 'start': 874, 'end': 879, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9150338), 'word': '##eo - location', 'start': 801, 'end': 812, 'label_readable': 'Personal Data'}, {'entity_group': 'CONS', 'score': np.float32(0.9130575), 'word': 'your', 'start': 837, 'end': 841, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.6408798), 'word': 'consent.', 'start': 923, 'end': 931, 'label_readable': 'Consent'}, {'entity_group': 'P', 'score': np.float32(0.99166226), 'word': 'share', 'start': 956, 'end': 961, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.9639435), 'word': 'anonymous location data', 'start': 967, 'end': 990, 'label_readable': 'Personal Data'}, {'entity_group': 'TP', 'score': np.float32(0.9203485), 'word': 'partners', 'start': 996, 'end': 1004, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.8890546), 'word': 'to improve the Services.', 'start': 1014, 'end': 1038, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.7439377), 'word': 'turn', 'start': 1115, 'end': 1119, 'label_readable': 'Consent'}, {'entity_group': 'P', 'score': np.float32(0.89294535), 'word': 'create', 'start': 1287, 'end': 1293, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.973485), 'word': 'unique', 'start': 1351, 'end': 1357, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9817777), 'word': 'user ID', 'start': 311, 'end': 318, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9911176), 'word': 'stored', 'start': 1369, 'end': 1375, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.88696444), 'word': 'profile information', 'start': 1400, 'end': 1419, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.87961), 'word': 'to track the G', 'start': 1420, 'end': 1434, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.75216645), 'word': '##ffe games you are playing.', 'start': 1437, 'end': 1463, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.8126074), 'word': 'Facebook', 'start': 1553, 'end': 1561, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.88335884), 'word': 'authentic', 'start': 1688, 'end': 1697, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.850689), 'word': '##ate your identity', 'start': 1697, 'end': 1714, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.7069034), 'word': 'resume', 'start': 1826, 'end': 1832, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.97993225), 'word': 'Con', 'start': 1891, 'end': 1894, 'label_readable': 'Personal Data'}, {'entity_group': 'DSO', 'score': np.float32(0.6404768), 'word': '##N Service', 'start': 70, 'end': 79, 'label_readable': 'Data Source'}, {'entity_group': 'PD', 'score': np.float32(0.99582183), 'word': 'contact information', 'start': 608, 'end': 627, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.9372175), 'word': 'used', 'start': 258, 'end': 262, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.67357725), 'word': 'sending communications to the', 'start': 287, 'end': 316, 'label_readable': 'Required Purpose'}, {'entity_group': 'DS', 'score': np.float32(0.86110175), 'word': 'You', 'start': 1398, 'end': 1401, 'label_readable': 'Data Subject'}, {'entity_group': 'DSR17', 'score': np.float32(0.6617263), 'word': 'removal', 'start': 411, 'end': 418, 'label_readable': 'Art. 17 Right to erasure (‘right to be forgotten’)'}, {'entity_group': 'P', 'score': np.float32(0.98678815), 'word': 'stores', 'start': 479, 'end': 485, 'label_readable': 'Processing'}, {'entity_group': 'RET', 'score': np.float32(0.78555775), 'word': 'when you contact', 'start': 34, 'end': 50, 'label_readable': 'Retention'}, {'entity_group': 'RP', 'score': np.float32(0.9941134), 'word': 'to contact you about your gaming experience with Giraffe games and notify you about company news and promotions.', 'start': 112, 'end': 224, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.96727484), 'word': 'op', 'start': 294, 'end': 296, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.9812479), 'word': '##t - out', 'start': 296, 'end': 301, 'label_readable': 'Consent'}, {'entity_group': 'RP', 'score': np.float32(0.62029004), 'word': 'send you game updates', 'start': 83, 'end': 104, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.66425526), 'word': 'high scores and other service related notifications', 'start': 106, 'end': 157, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.6441131), 'word': 'to you.', 'start': 184, 'end': 191, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.97088563), 'word': '##t - out from', 'start': 215, 'end': 225, 'label_readable': 'Consent'}, {'entity_group': 'NPD', 'score': np.float32(0.9261417), 'word': 'anonymous data', 'start': 40, 'end': 54, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.99128914), 'word': 'collected', 'start': 19, 'end': 28, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.854296), 'word': 'presented', 'start': 258, 'end': 267, 'label_readable': 'Processing'}, {'entity_group': 'NPD', 'score': np.float32(0.9340551), 'word': 'percentage of users who complete a particular level.', 'start': 324, 'end': 376, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.69255936), 'word': 'acquire', 'start': 12, 'end': 19, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.83635986), 'word': 'in', 'start': 199, 'end': 201, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9090511), 'word': 'sweepstakes', 'start': 204, 'end': 215, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.63518685), 'word': 'the', 'start': 235, 'end': 238, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.98432803), 'word': '.', 'start': 246, 'end': 247, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.7506714), 'word': 'participate in a sweepstakes or contest', 'start': 286, 'end': 325, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.71638167), 'word': 'our', 'start': 171, 'end': 174, 'label_readable': 'Required Purpose'}, {'entity_group': 'CONS', 'score': np.float32(0.7188373), 'word': 'participate', 'start': 354, 'end': 365, 'label_readable': 'Consent'}, {'entity_group': 'CONS', 'score': np.float32(0.70366013), 'word': 'choice whether or not to disclose', 'start': 510, 'end': 543, 'label_readable': 'Consent'}, {'entity_group': 'PD', 'score': np.float32(0.91401625), 'word': 'shipping address', 'start': 646, 'end': 662, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9931445), 'word': 'demographic information', 'start': 669, 'end': 692, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.7633662), 'word': 'z', 'start': 702, 'end': 703, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.81428605), 'word': '##ip code ).', 'start': 703, 'end': 712, 'label_readable': 'Personal Data'}, {'entity_group': 'RP', 'score': np.float32(0.9657351), 'word': 'to notify winners and award prizes', 'start': 737, 'end': 771, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.987816), 'word': 'to monitor traffic or personalise the Service.', 'start': 773, 'end': 819, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.7337005), 'word': 'third party service provider', 'start': 834, 'end': 862, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.7010201), 'word': 'to conduct', 'start': 863, 'end': 873, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.93137443), 'word': 'sweepstakes or contests', 'start': 880, 'end': 903, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.97900236), 'word': 'transfer', 'start': 38, 'end': 46, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.9653623), 'word': 'to identify a userâs computer / device', 'start': 79, 'end': 117, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9090732), 'word': 'to ârememberâ things about your visit, such', 'start': 122, 'end': 169, 'label_readable': 'Required Purpose'}, {'entity_group': 'PD', 'score': np.float32(0.9768945), 'word': 'user name', 'start': 195, 'end': 204, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.96958625), 'word': 'password.', 'start': 209, 'end': 218, 'label_readable': 'Personal Data'}, {'entity_group': 'P', 'score': np.float32(0.8378962), 'word': 'contained', 'start': 232, 'end': 241, 'label_readable': 'Processing'}, {'entity_group': 'P', 'score': np.float32(0.94208896), 'word': 'linked', 'start': 261, 'end': 267, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.98559004), 'word': 'for purposes such as improving the quality of our Service, tail', 'start': 320, 'end': 383, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.99058545), 'word': '##oring recommendations to your interests, and making the Service easier to use.', 'start': 383, 'end': 461, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.98185205), 'word': 'cookies', 'start': 302, 'end': 309, 'label_readable': 'Technical Measure'}, {'entity_group': 'OM', 'score': np.float32(0.88736755), 'word': 'any time', 'start': 490, 'end': 498, 'label_readable': 'Organisational Measure'}, {'entity_group': 'RP', 'score': np.float32(0.6484476), 'word': 'or', 'start': 539, 'end': 541, 'label_readable': 'Required Purpose'}, {'entity_group': 'RP', 'score': np.float32(0.9363521), 'word': 'features of the Service.', 'start': 546, 'end': 570, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.8992274), 'word': 'deliver', 'start': 630, 'end': 637, 'label_readable': 'Processing'}, {'entity_group': 'RP', 'score': np.float32(0.8520122), 'word': 'can be tracked.', 'start': 723, 'end': 738, 'label_readable': 'Required Purpose'}, {'entity_group': 'TP', 'score': np.float32(0.9722578), 'word': '##vert', 'start': 67, 'end': 71, 'label_readable': 'Third Party'}, {'entity_group': 'TP', 'score': np.float32(0.9344387), 'word': 'third party sites', 'start': 1000, 'end': 1017, 'label_readable': 'Third Party'}, {'entity_group': 'RP', 'score': np.float32(0.9842799), 'word': 'to measure advertisement performance and to provide advertisements about goods and services of interest to you.', 'start': 1044, 'end': 1155, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.8368174), 'word': 'cookies.', 'start': 1452, 'end': 1460, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.90759206), 'word': 'support analytics and logged in users on the Site.', 'start': 1486, 'end': 1536, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.9636185), 'word': 'software technology', 'start': 64, 'end': 83, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.9923518), 'word': 'clear gifs', 'start': 91, 'end': 101, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.96822727), 'word': 'Web Beacons /', 'start': 110, 'end': 122, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.8234052), 'word': 'Web Bugs ),', 'start': 122, 'end': 132, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.7506271), 'word': 'better manage content', 'start': 146, 'end': 167, 'label_readable': 'Required Purpose'}, {'entity_group': 'TM', 'score': np.float32(0.9763764), 'word': 'Clear gifs', 'start': 224, 'end': 234, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.84798855), 'word': 'track the online movements of Web users', 'start': 327, 'end': 366, 'label_readable': 'Required Purpose'}, {'entity_group': 'P', 'score': np.float32(0.70075804), 'word': 'embedded', 'start': 460, 'end': 468, 'label_readable': 'Processing'}, {'entity_group': 'PD', 'score': np.float32(0.94591296), 'word': 'device identifier', 'start': 458, 'end': 475, 'label_readable': 'Personal Data'}, {'entity_group': 'PD', 'score': np.float32(0.9666211), 'word': 'personal information.', 'start': 719, 'end': 740, 'label_readable': 'Personal Data'}, {'entity_group': 'TM', 'score': np.float32(0.78553873), 'word': 'mobile analytic', 'start': 7, 'end': 22, 'label_readable': 'Technical Measure'}, {'entity_group': 'TM', 'score': np.float32(0.82699287), 'word': '##s software', 'start': 22, 'end': 32, 'label_readable': 'Technical Measure'}, {'entity_group': 'RP', 'score': np.float32(0.95920247), 'word': 'us to better understand the functionality of our Mobile Software on your device.', 'start': 42, 'end': 122, 'label_readable': 'Required Purpose'}, {'entity_group': 'NPD', 'score': np.float32(0.8517284), 'word': 'how often you use the application,', 'start': 168, 'end': 202, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9144176), 'word': 'the events that occur within the application,', 'start': 203, 'end': 248, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.78735954), 'word': 'aggregate', 'start': 249, 'end': 258, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.9253774), 'word': '##d usage,', 'start': 258, 'end': 266, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.80897814), 'word': 'performance data,', 'start': 267, 'end': 284, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'NPD', 'score': np.float32(0.97440815), 'word': 'where the application was downloaded from.', 'start': 289, 'end': 331, 'label_readable': 'Non-Personal Data'}, {'entity_group': 'TM', 'score': np.float32(0.</t>
+  </si>
+  <si>
     <t>Personal Data (99.69999694824219%): This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. | Personal Data (90.69999694824219%): For information about how we collect, use, share, and otherwise process consumer health data as defined under Washingtonâs My Health My Data Act and other similar state laws, please refer to the Consumer Health Data Privacy Policy. | Personal Data (86.4000015258789%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (99.0999984741211%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (99.19999694824219%): This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. | Personal Data (99.4000015258789%): This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. | Personal Data (99.4000015258789%):  | Personal Data (99.5%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (99.19999694824219%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (98.9000015258789%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (99.4000015258789%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (96.80000305175781%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (95.30000305175781%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (99.19999694824219%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (73.5999984741211%):  | Personal Data (77.5%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (74.80000305175781%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (78.5999984741211%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (72.4000015258789%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (74.69999694824219%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (88.0999984741211%): Privacy Policy | TikTok U.S. | Personal Data (93.69999694824219%):  | Non-Personal Data (84.9000015258789%): That information includes the content of the message and information about the message, such as when it was sent, received, or read, and message participants. | Personal Data (78.80000305175781%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (92.5%): Information, including text, images, and videos, found in your deviceâs clipboard, with your permission. | Personal Data (88.4000015258789%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (85.80000305175781%):  | Personal Data (98.30000305175781%): Purchase information, including payment card numbers or other third-party payment information (such as PayPal) where required for the purpose of payment, and billing and shipping address. | Personal Data (97.69999694824219%): Purchase information, including payment card numbers or other third-party payment information (such as PayPal) where required for the purpose of payment, and billing and shipping address. | Personal Data (95.80000305175781%): Purchase information, including payment card numbers or other third-party payment information (such as PayPal) where required for the purpose of payment, and billing and shipping address. | Personal Data (97.0999984741211%):  | Personal Data (96.30000305175781%): Purchase information, including payment card numbers or other third-party payment information (such as PayPal) where required for the purpose of payment, and billing and shipping address. | Personal Data (83.0%): We also collect information that is required for extended warranty purposes and your transaction and purchase history on or through the Platform. | Personal Data (75.5%): Your phone and social network contacts, with your permission. | Personal Data (86.9000015258789%): If you choose to find other users through your phone contacts, we will access and collect information such as names, phone numbers, and email addresses, and match that information against existing users of the Platform. | Personal Data (84.30000305175781%): If you choose to find other users through your phone contacts, we will access and collect information such as names, phone numbers, and email addresses, and match that information against existing users of the Platform. | Personal Data (89.80000305175781%): If you choose to find other users through your phone contacts, we will access and collect information such as names, phone numbers, and email addresses, and match that information against existing users of the Platform. | Personal Data (99.4000015258789%): If you choose to find other users through your social network contacts, we will collect your public profile information as well as names and profiles of your social network contacts. | Personal Data (99.5999984741211%): If you choose to find other users through your phone contacts, we will access and collect information such as names, phone numbers, and email addresses, and match that information against existing users of the Platform. | Personal Data (91.19999694824219%): If you choose to find other users through your social network contacts, we will collect your public profile information as well as names and profiles of your social network contacts. | Personal Data (86.5999984741211%): Information to verify an account such as proof of identity or age.Â Information in correspondence you send to us, including when you contact us for support. | Personal Data (79.0%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (84.5%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Personal Data (72.9000015258789%): Your choices and communication preferences. | Personal Data (83.5999984741211%):  | Personal Data (98.80000305175781%): Information From Other Sources We may receive the information described in this Privacy Policy from other sources, such as: If you choose to sign-up or log-in to the Platform using a third-party service such as Facebook, Twitter, Instagram, or Google, or link your TikTok account to a third-party service, we may collect information from the serviceâfor example, your public profile information (such as nickname), email, and contact list. | Personal Data (92.9000015258789%): These partners also share information with us, such as mobile identifiers for advertising, hashed email addresses and phone numbers, and cookie identifiers, which we use to help match you and your actions outside of the Platform with your TikTok account. | Personal Data (89.4000015258789%): If you choose to find other users through your phone contacts, we will access and collect information such as names, phone numbers, and email addresses, and match that information against existing users of the Platform. | Personal Data (89.0999984741211%): These partners also share information with us, such as mobile identifiers for advertising, hashed email addresses and phone numbers, and cookie identifiers, which we use to help match you and your actions outside of the Platform with your TikTok account. | Personal Data (73.30000305175781%): We are committed to protecting and respecting your privacy. | Personal Data (76.19999694824219%): We may receive information about you from others, including where you are included or mentioned in User Content, direct messages, in a complaint, appeal, request or feedback submitted to us, or if your contact information is provided to us. | Personal Data (79.19999694824219%): Automatically Collected Information We automatically collect certain information from you when you use the Platform, including internet or other network activity information such as your IP address, geolocation-related data, unique device identifiers, browsing and search history (including content you have viewed in the Platform), and Cookies. | Personal Data (97.5%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Personal Data (97.4000015258789%):  | Personal Data (88.9000015258789%):  | Personal Data (91.5%): Automatically Collected Information We automatically collect certain information from you when you use the Platform, including internet or other network activity information such as your IP address, geolocation-related data, unique device identifiers, browsing and search history (including content you have viewed in the Platform), and Cookies. | Personal Data (89.5999984741211%): Automatically Collected Information We automatically collect certain information from you when you use the Platform, including internet or other network activity information such as your IP address, geolocation-related data, unique device identifiers, browsing and search history (including content you have viewed in the Platform), and Cookies. | Personal Data (74.19999694824219%):  | Non-Personal Data (83.19999694824219%):  | Non-Personal Data (82.4000015258789%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Non-Personal Data (74.5%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Personal Data (89.0%): Automatically Collected Information We automatically collect certain information from you when you use the Platform, including internet or other network activity information such as your IP address, geolocation-related data, unique device identifiers, browsing and search history (including content you have viewed in the Platform), and Cookies. | Non-Personal Data (89.30000305175781%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Non-Personal Data (96.19999694824219%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Personal Data (94.0999984741211%): The Platform is provided and controlled by TikTok Inc. | Personal Data (77.69999694824219%):  | Personal Data (84.9000015258789%):  | Non-Personal Data (95.19999694824219%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Non-Personal Data (90.0%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Non-Personal Data (83.5999984741211%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Non-Personal Data (82.0999984741211%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Non-Personal Data (86.5%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Non-Personal Data (77.5%): Capitalized terms that are not defined in this Privacy Policy have the meaning given to them in theÂ Terms of Service. | Non-Personal Data (73.19999694824219%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Non-Personal Data (84.80000305175781%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Personal Data (80.0999984741211%): Privacy Policy | TikTok U.S. | Personal Data (93.0%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Personal Data (84.5%): We automatically assign you a device ID and user ID. | Personal Data (98.9000015258789%): We automatically assign you a device ID and user ID. | Personal Data (75.5999984741211%): We may also associate you with information collected from devices other than those you use to log-in to the Platform.Â Location Data. | Personal Data (81.69999694824219%): We collect information about your approximate location, including location information based on your SIM card and/or IP address. | Personal Data (75.5999984741211%): We collect information about your approximate location, including location information based on your SIM card and/or IP address. | Personal Data (81.19999694824219%): We collect information about your approximate location, including location information based on your SIM card and/or IP address. | Personal Data (78.80000305175781%): Current versions of the app do not collect precise or approximate GPS information from U.S. | Personal Data (77.4000015258789%): We may collect information about the videos, images and audio that are a part of your User Content, such as identifying the objects and scenery that appear, the existence and location within an image of face and body features and attributes, the nature of the audio, and the text of the words spoken in your User Content. | Personal Data (99.0%): We may collect biometric identifiers and biometric information as defined under U.S. | Personal Data (99.5999984741211%):  | Personal Data (92.30000305175781%):  | Personal Data (97.80000305175781%): We may collect information about the videos, images and audio that are a part of your User Content, such as identifying the objects and scenery that appear, the existence and location within an image of face and body features and attributes, the nature of the audio, and the text of the words spoken in your User Content. | Personal Data (98.9000015258789%):  | Personal Data (86.69999694824219%): laws, such as faceprints and voiceprints, from your User Content. | Personal Data (81.80000305175781%): In addition, we collect location information (such as tourist attractions, shops, or other points of interest) if you choose to add the location information to your User Content. | Personal Data (92.0%): It also includes information, such as your account name, that enables other users to trace back the User Content to your user account. | Non-Personal Data (73.5%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Personal Data (93.4000015258789%): We may link your contact or account information with your activity on and off our Platform across all your devices, using your email or other log-in or device information. | Personal Data (89.69999694824219%): What Information We Collect We may collect information from and about you, including information that you provide, information from other sources, and automatically collected information. | Non-Personal Data (78.5999984741211%):  | Non-Personal Data (77.0%): Privacy Policy | TikTok U.S. | Non-Personal Data (90.4000015258789%):  | Personal Data (78.19999694824219%): How We Use Your Information As explained below, we use your information to improve, support and administer the Platform, to allow you to use its functionalities, and to fulfill and enforce our Terms of Service. | Personal Data (97.19999694824219%): Information you share through surveys or your participation in challenges, research, promotions, marketing campaigns, events, or contests such as your gender, age, likeness, and preferences. | Personal Data (89.80000305175781%): To infer additional information about you, such as your age, gender, and interests. | Personal Data (90.0999984741211%):  | Personal Data (90.9000015258789%): These service providers and business partners may include: Payment processors and transaction fulfillment providers, who may receive the Information You Provide, Information From Other Sources, and Automatically Collected Information but who do not receive your message data, including, in particular, the following third-party payment providers/processors: PayPal (https://www.paypal.com/us/webapps/mpp/ua/privacy-full) and Stripe (https://stripe.com/en-ie/privacy). | Personal Data (97.19999694824219%): Researchers who may receive the Information You Provide, Information From Other Sources, and Automatically Collected Information but would not receive your payment information or message data. | Personal Data (76.5999984741211%): If you choose to find other users through your phone contacts, we will access and collect information such as names, phone numbers, and email addresses, and match that information against existing users of the Platform. | Personal Data (90.69999694824219%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Personal Data (90.5999984741211%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Personal Data (86.9000015258789%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Personal Data (92.9000015258789%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Personal Data (87.4000015258789%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Personal Data (82.69999694824219%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Personal Data (96.69999694824219%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Personal Data (80.5999984741211%): For example, we may process your financial information in order to provide you the goods or services you request from us or your driverâs license number in order to verify your identity. | Personal Data (97.5%): For example, we may process your financial information in order to provide you the goods or services you request from us or your driverâs license number in order to verify your identity. | Personal Data (87.80000305175781%): Automatically Collected Information We automatically collect certain information from you when you use the Platform, including internet or other network activity information such as your IP address, geolocation-related data, unique device identifiers, browsing and search history (including content you have viewed in the Platform), and Cookies. | Personal Data (74.19999694824219%): These partners also share information with us, such as mobile identifiers for advertising, hashed email addresses and phone numbers, and cookie identifiers, which we use to help match you and your actions outside of the Platform with your TikTok account. | Personal Data (88.0%): These partners also share information with us, such as mobile identifiers for advertising, hashed email addresses and phone numbers, and cookie identifiers, which we use to help match you and your actions outside of the Platform with your TikTok account. | Personal Data (81.30000305175781%): TikTok may transmit your data to its servers or data centers outside of the United States for storage and/or processing.</t>
   </si>
   <si>
@@ -877,6 +2647,24 @@
     <t xml:space="preserve">Personal Data (86.5999984741211%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Personal Data (94.19999694824219%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Personal Data (96.69999694824219%): For example,  by default you are findable to others through your phone number and/or email address that you provided. | Personal Data (99.0%): For example,  by default you are findable to others through your phone number and/or email address that you provided. | Personal Data (87.9000015258789%): Below, we give you more details on the types of settings that are available, link out to our data download tool, and provide instructions on how to delete data or your account. | Personal Data (76.4000015258789%): To do this, we ask you to provide us with account details (information about you, like your name, username, email address, birthday, and phone number). | Personal Data (99.0%): Information for Law EnforcementSnap is committed to assisting law enforcement while respecting the privacy and rights of our users.Financial SextortionWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Combating Illicit DrugsWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Report a Safety ConcernIf you ever experience harassment, bullying, or any other safety concern, you can always report it right to us. | Personal Data (76.80000305175781%):  | Personal Data (84.0%): To do this, we ask you to provide us with account details (information about you, like your name, username, email address, birthday, and phone number). | Personal Data (74.5%): To do this, we ask you to provide us with account details (information about you, like your name, username, email address, birthday, and phone number). | Personal Data (92.5%): When you set up your profile, you’ll also provide us with profile details (like your Bitmoji and profile picture). | Personal Data (88.0%): If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history). | Personal Data (93.5999984741211%): If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history). | Personal Data (97.80000305175781%): If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history). | Non-Personal Data (86.30000305175781%):  | Non-Personal Data (86.0999984741211%):  | Non-Personal Data (75.80000305175781%): This includes usage information (information about how you interact with our Services — for example, which Lenses you view and apply, your premium subscriptions, Stories you watch, and how often you interact with other Snapchatters) and content information (information about content you create or provide, your engagement with the camera and creative tools, your interactions with My AI, and metadata — for example, information about the content itself like the date and time it was posted and who viewed it). | Non-Personal Data (83.0%): This includes usage information (information about how you interact with our Services — for example, which Lenses you view and apply, your premium subscriptions, Stories you watch, and how often you interact with other Snapchatters) and content information (information about content you create or provide, your engagement with the camera and creative tools, your interactions with My AI, and metadata — for example, information about the content itself like the date and time it was posted and who viewed it). | Personal Data (74.0%): This includes usage information (information about how you interact with our Services — for example, which Lenses you view and apply, your premium subscriptions, Stories you watch, and how often you interact with other Snapchatters) and content information (information about content you create or provide, your engagement with the camera and creative tools, your interactions with My AI, and metadata — for example, information about the content itself like the date and time it was posted and who viewed it). | Non-Personal Data (90.19999694824219%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Non-Personal Data (74.0%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Non-Personal Data (83.30000305175781%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Non-Personal Data (96.9000015258789%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Personal Data (90.0999984741211%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Non-Personal Data (89.80000305175781%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Non-Personal Data (89.5999984741211%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Non-Personal Data (80.9000015258789%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Non-Personal Data (86.0999984741211%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Non-Personal Data (83.5999984741211%):  | Personal Data (99.0%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Personal Data (93.4000015258789%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Personal Data (94.69999694824219%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Non-Personal Data (82.5%):  | Non-Personal Data (86.30000305175781%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Personal Data (97.0999984741211%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Personal Data (96.4000015258789%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Personal Data (89.69999694824219%): If you’ve explicitly granted device-level permissions, device information may also include information about your device phonebook (contacts and related information), images and other information from your device’s camera, photos, and microphone (like the ability to take photos, videos, view stored photos and videos, and access the microphone to record audio while recording video), and location information (precise location through methods like GPS signals). | Personal Data (95.80000305175781%): If you’ve explicitly granted device-level permissions, device information may also include information about your device phonebook (contacts and related information), images and other information from your device’s camera, photos, and microphone (like the ability to take photos, videos, view stored photos and videos, and access the microphone to record audio while recording video), and location information (precise location through methods like GPS signals). | Personal Data (99.0999984741211%): Of course, you’ll also provide us with information you send through or save within our Services, including content and information about that content, and content you share and generate with our AI Features (content, or “Inputs,” including text, images, video, audio, precise location, and engagement, used to generate content and responses, or “Outputs”). | Personal Data (79.0%): If you’ve explicitly granted device-level permissions, device information may also include information about your device phonebook (contacts and related information), images and other information from your device’s camera, photos, and microphone (like the ability to take photos, videos, view stored photos and videos, and access the microphone to record audio while recording video), and location information (precise location through methods like GPS signals). | Personal Data (76.5999984741211%): Of course, you’ll also provide us with information you send through or save within our Services, including content and information about that content, and content you share and generate with our AI Features (content, or “Inputs,” including text, images, video, audio, precise location, and engagement, used to generate content and responses, or “Outputs”). | Personal Data (99.0%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Personal Data (96.0%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Personal Data (94.19999694824219%): Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines). | Personal Data (71.30000305175781%): For example, if you watch a lot of sports content, but skip content with hair and makeup tips, our recommendation algorithms will prioritize sports, but not those makeup tips. | Personal Data (99.0999984741211%): Your information can help us decide what kind of improvements we should make, but we are always focused on privacy — and we don’t want to use more of your personal information than necessary to develop our features and models. | Personal Data (74.69999694824219%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Personal Data (71.0999984741211%): Previous ReportsTransparency Report archives Regional InformationEuropean UnionEU specific informationCalifornia California specific informationAustralia Australia specific informationIndiaIndia specific information ResourcesResearchersAccess for researchersAds GalleryFind European Union ads that delivered in the last 12 months and commercial content that’s live right now. | Personal Data (85.69999694824219%):  | Personal Data (83.0999984741211%):  | Personal Data (72.19999694824219%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Personal Data (82.19999694824219%): For example, by delivering a Snap you want to send to a friend or, if you share your location on Snap Map, to show you suggestions like places you might like in your neighborhood, content others have posted to the Map, or your friends if they’re sharing their location with you. | Personal Data (83.80000305175781%):  | Personal Data (99.30000305175781%):  | Non-Personal Data (83.80000305175781%): This Policy covers our Snapchat app as well as our other products, services, and features, such as Bitmoji, Spectacles, and our advertising and commerce initiatives. | Non-Personal Data (75.0999984741211%):  | Non-Personal Data (94.30000305175781%): We share your information, such as device and usage information, with industry partners working to prevent fraud. | Personal Data (74.80000305175781%): Content GuidelinesAdditional standards for algorithmic recommendation beyond the creator’s friends or subscribers Creator Monetization Policy Content must adhere to the policies to be eligible for monetization. | Personal Data (90.80000305175781%): Or if you provided access to your phone or third party platform contacts to make friending easier, you can change that later on in your app settings. | Personal Data (81.5999984741211%): </t>
   </si>
   <si>
+    <t>Personal Data (99.19999694824219%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Personal Data (99.5%):  | Personal Data (73.0999984741211%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Personal Data (94.9000015258789%): Our legal bases for using your data C. | Personal Data (99.80000305175781%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Personal Data (95.30000305175781%): If you use Uber in Nevada or Washington, please go here for information regarding Uber’s practices as relates to collection and use of consumer health data under those states’ privacy laws. | Personal Data (99.30000305175781%): Uber Privacy Notice: Drivers and Delivery People Previous version of the Privacy Notice I. | Personal Data (99.4000015258789%):  | Personal Data (92.0%):  | Personal Data (98.80000305175781%): We collect demographic data if necessary to enable certain features. | Personal Data (94.4000015258789%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Personal Data (82.0999984741211%):  | Personal Data (94.80000305175781%): We collect or infer your gender to enable Women Rider Preference, and for marketing and advertising. | Personal Data (99.0%): Identity verification information. | Personal Data (86.30000305175781%):  | Personal Data (98.9000015258789%):  | Personal Data (96.4000015258789%): Government-issued identification documents, such as driver’s licenses or passports (which may contain identification photos and numbers, expiration date, date of birth, and gender) User-submitted selfies d. | Personal Data (99.30000305175781%): Government-issued identification documents, such as driver’s licenses or passports (which may contain identification photos and numbers, expiration date, date of birth, and gender) User-submitted selfies d. | Personal Data (98.30000305175781%): This notice describes how we collect and use your data if you request or receive products or services through Uber’s apps or websites, except when you use Uber Freight, Careem or Uber Taxi (South Korea). | Personal Data (94.9000015258789%):  | Personal Data (99.19999694824219%): For example: We collect your date of birth and/or age to verify your eligibility to use age-restricted products or services, such as Uber for teens, or if you purchase alcohol, tobacco or cannabis products. | Personal Data (98.9000015258789%): We collect or infer your gender to enable Women Rider Preference, and for marketing and advertising. | Personal Data (75.80000305175781%): Receive services through Uber’s apps or websites requested by other account owners (a “Guest User”), including if you receive ride or delivery services ordered by Uber Health, Central, Uber Direct or Uber for Business customers (collectively, “Enterprise Customers”); or by friends, family members or other individual account owners, including via Uber Connect; or receive a gift card. | Personal Data (98.5%): Government-issued identification documents, such as driver’s licenses or passports (which may contain identification photos and numbers, expiration date, date of birth, and gender) User-submitted selfies d. | Personal Data (82.19999694824219%): Use features that enable you to create Lists or reviews of restaurants or merchants Upload photos and recordings (including those submitted for purposes of customer support) Provide ratings or feedback for drivers, delivery people, restaurants or merchants, or they provide feedback regarding you. | Personal Data (99.4000015258789%): Travel information. | Personal Data (99.5999984741211%): We collect travel itinerary information if you book bus, train or flight travel through Uber's apps. | Personal Data (97.80000305175781%): Location data. | Personal Data (72.5999984741211%):  | Personal Data (79.4000015258789%): We also determine your approximate location, and can determine your precise location if you allow us to do so through the settings on your phone. | Personal Data (81.80000305175781%): We also determine your approximate location, and can determine your precise location if you allow us to do so through the settings on your phone. | Personal Data (96.4000015258789%): You can use Uber without letting us collect your precise location. | Personal Data (96.19999694824219%): However, it may be less convenient for you, including because you will have to type your location into your phone instead of allowing us to detect it for you. | Personal Data (95.5999984741211%): See “Choice and transparency” section below for information on how to control whether Uber may collect your precise location data. | Personal Data (74.0999984741211%):  | Personal Data (74.30000305175781%): Legal information A. | Non-Personal Data (89.9000015258789%): Receive services through Uber’s apps or websites requested by other account owners (a “Guest User”), including if you receive ride or delivery services ordered by Uber Health, Central, Uber Direct or Uber for Business customers (collectively, “Enterprise Customers”); or by friends, family members or other individual account owners, including via Uber Connect; or receive a gift card. | Non-Personal Data (85.80000305175781%):  | Non-Personal Data (92.0999984741211%): This refers to data about how you interact with Uber’s apps and websites. | Non-Personal Data (91.4000015258789%): Scope This notice applies when you use Uber’s apps or websites to request or receive products or services, including rides or deliveries. | Personal Data (86.80000305175781%): Device data. | Personal Data (74.4000015258789%):  | Non-Personal Data (89.19999694824219%):  | Personal Data (97.19999694824219%): Communications data. | Personal Data (85.4000015258789%): Communication type (phone or text message) Content (including recordings of phone calls solely when users are notified of the recording in advance) Date and time 3. | Personal Data (94.69999694824219%): Communication type (phone or text message) Content (including recordings of phone calls solely when users are notified of the recording in advance) Date and time 3. | Personal Data (82.4000015258789%):  | Personal Data (98.69999694824219%): Service providers who help us verify your identity or detect fraud.* Confirmation of whether your account information relates to known persons Name and contact information Information relating to the wireless carrier associated with your phone number Information from government-issued identification documents such as driver’s licenses or passports (such as identification numbers, expiration date, date of birth, and gender) d. | Personal Data (80.0%): Communication type (phone or text message) Content (including recordings of phone calls solely when users are notified of the recording in advance) Date and time 3. | Personal Data (94.0%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Personal Data (76.0%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Personal Data (80.5%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Personal Data (91.5%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Personal Data (97.5%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Personal Data (87.0999984741211%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Personal Data (98.5%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Personal Data (97.19999694824219%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Personal Data (98.9000015258789%):  | Personal Data (85.80000305175781%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Personal Data (99.0999984741211%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Personal Data (89.30000305175781%): If you request a ride, we track your driver’s location during your trip, and link that data to your account. | Non-Personal Data (74.0999984741211%): Our algorithms then evaluate various factors to determine the best match, including your location, requested destination, the proximity and availability of drivers or delivery people, traffic conditions, and historical data (including, in some markets, whether the specific Rider and driver have previously reported having negative experiences with each other). | Personal Data (98.80000305175781%): Our algorithms then evaluate various factors to determine the best match, including your location, requested destination, the proximity and availability of drivers or delivery people, traffic conditions, and historical data (including, in some markets, whether the specific Rider and driver have previously reported having negative experiences with each other). | Personal Data (99.0999984741211%): See “Choice and transparency” section below for information on how to control whether Uber may collect your precise location data. | Personal Data (86.69999694824219%): To do this, Uber performs real-time monitoring of information collected from or generated by users, including location data, payment information, and Uber usage. | Personal Data (75.30000305175781%): To do this, Uber performs real-time monitoring of information collected from or generated by users, including location data, payment information, and Uber usage. | Personal Data (98.5%): In addition, if you create an account using an email address affiliated with an Uber for Business account owner (i.e., your employer), we may share your account data (such as name and email address) with such account owner, to help you expense trips or orders to that Uber for Business account.* We may also share information with that account owner about issues involving your trip, such as safety incidents or complaints. | Personal Data (83.80000305175781%):  | Personal Data (77.5%):  | Personal Data (98.5999984741211%): If you add a restaurant or merchant loyalty membership number to your user account, we share that data with the restaurant/merchant when you place an order with them. | Personal Data (91.4000015258789%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Personal Data (83.5%): We share data including advertising or device identifier, hashed email address, approximate location, current trip or order information, and ad interaction data with these intermediaries to enable their services and for such other purposes as are disclosed in their privacy notices. | Personal Data (92.19999694824219%): We share data including advertising or device identifier, hashed email address, approximate location, current trip or order information, and ad interaction data with these intermediaries to enable their services and for such other purposes as are disclosed in their privacy notices. | Personal Data (75.30000305175781%): Privacy settings You can set or update your preferences regarding location data collection and sharing, emergency data sharing, and notifications in Uber’s Privacy Center, which is accessible via the Privacy menu in the Uber apps. | Personal Data (73.0999984741211%):  | Personal Data (94.5999984741211%): Gender identityDown Small You can update your gender information through the Account &gt; Settings &gt; Privacy &gt; Ads and Data &gt; Gender Identity menu in Uber’s apps. | Personal Data (90.69999694824219%): Address Email First and last name Login name and password Phone number Payment method (including related payment verification information) Profile picture Settings (including accessibility settings) and preferences Uber partner loyalty program information b. | Personal Data (98.5%): Service providers who help us verify your identity or detect fraud.* Confirmation of whether your account information relates to known persons Name and contact information Information relating to the wireless carrier associated with your phone number Information from government-issued identification documents such as driver’s licenses or passports (such as identification numbers, expiration date, date of birth, and gender) d. | Personal Data (73.4000015258789%): If you do, we will share data including your name and phone number; approximate location at the time the emergency call was placed; the car’s make, model, color, and license plate information; pickup and dropoff locations; and your driver’s name. | Non-Personal Data (74.4000015258789%):  | Personal Data (76.19999694824219%):  | Personal Data (84.5999984741211%):  | Personal Data (89.0999984741211%):  | Personal Data (78.9000015258789%): Data sharing and trackingDown Small You can choose here whether Uber may share your data with third parties, or collect data regarding your visits and actions on third-party apps or websites, for purposes of personalized ads. | Personal Data (80.80000305175781%): Data sharing and trackingDown Small You can choose here whether Uber may share your data with third parties, or collect data regarding your visits and actions on third-party apps or websites, for purposes of personalized ads. | Personal Data (70.30000305175781%): Regardless of your location, you can access your data, including your profile data and trip or order history, through the Uber apps or website. | Personal Data (95.30000305175781%): Payment information (including amount charged and payment method) Proof of delivery (including photo or signature) Special instructions, allergies or food preferences Statistics derived from past trip/order information, such as  Averages Cancellation rates Total trips/orders Trip or order details, including Date and time Requested pickup and dropoff addresses Distance traveled Restaurant or merchant name and location Items ordered c. | Personal Data (96.30000305175781%): Changing or updating dataDown Small You can edit your name, phone number, email address, payment method, and profile picture through the Settings menu in Uber’s apps. | Personal Data (77.80000305175781%): If you request a ride, we track your driver’s location during your trip, and link that data to your account. | Personal Data (96.9000015258789%): Legal framework for data transfers Uber operates, and processes user data, globally.</t>
+  </si>
+  <si>
+    <t>Personal Data (99.5999984741211%): This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. | Personal Data (83.19999694824219%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (86.5999984741211%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (86.80000305175781%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (87.0999984741211%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (84.30000305175781%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (87.19999694824219%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (80.19999694824219%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (73.0999984741211%):  | Personal Data (78.30000305175781%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (97.69999694824219%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (93.9000015258789%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (96.19999694824219%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (99.0999984741211%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (87.80000305175781%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (76.5999984741211%):  | Personal Data (95.5%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (94.69999694824219%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (91.5999984741211%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (73.9000015258789%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (97.19999694824219%): | Boomplay Music Get APPGet APP What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player What’s Boomplay For Artists Advertising News Contact Go Web Player Privacy Policy EFFECTIVE AS OF OCTOBER 26, 2020 Welcome to Boomplay. | Personal Data (72.9000015258789%):  | Non-Personal Data (87.5%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Non-Personal Data (74.0999984741211%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Non-Personal Data (84.19999694824219%):  | Non-Personal Data (98.0%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Non-Personal Data (96.0999984741211%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Non-Personal Data (90.5999984741211%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Non-Personal Data (87.19999694824219%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Non-Personal Data (88.0999984741211%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Non-Personal Data (88.69999694824219%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Non-Personal Data (84.5%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (97.69999694824219%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (88.69999694824219%):  | Personal Data (96.80000305175781%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (98.19999694824219%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (81.4000015258789%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (72.80000305175781%): your comments on Boomplay or any other content that you Posted on or through the Services, views and interactions on Boomplay. | Personal Data (94.5999984741211%): In addition, we link your contact or subscriber information with your activity on Boomplay across all your devices using your email or social media log-in details, engagement (including without limitation likes, shares, comments, repeated views) and relate users based on your behavior. | Personal Data (82.5999984741211%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Personal Data (87.0%):  | Personal Data (88.9000015258789%): • Location data  We may collect and process information about your location, including location information based on your SIM card, IP address or mobile device location settings, and if activated on your mobile device, by use of a Global Positioning System (GPS). | Personal Data (71.69999694824219%): • Location data  We may collect and process information about your location, including location information based on your SIM card, IP address or mobile device location settings, and if activated on your mobile device, by use of a Global Positioning System (GPS). | Personal Data (76.30000305175781%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (86.80000305175781%): When you Post content, including images, text and audio to Boomplay, you automatically upload certain metadata that is connected to the content. | Personal Data (78.19999694824219%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Personal Data (77.69999694824219%): It further includes information such as your account name that enables other users to trace back the content to your user account. | Non-Personal Data (88.80000305175781%): Information you share with us will remain publicly-available for so long as you or a user that has shared such information retains it. | Non-Personal Data (80.19999694824219%):  | Non-Personal Data (72.5999984741211%):  | Non-Personal Data (75.69999694824219%):  | Personal Data (88.0999984741211%): • Contact Information. | Personal Data (99.4000015258789%): We may collect contact information from your contact list, address book and your social network to help you and others find people you may know and enable you to link your Boomplay contact list with the contact lists on your device and/or in your account on third party services. | Personal Data (81.30000305175781%): We may collect contact information from your contact list, address book and your social network to help you and others find people you may know and enable you to link your Boomplay contact list with the contact lists on your device and/or in your account on third party services. | Personal Data (78.0999984741211%): We may collect contact information from your contact list, address book and your social network to help you and others find people you may know and enable you to link your Boomplay contact list with the contact lists on your device and/or in your account on third party services. | Personal Data (79.5%): We may collect contact information from your contact list, address book and your social network to help you and others find people you may know and enable you to link your Boomplay contact list with the contact lists on your device and/or in your account on third party services. | Personal Data (92.0999984741211%): If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list. | Personal Data (99.5%): If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list. | Personal Data (97.9000015258789%): If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list. | Personal Data (97.5999984741211%): If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list. | Personal Data (95.80000305175781%): If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list. | Personal Data (73.5%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Personal Data (94.19999694824219%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Personal Data (90.4000015258789%): Wi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Data (90.0999984741211%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Personal Data (99.5999984741211%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Non-Personal Data (70.4000015258789%):  | Non-Personal Data (72.9000015258789%): To use less information that’s connected to individual users, in some cases we de-identify or aggregate information or anonymize it so that it no longer identifies you. | Personal Data (98.0%): Learn more To communicate with you We communicate with you using information you've given us, like contact information you've entered on your profile. | Personal Data (77.80000305175781%): If you do, these integrated partners receive information about you and your activity. | Personal Data (86.5%): How do we use your information? | Non-Personal Data (77.69999694824219%): Privacy notice for United States residents How to contact Meta with questions Why and how we process your information Other policies and articles Settings Privacy Policy What is the Privacy Policy and what does it cover? | Personal Data (92.80000305175781%): For example, messages sent using Messenger’s vanish mode are retained for less time than regular messages. | Personal Data (83.9000015258789%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings (like GPS location) Location-related information Information about the network you connect your device to Reports about our products’ performance on your device Information from cookies and similar technologies Information from partners, vendors and third parties Providing ads on the Meta Company Products: Our ads system automatically processes information that we’ve collected and stored associated with you. | Personal Data (73.80000305175781%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings (like GPS location) Location-related information Information about the network you connect your device to Reports about our products’ performance on your device Information from cookies and similar technologies Information from partners, vendors and third parties Providing ads on the Meta Company Products: Our ads system automatically processes information that we’ve collected and stored associated with you. | Personal Data (97.4000015258789%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings (like GPS location) Location-related information Information about the network you connect your device to Reports about our products’ performance on your device Information from cookies and similar technologies Information from partners, vendors and third parties Providing ads on the Meta Company Products: Our ads system automatically processes information that we’ve collected and stored associated with you. | Personal Data (95.4000015258789%): Your activity and information you provide Friends, followers and other connections App, browser and device information Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to: Create and maintain your account and profile, Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information, Facilitate the sharing of content and status, Provide and curate features, Provide messaging services, the ability to make voice and video calls and connect with others, Provide advertising products, Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide, Undertake analytics, and Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences. | Personal Data (71.0%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Personal Data (98.0999984741211%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Personal Data (98.0%):  | Personal Data (95.9000015258789%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Personal Data (82.19999694824219%):  | Personal Data (71.5999984741211%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Personal Data (84.0%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Personal Data (90.5%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Personal Data (91.69999694824219%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Personal Data (71.19999694824219%):  | Personal Data (76.4000015258789%): Your activity and information you provide:: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties To communicate with you: We use information you’ve given us (like contact information on your profile) to send you a communication, like an e-mail or in-product notice, for example: We’ll contact you via email or in-product notifications in relation to the Meta Products, product-related issues, research or to let you know about our terms and policies. | Personal Data (74.80000305175781%):  | Personal Data (80.0999984741211%): Privacy notice for United States residents How to contact Meta with questions Why and how we process your information Other policies and articles Settings Privacy Policy What is the Privacy Policy and what does it cover? | Personal Data (78.30000305175781%): We also use contact information like your email address to respond when you contact us. | Personal Data (94.0%): Your activity and information you provide: Contact information on your profile and your communications with us Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies. | Personal Data (91.0999984741211%): Your activity and information you provide: Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. | Personal Data (94.19999694824219%): Your activity and information you provide: Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. | Personal Data (93.69999694824219%): Your activity and information you provide: Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. | Personal Data (82.5%): In some cases, the decisions we make about violations are reviewed by the Oversight Board, Investigate suspicious activity, Detect, prevent and combat harmful or unlawful behavior, such as to review and, in some cases, remove content reported to us, Identify and combat disparities and racial bias against historically marginalized communities, Protect the life, physical or mental health, well-being or integrity of our users or others, Detect and prevent spam, other security matters and other bad experiences, Detect and stop threats to our personnel and property, and Maintain the integrity of our Products. | Personal Data (90.9000015258789%): Your activity and information you provide: Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. | Personal Data (72.4000015258789%): Your activity and information you provide: Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. | Personal Data (86.0999984741211%): Your activity and information you provide: Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. | Personal Data (72.5%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Personal Data (98.0999984741211%): We also use contact information like your email address to respond when you contact us. | Personal Data (85.4000015258789%): How do we use your information? | Personal Data (74.0999984741211%): Learn more To communicate with you We communicate with you using information you've given us, like contact information you've entered on your profile. | Personal Data (80.69999694824219%):  | Personal Data (82.9000015258789%): What information do we collect? | Personal Data (95.5999984741211%): For example, responses to legal requests where not compelled by law will typically include limited information (such as contact details and login information). | Personal Data (90.5999984741211%): We share information we collect, infrastructure, systems and technology with the other Meta Companies. | Personal Data (95.9000015258789%):  | Personal Data (93.4000015258789%): </t>
+  </si>
+  <si>
+    <t>Personal Data (99.19999694824219%): WhatsApp LLC is also the data controller for any processing of personal information about you and you can contact us using the details in the section Contact Us below. | Personal Data (99.0%): This WhatsApp Business App Privacy Policy (“Business App Privacy Policy”) explains WhatsApp’s data practices with respect to the Business Functions, and applies only to the extent information relating to users of the WhatsApp Business App would be considered personal data and is processed by WhatsApp as a controller, each under applicable law. | Personal Data (96.69999694824219%): In addition to your phone number, you must provide basic information about your business to create a WhatsApp business account, including your business name and business category. | Personal Data (97.5999984741211%): In addition to your phone number, you must provide basic information about your business to create a WhatsApp business account, including your business name and business category. | Personal Data (74.19999694824219%): In addition to your phone number, you must provide basic information about your business to create a WhatsApp business account, including your business name and business category. | Personal Data (82.80000305175781%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (88.69999694824219%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (97.30000305175781%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (73.19999694824219%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (86.19999694824219%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (85.9000015258789%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (85.4000015258789%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (91.0999984741211%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (75.4000015258789%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (95.19999694824219%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Non-Personal Data (80.5999984741211%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (84.69999694824219%):  | Non-Personal Data (88.5%): For example, we collect information about your business profile settings; how you use Business Functions like catalogs, labels and quick replies; purchases and transactions with your business; and metrics related to how customers interact with your business. | Non-Personal Data (84.4000015258789%):  | Personal Data (95.0%): Business profile information is publicly available, including your business name, phone number, hours of operation, business category, address, email address, website(s), description, and Facebook and Instagram accounts (if added). | Non-Personal Data (81.5999984741211%): Business profile information is publicly available, including your business name, phone number, hours of operation, business category, address, email address, website(s), description, and Facebook and Instagram accounts (if added). | Non-Personal Data (96.5%): In addition to your phone number, you must provide basic information about your business to create a WhatsApp business account, including your business name and business category. | Personal Data (98.19999694824219%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (96.30000305175781%): Business profile information is publicly available, including your business name, phone number, hours of operation, business category, address, email address, website(s), description, and Facebook and Instagram accounts (if added). | Non-Personal Data (94.69999694824219%):  | Non-Personal Data (80.0%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Personal Data (89.5999984741211%): We also use your information to respond to you when you contact us.</t>
+  </si>
+  <si>
+    <t>Personal Data (94.80000305175781%): For example, you must provide your mobile phone number to create an account to use our Services. | Personal Data (90.80000305175781%): For example, you cannot share your location with your contacts if you do not permit us to collect your location data from your device. | Personal Data (81.0999984741211%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Personal Data (85.4000015258789%): For example, you cannot share your location with your contacts if you do not permit us to collect your location data from your device. | Personal Data (79.30000305175781%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Personal Data (77.19999694824219%):  | Personal Data (74.4000015258789%):  | Personal Data (70.0999984741211%): You must provide your mobile phone number and basic information (including a profile name of your choice) to create a WhatsApp account. | Personal Data (89.0999984741211%): You can add other information to your account, such as a profile picture and "about" information. | Non-Personal Data (85.5999984741211%): When a user forwards media within a message, we store that media temporarily in encrypted form on our servers to aid in more efficient delivery of additional forwards. | Personal Data (89.5999984741211%): You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. | Personal Data (86.5999984741211%): If you use our payments services, or use our Services meant for purchases or other financial transactions, we process additional information about you, including payment account and transaction information. | Personal Data (77.9000015258789%):  | Personal Data (94.0%): When you contact us for customer support or otherwise communicate with us, you may provide us with information related to your use of our Services, including copies of your messages, any other information you deem helpful, and how to contact you (e.g., an email address). | Personal Data (86.4000015258789%): When you contact us for customer support or otherwise communicate with us, you may provide us with information related to your use of our Services, including copies of your messages, any other information you deem helpful, and how to contact you (e.g., an email address). | Non-Personal Data (86.4000015258789%): For example, you may send us an email with information relating to app performance or other issues. | Non-Personal Data (90.19999694824219%):  | Non-Personal Data (85.5999984741211%): We collect information about your activity on our Services, like service-related, diagnostic, and performance information. | Non-Personal Data (85.5999984741211%): This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. | Non-Personal Data (70.69999694824219%): This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. | Non-Personal Data (89.5%): This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. | Non-Personal Data (85.5999984741211%): This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. | Non-Personal Data (89.19999694824219%): This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. | Non-Personal Data (86.5%): This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. | Non-Personal Data (77.9000015258789%): This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information. | Personal Data (77.9000015258789%): You can add other information to your account, such as a profile picture and "about" information. | Personal Data (79.80000305175781%): This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information. | Non-Personal Data (79.69999694824219%): This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information. | Non-Personal Data (71.19999694824219%): This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information. | Non-Personal Data (88.5%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (86.5%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (84.5999984741211%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (85.0%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (86.5%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (88.19999694824219%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (88.0%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (86.80000305175781%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Personal Data (98.0%): For example, you must provide your mobile phone number to create an account to use our Services. | Non-Personal Data (73.0999984741211%): Express yourselfSay it with stickers, voice, GIFs and more. | Non-Personal Data (84.5%):  | Personal Data (99.0%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (82.80000305175781%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Personal Data (89.19999694824219%): Share your everydayShare photos, videos, voice notes on Status. | Personal Data (82.9000015258789%):  | Personal Data (77.19999694824219%):  | Personal Data (90.4000015258789%):  | Personal Data (99.0%): We collect and use precise location information from your device with your permission when you choose to use location-related features, like when you decide to share your location with your contacts or view locations nearby or locations others have shared with you. | Personal Data (99.69999694824219%): Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). | Personal Data (99.0999984741211%): Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). | Personal Data (71.5999984741211%): Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). | Personal Data (98.0999984741211%): We collect and use precise location information from your device with your permission when you choose to use location-related features, like when you decide to share your location with your contacts or view locations nearby or locations others have shared with you. | Personal Data (98.80000305175781%): You must provide your mobile phone number and basic information (including a profile name of your choice) to create a WhatsApp account. | Personal Data (91.30000305175781%): It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services. | Personal Data (72.4000015258789%): You should keep in mind that in general any user can capture screenshots of your chats or messages or make recordings of your calls with them and send them to WhatsApp or anyone else, or post them on another platform. | Personal Data (78.4000015258789%):  | Personal Data (89.5999984741211%):  | Personal Data (73.80000305175781%): For example, you may receive flight status information for upcoming travel, a receipt for something you purchased, or a notification when a delivery will be made. | Personal Data (96.30000305175781%): You must provide your mobile phone number and basic information (including a profile name of your choice) to create a WhatsApp account. | Personal Data (98.0%): Your phone number, profile name and photo, "about" information, last seen information, and message receipts are available to anyone who uses our Services, although you can configure your Services settings to manage certain information available to other users, including businesses, with whom you communicate. | Personal Data (98.5999984741211%): Your phone number, profile name and photo, "about" information, last seen information, and message receipts are available to anyone who uses our Services, although you can configure your Services settings to manage certain information available to other users, including businesses, with whom you communicate. | Non-Personal Data (97.5%): We offer specific services to businesses such as providing them with metrics regarding their use of our Services. | Personal Data (74.4000015258789%):  | Personal Data (89.5999984741211%): For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information. | Personal Data (93.30000305175781%): Changing Your Mobile Phone Number, Profile Name And Picture, And “About” Information. | Personal Data (96.19999694824219%): Changing Your Mobile Phone Number, Profile Name And Picture, And “About” Information. | Personal Data (93.9000015258789%): Changing Your Mobile Phone Number, Profile Name And Picture, And “About” Information. | Personal Data (84.0%): If you use our Services with such third-party services or Meta Company Products, we may receive information about you from them; for example, if you use the WhatsApp share button on a news service to share a news article with your WhatsApp contacts, groups, or broadcast lists on our Services, or if you choose to access our Services through a mobile carrier’s or device provider’s promotion of our Services. | Personal Data (91.5%): If you change your mobile phone number, you must update it using our in-app change number feature and transfer your account to your new mobile phone number. | Personal Data (83.4000015258789%): You can also change your profile name, profile picture, and "about" information at any time. | Personal Data (85.5%): You can also change your profile name, profile picture, and "about" information at any time. | Personal Data (72.19999694824219%):  | Personal Data (84.5999984741211%): You can create, join, or get added to groups and broadcast lists, and such groups and lists get associated with your account information. | Personal Data (96.80000305175781%): This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information. | Personal Data (94.4000015258789%): Deleting your account will, for example, delete your account info and profile photo, delete you from all WhatsApp groups, and delete your WhatsApp message history. | Personal Data (91.69999694824219%): Please remember that when you delete your account, it does not affect your information related to the groups you created or the information other users have relating to you, such as their copy of the messages you sent them. | Personal Data (86.4000015258789%): Please remember that when you delete your account, it does not affect your information related to the groups you created or the information other users have relating to you, such as their copy of the messages you sent them. | Personal Data (86.30000305175781%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls.</t>
+  </si>
+  <si>
+    <t>Personal Data (99.5999984741211%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (97.5%): We are responsible for processing personal data in accordance with the General Data Protection Regulation (âGDPRâ), an EU wide Regulation for the protection of personal data. | Personal Data (99.69999694824219%): This Privacy Policy (the âPolicyâ) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the âSitesâ) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the âServiceâ). | Personal Data (99.4000015258789%): If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. | Personal Data (99.30000305175781%): If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. | Personal Data (99.4000015258789%): If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. | Personal Data (99.0%): If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. | Personal Data (82.5%): Facebook third party account login If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. | Personal Data (84.19999694824219%):  | Non-Personal Data (90.80000305175781%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Non-Personal Data (93.0999984741211%):  | Non-Personal Data (95.0999984741211%):  | Personal Data (88.80000305175781%): Basic profile information (avatar, Facebook name, country) will be displayed to other users during game play and on public leader-boards. | Personal Data (90.0%): Basic profile information (avatar, Facebook name, country) will be displayed to other users during game play and on public leader-boards. | Personal Data (86.19999694824219%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (99.5%): You are not required to provide personally identifiable information to visit the Site; however, in order to take advantage of certain features you may need to provide some personally identifiable information. | Personal Data (96.5999984741211%): You are not required to provide personally identifiable information to visit the Site; however, in order to take advantage of certain features you may need to provide some personally identifiable information. | Personal Data (79.4000015258789%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (95.4000015258789%): Contact us Contact Information Giraffe Games Limited, 26 Upper Pembroke Street, Dublin 2 If you have any questions about this Policy, please contact us at contact@giraffe-games.com The Privacy Policy, together with any game license agreement are to be read as a whole and form an integral part of the Terms of Use. | Personal Data (98.80000305175781%):  | Personal Data (95.4000015258789%):  | Personal Data (99.0999984741211%): In order to access your third party message accounts, you must enter your applicable user name(s) and password(s). | Personal Data (91.9000015258789%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (89.80000305175781%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (62.0%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Non-Personal Data (60.400001525878906%):  | Non-Personal Data (60.79999923706055%):  | Personal Data (88.5%): Giraffe may collect usage data and other information on all users, including data about their usage of the site and its various features, but it is not personally identifiable except as described below under the IP Addresses section. | Personal Data (61.29999923706055%): This Privacy Policy (the âPolicyâ) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the âSitesâ) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the âServiceâ). | Personal Data (74.19999694824219%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Non-Personal Data (62.099998474121094%): Contact us Contact Information Giraffe Games Limited, 26 Upper Pembroke Street, Dublin 2 If you have any questions about this Policy, please contact us at contact@giraffe-games.com The Privacy Policy, together with any game license agreement are to be read as a whole and form an integral part of the Terms of Use. | Non-Personal Data (74.69999694824219%): Giraffe may collect usage data and other information on all users, including data about their usage of the site and its various features, but it is not personally identifiable except as described below under the IP Addresses section. | Personal Data (64.5%): You are not required to provide personally identifiable information to visit the Site; however, in order to take advantage of certain features you may need to provide some personally identifiable information. | Non-Personal Data (93.80000305175781%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Personal Data (99.0%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Non-Personal Data (80.19999694824219%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Non-Personal Data (94.5999984741211%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Non-Personal Data (65.30000305175781%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Non-Personal Data (66.0%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Personal Data (82.0%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Personal Data (89.9000015258789%): If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. | Personal Data (90.30000305175781%): Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. | Non-Personal Data (77.5999984741211%):  | Personal Data (73.0999984741211%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (90.0999984741211%): Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. | Personal Data (90.69999694824219%): Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. | Personal Data (80.69999694824219%): Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. | Personal Data (93.80000305175781%): Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. | Personal Data (99.5%): If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. | Personal Data (96.5%): Please note that your email address and the access token are encrypted. | Personal Data (94.80000305175781%): iOS, Android and Windows Phone Platforms When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address). | Non-Personal Data (70.4000015258789%): iOS, Android and Windows Phone Platforms When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address). | Personal Data (69.5999984741211%): iOS, Android and Windows Phone Platforms When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address). | Non-Personal Data (87.0999984741211%): iOS, Android and Windows Phone Platforms When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address). | Personal Data (87.69999694824219%): iOS, Android and Windows Phone Platforms When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address). | Personal Data (98.69999694824219%): Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. | Personal Data (97.0%): We may collect and process your location data to provide location related Services and advertisements. | Personal Data (68.5%): We may use various technologies to determine location, such as GPS, Wi-Fi or other network-based data such as IP address. | Personal Data (74.4000015258789%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (68.9000015258789%):  | Personal Data (98.80000305175781%): We may use various technologies to determine location, such as GPS, Wi-Fi or other network-based data such as IP address. | Personal Data (97.80000305175781%): Your GPS geo-location is not accessed without your consent. | Personal Data (91.5%):  | Personal Data (96.4000015258789%): Please note that we may share your anonymous location data with partners in order to improve the Services. | Personal Data (97.30000305175781%): iOS, Android and Windows Phone Platforms When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address). | Personal Data (98.19999694824219%): In addition, we create a unique user ID to track your use of our Service. | Personal Data (88.69999694824219%): Basic profile information (avatar, Facebook name, country) will be displayed to other users during game play and on public leader-boards. | Personal Data (70.69999694824219%): These services will authenticate your identity and provide you the option to share certain personal information with us such as your name, email address, and resume to pre-populate our sign up form. | Personal Data (98.0%): Contact us Contact Information Giraffe Games Limited, 26 Upper Pembroke Street, Dublin 2 If you have any questions about this Policy, please contact us at contact@giraffe-games.com The Privacy Policy, together with any game license agreement are to be read as a whole and form an integral part of the Terms of Use. | Personal Data (99.5999984741211%): Such contact information will be used only for the purpose of sending communications to the addressee. | Non-Personal Data (92.5999984741211%): Game Data Collection Whenever you play our games, we collect anonymous data using the service of http://www.gameanalytics.com and sometimes use http://www.flurry.com/solutions/analytics(or such other service providers as we may deem appropriate). | Non-Personal Data (93.4000015258789%): The data thereby collected is presented to us in an anonymous form to include, for example, the percentage of users who complete a particular level. | Personal Data (91.4000015258789%): The requested information typically includes contact information (such as name and shipping address), and demographic information (such as zip code). | Personal Data (99.30000305175781%): The requested information typically includes contact information (such as name and shipping address), and demographic information (such as zip code). | Personal Data (76.30000305175781%): The requested information typically includes contact information (such as name and shipping address), and demographic information (such as zip code). | Personal Data (81.4000015258789%):  | Personal Data (97.69999694824219%): In order to access your third party message accounts, you must enter your applicable user name(s) and password(s). | Personal Data (97.0%): Cookies A cookie is a small text file that we transfer to your computer and/or device, to identify a userâs computer/device and to ârememberâ things about your visit, such as your preferences or a user name and password. | Personal Data (94.5999984741211%): We may associate this information with your IP address or device identifier but do not tie the information gathered by clear gifs to our customersâ personal information. | Personal Data (96.69999694824219%): We may associate this information with your IP address or device identifier but do not tie the information gathered by clear gifs to our customersâ personal information. | Non-Personal Data (85.19999694824219%): This software may record information such as how often you use the application, the events that occur within the application, aggregated usage, performance data, and where the application was downloaded from. | Non-Personal Data (91.4000015258789%): This software may record information such as how often you use the application, the events that occur within the application, aggregated usage, performance data, and where the application was downloaded from. | Non-Personal Data (78.69999694824219%): This software may record information such as how often you use the application, the events that occur within the application, aggregated usage, performance data, and where the application was downloaded from. | Non-Personal Data (92.5%):  | Non-Personal Data (80.9000015258789%): This software may record information such as how often you use the application, the events that occur within the application, aggregated usage, performance data, and where the application was downloaded from. | Non-Personal Data (97.4000015258789%): This software may record information such as how often you use the application, the events that occur within the application, aggregated usage, performance data, and where the application was downloaded from. | Personal Data (82.30000305175781%): The third party may have access to information such as your device identifier, MAC address, IMEI, locale (specific location where a given language is spoken), geo-location information, and IP address for the purpose of providing their services under their respective privacy policies. | Personal Data (70.5%): The third party may have access to information such as your device identifier, MAC address, IMEI, locale (specific location where a given language is spoken), geo-location information, and IP address for the purpose of providing their services under their respective privacy policies. | Personal Data (64.30000305175781%):  | Personal Data (97.4000015258789%): The information we collect when you connect your user account to an SN Service may include: (1) your name, (2) your SN Service user identification number and/or user name, (3) locale, city, state and country, (4) sex, (5) birth date, (6) email address, (7) profile picture or its URL, and (8) the SN Service user identification numbers for your friends that are also connected to Giraffeâs game(s). | Personal Data (80.30000305175781%):  | Personal Data (95.30000305175781%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (89.69999694824219%):  | Non-Personal Data (78.4000015258789%): The advertisers may collect and use information about you, such as your Service session activity, device identifier, MAC address, IMEI, geo-location information and IP address. | Personal Data (80.0%): The third party may have access to information such as your device identifier, MAC address, IMEI, locale (specific location where a given language is spoken), geo-location information, and IP address for the purpose of providing their services under their respective privacy policies. | Non-Personal Data (64.5999984741211%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Personal Data (86.5%):  | Personal Data (63.20000076293945%):  | Non-Personal Data (65.5%): – We may share aggregate or anonymous information about you with advertisers, publishers, business partners, sponsors, and other third parties. | Personal Data (99.30000305175781%): Giraffe Games Limited and its affiliates (âGiraffeâ, âusâ, âourâ or âweâ) are dedicated to protecting the privacy rights of our users (âusersâ or âyouâ). | Personal Data (99.30000305175781%):  | Non-Personal Data (77.0%): Push Notifications We may occasionally send you push notifications through our mobile applications to send you game updates, high scores and other service related notifications that may be of importance to you. | Personal Data (68.9000015258789%): You have many rights in relation to your data under the GDPR, if you would like to exercise one of these rights, please contact us at: contact@giraffe-games.com You have the right to ; Access. | Personal Data (74.30000305175781%): For example, we may use your information to: – create game accounts and allow users to play our games; – identify and suggest connections with other Giraffe users; – operate and improve our Service; – understand you and your preferences to enhance your experience and enjoyment using our Service; – respond to your comments and questions and provide customer service; – provide and deliver products and services you request; – send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages; – communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners; – enable you to communicate with other users; and – link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services.</t>
+  </si>
+  <si>
     <t>Processing (99.69999694824219%): This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. | Processing (98.30000305175781%): This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. | Processing (99.5%): This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. | Processing (99.19999694824219%): This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. | Automated Decision Making (96.30000305175781%): What Information We Collect We may collect information from and about you, including information that you provide, information from other sources, and automatically collected information. | Processing (97.9000015258789%):  | Processing (76.0999984741211%): The Platform is provided and controlled by TikTok Inc. | Processing (91.80000305175781%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Processing (93.69999694824219%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Processing (91.0%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Processing (93.69999694824219%): When you create User Content, we may upload or import it to the Platform before you save or post the User Content (also known as pre-uploading), for example, in order to recommend audio options, generate captions, and provide other personalized recommendations. | Processing (85.80000305175781%): When you create User Content, we may upload or import it to the Platform before you save or post the User Content (also known as pre-uploading), for example, in order to recommend audio options, generate captions, and provide other personalized recommendations. | Required Purpose (92.5%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Required Purpose (79.5%): When you create User Content, we may upload or import it to the Platform before you save or post the User Content (also known as pre-uploading), for example, in order to recommend audio options, generate captions, and provide other personalized recommendations. | Required Purpose (92.19999694824219%): When you create User Content, we may upload or import it to the Platform before you save or post the User Content (also known as pre-uploading), for example, in order to recommend audio options, generate captions, and provide other personalized recommendations. | Required Purpose (98.80000305175781%): When you create User Content, we may upload or import it to the Platform before you save or post the User Content (also known as pre-uploading), for example, in order to recommend audio options, generate captions, and provide other personalized recommendations. | Retention (85.19999694824219%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Retention (97.19999694824219%): Messages, which include information you provide when you compose, send, or receive messages through the Platformâs messaging functionalities. | Technical Measure (92.0%): They include messages you send through our chat functionality when communicating with sellers who sell goods to you, and your use of virtual assistants when purchasing items through the Platform. | Processing (95.30000305175781%): For example, if you choose to initiate information sharing with a third-party platform, or choose to paste content from the clipboard onto the Platform, we access this information stored in your clipboard in order to fulfill your request. | Processing (98.4000015258789%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Processing (98.69999694824219%): For example, if you choose to initiate information sharing with a third-party platform, or choose to paste content from the clipboard onto the Platform, we access this information stored in your clipboard in order to fulfill your request. | Required Purpose (83.30000305175781%): Purchase information, including payment card numbers or other third-party payment information (such as PayPal) where required for the purpose of payment, and billing and shipping address. | Required Purpose (86.5%): We also collect information that is required for extended warranty purposes and your transaction and purchase history on or through the Platform. | Processing (97.19999694824219%): Messages, which include information you provide when you compose, send, or receive messages through the Platformâs messaging functionalities. | Required Purpose (96.30000305175781%): These partners also share information with us, such as mobile identifiers for advertising, hashed email addresses and phone numbers, and cookie identifiers, which we use to help match you and your actions outside of the Platform with your TikTok account. | Required Purpose (97.19999694824219%): Please be aware that messages you choose to send to other users of the Platform will be accessible by those users and that we are not responsible for the manner in which those users use or share the messages. | Required Purpose (75.5%): Information From Other Sources We may receive the information described in this Privacy Policy from other sources, such as: If you choose to sign-up or log-in to the Platform using a third-party service such as Facebook, Twitter, Instagram, or Google, or link your TikTok account to a third-party service, we may collect information from the serviceâfor example, your public profile information (such as nickname), email, and contact list. | Required Purpose (92.80000305175781%):  | Required Purpose (95.30000305175781%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Processing (96.9000015258789%): We may obtain information about you from certain affiliated entities within our corporate group, including about your activities on their platform. | Retention (86.19999694824219%): Automatically Collected Information We automatically collect certain information from you when you use the Platform, including internet or other network activity information such as your IP address, geolocation-related data, unique device identifiers, browsing and search history (including content you have viewed in the Platform), and Cookies. | Technical Measure (98.5%): Automatically Collected Information We automatically collect certain information from you when you use the Platform, including internet or other network activity information such as your IP address, geolocation-related data, unique device identifiers, browsing and search history (including content you have viewed in the Platform), and Cookies. | Technical Measure (97.4000015258789%):  | Required Purpose (71.30000305175781%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Required Purpose (96.9000015258789%): Where you log-in from multiple devices, we will be able to use information such as your device ID and user ID to identify your activity across devices. | Processing (99.0999984741211%): What Information We Collect We may collect information from and about you, including information that you provide, information from other sources, and automatically collected information. | Processing (94.9000015258789%): If you are still using an older version that allowed for collection of precise or approximate GPS information (last release in August 2020) and you granted us permission to do so, we may collect such information. | Required Purpose (99.5999984741211%): We may collect this information to enable special video effects, for content moderation, for demographic classification, for content and ad recommendations, and for other non-personally-identifying operations. | Required Purpose (96.0%):  | Automated Decision Making (83.80000305175781%): When you upload or create User Content, you automatically upload certain metadata that is connected to the User Content. | Required Purpose (79.5%): If you apply an effect to your User Content, we may collect a version of your User Content that does not include the effect. | Technical Measure (98.80000305175781%): We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (âCookiesâ) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. | Technical Measure (83.80000305175781%): We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (âCookiesâ) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. | Technical Measure (96.80000305175781%): We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (âCookiesâ) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. | Technical Measure (97.30000305175781%): We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (âCookiesâ) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. | Technical Measure (71.4000015258789%):  | Technical Measure (75.30000305175781%):  | Required Purpose (93.0%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Required Purpose (97.4000015258789%): We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (âCookiesâ) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. | Required Purpose (99.5%): We and our partners also use Cookies to promote the Platform on other platforms and websites. | Required Purpose (99.30000305175781%): Cookies enable the Platform to provide certain features and functionality. | Technical Measure (94.69999694824219%): Web beacons are very small images or small pieces of data embedded in images, also known as âpixel tagsâ or âclear GIFs,â that can recognize Cookies, the time and date a page is viewed, a description of the page where the pixel tag is placed, and similar information from your computer or device. | Required Purpose (73.0%): Web beacons are very small images or small pieces of data embedded in images, also known as âpixel tagsâ or âclear GIFs,â that can recognize Cookies, the time and date a page is viewed, a description of the page where the pixel tag is placed, and similar information from your computer or device. | Required Purpose (84.19999694824219%): Web beacons are very small images or small pieces of data embedded in images, also known as âpixel tagsâ or âclear GIFs,â that can recognize Cookies, the time and date a page is viewed, a description of the page where the pixel tag is placed, and similar information from your computer or device. | Processing (95.0999984741211%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Required Purpose (98.80000305175781%): We may use this information to display advertisements on our Platform tailored to your interests, preferences, and characteristics. | Processing (90.69999694824219%): We may aggregate or de-identify the information described above. | Required Purpose (99.19999694824219%): How We Use Your Information As explained below, we use your information to improve, support and administer the Platform, to allow you to use its functionalities, and to fulfill and enforce our Terms of Service. | Required Purpose (96.30000305175781%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Required Purpose (98.9000015258789%): We may also use your information to, among other things, show you suggestions, promote the Platform, and customize your ad experience. | Required Purpose (93.5%): We generally use the Information We Collect: To fulfill requests for products, services, Platform functionality, support and information for internal operations, including troubleshooting, data analysis, testing, research, statistical, and survey purposes and to solicit your feedback. | Required Purpose (96.19999694824219%): We generally use the Information We Collect: To fulfill requests for products, services, Platform functionality, support and information for internal operations, including troubleshooting, data analysis, testing, research, statistical, and survey purposes and to solicit your feedback. | Required Purpose (81.5999984741211%): We generally use the Information We Collect: To fulfill requests for products, services, Platform functionality, support and information for internal operations, including troubleshooting, data analysis, testing, research, statistical, and survey purposes and to solicit your feedback. | Required Purpose (92.9000015258789%):  | Required Purpose (87.5%): We generally use the Information We Collect: To fulfill requests for products, services, Platform functionality, support and information for internal operations, including troubleshooting, data analysis, testing, research, statistical, and survey purposes and to solicit your feedback. | Required Purpose (99.5999984741211%): To customize the content you see when you use the Platform. | Required Purpose (97.80000305175781%): To improve and develop our Platform and conduct product development. | Required Purpose (97.9000015258789%): Privacy Policy | TikTok U.S. | Required Purpose (92.4000015258789%): To support the social functions of the Platform, including to permit you and others to connect with each other (for example, through our Find Friends function), to suggest accounts to you and others, and for you and others to share, download, and otherwise interact with User Content posted through the Platform. | Required Purpose (80.9000015258789%): To support the social functions of the Platform, including to permit you and others to connect with each other (for example, through our Find Friends function), to suggest accounts to you and others, and for you and others to share, download, and otherwise interact with User Content posted through the Platform. | Required Purpose (89.5999984741211%): To support the social functions of the Platform, including to permit you and others to connect with each other (for example, through our Find Friends function), to suggest accounts to you and others, and for you and others to share, download, and otherwise interact with User Content posted through the Platform. | Required Purpose (94.5%): To use User Content as part of our advertising and marketing campaigns to promote the Platform. | Required Purpose (96.80000305175781%): To understand how you use the Platform, including across your devices. | Required Purpose (86.9000015258789%): To help us detect abuse, fraud, and illegal activity on the Platform. | Required Purpose (93.0%): To promote the safety and security of the Platform, including by scanning, analyzing, and reviewing User Content, messages and associated metadata for violations of our Terms of Service, Community Guidelines, or other conditions and policies. | Processing (93.5999984741211%): To promote the safety and security of the Platform, including by scanning, analyzing, and reviewing User Content, messages and associated metadata for violations of our Terms of Service, Community Guidelines, or other conditions and policies. | Processing (91.0999984741211%): To promote the safety and security of the Platform, including by scanning, analyzing, and reviewing User Content, messages and associated metadata for violations of our Terms of Service, Community Guidelines, or other conditions and policies. | Required Purpose (97.80000305175781%): To promote the safety and security of the Platform, including by scanning, analyzing, and reviewing User Content, messages and associated metadata for violations of our Terms of Service, Community Guidelines, or other conditions and policies. | Required Purpose (89.80000305175781%): To verify your identity in order to use certain features, such as livestream or verified accounts, or when you apply for a Business Account, to ensure that you are old enough to use the Platform (as required by law), or in other instances where verification may be required. | Required Purpose (90.69999694824219%): To verify your identity in order to use certain features, such as livestream or verified accounts, or when you apply for a Business Account, to ensure that you are old enough to use the Platform (as required by law), or in other instances where verification may be required. | Required Purpose (97.30000305175781%): To verify your identity in order to use certain features, such as livestream or verified accounts, or when you apply for a Business Account, to ensure that you are old enough to use the Platform (as required by law), or in other instances where verification may be required. | Required Purpose (98.5%): Privacy Policy | TikTok U.S. | Required Purpose (85.0%): To communicate with you, including to notify you about changes in our services. | Required Purpose (92.5999984741211%): To communicate with you, including to notify you about changes in our services. | Required Purpose (89.80000305175781%): To announce you as a winner of our contests or promotions if permitted by the promotion rule, and to send you any applicable prizes. | Required Purpose (76.9000015258789%): To announce you as a winner of our contests or promotions if permitted by the promotion rule, and to send you any applicable prizes. | Required Purpose (99.19999694824219%): To enforce our Terms of Service, Community Guidelines, and other conditions and policies. | Required Purpose (84.80000305175781%):  | Required Purpose (78.0%): To train and improve our technology, such as our machine learning models and algorithms. | Processing (77.4000015258789%): To combine all the Information We Collect or receive about you for any of the foregoing purposes. | Processing (94.19999694824219%):  | Required Purpose (96.0999984741211%): To facilitate sales, promotion, and purchases of goods and services and to provide user support. | Required Purpose (97.19999694824219%): To facilitate sales, promotion, and purchases of goods and services and to provide user support. | Processing (76.0999984741211%): What Information We Collect We may collect information from and about you, including information that you provide, information from other sources, and automatically collected information. | Required Purpose (86.5%): How We Share Your Information We are committed to maintaining your trust, and while TikTok does not sell your personal information or share your personal information with third parties for purposes of cross-context behavioral advertising where restricted by applicable law, we want you to understand when and with whom we may share the Information We Collect for business purposes. | Required Purpose (97.80000305175781%): Service Providers and Business Partners We share the categories of personal information listed above with service providers and business partners to help us perform business operations and for business purposes, including research, payment processing and transaction fulfillment, database maintenance, administering contests and special offers, technology services, deliveries, sending communications, advertising and marketing services, analytics, measurement, data storage and hosting, disaster recovery, search engine optimization, and data processing. | Required Purpose (90.30000305175781%): Within Our Corporate Group As a global company, the Platform is supported by certain entities within our corporate group, which are given limited remote access to Information We Collect as necessary to enable them to provide certain important functions. | Processing (99.0999984741211%): For any other purposes disclosed to you at the time we collect your information or pursuant to your consent. | Processing (98.19999694824219%):  | Not Required Purpose (91.0999984741211%): For Legal Reasons We may disclose any of the Information We Collect to respond to subpoenas, court orders, legal process, law enforcement requests, legal claims, or government inquiries, and to protect and defend the rights, interests, safety, and security of the Platform, our affiliates, users, or the public. | Required Purpose (74.69999694824219%): For Legal Reasons We may disclose any of the Information We Collect to respond to subpoenas, court orders, legal process, law enforcement requests, legal claims, or government inquiries, and to protect and defend the rights, interests, safety, and security of the Platform, our affiliates, users, or the public. | Required Purpose (97.0999984741211%): We may also share any of the Information We Collect to enforce any terms applicable to the Platform, to exercise or defend any legal claims, and comply with any applicable law.Â With Your Consent We may share your information for other purposes pursuant to your consent or at your direction. | Required Purpose (97.69999694824219%): We may also share any of the Information We Collect to enforce any terms applicable to the Platform, to exercise or defend any legal claims, and comply with any applicable law.Â With Your Consent We may share your information for other purposes pursuant to your consent or at your direction. | Required Purpose (98.69999694824219%):  | Processing (92.5%): That information includes the content of the message and information about the message, such as when it was sent, received, or read, and message participants. | Processing (75.19999694824219%): If you choose to engage in public activities on the Platform, you should be aware that any information you share may be read, collected, or used by other users. | Processing (99.19999694824219%): These entities may use the information shared in accordance with their privacy policies. | Processing (76.9000015258789%): This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. | Required Purpose (95.80000305175781%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Required Purpose (96.19999694824219%): For example, we may process your financial information in order to provide you the goods or services you request from us or your driverâs license number in order to verify your identity. | Required Purpose (97.80000305175781%): We are committed to protecting and respecting your privacy. | Required Purpose (96.0%):  | Required Purpose (96.69999694824219%): For example, we may process your financial information in order to provide you the goods or services you request from us or your driverâs license number in order to verify your identity. | Required Purpose (76.69999694824219%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Processing (73.0999984741211%): To promote the safety and security of the Platform, including by scanning, analyzing, and reviewing User Content, messages and associated metadata for violations of our Terms of Service, Community Guidelines, or other conditions and policies. | Processing (98.69999694824219%): Some browsers transmit âdo-not-trackâ signals to websites. | Organisational Measure (81.19999694824219%): Data Security and Retention We use reasonable measures to help protect information from loss, theft, misuse, unauthorized access, disclosure, alteration, or destruction. | Processing (95.0999984741211%): You should understand that no data storage system or transmission of data over the Internet or any other public network can be guaranteed to be 100 percent secure. | Processing (95.5%): We retain information for as long as necessary to provide the Platform and for the other purposes set out in this Privacy Policy. | Retention (89.9000015258789%): We retain information for as long as necessary to provide the Platform and for the other purposes set out in this Privacy Policy. | Required Purpose (71.0999984741211%): We retain information for as long as necessary to provide the Platform and for the other purposes set out in this Privacy Policy. | Required Purpose (75.0%): For example, when we process your information such as your profile information to provide you with the Platform, we keep this information for as long as you have an account. | Retention (93.4000015258789%): For example, when we process your information such as your profile information to provide you with the Platform, we keep this information for as long as you have an account. | Processing (85.30000305175781%): For example, when we process your information such as your profile information to provide you with the Platform, we keep this information for as long as you have an account. | Required Purpose (80.0999984741211%): If you violate our Terms of Service, Community Guidelines, or other conditions or policies, we may remove your profile immediately, but may keep other information about you to process the violation. | Required Purpose (99.0999984741211%): If you are a parent or guardian, our Guardian's Guide contains information and resources to help you understand the Platform and the tools and controls you can use. | Processing (81.0%): Privacy Policy Last updated: Aug 19, 2024 This Privacy Policy applies to TikTok services (the âPlatformâ), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. | Processing (90.19999694824219%):  | Processing (88.69999694824219%):  | Processing (74.0999984741211%):  | Organisational Measure (82.4000015258789%): When we update the Privacy Policy, we will notify you by updating the âLast Updatedâ date at the top of the new Privacy Policy, posting the new Privacy Policy, or providing any other notice required by applicable law.</t>
   </si>
   <si>
@@ -889,6 +2677,24 @@
     <t>Processing (99.5999984741211%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Processing (97.9000015258789%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Processing (82.69999694824219%): You control whether your Snaps can be saved within Snapchat.Privacy Through SecurityFeatures and recommendations to help secure your account. | Processing (99.0%): Teens on SnapchatAdditional protections for teens on Snapchat.Snap and AdsHow we collect, use, and share your data with respect to ads. | Required Purpose (98.0%): That’s why we did our best to make our Privacy Policy brief, clear, and easy-to-read!Learn More SafetySafety CenterHere are some steps you can take to help stay safe!Safety PoliciesWe created these safety policies to help our community enhance their relationships with friends, family, and the world.Safety ResourcesWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters in need. | Required Purpose (96.30000305175781%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Required Purpose (76.5999984741211%): That’s why we did our best to make our Privacy Policy brief, clear, and easy-to-read!Learn More SafetySafety CenterHere are some steps you can take to help stay safe!Safety PoliciesWe created these safety policies to help our community enhance their relationships with friends, family, and the world.Safety ResourcesWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters in need. | Processing (86.0999984741211%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Organisational Measure (86.80000305175781%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Required Purpose (94.80000305175781%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Organisational Measure (72.0%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Processing (98.69999694824219%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Processing (97.19999694824219%):  | Required Purpose (86.5999984741211%): Here we provide additional context and insight into our safety principles, policies, and practices, as well as links to various safety and privacy resources.Learn More News PrivacyPrivacyPrivacy Center Privacy Principles Privacy by Product Privacy Policy Teens on Snapchat Snap and Ads Privacy Through Security Privacy Policy Effective: April 7, 2025 Welcome to Snap Inc.’s Privacy Policy. | Processing (99.4000015258789%): If you’re looking for specific product privacy information, for example, how we process your Chats and Snaps, take a look at our Privacy by Product page. | Required Purpose (84.0999984741211%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Required Purpose (99.80000305175781%): For example, we process your information to provide you a more personalized experience, including to show you content and information that is most relevant to your experience, as well as more relevant advertisements. | Required Purpose (91.0999984741211%): Understanding your interests and preferences help us provide a better product experience. | Organisational Measure (82.0%): You can access, update, and delete your information, decide who can contact you, and download your data from within the Snapchat app. | Organisational Measure (78.5%): You can access, update, and delete your information, decide who can contact you, and download your data from within the Snapchat app. | Processing (79.69999694824219%): You can also delete some information within our Services, like content you’ve saved to Memories, content you’ve shared with My AI, Spotlight submissions, and more. | Organisational Measure (84.0%): Control who can see your content. | Organisational Measure (71.69999694824219%): Control who can contact you. | Organisational Measure (91.0999984741211%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Organisational Measure (94.69999694824219%): Snapchat is intended for close friends and family, that’s why we’ve built controls that help you decide who can contact you. | Organisational Measure (93.9000015258789%): If you receive unwanted communications, you can always block and report that person. | Organisational Measure (79.4000015258789%): Or if you provided access to your phone or third party platform contacts to make friending easier, you can change that later on in your app settings. | Organisational Measure (75.69999694824219%): Or if you provided access to your phone or third party platform contacts to make friending easier, you can change that later on in your app settings. | Required Purpose (78.4000015258789%): Set advertising preferences. | Processing (96.9000015258789%): When you use our Services, such as Snapchat, we collect information you provide to us, generate information when you use our Services, and in some cases receive data from others. | Processing (95.30000305175781%): If you receive unwanted communications, you can always block and report that person. | Processing (97.4000015258789%): That’s why we did our best to make our Privacy Policy brief, clear, and easy-to-read!Learn More SafetySafety CenterHere are some steps you can take to help stay safe!Safety PoliciesWe created these safety policies to help our community enhance their relationships with friends, family, and the world.Safety ResourcesWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters in need. | Required Purpose (77.0%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Required Purpose (81.0%): If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history). | Required Purpose (95.0%): If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history). | Required Purpose (75.0%): If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history). | Processing (95.9000015258789%): You control whether your Snaps can be saved within Snapchat.Privacy Through SecurityFeatures and recommendations to help secure your account. | Required Purpose (98.30000305175781%): This helps us better understand the way our community uses our Services so that we can make improvements. | Required Purpose (99.0%): Content information includes information based on the content of the image, video, or audio — so if you post a Spotlight of a basketball game, we may use that information to show you more content on Spotlight about basketball. | Processing (99.5999984741211%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Technical Measure (98.0999984741211%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Technical Measure (85.30000305175781%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Technical Measure (90.4000015258789%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Technical Measure (90.19999694824219%):  | Technical Measure (86.30000305175781%):  | Required Purpose (76.0%): You control whether your Snaps can be saved within Snapchat.Privacy Through SecurityFeatures and recommendations to help secure your account. | Required Purpose (92.69999694824219%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Processing (98.0999984741211%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Required Purpose (99.80000305175781%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Required Purpose (99.30000305175781%): Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines). | Required Purpose (90.9000015258789%): Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines). | Required Purpose (97.69999694824219%): Among other things, we use the information we collect to provide you with personalized products and Services that we work hard to build and improve. | Required Purpose (89.0%): Keep Things Up &amp; Running (i.e., operate, deliver, and maintain our Services) We use the information we collect in order to operate, deliver, and maintain our Services. | Required Purpose (74.19999694824219%): Previous ReportsTransparency Report archives Regional InformationEuropean UnionEU specific informationCalifornia California specific informationAustralia Australia specific informationIndiaIndia specific information ResourcesResearchersAccess for researchersAds GalleryFind European Union ads that delivered in the last 12 months and commercial content that’s live right now. | Required Purpose (92.4000015258789%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Required Purpose (74.0%): Keep Things Up &amp; Running (i.e., operate, deliver, and maintain our Services) We use the information we collect in order to operate, deliver, and maintain our Services. | Required Purpose (98.9000015258789%): Keep Things Up &amp; Running (i.e., operate, deliver, and maintain our Services) We use the information we collect in order to operate, deliver, and maintain our Services. | Required Purpose (71.4000015258789%): For example, by delivering a Snap you want to send to a friend or, if you share your location on Snap Map, to show you suggestions like places you might like in your neighborhood, content others have posted to the Map, or your friends if they’re sharing their location with you. | Required Purpose (89.69999694824219%): In some cases you may want to share content with your friends, and in other instances you may want to share it with the public. | Required Purpose (70.5999984741211%):  | Required Purpose (99.80000305175781%): For example, by delivering a Snap you want to send to a friend or, if you share your location on Snap Map, to show you suggestions like places you might like in your neighborhood, content others have posted to the Map, or your friends if they’re sharing their location with you. | Required Purpose (74.5999984741211%): Just navigate to your settings and you will see the options available to you. | Required Purpose (95.80000305175781%): We also use some of your information to help keep our products up to date, for example to make sure that our Services work with the latest operating systems and devices. | Required Purpose (96.5999984741211%): We also use some of your information to help keep our products up to date, for example to make sure that our Services work with the latest operating systems and devices. | Required Purpose (93.0%): To do so, we use information about you across different areas of the Services in order to add context to your Snapchat experience. | Required Purpose (84.4000015258789%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Required Purpose (97.5%): Personalize Your Experience &amp; Give Context We offer personalized Services to Snapchatters. | Required Purpose (96.30000305175781%):  | Required Purpose (83.0%): Personalization can also help with suggesting friends or recommending a new friend to send a Snap to based on who you Snap with the most. | Required Purpose (80.69999694824219%):  | Required Purpose (72.0%): Personalization can also help with suggesting friends or recommending a new friend to send a Snap to based on who you Snap with the most. | Required Purpose (96.0999984741211%): We may show recommended places on the Snap Map, generate stickers, or even generate Snaps and other content using AI, infer your interests based on your content or activity, or customize the content we show you, including ads. | Required Purpose (95.69999694824219%):  | Required Purpose (97.5%): Below, we give you more details on the types of settings that are available, link out to our data download tool, and provide instructions on how to delete data or your account. | Required Purpose (84.9000015258789%):  | Required Purpose (76.19999694824219%): Personalization also includes tailoring your experience based on who you interact with most and what your friends are doing, including showing you content your friends create, like, or enjoy on Spotlight or Place recommendations that are popular with your friends. | Required Purpose (79.0999984741211%): Our goal is to continuously provide you with more relevant and interesting content. | Automated Decision Making (93.80000305175781%): For example, we automatically tag content with labels based on the content, your location, or the time of day. | Required Purpose (98.0%): We use your interests and preferences from the information we’ve collected to personalize, target, and measure ads. | Required Purpose (85.0%):  | Processing (82.5%): Teens on SnapchatAdditional protections for teens on Snapchat.Snap and AdsHow we collect, use, and share your data with respect to ads. | Required Purpose (93.4000015258789%): You can learn more about how we collect, use, and share your information for advertising purposes here. | Technical Measure (83.9000015258789%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Required Purpose (98.5%): For example, we may use information collected on an advertiser’s website to show you more relevant ads. | Organisational Measure (94.80000305175781%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Required Purpose (80.9000015258789%): Keep in mind, though, that removing or rejecting cookies could affect the availability and functionality of our Services. | Required Purpose (71.4000015258789%): This Policy covers our Snapchat app as well as our other products, services, and features, such as Bitmoji, Spectacles, and our advertising and commerce initiatives. | Required Purpose (87.4000015258789%): Develop &amp; Improve Features, Algorithms &amp; Machine Learning Models Our teams are constantly coming up with new ideas for features and ways to improve our Services. | Technical Measure (96.30000305175781%): For example, if you watch barista content on Spotlight, talk to My AI about your favorite espresso machine, or save a lot of coffee-related Snaps in your Memories, we may highlight coffee shops on the Snap Map when you visit a new city or show you content about coffee that you may find interesting or relevant. | Processing (90.9000015258789%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Technical Measure (73.5999984741211%): When you use our Services, such as Snapchat, we collect information you provide to us, generate information when you use our Services, and in some cases receive data from others. | Technical Measure (81.69999694824219%):  | Technical Measure (75.4000015258789%): In order to do this, we also develop and improve the algorithms and machine learning models (an expression of an algorithm that combs through significant amounts of data to find patterns or make predictions) that make our features and Services work, including through generative AI features (artificial intelligence capable of generating text, images, or other media, using generative models. | Technical Measure (96.5%): For example, if you watch a lot of sports content, but skip content with hair and makeup tips, our recommendation algorithms will prioritize sports, but not those makeup tips. | Technical Measure (91.5%): In order to do this, we also develop and improve the algorithms and machine learning models (an expression of an algorithm that combs through significant amounts of data to find patterns or make predictions) that make our features and Services work, including through generative AI features (artificial intelligence capable of generating text, images, or other media, using generative models. | Required Purpose (94.5999984741211%):  | Required Purpose (97.9000015258789%): We use algorithms and machine learning models for personalization, advertising, safety and security, fairness and inclusivity, augmented reality, and to prevent abuse or other Terms of Service violations. | Required Purpose (75.19999694824219%): This helps us better understand the way our community uses our Services so that we can make improvements. | Required Purpose (71.0%): Your information can help us decide what kind of improvements we should make, but we are always focused on privacy — and we don’t want to use more of your personal information than necessary to develop our features and models. | Required Purpose (81.5%): Your information can help us decide what kind of improvements we should make, but we are always focused on privacy — and we don’t want to use more of your personal information than necessary to develop our features and models. | Required Purpose (91.80000305175781%): Analytics In order to understand what to build or how to improve our Services, we need to understand trends and demand for our features. | Required Purpose (95.69999694824219%): Analytics In order to understand what to build or how to improve our Services, we need to understand trends and demand for our features. | Processing (94.5%): For example, we monitor metadata and trends about Group Chat use to help decide whether we should change parts of the feature, like the maximum size of a Group. | Required Purpose (79.30000305175781%): Analytics In order to understand what to build or how to improve our Services, we need to understand trends and demand for our features. | Required Purpose (98.9000015258789%): For example, we monitor metadata and trends about Group Chat use to help decide whether we should change parts of the feature, like the maximum size of a Group. | Processing (96.0%): Studying data from Snapchatters can help us see trends in the ways that people use the Services. | Processing (95.69999694824219%):  | Required Purpose (96.0%): Studying data from Snapchatters can help us see trends in the ways that people use the Services. | Required Purpose (96.9000015258789%): This helps inspire us to improve Snapchat on a larger scale. | Required Purpose (93.69999694824219%):  | Processing (96.5%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Required Purpose (99.5%): Based on this information, we will, among other things, create information about our users to help us understand demand. | Required Purpose (98.5999984741211%): Research We conduct research to better understand general consumer interests, trends, and how our Services are used by you and others in our community. | Required Purpose (85.19999694824219%): We perform analytics in order to identify, monitor, and analyze trends and usage. | Required Purpose (78.5%):  | Required Purpose (97.4000015258789%): This information, along with analytics (as we described above), helps us understand more about our community and about how our Services fit into the lives of those in our community. | Technical Measure (83.0%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Technical Measure (86.4000015258789%):  | Processing (86.69999694824219%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Required Purpose (99.30000305175781%): Enhance the Safety &amp; Security of Our Services We use your information to enhance the safety and security of our Services, verify Snapchatter identity, and prevent fraud or other unauthorized or illegal activity. | Technical Measure (83.30000305175781%):  | Required Purpose (93.4000015258789%): For example, we provide two-factor authentication to help protect your account and can send you email or text messages if we notice any suspicious activity. | Required Purpose (74.4000015258789%): For example, we provide two-factor authentication to help protect your account and can send you email or text messages if we notice any suspicious activity. | Required Purpose (72.80000305175781%): For example, we provide two-factor authentication to help protect your account and can send you email or text messages if we notice any suspicious activity. | Processing (92.0%): We also scan URLs sent on Snapchat to see if that webpage is potentially harmful, and can give you a warning about it. | Required Purpose (77.5999984741211%): We also scan URLs sent on Snapchat to see if that webpage is potentially harmful, and can give you a warning about it. | Required Purpose (77.5%): We also scan URLs sent on Snapchat to see if that webpage is potentially harmful, and can give you a warning about it. | Required Purpose (94.19999694824219%): Contacting You Sometimes we’ll get in touch with you to promote new or existing features. | Required Purpose (89.0999984741211%): For example, we may use the Snapchat app, email, SMS, or other messaging platforms to share information about our Services and promotional offers that we think may interest you. | Required Purpose (80.30000305175781%): Other times, we need to communicate with you to provide information, alerts, or to send messages our users ask us to deliver at their request. | Required Purpose (88.30000305175781%): Other times, we need to communicate with you to provide information, alerts, or to send messages our users ask us to deliver at their request. | Required Purpose (78.30000305175781%): This may include sending communications through Snapchat, email, SMS, or other messaging platforms, where permitted, to deliver account sta</t>
   </si>
   <si>
+    <t xml:space="preserve">Processing (99.4000015258789%): This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. | Processing (96.0999984741211%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Processing (99.5%): The types of data processing that such laws require, allow, or prohibit vary globally. | Processing (77.5%): Data collections and uses A. | Processing (98.0%): If you use Uber outside of these regions, your data may be collected and used for the purposes indicated with an asterisk. | Processing (90.4000015258789%): This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. | Automated Decision Making (92.0999984741211%): Quebec, CanadaDown Small You may contact Uber here with questions about Uber’s use of your data for purposes of automated decision making, including regarding the factors considered in connection with such decision, to request correction of any personal data relating to such decisions, and to request review of any such decisions by Uber personnel. | Processing (84.0999984741211%): Legal framework for data transfers D. | Retention (75.5%): We collect data when you create or update your Uber account. | Required Purpose (97.0%): We collect demographic data if necessary to enable certain features. | Required Purpose (97.80000305175781%):  | Processing (87.69999694824219%): We collect or infer your gender to enable Women Rider Preference, and for marketing and advertising. | Processing (90.9000015258789%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Required Purpose (94.0999984741211%): We collect or infer your gender to enable Women Rider Preference, and for marketing and advertising. | Required Purpose (95.4000015258789%): We collect or infer your gender to enable Women Rider Preference, and for marketing and advertising. | Required Purpose (88.30000305175781%): This refers to the data that we collect to verify your account or identity. | Processing (79.5999984741211%):  | Required Purpose (99.0%): Data controllers and Data Protection Officer B. | Required Purpose (89.0999984741211%):  | Processing (95.30000305175781%): If you request a ride, we track your driver’s location during your trip, and link that data to your account. | Processing (86.0999984741211%): If you request a ride, we track your driver’s location during your trip, and link that data to your account. | Required Purpose (70.9000015258789%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Required Purpose (95.19999694824219%): This allows us to display where you are on your trip. | Retention (88.0%): If you do, we will collect your precise location from the time you request a ride or order until the ride is finished or your order is delivered. | Retention (97.4000015258789%): If you do, we will collect your precise location from the time you request a ride or order until the ride is finished or your order is delivered. | Processing (73.80000305175781%): The types of data processing that such laws require, allow, or prohibit vary globally. | Processing (86.9000015258789%): Scope This notice applies when you use Uber’s apps or websites to request or receive products or services, including rides or deliveries. | Processing (95.69999694824219%): The information received from Uber business partners depends on which partners you use to create or access your Uber account, or the API used. | Processing (99.30000305175781%): Data collections and uses A. | Required Purpose (99.80000305175781%): How we use data Uber uses data to enable reliable and convenient transportation, delivery, and other products and services. | Required Purpose (88.5999984741211%): Payment information (including amount charged and payment method) Proof of delivery (including photo or signature) Special instructions, allergies or food preferences Statistics derived from past trip/order information, such as  Averages Cancellation rates Total trips/orders Trip or order details, including Date and time Requested pickup and dropoff addresses Distance traveled Restaurant or merchant name and location Items ordered c. | Required Purpose (97.30000305175781%): We also use data: To enhance the safety and security of our users and services, and to prevent and detect fraud For marketing and advertising To enable communications between users For customer support For research and development To send non-marketing communications to users In connection with legal proceedings 1. | Required Purpose (94.9000015258789%): We also use data: To enhance the safety and security of our users and services, and to prevent and detect fraud For marketing and advertising To enable communications between users For customer support For research and development To send non-marketing communications to users In connection with legal proceedings 1. | Required Purpose (99.0999984741211%): To provide our services. | Required Purpose (99.5%): Uber uses data to provide, personalize, maintain, and improve our services. | Required Purpose (95.0%): Receive services through Uber’s apps or websites requested by other account owners (a “Guest User”), including if you receive ride or delivery services ordered by Uber Health, Central, Uber Direct or Uber for Business customers (collectively, “Enterprise Customers”); or by friends, family members or other individual account owners, including via Uber Connect; or receive a gift card. | Required Purpose (96.4000015258789%):  | Required Purpose (97.69999694824219%):  | Required Purpose (95.5%): This includes: Enabling navigation to pickups and dropoffs, calculating ETAs and tracking the progress of rides or deliveries Matching you with available drivers or delivery people when you request transportation or deliveries Enabling features that involve data sharing, such as ETA sharing and fare splitting Enabling accessibility features Enabling features that involve account linking, such as linking with Uber partners’ loyalty programs Facilitating and optimizing rental car reservations, pickup and dropoff through Uber Rent Account Data from other sources Demographics Device Ratings Travel c. | Required Purpose (99.0%): This includes: Enabling navigation to pickups and dropoffs, calculating ETAs and tracking the progress of rides or deliveries Matching you with available drivers or delivery people when you request transportation or deliveries Enabling features that involve data sharing, such as ETA sharing and fare splitting Enabling accessibility features Enabling features that involve account linking, such as linking with Uber partners’ loyalty programs Facilitating and optimizing rental car reservations, pickup and dropoff through Uber Rent Account Data from other sources Demographics Device Ratings Travel c. | Processing (72.69999694824219%): This includes: Enabling navigation to pickups and dropoffs, calculating ETAs and tracking the progress of rides or deliveries Matching you with available drivers or delivery people when you request transportation or deliveries Enabling features that involve data sharing, such as ETA sharing and fare splitting Enabling accessibility features Enabling features that involve account linking, such as linking with Uber partners’ loyalty programs Facilitating and optimizing rental car reservations, pickup and dropoff through Uber Rent Account Data from other sources Demographics Device Ratings Travel c. | Processing (98.30000305175781%): Data sharing and disclosure F. | Required Purpose (98.0999984741211%): Data sharing and disclosure F. | Required Purpose (98.5%):  | Required Purpose (94.4000015258789%):  | Required Purpose (82.19999694824219%): Processing payments and enabling payment and e-money products such as Uber Money. | Required Purpose (91.30000305175781%):  | Required Purpose (92.80000305175781%):  | Required Purpose (99.30000305175781%): MexicoDown Small Please go here for information regarding Uber’s privacy practices as relates to Mexico’s Personal Data Protection Law (Ley Federal de Protección de Datos Personales en Posesión de los Particulares), and here for information regarding Uber Money's processing of personal data. | Required Purpose (93.30000305175781%):  | Required Purpose (99.19999694824219%):  | Required Purpose (99.5999984741211%):  | Required Purpose (94.9000015258789%): Providing you with trip or delivery updates and generating receipts. | Required Purpose (75.69999694824219%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Required Purpose (74.4000015258789%):  | Required Purpose (90.19999694824219%):  | Required Purpose (97.9000015258789%): For safety, security, and fraud prevention and detection. | Required Purpose (99.69999694824219%): Uber uses data to help maintain the safety and security of our services and users. | Required Purpose (97.0999984741211%): Choice and transparency IV. | Required Purpose (95.9000015258789%):  | Required Purpose (92.0%):  | Required Purpose (76.19999694824219%):  | Processing (85.0%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Processing (75.30000305175781%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Processing (96.0999984741211%):  | Processing (89.9000015258789%):  | Required Purpose (82.0999984741211%):  | Required Purpose (80.5%):  | Processing (97.0%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Required Purpose (73.5999984741211%): Uber Privacy Notice: Drivers and Delivery People Previous version of the Privacy Notice I. | Required Purpose (72.5%):  | Required Purpose (88.0%):  | Required Purpose (91.80000305175781%): Uber uses data (except Guest Users’ data) to market its services, and those of Uber partners. | Required Purpose (85.19999694824219%): Scope This notice applies when you use Uber’s apps or websites to request or receive products or services, including rides or deliveries. | Required Purpose (88.80000305175781%):  | Required Purpose (87.69999694824219%): Request or receive food or other products and services for delivery or pickup, including via your Uber Eats or Postmates account, or through the guest checkout features that allow you to access delivery or pickup services without creating and/or signing into your account (an “Order Recipient”). | Required Purpose (86.80000305175781%):  | Required Purpose (88.69999694824219%): Data uses Data used includes This includes investigating and addressing user concerns, monitoring and improving our customer support responses and processes, and identifying potential participants in research studies relating to customer support issues. | Required Purpose (94.80000305175781%): Data uses Data used includes This includes investigating and addressing user concerns, monitoring and improving our customer support responses and processes, and identifying potential participants in research studies relating to customer support issues. | Required Purpose (96.19999694824219%): Data uses Data used includes This includes investigating and addressing user concerns, monitoring and improving our customer support responses and processes, and identifying potential participants in research studies relating to customer support issues. | Required Purpose (95.0%): Data uses Data used includes This includes investigating and addressing user concerns, monitoring and improving our customer support responses and processes, and identifying potential participants in research studies relating to customer support issues. | Required Purpose (96.5999984741211%): Data uses Data used includes This includes investigating and addressing user concerns, monitoring and improving our customer support responses and processes, and identifying potential participants in research studies relating to customer support issues. | Required Purpose (92.4000015258789%): Data uses Data used includes We use data for analysis, research and product development, including training machine learning models. | Required Purpose (87.0%):  | Required Purpose (79.4000015258789%): Data uses Data used includes We use data to investigate or address claims or disputes relating to use of Uber’s services; to satisfy requirements under applicable laws, regulations, operating licenses or agreements, insurance policies; or pursuant to legal process or governmental request, including from law enforcement. | Required Purpose (75.19999694824219%): Data uses Data used includes We use data to investigate or address claims or disputes relating to use of Uber’s services; to satisfy requirements under applicable laws, regulations, operating licenses or agreements, insurance policies; or pursuant to legal process or governmental request, including from law enforcement. | Automated Decision Making (93.9000015258789%): Core automated processes D. | Required Purpose (93.5%): Core automated processes Uber uses automated processes to enable certain parts of our services, including functions essential to our business such as matching, pricing and fraud prevention and detection. | Required Purpose (91.19999694824219%): Uber relies on automated processes to enable essential parts of our services, including matching (pairing users requesting and providing transportation and/or delivery services), pricing (calculating the amount owed for such services) and fraud detection and prevention. | Technical Measure (96.0999984741211%): MatchingDown Small Uber uses algorithms to efficiently match Riders and drivers, or delivery people and Order Recipients. | Processing (77.5999984741211%): The trip or delivery request is then communicated to the driver/delivery person matched through this process. | Organisational Measure (76.30000305175781%): We are constantly refining our matching process to provide the best experience to all users on our platform and may consider different factors depending on the location where you use Uber. | Organisational Measure (70.80000305175781%): Core automated processes D. | Required Purpose (77.5%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Required Purpose (79.5%): We are constantly refining our matching process to provide the best experience to all users on our platform and may consider different factors depending on the location where you use Uber. | Required Purpose (79.5%): This encourages more drivers to serve the busy area over time and shifts Rider demand, to maintain reliability and restore balance. | Required Purpose (90.80000305175781%): This encourages more drivers to serve the busy area over time and shifts Rider demand, to maintain reliability and restore balance. | Technical Measure (92.19999694824219%): Data uses Data used includes We use data for analysis, research and product development, including training machine learning models. | Required Purpose (96.0999984741211%): Fraud prevention and detectionDown Small Uber uses algorithms and machine learning models to prevent and detect fraud against Uber or our users. | Required Purpose (74.9000015258789%): Fraud prevention and detectionDown Small Uber uses algorithms and machine learning models to prevent and detect fraud against Uber or our users. | Processing (93.4000015258789%): To do this, Uber performs real-time monitoring of information collected from or generated by users, including location data, payment information, and Uber usage. | Processing (87.19999694824219%): We also examine historical data and compare it against real-time data to help detect suspicious behavior. | Required Purpose (95.9000015258789%): We also examine historical data and compare it against real-time data to help detect suspicious behavior. | Technical Measure (98.4000015258789%): Cookies and related technologies Uber and its partners use cookies and other identification technologies on our apps, websites, emails, and online ads for purposes described in this notice, and Uber’s Cookie Notice. | Technical Measure (96.0999984741211%): Cookies and related technologies Uber and its partners use cookies and other identification technologies on our apps, websites, emails, and online ads for purposes described in this notice, and Uber’s Cookie Notice. | Technical Measure (96.5999984741211%): Cookies and related technologies E. | Technical Measure (90.0999984741211%):  | Processing (92.69999694824219%): Cookies are small text files that are stored on browsers or devices by websites, apps, online media, and ads. | Technical Measure (87.9000015258789%): Uber uses cookies and similar technologies for purposes such as: Authenticating users Remembering user preferences and settings Determining the popularity of content Delivering and measuring the effectiveness of advertising campaigns Analyzing site traffic and trends, and generally understanding the online behaviors and interests of people who interact with our services. | Required Purpose (95.69999694824219%): Uber uses cookies and similar technologies for purposes such as: Authenticating users Remembering user preferences and settings Determining the popularity of content Delivering and measuring the effectiveness of advertising campaigns Analyzing site traffic and trends, and generally understanding the online behaviors and interests of people who interact with our services. | Required Purpose (92.5999984741211%):  | Required Purpose (94.69999694824219%):  | Required Purpose (73.9000015258789%): Uber uses cookies and similar technologies for purposes such as: Authenticating users Remembering user preferences and settings Determining the popularity of content Delivering and measuring the effectiveness of advertising campaigns Analyzing site traffic and trends, and generally understanding the online behaviors and interests of people who interact with our services. | Required Purpose (79.69999694824219%): Uber uses cookies and similar technologies for purposes such as: Authenticating users Remembering user preferences and settings Determining the popularity of content Delivering and measuring the effectiveness of advertising campaigns Analyzing site traffic and trends, and generally understanding the online behaviors and interests of people who interact with our services. | Required Purpose (72.5%): We may also allow others to provide audience measurement and analytics services for us, to serve ads on our behalf across the internet or for other companies’ products and services on our apps, and to track and report on the performance of those ads. | Required Purpose (85.0%): Legal information A. | Required Purpose (86.5999984741211%):  | Required Purpose (94.80000305175781%): We may also allow others to provide audience measurement and analytics services for us, to serve ads on our behalf across the internet or for other companies’ products and services on our apps, and to track and report on the performance of those ads. | Technical Measure (96.69999694824219%): These entities may use cookies, web beacons, SDKs and other technologies to identify the devices used by visitors to our websites, as well as when they visit other online sites and services. | Required Purpose (81.69999694824219%): These entities may use cookies, web beacons, SDKs and other technologies to identify the devices used by visitors to our websites, as well as when they visit other online sites and services. | Processing (98.69999694824219%): This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. | Required Purpose (91.5999984741211%): Data sharing and disclosure We share your data with other users where necessary to provide our services or features, at your request, or with your consent. | Required Purpose (90.19999694824219%): In addition, if you create an account using an email address affiliated with an Uber for Business account owner (i.e., your employer), we may share your account data (such as name and email address) with such account owner, to help you expense trips or orders to that Uber for Business account.* We may also share information with that account owner about issues involving your trip, such as safety incidents or complaints. | Required Purpose (92.5999984741211%): We may share your data as necessary to determine their referral bonus Trip/order infoTrip count Other Uber Eats users. | Required Purpose (73.9000015258789%): We share data with companies whose apps or websites you access through Uber, including for purposes of promotions, contests or specialized services. | Required Purpose (78.69999694824219%): If you are involved in an incident, or report or submit a claim to an insurance company relating to Uber’s services, Uber will share data with that insurance company for the purpose of adjusting or handling that claim. | Required Purpose (78.5%): Data necessary to adjust or handle the claim, which may include: Account Communications between users Device Location Trip/order info Usage User content Merchants or restaurants. | Retention (72.0%): If you add a restaurant or merchant loyalty membership number to your user account, we share that data with the restaurant/merchant when you place an order with them. | Required Purpose (98.69999694824219%): Uber uses these vendors to reach or better understand current and potential users of Uber services or of our advertising partners, and measure and improve ad effectiveness. | Required Purpose (93.4000015258789%): Uber uses these vendors to reach or better understand current and potential users of Uber services or of our advertising partners, and measure and improve ad effectiveness. | Technical Measure (73.9000015258789%): Providers of bikes and scooters that can be rented through Uber apps, such as Lime and Tembici. | Technical Measure (73.30000305175781%):  | Technical Measure (75.69999694824219%): Service providers that provide us with artificial intelligence and machine learning tools and services. | Required Purpose (95.4000015258789%): We collect demographic data if necessary to enable certain features. | Required Purpose (87.0%): We share data including advertising or device identifier, hashed email address, approximate location, current trip or order information, and ad interaction data with these intermediaries to enable their services and for such other purposes as are disclosed in their privacy notices. | Required Purpose (84.0999984741211%): To provide our services. | Required Purpose (76.19999694824219%): With Uber subsidiaries and affiliates We share data with our subsidiaries and affiliates to help us provide our services or conduct data processing on our behalf. | Required Purpose (98.5%): This includes sharing data with law enforcement officials, public health officials, other government authorities, insurance companies, or other third parties as necessary to enforce our Terms and Conditions, user agreements, or other policies; to protect Uber’s rights or property or the rights, safety, or property of others; or in the event of a claim or dispute relating to the use of our services. | Required Purpose (99.19999694824219%):  | Required Purpose (83.4000015258789%): This includes sharing data with law enforcement officials, public health officials, other government authorities, insurance companies, or other third parties as necessary to enforce our Terms and Conditions, user agreements, or other policies; to protect Uber’s rights or property or the rights, safety, or property of others; or in the event of a claim or dispute relating to the use of our services. | Retention (87.9000015258789%): Data retention and deletion Uber retains your data for as long as necessary for the purposes described above. | Retention (88.0%): Data retention and deletion Uber retains your data for as long as necessary for the purposes described above. | Retention (97.0%): Uber retains your data for as long as necessary for the purposes described above, which varies depending on data type, the category of user to whom the data relates, the purposes for which we collected the data, and whether the data must be retained after an account deletion request for the purposes described below. | Retention (71.5%): For example, we retain data: For the life of your account if such data is necessary to provide our services (such as account data) For defined periods as necessary, including as necessary to meet tax, insurance, legal or regulatory requirements (for example, we retain transaction information for 7 years) You may request that we delete your account through the Privacy menus in the Uber app, or through Uber’s website (Riders and Order Recipients here; Guest Users here). | Required Purpose (89.0%): Data sharing and disclosure We share your data with other users where necessary to provide our services or features, at your request, or with your consent. | Retention (85.4000015258789%): For example, we retain data: For the life of your account if such data is necessary to provide our services (such as account data) For defined periods as necessary, including as necessary to meet tax, insurance, legal or regulatory requirements (for example, we retain transaction information for 7 years) You may request that we delete your account through the Privacy menus in the Uber app, or through Uber’s website (Riders and Order Recipients here; Guest Users here). | Required Purpose (82.0%): For example, we retain data: For the life of your account if such data is necessary to provide our services (such as account data) For defined periods as necessary, including as necessary to meet tax, insurance, legal or regulatory requirements (for example, we retain transaction information for 7 years) You may request that we delete your account through the Privacy menus in the Uber app, or through Uber’s website (Riders and Order Recipients here; Guest Users here). | Retention (72.9000015258789%): For example: We collect your date of birth and/or age to verify your eligibility to use age-restricted products or services, such as Uber for teens, or if you purchase alcohol, tobacco or cannabis products. | Retention (77.0%): For example, we retain data: For the life of your account if such data is necessary to provide our services (such as account data) For defined periods as necessary, including as necessary to meet tax, insurance, legal or regulatory requirements (for example, we retain transaction information for 7 years) You may request that we delete your account through the Privacy menus in the Uber app, or through Uber’s website (Riders and Order Recipients here; Guest Users here). | Retention (89.0%):  | Retention (88.19999694824219%): Following an account deletion request, we delete your account and data, except as necessary for purposes of safety, security, fraud prevention or compliance with legal requirements, or because of issues relating to your account (such as an outstanding credit or an unresolved claim or dispute). | Retention (70.9000015258789%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Required Purpose (94.30000305175781%): Following an account deletion request, we delete your account and data, except as necessary for purposes of safety, security, fraud prevention or compliance with legal requirements, or because of issues relating to your account (such as an outstanding credit or an unresolved claim or dispute). | Retention (83.9000015258789%): We generally delete data within 90 days of an account deletion request, except where retention is necessary for the above reasons. | Processing (98.69999694824219%): The data we collect Uber collects data: 1. | Processing (96.19999694824219%): Data collections and uses A. | Organisational Measure (80.5999984741211%):  | Organisational Measure (83.69999694824219%):  | Organisational Measure (84.69999694824219%): Share live locationDown Small You can enable/disable Uber’s sharing of your mobile device real-time location data with your drivers or delivery people through your device settings, which are accessible via the Account &gt; Settings &gt; Privacy &gt; Location sharing menu in Uber’s apps. | Processing (92.19999694824219%): Request or receive food or other products and services for delivery or pickup, including via your Uber Eats or Postmates account, or through </t>
+  </si>
+  <si>
+    <t>Processing (89.30000305175781%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Processing (91.30000305175781%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Processing (99.5999984741211%): This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. | Processing (99.4000015258789%): This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. | Processing (97.19999694824219%): The Types of Personal Data We Collect and Use We may collect and use the following information about you: • Information you share with us. | Processing (99.19999694824219%): The Types of Personal Data We Collect and Use We may collect and use the following information about you: • Information you share with us. | Processing (98.4000015258789%): This is the information about you or relating to you that is voluntarily shared by you on Boomplay. | Processing (95.4000015258789%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Processing (97.80000305175781%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Retention (92.19999694824219%): Information you share with us will remain publicly-available for so long as you or a user that has shared such information retains it. | Processing (75.19999694824219%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Processing (99.0999984741211%): For further information as to how and for what purpose the social network provider processes your data, please see their privacy policies. | Automated Decision Making (78.0999984741211%):  | Required Purpose (86.30000305175781%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Required Purpose (86.5999984741211%):  | Required Purpose (89.9000015258789%):  | Required Purpose (90.80000305175781%):  | Processing (96.5999984741211%): If you choose to link Boomplay to your social network or public forum account (including without limitation Facebook, Twitter or Google account), you may provide us or allow your social network to provide us with information from your social network or public forum accounts. | Processing (98.30000305175781%): This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. | Technical Measure (89.30000305175781%):  | Required Purpose (99.80000305175781%):  | Processing (96.69999694824219%): your comments on Boomplay or any other content that you Posted on or through the Services, views and interactions on Boomplay. | Automated Decision Making (71.5999984741211%): When you Post content, including images, text and audio to Boomplay, you automatically upload certain metadata that is connected to the content. | Processing (81.80000305175781%): In essence, metadata describes other data and provides information about your content that will not always be evident to the viewer. | Processing (98.69999694824219%): Any automated decision-making, including profiling, based on the data automatically collected from you, will solely be used in optimizing the Services and tailoring it to your preferences. | Processing (76.69999694824219%): The Types of Personal Data We Collect and Use We may collect and use the following information about you: • Information you share with us. | Processing (93.9000015258789%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Required Purpose (99.80000305175781%):  | Technical Measure (98.4000015258789%): Cookies We use cookies and other similar technologies (e.g. | Technical Measure (72.4000015258789%): Cookies We use cookies and other similar technologies (e.g. | Technical Measure (86.4000015258789%): web beacons, Flash cookies, App cache, etc.) (“ Cookies ”) to enhance your experience using Boomplay. | Technical Measure (84.0999984741211%): web beacons, Flash cookies, App cache, etc.) (“ Cookies ”) to enhance your experience using Boomplay. | Technical Measure (86.9000015258789%): | Boomplay Music Get APPGet APP What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player What’s Boomplay For Artists Advertising News Contact Go Web Player Privacy Policy EFFECTIVE AS OF OCTOBER 26, 2020 Welcome to Boomplay. | Technical Measure (74.80000305175781%):  | Required Purpose (98.30000305175781%): web beacons, Flash cookies, App cache, etc.) (“ Cookies ”) to enhance your experience using Boomplay. | Technical Measure (99.4000015258789%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Technical Measure (99.19999694824219%):  | Required Purpose (79.9000015258789%): Cookies are small files which, when placed on your device, enable us to provide certain features and functionality. | Required Purpose (93.19999694824219%): These are Cookies that are required for the operation of Boomplay and to keep your account and data safe and secure. | Required Purpose (94.69999694824219%): They allow us to recognize and count the number of visitors and to see how visitors move around Boomplay when they are using it. | Required Purpose (89.9000015258789%):  | Required Purpose (76.0999984741211%): They allow us to recognize and count the number of visitors and to see how visitors move around Boomplay when they are using it. | Required Purpose (84.9000015258789%): This helps us to improve the way Boomplay works, for example, by ensuring that users are able to find what they are looking for easily. | Required Purpose (96.5999984741211%): This helps us to improve the way Boomplay works, for example, by ensuring that users are able to find what they are looking for easily. | Required Purpose (73.5%): | Boomplay Music Get APPGet APP What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player What’s Boomplay For Artists Advertising News Contact Go Web Player Privacy Policy EFFECTIVE AS OF OCTOBER 26, 2020 Welcome to Boomplay. | Required Purpose (74.69999694824219%): They allow us to recognize and count the number of visitors and to see how visitors move around Boomplay when they are using it. | Retention (76.69999694824219%): In connection with your content the metadata can describe how, when and by whom the piece of content was collected and how that content is formatted. | Required Purpose (77.80000305175781%): This enables us to personalize our content for you, greet you by name and remember your preferences (for example, your choice of language or region). | Required Purpose (79.30000305175781%): This enables us to personalize our content for you, greet you by name and remember your preferences (for example, your choice of language or region). | Required Purpose (83.30000305175781%): This enables us to personalize our content for you, greet you by name and remember your preferences (for example, your choice of language or region). | Required Purpose (97.69999694824219%): We will use this information to make Boomplay and the advertising displayed on it more relevant to your interests. | Required Purpose (75.4000015258789%): The Types of Personal Data We Collect and Use We may collect and use the following information about you: • Information you share with us. | Required Purpose (80.5%): We may also share this information with third parties for this purpose. | Technical Measure (76.80000305175781%):  | Required Purpose (94.0999984741211%): Analytics information On Boomplay, we use third-party analytics tools to help us measure traffic and usage trends for the Services. | Required Purpose (85.5999984741211%): These tools, for example, collect information sent by your device or our Services, including the pages you visit, add-ons, and other information that assists us in improving the Service. | Processing (85.30000305175781%): Any automated decision-making, including profiling, based on the data automatically collected from you, will solely be used in optimizing the Services and tailoring it to your preferences. | Required Purpose (97.4000015258789%): The information will be used to report and evaluate your activities and patterns as a user of Boomplay to provide services in accordance with these activities. | Required Purpose (99.5%): The information will be used to report and evaluate your activities and patterns as a user of Boomplay to provide services in accordance with these activities. | Required Purpose (85.9000015258789%): How We Use Your Personal Data We will use the information we collect about you in the following ways: • To administer Boomplay (i.e. | Required Purpose (89.19999694824219%): How We Use Your Personal Data We will use the information we collect about you in the following ways: • To administer Boomplay (i.e. | Required Purpose (98.19999694824219%):  | Required Purpose (88.4000015258789%): to provide our Services to you) and for internal operations, including troubleshooting, data analysis, testing, research, statistical and survey purposes (i.e. | Required Purpose (75.9000015258789%): to provide our Services to you) and for internal operations, including troubleshooting, data analysis, testing, research, statistical and survey purposes (i.e. | Required Purpose (72.30000305175781%):  | Required Purpose (95.69999694824219%):  | Required Purpose (92.80000305175781%): to provide our Services to you) and for internal operations, including troubleshooting, data analysis, testing, research, statistical and survey purposes (i.e. | Required Purpose (94.19999694824219%):  | Required Purpose (81.0999984741211%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (88.0%): This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. | Required Purpose (96.0999984741211%):  | Required Purpose (94.80000305175781%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Required Purpose (81.0999984741211%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (95.30000305175781%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (84.4000015258789%): Please read the following carefully to understand our views and practices regarding your personal data and how we will treat it. | Required Purpose (87.4000015258789%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (93.5999984741211%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (97.19999694824219%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (74.19999694824219%): your comments on Boomplay or any other content that you Posted on or through the Services, views and interactions on Boomplay. | Required Purpose (89.0%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (93.19999694824219%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (96.9000015258789%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason pr</t>
+  </si>
+  <si>
+    <t>Processing (99.5999984741211%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Processing (98.30000305175781%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Processing (99.5999984741211%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Processing (97.4000015258789%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Processing (99.19999694824219%): Privacy notice for United States residents How to contact Meta with questions Why and how we process your information Other policies and articles Settings Privacy Policy What is the Privacy Policy and what does it cover? | Required Purpose (86.0%): Some information is required for our Products to work. | Required Purpose (70.80000305175781%): Other information is optional, but without it, the quality of your experience might be affected. | Required Purpose (89.19999694824219%): You can update these settings to shape your experience. | Processing (72.5%):  | Retention (73.19999694824219%):  | Retention (85.0999984741211%): In some cases information is de-identified, aggregated, or anonymized by third parties so that it no longer identifies individuals before it’s made available to us. | Required Purpose (97.4000015258789%): Highlights We use information we collect to provide a personalized experience to you, including ads, along with the other purposes we explain in detail below. | Required Purpose (91.9000015258789%): Highlights We use information we collect to provide a personalized experience to you, including ads, along with the other purposes we explain in detail below. | Automated Decision Making (70.69999694824219%): The information we use for these purposes is automatically processed by our systems. | Processing (97.30000305175781%): But in some cases, we also use manual review to access and review your information. | Processing (82.4000015258789%): But in some cases, we also use manual review to access and review your information. | Required Purpose (98.9000015258789%): Here are the ways we use your information: To provide, personalize and improve our Products We use information we have to provide and improve our Products. | Required Purpose (92.0%): Highlights We use information we collect to provide a personalized experience to you, including ads, along with the other purposes we explain in detail below. | Required Purpose (78.4000015258789%):  | Required Purpose (74.80000305175781%): This includes personalizing features, content and recommendations, such as your Facebook Feed, Instagram Feed, Stories and ads. | Required Purpose (91.9000015258789%): Read more about how we use information to provide, personalize and improve our Products: How we show ads and other sponsored or commercial content How we use information to improve our Products How we use location-related information To promote safety, security and integrity We use information we collect to help protect people from harm and provide safe, secure Products. | Required Purpose (97.80000305175781%): Read more about how we use information to provide, personalize and improve our Products: How we show ads and other sponsored or commercial content How we use information to improve our Products How we use location-related information To promote safety, security and integrity We use information we collect to help protect people from harm and provide safe, secure Products. | Required Purpose (72.4000015258789%): Learn more To provide measurement, analytics and business services Lots of people rely on our Products to run or promote their businesses or share content. | Required Purpose (89.80000305175781%): Learn more To research and innovate for social good We use information we have, information from researchers and datasets from publicly available sources, professional groups and non-profit groups to conduct and support research. | Processing (99.5%): How is your information shared on Meta Products or with integrated partners? | Processing (97.9000015258789%): If you do, these integrated partners receive information about you and your activity. | Organisational Measure (74.19999694824219%): We also require partners and other third parties to follow rules about how they can and cannot use and disclose the information we provide. | Organisational Measure (97.0%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Processing (98.5%): How is your information shared on Meta Products or with integrated partners? | Required Purpose (86.5999984741211%): Here’s more detail about who we share information with: Partners Advertisers and Audience Network publishers Partners who use our analytics services Partners who offer goods or services on our Products and commerce services platforms Integrated partners Vendors Measurement vendors Marketing vendors Service providers Service providers Third parties External researchers AI integrations Other third parties We also share information with other third parties in response to legal requests, to comply with applicable law or to prevent harm. | Processing (97.0%): How do we transfer information? | Required Purpose (89.69999694824219%): Why we share across the Meta Companies Meta Products share information with other Meta Companies: To promote safety, security and integrity and comply with applicable laws To personalize offers, ads and other sponsored or commercial content To develop and provide features and integrations To understand how people use and interact with Meta Company Products See some examples of why we share. | Required Purpose (74.0%): Why we share across the Meta Companies Meta Products share information with other Meta Companies: To promote safety, security and integrity and comply with applicable laws To personalize offers, ads and other sponsored or commercial content To develop and provide features and integrations To understand how people use and interact with Meta Company Products See some examples of why we share. | Required Purpose (74.4000015258789%):  | Processing (81.4000015258789%): How long do we keep your information? | Retention (96.30000305175781%): Highlights We keep information as long as we need it to provide our Products, comply with legal obligations or protect our or other’s interests. | Retention (89.9000015258789%): Highlights We keep information as long as we need it to provide our Products, comply with legal obligations or protect our or other’s interests. | Required Purpose (71.80000305175781%): How is your information shared on Meta Products or with integrated partners? | Retention (74.0999984741211%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Retention (77.5%): Here's the information we collect: Your activity and information you provide Friends, followers and other connections App, browser and device information Information from partners, vendors and other third parties What if you don’t let us collect certain information? | Retention (95.4000015258789%):  | Required Purpose (97.4000015258789%): Here’s what we consider when we decide: If we need it to operate or provide our Products. | Required Purpose (99.19999694824219%): For example, we need to keep some of your information to maintain your account. | Retention (73.19999694824219%): For example, messages sent using Messenger’s vanish mode are retained for less time than regular messages. | Retention (75.5%): For example, messages sent using Messenger’s vanish mode are retained for less time than regular messages. | Retention (96.5%): How long we need to retain the information to comply with certain legal obligations. | Required Purpose (72.0%): Read more about how we use information to provide, personalize and improve our Products: How we show ads and other sponsored or commercial content How we use information to improve our Products How we use location-related information To promote safety, security and integrity We use information we collect to help protect people from harm and provide safe, secure Products. | Retention (87.0%): If we need it for other legitimate purposes, such as to prevent harm; investigate possible violations of our terms or policies; promote safety, security and integrity; or protect ourselves, including our rights, property or products In some instances and for specific reasons, we’ll keep information for an extended period of time. | Processing (95.69999694824219%): Read our Policy about when we may preserve your information. | Organisational Measure (73.0%): Highlights We access, preserve, use and share your information: In response to legal requests, like search warrants, court orders, production orders or subpoenas. | Organisational Measure (72.80000305175781%): Highlights We access, preserve, use and share your information: In response to legal requests, like search warrants, court orders, production orders or subpoenas. | Required Purpose (90.30000305175781%): To use less information that’s connected to individual users, in some cases we de-identify or aggregate information or anonymize it so that it no longer identifies you. | Required Purpose (98.0%): In accordance with applicable law To promote the safety, security and integrity of Meta Products, users, employees, property and the public. | Retention (94.0%): We may access or preserve your information for an extended amount of time. | Organisational Measure (97.5999984741211%):  | Processing (99.19999694824219%): The information we use for these purposes is automatically processed by our systems. | Automated Decision Making (95.0999984741211%): The information we use for these purposes is automatically processed by our systems. | Processing (78.30000305175781%): ATTN: Privacy Operations 1601 Willow Road Menlo Park, CA 94025 Why and how we process your information The categories of information we use, and why and how information is processed, are set out below: Why and how we process your information Information categories we use (see 'What Information do we collect?' for more information on each information category) The actual information we use depends on your factual circumstances, but could include any of the following: Personalizing the Meta Products (other than ads, see below): Our systems automatically process information we collect and store associated with you and others to assess and understand your interests and your preferences and provide you personalized experiences across the Meta Products in accordance with our terms. | Required Purpose (99.4000015258789%): ATTN: Privacy Operations 1601 Willow Road Menlo Park, CA 94025 Why and how we process your information The categories of information we use, and why and how information is processed, are set out below: Why and how we process your information Information categories we use (see 'What Information do we collect?' for more information on each information category) The actual information we use depends on your factual circumstances, but could include any of the following: Personalizing the Meta Products (other than ads, see below): Our systems automatically process information we collect and store associated with you and others to assess and understand your interests and your preferences and provide you personalized experiences across the Meta Products in accordance with our terms. | Required Purpose (96.30000305175781%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Required Purpose (86.5%):  | Processing (75.9000015258789%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings (like GPS location) Location-related information Information about the network you connect your device to Reports about our products’ performance on your device Information from cookies and similar technologies Information from partners, vendors and third parties Providing ads on the Meta Company Products: Our ads system automatically processes information that we’ve collected and stored associated with you. | Processing (98.5%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings (like GPS location) Location-related information Information about the network you connect your device to Reports about our products’ performance on your device Information from cookies and similar technologies Information from partners, vendors and third parties Providing ads on the Meta Company Products: Our ads system automatically processes information that we’ve collected and stored associated with you. | Processing (97.5%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings (like GPS location) Location-related information Information about the network you connect your device to Reports about our products’ performance on your device Information from cookies and similar technologies Information from partners, vendors and third parties Providing ads on the Meta Company Products: Our ads system automatically processes information that we’ve collected and stored associated with you. | Required Purpose (99.0%): Our ads system uses this information to understand your interests and your preferences and personalize your ads across the Meta Company Products. | Processing (92.69999694824219%): Then we match the ad to people who might be interested. | Processing (97.69999694824219%): For information that WhatsApp shares with Meta see the WhatsApp Help Center article. | Required Purpose (95.80000305175781%): How is your information shared on Meta Products or with integrated partners? | Required Purpose (94.5%):  | Required Purpose (92.5%):  | Processing (85.80000305175781%): Your activity and information you provide Friends, followers and other connections App, browser and device information Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to: Create and maintain your account and profile, Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information, Facilitate the sharing of content and status, Provide and curate features, Provide messaging services, the ability to make voice and video calls and connect with others, Provide advertising products, Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide, Undertake analytics, and Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences. | Processing (73.0999984741211%): Your activity and information you provide Friends, followers and other connections App, browser and device information Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to: Create and maintain your account and profile, Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information, Facilitate the sharing of content and status, Provide and curate features, Provide messaging services, the ability to make voice and video calls and connect with others, Provide advertising products, Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide, Undertake analytics, and Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences. | Processing (72.30000305175781%): Your activity and information you provide Friends, followers and other connections App, browser and device information Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to: Create and maintain your account and profile, Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information, Facilitate the sharing of content and status, Provide and curate features, Provide messaging services, the ability to make voice and video calls and connect with others, Provide advertising products, Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide, Undertake analytics, and Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences. | Processing (75.19999694824219%): Privacy notice for United States residents How to contact Meta with questions Why and how we process your information Other policies and articles Settings Privacy Policy What is the Privacy Policy and what does it cover? | Processing (73.80000305175781%):  | Processing (84.9000015258789%):  | Automated Decision Making (91.0%): Your activity and information you provide Friends, followers and other connections App, browser and device information Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to: Create and maintain your account and profile, Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information, Facilitate the sharing of content and status, Provide and curate features, Provide messaging services, the ability to make voice and video calls and connect with others, Provide advertising products, Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide, Undertake analytics, and Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences. | Required Purpose (84.5999984741211%):  | Required Purpose (77.80000305175781%): Your activity and information you provide Friends, followers and other connections App, browser and device information Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to: Create and maintain your account and profile, Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information, Facilitate the sharing of content and status, Provide and curate features, Provide messaging services, the ability to make voice and video calls and connect with others, Provide advertising products, Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide, Undertake analytics, and Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences. | Technical Measure (96.0%): Your activity and information you provide Friends, followers and other connections App, browser and device information Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to: Create and maintain your account and profile, Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information, Facilitate the sharing of content and status, Provide and curate features, Provide messaging services, the ability to make voice and video calls and connect with others, Provide advertising products, Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide, Undertake analytics, and Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences. | Required Purpose (99.30000305175781%): For example, we collect different information if you sell furniture on Marketplace than if you post a reel on Instagram. | Required Purpose (99.30000305175781%):  | Required Purpose (99.5%):  | Required Purpose (97.30000305175781%):  | Required Purpose (99.5999984741211%): We also use information to develop, research and test improvements to our Products. | Required Purpose (94.5%): We use information we have to: See if a product is working correctly, Troubleshoot and fix it when it’s not, Test out new products and features to see if they work, Get feedback on our ideas for products or features, and Conduct surveys and other research about what you like about our Products and brands and what we can do better. | Required Purpose (74.0%): We use information we have to: See if a product is working correctly, Troubleshoot and fix it when it’s not, Test out new products and features to see if they work, Get feedback on our ideas for products or features, and Conduct surveys and other research about what you like about our Products and brands and what we can do better. | Required Purpose (81.69999694824219%):  | Required Purpose (88.9000015258789%):  | Required Purpose (91.5999984741211%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Required Purpose (85.5999984741211%):  | Automated Decision Making (79.69999694824219%): We process information we have associated with you and apply automated processing techniques and, in some instances, conduct manual (human) review to: Verify accounts and activity, Find and address violations of our terms or policies. | Processing (70.5999984741211%): In some cases, the decisions we make about violations are reviewed by the Oversight Board, Investigate suspicious activity, Detect, prevent and combat harmful or unlawful behavior, such as to review and, in some cases, remove content reported to us, Identify and combat disparities and racial bias against historically marginalized communities, Protect the life, physical or mental health, well-being or integrity of our users or others, Detect and prevent spam, other security matters and other bad experiences, Detect and stop threats to our personnel and property, and Maintain the integrity of our Products. | Required Purpose (93.5%):  | Required Purpose (75.5%):  | Required Purpose (93.19999694824219%):  | Required Purpose (87.69999694824219%):  | Required Purpose (93.69999694824219%): In some cases, the decisions we make about violations are reviewed by the Oversight Board, Investigate suspicious activity, Detect, prevent and combat harmful or unlawful behavior, such as to review and, in some cases, remove content reported to us, Identify and combat disparities and racial bias against historically marginalized communities, Protect the life, physical or mental health, well-being or integrity of our users or others, Detect and prevent spam, other security matters and other bad experiences, Detect and stop threats to our personnel and property, and Maintain the integrity of our Products. | Required Purpose (90.5999984741211%):  | Required Purpose (92.80000305175781%):  | Required Purpose (71.19999694824219%): In some cases, the decisions we make about violations are reviewed by the Oversight Board, Investigate suspicious activity, Detect, prevent and combat harmful or unlawful behavior, such as to review and, in some cases, remove content reported to us, Identify and combat disparities and racial bias against historically marginalized communities, Protect the life, physical or mental health, well-being or integrity of our users or others, Detect and prevent spam, other security matters and other bad experiences, Detect and stop threats to our personnel and property, and Maintain the integrity of our Products. | Required Purpose (95.0%): Learn more To communicate with you We communicate with you using information you've given us, like contact information you've entered on your profile. | Required Purpose (91.30000305175781%): Your activity and information you provide:: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties To communicate with you: We use information you’ve given us (like contact information on your profile) to send you a communication, like an e-mail or in-product notice, for example: We’ll contact you via email or in-product notifications in relation to the Meta Products, product-related issues, research or to let you know about our terms and policies. | Required Purpose (80.0999984741211%): We also use contact information like your email address to respond when you contact us. | Processing (82.4000015258789%): Transferring, storing or processing your information across borders, including from and to the United States and other countries: We share information we collect globally, both internally across our offices and data centers and externally with our partners, third parties and service providers. | Processing (96.5999984741211%):  | Processing (94.19999694824219%): Because Meta is global, with users, partners, vendors and employees around the world, transfers are necessary: To operate and provide the services described in the terms that apply to the Meta Product(s) you are using. | Required Purpose (87.5999984741211%): Because Meta is global, with users, partners, vendors and employees around the world, transfers are necessary: To operate and provide the services described in the terms that apply to the Meta Product(s) you are using. | Required Purpose (76.19999694824219%):  | Required Purpose (74.5%): Here's the information we collect: Your activity and information you provide Friends, followers and other connections App, browser and device information Information from partners, vendors and other third parties What if you don’t let us collect certain information? | Processing (97.80000305175781%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, includin</t>
+  </si>
+  <si>
+    <t>Processing (96.0999984741211%): WhatsApp LLC is also the data controller for any processing of personal information about you and you can contact us using the details in the section Contact Us below. | Processing (99.5999984741211%): This WhatsApp Business App Privacy Policy (“Business App Privacy Policy”) explains WhatsApp’s data practices with respect to the Business Functions, and applies only to the extent information relating to users of the WhatsApp Business App would be considered personal data and is processed by WhatsApp as a controller, each under applicable law. | Processing (99.30000305175781%): Information We Collect In addition to the information described in the applicable WhatsApp Privacy Policy, we collect the following information. | Processing (95.4000015258789%): Privacy Help Center Blog For Business Apps Log inDownload WhatsApp Business App Privacy Policy Effective July 14, 2025 Table of Contents WhatsApp Legal Info Scope of This WhatsApp Business App Privacy Policy Information We Collect How We Use Information Information You and We Share How We Work With Other Meta Companies Region Specific Information Assignment, Change Of Control, And Transfer Managing Your Information Law, Our Rights, And Protection Our Global Operations Updates to Our Privacy Policy Contact Us If you are located in the UK, WhatsApp LLC provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy. | Required Purpose (70.9000015258789%): In addition to your phone number, you must provide basic information about your business to create a WhatsApp business account, including your business name and business category. | Processing (97.0999984741211%): This WhatsApp Business App Privacy Policy (“Business App Privacy Policy”) explains WhatsApp’s data practices with respect to the Business Functions, and applies only to the extent information relating to users of the WhatsApp Business App would be considered personal data and is processed by WhatsApp as a controller, each under applicable law. | Required Purpose (83.80000305175781%): WhatsApp Business App Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어 FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Required Purpose (83.30000305175781%): WhatsApp LLC is also the data controller for any processing of personal information about you and you can contact us using the details in the section Contact Us below. | Required Purpose (99.0999984741211%): How We Use Information We use the information we collect for the same purposes described in the WhatsApp Privacy Policy, and also to operate, provide, improve, understand, customize, support, and market our WhatsApp Business App and Business Functions. | Required Purpose (98.80000305175781%): We use the information we have to operate and provide our WhatsApp Business App and Business Functions, including providing you with business support; providing onboarding tools; providing message creation and delivery tools; providing you new and premium Business Functions (some of which may be offered by third parties and/or Meta); and improving, fixing, and customizing our WhatsApp Business App. | Required Purpose (95.5%):  | Required Purpose (92.5%):  | Required Purpose (94.69999694824219%):  | Required Purpose (82.4000015258789%): Business Functions may be offered by WhatsApp, third parties and/or Meta, via integrations into our Business App, and may be subject to the third parties’ own terms of service and privacy policies. | Required Purpose (91.69999694824219%): While the WhatsApp Business App includes various features available in the WhatsApp Messenger App, some features may not be available; and not all Business Functions are available everywhere. | Required Purpose (95.9000015258789%): We use the information we have to operate and provide our WhatsApp Business App and Business Functions, including providing you with business support; providing onboarding tools; providing message creation and delivery tools; providing you new and premium Business Functions (some of which may be offered by third parties and/or Meta); and improving, fixing, and customizing our WhatsApp Business App. | Required Purpose (99.5%):  | Required Purpose (96.19999694824219%): We also use your information to respond to you when you contact us. | Required Purpose (98.0%): In addition to the safety, security and integrity purposes described in the WhatsApp Privacy Policy, we also use the information we have to maintain safety, security and integrity on our WhatsApp Business App, for example: to create quality and integrity inferences about businesses; secure WhatsApp systems and WhatsApp Business App users’ accounts; fight threats, abuse, or infringement activities; promote safety, security, and integrity on the WhatsApp Business App; and to ensure compliance with our terms and policies. | Required Purpose (80.80000305175781%):  | Required Purpose (98.80000305175781%):  | Required Purpose (96.80000305175781%):  | Processing (99.4000015258789%): Information You and We Share You and we share information as described in the WhatsApp Privacy Policy, plus additional sharing relevant to the Business Functions. | Processing (85.0999984741211%): Information You and We Share You and we share information as described in the WhatsApp Privacy Policy, plus additional sharing relevant to the Business Functions. | Processing (97.69999694824219%): Law, Our Rights, And Protection Review the WhatsApp Privacy Policy to understand how we access, preserve, and share your information in response to legal obligations. | Processing (97.0999984741211%): Law, Our Rights, And Protection Review the WhatsApp Privacy Policy to understand how we access, preserve, and share your information in response to legal obligations.</t>
+  </si>
+  <si>
+    <t>Processing (99.5999984741211%): Our Privacy Policy ("Privacy Policy") helps explain our data practices, including the information we process to provide our Services. | Required Purpose (99.5%): Our Privacy Policy ("Privacy Policy") helps explain our data practices, including the information we process to provide our Services. | Processing (99.4000015258789%): For example, our Privacy Policy talks about what information we collect and how this affects you. | Processing (91.5999984741211%): It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services. | Processing (99.5999984741211%): You can learn more further below in this Privacy Policy about the ways in which we share information across this family of companies. | Organisational Measure (76.30000305175781%): Since we started WhatsApp, we’ve built our services with a set of strong privacy principles in mind. | Organisational Measure (84.9000015258789%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Processing (97.5%): In our updated Terms of Service and Privacy Policy you’ll find: Additional Information On How We Handle Your Data. | Processing (96.30000305175781%):  | Organisational Measure (76.0%): For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information. | Processing (99.30000305175781%): Back to top Information We Collect WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services. | Required Purpose (99.69999694824219%): Back to top Information We Collect WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services. | Required Purpose (98.9000015258789%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Processing (98.80000305175781%): Please also read WhatsApp’s Terms of Service ("Terms"), which describe the terms under which you use and we provide our Services. | Processing (86.5999984741211%): We require certain information to deliver our Services and without this we will not be able to provide our Services to you. | Required Purpose (99.30000305175781%): We require certain information to deliver our Services and without this we will not be able to provide our Services to you. | Processing (98.9000015258789%): Privacy Help Center Blog For Business Apps Log inDownload WhatsApp Privacy Policy Effective January 4, 2021archived versions If you live in the European Region, WhatsApp Ireland Limited provides the Services to you under this Terms of Service and Privacy Policy. | Required Purpose (89.4000015258789%): For example, you must provide your mobile phone number to create an account to use our Services. | Processing (96.0%): Our Services have optional features which, if used by you, require us to collect additional information to provide such features. | Required Purpose (98.0%): Our Services have optional features which, if used by you, require us to collect additional information to provide such features. | Organisational Measure (95.0%): You will be notified of such collection, as appropriate. | Organisational Measure (80.0999984741211%): You will be notified of such collection, as appropriate. | Processing (75.19999694824219%): For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information. | Processing (79.5%): We do not retain your messages in the ordinary course of providing our Services to you. | Processing (98.4000015258789%): It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services. | Retention (90.0%): If a message cannot be delivered immediately (for example, if the recipient is offline), we keep it in encrypted form on our servers for up to 30 days as we try to deliver it. | Processing (93.19999694824219%):  | Required Purpose (98.80000305175781%): When a user forwards media within a message, we store that media temporarily in encrypted form on our servers to aid in more efficient delivery of additional forwards. | Organisational Measure (86.69999694824219%):  | Technical Measure (89.69999694824219%):  | Required Purpose (98.69999694824219%): End-to-end encryption means that your messages are encrypted to protect against us and third parties from reading them. | Required Purpose (94.30000305175781%): Payment account and transaction information includes information needed to complete the transaction (for example, information about your payment method, shipping details and transaction amount). | Retention (79.30000305175781%): Back to top Information We Collect WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services. | Processing (82.5%): We collect and use precise location information from your device with your permission when you choose to use location-related features, like when you decide to share your location with your contacts or view locations nearby or locations others have shared with you. | Processing (90.5%): There are certain settings relating to location-related information which you can find in your device settings or the in-app settings, such as location sharing. | Required Purpose (99.0999984741211%): Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). | Required Purpose (89.4000015258789%): Stay connectedMessage and call for free* around the world. | Required Purpose (84.5999984741211%): We also use your location information for diagnostics and troubleshooting purposes. | Technical Measure (97.69999694824219%): Cookies. | Technical Measure (95.9000015258789%):  | Technical Measure (93.4000015258789%): We use cookies to operate and provide our Services, including to provide our Services that are web-based, improve your experiences, understand how our Services are being used, and customize them. | Required Purpose (99.80000305175781%):  | Required Purpose (99.69999694824219%):  | Required Purpose (98.5999984741211%):  | Required Purpose (98.69999694824219%): Additionally, we may use cookies to remember your choices, like your language preferences, to provide a safer experience, and otherwise to customize our Services for you. | Required Purpose (74.19999694824219%): Learn more about how we use cookies to provide you our Services. | Required Purpose (97.30000305175781%): Learn more about how we use cookies to provide you our Services. | Processing (88.19999694824219%): We do not retain your messages in the ordinary course of providing our Services to you. | Processing (98.5999984741211%): You should keep in mind that in general any user can capture screenshots of your chats or messages or make recordings of your calls with them and send them to WhatsApp or anyone else, or post them on another platform. | Required Purpose (99.69999694824219%): Just as you can report other users, other users or third parties may also choose to report to us your interactions and your messages with them or others on our Services; for example, to report possible violations of our Terms or policies. | Required Purpose (94.0%): In addition, some businesses might be working with third-party service providers (which may include Meta) to help manage their communications with their customers. | Processing (83.30000305175781%): For example, a business may give such third-party service provider access to its communications to send, store, read, manage, or otherwise process them for the business. | Processing (92.0999984741211%): To understand how a business processes your information, including how it might share your information with third parties or Meta, you should review that business’ privacy policy or contact the business directly. | Required Purpose (99.9000015258789%): We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. | Required Purpose (99.19999694824219%):  | Required Purpose (99.30000305175781%): These companies may provide us with information about you in certain circumstances; for example, app stores may provide us with reports to help us diagnose and fix service issues. | Processing (99.30000305175781%): The "How We Work With Other Meta Companies" section below provides more information about how WhatsApp collects and shares information with the other Meta Companies. | Processing (99.30000305175781%): The "How We Work With Other Meta Companies" section below provides more information about how WhatsApp collects and shares information with the other Meta Companies. | Required Purpose (99.69999694824219%): Back to top How We Use Information We use information we have (subject to choices you make and applicable law) to operate, provide, improve, understand, customize, support, and market our Services. | Required Purpose (99.30000305175781%): Here's how: Our Services. | Required Purpose (99.69999694824219%):  | Required Purpose (99.4000015258789%):  | Required Purpose (99.0999984741211%): We also use your information to respond to you when you contact us. | Required Purpose (78.5999984741211%): For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information. | Required Purpose (82.4000015258789%): Safety, security, and integrity are an integral part of our Services. | Required Purpose (98.0999984741211%):  | Required Purpose (92.19999694824219%):  | Required Purpose (98.5999984741211%):  | Required Purpose (99.5999984741211%): We use information we have to communicate with you about our Services and let you know about our terms, policies, and other important updates. | Processing (74.0%): For example, you may send us an email with information relating to app performance or other issues. | Processing (87.0%): It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services. | Required Purpose (81.0999984741211%): Our Privacy Policy ("Privacy Policy") helps explain our data practices, including the information we process to provide our Services. | Processing (95.69999694824219%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Processing (96.0%):  | Processing (88.19999694824219%):  | Required Purpose (99.80000305175781%):  | Required Purpose (99.9000015258789%): You can learn more further below in this Privacy Policy about the ways in which we share information across this family of companies. | Required Purpose (79.80000305175781%): When we share information with third-party service providers and other Meta Companies in this capacity, we require them to use your information on our behalf in accordance with our instructions and terms. | Processing (95.5999984741211%): If you interact with a third-party service or another Meta Company Product linked through our Services, such as when you use the in-app player to play content from a third-party platform, information about you, like your IP address and the fact that you are a WhatsApp user, may be provided to such third party or Meta Company Product. | Processing (99.30000305175781%): Back to top How We Work With Other Meta Companies As part of the Meta Companies, WhatsApp receives information from, and shares information (see here) with, the other Meta Companies. | Required Purpose (99.80000305175781%): We may use the information we receive from them, and they may use the information we share with them, to help operate, provide, improve, understand, customize, support, and market our Services and their offerings, including the Meta Company Products. | Required Purpose (89.0%):  | Required Purpose (95.19999694824219%):  | Required Purpose (97.4000015258789%): This includes: helping improve infrastructure and delivery systems; understanding how our Services or theirs are used; promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities; improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. | Required Purpose (81.0%):  | Required Purpose (94.0%): This includes: helping improve infrastructure and delivery systems; understanding how our Services or theirs are used; promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities; improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. | Required Purpose (92.69999694824219%): This includes: helping improve infrastructure and delivery systems; understanding how our Services or theirs are used; promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities; improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. | Required Purpose (93.0999984741211%): This includes: helping improve infrastructure and delivery systems; understanding how our Services or theirs are used; promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities; improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. | Required Purpose (98.5%):  | Required Purpose (91.5999984741211%): This includes: helping improve infrastructure and delivery systems; understanding how our Services or theirs are used; promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities; improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. | Required Purpose (98.30000305175781%): This includes: helping improve infrastructure and delivery systems; understanding how our Services or theirs are used; promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities; improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. | Required Purpose (95.0%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Required Purpose (95.69999694824219%): This includes: helping improve infrastructure and delivery systems; understanding how our Services or theirs are used; promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities; improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. | Retention (94.0%): We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. | Required Purpose (97.69999694824219%): We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. | Retention (87.69999694824219%):  | Processing (97.4000015258789%): The storage periods are determined on a case-by-case basis that depends on factors like the nature of the information, why it is collected and processed, relevant legal or operational retention needs, and legal obligations. | Processing (95.0%): The storage periods are determined on a case-by-case basis that depends on factors like the nature of the information, why it is collected and processed, relevant legal or operational retention needs, and legal obligations. | Processing (91.5999984741211%): If you change your mobile phone number, you must update it using our in-app change number feature and transfer your account to your new mobile phone number. | Processing (74.5999984741211%): Once your messages are delivered, they are deleted from our servers. | Processing (93.5%): It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services. | Retention (82.0%): Be mindful that if you only delete WhatsApp from your device without using our in-app delete my account feature, your information will be stored with us for a longer period. | Processing (98.5999984741211%): Back to top Information We Collect WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services. | Processing (93.9000015258789%): Back to top Law, Our Rights, And Protection We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm. | Required Purpose (94.0999984741211%):  | Required Purpose (96.19999694824219%):  | Required Purpose (97.69999694824219%): Back to top Law, Our Rights, And Protection We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm. | Required Purpose (97.4000015258789%):  | Required Purpose (84.9000015258789%): Back to top Law, Our Rights, And Protection We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm. | Required Purpose (92.19999694824219%): Back to top Law, Our Rights, And Protection We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm. | Required Purpose (98.80000305175781%): Back to top Our Global Operations WhatsApp shares information globally, both internally within the Meta Companies and externally with our partners and service providers, and with those with whom you communicate around the world, in accordance with this Privacy Policy. | Processing (99.0999984741211%): Your information may, for example, be transferred or transmitted to, or stored and processed in, the United States; countries or territories where the Meta Companies’ affiliates and partners, or our service providers are located; or any other country or territory globally where our Services are provided outside of where you live for the purposes as described in this Privacy Policy. | Processing (95.0%): Your information may, for example, be transferred or transmitted to, or stored and processed in, the United States; countries or territories where the Meta Companies’ affiliates and partners, or our service providers are located; or any other country or territory globally where our Services are provided outside of where you live for the purposes as described in this Privacy Policy. | Required Purpose (83.69999694824219%): We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. | Required Purpose (91.0%): Back to top Our Global Operations WhatsApp shares information globally, both internally within the Meta Companies and externally with our partners and service providers, and with those with whom you communicate around the world, in accordance with this Privacy Policy. | Processing (97.0%): Your phone number, profile name and photo, "about" information, last seen information, and message receipts are available to anyone who uses our Services, although you can configure your Services settings to manage certain information available to other users, including businesses, with whom you communicate. | Processing (94.5%): These transfers are necessary to provide the global Services set forth in our Terms. | Required Purpose (82.0%): We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. | Required Purpose (96.4000015258789%): These transfers are necessary to provide the global Services set forth in our Terms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processing (96.0%): We are responsible for processing personal data in accordance with the General Data Protection Regulation (âGDPRâ), an EU wide Regulation for the protection of personal data. | Processing (99.4000015258789%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Processing (83.0%): This Privacy Policy (the âPolicyâ) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the âSitesâ) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the âServiceâ). | Processing (75.0999984741211%): This Privacy Policy (the âPolicyâ) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the âSitesâ) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the âServiceâ). | Processing (65.5999984741211%): This Privacy Policy (the âPolicyâ) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the âSitesâ) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the âServiceâ). | Processing (97.5%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Processing (98.9000015258789%): We are responsible for processing personal data in accordance with the General Data Protection Regulation (âGDPRâ), an EU wide Regulation for the protection of personal data. | Organisational Measure (70.69999694824219%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Processing (92.4000015258789%): Basic profile information (avatar, Facebook name, country) will be displayed to other users during game play and on public leader-boards. | Required Purpose (77.5%): Signing in with Facebook allows us to offer other functionalities such as to invite and play with friends, create challenges for friends and see friendsâ game progress. | Required Purpose (92.30000305175781%):  | Required Purpose (70.5%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Required Purpose (66.9000015258789%): This is also to allow you to log in on multiple devices and synchronise progress across multiple devices on multiple platforms. | Required Purpose (89.19999694824219%): This is also to allow you to log in on multiple devices and synchronise progress across multiple devices on multiple platforms. | Processing (99.30000305175781%): Giraffe collects information as described below. | Processing (99.30000305175781%): Giraffeâs primary goals in collecting and using information is to create your account, provide Services to you, improve our Service, contact you, conduct research and create reports for internal use. | Processing (97.9000015258789%): Giraffeâs primary goals in collecting and using information is to create your account, provide Services to you, improve our Service, contact you, conduct research and create reports for internal use. | Required Purpose (98.80000305175781%): Giraffeâs primary goals in collecting and using information is to create your account, provide Services to you, improve our Service, contact you, conduct research and create reports for internal use. | Processing (99.0999984741211%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Processing (99.30000305175781%): This Privacy Policy (the âPolicyâ) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the âSitesâ) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the âServiceâ). | Required Purpose (94.80000305175781%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Required Purpose (85.5999984741211%): You are not required to provide personally identifiable information to visit the Site; however, in order to take advantage of certain features you may need to provide some personally identifiable information. | Processing (88.69999694824219%): If you wish to utilise advanced features of Site, such as automatic sign-in, storage of your and password(s) may be necessary. | Processing (87.19999694824219%): Whenever a social feature involves the disclosure of personally identifiable information about you to other people, Giraffe will either provide you with an opportunity to opt out of the disclosure or will seek your consent prior to making the disclosure. | Automated Decision Making (62.400001525878906%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Automated Decision Making (61.20000076293945%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Required Purpose (96.4000015258789%): We may use this information to monitor, develop and analyse your use of the Service. | Processing (70.5%): Facebook third party account login If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. | Processing (89.5999984741211%): Should you give us such permission, we will store the information received based on your use of the Services. | Processing (93.4000015258789%): We are responsible for processing personal data in accordance with the General Data Protection Regulation (âGDPRâ), an EU wide Regulation for the protection of personal data. | Processing (80.0999984741211%):  | Processing (86.5%):  | Technical Measure (96.9000015258789%): These Features may collect your IP address, which page you are visiting on our site, and may set a cookie to enable the Feature to function properly. | Processing (98.5%): iOS, Android and Windows Phone Platforms When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address). | Required Purpose (78.30000305175781%): This information is useful to us for troubleshooting and helps us understand usage trends. | Required Purpose (67.80000305175781%): This information is useful to us for troubleshooting and helps us understand usage trends. | Required Purpose (96.80000305175781%): This information is useful to us for troubleshooting and helps us understand usage trends. | Required Purpose (97.5%): We may collect and process your location data to provide location related Services and advertisements. | Technical Measure (90.30000305175781%): We may use various technologies to determine location, such as GPS, Wi-Fi or other network-based data such as IP address. | Technical Measure (66.19999694824219%): We may use various technologies to determine location, such as GPS, Wi-Fi or other network-based data such as IP address. | Processing (99.19999694824219%): We will not share your GPS geo-location with third parties without your consent. | Required Purpose (88.9000015258789%): Please note that we may share your anonymous location data with partners in order to improve the Services. | Processing (89.30000305175781%): Signing in with Facebook allows us to offer other functionalities such as to invite and play with friends, create challenges for friends and see friendsâ game progress. | Processing (99.0999984741211%): This unique user ID is stored in connection with your profile information to track the Giraffe games you are playing. | Required Purpose (88.0%): This unique user ID is stored in connection with your profile information to track the Giraffe games you are playing. | Required Purpose (75.19999694824219%):  | Required Purpose (88.30000305175781%): These services will authenticate your identity and provide you the option to share certain personal information with us such as your name, email address, and resume to pre-populate our sign up form. | Required Purpose (85.0999984741211%):  | Processing (93.69999694824219%): Such contact information will be used only for the purpose of sending communications to the addressee. | Required Purpose (67.4000015258789%): Such contact information will be used only for the purpose of sending communications to the addressee. | Processing (98.69999694824219%): You or the third party may contact us at support@giraffe-games.com to request the removal of this information from our database to the extent Giraffe stores any of this information. | Retention (78.5999984741211%): Customer Service We may collect your email address when you contact our customer service group and we may use that email address to contact you about your gaming experience with Giraffe games and notify you about company news and promotions. | Required Purpose (99.4000015258789%): Customer Service We may collect your email address when you contact our customer service group and we may use that email address to contact you about your gaming experience with Giraffe games and notify you about company news and promotions. | Required Purpose (62.0%): Push Notifications We may occasionally send you push notifications through our mobile applications to send you game updates, high scores and other service related notifications that may be of importance to you. | Required Purpose (66.4000015258789%): Push Notifications We may occasionally send you push notifications through our mobile applications to send you game updates, high scores and other service related notifications that may be of importance to you. | Required Purpose (64.4000015258789%): Push Notifications We may occasionally send you push notifications through our mobile applications to send you game updates, high scores and other service related notifications that may be of importance to you. | Processing (99.0999984741211%): The data thereby collected is presented to us in an anonymous form to include, for example, the percentage of users who complete a particular level. | Processing (85.4000015258789%): The data thereby collected is presented to us in an anonymous form to include, for example, the percentage of users who complete a particular level. | Processing (69.30000305175781%): Other Collection We may also acquire information from you through (1) your access and participation in message boards on the Service, (2) your participation in surveys regarding the Service or (3) your participation in a sweepstakes or contest through the Service. | Required Purpose (83.5999984741211%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Required Purpose (90.9000015258789%): Other Collection We may also acquire information from you through (1) your access and participation in message boards on the Service, (2) your participation in surveys regarding the Service or (3) your participation in a sweepstakes or contest through the Service. | Required Purpose (63.5%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Required Purpose (98.4000015258789%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Required Purpose (75.0999984741211%): We may provide you the opportunity to participate in a sweepstakes or contest through our Service. | Required Purpose (71.5999984741211%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Required Purpose (96.5999984741211%): We use this information to notify winners and award prizes, to monitor traffic or personalise the Service. | Required Purpose (98.80000305175781%): We use this information to notify winners and award prizes, to monitor traffic or personalise the Service. | Required Purpose (70.0999984741211%): We may use a third party service provider to conduct these sweepstakes or contests; that company is prohibited from using your usersâ personal information for any other purpose. | Required Purpose (93.0999984741211%): We may use a third party service provider to conduct these sweepstakes or contests; that company is prohibited from using your usersâ personal information for any other purpose. | Processing (97.9000015258789%): Cookies A cookie is a small text file that we transfer to your computer and/or device, to identify a userâs computer/device and to ârememberâ things about your visit, such as your preferences or a user name and password. | Required Purpose (96.5%):  | Required Purpose (90.9000015258789%):  | Processing (83.80000305175781%): Information contained in a cookie may be linked to your personal information, such as your user ID, for purposes such as improving the quality of our Service, tailoring recommendations to your interests, and making the Service easier to use. | Processing (94.19999694824219%): Information contained in a cookie may be linked to your personal information, such as your user ID, for purposes such as improving the quality of our Service, tailoring recommendations to your interests, and making the Service easier to use. | Required Purpose (98.5999984741211%): Information contained in a cookie may be linked to your personal information, such as your user ID, for purposes such as improving the quality of our Service, tailoring recommendations to your interests, and making the Service easier to use. | Required Purpose (99.0999984741211%):  | Technical Measure (98.19999694824219%): You can disable cookies at any time, although you may not be able to access or use features of the Service. | Organisational Measure (88.69999694824219%): If you no longer wish to receive certain email notifications you may opt-out at any time by following the unsubscribe link located at the bottom of each communication or by emailing us at support@giraffe-games.com. | Required Purpose (64.80000305175781%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Required Purpose (93.5999984741211%): You can disable cookies at any time, although you may not be able to access or use features of the Service. | Processing (89.9000015258789%): We may feature advertisements served by third parties that deliver cookies to your computer/device so the content you access and advertisements you see can be tracked. | Required Purpose (85.19999694824219%): We may feature advertisements served by third parties that deliver cookies to your computer/device so the content you access and advertisements you see can be tracked. | Required Purpose (98.4000015258789%): These advertisers may use information about your visits to our Service and third party sites and applications in order to measure advertisement performance and to provide advertisements about goods and services of interest to you. | Technical Measure (83.69999694824219%): You cannot use the Sites without accepting the use of cookies. | Required Purpose (90.80000305175781%): The cookies are used to support analytics and logged in users on the Site. | Technical Measure (96.4000015258789%): Clear Gifs (Web Beacons/Web Bugs) We employ or our third party tracking utility partner employs a software technology called clear gifs (a.k.a. | Technical Measure (99.19999694824219%): Clear Gifs (Web Beacons/Web Bugs) We employ or our third party tracking utility partner employs a software technology called clear gifs (a.k.a. | Technical Measure (96.80000305175781%):  | Technical Measure (82.30000305175781%):  | Required Purpose (75.0999984741211%): Web Beacons/Web Bugs), that help us better manage content on our site by informing us what content is effective. | Technical Measure (97.5999984741211%): Clear gifs are tiny graphics with a unique identifier, similar in function to cookies, and are used to track the online movements of Web users. | Required Purpose (84.80000305175781%): Clear gifs are tiny graphics with a unique identifier, similar in function to cookies, and are used to track the online movements of Web users. | Processing (70.0999984741211%): In contrast to cookies, which are stored on a userâs computer hard drive, clear gifs are embedded invisibly on Web pages or e-mails and are about the size of the period at the end of this sentence. | Technical Measure (78.5999984741211%): Mobile Analytics We use mobile analytics software to allow us to better understand the functionality of our Mobile Software on your device. | Technical Measure (82.69999694824219%):  | Required Purpose (95.9000015258789%): Mobile Analytics We use mobile analytics software to allow us to better understand the functionality of our Mobile Software on your device. | Technical Measure (80.69999694824219%): Third Party Services Our services may contain third party tracking tools from Google Analytics, our service provider. | Required Purpose (90.69999694824219%): Such third party may use cookies, APIs, and SDKs in our services to enable them to collect and analyse user information on our behalf. | Required Purpose (88.0999984741211%): Your interactions with these features are governed by the privacy policy of the company providing it. | Required Purpose (98.19999694824219%): Please review Facebookâs terms and conditions and privacy policy (here: https://www.facebook.com/about/privacy/update) because these third-party services are governed by their terms. | Required Purpose (67.5%): The third party may have access to information such as your device identifier, MAC address, IMEI, locale (specific location where a given language is spoken), geo-location information, and IP address for the purpose of providing their services under their respective privacy policies. | Required Purpose (65.30000305175781%): Ad Networks We do not serve ads within the Sites, but we do serve ads within our games and the advertisers we use have their own terms of service which are compatible with the terms of services of the mobile platforms. | Required Purpose (96.0%): They may use this information to provide advertisements of interest to you. | Processing (97.5999984741211%): In order to verify the installs, a device identifier may be shared with the advertiser. | Required Purpose (96.69999694824219%): We use information collected through our Service for purposes described in this Policy or disclosed to you in connection with our Service. | Required Purpose (89.80000305175781%): We use information collected through our Service for purposes described in this Policy or disclosed to you in connection with our Service. | Required Purpose (63.099998474121094%): For example, we may use your information to: – create game accounts and allow users to play our games; – identify and suggest connections with other Giraffe users; – operate and improve our Service; – understand you and your preferences to enhance your experience and enjoyment using our Service; – respond to your comments and questions and provide customer service; – provide and deliver products and services you request; – send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages; – communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners; – enable you to communicate with other users; and – link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services. | Required Purpose (89.19999694824219%): For example, we may use your information to: – create game accounts and allow users to play our games; – identify and suggest connections with other Giraffe users; – operate and improve our Service; – understand you and your preferences to enhance your experience and enjoyment using our Service; – respond to your comments and questions and provide customer service; – provide and deliver products and services you request; – send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages; – communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners; – enable you to communicate with other users; and – link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services. | Required Purpose (95.9000015258789%): For example, we may use your information to: – create game accounts and allow users to play our games; – identify and suggest connections with other Giraffe users; – operate and improve our Service; – understand you and your preferences to enhance your experience and enjoyment using our Service; – respond to your comments and questions and provide customer service; – provide and deliver products and services you request; – send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages; – communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners; – enable you to communicate with other users; and – link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services. | Processing (64.9000015258789%): If you no longer wish to receive certain email notifications you may opt-out at any time by following the unsubscribe link located at the bottom of each communication or by emailing us at support@giraffe-games.com. | Processing (80.0%): For example, we may use your information to: – create game accounts and allow users to play our games; – identify and suggest connections with other Giraffe users; – operate and improve our Service; – understand you and your preferences to enhance your experience and enjoyment using our Service; – respond to your comments and questions and provide customer service; – provide and deliver products and services you request; – send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages; – communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners; – enable you to communicate with other users; and – link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services. | Required Purpose (99.5%): For example, we may use your information to: – create game accounts and allow users to play our games; – identify and suggest connections with other Giraffe users; – operate and improve our Service; – understand you and your preferences to enhance your experience and enjoyment using our Service; – respond to your comments and questions and provide customer service; – provide and deliver products and services you request; – send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages; – communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners; – enable you to communicate with other users; and – link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services. | Processing (90.19999694824219%): We may use this information to monitor, develop and analyse your use of the Service. | Processing (94.80000305175781%):  | Processing (95.69999694824219%):  | Required Purpose (97.69999694824219%): An example of these services include analysing data and providing customer support. | Processing (97.9000015258789%): – We may release your information as permitted by law, such as to comply with a court order, or when we believe that release is appropriate to comply with the law; investigate fraud, respond to a government request, enforce or apply our rights; or protect the rights, property, or safety of us or our users, or others. | Required Purpose (72.0%): – We may release your information as permitted by law, such as to comply with a court order, or when we believe that release is appropriate to comply with the law; investigate fraud, respond to a government request, enforce or apply our rights; or protect the rights, property, or safety of us or our users, or others. | Required Purpose (83.30000305175781%):  | Required Purpose (94.0999984741211%): – We may release your information as permitted by law, such as to comply with a court order, or when we believe that release is appropriate to comply with the law; investigate fraud, respond to a government request, enforce or apply our rights; or protect the rights, property, or safety of us or our users, or others. | Processing (99.0999984741211%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Processing (99.30000305175781%):  | Required Purpose (76.5999984741211%): This includes exchanging information with other companies and organizations for fraud protection. | Organisational Measure (68.30000305175781%): You will be notified via email and/or notice on our site of any change in ownership or users of your personal information. | Organisational Measure (66.69999694824219%): You will be notified via email and/or notice on our site of any change in ownership or users of your personal information. | Organisational Measure (61.20000076293945%): Giraffe Games Limited and its affiliates (âGiraffeâ, âusâ, âourâ or âweâ) are dedicated to protecting the privacy rights of our users (âusersâ or âyouâ). | Organisational Measure (64.69999694824219%): Changes to the Policy We may update this privacy policy to reflect changes to our information practices. | Organisational Measure (72.80000305175781%): Changes to the Policy We may update this privacy policy to reflect changes to our information practices. | Organisational Measure (66.5999984741211%): If we make any material changes we will notify you by means of a notice on this Site prior to the change becoming effective. | Organisational Measure (93.69999694824219%): If we make any material changes we will notify you by means of a notice on this Site prior to the change becoming effective. | Organisational Measure (74.4000015258789%): Security We take reasonable measures to protect your information from unauthorised access or against loss, misuse or alteration by third parties. | Processing (93.69999694824219%): Although we make good faith efforts to store the information collected on the Service in a secure operating environment that is not available to the public, we cannot guarantee the absolute security of that information during its transmission or its storage on our systems. | Organisational Measure (63.29999923706055%): Further, while we attempt to ensure the integrity and security of our network and systems, we cannot guarantee that our security measures will prevent third-party âhackersâ from illegally obtaining access to this information. | Processing (80.0999984741211%): Further, while we attempt to ensure the integrity and security of our network and systems, we cannot guarantee that our security measures will prevent third-party âhackersâ from illegally obtaining access to this information. | Processing (77.69999694824219%):  | Retention (90.19999694824219%): Data Retention We will retain your information for as long as your account is active or as needed to provide you services. | Processing (95.69999694824219%): Data Retention We will retain your information for as long as your account is active or as needed to provide you services. | Required Purpose (83.0999984741211%): We will retain and use your information as necessary to comply with our legal obligations, resolve disputes, and enforce our agreements. | Processing (72.69999694824219%):  | Processing (81.80000305175781%):  | Processing (86.0%): Executing this request will depend on you deleting our games from your devices and clearing cookies from any device where you have accessed our Site. | Processing (97.9000015258789%): In some instances, personal information about you that is visible through gameplay such as username, avatar, your high scores may be cached on other playersâ devices and we may not be able to remove or update that data from those devices. | Processing (82.5999984741211%):  | Processing (79.4000015258789%): In some instances, personal information about you that is visible through gameplay such as username, avatar, your high scores may be cached on other playersâ devices and we may not be able to remove or update that data from those devices. | Processing (77.0999984741211%): You may have the right to request that data which you have provided to us is exported and provided to you, so you can </t>
+  </si>
+  <si>
     <t>Legal Basis (74.80000305175781%): For information about how we collect, use, share, and otherwise process consumer health data as defined under Washingtonâs My Health My Data Act and other similar state laws, please refer to the Consumer Health Data Privacy Policy. | Consent (95.9000015258789%): User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (âUser Contentâ) and the associated metadata, such as when, where, and by whom the content was created. | Consent (78.0%): Information, including text, images, and videos, found in your deviceâs clipboard, with your permission. | Consent (75.5999984741211%): Even if you are not a user, information about you may appear in User Content created or published by users on the Platform. | Consent (80.0%): We are committed to protecting and respecting your privacy. | Consent (80.5%): If you are still using an older version that allowed for collection of precise or approximate GPS information (last release in August 2020) and you granted us permission to do so, we may collect such information. | Legal Basis (98.5%):  | Consent (79.19999694824219%):  | Consent (79.30000305175781%): Consistent with your permissions, to provide you with location-based services, such as advertising and other personalized content. | Consent (87.30000305175781%): Even if you are not a user, information about you may appear in User Content created or published by users on the Platform. | Consent (79.0%):  | Consent (96.5%):  | Consent (74.5%): For any other purposes disclosed to you at the time we collect your information or pursuant to your consent. | Legal Basis (99.19999694824219%): Profiling: We do not engage in profiling which results in legal or similarly significant effects, as defined under applicable law. | Legal Basis (95.30000305175781%): How We Share Your Information We are committed to maintaining your trust, and while TikTok does not sell your personal information or share your personal information with third parties for purposes of cross-context behavioral advertising where restricted by applicable law, we want you to understand when and with whom we may share the Information We Collect for business purposes. | Consent (74.4000015258789%): Information, including text, images, and videos, found in your deviceâs clipboard, with your permission. | Legal Basis (99.30000305175781%): Profiling: We do not engage in profiling which results in legal or similarly significant effects, as defined under applicable law. | Legal Basis (76.9000015258789%): More information about requests that we received can be found here.Â While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. | Consent (91.0%): Your choices and communication preferences. | Consent (89.69999694824219%): Your Choices You may be able to control some of the Information We Collect through your device browser settings to refuse or disable Cookies. | Consent (77.80000305175781%):  | Consent (90.30000305175781%): Your choices and communication preferences. | Consent (97.9000015258789%): When you create User Content, we may upload or import it to the Platform before you save or post the User Content (also known as pre-uploading), for example, in order to recommend audio options, generate captions, and provide other personalized recommendations. | Consent (98.19999694824219%):  | Consent (98.5%): For information about how we collect, use, share, and otherwise process the personal information of users under age 13 (âChildrenâ), please refer to our Childrenâs Privacy Policy. | Consent (78.5%):  | Legitimate Interest (78.69999694824219%): We also retain information when necessary to comply with contractual and legal obligations, when we have a legitimate business interest to do so (such as improving and developing the Platform, and enhancing its safety, security and stability), and for the exercise or defense of legal claims. | Legitimate Interest (80.80000305175781%):  | Legitimate Interest (85.19999694824219%):  | Legitimate Interest (95.5%): We also retain information when necessary to comply with contractual and legal obligations, when we have a legitimate business interest to do so (such as improving and developing the Platform, and enhancing its safety, security and stability), and for the exercise or defense of legal claims.</t>
   </si>
   <si>
@@ -898,12 +2704,48 @@
     <t>Consent (95.19999694824219%): Also, if you see us refer to our "Terms," we mean the Terms of Service that you agree to when you sign up for our Services. | Consent (81.30000305175781%): Let’s get started with the controls you have over your information: Control Over Your Information Control over your information and settings is a core part of Snapchat experience. | Consent (90.4000015258789%): We want you to be in control of your information, so we provide you with a range of tools, including: Access and update your information. | Consent (98.0999984741211%): Change your permissions. | Consent (94.5999984741211%): In most cases, you can change your permissions at any time. | Consent (89.0%): Opt out of promotional messages. | Consent (92.69999694824219%):  | Consent (79.80000305175781%): Just navigate to your settings and you will see the options available to you. | Consent (78.30000305175781%):  | Consent (72.80000305175781%): Change your permissions. | Consent (72.30000305175781%): If you’ve explicitly granted device-level permissions, device information may also include information about your device phonebook (contacts and related information), images and other information from your device’s camera, photos, and microphone (like the ability to take photos, videos, view stored photos and videos, and access the microphone to record audio while recording video), and location information (precise location through methods like GPS signals). | Consent (85.4000015258789%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Consent (96.80000305175781%): Change your permissions. | Consent (77.19999694824219%): Change your permissions. | Consent (72.30000305175781%): You can learn about the different types of advertising and your choices about which ads you receive here. | Consent (71.80000305175781%): For example, the content you post to Stories, or your status as a premium subscriber, can be viewed by your Friends if you allow them. | Consent (79.69999694824219%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Consent (79.0999984741211%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Consent (77.5%):  | Legal Basis (81.0999984741211%): We share your information as necessary for the following legal, safety, and security reasons: comply with any valid legal process, governmental request, or applicable law, rule, or regulation. | Legal Basis (72.5999984741211%): Whenever we share information outside of where you live, we ensure safeguards are in place to protect the data as required by law where you live. | Legal Basis (76.4000015258789%): As a general rule, we keep information as long as you tell us to, and otherwise as long as we need it to provide our Services, or as required by law. | Consent (82.69999694824219%): That’s why from day one our philosophy has been to delete content by default and to give Snapchatters control by providing the tools that allow them to decide what happens with their content, like who to share it with or when to save it. | Legitimate Interest (88.5%): If we need it for other legitimate purposes, such as to prevent harm, investigate possible violations of our Terms of Service or other policies, investigate reports of abuse, or protect ourselves or others. | Legitimate Interest (79.0%): If we need it for other legitimate purposes, such as to prevent harm, investigate possible violations of our Terms of Service or other policies, investigate reports of abuse, or protect ourselves or others. | Legitimate Interest (78.19999694824219%): If we need it for other legitimate purposes, such as to prevent harm, investigate possible violations of our Terms of Service or other policies, investigate reports of abuse, or protect ourselves or others. | Legal Basis (79.0999984741211%): This includes enforcing, investigating, and reporting conduct that violates our Terms, policies, or the law, responding to requests from law enforcement, and complying with legal requirements. | Legal Basis (72.5%): As a general rule, we keep information as long as you tell us to, and otherwise as long as we need it to provide our Services, or as required by law. | Legal Basis (90.0999984741211%):  | Legal Basis (82.69999694824219%): Some jurisdictions require that we state our legal basis for processing data for particular purposes. | Legal Basis (81.69999694824219%): Some jurisdictions require that we state our legal basis for processing data for particular purposes.</t>
   </si>
   <si>
+    <t>Legal Basis (91.69999694824219%): Our privacy practices are subject to applicable laws in the places in which we operate. | Legal Basis (90.4000015258789%): This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. | Legal Basis (92.0%): In addition, please note the following if you use Uber in: ArgentinaDown Small The Agency of Access to Public Information, in its role of Regulating Body of Law 25.326, is responsible for receiving complaints and reports presented by any data subjects who believe their rights have been impacted by a violation of the local data protection regulation. | Legal Basis (86.0999984741211%): AustraliaDown Small You may contact Uber here regarding our compliance with the Australian Privacy Principles. | Legal Basis (91.19999694824219%):  | Legal Basis (84.4000015258789%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Legal Basis (85.30000305175781%):  | Legal Basis (91.30000305175781%):  | Legal Basis (97.5999984741211%):  | Legal Basis (94.30000305175781%):  | Legal Basis (89.4000015258789%): SwitzerlandDown Small Uber Switzerland GmbH (Stockerstrasse 33 8002 Zürich, Switzerland) is Uber’s appointed representative for purposes of the Federal Act on Data Protection and may be contacted here or by mail as relates to that act. | Legal Basis (93.5%):  | Legal Basis (85.9000015258789%): TaiwanDown Small Please see here for information on the measures adopted by Uber when conducting cross-border data transfers in accordance with Taiwan’s Personal Data Protection Act and its relevant regulations, as well as other related information. | Legal Basis (86.5999984741211%): United StatesDown Small Please go here for information regarding Uber’s privacy practices as relates to US state privacy laws, including the California Consumer Privacy Act. | Legal Basis (83.19999694824219%): United StatesDown Small Please go here for information regarding Uber’s privacy practices as relates to US state privacy laws, including the California Consumer Privacy Act. | Legal Basis (95.5%): United StatesDown Small Please go here for information regarding Uber’s privacy practices as relates to US state privacy laws, including the California Consumer Privacy Act. | Legal Basis (97.4000015258789%):  | Consent (77.5%): Data sharing and disclosure We share your data with other users where necessary to provide our services or features, at your request, or with your consent. | Legitimate Interest (82.4000015258789%): We also share data with our affiliates, subsidiaries, service providers and partners, for legal reasons, or in connection with claims or disputes. | Legitimate Interest (92.19999694824219%): We also share data with our affiliates, subsidiaries, service providers and partners, for legal reasons, or in connection with claims or disputes. | Consent (88.30000305175781%): Uber Privacy Notice: Drivers and Delivery People Previous version of the Privacy Notice I. | Consent (76.19999694824219%):  | Legal Basis (92.80000305175781%): Our privacy practices are subject to applicable laws in the places in which we operate. | Legal Basis (72.30000305175781%): Our legal bases for using your data C. | Consent (85.0999984741211%): Choice and transparency Uber enables you to access and/or control data that Uber collects, including through: Privacy settings Device permissions In-app ratings pages Marketing and advertising choices You may also request access to or copies of your data, make changes or updates to your account, request account deletion, or request that Uber restrict its processing of your data. | Consent (82.0999984741211%): Marketing and advertising choices Personalized marketing communications from UberDown Small You can choose here whether Uber may personalize marketing communications (such as emails, push notifications and in-app messages) about Uber products and services. | Legal Basis (96.69999694824219%): Uber may continue to process data after such objection or request to the extent necessary to provide our services, or required or permitted by law. | Legal Basis (98.30000305175781%): Our legal bases for using your data C. | Legal Basis (86.0999984741211%): Our legal bases for using your data Depending on where you use our services, and our purpose for using your data, Uber relies on the following legal bases for processing your data: Necessity to perform our contract with you Consent Uber's legitimate interests Legal obligation Data protection laws in some countries and areas, including the EEA, UK, Switzerland, Brazil and Nigeria, only allow Uber to use your data when certain circumstances defined under those laws apply. | Legal Basis (95.4000015258789%): Our privacy practices are subject to applicable laws in the places in which we operate. | Legal Basis (92.0%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Legal Basis (93.4000015258789%): This is called having a “legal basis” for using your data. | Contract (80.4000015258789%): This includes sharing data with law enforcement officials, public health officials, other government authorities, insurance companies, or other third parties as necessary to enforce our Terms and Conditions, user agreements, or other policies; to protect Uber’s rights or property or the rights, safety, or property of others; or in the event of a claim or dispute relating to the use of our services. | Consent (88.30000305175781%): Data uses Data used includes We use data to investigate or address claims or disputes relating to use of Uber’s services; to satisfy requirements under applicable laws, regulations, operating licenses or agreements, insurance policies; or pursuant to legal process or governmental request, including from law enforcement. | Consent (95.4000015258789%): Data sharing and disclosure We share your data with other users where necessary to provide our services or features, at your request, or with your consent. | Consent (82.5%): Where we rely on consent, you have the right to withdraw your consent at any time, in which case we will cease that collection and use of your data. | Legal Basis (71.80000305175781%): This is called having a “legal basis” for using your data. | Legitimate Interest (80.5999984741211%): This includes objecting to our use of data that is based on Uber’s legitimate interests. | Legal Basis (90.0999984741211%): Displaying ads that are targeted based on data about your current trip or delivery request Predicting and helping avoid pairings of users that may result in increased risk of conflict Preventing, detecting and combating fraud Verifying your account, identity or compliance with safety requirements Providing live support from safety experts during trips or deliveries Measuring the effectiveness of the marketing communications and ads Personalizing marketing communications and ads relating to Uber products and services, and those offered by other companies For non-marketing communications For research and development Legal obligation This legal basis applies when we are required to use your data to comply with the law. | Legal Basis (88.0999984741211%): We comply with applicable legal frameworks relating to the transfer of data. | Legal Basis (72.4000015258789%): Our privacy practices are subject to applicable laws in the places in which we operate. | Contract (71.5%): Data uses Data used includes We use data to investigate or address claims or disputes relating to use of Uber’s services; to satisfy requirements under applicable laws, regulations, operating licenses or agreements, insurance policies; or pursuant to legal process or governmental request, including from law enforcement. | Legal Basis (86.9000015258789%):  | Legal Basis (86.19999694824219%):  | Legal Basis (92.30000305175781%):  | Legal Basis (82.19999694824219%):  | Legal Basis (82.30000305175781%):  | Legal Basis (83.80000305175781%):  | Consent (76.0999984741211%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Consent (79.4000015258789%): Use of our services after an update constitutes consent to the updated notice to the extent permitted by law.</t>
+  </si>
+  <si>
+    <t>Consent (96.0999984741211%): By accessing or using our website, software, services, applications, products and content offered via Boomplay (collectively, the “ Services ”), you are accepting and consenting to the practices described in this Policy. | Consent (88.0%):  | Consent (93.69999694824219%): If you choose to link Boomplay to your social network or public forum account (including without limitation Facebook, Twitter or Google account), you may provide us or allow your social network to provide us with information from your social network or public forum accounts. | Consent (74.80000305175781%): We will ask for your consent to access your contact list and address book before doing so. | Consent (79.0999984741211%): | Boomplay Music Get APPGet APP What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player What’s Boomplay For Artists Advertising News Contact Go Web Player Privacy Policy EFFECTIVE AS OF OCTOBER 26, 2020 Welcome to Boomplay. | Consent (73.69999694824219%): You may at any time allow or disallow us to access your contact list and address book by changing your settings. | Consent (81.5%):  | Consent (81.69999694824219%): You may at any time allow or disallow us to access your contact list and address book by changing your settings. | Consent (95.0999984741211%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Consent (96.9000015258789%):  | Consent (87.4000015258789%): Unless you opt out of Cookies, we will assume you consent to the use of Cookies. | Legitimate Interest (96.0%): It is in our legitimate interest to promote the Services, and we may use information that you give to us, such as content that you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services. | Legal Basis (79.4000015258789%): We may share your information with law enforcement agencies, public or tax authorities or other organizations if legally required to do so, or if we have a good faith belief that such use is reasonably necessary to: • Comply with a legal obligation, process or request (including tax and related reporting requirements); • Enforce our Terms of Service and other agreements, policies, and standards, including investigation of any potential violation thereof; • Detect, prevent or otherwise address security, fraud or technical issues; • Protect the rights, property or safety of us, our users, a third party or the public as required or permitted by law (including exchanging information with other companies and organizations for the purposes of fraud protection and credit risk reduction). | Legal Basis (78.0999984741211%): We may share your information with law enforcement agencies, public or tax authorities or other organizations if legally required to do so, or if we have a good faith belief that such use is reasonably necessary to: • Comply with a legal obligation, process or request (including tax and related reporting requirements); • Enforce our Terms of Service and other agreements, policies, and standards, including investigation of any potential violation thereof; • Detect, prevent or otherwise address security, fraud or technical issues; • Protect the rights, property or safety of us, our users, a third party or the public as required or permitted by law (including exchanging information with other companies and organizations for the purposes of fraud protection and credit risk reduction). | Contract (95.0999984741211%): Without your consent, we will not share your contact details to our business partners to avoid direct contact from them, but we may share other information so that they can make you offers tailored to your requirements; • Cloud storage providers to store the information you provide and for disaster recovery services, as well as for the performance of any contract we have entered into with you; • Analytics and search engine providers that assist us in the improvement and optimization of Boomplay. | Contract (74.5999984741211%):  | Legal Basis (92.0999984741211%):  | Legal Basis (97.4000015258789%): Information Relating to Children The Services are not offered to children whose age makes it illegal to process their personal data or requires parental consent for the processing of their personal data under any applicable laws.</t>
+  </si>
+  <si>
+    <t>Legal Basis (97.5999984741211%): How do we respond to legal requests, comply with applicable law and prevent harm? | Legitimate Interest (72.0%): How do we respond to legal requests, comply with applicable law and prevent harm? | Legal Basis (92.80000305175781%): And if we sell or transfer all or part of our business to someone else, in some cases we’ll give the new owner your information as part of that transaction, but only as the law allows. | Legal Basis (88.5999984741211%): We also process information that we receive about you from other Meta Companies, according to their terms and policies and as permitted by applicable law. | Legal Basis (93.0%): We also process information that we receive about you from other Meta Companies, according to their terms and policies and as permitted by applicable law. | Legal Basis (93.4000015258789%): Why we share across the Meta Companies Meta Products share information with other Meta Companies: To promote safety, security and integrity and comply with applicable laws To personalize offers, ads and other sponsored or commercial content To develop and provide features and integrations To understand how people use and interact with Meta Company Products See some examples of why we share. | Legal Basis (98.30000305175781%): You may also have other privacy rights under applicable laws. | Legitimate Interest (83.0999984741211%): If we need it for other legitimate purposes, such as to prevent harm; investigate possible violations of our terms or policies; promote safety, security and integrity; or protect ourselves, including our rights, property or products In some instances and for specific reasons, we’ll keep information for an extended period of time. | Legitimate Interest (74.69999694824219%): Here’s more detail about who we share information with: Partners Advertisers and Audience Network publishers Partners who use our analytics services Partners who offer goods or services on our Products and commerce services platforms Integrated partners Vendors Measurement vendors Marketing vendors Service providers Service providers Third parties External researchers AI integrations Other third parties We also share information with other third parties in response to legal requests, to comply with applicable law or to prevent harm. | Legitimate Interest (77.5999984741211%): If we need it for other legitimate purposes, such as to prevent harm; investigate possible violations of our terms or policies; promote safety, security and integrity; or protect ourselves, including our rights, property or products In some instances and for specific reasons, we’ll keep information for an extended period of time. | Legitimate Interest (78.5999984741211%): Read more about how we use information to provide, personalize and improve our Products: How we show ads and other sponsored or commercial content How we use information to improve our Products How we use location-related information To promote safety, security and integrity We use information we collect to help protect people from harm and provide safe, secure Products. | Legitimate Interest (71.5999984741211%): If we need it for other legitimate purposes, such as to prevent harm; investigate possible violations of our terms or policies; promote safety, security and integrity; or protect ourselves, including our rights, property or products In some instances and for specific reasons, we’ll keep information for an extended period of time. | Consent (83.30000305175781%): We use information with special protections you choose to provide for these purposes, but not to show you ads. | Consent (84.0%): We decide how long we need information on a case-by-case basis. | Consent (84.80000305175781%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Consent (70.5999984741211%): In some countries, you may also be able to contact the Data Protection Officer for Meta Platforms, Inc., and depending on your jurisdiction, you may also contact your local Data Protection Authority (“DPA”) directly. | Legitimate Interest (76.5%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Sharing information with others, including law enforcement and to respond to legal requests. | Legal Basis (83.30000305175781%): How do we respond to legal requests, comply with applicable law and prevent harm? | Legal Basis (71.30000305175781%): How do we respond to legal requests, comply with applicable law and prevent harm? | Legal Basis (75.0999984741211%): Highlights We keep information as long as we need it to provide our Products, comply with legal obligations or protect our or other’s interests.</t>
+  </si>
+  <si>
+    <t>Legal Basis (99.19999694824219%): This WhatsApp Business App Privacy Policy (“Business App Privacy Policy”) explains WhatsApp’s data practices with respect to the Business Functions, and applies only to the extent information relating to users of the WhatsApp Business App would be considered personal data and is processed by WhatsApp as a controller, each under applicable law. | Legal Basis (96.0%): Assignment, Change Of Control, And Transfer In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws. | Legal Basis (76.4000015258789%): Law, Our Rights, And Protection Review the WhatsApp Privacy Policy to understand how we access, preserve, and share your information in response to legal obligations.</t>
+  </si>
+  <si>
+    <t>Consent (91.4000015258789%): If you choose not to provide the information needed to use a feature, you will be unable to use the feature. | Consent (95.9000015258789%): Permissions can be managed through your Settings menu on both Android and iOS devices. | Consent (96.0999984741211%):  | Consent (95.69999694824219%):  | Legal Basis (81.0999984741211%): You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. | Legal Basis (98.30000305175781%): You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. | Legal Basis (99.5%): You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. | Consent (96.0999984741211%): Additionally, we may use cookies to remember your choices, like your language preferences, to provide a safer experience, and otherwise to customize our Services for you. | Legal Basis (95.69999694824219%):  | Consent (72.0999984741211%): You should keep in mind that in general any user can capture screenshots of your chats or messages or make recordings of your calls with them and send them to WhatsApp or anyone else, or post them on another platform. | Consent (94.0999984741211%): Send Your Information To Those With Whom You Choose To Communicate. | Consent (92.5999984741211%):  | Consent (73.4000015258789%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Consent (81.4000015258789%):  | Consent (85.9000015258789%):  | Legal Basis (96.0%): Back to top Assignment, Change Of Control, And Transfer In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws. | Consent (79.69999694824219%): You can change your Services settings to manage certain information available to other users. | Legal Basis (81.5%): Please keep in mind that the countries or territories to which your information is transferred may have different privacy laws and protections than what you have in your home country or territory.</t>
+  </si>
+  <si>
+    <t>Legal Basis (96.30000305175781%):  | Legal Basis (92.0999984741211%): We are responsible for processing personal data in accordance with the General Data Protection Regulation (âGDPRâ), an EU wide Regulation for the protection of personal data. | Consent (60.70000076293945%): Facebook third party account login If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. | Consent (91.5999984741211%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Consent (72.9000015258789%): Whenever a social feature involves the disclosure of personally identifiable information about you to other people, Giraffe will either provide you with an opportunity to opt out of the disclosure or will seek your consent prior to making the disclosure. | Consent (72.30000305175781%): Whenever a social feature involves the disclosure of personally identifiable information about you to other people, Giraffe will either provide you with an opportunity to opt out of the disclosure or will seek your consent prior to making the disclosure. | Consent (86.69999694824219%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Consent (91.30000305175781%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Consent (64.0999984741211%): Your GPS geo-location is not accessed without your consent. | Consent (74.4000015258789%): If you no longer wish to allow us to track or use this information, you may turn it off at the device level. | Consent (96.69999694824219%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Consent (98.0999984741211%):  | Consent (97.0999984741211%):  | Consent (71.9000015258789%): We may provide you the opportunity to participate in a sweepstakes or contest through our Service. | Consent (70.4000015258789%): Participation in these sweepstakes and contests are voluntary and you therefore have a choice whether or not to disclose this information. | Consent (64.5999984741211%): Whenever a social feature involves the disclosure of personally identifiable information about you to other people, Giraffe will either provide you with an opportunity to opt out of the disclosure or will seek your consent prior to making the disclosure. | Legal Basis (74.0999984741211%): – We may release your information as permitted by law, such as to comply with a court order, or when we believe that release is appropriate to comply with the law; investigate fraud, respond to a government request, enforce or apply our rights; or protect the rights, property, or safety of us or our users, or others. | Legal Basis (84.5%): – We may release your information as permitted by law, such as to comply with a court order, or when we believe that release is appropriate to comply with the law; investigate fraud, respond to a government request, enforce or apply our rights; or protect the rights, property, or safety of us or our users, or others. | Legal Basis (71.5%): You have many rights in relation to your data under the GDPR, if you would like to exercise one of these rights, please contact us at: contact@giraffe-games.com You have the right to ; Access. | Legal Basis (91.4000015258789%): International Transfer Under EU data protection law, personal data transferred outside of the EU must have a legal mechanism for transfer (in order to ensure that the same protections are afforded to your personal data once it travels outside of the EU jurisdictions). | Legal Basis (94.9000015258789%): International Transfer Under EU data protection law, personal data transferred outside of the EU must have a legal mechanism for transfer (in order to ensure that the same protections are afforded to your personal data once it travels outside of the EU jurisdictions).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Art. 16 Right to rectification (73.0999984741211%): Your Rights You may submit a request to know, access, correct or delete the information we have collected from or about you at https://www.tiktok.com/legal/report/privacy. | Art. 17 Right to erasure (‘right to be forgotten’) (92.80000305175781%): We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â battery state, audio settings and connected audio devices. | Art. 17 Right to erasure (‘right to be forgotten’) (89.0999984741211%):  | Right (70.0999984741211%): We are committed to protecting and respecting your privacy. | Right (94.0999984741211%): For Legal Reasons We may disclose any of the Information We Collect to respond to subpoenas, court orders, legal process, law enforcement requests, legal claims, or government inquiries, and to protect and defend the rights, interests, safety, and security of the Platform, our affiliates, users, or the public. | Right (92.69999694824219%): If you are a parent or guardian, depending on your state of residence, you may have the ability to exercise certain rights over your child's or teen's account. | Right (87.30000305175781%):  | Right (88.9000015258789%):  | Right (87.19999694824219%): You may be entitled, in accordance with applicable law, to submit a request through an authorized agent. | Art. 17 Right to erasure (‘right to be forgotten’) (75.0999984741211%): </t>
   </si>
   <si>
     <t>Right (92.30000305175781%): Information for Law EnforcementSnap is committed to assisting law enforcement while respecting the privacy and rights of our users.Financial SextortionWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Combating Illicit DrugsWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Report a Safety ConcernIf you ever experience harassment, bullying, or any other safety concern, you can always report it right to us. | Art. 17 Right to erasure (‘right to be forgotten’) (87.9000015258789%): Delete your information. | Art. 17 Right to erasure (‘right to be forgotten’) (91.9000015258789%):  | Art. 17 Right to erasure (‘right to be forgotten’) (75.0%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Art. 17 Right to erasure (‘right to be forgotten’) (78.9000015258789%):  | Art. 21 Right to object (84.9000015258789%): Depending on where you live and the particular data we are processing, you may have the right to object to our processing of that information. | Art. 21 Right to object (79.0999984741211%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day.</t>
   </si>
   <si>
+    <t>Right (76.30000305175781%): KenyaDown Small You may contact Uber here with questions regarding Uber’s compliance with, or to request exercise of your rights under, Kenya’s Data Protection Act of 2019. | Right (89.9000015258789%): In addition, please note the following if you use Uber in: ArgentinaDown Small The Agency of Access to Public Information, in its role of Regulating Body of Law 25.326, is responsible for receiving complaints and reports presented by any data subjects who believe their rights have been impacted by a violation of the local data protection regulation. | Art. 17 Right to erasure (‘right to be forgotten’) (72.4000015258789%): Data retention and deletion III. | Art. 17 Right to erasure (‘right to be forgotten’) (72.4000015258789%):  | Art. 18 Right to restriction of processing (73.5%): Objections, restrictions and complaintsDown Small You may request that we stop using all or some of your data, or that we limit our use of your data. | Right (76.80000305175781%): (Burgerweeshuispad 301, 1076 HR Amsterdam, the Netherlands), regarding issues relating to Uber's processing of your personal data and your data protection rights. | Right (72.9000015258789%): Data access and portabilityDown Small Depending on where you are located, you may have the right to access your data and to portability of your data.</t>
+  </si>
+  <si>
+    <t>Right (94.80000305175781%): We may share your information with law enforcement agencies, public or tax authorities or other organizations if legally required to do so, or if we have a good faith belief that such use is reasonably necessary to: • Comply with a legal obligation, process or request (including tax and related reporting requirements); • Enforce our Terms of Service and other agreements, policies, and standards, including investigation of any potential violation thereof; • Detect, prevent or otherwise address security, fraud or technical issues; • Protect the rights, property or safety of us, our users, a third party or the public as required or permitted by law (including exchanging information with other companies and organizations for the purposes of fraud protection and credit risk reduction). | Art. 17 Right to erasure (‘right to be forgotten’) (75.9000015258789%): If you are a parent of a child under the Age Limit and become aware that your child has provided personal data to us, please contact us at privacy.boomplay@transsnet.com to delete such data. | Art. 17 Right to erasure (‘right to be forgotten’) (77.0%):  | Art. 16 Right to rectification (74.0%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Art. 16 Right to rectification (84.4000015258789%): Your rights You have the right to make a request to access and delete the personal data we hold about you, to rectify any personal data held about you that is inaccurate, the right to data portability and the right to request the suspension of the processing of your personal data. | Art. 16 Right to rectification (95.30000305175781%): Your rights You have the right to make a request to access and delete the personal data we hold about you, to rectify any personal data held about you that is inaccurate, the right to data portability and the right to request the suspension of the processing of your personal data.</t>
+  </si>
+  <si>
+    <t>Art. 17 Right to erasure (‘right to be forgotten’) (79.30000305175781%): How can you manage or delete your information and exercise your rights? | Right (74.80000305175781%): How can you manage or delete your information and exercise your rights? | Right (78.19999694824219%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Art. 17 Right to erasure (‘right to be forgotten’) (76.69999694824219%):  | Right (81.0999984741211%): You may also have other privacy rights under applicable laws.</t>
+  </si>
+  <si>
+    <t>Right (73.19999694824219%): Region Specific Information Additional information for users located in the US You can learn more about the consumer privacy rights that may be available to you, by reviewing the WhatsApp Business App United States Regional Privacy Notice here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right (75.69999694824219%): You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. | Right (71.30000305175781%):  | Art. 17 Right to erasure (‘right to be forgotten’) (84.4000015258789%): It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services. | Art. 17 Right to erasure (‘right to be forgotten’) (78.69999694824219%): </t>
+  </si>
+  <si>
+    <t>Art. 17 Right to erasure (‘right to be forgotten’) (66.19999694824219%): You or the third party may contact us at support@giraffe-games.com to request the removal of this information from our database to the extent Giraffe stores any of this information. | Right (76.80000305175781%): You have many rights in relation to your data under the GDPR, if you would like to exercise one of these rights, please contact us at: contact@giraffe-games.com You have the right to ; Access. | Right (85.5%): Giraffe Games Limited and its affiliates (âGiraffeâ, âusâ, âourâ or âweâ) are dedicated to protecting the privacy rights of our users (âusersâ or âyouâ). | Right (70.0%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Right (63.79999923706055%): We are entitled to request reasonable evidence to verify your identity before we provide you with information. | Right (66.69999694824219%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Art. 17 Right to erasure (‘right to be forgotten’) (72.69999694824219%):  | Art. 17 Right to erasure (‘right to be forgotten’) (76.19999694824219%): We are responsible for processing personal data in accordance with the General Data Protection Regulation (âGDPRâ), an EU wide Regulation for the protection of personal data. | Art. 17 Right to erasure (‘right to be forgotten’) (77.4000015258789%): In some circumstances you have the right for your personal information to be erased. | Right (60.70000076293945%): Giraffe Games Limited and its affiliates (âGiraffeâ, âusâ, âourâ or âweâ) are dedicated to protecting the privacy rights of our users (âusersâ or âyouâ). | Art. 18 Right to restriction of processing (70.19999694824219%): (contact us if you would like more information) Restriction of processing. | Art. 18 Right to restriction of processing (68.69999694824219%): You may have the right to request a restriction of the processing of your personal data, for example as an intermediate measure if we are investigating your claim for inaccurate data held. | Art. 18 Right to restriction of processing (75.5%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Art. 21 Right to object (90.0%): Right to object. | Art. 21 Right to object (87.69999694824219%): You have the right to object to the processing of personal data about you which is processed on the grounds of legitimate interests How long do we keep your data for? | Art. 21 Right to object (80.30000305175781%): You have the right to object to the processing of personal data about you which is processed on the grounds of legitimate interests How long do we keep your data for?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Controller (99.30000305175781%): ï»¿ privacy policy Privacy Policy As noted in the policy above, the English language version of the Privacy Policy and Terms of Use will govern your relationship with Pandas Of Caribbean Limited. | Data Controller (97.80000305175781%): </t>
   </si>
   <si>
@@ -916,6 +2758,24 @@
     <t xml:space="preserve">Data Controller (96.0999984741211%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Data Controller (99.4000015258789%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Data Controller (70.80000305175781%):  | Data Controller (94.69999694824219%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Data Source (92.5%): For example,  by default you are findable to others through your phone number and/or email address that you provided. | Data Subject (85.30000305175781%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Data Controller (99.69999694824219%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Data Controller (99.4000015258789%):  | Data Controller (72.0999984741211%): Information for Law EnforcementSnap is committed to assisting law enforcement while respecting the privacy and rights of our users.Financial SextortionWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Combating Illicit DrugsWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Report a Safety ConcernIf you ever experience harassment, bullying, or any other safety concern, you can always report it right to us. | Data Protection Officer (90.4000015258789%): </t>
   </si>
   <si>
+    <t>Data Controller (99.69999694824219%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Data Controller (99.80000305175781%):  | Data Controller (91.0%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Data Controller (98.4000015258789%): We’re committed to keeping that trust. | Data Subject (93.5999984741211%): In addition, please note the following if you use Uber in: ArgentinaDown Small The Agency of Access to Public Information, in its role of Regulating Body of Law 25.326, is responsible for receiving complaints and reports presented by any data subjects who believe their rights have been impacted by a violation of the local data protection regulation. | Authority (78.0999984741211%): You may also contact the Office of the Australian Information Commissioner here with concerns regarding such compliance. | Authority (90.69999694824219%): You may also contact the Office of the Data Protection Commissioner here with concerns regarding such compliance or exercise of your rights. | Data Controller (96.80000305175781%): This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. | Authority (82.19999694824219%): Law enforcement officials, public health officials and other government authorities. | Data Subject (87.9000015258789%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Data Source (72.0%): Uber business partners (account creation and access, and APIs). | Data Subject (71.0999984741211%): Users or others providing information in connection with customer support issues, claims or disputes. | Data Source (84.4000015258789%): Those who use Uber to either request, receive or provide services are referred to as “users” in this notice. | Data Subject (88.4000015258789%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Data Subject (72.5%): Receive services through Uber’s apps or websites requested by other account owners (a “Guest User”), including if you receive ride or delivery services ordered by Uber Health, Central, Uber Direct or Uber for Business customers (collectively, “Enterprise Customers”); or by friends, family members or other individual account owners, including via Uber Connect; or receive a gift card. | Data Controller (75.5%):  | Data Subject (75.80000305175781%): We may share your data as necessary to determine their referral bonus Trip/order infoTrip count Other Uber Eats users. | Authority (89.80000305175781%): This includes sharing data with law enforcement officials, public health officials, other government authorities, insurance companies, or other third parties as necessary to enforce our Terms and Conditions, user agreements, or other policies; to protect Uber’s rights or property or the rights, safety, or property of others; or in the event of a claim or dispute relating to the use of our services. | Authority (75.0%): Law enforcement officials, public health officials and other government authorities. | Data Subject (79.69999694824219%): AustraliaDown Small You may contact Uber here regarding our compliance with the Australian Privacy Principles. | Data Subject (95.69999694824219%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Authority (81.69999694824219%): In addition, depending on your location, you may have the right to file a complaint relating to Uber’s handling of your data with the data protection authority in your country. | Data Controller (99.0999984741211%):  | Data Controller (95.0999984741211%):  | Data Controller (97.30000305175781%):  | Data Controller (99.5999984741211%):  | Data Controller (97.0999984741211%):  | Data Controller (99.5999984741211%):  | Data Controller (82.0%):  | Data Protection Officer (84.69999694824219%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Data Protection Officer (84.69999694824219%):  | Data Protection Officer (75.80000305175781%):  | Data Controller (77.0%):  | Authority (78.5999984741211%): Name and contact information Information relating to law enforcement, health or other investigations b. | Authority (73.0%): When we transfer user data from the EEA, UK and Switzerland, we do so on the basis of the necessity to fulfill our agreements with you, consent, adequacy decisions regarding the country of transfer (available here, here or here, and transfer mechanisms such as the Standard Contractual Clauses adopted by the European Commission (and their approved equivalents for the UK and Switzerland), and the EU-US Data Privacy Framework (“EU-US DPF”), the UK Extension to the EU-US DPF, and the Swiss-US Data Privacy Framework (“Swiss-US DPF”), as set forth by the US Department of Commerce. | Authority (81.30000305175781%): UTI has certified to the United States Department of Commerce that it adheres to (1) the EU-US Data Privacy Framework Principles regarding the processing of personal data received from EEA member countries in reliance on the EU-US DPF, and from the UK (and Gibraltar) in reliance on the UK Extension to the EU-US DPF; and (2) the Swiss-US Data Privacy Framework Principles regarding the processing of personal data received from Switzerland in reliance on the Swiss-US DPF. | Authority (79.0%): Data uses Data used includes We use data to investigate or address claims or disputes relating to use of Uber’s services; to satisfy requirements under applicable laws, regulations, operating licenses or agreements, insurance policies; or pursuant to legal process or governmental request, including from law enforcement. | Authority (84.69999694824219%): This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. | Authority (92.80000305175781%): Uber is subject to the investigatory and enforcement powers of the US Federal Trade Commission. | Authority (90.5999984741211%):  | Authority (92.80000305175781%):  | Authority (93.0%):  | Authority (88.0999984741211%): You may also refer a complaint to your local data protection authority, and Uber will work with that authority to resolve that complaint.</t>
+  </si>
+  <si>
+    <t>Data Controller (97.0999984741211%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Data Source (77.5%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Data Controller (99.0999984741211%): | Boomplay Music Get APPGet APP What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player What’s Boomplay For Artists Advertising News Contact Go Web Player Privacy Policy EFFECTIVE AS OF OCTOBER 26, 2020 Welcome to Boomplay. | Data Controller (97.5%): | Boomplay Music Get APPGet APP What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player What’s Boomplay For Artists Advertising News Contact Go Web Player Privacy Policy EFFECTIVE AS OF OCTOBER 26, 2020 Welcome to Boomplay. | Data Subject (88.4000015258789%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Data Source (85.9000015258789%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Data Source (84.69999694824219%): • Information you share from your social networks. | Data Source (80.30000305175781%): This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. | Data Source (82.80000305175781%): • Information you share from your social networks. | Data Source (87.5%): If you choose to link Boomplay to your social network or public forum account (including without limitation Facebook, Twitter or Google account), you may provide us or allow your social network to provide us with information from your social network or public forum accounts. | Data Source (70.0999984741211%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Authority (96.5%): We may share your information with law enforcement agencies, public or tax authorities or other organizations if legally required to do so, or if we have a good faith belief that such use is reasonably necessary to: • Comply with a legal obligation, process or request (including tax and related reporting requirements); • Enforce our Terms of Service and other agreements, policies, and standards, including investigation of any potential violation thereof; • Detect, prevent or otherwise address security, fraud or technical issues; • Protect the rights, property or safety of us, our users, a third party or the public as required or permitted by law (including exchanging information with other companies and organizations for the purposes of fraud protection and credit risk reduction). | Authority (71.0%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Authority (79.0%): We may share your information with law enforcement agencies, public or tax authorities or other organizations if legally required to do so, or if we have a good faith belief that such use is reasonably necessary to: • Comply with a legal obligation, process or request (including tax and related reporting requirements); • Enforce our Terms of Service and other agreements, policies, and standards, including investigation of any potential violation thereof; • Detect, prevent or otherwise address security, fraud or technical issues; • Protect the rights, property or safety of us, our users, a third party or the public as required or permitted by law (including exchanging information with other companies and organizations for the purposes of fraud protection and credit risk reduction).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Controller (96.30000305175781%): Highlights We at Meta want you to understand what information we collect, and how we use and share it. | Data Controller (98.0%): What information do we collect? | Data Controller (75.19999694824219%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Data Controller (75.19999694824219%):  | Data Subject (92.9000015258789%): How do we use your information? | Data Source (71.5%): Learn more To communicate with you We communicate with you using information you've given us, like contact information you've entered on your profile. | Data Source (74.5999984741211%): Learn more To research and innovate for social good We use information we have, information from researchers and datasets from publicly available sources, professional groups and non-profit groups to conduct and support research. | Data Source (91.9000015258789%): Learn more To research and innovate for social good We use information we have, information from researchers and datasets from publicly available sources, professional groups and non-profit groups to conduct and support research. | Data Controller (99.19999694824219%):  | Data Source (76.80000305175781%):  | Data Controller (70.5%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Data Controller (87.9000015258789%):  | Data Protection Officer (80.19999694824219%): In some countries, you may also be able to contact the Data Protection Officer for Meta Platforms, Inc., and depending on your jurisdiction, you may also contact your local Data Protection Authority (“DPA”) directly. | Authority (79.9000015258789%):  | Authority (95.19999694824219%): These requests come from third parties such as civil litigants, law enforcement and other government authorities. | Data Controller (76.4000015258789%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Data Source (83.80000305175781%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Data Controller (94.5999984741211%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Data Controller (99.0999984741211%):  | Data Controller (97.19999694824219%):  | Data Controller (71.4000015258789%):  | Authority (71.19999694824219%): These requests come from third parties such as civil litigants, law enforcement and other government authorities. | Authority (90.30000305175781%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties For processing information when the law requires it: Where we are under an obligation to disclose information such as, for example, if we receive a valid legal request for certain information such as a search warrant, we will access, preserve and/or share your information with regulators, law enforcement or others. | Authority (95.30000305175781%): </t>
+  </si>
+  <si>
+    <t>Data Controller (99.69999694824219%): WhatsApp Business App Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어 FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Data Controller (99.80000305175781%):  | Data Controller (99.5999984741211%):  | Data Controller (99.5999984741211%):  | Data Controller (99.5%):  | Data Controller (98.5999984741211%):  | Data Controller (86.9000015258789%):  | Data Controller (95.5%):  | Data Controller (93.5%):  | Data Controller (93.9000015258789%):  | Data Subject (82.0999984741211%): WhatsApp Business App Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어 FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Data Controller (94.0999984741211%): WhatsApp Business App Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어 FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Data Controller (98.5999984741211%):  | Data Controller (99.69999694824219%):  | Data Controller (85.80000305175781%):  | Data Subject (84.0999984741211%): This WhatsApp Business App Privacy Policy (“Business App Privacy Policy”) explains WhatsApp’s data practices with respect to the Business Functions, and applies only to the extent information relating to users of the WhatsApp Business App would be considered personal data and is processed by WhatsApp as a controller, each under applicable law. | Data Controller (98.0%): WhatsApp Legal Info If you are located in the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Business App to you under this Terms of Service and this WhatsApp Business App Privacy Policy. | Data Controller (93.0%): Privacy Help Center Blog For Business Apps Log inDownload WhatsApp Business App Privacy Policy Effective July 14, 2025 Table of Contents WhatsApp Legal Info Scope of This WhatsApp Business App Privacy Policy Information We Collect How We Use Information Information You and We Share How We Work With Other Meta Companies Region Specific Information Assignment, Change Of Control, And Transfer Managing Your Information Law, Our Rights, And Protection Our Global Operations Updates to Our Privacy Policy Contact Us If you are located in the UK, WhatsApp LLC provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy. | Data Subject (83.5999984741211%): Privacy Help Center Blog For Business Apps Log inDownload WhatsApp Business App Privacy Policy Effective July 14, 2025 Table of Contents WhatsApp Legal Info Scope of This WhatsApp Business App Privacy Policy Information We Collect How We Use Information Information You and We Share How We Work With Other Meta Companies Region Specific Information Assignment, Change Of Control, And Transfer Managing Your Information Law, Our Rights, And Protection Our Global Operations Updates to Our Privacy Policy Contact Us If you are located in the UK, WhatsApp LLC provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy.</t>
+  </si>
+  <si>
+    <t>Data Controller (99.5%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Data Controller (99.80000305175781%):  | Data Controller (99.69999694824219%):  | Data Controller (99.19999694824219%):  | Data Controller (99.30000305175781%):  | Data Controller (99.19999694824219%):  | Data Controller (93.69999694824219%):  | Data Controller (96.30000305175781%):  | Data Controller (98.4000015258789%): WhatsApp Legal Info If you live outside the European Region or the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Services to you under this Terms of Service and Privacy Policy. | Data Controller (95.9000015258789%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Data Controller (97.9000015258789%): We are one of the Meta Companies. | Data Subject (97.5%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Data Controller (99.9000015258789%):  | Data Controller (71.69999694824219%):  | Data Controller (77.5999984741211%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Data Source (85.5%): For example, you cannot share your location with your contacts if you do not permit us to collect your location data from your device. | Data Source (72.5999984741211%): We receive information about you from other users. | Data Subject (89.30000305175781%): When a report is made, we collect information on both the reporting user and reported user. | Data Subject (86.9000015258789%): When a report is made, we collect information on both the reporting user and reported user. | Data Source (78.69999694824219%): This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. | Data Subject (89.30000305175781%): You can learn more further below in this Privacy Policy about the ways in which we share information across this family of companies. | Data Subject (77.4000015258789%): For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information.</t>
+  </si>
+  <si>
+    <t>Data Controller (98.5999984741211%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Data Controller (97.4000015258789%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Data Controller (91.30000305175781%):  | Data Controller (94.19999694824219%):  | Data Controller (92.5999984741211%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Data Controller (93.30000305175781%):  | Data Controller (65.30000305175781%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Data Controller (97.9000015258789%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Data Subject (94.5%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Data Controller (87.80000305175781%):  | Data Controller (65.80000305175781%): Facebook third party account login If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. | Data Source (82.0%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Data Source (64.0%):  | Data Subject (86.0999984741211%): You are not required to provide personally identifiable information to visit the Site; however, in order to take advantage of certain features you may need to provide some personally identifiable information. | Data Source (74.19999694824219%): Third Party Services Our services may contain third party tracking tools from Google Analytics, our service provider. | Data Source (63.20000076293945%): Game Data Collection Whenever you play our games, we collect anonymous data using the service of http://www.gameanalytics.com and sometimes use http://www.flurry.com/solutions/analytics(or such other service providers as we may deem appropriate). | Data Source (61.79999923706055%): We may provide you the opportunity to participate in a sweepstakes or contest through our Service. | Data Processor (61.0%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services.</t>
+  </si>
+  <si>
     <t>Third Party (97.9000015258789%):  | Third Party (97.5%):  | Third Party (98.80000305175781%):  | Third Party (86.80000305175781%): Information From Other Sources We may receive the information described in this Privacy Policy from other sources, such as: If you choose to sign-up or log-in to the Platform using a third-party service such as Facebook, Twitter, Instagram, or Google, or link your TikTok account to a third-party service, we may collect information from the serviceâfor example, your public profile information (such as nickname), email, and contact list. | Third Party (73.30000305175781%): Information From Other Sources We may receive the information described in this Privacy Policy from other sources, such as: If you choose to sign-up or log-in to the Platform using a third-party service such as Facebook, Twitter, Instagram, or Google, or link your TikTok account to a third-party service, we may collect information from the serviceâfor example, your public profile information (such as nickname), email, and contact list. | Third Party (98.69999694824219%): Advertisers, measurement and other partners share information with us about you and the actions you have taken outside of the Platform, such as your activities on other websites and apps or in stores, including the products or services you purchased, online or in person. | Third Party (98.80000305175781%):  | Third Party (93.80000305175781%):  | Third Party (96.0999984741211%): Advertisers, measurement and other partners share information with us about you and the actions you have taken outside of the Platform, such as your activities on other websites and apps or in stores, including the products or services you purchased, online or in person. | Third Party (90.5%): Advertisers, measurement and other partners share information with us about you and the actions you have taken outside of the Platform, such as your activities on other websites and apps or in stores, including the products or services you purchased, online or in person. | Third Party (95.0%): Information You Provide When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information: Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image. | Third Party (93.4000015258789%):  | Third Party (72.69999694824219%): Advertisers, measurement and other partners share information with us about you and the actions you have taken outside of the Platform, such as your activities on other websites and apps or in stores, including the products or services you purchased, online or in person. | Third Party (97.0999984741211%): We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (âCookiesâ) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. | Third Party (74.0999984741211%): We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (âCookiesâ) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. | Third Party (92.19999694824219%): To send promotional materials from us or on behalf of our affiliates and trusted third parties. | Third Party (99.30000305175781%): To send promotional materials from us or on behalf of our affiliates and trusted third parties. | Recipient (79.30000305175781%): We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (âCookiesâ) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. | Recipient (82.0999984741211%): We may obtain information about you from certain affiliated entities within our corporate group, including about your activities on their platform. | Recipient (89.0%): To learn more about how we share information with certain corporate group entities, see here. | Third Party (91.0999984741211%):  | Third Party (74.5%): We partner with third-party services (such as Facebook, Instagram, Twitter, and Google) to offer you a seamless sign-up, log-in, and content-sharing experience. | Third Party (97.69999694824219%):  | Third Party (97.69999694824219%): If you choose to allow a third-party service to access your account, we will share certain information about you with the third party. | Third Party (98.0%): If you choose to allow a third-party service to access your account, we will share certain information about you with the third party. | Third Party (80.4000015258789%): If you choose to engage in public activities on the Platform, you should be aware that any information you share may be read, collected, or used by other users. | Scale Non-EU (98.5999984741211%): TikTok may transmit your data to its servers or data centers outside of the United States for storage and/or processing. | Scale Non-EU (96.30000305175781%): Other entities with whom TikTok may share your data as described herein may be located outside of the United States. | Scale Non-EU (71.5%): TikTok may transmit your data to its servers or data centers outside of the United States for storage and/or processing. | Scale Non-EU (75.0%): Other Rights Sharing for Direct Marketing Purposes (Shine the Light) If you are a California resident, once a calendar year, you may be entitled to obtain information about personal information that we shared, if any, with other businesses for their own direct marketing uses.</t>
   </si>
   <si>
@@ -925,6 +2785,24 @@
     <t xml:space="preserve">Third Party (85.19999694824219%):  | Third Party (79.30000305175781%): Data We Receive From Others The last category of data we collect is information about you that we may receive from others, such as other users, our affiliates, and third parties. | Third Party (81.5%): Data We Receive From Others The last category of data we collect is information about you that we may receive from others, such as other users, our affiliates, and third parties. | Third Party (96.4000015258789%): Data We Receive From Others The last category of data we collect is information about you that we may receive from others, such as other users, our affiliates, and third parties. | Third Party (98.5%):  | Third Party (83.80000305175781%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Third Party (75.69999694824219%):  | Third Party (91.5%):  | Third Party (82.0999984741211%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Third Party (92.19999694824219%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Third Party (98.4000015258789%): Data We Receive From Others The last category of data we collect is information about you that we may receive from others, such as other users, our affiliates, and third parties. | Third Party (86.9000015258789%): Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines). | Third Party (95.9000015258789%): Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines). | Third Party (97.80000305175781%): Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines). | Third Party (81.9000015258789%): Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines). | Third Party (83.5999984741211%): Or if you provided access to your phone or third party platform contacts to make friending easier, you can change that later on in your app settings. | Third Party (76.69999694824219%): A note about information collected by cookies and other technologies: we may use these technologies to collect information when you interact with Services we offer through one of our partners. | Third Party (80.19999694824219%):  | Third Party (95.0999984741211%): A note about information collected by cookies and other technologies: we may use these technologies to collect information when you interact with Services we offer through one of our partners. | Third Party (99.0999984741211%):  | Third Party (98.69999694824219%):  | Third Party (75.0999984741211%):  | Recipient (95.19999694824219%): We share your information with business and integrated partners in order to provide the Services. | Third Party (72.69999694824219%): This does not include private communications. | Third Party (90.80000305175781%):  | Third Party (91.0999984741211%): Integrated Partners Our Services may contain content and integrations offered by our integrated partners. | Third Party (91.5%):  | Third Party (83.80000305175781%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Scale Non-EU (94.69999694824219%): To make that possible, we may collect your personal information from, transfer it to, and store and process it in the United States or other countries outside of where you live. | Scale Non-EU (70.4000015258789%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Scale Non-EU (86.5%): </t>
   </si>
   <si>
+    <t xml:space="preserve">Scale EU (92.0999984741211%):  | Scale Non-EU (97.0999984741211%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Scale Non-EU (94.4000015258789%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Scale Non-EU (86.5%): If you use Uber in Nevada or Washington, please go here for information regarding Uber’s practices as relates to collection and use of consumer health data under those states’ privacy laws. | Scale Non-EU (85.0999984741211%): If you use Uber in Nevada or Washington, please go here for information regarding Uber’s practices as relates to collection and use of consumer health data under those states’ privacy laws. | Third Party (71.30000305175781%): Please go here for more information about how ratings provided by other users are determined and used. | Third Party (92.30000305175781%): Marketing partners and service providers. | Recipient (75.69999694824219%):  | Third Party (98.9000015258789%):  | Third Party (82.5%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Third Party (84.0%):  | Recipient (71.69999694824219%): Please go here for more information about how ratings provided by other users are determined and used. | Recipient (96.30000305175781%): Marketing partners and service providers. | Recipient (89.5999984741211%): Marketing partners and service providers. | Recipient (82.80000305175781%): Receive services through Uber’s apps or websites requested by other account owners (a “Guest User”), including if you receive ride or delivery services ordered by Uber Health, Central, Uber Direct or Uber for Business customers (collectively, “Enterprise Customers”); or by friends, family members or other individual account owners, including via Uber Connect; or receive a gift card. | Recipient (83.19999694824219%): Depending on the feature used, may include: Account Location Trip/order info Uber business partners. | Recipient (72.0999984741211%): Personalizing marketing communications and ads relating to Uber products and services, and those offered by other companies. | Recipient (81.0999984741211%): AccountName Phone number Location Trip/order infoRequested pickup/dropoff Insurance companies. | Recipient (87.9000015258789%): If you are involved in an incident, or report or submit a claim to an insurance company relating to Uber’s services, Uber will share data with that insurance company for the purpose of adjusting or handling that claim. | Recipient (90.80000305175781%):  | Recipient (88.69999694824219%):  | Recipient (71.30000305175781%): Use features that enable you to create Lists or reviews of restaurants or merchants Upload photos and recordings (including those submitted for purposes of customer support) Provide ratings or feedback for drivers, delivery people, restaurants or merchants, or they provide feedback regarding you. | Third Party (98.69999694824219%): With Uber service providers and business partners These include the third parties, or categories of third parties, listed below. | Third Party (79.4000015258789%): Where a third party is identified, please go to their linked privacy notices for information regarding their collection and use of personal data. | Third Party (75.4000015258789%): Ad and marketing partners and providers, including ad and marketing publishers (such as social media platforms), ad networks and advertisers, third-party data providers, ad technology vendors, measurement and analytics providers, and other service providers. | Third Party (90.4000015258789%): Ad and marketing partners and providers, including ad and marketing publishers (such as social media platforms), ad networks and advertisers, third-party data providers, ad technology vendors, measurement and analytics providers, and other service providers. | Third Party (92.69999694824219%): Ad and marketing partners and providers, including ad and marketing publishers (such as social media platforms), ad networks and advertisers, third-party data providers, ad technology vendors, measurement and analytics providers, and other service providers. | Third Party (71.0999984741211%): We recommend that you read this along with our privacy overview, which highlights key points about our privacy practices. | Third Party (71.0999984741211%):  | Third Party (78.69999694824219%):  | Third Party (74.0%): Service providers who help us verify your identity or detect fraud.* Confirmation of whether your account information relates to known persons Name and contact information Information relating to the wireless carrier associated with your phone number Information from government-issued identification documents such as driver’s licenses or passports (such as identification numbers, expiration date, date of birth, and gender) d. | Third Party (78.80000305175781%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Third Party (77.5%): Google, in connection with the use of Google Maps in Uber’s apps. | Third Party (75.80000305175781%): This also includes ad intermediaries, such as Criteo, Google,  Rokt, The Trade Desk,   TripleLift   and others. | Recipient (91.5%): Users or others providing information in connection with customer support issues, claims or disputes. | Third Party (97.0%):  | Third Party (90.0999984741211%):  | Scale EU (70.0%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Scale Non-EU (85.69999694824219%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Scale Non-EU (72.0999984741211%): BrazilDown Small Please go here for information regarding Uber’s privacy practices as relates to Brazil’s General Data Protection Law (Lei Geral de Proteção de Dados - LGPD). | Scale Non-EU (75.80000305175781%): NigeriaDown Small You may contact Uber here regarding Uber’s compliance with, or to request exercise of your rights under, Nigeria’s Data Protection Act of 2023. | Scale Non-EU (86.0%): United StatesDown Small Please go here for information regarding Uber’s privacy practices as relates to US state privacy laws, including the California Consumer Privacy Act. | Scale EU (75.5%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Scale EU (78.0999984741211%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Scale Non-EU (75.69999694824219%): UTI has certified to the United States Department of Commerce that it adheres to (1) the EU-US Data Privacy Framework Principles regarding the processing of personal data received from EEA member countries in reliance on the EU-US DPF, and from the UK (and Gibraltar) in reliance on the UK Extension to the EU-US DPF; and (2) the Swiss-US Data Privacy Framework Principles regarding the processing of personal data received from Switzerland in reliance on the Swiss-US DPF. | Third Party (96.0999984741211%): Uber is responsible for the transfer of personal data, subject to its certification to third parties. | Scale EU (91.0%):  | Scale EU (72.0999984741211%): When we transfer user data from the EEA, UK and Switzerland, we do so on the basis of the necessity to fulfill our agreements with you, consent, adequacy decisions regarding the country of transfer (available here, here or here, and transfer mechanisms such as the Standard Contractual Clauses adopted by the European Commission (and their approved equivalents for the UK and Switzerland), and the EU-US Data Privacy Framework (“EU-US DPF”), the UK Extension to the EU-US DPF, and the Swiss-US Data Privacy Framework (“Swiss-US DPF”), as set forth by the US Department of Commerce. | Scale EU (73.19999694824219%): </t>
+  </si>
+  <si>
+    <t>Third Party (84.30000305175781%): For further information as to how and for what purpose the social network provider processes your data, please see their privacy policies. | Third Party (95.30000305175781%): • Information from third parties. | Third Party (95.5999984741211%): • Information from third parties. | Third Party (79.19999694824219%):  | Third Party (91.5%):  | Third Party (91.0%): If you choose to link Boomplay to your social network or public forum account (including without limitation Facebook, Twitter or Google account), you may provide us or allow your social network to provide us with information from your social network or public forum accounts. | Third Party (74.9000015258789%): If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list. | Third Party (73.19999694824219%):  | Third Party (98.69999694824219%):  | Third Party (99.19999694824219%):  | Third Party (90.69999694824219%): "Do not track" signals are preferences that users can set on their web browser to limit how their activity is tracked across third-party websites or online services. | Third Party (73.19999694824219%): How We Share Your Personal Data We may share your personal data with selected third parties in or outside your country, including without limitation: • Our business partners so that we can make you special offers via Boomplay; • With respect to on-screen ads, advertisers and advertising networks that require the data to select and serve advertisements to you and others. | Third Party (88.80000305175781%):  | Third Party (74.4000015258789%): We may also receive information from third parties (such as advertising networks and analytics providers) and from other sources, including business directories and other commercially or publicly available sources. | Recipient (77.0%): We may also disclose your information to third parties: • In the event that we sell or buy any business or assets, in which case we may disclose your data to the prospective seller or buyer of such business or assets; or • If we sell, buy, merge or partner with other companies or businesses, or sell some or all of our assets. | Third Party (79.0%): We may share your information with any member or affiliate of our group, which includes our subsidiaries, our ultimate holding company and its subsidiaries, and companies that we control, are controlled by or under common control, and our service providers and strategic business partners, and their respective subsidiaries, in each case in or outside your country, for the purposes set out above (“ How We Use Your Personal Data ”). | Third Party (96.69999694824219%): In any such cases, the third party company or business will adhere to the provisions of this Privacy Policy and where it will result in a change in any of the provisions herein, such changes will be communicated to you and you will be given the chance to consent or opt out at your discretion. | Third Party (76.19999694824219%): We may also receive information from third parties (such as advertising networks and analytics providers) and from other sources, including business directories and other commercially or publicly available sources. | Third Party (74.19999694824219%): We will, from time to time, include links to and from the websites of our partner networks, advertisers and affiliates. | Third Party (92.19999694824219%): Please read the following carefully to understand our views and practices regarding your personal data and how we will treat it. | Third Party (88.19999694824219%):  | Third Party (89.69999694824219%): We will, from time to time, include links to and from the websites of our partner networks, advertisers and affiliates.</t>
+  </si>
+  <si>
+    <t>Third Party (96.30000305175781%): How is your information shared on Meta Products or with integrated partners? | Third Party (97.80000305175781%): How do we share information with third parties? | Third Party (71.0%): Learn more To research and innovate for social good We use information we have, information from researchers and datasets from publicly available sources, professional groups and non-profit groups to conduct and support research. | Third Party (84.0%):  | Third Party (86.0999984741211%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Third Party (95.0%): How is your information shared on Meta Products or with integrated partners? | Third Party (95.0999984741211%): Here's the information we collect: Your activity and information you provide Friends, followers and other connections App, browser and device information Information from partners, vendors and other third parties What if you don’t let us collect certain information? | Recipient (83.19999694824219%):  | Third Party (83.30000305175781%): These requests come from third parties such as civil litigants, law enforcement and other government authorities. | Scale Non-EU (74.19999694824219%): Privacy notice for United States residents How to contact Meta with questions Why and how we process your information Other policies and articles Settings Privacy Policy What is the Privacy Policy and what does it cover? | Scale Non-EU (86.30000305175781%): Privacy notice for United States residents How to contact Meta with questions Why and how we process your information Other policies and articles Settings Privacy Policy What is the Privacy Policy and what does it cover? | Scale Non-EU (85.5%): Learn more about how we transfer information to other countries. | Third Party (86.4000015258789%): To use less information that’s connected to individual users, in some cases we de-identify or aggregate information or anonymize it so that it no longer identifies you. | Third Party (77.5%): Here's the information we collect: Your activity and information you provide Friends, followers and other connections App, browser and device information Information from partners, vendors and other third parties What if you don’t let us collect certain information? | Third Party (98.5999984741211%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Third Party (98.69999694824219%):  | Third Party (98.5999984741211%):  | Third Party (98.0999984741211%): Learn more To provide measurement, analytics and business services Lots of people rely on our Products to run or promote their businesses or share content. | Third Party (90.80000305175781%): Your activity and information you provide: Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. | Third Party (98.69999694824219%): Your activity and information you provide: Information and content you provide, such as your name or email address Information from partners, vendors and third parties Sharing your contact, profile or other information with third parties upon your request: The type of third party and categories of information shared depend on the circumstances of what you ask us to share. | Third Party (73.80000305175781%): These requests come from third parties such as civil litigants, law enforcement and other government authorities.</t>
+  </si>
+  <si>
+    <t>Scale Non-EU (75.19999694824219%): Privacy Help Center Blog For Business Apps Log inDownload WhatsApp Business App Privacy Policy Effective July 14, 2025 Table of Contents WhatsApp Legal Info Scope of This WhatsApp Business App Privacy Policy Information We Collect How We Use Information Information You and We Share How We Work With Other Meta Companies Region Specific Information Assignment, Change Of Control, And Transfer Managing Your Information Law, Our Rights, And Protection Our Global Operations Updates to Our Privacy Policy Contact Us If you are located in the UK, WhatsApp LLC provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy. | Scale EU (81.30000305175781%): If you are located in the European Region, WhatsApp Ireland Ltd. | Third Party (98.9000015258789%): Business Functions may be offered by WhatsApp, third parties and/or Meta, via integrations into our Business App, and may be subject to the third parties’ own terms of service and privacy policies. | Third Party (77.5999984741211%): WhatsApp Business App Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어 FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Third Party (75.5999984741211%):  | Recipient (79.69999694824219%): Assignment, Change Of Control, And Transfer In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws.</t>
+  </si>
+  <si>
+    <t>Scale EU (78.4000015258789%): Privacy Help Center Blog For Business Apps Log inDownload WhatsApp Privacy Policy Effective January 4, 2021archived versions If you live in the European Region, WhatsApp Ireland Limited provides the Services to you under this Terms of Service and Privacy Policy. | Scale Non-EU (74.30000305175781%): If you live in the UK, WhatsApp LLC provides the Services to you under this Terms of Service  and Privacy Policy. | Third Party (92.80000305175781%): Many businesses rely on WhatsApp to communicate with their customers and clients. | Third Party (98.69999694824219%): We work with businesses that use Meta or third parties to help store and better manage their communications with you on WhatsApp. | Third Party (87.5999984741211%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Third Party (89.0999984741211%): Many businesses rely on WhatsApp to communicate with their customers and clients. | Third Party (92.9000015258789%):  | Third Party (98.9000015258789%):  | Third Party (71.80000305175781%): In addition, some businesses might be working with third-party service providers (which may include Meta) to help manage their communications with their customers. | Third Party (86.9000015258789%):  | Third Party (91.5999984741211%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Third Party (91.9000015258789%):  | Recipient (82.30000305175781%):  | Third Party (98.4000015258789%):  | Third Party (99.5999984741211%):  | Third Party (74.69999694824219%): We allow you to use our Services in connection with third-party services and Meta Company Products. | Third Party (93.0999984741211%):  | Third Party (88.19999694824219%):  | Third Party (86.19999694824219%):  | Recipient (82.0%): Many businesses rely on WhatsApp to communicate with their customers and clients. | Third Party (95.9000015258789%):  | Third Party (98.5%):  | Third Party (79.5999984741211%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Third Party (98.5999984741211%):  | Third Party (99.0%): If you interact with a third-party service or another Meta Company Product linked through our Services, such as when you use the in-app player to play content from a third-party platform, information about you, like your IP address and the fact that you are a WhatsApp user, may be provided to such third party or Meta Company Product. | Third Party (83.30000305175781%):  | Recipient (79.69999694824219%): Back to top Assignment, Change Of Control, And Transfer In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws. | Third Party (74.5999984741211%): As part of the Meta Companies, WhatsApp partners with Meta to offer experiences and integrations across Meta’s family of apps and products. | Scale Non-EU (97.0%): Your information may, for example, be transferred or transmitted to, or stored and processed in, the United States; countries or territories where the Meta Companies’ affiliates and partners, or our service providers are located; or any other country or territory globally where our Services are provided outside of where you live for the purposes as described in this Privacy Policy. | Third Party (71.69999694824219%): In addition, some businesses might be working with third-party service providers (which may include Meta) to help manage their communications with their customers. | Scale Non-EU (93.30000305175781%): WhatsApp uses Meta’s global infrastructure and data centers, including in the United States.</t>
+  </si>
+  <si>
+    <t>Third Party (84.0999984741211%): Facebook third party account login If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. | Third Party (98.80000305175781%): We use third parties to store information on servers located in the European Union and may store information on servers and equipment in other jurisdictions from time to time. | Scale EU (83.0999984741211%): We use third parties to store information on servers located in the European Union and may store information on servers and equipment in other jurisdictions from time to time. | Third Party (84.5%): In order to access your third party message accounts, you must enter your applicable user name(s) and password(s). | Third Party (98.5999984741211%):  | Third Party (99.0%): Facebook third party account login If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. | Third Party (75.80000305175781%):  | Third Party (92.0%): Please note that we may share your anonymous location data with partners in order to improve the Services. | Third Party (81.30000305175781%): Facebook third party account login If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. | Third Party (73.4000015258789%): We may use a third party service provider to conduct these sweepstakes or contests; that company is prohibited from using your usersâ personal information for any other purpose. | Third Party (97.19999694824219%):  | Third Party (93.4000015258789%): These advertisers may use information about your visits to our Service and third party sites and applications in order to measure advertisement performance and to provide advertisements about goods and services of interest to you. | Third Party (61.5%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Third Party (96.4000015258789%):  | Third Party (96.9000015258789%): Contact us Contact Information Giraffe Games Limited, 26 Upper Pembroke Street, Dublin 2 If you have any questions about this Policy, please contact us at contact@giraffe-games.com The Privacy Policy, together with any game license agreement are to be read as a whole and form an integral part of the Terms of Use. | Third Party (70.0%): Since the third party advertising companies associate your computer/device with a number, they will be able to recognise your computer/device each time they send you an advertisement. | Third Party (66.0999984741211%): These agents and service providers may have access to your personal information in connection with the performance of services for Giraffe. | Third Party (95.80000305175781%): – We may share aggregate or anonymous information about you with advertisers, publishers, business partners, sponsors, and other third parties. | Third Party (94.0%): – We may share aggregate or anonymous information about you with advertisers, publishers, business partners, sponsors, and other third parties. | Third Party (88.4000015258789%): – We may share aggregate or anonymous information about you with advertisers, publishers, business partners, sponsors, and other third parties. | Third Party (99.0999984741211%): – We may share aggregate or anonymous information about you with advertisers, publishers, business partners, sponsors, and other third parties. | Scale EU (73.19999694824219%): Our hosted servers store your data in the EU. | Scale Non-EU (76.0999984741211%): International Transfer Under EU data protection law, personal data transferred outside of the EU must have a legal mechanism for transfer (in order to ensure that the same protections are afforded to your personal data once it travels outside of the EU jurisdictions).</t>
+  </si>
+  <si>
     <t>Data Controller (99.3%): ï»¿ privacy policy Privacy Policy As noted in the policy above, the English language version of the Privacy Policy and Terms of Use will govern your relationship with Pandas Of Caribbean Limited.</t>
   </si>
   <si>
@@ -940,6 +2818,24 @@
     <t>Data Controller (96.1%), Data Subject (85.3%), Non-Personal Data (90.2%), Personal Data (94.2%), Processing (99.6%), Required Purpose (84.4%), Retention (71.9%): PrivacyPrivacy PolicyThis Policy explains how we collect and use your data and how you can control your information. | Art. 17 Right to erasure (‘right to be forgotten’) (75.0%), Art. 21 Right to object (79.1%), Consent (85.4%), Data Controller (99.7%), Organisational Measure (94.8%), Processing (97.9%), Required Purpose (96.3%), Retention (90.6%), Scale Non-EU (70.4%), Technical Measure (90.4%), Third Party (83.8%): Privacy Policy | Snapchat Privacy Snap ValuesPolicyPolicyYour resource for understanding the rules and policies across Snapchat.Community GuidelinesWe created these guidelines to encourage the broadest range of self-expression, while striving to make sure Snapchatters can use our services safely every day. | Processing (95.9%), Required Purpose (76.0%): You control whether your Snaps can be saved within Snapchat.Privacy Through SecurityFeatures and recommendations to help secure your account. | Processing (99.0%): Teens on SnapchatAdditional protections for teens on Snapchat.Snap and AdsHow we collect, use, and share your data with respect to ads. | Processing (97.4%), Required Purpose (98.0%): That’s why we did our best to make our Privacy Policy brief, clear, and easy-to-read!Learn More SafetySafety CenterHere are some steps you can take to help stay safe!Safety PoliciesWe created these safety policies to help our community enhance their relationships with friends, family, and the world.Safety ResourcesWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters in need. | Data Controller (72.1%), Personal Data (99.0%), Right (92.3%): Information for Law EnforcementSnap is committed to assisting law enforcement while respecting the privacy and rights of our users.Financial SextortionWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Combating Illicit DrugsWe work with industry experts and non-governmental agencies to provide resources and support to Snapchatters.Report a Safety ConcernIf you ever experience harassment, bullying, or any other safety concern, you can always report it right to us. | Consent (79.1%), Organisational Measure (91.1%), Processing (98.7%), Required Purpose (94.8%): Information for ParentsThe Parent’s Guide to Snapchat covers how Snapchat works, the key protections we offer for teens, how to use our parental controls, and answers common questions.Learn More TransparencyTransparency ReportTransparency ReportTwice a year, we publish transparency reports to provide insight and visibility into the nature and volume of content and accounts reported to us.GlossaryDefinitions of commonly used terms, policies, and operational practices discussed in our transparency report. | Required Purpose (86.6%): Here we provide additional context and insight into our safety principles, policies, and practices, as well as links to various safety and privacy resources.Learn More News PrivacyPrivacyPrivacy Center Privacy Principles Privacy by Product Privacy Policy Teens on Snapchat Snap and Ads Privacy Through Security Privacy Policy Effective: April 7, 2025 Welcome to Snap Inc.’s Privacy Policy. | Processing (99.4%): If you’re looking for specific product privacy information, for example, how we process your Chats and Snaps, take a look at our Privacy by Product page. | Required Purpose (99.8%): For example, we process your information to provide you a more personalized experience, including to show you content and information that is most relevant to your experience, as well as more relevant advertisements. | Required Purpose (91.1%): Understanding your interests and preferences help us provide a better product experience. | Consent (95.2%): Also, if you see us refer to our "Terms," we mean the Terms of Service that you agree to when you sign up for our Services. | Consent (81.3%): Let’s get started with the controls you have over your information: Control Over Your Information Control over your information and settings is a core part of Snapchat experience. | Organisational Measure (82.0%): You can access, update, and delete your information, decide who can contact you, and download your data from within the Snapchat app. | Consent (90.4%): We want you to be in control of your information, so we provide you with a range of tools, including: Access and update your information. | Art. 17 Right to erasure (‘right to be forgotten’) (87.9%): Delete your information. | Processing (79.7%): You can also delete some information within our Services, like content you’ve saved to Memories, content you’ve shared with My AI, Spotlight submissions, and more. | Organisational Measure (84.0%): Control who can see your content. | Organisational Measure (71.7%): Control who can contact you. | Organisational Measure (94.7%): Snapchat is intended for close friends and family, that’s why we’ve built controls that help you decide who can contact you. | Organisational Measure (93.9%), Processing (95.3%): If you receive unwanted communications, you can always block and report that person. | Consent (98.1%): Change your permissions. | Consent (94.6%): In most cases, you can change your permissions at any time. | Data Source (92.5%), Personal Data (99.0%): For example,  by default you are findable to others through your phone number and/or email address that you provided. | Organisational Measure (79.4%), Personal Data (90.8%), Third Party (83.6%): Or if you provided access to your phone or third party platform contacts to make friending easier, you can change that later on in your app settings. | Consent (89.0%): Opt out of promotional messages. | Consent (79.8%), Required Purpose (74.6%): Just navigate to your settings and you will see the options available to you. | Art. 21 Right to object (84.9%): Depending on where you live and the particular data we are processing, you may have the right to object to our processing of that information. | Required Purpose (78.4%): Set advertising preferences. | Processing (96.9%), Technical Measure (73.6%): When you use our Services, such as Snapchat, we collect information you provide to us, generate information when you use our Services, and in some cases receive data from others. | Personal Data (87.9%), Required Purpose (97.5%): Below, we give you more details on the types of settings that are available, link out to our data download tool, and provide instructions on how to delete data or your account. | Personal Data (84.0%): To do this, we ask you to provide us with account details (information about you, like your name, username, email address, birthday, and phone number). | Personal Data (92.5%): When you set up your profile, you’ll also provide us with profile details (like your Bitmoji and profile picture). | Personal Data (97.8%), Required Purpose (95.0%): If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history). | Required Purpose (98.3%): This helps us better understand the way our community uses our Services so that we can make improvements. | Non-Personal Data (83.0%), Personal Data (74.0%), Processing (86.2%): This includes usage information (information about how you interact with our Services — for example, which Lenses you view and apply, your premium subscriptions, Stories you watch, and how often you interact with other Snapchatters) and content information (information about content you create or provide, your engagement with the camera and creative tools, your interactions with My AI, and metadata — for example, information about the content itself like the date and time it was posted and who viewed it). | Required Purpose (99.0%): Content information includes information based on the content of the image, video, or audio — so if you post a Spotlight of a basketball game, we may use that information to show you more content on Spotlight about basketball. | Non-Personal Data (96.9%), Personal Data (99.0%), Processing (99.6%), Technical Measure (98.1%): This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies). | Consent (72.3%), Personal Data (95.8%), Processing (97.7%): If you’ve explicitly granted device-level permissions, device information may also include information about your device phonebook (contacts and related information), images and other information from your device’s camera, photos, and microphone (like the ability to take photos, videos, view stored photos and videos, and access the microphone to record audio while recording video), and location information (precise location through methods like GPS signals). | Personal Data (99.1%): Of course, you’ll also provide us with information you send through or save within our Services, including content and information about that content, and content you share and generate with our AI Features (content, or “Inputs,” including text, images, video, audio, precise location, and engagement, used to generate content and responses, or “Outputs”). | Third Party (98.4%): Data We Receive From Others The last category of data we collect is information about you that we may receive from others, such as other users, our affiliates, and third parties. | Personal Data (99.0%), Processing (98.1%), Required Purpose (99.8%), Third Party (92.2%): This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. | Personal Data (94.2%), Required Purpose (99.3%), Third Party (97.8%): Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines). | Required Purpose (97.7%): Among other things, we use the information we collect to provide you with personalized products and Services that we work hard to build and improve. | Processing (93.0%), Required Purpose (98.9%): Keep Things Up &amp; Running (i.e., operate, deliver, and maintain our Services) We use the information we collect in order to operate, deliver, and maintain our Services. | Personal Data (71.1%), Required Purpose (74.2%): Previous ReportsTransparency Report archives Regional InformationEuropean UnionEU specific informationCalifornia California specific informationAustralia Australia specific informationIndiaIndia specific information ResourcesResearchersAccess for researchersAds GalleryFind European Union ads that delivered in the last 12 months and commercial content that’s live right now. | Personal Data (82.2%), Processing (89.4%), Required Purpose (99.8%): For example, by delivering a Snap you want to send to a friend or, if you share your location on Snap Map, to show you suggestions like places you might like in your neighborhood, content others have posted to the Map, or your friends if they’re sharing their location with you. | Required Purpose (89.7%): In some cases you may want to share content with your friends, and in other instances you may want to share it with the public. | Processing (92.0%), Required Purpose (96.6%): We also use some of your information to help keep our products up to date, for example to make sure that our Services work with the latest operating systems and devices. | Required Purpose (93.0%): To do so, we use information about you across different areas of the Services in order to add context to your Snapchat experience. | Required Purpose (97.5%): Personalize Your Experience &amp; Give Context We offer personalized Services to Snapchatters. | Required Purpose (83.0%): Personalization can also help with suggesting friends or recommending a new friend to send a Snap to based on who you Snap with the most. | Required Purpose (96.1%): We may show recommended places on the Snap Map, generate stickers, or even generate Snaps and other content using AI, infer your interests based on your content or activity, or customize the content we show you, including ads. | Required Purpose (76.2%): Personalization also includes tailoring your experience based on who you interact with most and what your friends are doing, including showing you content your friends create, like, or enjoy on Spotlight or Place recommendations that are popular with your friends. | Required Purpose (79.1%): Our goal is to continuously provide you with more relevant and interesting content. | Personal Data (71.3%), Technical Measure (96.5%): For example, if you watch a lot of sports content, but skip content with hair and makeup tips, our recommendation algorithms will prioritize sports, but not those makeup tips. | Automated Decision Making (93.8%): For example, we automatically tag content with labels based on the content, your location, or the time of day. | Required Purpose (98.0%): We use your interests and preferences from the information we’ve collected to personalize, target, and measure ads. | Consent (72.3%): You can learn about the different types of advertising and your choices about which ads you receive here. | Required Purpose (93.4%): You can learn more about how we collect, use, and share your information for advertising purposes here. | Third Party (95.1%): A note about information collected by cookies and other technologies: we may use these technologies to collect information when you interact with Services we offer through one of our partners. | Required Purpose (98.5%): For example, we may use information collected on an advertiser’s website to show you more relevant ads. | Required Purpose (80.9%): Keep in mind, though, that removing or rejecting cookies could affect the availability and functionality of our Services. | Non-Personal Data (83.8%), Required Purpose (71.4%): This Policy covers our Snapchat app as well as our other products, services, and features, such as Bitmoji, Spectacles, and our advertising and commerce initiatives. | Required Purpose (87.4%): Develop &amp; Improve Features, Algorithms &amp; Machine Learning Models Our teams are constantly coming up with new ideas for features and ways to improve our Services. | Technical Measure (96.3%): For example, if you watch barista content on Spotlight, talk to My AI about your favorite espresso machine, or save a lot of coffee-related Snaps in your Memories, we may highlight coffee shops on the Snap Map when you visit a new city or show you content about coffee that you may find interesting or relevant. | Technical Measure (91.5%): In order to do this, we also develop and improve the algorithms and machine learning models (an expression of an algorithm that combs through significant amounts of data to find patterns or make predictions) that make our features and Services work, including through generative AI features (artificial intelligence capable of generating text, images, or other media, using generative models. | Required Purpose (97.9%): We use algorithms and machine learning models for personalization, advertising, safety and security, fairness and inclusivity, augmented reality, and to prevent abuse or other Terms of Service violations. | Personal Data (99.1%), Required Purpose (81.5%): Your information can help us decide what kind of improvements we should make, but we are always focused on privacy — and we don’t want to use more of your personal information than necessary to develop our features and models. | Required Purpose (95.7%): Analytics In order to understand what to build or how to improve our Services, we need to understand trends and demand for our features. | Processing (94.5%), Required Purpose (98.9%): For example, we monitor metadata and trends about Group Chat use to help decide whether we should change parts of the feature, like the maximum size of a Group. | Processing (96.0%), Required Purpose (96.0%): Studying data from Snapchatters can help us see trends in the ways that people use the Services. | Required Purpose (96.9%): This helps inspire us to improve Snapchat on a larger scale. | Required Purpose (99.5%): Based on this information, we will, among other things, create information about our users to help us understand demand. | Required Purpose (98.6%): Research We conduct research to better understand general consumer interests, trends, and how our Services are used by you and others in our community. | Required Purpose (85.2%): We perform analytics in order to identify, monitor, and analyze trends and usage. | Required Purpose (97.4%): This information, along with analytics (as we described above), helps us understand more about our community and about how our Services fit into the lives of those in our community. | Required Purpose (99.3%): Enhance the Safety &amp; Security of Our Services We use your information to enhance the safety and security of our Services, verify Snapchatter identity, and prevent fraud or other unauthorized or illegal activity. | Required Purpose (93.4%): For example, we provide two-factor authentication to help protect your account and can send you email or text messages if we notice any suspicious activity. | Processing (92.0%), Required Purpose (77.6%): We also scan URLs sent on Snapchat to see if that webpage is potentially harmful, and can give you a warning about it. | Required Purpose (94.2%): Contacting You Sometimes we’ll get in touch with you to promote new or existing features. | Required Purpose (89.1%): For example, we may use the Snapchat app, email, SMS, or other messaging platforms to share information about our Services and promotional offers that we think may interest you. | Required Purpose (88.3%): Other times, we need to communicate with you to provide information, alerts, or to send messages our users ask us to deliver at their request. | Required Purpose (78.3%): This may include sending communications through Snapchat, email, SMS, or other messaging platforms, where permitted, to deliver account status updates, security alerts, and Chat or friending reminders; it may also include fulfilling our user’s request to send invites or Snapchat content to non-Snapchatters. | Required Purpose (99.2%): In order to provide you, the Snapchatter community, and our business partners with the help needed to resolve issues with our Services, we often need to use the information we have collected to respond. | Required Purpose (95.5%): Enforce Our Terms &amp; Policies We use the data we collect to enforce our Terms and the law. | Legal Basis (79.1%), Required Purpose (84.2%): This includes enforcing, investigating, and reporting conduct that violates our Terms, policies, or the law, responding to requests from law enforcement, and complying with legal requirements. | Required Purpose (85.8%): For example, when unlawful content is posted on our Services, we may need to enforce our Terms and other policies. | Required Purpose (89.6%): In some cases, we may also use or share your information to cooperate with law enforcement requests, escalate safety issues to law enforcement, industry partners, or others, or comply with our legal obligations. | Processing (96.1%): How We Share Information This section explains who we share information with, what that information may include, and the reasons for sharing that information, including when we need to transfer it outside of the country it was collected from. | Required Purpose (98.5%): To provide our Services to you and our community, we may share your information with your friends on Snapchat or other Snapchatters. | Consent (71.8%): For example, the content you post to Stories, or your status as a premium subscriber, can be viewed by your Friends if you allow them. | Required Purpose (82.6%): When you have enabled Family Center, we share information about the connected teen account to the parent or guardian to provide insight about how the account is used, for example, who your Friends are on Snapchat or which friends you may be sharing your location with. | Required Purpose (98.4%): For example, we rely on such Service Providers to facilitate payments, measure and optimize the performance of ads, or protect the services. | Recipient (95.2%), Required Purpose (97.5%): We share your information with business and integrated partners in order to provide the Services. | Third Party (72.7%): This does not include private communications. | Non-Personal Data (94.3%): We share your information, such as device and usage information, with industry partners working to prevent fraud. | Legal Basis (81.1%): We share your information as necessary for the following legal, safety, and security reasons: comply with any valid legal process, governmental request, or applicable law, rule, or regulation. | Required Purpose (88.4%): investigate, remedy, or enforce potential Terms of Service and Community Guidelines violations. | Required Purpose (97.4%): We may share your information within those internal subsidiaries as needed to carry out our Services. | Third Party (91.1%): Integrated Partners Our Services may contain content and integrations offered by our integrated partners. | Required Purpose (91.0%): Examples include integrations in Lenses, Camera editing tools, to provide Scan results, and third-party developer integrations. | Consent (82.7%), Processing (92.0%): That’s why from day one our philosophy has been to delete content by default and to give Snapchatters control by providing the tools that allow them to decide what happens with their content, like who to share it with or when to save it. | Required Purpose (96.7%), Technical Measure (91.8%): On iOS we use Apple’s TrueDepth camera to improve the quality of Lenses. | Required Purpose (70.8%), Scale Non-EU (94.7%): To make that possible, we may collect your personal information from, transfer it to, and store and process it in the United States or other countries outside of where you live. | Legal Basis (72.6%), Organisational Measure (87.7%): Whenever we share information outside of where you live, we ensure safeguards are in place to protect the data as required by law where you live. | Required Purpose (87.8%): How Long We Keep Your Information In this section we provide you with information on how long we keep your information, why we keep your information, and also highlight how we may need to keep your information to comply with laws, courts, and other obligations. | Legal Basis (76.4%), Retention (87.3%): As a general rule, we keep information as long as you tell us to, and otherwise as long as we need it to provide our Services, or as required by law. | Retention (87.2%): For example, if you store something in Memories, we will keep it as long as you need it, but when you Chat with a friend, our systems are designed to delete Chats you send within 24 hours after your friend reads it (unless you’ve changed your default settings or decide to save it). | Required Purpose (99.1%): Here are some more factors we consider when we decide how long to keep your information: If we need the information to operate or provide our Services. | Required Purpose (94.2%): For example, we store your basic account details — like your name, phone number, and email address — to maintain your account. | Personal Data (74.8%), Retention (96.1%): Content GuidelinesAdditional standards for algorithmic recommendation beyond the creator’s friends or subscribers Creator Monetization Policy Content must adhere to the policies to be eligible for monetization. | Retention (93.9%): For example, we maintain your list of friends until you ask us to delete them since friends are key to expressing yourself. | Retention (92.8%): Similarly, we keep your shared list of contacts until you ask us to remove them in our app settings (note: updating your device permissions may not remove the contacts you’ve previously shared with Snapchat). | Retention (92.6%): For example, we store location information for different lengths of time based on how precise it is and which Services you use. | Retention (96.3%): If location information is associated with a Snap — like those saved to Memories or posted to Snap Map or Spotlight — we’ll retain that location as long as we store the Snap. | Processing (77.5%): Whether we retain your data depends on the specific feature, your settings, and how you’re using the Services. | Retention (95.2%): How long we need to retain the information to comply with certain legal obligations. | Legitimate Interest (88.5%): If we need it for other legitimate purposes, such as to prevent harm, investigate possible violations of our Terms of Service or other policies, investigate reports of abuse, or protect ourselves or others. | Legal Basis (82.7%): Some jurisdictions require that we state our legal basis for processing data for particular purposes. | Processing (93.5%): Object to processing. | Required Purpose (81.9%): Our Services are not directed to children under the age of 13, and you must confirm that you are 13 years or older in order to create an account and use our Services. | Organisational Measure (71.8%): If we have actual knowledge that you are under the age of 13 (or the minimum age at which a person may use the Services in your state, province, or country without parental consent, if greater), we will stop providing Services to you and delete your account and data. | Organisational Measure (73.5%): Download your data. | Organisational Measure (71.3%): Sometimes, we’ll let you know by revising the date at the top of the Privacy Policy that’s available on our website and mobile application. | Organisational Measure (74.5%): Other times, we may provide you with additional notice (such as adding a statement to our websites’ homepages or providing you with an in-app notification).</t>
   </si>
   <si>
+    <t>Consent (76.1%), Data Controller (99.7%), Data Protection Officer (84.7%), Data Subject (88.4%), Legal Basis (92.0%), Organisational Measure (77.3%), Personal Data (99.8%), Processing (96.1%), Required Purpose (77.5%), Retention (70.9%), Scale EU (78.1%), Third Party (82.5%): Uber Privacy Notice: Riders &amp; Order Recipients Skip to main content UberRide Drive Business Uber Eats About About us Our offerings How Uber works Sustainability Newsroom Investor relations Autonomous Blog Careers More No results EN Help Log in Sign up UberLog in Sign up , Uber Privacy Notice: Riders and Order Recipients When you use Uber, you trust us with your personal data. | Data Controller (98.4%): We’re committed to keeping that trust. | Authority (84.7%), Data Controller (96.8%), Legal Basis (90.4%), Processing (99.4%): This notice describes the personal data (“data”) we collect, how it’s used and shared, and your choices regarding this data. | Legal Basis (98.3%), Personal Data (94.9%), Processing (76.6%): Our legal bases for using your data C. | Legal Basis (95.4%): Our privacy practices are subject to applicable laws in the places in which we operate. | Processing (99.5%): The types of data processing that such laws require, allow, or prohibit vary globally. | Data Subject (93.6%), Legal Basis (92.0%), Right (89.9%): In addition, please note the following if you use Uber in: ArgentinaDown Small The Agency of Access to Public Information, in its role of Regulating Body of Law 25.326, is responsible for receiving complaints and reports presented by any data subjects who believe their rights have been impacted by a violation of the local data protection regulation. | Data Subject (79.7%), Legal Basis (86.1%): AustraliaDown Small You may contact Uber here regarding our compliance with the Australian Privacy Principles. | Authority (78.1%): You may also contact the Office of the Australian Information Commissioner here with concerns regarding such compliance. | Data Subject (95.7%), Legal Basis (84.4%), Processing (75.3%), Scale EU (75.5%), Scale Non-EU (97.1%): Colombia, Honduras and JamaicaDown Small “Riders” and “drivers” as used in this notice are known respectively as “lessees” and “lessors.” European Economic Area (“EEA”), United Kingdom (“UK”), and SwitzerlandDown Small Due to data protection and other laws in these regions, including the European Union’s General Data Protection Regulation (“GDPR”), Uber does not perform some of the data collections and uses described in this notice in the EEA, UK or Switzerland. | Processing (99.3%): Data collections and uses A. | Processing (98.0%): If you use Uber outside of these regions, your data may be collected and used for the purposes indicated with an asterisk. | Right (76.3%): KenyaDown Small You may contact Uber here with questions regarding Uber’s compliance with, or to request exercise of your rights under, Kenya’s Data Protection Act of 2019. | Authority (90.7%): You may also contact the Office of the Data Protection Commissioner here with concerns regarding such compliance or exercise of your rights. | Automated Decision Making (92.1%): Quebec, CanadaDown Small You may contact Uber here with questions about Uber’s use of your data for purposes of automated decision making, including regarding the factors considered in connection with such decision, to request correction of any personal data relating to such decisions, and to request review of any such decisions by Uber personnel. | Legal Basis (89.4%): SwitzerlandDown Small Uber Switzerland GmbH (Stockerstrasse 33 8002 Zürich, Switzerland) is Uber’s appointed representative for purposes of the Federal Act on Data Protection and may be contacted here or by mail as relates to that act. | Processing (97.5%): Legal framework for data transfers D. | Legal Basis (85.9%): TaiwanDown Small Please see here for information on the measures adopted by Uber when conducting cross-border data transfers in accordance with Taiwan’s Personal Data Protection Act and its relevant regulations, as well as other related information. | Legal Basis (95.5%), Scale Non-EU (86.0%): United StatesDown Small Please go here for information regarding Uber’s privacy practices as relates to US state privacy laws, including the California Consumer Privacy Act. | Personal Data (95.3%), Scale Non-EU (86.5%): If you use Uber in Nevada or Washington, please go here for information regarding Uber’s practices as relates to collection and use of consumer health data under those states’ privacy laws. | Retention (75.5%): We collect data when you create or update your Uber account. | Consent (88.3%), Personal Data (99.3%), Required Purpose (73.6%): Uber Privacy Notice: Drivers and Delivery People Previous version of the Privacy Notice I. | Personal Data (98.8%), Required Purpose (97.0%): We collect demographic data if necessary to enable certain features. | Personal Data (98.9%), Processing (87.7%), Required Purpose (95.4%): We collect or infer your gender to enable Women Rider Preference, and for marketing and advertising. | Personal Data (99.0%): Identity verification information. | Required Purpose (88.3%): This refers to the data that we collect to verify your account or identity. | Personal Data (99.3%): Government-issued identification documents, such as driver’s licenses or passports (which may contain identification photos and numbers, expiration date, date of birth, and gender) User-submitted selfies d. | Personal Data (98.3%): This notice describes how we collect and use your data if you request or receive products or services through Uber’s apps or websites, except when you use Uber Freight, Careem or Uber Taxi (South Korea). | Personal Data (99.2%), Retention (72.9%): For example: We collect your date of birth and/or age to verify your eligibility to use age-restricted products or services, such as Uber for teens, or if you purchase alcohol, tobacco or cannabis products. | Data Subject (72.5%), Non-Personal Data (89.9%), Personal Data (75.8%), Processing (78.3%), Recipient (82.8%), Required Purpose (95.0%): Receive services through Uber’s apps or websites requested by other account owners (a “Guest User”), including if you receive ride or delivery services ordered by Uber Health, Central, Uber Direct or Uber for Business customers (collectively, “Enterprise Customers”); or by friends, family members or other individual account owners, including via Uber Connect; or receive a gift card. | Personal Data (82.2%), Recipient (71.3%): Use features that enable you to create Lists or reviews of restaurants or merchants Upload photos and recordings (including those submitted for purposes of customer support) Provide ratings or feedback for drivers, delivery people, restaurants or merchants, or they provide feedback regarding you. | Processing (77.1%), Required Purpose (99.0%): Data controllers and Data Protection Officer B. | Recipient (71.7%), Third Party (71.3%): Please go here for more information about how ratings provided by other users are determined and used. | Personal Data (99.4%): Travel information. | Personal Data (99.6%): We collect travel itinerary information if you book bus, train or flight travel through Uber's apps. | Personal Data (97.8%): Location data. | Personal Data (89.3%), Processing (95.3%): If you request a ride, we track your driver’s location during your trip, and link that data to your account. | Required Purpose (95.2%): This allows us to display where you are on your trip. | Personal Data (81.8%): We also determine your approximate location, and can determine your precise location if you allow us to do so through the settings on your phone. | Retention (97.4%): If you do, we will collect your precise location from the time you request a ride or order until the ride is finished or your order is delivered. | Personal Data (96.4%): You can use Uber without letting us collect your precise location. | Personal Data (96.2%): However, it may be less convenient for you, including because you will have to type your location into your phone instead of allowing us to detect it for you. | Personal Data (99.1%): See “Choice and transparency” section below for information on how to control whether Uber may collect your precise location data. | Personal Data (74.3%), Required Purpose (85.0%): Legal information A. | Non-Personal Data (92.1%): This refers to data about how you interact with Uber’s apps and websites. | Non-Personal Data (91.4%), Processing (86.9%), Required Purpose (85.2%): Scope This notice applies when you use Uber’s apps or websites to request or receive products or services, including rides or deliveries. | Personal Data (86.8%): Device data. | Personal Data (97.2%): Communications data. | Personal Data (94.7%): Communication type (phone or text message) Content (including recordings of phone calls solely when users are notified of the recording in advance) Date and time 3. | Authority (82.2%), Required Purpose (72.0%): Law enforcement officials, public health officials and other government authorities. | Personal Data (98.7%), Third Party (74.0%): Service providers who help us verify your identity or detect fraud.* Confirmation of whether your account information relates to known persons Name and contact information Information relating to the wireless carrier associated with your phone number Information from government-issued identification documents such as driver’s licenses or passports (such as identification numbers, expiration date, date of birth, and gender) d. | Data Source (72.0%): Uber business partners (account creation and access, and APIs). | Processing (95.7%): The information received from Uber business partners depends on which partners you use to create or access your Uber account, or the API used. | Recipient (96.3%), Third Party (92.3%): Marketing partners and service providers. | Data Subject (71.1%), Recipient (91.5%): Users or others providing information in connection with customer support issues, claims or disputes. | Data Source (84.4%): Those who use Uber to either request, receive or provide services are referred to as “users” in this notice. | Required Purpose (99.8%): How we use data Uber uses data to enable reliable and convenient transportation, delivery, and other products and services. | Personal Data (95.3%), Required Purpose (88.6%): Payment information (including amount charged and payment method) Proof of delivery (including photo or signature) Special instructions, allergies or food preferences Statistics derived from past trip/order information, such as  Averages Cancellation rates Total trips/orders Trip or order details, including Date and time Requested pickup and dropoff addresses Distance traveled Restaurant or merchant name and location Items ordered c. | Required Purpose (97.3%): We also use data: To enhance the safety and security of our users and services, and to prevent and detect fraud For marketing and advertising To enable communications between users For customer support For research and development To send non-marketing communications to users In connection with legal proceedings 1. | Required Purpose (99.1%): To provide our services. | Required Purpose (99.5%): Uber uses data to provide, personalize, maintain, and improve our services. | Processing (72.7%), Required Purpose (99.0%): This includes: Enabling navigation to pickups and dropoffs, calculating ETAs and tracking the progress of rides or deliveries Matching you with available drivers or delivery people when you request transportation or deliveries Enabling features that involve data sharing, such as ETA sharing and fare splitting Enabling accessibility features Enabling features that involve account linking, such as linking with Uber partners’ loyalty programs Facilitating and optimizing rental car reservations, pickup and dropoff through Uber Rent Account Data from other sources Demographics Device Ratings Travel c. | Processing (98.3%), Required Purpose (98.1%): Data sharing and disclosure F. | Processing (78.8%), Required Purpose (82.2%): Processing payments and enabling payment and e-money products such as Uber Money. | Required Purpose (99.3%): MexicoDown Small Please go here for information regarding Uber’s privacy practices as relates to Mexico’s Personal Data Protection Law (Ley Federal de Protección de Datos Personales en Posesión de los Particulares), and here for information regarding Uber Money's processing of personal data. | Required Purpose (94.9%): Providing you with trip or delivery updates and generating receipts. | Required Purpose (97.9%): For safety, security, and fraud prevention and detection. | Required Purpose (99.7%): Uber uses data to help maintain the safety and security of our services and users. | Required Purpose (97.1%): Choice and transparency IV. | Personal Data (97.5%), Processing (97.0%): This includes: Verifying that you are who you say you are by cross-checking the account information you provide during signup (such as name, email, telephone number, date of birth or payment information) against third-party databases* Verifying that your account is being used by you and not someone else by: Collecting your ID number and/or a photo of your ID, and completing a verification to confirm that the ID is valid, unaltered and that no other account is associated with that document* Collecting a real-time selfie that we compare against the photo on your ID to confirm that it’s the same person* Verifying your identity and/or age by collecting a photo of your ID when you receive delivery of age-restricted items like alcohol, tobacco or cannabis, or use products like Uber Rent and Uber Connect Verifying, when you rent a bike or scooter through Uber, that you are wearing a helmet, or other mandatory safety gear, by collecting a real-time selfie and using object verification technology Verifying your eligibility to subscribe to an Uber One for Students membership Account Data from other sources (third-party databases) Identity verification info User content b. | Required Purpose (91.8%): Uber uses data (except Guest Users’ data) to market its services, and those of Uber partners. | Processing (92.2%), Required Purpose (87.7%): Request or receive food or other products and services for delivery or pickup, including via your Uber Eats or Postmates account, or through the guest checkout features that allow you to access delivery or pickup services without creating and/or signing into your account (an “Order Recipient”). | Required Purpose (96.6%): Data uses Data used includes This includes investigating and addressing user concerns, monitoring and improving our customer support responses and processes, and identifying potential participants in research studies relating to customer support issues. | Required Purpose (92.4%), Technical Measure (92.2%): Data uses Data used includes We use data for analysis, research and product development, including training machine learning models. | Authority (79.0%), Consent (88.3%), Contract (71.5%), Required Purpose (79.4%): Data uses Data used includes We use data to investigate or address claims or disputes relating to use of Uber’s services; to satisfy requirements under applicable laws, regulations, operating licenses or agreements, insurance policies; or pursuant to legal process or governmental request, including from law enforcement. | Automated Decision Making (93.9%), Organisational Measure (70.8%), Processing (99.2%): Core automated processes D. | Required Purpose (93.5%): Core automated processes Uber uses automated processes to enable certain parts of our services, including functions essential to our business such as matching, pricing and fraud prevention and detection. | Required Purpose (91.2%): Uber relies on automated processes to enable essential parts of our services, including matching (pairing users requesting and providing transportation and/or delivery services), pricing (calculating the amount owed for such services) and fraud detection and prevention. | Technical Measure (96.1%): MatchingDown Small Uber uses algorithms to efficiently match Riders and drivers, or delivery people and Order Recipients. | Non-Personal Data (74.1%), Personal Data (98.8%): Our algorithms then evaluate various factors to determine the best match, including your location, requested destination, the proximity and availability of drivers or delivery people, traffic conditions, and historical data (including, in some markets, whether the specific Rider and driver have previously reported having negative experiences with each other). | Processing (77.6%): The trip or delivery request is then communicated to the driver/delivery person matched through this process. | Organisational Measure (76.3%), Required Purpose (79.5%): We are constantly refining our matching process to provide the best experience to all users on our platform and may consider different factors depending on the location where you use Uber. | Required Purpose (90.8%): This encourages more drivers to serve the busy area over time and shifts Rider demand, to maintain reliability and restore balance. | Required Purpose (96.1%): Fraud prevention and detectionDown Small Uber uses algorithms and machine learning models to prevent and detect fraud against Uber or our users. | Personal Data (86.7%), Processing (93.4%): To do this, Uber performs real-time monitoring of information collected from or generated by users, including location data, payment information, and Uber usage. | Processing (87.2%), Required Purpose (95.9%): We also examine historical data and compare it against real-time data to help detect suspicious behavior. | Technical Measure (98.4%): Cookies and related technologies Uber and its partners use cookies and other identification technologies on our apps, websites, emails, and online ads for purposes described in this notice, and Uber’s Cookie Notice. | Technical Measure (96.6%): Cookies and related technologies E. | Processing (92.7%): Cookies are small text files that are stored on browsers or devices by websites, apps, online media, and ads. | Required Purpose (95.7%), Technical Measure (87.9%): Uber uses cookies and similar technologies for purposes such as: Authenticating users Remembering user preferences and settings Determining the popularity of content Delivering and measuring the effectiveness of advertising campaigns Analyzing site traffic and trends, and generally understanding the online behaviors and interests of people who interact with our services. | Required Purpose (94.8%): We may also allow others to provide audience measurement and analytics services for us, to serve ads on our behalf across the internet or for other companies’ products and services on our apps, and to track and report on the performance of those ads. | Required Purpose (81.7%), Technical Measure (96.7%): These entities may use cookies, web beacons, SDKs and other technologies to identify the devices used by visitors to our websites, as well as when they visit other online sites and services. | Consent (95.4%), Required Purpose (91.6%): Data sharing and disclosure We share your data with other users where necessary to provide our services or features, at your request, or with your consent. | Legitimate Interest (92.2%): We also share data with our affiliates, subsidiaries, service providers and partners, for legal reasons, or in connection with claims or disputes. | Personal Data (98.5%), Required Purpose (90.2%): In addition, if you create an account using an email address affiliated with an Uber for Business account owner (i.e., your employer), we may share your account data (such as name and email address) with such account owner, to help you expense trips or orders to that Uber for Business account.* We may also share information with that account owner about issues involving your trip, such as safety incidents or complaints. | Data Subject (75.8%), Required Purpose (92.6%): We may share your data as necessary to determine their referral bonus Trip/order infoTrip count Other Uber Eats users. | Recipient (83.2%): Depending on the feature used, may include: Account Location Trip/order info Uber business partners. | Recipient (72.1%): Personalizing marketing communications and ads relating to Uber products and services, and those offered by other companies. | Required Purpose (73.9%): We share data with companies whose apps or websites you access through Uber, including for purposes of promotions, contests or specialized services. | Recipient (81.1%): AccountName Phone number Location Trip/order infoRequested pickup/dropoff Insurance companies. | Recipient (87.9%), Required Purpose (78.7%): If you are involved in an incident, or report or submit a claim to an insurance company relating to Uber’s services, Uber will share data with that insurance company for the purpose of adjusting or handling that claim. | Required Purpose (78.5%): Data necessary to adjust or handle the claim, which may include: Account Communications between users Device Location Trip/order info Usage User content Merchants or restaurants. | Personal Data (98.6%), Retention (72.0%): If you add a restaurant or merchant loyalty membership number to your user account, we share that data with the restaurant/merchant when you place an order with them. | Third Party (98.7%): With Uber service providers and business partners These include the third parties, or categories of third parties, listed below. | Third Party (79.4%): Where a third party is identified, please go to their linked privacy notices for information regarding their collection and use of personal data. | Third Party (92.7%): Ad and marketing partners and providers, including ad and marketing publishers (such as social media platforms), ad networks and advertisers, third-party data providers, ad technology vendors, measurement and analytics providers, and other service providers. | Third Party (71.1%): We recommend that you read this along with our privacy overview, which highlights key points about our privacy practices. | Required Purpose (98.7%): Uber uses these vendors to reach or better understand current and potential users of Uber services or of our advertising partners, and measure and improve ad effectiveness. | Technical Measure (73.9%): Providers of bikes and scooters that can be rented through Uber apps, such as Lime and Tembici. | Technical Measure (75.7%): Service providers that provide us with artificial intelligence and machine learning tools and services. | Third Party (77.5%): Google, in connection with the use of Google Maps in Uber’s apps. | Third Party (75.8%): This also includes ad intermediaries, such as Criteo, Google,  Rokt, The Trade Desk,   TripleLift   and others. | Personal Data (92.2%), Required Purpose (87.0%): We share data including advertising or device identifier, hashed email address, approximate location, current trip or order information, and ad interaction data with these intermediaries to enable their services and for such other purposes as are disclosed in their privacy notices. | Required Purpose (76.2%): With Uber subsidiaries and affiliates We share data with our subsidiaries and affiliates to help us provide our services or conduct data processing on our behalf. | Authority (89.8%), Contract (80.4%), Required Purpose (98.5%): This includes sharing data with law enforcement officials, public health officials, other government authorities, insurance companies, or other third parties as necessary to enforce our Terms and Conditions, user agreements, or other policies; to protect Uber’s rights or property or the rights, safety, or property of others; or in the event of a claim or dispute relating to the use of our services. | Retention (88.0%): Data retention and deletion Uber retains your data for as long as necessary for the purposes described above. | Retention (97.0%): Uber retains your data for as long as necessary for the purposes described above, which varies depending on data type, the category of user to whom the data relates, the purposes for which we collected the data, and whether the data must be retained after an account deletion request for the purposes described below. | Required Purpose (82.0%), Retention (85.4%): For example, we retain data: For the life of your account if such data is necessary to provide our services (such as account data) For defined periods as necessary, including as necessary to meet tax, insurance, legal or regulatory requirements (for example, we retain transaction information for 7 years) You may request that we delete your account through the Privacy menus in the Uber app, or through Uber’s website (Riders and Order Recipients here; Guest Users here). | Required Purpose (94.3%), Retention (88.2%): Following an account deletion request, we delete your account and data, except as necessary for purposes of safety, security, fraud prevention or compliance with legal requirements, or because of issues relating to your account (such as an outstanding credit or an unresolved claim or dispute). | Retention (83.9%): We generally delete data within 90 days of an account deletion request, except where retention is necessary for the above reasons. | Processing (98.7%): The data we collect Uber collects data: 1. | Personal Data (75.3%): Privacy settings You can set or update your preferences regarding location data collection and sharing, emergency data sharing, and notifications in Uber’s Privacy Center, which is accessible via the Privacy menu in the Uber apps. | Organisational Measure (84.7%): Share live locationDown Small You can enable/disable Uber’s sharing of your mobile device real-time location data with your drivers or delivery people through your device settings, which are accessible via the Account &gt; Settings &gt; Privacy &gt; Location sharing menu in Uber’s apps. | Personal Data (94.6%): Gender identityDown Small You can update your gender information through the Account &gt; Settings &gt; Privacy &gt; Ads and Data &gt; Gender Identity menu in Uber’s apps. | Personal Data (90.7%): Address Email First and last name Login name and password Phone number Payment method (including related payment verification information) Profile picture Settings (including accessibility settings) and preferences Uber partner loyalty program information b. | Personal Data (73.4%): If you do, we will share data including your name and phone number; approximate location at the time the emergency call was placed; the car’s make, model, color, and license plate information; pickup and dropoff locations; and your driver’s name. | Required Purpose (92.1%): Third-party app access Down Small You may authorize third-party applications to access your Uber account data to enable additional features. | Consent (85.1%): Choice and transparency Uber enables you to access and/or control data that Uber collects, including through: Privacy settings Device permissions In-app ratings pages Marketing and advertising choices You may also request access to or copies of your data, make changes or updates to your account, request account deletion, or request that Uber restrict its processing of your data. | Consent (82.1%): Marketing and advertising choices Personalized marketing communications from UberDown Small You can choose here whether Uber may personalize marketing communications (such as emails, push notifications and in-app messages) about Uber products and services. | Personal Data (80.8%): Data sharing and trackingDown Small You can choose here whether Uber may share your data with third parties, or collect data regarding your visits and actions on third-party apps or websites, for purposes of personalized ads. | Personal Data (70.3%): Regardless of your location, you can access your data, including your profile data and trip or order history, through the Uber apps or website. | Processing (75.2%): Uber business partners (debit or credit cards). | Personal Data (96.3%): Changing or updating dataDown Small You can edit your name, phone number, email address, payment method, and profile picture through the Settings menu in Uber’s apps. | Art. 17 Right to erasure (‘right to be forgotten’) (72.4%): Data retention and deletion III. | Art. 18 Right to restriction of processing (73.5%): Objections, restrictions and complaintsDown Small You may request that we stop using all or some of your data, or that we limit our use of your data. | Legal Basis (96.7%): Uber may continue to process data after such objection or request to the extent necessary to provide our services, or required or permitted by law. | Authority (81.7%): In addition, depending on your location, you may have the right to file a complaint relating to Uber’s handling of your data with the data protection authority in your country. | Processing (98.5%): is the sole controller of the data processed by Uber when you use Uber’s services globally, except where it is a joint controller with other Uber affiliates. | Right (76.8%): (Burgerweeshuispad 301, 1076 HR Amsterdam, the Netherlands), regarding issues relating to Uber's processing of your personal data and your data protection rights. | Legal Basis (86.1%): Our legal bases for using your data Depending on where you use our services, and our purpose for using your data, Uber relies on the following legal bases for processing your data: Necessity to perform our contract with you Consent Uber's legitimate interests Legal obligation Data protection laws in some countries and areas, including the EEA, UK, Switzerland, Brazil and Nigeria, only allow Uber to use your data when certain circumstances defined under those laws apply. | Scale Non-EU (72.1%): BrazilDown Small Please go here for information regarding Uber’s privacy practices as relates to Brazil’s General Data Protection Law (Lei Geral de Proteção de Dados - LGPD). | Scale Non-EU (75.8%): NigeriaDown Small You may contact Uber here regarding Uber’s compliance with, or to request exercise of your rights under, Nigeria’s Data Protection Act of 2023. | Legal Basis (93.4%): This is called having a “legal basis” for using your data. | Required Purpose (93.4%): This legal basis applies when we must use your data in order to provide the services you request and meet our responsibilities under that contract. | Required Purpose (96.5%): Calculating rider/recipient prices and driver/delivery person fares Creating or updating your account Enabling services and features For customer support Enabling communications between you and your driver or delivery person Performing necessary operations to maintain our services Personalizing your account Processing payments Providing you with trip or delivery updates, generating receipts, and informing you of changes to our terms, services, or policies Consent This legal basis applies when we notify you of how we will collect and use your data, and you voluntarily agree to that use of your data (in some cases, by enabling that collection and use through a device or Uber setting). | Consent (82.5%): Where we rely on consent, you have the right to withdraw your consent at any time, in which case we will cease that collection and use of your data. | Required Purpose (72.8%): Personalizing ads relating to products and services offered by other companies Processing health data, or other sensitive data, depending on the region you live in Legitimate interests This legal basis applies when Uber has a legitimate purpose for using your data (such as for purposes of safety, security, and fraud prevention and detection), its processing of data is necessary for that purpose, and the benefit of such purpose is not outweighed by risks to your privacy (such as because you would not expect Uber’s use of your data, or because it would prevent you from exercising your rights). | Legitimate Interest (80.6%): This includes objecting to our use of data that is based on Uber’s legitimate interests. | Legal Basis (90.1%): Displaying ads that are targeted based on data about your current trip or delivery request Predicting and helping avoid pairings of users that may result in increased risk of conflict Preventing, detecting and combating fraud Verifying your account, identity or compliance with safety requirements Providing live support from safety experts during trips or deliveries Measuring the effectiveness of the marketing communications and ads Personalizing marketing communications and ads relating to Uber products and services, and those offered by other companies For non-marketing communications For research and development Legal obligation This legal basis applies when we are required to use your data to comply with the law. | Personal Data (96.9%): Legal framework for data transfers Uber opera</t>
+  </si>
+  <si>
+    <t>Art. 16 Right to rectification (74.0%), Data Controller (97.1%), Data Source (85.9%), Data Subject (88.4%), Personal Data (78.2%), Processing (95.4%): Boomplay is provided or controlled by TRANSSNET MUSIC LIMITED (hereinafter “ TML ”, “ we ” or “ us ”) We are committed to protecting and respecting your privacy. | Data Source (80.3%), Personal Data (99.6%), Processing (99.6%), Required Purpose (88.0%): This Privacy Policy (hereinafter the “ Policy ”) sets out the basis on which any personal data we collect from you, or that you provide to us, will be processed by us. | Consent (79.1%), Data Controller (99.1%), Organisational Measure (86.4%), Personal Data (97.2%), Required Purpose (73.5%), Technical Measure (86.9%): | Boomplay Music Get APPGet APP What’s BoomplayFor ArtistsAdvertisingNewsContactGo Web Player What’s Boomplay For Artists Advertising News Contact Go Web Player Privacy Policy EFFECTIVE AS OF OCTOBER 26, 2020 Welcome to Boomplay. | Consent (96.1%): By accessing or using our website, software, services, applications, products and content offered via Boomplay (collectively, the “ Services ”), you are accepting and consenting to the practices described in this Policy. | Processing (99.2%), Required Purpose (75.4%): The Types of Personal Data We Collect and Use We may collect and use the following information about you: • Information you share with us. | Processing (98.4%): This is the information about you or relating to you that is voluntarily shared by you on Boomplay. | Authority (71.0%), Personal Data (99.1%), Processing (97.8%): Information you share with us may include without limitation postings that you make on Boomplay (including your public profile, name, identification number, address, email address, social media login details, telephone number, information about your device, your browsing records, the comments you make on Boomplay, as well as account and billing details, the lists you create, and photos, videos and voice recordings as accessed with your prior consent through your device settings you turn on), any postings from others that you re-post and location data and log data associated with such postings. | Non-Personal Data (88.8%), Processing (79.8%), Retention (92.2%): Information you share with us will remain publicly-available for so long as you or a user that has shared such information retains it. | Data Source (84.7%): • Information you share from your social networks. | Consent (93.7%), Data Source (87.5%), Processing (96.6%), Third Party (91.0%): If you choose to link Boomplay to your social network or public forum account (including without limitation Facebook, Twitter or Google account), you may provide us or allow your social network to provide us with information from your social network or public forum accounts. | Personal Data (96.9%), Processing (99.1%), Third Party (84.3%): For further information as to how and for what purpose the social network provider processes your data, please see their privacy policies. | Consent (95.1%), Non-Personal Data (98.0%), Personal Data (98.2%), Processing (93.9%), Required Purpose (94.8%), Technical Measure (99.4%): We automatically collect certain data from you, including IP address or other unique device identifiers such as Google advertising ID, Android ID,  Identifier for Advertising, Cookies (as defined below), mobile carrier, time zone and locale setting, operating system and platform, hardware and software versions, battery level, signal strength, available storage space, browser type, app and file names and types, Bluetooth signals, International Mobile Equipment Identity, International Mobile Subscriber Identity, data from device settings: information you allow us to receive through device settings you turn on, such as access to your GPS location, photos, videos and voice recordings and such other information on your device. | Personal Data (72.8%), Processing (96.7%), Required Purpose (74.2%): your comments on Boomplay or any other content that you Posted on or through the Services, views and interactions on Boomplay. | Personal Data (94.6%): In addition, we link your contact or subscriber information with your activity on Boomplay across all your devices using your email or social media log-in details, engagement (including without limitation likes, shares, comments, repeated views) and relate users based on your behavior. | Personal Data (88.9%): • Location data  We may collect and process information about your location, including location information based on your SIM card, IP address or mobile device location settings, and if activated on your mobile device, by use of a Global Positioning System (GPS). | Automated Decision Making (71.6%), Personal Data (86.8%), Processing (73.5%): When you Post content, including images, text and audio to Boomplay, you automatically upload certain metadata that is connected to the content. | Processing (81.8%): In essence, metadata describes other data and provides information about your content that will not always be evident to the viewer. | Processing (98.7%): Any automated decision-making, including profiling, based on the data automatically collected from you, will solely be used in optimizing the Services and tailoring it to your preferences. | Personal Data (77.7%): It further includes information such as your account name that enables other users to trace back the content to your user account. | Third Party (95.6%): • Information from third parties. | Personal Data (88.1%): • Contact Information. | Personal Data (99.4%): We may collect contact information from your contact list, address book and your social network to help you and others find people you may know and enable you to link your Boomplay contact list with the contact lists on your device and/or in your account on third party services. | Consent (74.8%): We will ask for your consent to access your contact list and address book before doing so. | Consent (81.7%): You may at any time allow or disallow us to access your contact list and address book by changing your settings. | Personal Data (99.5%), Third Party (74.9%): If you create a Boomplay account by connecting with a third-party service, such as Facebook, Google, Instagram, Whatsapp or Email, we may collect information from such third-party service, including without limitation your third-party service user name, gender, profile image, birthday and third-party service contact list. | Technical Measure (98.4%): Cookies We use cookies and other similar technologies (e.g. | Required Purpose (98.3%), Technical Measure (86.4%): web beacons, Flash cookies, App cache, etc.) (“ Cookies ”) to enhance your experience using Boomplay. | Required Purpose (79.9%): Cookies are small files which, when placed on your device, enable us to provide certain features and functionality. | Required Purpose (93.2%): These are Cookies that are required for the operation of Boomplay and to keep your account and data safe and secure. | Required Purpose (94.7%): They allow us to recognize and count the number of visitors and to see how visitors move around Boomplay when they are using it. | Required Purpose (96.6%): This helps us to improve the way Boomplay works, for example, by ensuring that users are able to find what they are looking for easily. | Retention (76.7%): In connection with your content the metadata can describe how, when and by whom the piece of content was collected and how that content is formatted. | Required Purpose (83.3%): This enables us to personalize our content for you, greet you by name and remember your preferences (for example, your choice of language or region). | Required Purpose (97.7%): We will use this information to make Boomplay and the advertising displayed on it more relevant to your interests. | Required Purpose (80.5%): We may also share this information with third parties for this purpose. | Consent (87.4%): Unless you opt out of Cookies, we will assume you consent to the use of Cookies. | Third Party (90.7%): "Do not track" signals are preferences that users can set on their web browser to limit how their activity is tracked across third-party websites or online services. | Required Purpose (94.1%): Analytics information On Boomplay, we use third-party analytics tools to help us measure traffic and usage trends for the Services. | Required Purpose (85.6%): These tools, for example, collect information sent by your device or our Services, including the pages you visit, add-ons, and other information that assists us in improving the Service. | Required Purpose (99.5%): The information will be used to report and evaluate your activities and patterns as a user of Boomplay to provide services in accordance with these activities. | Required Purpose (89.2%): How We Use Your Personal Data We will use the information we collect about you in the following ways: • To administer Boomplay (i.e. | Required Purpose (92.8%): to provide our Services to you) and for internal operations, including troubleshooting, data analysis, testing, research, statistical and survey purposes (i.e. | Data Source (70.1%), Personal Data (94.2%), Required Purpose (97.2%): to guarantee Boomplay’s stability and security) and to solicit your feedback; • To allow you to participate in interactive features of Boomplay, when you choose to do so; • To personalize the content you receive and provide you with tailored content that will be of interest to you; • To improve and develop Boomplay and conduct product development; • To measure and understand the effectiveness of our recommendation and service we offer to you and others; • To provide you with tailored services based on the country settings you have chosen, such as recommendations and other content that is related to the country settings; • To make suggestions and recommendations to you and other users of Boomplay about goods or services that will interest you or them; • To allow other users to identify you as a user of the Service and to support the socializing function of the Services; • To provide you with your profile information to send to anyone you choose and to enable you to participate on Boomplay and interact with other users; • To make your information available to other users in accordance with the privacy settings you chose for the respective information; • To show you content that is similar to content you liked or interacted with (by commenting and/or watching the content), content from your region as well as content from users you follow; • To promote the Services and use information that you give to us, such as content which you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services; • To enable our messenger service to function; • To verify accounts and activity, combat harmful conduct, detect and prevent spam and other bad experiences, maintain the integrity of Boomplay, and promote safety and security on and off of Boomplay; • To notify you about changes to our Services; • To communicate with you; • To provide you with user support; • To enforce our terms, conditions and policies; • For any other specific reason provided to you at the time we collect your information. | Required Purpose (84.4%), Third Party (92.2%): Please read the following carefully to understand our views and practices regarding your personal data and how we will treat it. | Legitimate Interest (96.0%): It is in our legitimate interest to promote the Services, and we may use information that you give to us, such as content that you choose to Post on or through the Services, as part of our advertising and marketing campaigns to promote the Services. | Third Party (73.2%): How We Share Your Personal Data We may share your personal data with selected third parties in or outside your country, including without limitation: • Our business partners so that we can make you special offers via Boomplay; • With respect to on-screen ads, advertisers and advertising networks that require the data to select and serve advertisements to you and others. | Third Party (76.2%): We may also receive information from third parties (such as advertising networks and analytics providers) and from other sources, including business directories and other commercially or publicly available sources. | Contract (95.1%), Personal Data (90.4%), Processing (97.4%), Required Purpose (88.9%): Without your consent, we will not share your contact details to our business partners to avoid direct contact from them, but we may share other information so that they can make you offers tailored to your requirements; • Cloud storage providers to store the information you provide and for disaster recovery services, as well as for the performance of any contract we have entered into with you; • Analytics and search engine providers that assist us in the improvement and optimization of Boomplay. | Authority (96.5%), Legal Basis (79.4%), Required Purpose (75.3%), Right (94.8%): We may share your information with law enforcement agencies, public or tax authorities or other organizations if legally required to do so, or if we have a good faith belief that such use is reasonably necessary to: • Comply with a legal obligation, process or request (including tax and related reporting requirements); • Enforce our Terms of Service and other agreements, policies, and standards, including investigation of any potential violation thereof; • Detect, prevent or otherwise address security, fraud or technical issues; • Protect the rights, property or safety of us, our users, a third party or the public as required or permitted by law (including exchanging information with other companies and organizations for the purposes of fraud protection and credit risk reduction). | Processing (93.6%), Recipient (77.0%): We may also disclose your information to third parties: • In the event that we sell or buy any business or assets, in which case we may disclose your data to the prospective seller or buyer of such business or assets; or • If we sell, buy, merge or partner with other companies or businesses, or sell some or all of our assets. | Third Party (79.0%): We may share your information with any member or affiliate of our group, which includes our subsidiaries, our ultimate holding company and its subsidiaries, and companies that we control, are controlled by or under common control, and our service providers and strategic business partners, and their respective subsidiaries, in each case in or outside your country, for the purposes set out above (“ How We Use Your Personal Data ”). | Personal Data (98.3%), Processing (73.5%): In such transactions, user information may be among the transferred assets. | Third Party (96.7%): In any such cases, the third party company or business will adhere to the provisions of this Privacy Policy and where it will result in a change in any of the provisions herein, such changes will be communicated to you and you will be given the chance to consent or opt out at your discretion. | Organisational Measure (72.6%): The Security of Your Personal Data We take steps to ensure that your information is treated securely and in accordance with this policy. | Processing (97.8%): Unfortunately, the transmission of information via the internet is not completely secure. | Processing (93.4%): Although we will do our best to protect your information, for example, by encryption, we cannot guarantee the security of your information transmitted through Boomplay; thus, any transmission is at your own risk. | Organisational Measure (84.2%): We have put in place appropriate technical and organizational measures to ensure a level of security appropriate to the risk of varying likelihood and severity for the rights and freedoms of you and other users. | Organisational Measure (92.8%): We maintain these technical and organizational measures and will amend them from time to time to improve the overall security of our systems. | Third Party (89.7%): We will, from time to time, include links to and from the websites of our partner networks, advertisers and affiliates. | Retention (78.5%): After you have terminated your use of our Services, we can store your information in an aggregated and anonymized format. | Personal Data (98.9%), Required Purpose (93.7%): Notwithstanding the foregoing, we can also retain any personal information as reasonably necessary to comply with our legal obligations, allow us to resolve and litigate disputes, and to enforce our agreements. | Legal Basis (97.4%), Processing (77.8%): Information Relating to Children The Services are not offered to children whose age makes it illegal to process their personal data or requires parental consent for the processing of their personal data under any applicable laws. | Art. 17 Right to erasure (‘right to be forgotten’) (75.9%): If you are a parent of a child under the Age Limit and become aware that your child has provided personal data to us, please contact us at privacy.boomplay@transsnet.com to delete such data. | Organisational Measure (70.5%): If you are under the Age Limit, please do not use the Services, and do not provide any personal data to us. | Organisational Measure (75.0%), Personal Data (78.2%): If we are aware that we have collected the personal data of a child under the Age Limit, we will take reasonable steps to delete the personal data. | Personal Data (97.7%): Complaints In the event that you wish to make a complaint about how we process your personal data, please contact us in the first instance at privacy.boomplay@transsnet.com and we will endeavor to deal with your request as soon as possible. | Organisational Measure (82.2%): It is your responsibility to remain informed of any changes. | Art. 16 Right to rectification (95.3%): Your rights You have the right to make a request to access and delete the personal data we hold about you, to rectify any personal data held about you that is inaccurate, the right to data portability and the right to request the suspension of the processing of your personal data.</t>
+  </si>
+  <si>
+    <t>Data Controller (94.6%), Personal Data (98.1%), Processing (99.6%), Retention (74.1%): Meta Privacy Policy - How Meta collects and uses user data Privacy Policy Search Privacy topics More privacy resources Privacy Policy What is the Privacy Policy and what does it cover? | Processing (99.5%), Required Purpose (95.8%), Third Party (96.3%): How is your information shared on Meta Products or with integrated partners? | Art. 17 Right to erasure (‘right to be forgotten’) (79.3%), Right (74.8%): How can you manage or delete your information and exercise your rights? | Legal Basis (97.6%), Legitimate Interest (72.0%): How do we respond to legal requests, comply with applicable law and prevent harm? | Consent (84.8%), Data Source (83.8%), Organisational Measure (97.0%), Personal Data (99.6%), Processing (99.0%), Required Purpose (96.3%), Right (78.2%), Third Party (98.6%): Effective June 16, 2025 | View printable version | See previous versions Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights. | Data Controller (96.3%): Highlights We at Meta want you to understand what information we collect, and how we use and share it. | Data Controller (98.0%), Personal Data (82.9%): What information do we collect? | Non-Personal Data (77.7%), Personal Data (80.1%), Processing (99.2%), Scale Non-EU (86.3%): Privacy notice for United States residents How to contact Meta with questions Why and how we process your information Other policies and articles Settings Privacy Policy What is the Privacy Policy and what does it cover? | Data Subject (92.9%), Personal Data (86.5%): How do we use your information? | Required Purpose (86.0%): Some information is required for our Products to work. | Required Purpose (70.8%): Other information is optional, but without it, the quality of your experience might be affected. | Required Purpose (89.2%): You can update these settings to shape your experience. | Third Party (97.8%): How do we share information with third parties? | Retention (85.1%): In some cases information is de-identified, aggregated, or anonymized by third parties so that it no longer identifies individuals before it’s made available to us. | Required Purpose (97.4%): Highlights We use information we collect to provide a personalized experience to you, including ads, along with the other purposes we explain in detail below. | Automated Decision Making (95.1%), Processing (99.2%): The information we use for these purposes is automatically processed by our systems. | Processing (97.3%): But in some cases, we also use manual review to access and review your information. | Non-Personal Data (72.9%), Required Purpose (90.3%), Third Party (86.4%): To use less information that’s connected to individual users, in some cases we de-identify or aggregate information or anonymize it so that it no longer identifies you. | Required Purpose (98.9%): Here are the ways we use your information: To provide, personalize and improve our Products We use information we have to provide and improve our Products. | Required Purpose (74.8%): This includes personalizing features, content and recommendations, such as your Facebook Feed, Instagram Feed, Stories and ads. | Legitimate Interest (78.6%), Required Purpose (97.8%): Read more about how we use information to provide, personalize and improve our Products: How we show ads and other sponsored or commercial content How we use information to improve our Products How we use location-related information To promote safety, security and integrity We use information we collect to help protect people from harm and provide safe, secure Products. | Required Purpose (72.4%), Third Party (98.1%): Learn more To provide measurement, analytics and business services Lots of people rely on our Products to run or promote their businesses or share content. | Data Source (71.5%), Personal Data (98.0%), Processing (93.2%), Required Purpose (95.0%): Learn more To communicate with you We communicate with you using information you've given us, like contact information you've entered on your profile. | Data Source (91.9%), Required Purpose (89.8%), Third Party (71.0%): Learn more To research and innovate for social good We use information we have, information from researchers and datasets from publicly available sources, professional groups and non-profit groups to conduct and support research. | Personal Data (77.8%), Processing (97.9%): If you do, these integrated partners receive information about you and your activity. | Processing (86.6%), Required Purpose (74.5%), Retention (77.5%), Third Party (95.1%): Here's the information we collect: Your activity and information you provide Friends, followers and other connections App, browser and device information Information from partners, vendors and other third parties What if you don’t let us collect certain information? | Organisational Measure (74.2%), Processing (84.7%): We also require partners and other third parties to follow rules about how they can and cannot use and disclose the information we provide. | Legitimate Interest (74.7%), Required Purpose (86.6%): Here’s more detail about who we share information with: Partners Advertisers and Audience Network publishers Partners who use our analytics services Partners who offer goods or services on our Products and commerce services platforms Integrated partners Vendors Measurement vendors Marketing vendors Service providers Service providers Third parties External researchers AI integrations Other third parties We also share information with other third parties in response to legal requests, to comply with applicable law or to prevent harm. | Processing (97.0%): How do we transfer information? | Legal Basis (92.8%): And if we sell or transfer all or part of our business to someone else, in some cases we’ll give the new owner your information as part of that transaction, but only as the law allows. | Legal Basis (93.0%): We also process information that we receive about you from other Meta Companies, according to their terms and policies and as permitted by applicable law. | Legal Basis (93.4%), Required Purpose (89.7%): Why we share across the Meta Companies Meta Products share information with other Meta Companies: To promote safety, security and integrity and comply with applicable laws To personalize offers, ads and other sponsored or commercial content To develop and provide features and integrations To understand how people use and interact with Meta Company Products See some examples of why we share. | Legal Basis (98.3%), Right (81.1%): You may also have other privacy rights under applicable laws. | Consent (70.6%), Data Protection Officer (80.2%): In some countries, you may also be able to contact the Data Protection Officer for Meta Platforms, Inc., and depending on your jurisdiction, you may also contact your local Data Protection Authority (“DPA”) directly. | Processing (81.4%): How long do we keep your information? | Legal Basis (75.1%), Retention (96.3%): Highlights We keep information as long as we need it to provide our Products, comply with legal obligations or protect our or other’s interests. | Required Purpose (97.4%): Here’s what we consider when we decide: If we need it to operate or provide our Products. | Required Purpose (99.2%): For example, we need to keep some of your information to maintain your account. | Personal Data (92.8%), Retention (75.5%): For example, messages sent using Messenger’s vanish mode are retained for less time than regular messages. | Retention (96.5%): How long we need to retain the information to comply with certain legal obligations. | Legitimate Interest (83.1%), Retention (87.0%): If we need it for other legitimate purposes, such as to prevent harm; investigate possible violations of our terms or policies; promote safety, security and integrity; or protect ourselves, including our rights, property or products In some instances and for specific reasons, we’ll keep information for an extended period of time. | Processing (95.7%): Read our Policy about when we may preserve your information. | Organisational Measure (73.0%): Highlights We access, preserve, use and share your information: In response to legal requests, like search warrants, court orders, production orders or subpoenas. | Authority (95.2%), Third Party (83.3%): These requests come from third parties such as civil litigants, law enforcement and other government authorities. | Required Purpose (98.0%): In accordance with applicable law To promote the safety, security and integrity of Meta Products, users, employees, property and the public. | Retention (94.0%): We may access or preserve your information for an extended amount of time. | Consent (83.3%): We use information with special protections you choose to provide for these purposes, but not to show you ads. | Processing (78.3%), Required Purpose (99.4%): ATTN: Privacy Operations 1601 Willow Road Menlo Park, CA 94025 Why and how we process your information The categories of information we use, and why and how information is processed, are set out below: Why and how we process your information Information categories we use (see 'What Information do we collect?' for more information on each information category) The actual information we use depends on your factual circumstances, but could include any of the following: Personalizing the Meta Products (other than ads, see below): Our systems automatically process information we collect and store associated with you and others to assess and understand your interests and your preferences and provide you personalized experiences across the Meta Products in accordance with our terms. | Personal Data (97.4%), Processing (98.5%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings (like GPS location) Location-related information Information about the network you connect your device to Reports about our products’ performance on your device Information from cookies and similar technologies Information from partners, vendors and third parties Providing ads on the Meta Company Products: Our ads system automatically processes information that we’ve collected and stored associated with you. | Required Purpose (99.0%): Our ads system uses this information to understand your interests and your preferences and personalize your ads across the Meta Company Products. | Processing (92.7%): Then we match the ad to people who might be interested. | Consent (84.0%): We decide how long we need information on a case-by-case basis. | Processing (97.7%): For information that WhatsApp shares with Meta see the WhatsApp Help Center article. | Automated Decision Making (91.0%), Personal Data (95.4%), Processing (94.6%), Required Purpose (77.8%), Technical Measure (96.0%): Your activity and information you provide Friends, followers and other connections App, browser and device information Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to: Create and maintain your account and profile, Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information, Facilitate the sharing of content and status, Provide and curate features, Provide messaging services, the ability to make voice and video calls and connect with others, Provide advertising products, Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide, Undertake analytics, and Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences. | Required Purpose (99.3%): For example, we collect different information if you sell furniture on Marketplace than if you post a reel on Instagram. | Required Purpose (99.6%): We also use information to develop, research and test improvements to our Products. | Required Purpose (94.5%): We use information we have to: See if a product is working correctly, Troubleshoot and fix it when it’s not, Test out new products and features to see if they work, Get feedback on our ideas for products or features, and Conduct surveys and other research about what you like about our Products and brands and what we can do better. | Personal Data (95.9%), Required Purpose (91.6%): Your activity and information you provide: Content you create, like posts, comments or audio Your public profile information (including your name, username and profile picture) Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. | Automated Decision Making (79.7%): We process information we have associated with you and apply automated processing techniques and, in some instances, conduct manual (human) review to: Verify accounts and activity, Find and address violations of our terms or policies. | Personal Data (82.5%), Processing (70.6%), Required Purpose (93.7%): In some cases, the decisions we make about violations are reviewed by the Oversight Board, Investigate suspicious activity, Detect, prevent and combat harmful or unlawful behavior, such as to review and, in some cases, remove content reported to us, Identify and combat disparities and racial bias against historically marginalized communities, Protect the life, physical or mental health, well-being or integrity of our users or others, Detect and prevent spam, other security matters and other bad experiences, Detect and stop threats to our personnel and property, and Maintain the integrity of our Products. | Personal Data (76.4%), Required Purpose (91.3%): Your activity and information you provide:: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Messages you send and receive, including their content, subject to applicable law Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties To communicate with you: We use information you’ve given us (like contact information on your profile) to send you a communication, like an e-mail or in-product notice, for example: We’ll contact you via email or in-product notifications in relation to the Meta Products, product-related issues, research or to let you know about our terms and policies. | Personal Data (98.1%), Required Purpose (80.1%): We also use contact information like your email address to respond when you contact us. | Personal Data (94.0%): Your activity and information you provide: Contact information on your profile and your communications with us Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies. | Processing (82.4%): Transferring, storing or processing your information across borders, including from and to the United States and other countries: We share information we collect globally, both internally across our offices and data centers and externally with our partners, third parties and service providers. | Scale Non-EU (85.5%): Learn more about how we transfer information to other countries. | Processing (94.2%), Required Purpose (87.6%): Because Meta is global, with users, partners, vendors and employees around the world, transfers are necessary: To operate and provide the services described in the terms that apply to the Meta Product(s) you are using. | Processing (97.8%), Required Purpose (95.9%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make, including truncated credit card information Hashtags you use The time, frequency and duration of your activities on our Products Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Processing information subject to special protections under applicable laws that you provide so we can share it with those you choose, to provide, personalize and improve our Products and to undertake analytics. | Personal Data (94.2%), Required Purpose (96.9%), Third Party (90.8%): Your activity and information you provide: Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. | Third Party (98.7%): Your activity and information you provide: Information and content you provide, such as your name or email address Information from partners, vendors and third parties Sharing your contact, profile or other information with third parties upon your request: The type of third party and categories of information shared depend on the circumstances of what you ask us to share. | Required Purpose (91.2%): We use this information to: Provide insights and measurement reports to businesses, advertisers and other partners to help them measure the effectiveness and distribution of their or their clients’ ads, content and services, to understand the kinds of people who are seeing their content and ads, and how their content and ads are performing on and off Meta Products, and Provide aggregated user analytics and insights reports that help users, businesses, advertisers and other partners better understand the audiences with whom they may want to connect, as well as the types of people who use their services and how people interact with their content, websites, apps and services. | Required Purpose (81.3%): Highlights On Meta Products Learn more about the different cases when your information can be shared on our Products: People and accounts you share and communicate with Content others share or reshare about you Public content With integrated partners You can choose to connect with integrated partners who use our Products. | Required Purpose (86.8%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users' Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Business intelligence and analytics: To understand, in aggregate, your usage of and across our Products, to accurately count people and businesses; and To validate metrics directly related to these, in order to inform and improve product direction and development and to adhere to (shareholder/earning) reporting obligations. | Required Purpose (99.1%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users' Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Identifying you as a Meta Product user and personalizing the ads we show you through Meta Audience Network when you visit other apps: When we show you ads through Meta Audience Network when you visit other apps, our systems automatically process the information we have collected and stored about you and others to identify you as a Meta Product user and tailor the ads you see. | Required Purpose (78.8%): We’ll collect and store your information and use it to send marketing communications to you, like an email, subject to applicable laws. | Processing (94.3%): Your activity and information you provide: Information and content you provide, including your contact information like email address App, browser and device information: Device identifiers Research and innovate for social good: We carry out surveys and use information (including from researchers we collaborate with) to conduct and support research and innovation on topics of general social welfare, technological advancement, public interest, health and well-being. | Processing (97.6%): This includes allowing you to share information and connect with your family and friends around the globe; and To fix, analyze and improve our Products. | Processing (78.0%), Required Purpose (94.9%): We collect, store, combine, analyze and apply automatic processing techniques like aggregation of information as well as manual (human) review, and share information, as necessary to research and innovate for social good in this way. | Required Purpose (99.5%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content and messages, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Anonymizing your information In some cases, we anonymize information we have associated with you, such as your activity on and off our Products, and use the resulting information, for example, to provide and improve our Meta Products, including ads. | Legitimate Interest (76.5%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use The time, frequency and duration of your activities on our Products Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties Sharing information with others, including law enforcement and to respond to legal requests. | Personal Data (95.6%): For example, responses to legal requests where not compelled by law will typically include limited information (such as contact details and login information). | Personal Data (90.6%): We share information we collect, infrastructure, systems and technology with the other Meta Companies. | Required Purpose (78.5%): How do the Meta Companies work together? | Authority (90.3%): Your activity and information you provide: Content you create, like posts, comments or audio Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features Metadata about content, subject to applicable law Types of content you view or interact with, and how you interact with it Apps and features you use, and what actions you take in them Purchases or other transactions you make Hashtags you use Your photo or video selfie if you provide it when you contact us for account support Friends, followers and other connections App, browser and device information: Device characteristics and device software What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots) Identifiers that tell your device apart from other users’ Device signals Information you’ve shared through your device settings Location-related information Information about the network you connect your device to, including your IP address Information from cookies and similar technologies Information from partners, vendors and third parties For processing information when the law requires it: Where we are under an obligation to disclose information such as, for example, if we receive a valid legal request for certain information such as a search warrant, we will access, preserve and/or share your information with regulators, law enforcement or others. | Processing (84.6%): Only the information necessary to comply with the relevant legal obligation will be shared or otherwise processed.</t>
+  </si>
+  <si>
+    <t>Data Controller (93.0%), Data Subject (83.6%), Processing (95.4%), Scale Non-EU (75.2%): Privacy Help Center Blog For Business Apps Log inDownload WhatsApp Business App Privacy Policy Effective July 14, 2025 Table of Contents WhatsApp Legal Info Scope of This WhatsApp Business App Privacy Policy Information We Collect How We Use Information Information You and We Share How We Work With Other Meta Companies Region Specific Information Assignment, Change Of Control, And Transfer Managing Your Information Law, Our Rights, And Protection Our Global Operations Updates to Our Privacy Policy Contact Us If you are located in the UK, WhatsApp LLC provides the Business App to you under this WhatsApp Business Terms of Service and WhatsApp Business App Privacy Policy. | Data Controller (99.7%), Data Subject (82.1%), Required Purpose (83.8%), Third Party (77.6%): WhatsApp Business App Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC AzərbaycanAfrikaansBahasa IndonesiaMelayuCatalàčeštinaDanskDeutschEestiEnglishEspañolFrançaisGaeilgeHrvatskiItalianoKiswahiliLatviešuLietuviųMagyarNederlandsNorsk bokmålO‘zbekFilipinoPolskiPortuguês (Brasil)Português (Portugal)RomânăShqipSlovenčinaSlovenščinaSuomiSvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어azərbaycanAfrikaansBahasa IndonesiaMelayucatalàčeštinadanskDeutscheestiEnglishespañolfrançaisGaeilgehrvatskiitalianoKiswahililatviešulietuviųmagyarNederlandsnorsk bokmålo‘zbekFilipinopolskiPortuguês (Brasil)Português (Portugal)românăshqipslovenčinaslovenščinasuomisvenskaTiếng ViệtTürkçeΕλληνικάбългарскиқазақ тілімакедонскирусскийсрпскиукраїнськаעבריתالعربيةفارسیاردوবাংলাहिन्दीગુજરાતીಕನ್ನಡमराठीਪੰਜਾਬੀதமிழ்తెలుగుമലയാളംไทย简体中文繁體中文（台灣）繁體中文（香港）日本語한국어 FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Scale EU (81.3%): If you are located in the European Region, WhatsApp Ireland Ltd. | Personal Data (99.2%), Processing (96.1%), Required Purpose (83.3%): WhatsApp LLC is also the data controller for any processing of personal information about you and you can contact us using the details in the section Contact Us below. | Required Purpose (82.4%), Third Party (98.9%): Business Functions may be offered by WhatsApp, third parties and/or Meta, via integrations into our Business App, and may be subject to the third parties’ own terms of service and privacy policies. | Data Subject (84.1%), Legal Basis (99.2%), Personal Data (99.0%), Processing (99.6%): This WhatsApp Business App Privacy Policy (“Business App Privacy Policy”) explains WhatsApp’s data practices with respect to the Business Functions, and applies only to the extent information relating to users of the WhatsApp Business App would be considered personal data and is processed by WhatsApp as a controller, each under applicable law. | Data Controller (98.0%): WhatsApp Legal Info If you are located in the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Business App to you under this Terms of Service and this WhatsApp Business App Privacy Policy. | Processing (99.3%): Information We Collect In addition to the information described in the applicable WhatsApp Privacy Policy, we collect the following information. | Non-Personal Data (96.5%), Personal Data (97.6%), Required Purpose (70.9%): In addition to your phone number, you must provide basic information about your business to create a WhatsApp business account, including your business name and business category. | Non-Personal Data (80.6%), Personal Data (98.2%): You can add other optional information to your business account, such as a profile picture and cover photo; contact information like your business address, business email, and website; a description of your business and any products or services you offer (such as their names, descriptions, images, videos, prices, and related marketing materials); and your intended audience. | Non-Personal Data (88.5%): For example, we collect information about your business profile settings; how you use Business Functions like catalogs, labels and quick replies; purchases and transactions with your business; and metrics related to how customers interact with your business. | Required Purpose (99.1%): How We Use Information We use the information we collect for the same purposes described in the WhatsApp Privacy Policy, and also to operate, provide, improve, understand, customize, support, and market our WhatsApp Business App and Business Functions. | Required Purpose (98.8%): We use the information we have to operate and provide our WhatsApp Business App and Business Functions, including providing you with business support; providing onboarding tools; providing message creation and delivery tools; providing you new and premium Business Functions (some of which may be offered by third parties and/or Meta); and improving, fixing, and customizing our WhatsApp Business App. | Required Purpose (91.7%): While the WhatsApp Business App includes various features available in the WhatsApp Messenger App, some features may not be available; and not all Business Functions are available everywhere. | Personal Data (89.6%), Required Purpose (96.2%): We also use your information to respond to you when you contact us. | Required Purpose (98.0%): In addition to the safety, security and integrity purposes described in the WhatsApp Privacy Policy, we also use the information we have to maintain safety, security and integrity on our WhatsApp Business App, for example: to create quality and integrity inferences about businesses; secure WhatsApp systems and WhatsApp Business App users’ accounts; fight threats, abuse, or infringement activities; promote safety, security, and integrity on the WhatsApp Business App; and to ensure compliance with our terms and policies. | Processing (99.4%): Information You and We Share You and we share information as described in the WhatsApp Privacy Policy, plus additional sharing relevant to the Business Functions. | Non-Personal Data (81.6%), Personal Data (96.3%): Business profile information is publicly available, including your business name, phone number, hours of operation, business category, address, email address, website(s), description, and Facebook and Instagram accounts (if added). | Right (73.2%): Region Specific Information Additional information for users located in the US You can learn more about the consumer privacy rights that may be available to you, by reviewing the WhatsApp Business App United States Regional Privacy Notice here. | Legal Basis (96.0%), Recipient (79.7%): Assignment, Change Of Control, And Transfer In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws. | Legal Basis (76.4%), Processing (97.7%): Law, Our Rights, And Protection Review the WhatsApp Privacy Policy to understand how we access, preserve, and share your information in response to legal obligations.</t>
+  </si>
+  <si>
+    <t>Processing (98.9%), Scale EU (78.4%): Privacy Help Center Blog For Business Apps Log inDownload WhatsApp Privacy Policy Effective January 4, 2021archived versions If you live in the European Region, WhatsApp Ireland Limited provides the Services to you under this Terms of Service and Privacy Policy. | Consent (73.4%), Data Controller (99.5%), Data Subject (97.5%), Organisational Measure (84.9%), Personal Data (86.3%), Processing (95.7%), Required Purpose (98.9%), Third Party (91.6%): Privacy Policy Skip to contentHome Features Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI Privacy Help Center Blog For Business Download Download Terms &amp; Privacy Policy2025 © WhatsApp LLC Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港） FeaturesMessage privatelyEnd-to-end encryption and privacy controls. | Scale Non-EU (74.3%): If you live in the UK, WhatsApp LLC provides the Services to you under this Terms of Service  and Privacy Policy. | Data Controller (98.4%): WhatsApp Legal Info If you live outside the European Region or the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Services to you under this Terms of Service and Privacy Policy. | Processing (99.6%), Required Purpose (99.5%): Our Privacy Policy ("Privacy Policy") helps explain our data practices, including the information we process to provide our Services. | Processing (99.4%): For example, our Privacy Policy talks about what information we collect and how this affects you. | Art. 17 Right to erasure (‘right to be forgotten’) (84.4%), Personal Data (91.3%), Processing (98.4%): It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services. | Data Controller (97.9%): We are one of the Meta Companies. | Data Subject (89.3%), Processing (99.6%), Required Purpose (99.9%): You can learn more further below in this Privacy Policy about the ways in which we share information across this family of companies. | Organisational Measure (76.3%): Since we started WhatsApp, we’ve built our services with a set of strong privacy principles in mind. | Processing (97.5%): In our updated Terms of Service and Privacy Policy you’ll find: Additional Information On How We Handle Your Data. | Data Subject (77.4%), Organisational Measure (76.0%), Personal Data (89.6%), Processing (75.2%), Required Purpose (78.6%): For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information. | Recipient (82.0%), Third Party (92.8%): Many businesses rely on WhatsApp to communicate with their customers and clients. | Third Party (98.7%): We work with businesses that use Meta or third parties to help store and better manage their communications with you on WhatsApp. | Processing (99.3%), Required Purpose (99.7%), Retention (79.3%): Back to top Information We Collect WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services. | Processing (98.8%): Please also read WhatsApp’s Terms of Service ("Terms"), which describe the terms under which you use and we provide our Services. | Processing (86.6%), Required Purpose (99.3%): We require certain information to deliver our Services and without this we will not be able to provide our Services to you. | Personal Data (98.0%), Required Purpose (89.4%): For example, you must provide your mobile phone number to create an account to use our Services. | Processing (96.0%), Required Purpose (98.0%): Our Services have optional features which, if used by you, require us to collect additional information to provide such features. | Organisational Measure (95.0%): You will be notified of such collection, as appropriate. | Consent (91.4%): If you choose not to provide the information needed to use a feature, you will be unable to use the feature. | Data Source (85.5%), Personal Data (90.8%): For example, you cannot share your location with your contacts if you do not permit us to collect your location data from your device. | Consent (95.9%): Permissions can be managed through your Settings menu on both Android and iOS devices. | Personal Data (98.8%): You must provide your mobile phone number and basic information (including a profile name of your choice) to create a WhatsApp account. | Personal Data (89.1%): You can add other information to your account, such as a profile picture and "about" information. | Processing (88.2%): We do not retain your messages in the ordinary course of providing our Services to you. | Retention (90.0%): If a message cannot be delivered immediately (for example, if the recipient is offline), we keep it in encrypted form on our servers for up to 30 days as we try to deliver it. | Non-Personal Data (85.6%), Required Purpose (98.8%): When a user forwards media within a message, we store that media temporarily in encrypted form on our servers to aid in more efficient delivery of additional forwards. | Required Purpose (98.7%): End-to-end encryption means that your messages are encrypted to protect against us and third parties from reading them. | Legal Basis (99.5%), Personal Data (89.6%), Right (75.7%): You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. | Personal Data (86.6%): If you use our payments services, or use our Services meant for purchases or other financial transactions, we process additional information about you, including payment account and transaction information. | Required Purpose (94.3%): Payment account and transaction information includes information needed to complete the transaction (for example, information about your payment method, shipping details and transaction amount). | Personal Data (94.0%): When you contact us for customer support or otherwise communicate with us, you may provide us with information related to your use of our Services, including copies of your messages, any other information you deem helpful, and how to contact you (e.g., an email address). | Non-Personal Data (86.4%), Processing (74.0%): For example, you may send us an email with information relating to app performance or other issues. | Non-Personal Data (85.6%): We collect information about your activity on our Services, like service-related, diagnostic, and performance information. | Data Source (78.7%), Non-Personal Data (89.5%): This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. | Non-Personal Data (79.7%), Personal Data (96.8%): This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information. | Non-Personal Data (88.5%), Personal Data (99.0%), Third Party (79.6%): This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account). | Non-Personal Data (73.1%): Express yourselfSay it with stickers, voice, GIFs and more. | Personal Data (89.2%): Share your everydayShare photos, videos, voice notes on Status. | Personal Data (99.0%), Processing (82.5%): We collect and use precise location information from your device with your permission when you choose to use location-related features, like when you decide to share your location with your contacts or view locations nearby or locations others have shared with you. | Processing (90.5%): There are certain settings relating to location-related information which you can find in your device settings or the in-app settings, such as location sharing. | Personal Data (99.7%), Required Purpose (99.1%): Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). | Required Purpose (89.4%): Stay connectedMessage and call for free* around the world. | Required Purpose (84.6%): We also use your location information for diagnostics and troubleshooting purposes. | Technical Measure (97.7%): Cookies. | Technical Measure (93.4%): We use cookies to operate and provide our Services, including to provide our Services that are web-based, improve your experiences, understand how our Services are being used, and customize them. | Consent (96.1%), Required Purpose (98.7%): Additionally, we may use cookies to remember your choices, like your language preferences, to provide a safer experience, and otherwise to customize our Services for you. | Required Purpose (97.3%): Learn more about how we use cookies to provide you our Services. | Data Source (72.6%): We receive information about you from other users. | Consent (72.1%), Personal Data (72.4%), Processing (98.6%): You should keep in mind that in general any user can capture screenshots of your chats or messages or make recordings of your calls with them and send them to WhatsApp or anyone else, or post them on another platform. | Required Purpose (99.7%): Just as you can report other users, other users or third parties may also choose to report to us your interactions and your messages with them or others on our Services; for example, to report possible violations of our Terms or policies. | Data Subject (89.3%): When a report is made, we collect information on both the reporting user and reported user. | Required Purpose (94.0%), Third Party (71.8%): In addition, some businesses might be working with third-party service providers (which may include Meta) to help manage their communications with their customers. | Processing (83.3%): For example, a business may give such third-party service provider access to its communications to send, store, read, manage, or otherwise process them for the business. | Processing (92.1%): To understand how a business processes your information, including how it might share your information with third parties or Meta, you should review that business’ privacy policy or contact the business directly. | Required Purpose (99.9%): We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. | Required Purpose (99.3%): These companies may provide us with information about you in certain circumstances; for example, app stores may provide us with reports to help us diagnose and fix service issues. | Processing (99.3%): The "How We Work With Other Meta Companies" section below provides more information about how WhatsApp collects and shares information with the other Meta Companies. | Third Party (74.7%): We allow you to use our Services in connection with third-party services and Meta Company Products. | Required Purpose (99.7%): Back to top How We Use Information We use information we have (subject to choices you make and applicable law) to operate, provide, improve, understand, customize, support, and market our Services. | Required Purpose (99.3%): Here's how: Our Services. | Required Purpose (99.1%): We also use your information to respond to you when you contact us. | Required Purpose (82.4%): Safety, security, and integrity are an integral part of our Services. | Required Purpose (99.6%): We use information we have to communicate with you about our Services and let you know about our terms, policies, and other important updates. | Personal Data (73.8%): For example, you may receive flight status information for upcoming travel, a receipt for something you purchased, or a notification when a delivery will be made. | Consent (94.1%): Send Your Information To Those With Whom You Choose To Communicate. | Personal Data (98.6%), Processing (97.0%): Your phone number, profile name and photo, "about" information, last seen information, and message receipts are available to anyone who uses our Services, although you can configure your Services settings to manage certain information available to other users, including businesses, with whom you communicate. | Non-Personal Data (97.5%): We offer specific services to businesses such as providing them with metrics regarding their use of our Services. | Required Purpose (79.8%): When we share information with third-party service providers and other Meta Companies in this capacity, we require them to use your information on our behalf in accordance with our instructions and terms. | Processing (95.6%), Third Party (99.0%): If you interact with a third-party service or another Meta Company Product linked through our Services, such as when you use the in-app player to play content from a third-party platform, information about you, like your IP address and the fact that you are a WhatsApp user, may be provided to such third party or Meta Company Product. | Processing (99.3%): Back to top How We Work With Other Meta Companies As part of the Meta Companies, WhatsApp receives information from, and shares information (see here) with, the other Meta Companies. | Required Purpose (99.8%): We may use the information we receive from them, and they may use the information we share with them, to help operate, provide, improve, understand, customize, support, and market our Services and their offerings, including the Meta Company Products. | Required Purpose (98.3%): This includes: helping improve infrastructure and delivery systems; understanding how our Services or theirs are used; promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities; improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. | Legal Basis (96.0%), Recipient (79.7%): Back to top Assignment, Change Of Control, And Transfer In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws. | Required Purpose (97.7%), Retention (94.0%): We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. | Processing (97.4%): The storage periods are determined on a case-by-case basis that depends on factors like the nature of the information, why it is collected and processed, relevant legal or operational retention needs, and legal obligations. | Consent (79.7%): You can change your Services settings to manage certain information available to other users. | Personal Data (96.2%): Changing Your Mobile Phone Number, Profile Name And Picture, And “About” Information. | Personal Data (91.5%), Processing (91.6%): If you change your mobile phone number, you must update it using our in-app change number feature and transfer your account to your new mobile phone number. | Personal Data (84.0%): If you use our Services with such third-party services or Meta Company Products, we may receive information about you from them; for example, if you use the WhatsApp share button on a news service to share a news article with your WhatsApp contacts, groups, or broadcast lists on our Services, or if you choose to access our Services through a mobile carrier’s or device provider’s promotion of our Services. | Personal Data (85.5%): You can also change your profile name, profile picture, and "about" information at any time. | Processing (74.6%): Once your messages are delivered, they are deleted from our servers. | Personal Data (84.6%): You can create, join, or get added to groups and broadcast lists, and such groups and lists get associated with your account information. | Personal Data (94.4%): Deleting your account will, for example, delete your account info and profile photo, delete you from all WhatsApp groups, and delete your WhatsApp message history. | Retention (82.0%): Be mindful that if you only delete WhatsApp from your device without using our in-app delete my account feature, your information will be stored with us for a longer period. | Personal Data (91.7%): Please remember that when you delete your account, it does not affect your information related to the groups you created or the information other users have relating to you, such as their copy of the messages you sent them. | Processing (93.9%), Required Purpose (97.7%): Back to top Law, Our Rights, And Protection We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm. | Third Party (74.6%): As part of the Meta Companies, WhatsApp partners with Meta to offer experiences and integrations across Meta’s family of apps and products. | Required Purpose (98.8%): Back to top Our Global Operations WhatsApp shares information globally, both internally within the Meta Companies and externally with our partners and service providers, and with those with whom you communicate around the world, in accordance with this Privacy Policy. | Processing (99.1%), Scale Non-EU (97.0%): Your information may, for example, be transferred or transmitted to, or stored and processed in, the United States; countries or territories where the Meta Companies’ affiliates and partners, or our service providers are located; or any other country or territory globally where our Services are provided outside of where you live for the purposes as described in this Privacy Policy. | Scale Non-EU (93.3%): WhatsApp uses Meta’s global infrastructure and data centers, including in the United States. | Processing (94.5%), Required Purpose (96.4%): These transfers are necessary to provide the global Services set forth in our Terms. | Legal Basis (81.5%): Please keep in mind that the countries or territories to which your information is transferred may have different privacy laws and protections than what you have in your home country or territory.</t>
+  </si>
+  <si>
+    <t>Art. 18 Right to restriction of processing (75.5%), Consent (86.7%), Data Controller (98.6%), Data Processor (61.0%), Data Source (82.0%), Non-Personal Data (90.8%), Organisational Measure (70.7%), Personal Data (99.6%), Processing (99.1%), Required Purpose (98.4%), Right (70.0%), Third Party (61.5%): Privacy Policy – Giraffe Games GIRAFFE GAMESâ PRIVACY POLICY Effective date : 25th May 2018 About us We are a limited company (company number : 535897) and out registered office is: Giraffe Games Limited 26 Upper Pembroke Street, Dublin 2 Giraffe Games is the âdata controllerâ for the personal data provided to us via the Giraffe Games Site and through the use of its Services. | Art. 17 Right to erasure (‘right to be forgotten’) (76.2%), Legal Basis (92.1%), Personal Data (97.5%), Processing (98.9%): We are responsible for processing personal data in accordance with the General Data Protection Regulation (âGDPRâ), an EU wide Regulation for the protection of personal data. | Consent (96.7%), Data Controller (97.9%), Data Subject (94.5%), Personal Data (62.0%), Processing (99.4%), Required Purpose (71.6%): This Privacy Policy explains: – What personal data we collect from you and why – How we use your personal data, and – The options you have in relation to your personal data. | Personal Data (99.7%), Processing (99.3%): This Privacy Policy (the âPolicyâ) describes the ways we collect, store, use, and manage the information, including personal information, that you provide or we collect in connection with our websites, including www.giraffe-games.com (the âSitesâ) or any Giraffe game provided on a mobile platform (for example, iOS, Android and Windows Phone) (collectively, the âServiceâ). | Personal Data (99.5%): If you are under 16, please do not send any data about yourself to us, including your name, address, telephone number, or email address. | Consent (60.7%), Data Controller (65.8%), Personal Data (82.5%), Processing (70.5%), Third Party (99.0%): Facebook third party account login If you choose to login with your Facebook account or other third party account (if applicable â for other games maybe?) please be aware that depending on your settings, we will receive some of your Facebook login account information. | Personal Data (90.0%), Processing (92.4%): Basic profile information (avatar, Facebook name, country) will be displayed to other users during game play and on public leader-boards. | Processing (89.3%), Required Purpose (77.5%): Signing in with Facebook allows us to offer other functionalities such as to invite and play with friends, create challenges for friends and see friendsâ game progress. | Required Purpose (89.2%): This is also to allow you to log in on multiple devices and synchronise progress across multiple devices on multiple platforms. | Processing (99.3%): Giraffe collects information as described below. | Processing (99.3%), Required Purpose (98.8%): Giraffeâs primary goals in collecting and using information is to create your account, provide Services to you, improve our Service, contact you, conduct research and create reports for internal use. | Scale EU (83.1%), Third Party (98.8%): We use third parties to store information on servers located in the European Union and may store information on servers and equipment in other jurisdictions from time to time. | Data Subject (86.1%), Personal Data (99.5%), Required Purpose (85.6%): You are not required to provide personally identifiable information to visit the Site; however, in order to take advantage of certain features you may need to provide some personally identifiable information. | Non-Personal Data (62.1%), Personal Data (98.0%), Third Party (96.9%): Contact us Contact Information Giraffe Games Limited, 26 Upper Pembroke Street, Dublin 2 If you have any questions about this Policy, please contact us at contact@giraffe-games.com The Privacy Policy, together with any game license agreement are to be read as a whole and form an integral part of the Terms of Use. | Personal Data (99.1%), Third Party (84.5%): In order to access your third party message accounts, you must enter your applicable user name(s) and password(s). | Processing (88.7%): If you wish to utilise advanced features of Site, such as automatic sign-in, storage of your and password(s) may be necessary. | Non-Personal Data (74.7%), Personal Data (88.5%): Giraffe may collect usage data and other information on all users, including data about their usage of the site and its various features, but it is not personally identifiable except as described below under the IP Addresses section. | Consent (72.9%), Processing (87.2%): Whenever a social feature involves the disclosure of personally identifiable information about you to other people, Giraffe will either provide you with an opportunity to opt out of the disclosure or will seek your consent prior to making the disclosure. | Automated Decision Making (62.4%), Non-Personal Data (94.6%), Personal Data (99.0%): Our Sites While you are browsing Giraffeâs Sites, your computerâs operating system, IP address, access times, browser type and language and referring Web site addresses may be logged automatically. | Processing (90.2%), Required Purpose (96.4%): We may use this information to monitor, develop and analyse your use of the Service. | Personal Data (98.7%): Facebook Connect enables you to give permission such that we may receive information from Facebook including but not limited to your name, profile picture / avatar, gender, location, email address and date of birth. | Processing (89.6%): Should you give us such permission, we will store the information received based on your use of the Services. | Personal Data (96.5%): Please note that your email address and the access token are encrypted. | Technical Measure (96.9%): These Features may collect your IP address, which page you are visiting on our site, and may set a cookie to enable the Feature to function properly. | Non-Personal Data (87.1%), Personal Data (97.3%), Processing (98.5%): iOS, Android and Windows Phone Platforms When you use any of the Giraffe games or applications on a mobile platform, we may collect and record certain information such as your unique device ID (persistent / non-persistent), hardware type, media access control (âMACâ) address, international mobile equipment identity (âIMEIâ), the version of your operating system (âOSâ), your device name, your email address (if you have connected to Facebook or Google+), and your location (based on your IP address). | Required Purpose (96.8%): This information is useful to us for troubleshooting and helps us understand usage trends. | Personal Data (97.0%), Required Purpose (97.5%): We may collect and process your location data to provide location related Services and advertisements. | Personal Data (98.8%), Technical Measure (90.3%): We may use various technologies to determine location, such as GPS, Wi-Fi or other network-based data such as IP address. | Consent (64.1%), Personal Data (97.8%): Your GPS geo-location is not accessed without your consent. | Processing (99.2%): We will not share your GPS geo-location with third parties without your consent. | Personal Data (96.4%), Required Purpose (88.9%), Third Party (92.0%): Please note that we may share your anonymous location data with partners in order to improve the Services. | Consent (74.4%): If you no longer wish to allow us to track or use this information, you may turn it off at the device level. | Personal Data (98.2%): In addition, we create a unique user ID to track your use of our Service. | Processing (99.1%), Required Purpose (88.0%): This unique user ID is stored in connection with your profile information to track the Giraffe games you are playing. | Personal Data (70.7%), Required Purpose (88.3%): These services will authenticate your identity and provide you the option to share certain personal information with us such as your name, email address, and resume to pre-populate our sign up form. | Personal Data (99.6%), Processing (93.7%), Required Purpose (67.4%): Such contact information will be used only for the purpose of sending communications to the addressee. | Art. 17 Right to erasure (‘right to be forgotten’) (66.2%), Processing (98.7%): You or the third party may contact us at support@giraffe-games.com to request the removal of this information from our database to the extent Giraffe stores any of this information. | Required Purpose (99.4%), Retention (78.6%): Customer Service We may collect your email address when you contact our customer service group and we may use that email address to contact you about your gaming experience with Giraffe games and notify you about company news and promotions. | Non-Personal Data (77.0%), Required Purpose (66.4%): Push Notifications We may occasionally send you push notifications through our mobile applications to send you game updates, high scores and other service related notifications that may be of importance to you. | Data Source (63.2%), Non-Personal Data (92.6%): Game Data Collection Whenever you play our games, we collect anonymous data using the service of http://www.gameanalytics.com and sometimes use http://www.flurry.com/solutions/analytics(or such other service providers as we may deem appropriate). | Non-Personal Data (93.4%), Processing (99.1%): The data thereby collected is presented to us in an anonymous form to include, for example, the percentage of users who complete a particular level. | Processing (69.3%), Required Purpose (90.9%): Other Collection We may also acquire information from you through (1) your access and participation in message boards on the Service, (2) your participation in surveys regarding the Service or (3) your participation in a sweepstakes or contest through the Service. | Consent (71.9%), Data Source (61.8%), Required Purpose (75.1%): We may provide you the opportunity to participate in a sweepstakes or contest through our Service. | Consent (70.4%): Participation in these sweepstakes and contests are voluntary and you therefore have a choice whether or not to disclose this information. | Personal Data (99.3%): The requested information typically includes contact information (such as name and shipping address), and demographic information (such as zip code). | Required Purpose (98.8%): We use this information to notify winners and award prizes, to monitor traffic or personalise the Service. | Required Purpose (93.1%), Third Party (73.4%): We may use a third party service provider to conduct these sweepstakes or contests; that company is prohibited from using your usersâ personal information for any other purpose. | Personal Data (97.0%), Processing (97.9%): Cookies A cookie is a small text file that we transfer to your computer and/or device, to identify a userâs computer/device and to ârememberâ things about your visit, such as your preferences or a user name and password. | Processing (94.2%), Required Purpose (98.6%): Information contained in a cookie may be linked to your personal information, such as your user ID, for purposes such as improving the quality of our Service, tailoring recommendations to your interests, and making the Service easier to use. | Required Purpose (93.6%), Technical Measure (98.2%): You can disable cookies at any time, although you may not be able to access or use features of the Service. | Organisational Measure (88.7%), Processing (64.9%): If you no longer wish to receive certain email notifications you may opt-out at any time by following the unsubscribe link located at the bottom of each communication or by emailing us at support@giraffe-games.com. | Processing (89.9%), Required Purpose (85.2%): We may feature advertisements served by third parties that deliver cookies to your computer/device so the content you access and advertisements you see can be tracked. | Required Purpose (98.4%), Third Party (93.4%): These advertisers may use information about your visits to our Service and third party sites and applications in order to measure advertisement performance and to provide advertisements about goods and services of interest to you. | Technical Measure (83.7%): You cannot use the Sites without accepting the use of cookies. | Required Purpose (90.8%): The cookies are used to support analytics and logged in users on the Site. | Technical Measure (99.2%): Clear Gifs (Web Beacons/Web Bugs) We employ or our third party tracking utility partner employs a software technology called clear gifs (a.k.a. | Required Purpose (75.1%): Web Beacons/Web Bugs), that help us better manage content on our site by informing us what content is effective. | Required Purpose (84.8%), Technical Measure (97.6%): Clear gifs are tiny graphics with a unique identifier, similar in function to cookies, and are used to track the online movements of Web users. | Processing (70.1%): In contrast to cookies, which are stored on a userâs computer hard drive, clear gifs are embedded invisibly on Web pages or e-mails and are about the size of the period at the end of this sentence. | Personal Data (96.7%): We may associate this information with your IP address or device identifier but do not tie the information gathered by clear gifs to our customersâ personal information. | Required Purpose (95.9%), Technical Measure (78.6%): Mobile Analytics We use mobile analytics software to allow us to better understand the functionality of our Mobile Software on your device. | Non-Personal Data (97.4%): This software may record information such as how often you use the application, the events that occur within the application, aggregated usage, performance data, and where the application was downloaded from. | Data Source (74.2%), Technical Measure (80.7%): Third Party Services Our services may contain third party tracking tools from Google Analytics, our service provider. | Required Purpose (90.7%): Such third party may use cookies, APIs, and SDKs in our services to enable them to collect and analyse user information on our behalf. | Personal Data (82.3%), Required Purpose (67.5%): The third party may have access to information such as your device identifier, MAC address, IMEI, locale (specific location where a given language is spoken), geo-location information, and IP address for the purpose of providing their services under their respective privacy policies. | Personal Data (97.4%): The information we collect when you connect your user account to an SN Service may include: (1) your name, (2) your SN Service user identification number and/or user name, (3) locale, city, state and country, (4) sex, (5) birth date, (6) email address, (7) profile picture or its URL, and (8) the SN Service user identification numbers for your friends that are also connected to Giraffeâs game(s). | Required Purpose (88.1%): Your interactions with these features are governed by the privacy policy of the company providing it. | Required Purpose (98.2%): Please review Facebookâs terms and conditions and privacy policy (here: https://www.facebook.com/about/privacy/update) because these third-party services are governed by their terms. | Required Purpose (65.3%): Ad Networks We do not serve ads within the Sites, but we do serve ads within our games and the advertisers we use have their own terms of service which are compatible with the terms of services of the mobile platforms. | Non-Personal Data (78.4%): The advertisers may collect and use information about you, such as your Service session activity, device identifier, MAC address, IMEI, geo-location information and IP address. | Required Purpose (96.0%): They may use this information to provide advertisements of interest to you. | Processing (97.6%): In order to verify the installs, a device identifier may be shared with the advertiser. | Required Purpose (96.7%): We use information collected through our Service for purposes described in this Policy or disclosed to you in connection with our Service. | Personal Data (74.3%), Processing (80.0%), Required Purpose (99.5%): For example, we may use your information to: – create game accounts and allow users to play our games; – identify and suggest connections with other Giraffe users; – operate and improve our Service; – understand you and your preferences to enhance your experience and enjoyment using our Service; – respond to your comments and questions and provide customer service; – provide and deliver products and services you request; – send you related information, including confirmations, invoices, technical notices, updates, security alerts, and support and administrative messages; – communicate with you about promotions, rewards, upcoming events, and other news about products and services offered by Giraffe and our selected partners; – enable you to communicate with other users; and – link or combine it with other information we get from third parties, to help understand your preferences and provide you with better services. | Third Party (70.0%): Since the third party advertising companies associate your computer/device with a number, they will be able to recognise your computer/device each time they send you an advertisement. | Required Purpose (97.7%): An example of these services include analysing data and providing customer support. | Third Party (66.1%): These agents and service providers may have access to your personal information in connection with the performance of services for Giraffe. | Legal Basis (84.5%), Processing (97.9%), Required Purpose (94.1%): – We may release your information as permitted by law, such as to comply with a court order, or when we believe that release is appropriate to comply with the law; investigate fraud, respond to a government request, enforce or apply our rights; or protect the rights, property, or safety of us or our users, or others. | Required Purpose (76.6%): This includes exchanging information with other companies and organizations for fraud protection. | Organisational Measure (68.3%): You will be notified via email and/or notice on our site of any change in ownership or users of your personal information. | Organisational Measure (61.2%), Personal Data (99.3%), Right (85.5%): Giraffe Games Limited and its affiliates (âGiraffeâ, âusâ, âourâ or âweâ) are dedicated to protecting the privacy rights of our users (âusersâ or âyouâ). | Non-Personal Data (65.5%), Third Party (99.1%): – We may share aggregate or anonymous information about you with advertisers, publishers, business partners, sponsors, and other third parties. | Organisational Measure (72.8%): Changes to the Policy We may update this privacy policy to reflect changes to our information practices. | Organisational Measure (93.7%): If we make any material changes we will notify you by means of a notice on this Site prior to the change becoming effective. | Organisational Measure (74.4%): Security We take reasonable measures to protect your information from unauthorised access or against loss, misuse or alteration by third parties. | Processing (93.7%): Although we make good faith efforts to store the information collected on the Service in a secure operating environment that is not available to the public, we cannot guarantee the absolute security of that information during its transmission or its storage on our systems. | Organisational Measure (63.3%), Processing (80.1%): Further, while we attempt to ensure the integrity and security of our network and systems, we cannot guarantee that our security measures will prevent third-party âhackersâ from illegally obtaining access to this information. | Processing (95.7%), Retention (90.2%): Data Retention We will retain your information for as long as your account is active or as needed to provide you services. | Required Purpose (83.1%): We will retain and use your information as necessary to comply with our legal obligations, resolve disputes, and enforce our agreements. | Legal Basis (71.5%), Personal Data (68.9%), Right (76.8%): You have many rights in relation to your data under the GDPR, if you would like to exercise one of these rights, please contact us at: contact@giraffe-games.com You have the right to ; Access. | Right (63.8%): We are entitled to request reasonable evidence to verify your identity before we provide you with information. | Art. 17 Right to erasure (‘right to be forgotten’) (77.4%): In some circumstances you have the right for your personal information to be erased. | Processing (86.0%): Executing this request will depend on you deleting our games from your devices and clearing cookies from any device where you have accessed our Site. | Processing (97.9%): In some instances, personal information about you that is visible through gameplay such as username, avatar, your high scores may be cached on other playersâ devices and we may not be able to remove or update that data from those devices. | Processing (77.1%): You may have the right to request that data which you have provided to us is exported and provided to you, so you can transfer this to another data controller, or that we transfer this data directly to another data controller. | Art. 18 Right to restriction of processing (70.2%): (contact us if you would like more information) Restriction of processing. | Art. 18 Right to restriction of processing (68.7%): You may have the right to request a restriction of the processing of your personal data, for example as an intermediate measure if we are investigating your claim for inaccurate data held. | Art. 21 Right to object (90.0%): Right to object. | Art. 21 Right to object (87.7%), Processing (93.9%): You have the right to object to the processing of personal data about you which is processed on the grounds of legitimate interests How long do we keep your data for? | Legal Basis (94.9%), Processing (96.6%), Scale Non-EU (76.1%): International Transfer Under EU data protection law, personal data transferred outside of the EU must have a legal mechanism for transfer (in order to ensure that the same protections are afforded to your personal data once it travels outside of the EU jurisdictions). | Scale EU (73.2%): Our hosted servers store your data in the EU. | Organisational Measure (88.3%): We take steps to ensure that there are adequate safeguards and mechanisms in place (including the use of EU model clauses and verifying the presence of agreements to privacy shield) to allow the transfer of your information across borders and outside of the EEA that might arise where data is processed by our third party service providers.</t>
+  </si>
+  <si>
     <t>['Data Controller (99%) - Meaning: Who decides how your data is used, eg. The app company']</t>
   </si>
   <si>
@@ -953,6 +2849,24 @@
   </si>
   <si>
     <t>['Data Controller (100%) - Meaning: Who decides how your data is used, eg. The app company', 'Processing (100%) - Meaning: How your data is handled and used, eg. Analyzing usage patterns', 'Required Purpose (100%) - Meaning: The reason your data is needed, eg. To provide app features', 'Third Party (99%) - Meaning: External companies that may get your data, eg. Advertisers', 'Right (92%) - Meaning: Your rights over your data, eg. Right to access or delete', 'Organisational Measure (97%) - Meaning: Company policies protecting your data, eg. Staff training', 'Personal Data (99%) - Meaning: Information that identifies you, eg. Name, email', 'Consent (98%) - Meaning: Your permission to use data, eg. Accepting terms', 'Art. 17 Right to erasure (‘right to be forgotten’) (92%) - Meaning: Your right to delete data, eg. Request app to delete account', 'Art. 21 Right to object (85%) - Meaning: Your right to object to processing, eg. Opt-out of marketing', 'Data Source (92%) - Meaning: Where your data comes from, eg. Your device or app usage', 'Data Subject (85%) - Meaning: The person whose data is collected, eg. You or your child', 'Non-Personal Data (97%) - Meaning: Data that doesn’t identify you, eg. Device model', 'Technical Measure (98%) - Meaning: Technology to secure your data, eg. Encryption', 'Automated Decision Making (94%) - Meaning: Decisions made by computers, eg. Personalized ads', 'Recipient (95%) - Meaning: Who receives your data, eg. Partner companies', 'Legal Basis (90%) - Meaning: Legal reason for data use, eg. Consent or contract', 'Scale Non-EU (95%) - Meaning: App operates outside EU, eg. US or Asia', 'Retention (96%) - Meaning: How long data is kept, eg. 1 year after last use', 'Legitimate Interest (89%) - Meaning: Valid reason for data use without consent, eg. Fraud prevention', 'Data Protection Officer (90%) - Meaning: Person responsible for data protection compliance in the company, eg. Privacy officer']</t>
+  </si>
+  <si>
+    <t>['Data Controller (100%) - Meaning: Who decides how your data is used, eg. The app company', 'Personal Data (100%) - Meaning: Information that identifies you, eg. Name, email', 'Processing (99%) - Meaning: How your data is handled and used, eg. Analyzing usage patterns', 'Legal Basis (98%) - Meaning: Legal reason for data use, eg. Consent or contract', 'Data Subject (96%) - Meaning: The person whose data is collected, eg. You or your child', 'Authority (93%) - Meaning: Regulatory bodies overseeing data protection, eg. Data protection commission', 'Scale EU (92%) - Meaning: App operates across EU countries, eg. Available in multiple EU nations', 'Scale Non-EU (97%) - Meaning: App operates outside EU, eg. US or Asia', 'Right (90%) - Meaning: Your rights over your data, eg. Right to access or delete', 'Automated Decision Making (94%) - Meaning: Decisions made by computers, eg. Personalized ads', 'Retention (97%) - Meaning: How long data is kept, eg. 1 year after last use', 'Required Purpose (100%) - Meaning: The reason your data is needed, eg. To provide app features', 'Third Party (99%) - Meaning: External companies that may get your data, eg. Advertisers', 'Non-Personal Data (92%) - Meaning: Data that doesn’t identify you, eg. Device model', 'Data Source (84%) - Meaning: Where your data comes from, eg. Your device or app usage', 'Recipient (96%) - Meaning: Who receives your data, eg. Partner companies', 'Technical Measure (98%) - Meaning: Technology to secure your data, eg. Encryption', 'Organisational Measure (90%) - Meaning: Company policies protecting your data, eg. Staff training', 'Consent (95%) - Meaning: Your permission to use data, eg. Accepting terms', 'Legitimate Interest (92%) - Meaning: Valid reason for data use without consent, eg. Fraud prevention', 'Art. 17 Right to erasure (‘right to be forgotten’) (72%) - Meaning: Your right to delete data, eg. Request app to delete account', 'Art. 18 Right to restriction of processing (74%) - Meaning: Your right to limit use, eg. Temporarily stop processing', 'Data Protection Officer (85%) - Meaning: Person responsible for data protection compliance in the company, eg. Privacy officer', 'Contract (80%) - Meaning: Agreement between you and app, eg. Service agreement']</t>
+  </si>
+  <si>
+    <t>['Processing (100%) - Meaning: How your data is handled and used, eg. Analyzing usage patterns', 'Personal Data (100%) - Meaning: Information that identifies you, eg. Name, email', 'Data Controller (99%) - Meaning: Who decides how your data is used, eg. The app company', 'Data Source (88%) - Meaning: Where your data comes from, eg. Your device or app usage', 'Consent (97%) - Meaning: Your permission to use data, eg. Accepting terms', 'Data Subject (88%) - Meaning: The person whose data is collected, eg. You or your child', 'Retention (92%) - Meaning: How long data is kept, eg. 1 year after last use', 'Third Party (99%) - Meaning: External companies that may get your data, eg. Advertisers', 'Non-Personal Data (98%) - Meaning: Data that doesn’t identify you, eg. Device model', 'Automated Decision Making (78%) - Meaning: Decisions made by computers, eg. Personalized ads', 'Required Purpose (100%) - Meaning: The reason your data is needed, eg. To provide app features', 'Technical Measure (99%) - Meaning: Technology to secure your data, eg. Encryption', 'Legitimate Interest (96%) - Meaning: Valid reason for data use without consent, eg. Fraud prevention', 'Authority (96%) - Meaning: Regulatory bodies overseeing data protection, eg. Data protection commission', 'Legal Basis (97%) - Meaning: Legal reason for data use, eg. Consent or contract', 'Recipient (77%) - Meaning: Who receives your data, eg. Partner companies', 'Organisational Measure (93%) - Meaning: Company policies protecting your data, eg. Staff training', 'Contract (95%) - Meaning: Agreement between you and app, eg. Service agreement', 'Right (95%) - Meaning: Your rights over your data, eg. Right to access or delete', 'Art. 17 Right to erasure (‘right to be forgotten’) (77%) - Meaning: Your right to delete data, eg. Request app to delete account', 'Art. 16 Right to rectification (95%) - Meaning: Your right to correct data, eg. Fixing wrong info']</t>
+  </si>
+  <si>
+    <t>['Processing (100%) - Meaning: How your data is handled and used, eg. Analyzing usage patterns', 'Personal Data (100%) - Meaning: Information that identifies you, eg. Name, email', 'Third Party (99%) - Meaning: External companies that may get your data, eg. Advertisers', 'Art. 17 Right to erasure (‘right to be forgotten’) (79%) - Meaning: Your right to delete data, eg. Request app to delete account', 'Legal Basis (98%) - Meaning: Legal reason for data use, eg. Consent or contract', 'Right (81%) - Meaning: Your rights over your data, eg. Right to access or delete', 'Data Controller (99%) - Meaning: Who decides how your data is used, eg. The app company', 'Data Subject (93%) - Meaning: The person whose data is collected, eg. You or your child', 'Required Purpose (100%) - Meaning: The reason your data is needed, eg. To provide app features', 'Retention (96%) - Meaning: How long data is kept, eg. 1 year after last use', 'Automated Decision Making (95%) - Meaning: Decisions made by computers, eg. Personalized ads', 'Non-Personal Data (78%) - Meaning: Data that doesn’t identify you, eg. Device model', 'Data Source (92%) - Meaning: Where your data comes from, eg. Your device or app usage', 'Organisational Measure (98%) - Meaning: Company policies protecting your data, eg. Staff training', 'Legitimate Interest (83%) - Meaning: Valid reason for data use without consent, eg. Fraud prevention', 'Recipient (83%) - Meaning: Who receives your data, eg. Partner companies', 'Data Protection Officer (80%) - Meaning: Person responsible for data protection compliance in the company, eg. Privacy officer', 'Authority (95%) - Meaning: Regulatory bodies overseeing data protection, eg. Data protection commission', 'Consent (85%) - Meaning: Your permission to use data, eg. Accepting terms', 'Scale Non-EU (86%) - Meaning: App operates outside EU, eg. US or Asia', 'Technical Measure (96%) - Meaning: Technology to secure your data, eg. Encryption']</t>
+  </si>
+  <si>
+    <t>['Scale Non-EU (75%) - Meaning: App operates outside EU, eg. US or Asia', 'Data Controller (100%) - Meaning: Who decides how your data is used, eg. The app company', 'Scale EU (81%) - Meaning: App operates across EU countries, eg. Available in multiple EU nations', 'Processing (100%) - Meaning: How your data is handled and used, eg. Analyzing usage patterns', 'Personal Data (99%) - Meaning: Information that identifies you, eg. Name, email', 'Data Subject (84%) - Meaning: The person whose data is collected, eg. You or your child', 'Third Party (99%) - Meaning: External companies that may get your data, eg. Advertisers', 'Legal Basis (99%) - Meaning: Legal reason for data use, eg. Consent or contract', 'Required Purpose (100%) - Meaning: The reason your data is needed, eg. To provide app features', 'Non-Personal Data (96%) - Meaning: Data that doesn’t identify you, eg. Device model', 'Right (73%) - Meaning: Your rights over your data, eg. Right to access or delete', 'Recipient (80%) - Meaning: Who receives your data, eg. Partner companies']</t>
+  </si>
+  <si>
+    <t>['Scale EU (78%) - Meaning: App operates across EU countries, eg. Available in multiple EU nations', 'Data Controller (100%) - Meaning: Who decides how your data is used, eg. The app company', 'Scale Non-EU (97%) - Meaning: App operates outside EU, eg. US or Asia', 'Processing (100%) - Meaning: How your data is handled and used, eg. Analyzing usage patterns', 'Required Purpose (100%) - Meaning: The reason your data is needed, eg. To provide app features', 'Data Subject (98%) - Meaning: The person whose data is collected, eg. You or your child', 'Organisational Measure (95%) - Meaning: Company policies protecting your data, eg. Staff training', 'Third Party (100%) - Meaning: External companies that may get your data, eg. Advertisers', 'Personal Data (100%) - Meaning: Information that identifies you, eg. Name, email', 'Consent (96%) - Meaning: Your permission to use data, eg. Accepting terms', 'Retention (94%) - Meaning: How long data is kept, eg. 1 year after last use', 'Non-Personal Data (97%) - Meaning: Data that doesn’t identify you, eg. Device model', 'Technical Measure (98%) - Meaning: Technology to secure your data, eg. Encryption', 'Legal Basis (99%) - Meaning: Legal reason for data use, eg. Consent or contract', 'Data Source (86%) - Meaning: Where your data comes from, eg. Your device or app usage', 'Right (76%) - Meaning: Your rights over your data, eg. Right to access or delete', 'Recipient (82%) - Meaning: Who receives your data, eg. Partner companies', 'Art. 17 Right to erasure (‘right to be forgotten’) (84%) - Meaning: Your right to delete data, eg. Request app to delete account']</t>
+  </si>
+  <si>
+    <t>['Data Controller (99%) - Meaning: Who decides how your data is used, eg. The app company', 'Personal Data (100%) - Meaning: Information that identifies you, eg. Name, email', 'Processing (99%) - Meaning: How your data is handled and used, eg. Analyzing usage patterns', 'Legal Basis (96%) - Meaning: Legal reason for data use, eg. Consent or contract', 'Data Subject (95%) - Meaning: The person whose data is collected, eg. You or your child', 'Organisational Measure (94%) - Meaning: Company policies protecting your data, eg. Staff training', 'Consent (98%) - Meaning: Your permission to use data, eg. Accepting terms', 'Third Party (99%) - Meaning: External companies that may get your data, eg. Advertisers', 'Non-Personal Data (97%) - Meaning: Data that doesn’t identify you, eg. Device model', 'Required Purpose (100%) - Meaning: The reason your data is needed, eg. To provide app features', 'Scale EU (83%) - Meaning: App operates across EU countries, eg. Available in multiple EU nations', 'Automated Decision Making (62%) - Meaning: Decisions made by computers, eg. Personalized ads', 'Data Source (82%) - Meaning: Where your data comes from, eg. Your device or app usage', 'Technical Measure (99%) - Meaning: Technology to secure your data, eg. Encryption', 'Art. 17 Right to erasure (‘right to be forgotten’) (77%) - Meaning: Your right to delete data, eg. Request app to delete account', 'Retention (90%) - Meaning: How long data is kept, eg. 1 year after last use', 'Right (86%) - Meaning: Your rights over your data, eg. Right to access or delete', 'Data Processor (61%) - Meaning: Who handles your data on behalf of the controller, eg. Cloud service provider', 'Art. 18 Right to restriction of processing (75%) - Meaning: Your right to limit use, eg. Temporarily stop processing', 'Art. 21 Right to object (90%) - Meaning: Your right to object to processing, eg. Opt-out of marketing', 'Scale Non-EU (76%) - Meaning: App operates outside EU, eg. US or Asia']</t>
   </si>
   <si>
     <t>Mentions Personal Data, Mentions Purpose of Use, Mentions Legal Basis, Mentions Your Rights, Mentions Responsible Parties, Mentions Third-Party Sharing</t>
@@ -1010,6 +2924,14 @@
  It does not explain user rights under data protection laws.</t>
   </si>
   <si>
+    <t>This privacy policy appears to comply with GDPR transparency requirements.
+ This privacy policy explains who is responsible for handling your child’s data.
+ It explains why the data is collected and how it's used to support their experience.
+ It mentions legal reasons for collecting and using this data, and that some information may be shared with other companies when needed.
+ The policy explains user rights when it comes to personal data.
+ However, It does not clearly explain how your data is kept safe.</t>
+  </si>
+  <si>
     <t>output_gdpr\bible_offline_kjv_holy_bible.pdf</t>
   </si>
   <si>
@@ -1026,6 +2948,27 @@
   </si>
   <si>
     <t>output_gdpr\snapchat.pdf</t>
+  </si>
+  <si>
+    <t>output_gdpr\uber___request_a_ride.pdf</t>
+  </si>
+  <si>
+    <t>output_gdpr\boomplay__music___live_stream.pdf</t>
+  </si>
+  <si>
+    <t>output_gdpr\youtube_kids.pdf</t>
+  </si>
+  <si>
+    <t>output_gdpr\facebook_lite.pdf</t>
+  </si>
+  <si>
+    <t>output_gdpr\whatsapp_business.pdf</t>
+  </si>
+  <si>
+    <t>output_gdpr\whatsapp_messenger.pdf</t>
+  </si>
+  <si>
+    <t>output_gdpr\car_restore___car_mechanic.pdf</t>
   </si>
   <si>
     <t>⚠️ **Bible Offline-KJV Holy Bible** is likely to share your or your child’s data with other companies.
@@ -1053,6 +2996,40 @@
     <t>⚠️ **Snapchat** is likely to share your or your child’s data with other companies.
 - It might say this clearly in the privacy policy (**25% chance**).
 - The way the policy is written strongly suggests sharing (**73% chance**), with about **1 parts** of the policy pointing to this.</t>
+  </si>
+  <si>
+    <t>⚠️ **Uber - Request a ride** is likely to share your or your child’s data with other companies.
+- It might say this clearly in the privacy policy (**70% chance**).
+- The way the policy is written strongly suggests sharing (**86% chance**), with about **1 parts** of the policy pointing to this.</t>
+  </si>
+  <si>
+    <t>⚠️ **Boomplay: Music &amp; Live Stream** is likely to share your or your child’s data with other companies.
+- It might say this clearly in the privacy policy (**69% chance**).
+- The way the policy is written strongly suggests sharing (**88% chance**), with about **9 parts** of the policy pointing to this.</t>
+  </si>
+  <si>
+    <t>✅ **YouTube Kids** probably doesn’t share your or your child’s data with other companies.
+- It doesn’t clearly say it does (**24% chance**).</t>
+  </si>
+  <si>
+    <t>⚠️ **Facebook Lite** is likely to share your or your child’s data with other companies.
+- It might say this clearly in the privacy policy (**33% chance**).
+- The way the policy is written strongly suggests sharing (**80% chance**), with about **6 parts** of the policy pointing to this.</t>
+  </si>
+  <si>
+    <t>⚠️ **WhatsApp Business** is likely to share your or your child’s data with other companies.
+- It might say this clearly in the privacy policy (**79% chance**).
+- The way the policy is written strongly suggests sharing (**79% chance**), with about **2 parts** of the policy pointing to this.</t>
+  </si>
+  <si>
+    <t>⚠️ **WhatsApp Messenger** is likely to share your or your child’s data with other companies.
+- It might say this clearly in the privacy policy (**76% chance**).
+- The way the policy is written strongly suggests sharing (**74% chance**), with about **5 parts** of the policy pointing to this.</t>
+  </si>
+  <si>
+    <t>⚠️ **Car Restore - Car Mechanic** is likely to share your or your child’s data with other companies.
+- It might say this clearly in the privacy policy (**55% chance**).
+- The way the policy is written strongly suggests sharing (**79% chance**), with about **4 parts** of the policy pointing to this.</t>
   </si>
 </sst>
 </file>
@@ -1423,7 +3400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AL15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1547,88 +3524,88 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="J2" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="K2" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="L2" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="M2" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="N2" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="O2" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="P2" t="s">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="Q2" t="s">
-        <v>121</v>
+        <v>210</v>
       </c>
       <c r="R2" t="s">
-        <v>124</v>
+        <v>213</v>
       </c>
       <c r="S2" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="T2" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="U2" t="s">
-        <v>131</v>
+        <v>220</v>
       </c>
       <c r="W2" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="X2" t="s">
-        <v>146</v>
+        <v>251</v>
       </c>
       <c r="AC2" t="s">
-        <v>164</v>
+        <v>299</v>
       </c>
       <c r="AE2" t="s">
-        <v>171</v>
+        <v>318</v>
       </c>
       <c r="AF2" t="s">
-        <v>176</v>
+        <v>329</v>
       </c>
       <c r="AG2" t="s">
         <v>28</v>
       </c>
       <c r="AH2" t="s">
-        <v>185</v>
+        <v>344</v>
       </c>
       <c r="AI2" t="s">
-        <v>190</v>
+        <v>350</v>
       </c>
       <c r="AJ2">
         <v>0</v>
@@ -1637,7 +3614,7 @@
         <v>0.4210513583689294</v>
       </c>
       <c r="AL2" t="s">
-        <v>196</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1645,106 +3622,106 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="G3" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="J3" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="K3" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="L3" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="M3" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="N3" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="O3" t="s">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
       <c r="Q3" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="R3" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="S3" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="T3" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="U3" t="s">
-        <v>132</v>
+        <v>221</v>
       </c>
       <c r="V3" t="s">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="W3" t="s">
-        <v>141</v>
+        <v>242</v>
       </c>
       <c r="X3" t="s">
-        <v>147</v>
+        <v>252</v>
       </c>
       <c r="Y3" t="s">
-        <v>151</v>
+        <v>262</v>
       </c>
       <c r="Z3" t="s">
-        <v>155</v>
+        <v>272</v>
       </c>
       <c r="AA3" t="s">
-        <v>159</v>
+        <v>282</v>
       </c>
       <c r="AB3" t="s">
-        <v>162</v>
+        <v>291</v>
       </c>
       <c r="AC3" t="s">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="AD3" t="s">
-        <v>168</v>
+        <v>309</v>
       </c>
       <c r="AE3" t="s">
-        <v>172</v>
+        <v>319</v>
       </c>
       <c r="AF3" t="s">
-        <v>177</v>
+        <v>330</v>
       </c>
       <c r="AG3" t="s">
-        <v>181</v>
+        <v>340</v>
       </c>
       <c r="AH3" t="s">
-        <v>186</v>
+        <v>345</v>
       </c>
       <c r="AI3" t="s">
-        <v>191</v>
+        <v>351</v>
       </c>
       <c r="AJ3">
         <v>1</v>
@@ -1753,7 +3730,7 @@
         <v>0.6122543312150134</v>
       </c>
       <c r="AL3" t="s">
-        <v>197</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1761,85 +3738,85 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="J4" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="K4" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="L4" t="s">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="M4" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="N4" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="O4" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="P4" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="Q4" t="s">
-        <v>123</v>
+        <v>212</v>
       </c>
       <c r="R4" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="S4" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="T4" t="s">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="U4" t="s">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="V4" t="s">
-        <v>137</v>
+        <v>232</v>
       </c>
       <c r="W4" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="X4" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="AF4" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="AG4" t="s">
-        <v>182</v>
+        <v>341</v>
       </c>
       <c r="AH4" t="s">
-        <v>187</v>
+        <v>346</v>
       </c>
       <c r="AI4" t="s">
-        <v>192</v>
+        <v>352</v>
       </c>
       <c r="AJ4">
         <v>0</v>
@@ -1848,7 +3825,7 @@
         <v>0.2902858589633263</v>
       </c>
       <c r="AL4" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1856,91 +3833,91 @@
         <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J5" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="K5" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="L5" t="s">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="M5" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="N5" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="O5" t="s">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="P5" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="Q5" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="R5" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="S5" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="T5" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="U5" t="s">
-        <v>131</v>
+        <v>220</v>
       </c>
       <c r="W5" t="s">
-        <v>143</v>
+        <v>244</v>
       </c>
       <c r="X5" t="s">
-        <v>148</v>
+        <v>253</v>
       </c>
       <c r="Y5" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="Z5" t="s">
-        <v>156</v>
+        <v>273</v>
       </c>
       <c r="AE5" t="s">
-        <v>173</v>
+        <v>320</v>
       </c>
       <c r="AF5" t="s">
-        <v>178</v>
+        <v>331</v>
       </c>
       <c r="AG5" t="s">
-        <v>183</v>
+        <v>342</v>
       </c>
       <c r="AH5" t="s">
-        <v>188</v>
+        <v>347</v>
       </c>
       <c r="AI5" t="s">
-        <v>193</v>
+        <v>353</v>
       </c>
       <c r="AJ5">
         <v>0</v>
@@ -1949,7 +3926,7 @@
         <v>0.4989213822451439</v>
       </c>
       <c r="AL5" t="s">
-        <v>199</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1957,103 +3934,103 @@
         <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="I6" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="J6" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="K6" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="L6" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="N6" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="O6" t="s">
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="P6" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="Q6" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="R6" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="S6" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="T6" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="U6" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="V6" t="s">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="W6" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c r="X6" t="s">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="Y6" t="s">
-        <v>153</v>
+        <v>264</v>
       </c>
       <c r="Z6" t="s">
-        <v>157</v>
+        <v>274</v>
       </c>
       <c r="AA6" t="s">
-        <v>160</v>
+        <v>283</v>
       </c>
       <c r="AC6" t="s">
-        <v>166</v>
+        <v>301</v>
       </c>
       <c r="AD6" t="s">
-        <v>169</v>
+        <v>310</v>
       </c>
       <c r="AE6" t="s">
-        <v>174</v>
+        <v>321</v>
       </c>
       <c r="AF6" t="s">
-        <v>179</v>
+        <v>332</v>
       </c>
       <c r="AG6" t="s">
-        <v>184</v>
+        <v>343</v>
       </c>
       <c r="AH6" t="s">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="AI6" t="s">
-        <v>194</v>
+        <v>354</v>
       </c>
       <c r="AJ6">
         <v>1</v>
@@ -2062,7 +4039,7 @@
         <v>0.6355248737535333</v>
       </c>
       <c r="AL6" t="s">
-        <v>200</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -2070,106 +4047,106 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="H7" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="I7" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="J7" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="K7" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="L7" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
       <c r="M7" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="N7" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="O7" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="P7" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="Q7" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="R7" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="S7" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="T7" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="U7" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="V7" t="s">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="W7" t="s">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="X7" t="s">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="Y7" t="s">
-        <v>154</v>
+        <v>265</v>
       </c>
       <c r="Z7" t="s">
-        <v>158</v>
+        <v>275</v>
       </c>
       <c r="AA7" t="s">
-        <v>161</v>
+        <v>284</v>
       </c>
       <c r="AB7" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
       <c r="AC7" t="s">
-        <v>167</v>
+        <v>302</v>
       </c>
       <c r="AD7" t="s">
-        <v>170</v>
+        <v>311</v>
       </c>
       <c r="AE7" t="s">
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="AF7" t="s">
-        <v>180</v>
+        <v>333</v>
       </c>
       <c r="AG7" t="s">
-        <v>181</v>
+        <v>340</v>
       </c>
       <c r="AH7" t="s">
-        <v>186</v>
+        <v>345</v>
       </c>
       <c r="AI7" t="s">
-        <v>195</v>
+        <v>355</v>
       </c>
       <c r="AJ7">
         <v>0</v>
@@ -2178,7 +4155,845 @@
         <v>0.251150477790481</v>
       </c>
       <c r="AL7" t="s">
-        <v>201</v>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" t="s">
+        <v>135</v>
+      </c>
+      <c r="J8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K8" t="s">
+        <v>158</v>
+      </c>
+      <c r="L8" t="s">
+        <v>171</v>
+      </c>
+      <c r="M8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N8" t="s">
+        <v>179</v>
+      </c>
+      <c r="O8" t="s">
+        <v>188</v>
+      </c>
+      <c r="P8" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>211</v>
+      </c>
+      <c r="R8" t="s">
+        <v>179</v>
+      </c>
+      <c r="S8" t="s">
+        <v>216</v>
+      </c>
+      <c r="T8" t="s">
+        <v>218</v>
+      </c>
+      <c r="U8" t="s">
+        <v>225</v>
+      </c>
+      <c r="V8" t="s">
+        <v>235</v>
+      </c>
+      <c r="W8" t="s">
+        <v>247</v>
+      </c>
+      <c r="X8" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>303</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>312</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>323</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>334</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>340</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>356</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>0.6989835343534325</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" t="s">
+        <v>136</v>
+      </c>
+      <c r="J9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" t="s">
+        <v>159</v>
+      </c>
+      <c r="L9" t="s">
+        <v>172</v>
+      </c>
+      <c r="M9" t="s">
+        <v>126</v>
+      </c>
+      <c r="N9" t="s">
+        <v>179</v>
+      </c>
+      <c r="O9" t="s">
+        <v>189</v>
+      </c>
+      <c r="P9" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>211</v>
+      </c>
+      <c r="R9" t="s">
+        <v>179</v>
+      </c>
+      <c r="S9" t="s">
+        <v>216</v>
+      </c>
+      <c r="T9" t="s">
+        <v>218</v>
+      </c>
+      <c r="U9" t="s">
+        <v>226</v>
+      </c>
+      <c r="V9" t="s">
+        <v>236</v>
+      </c>
+      <c r="W9" t="s">
+        <v>246</v>
+      </c>
+      <c r="X9" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>267</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>294</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>304</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>313</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>324</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>335</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>340</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>0.6857878731128222</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H10" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K10" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" t="s">
+        <v>173</v>
+      </c>
+      <c r="M10" t="s">
+        <v>179</v>
+      </c>
+      <c r="N10" t="s">
+        <v>179</v>
+      </c>
+      <c r="O10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P10" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>211</v>
+      </c>
+      <c r="R10" t="s">
+        <v>179</v>
+      </c>
+      <c r="S10" t="s">
+        <v>216</v>
+      </c>
+      <c r="T10" t="s">
+        <v>218</v>
+      </c>
+      <c r="U10" t="s">
+        <v>220</v>
+      </c>
+      <c r="W10" t="s">
+        <v>244</v>
+      </c>
+      <c r="X10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>341</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>358</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0.2393871878588744</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" t="s">
+        <v>132</v>
+      </c>
+      <c r="J11" t="s">
+        <v>148</v>
+      </c>
+      <c r="K11" t="s">
+        <v>161</v>
+      </c>
+      <c r="L11" t="s">
+        <v>174</v>
+      </c>
+      <c r="M11" t="s">
+        <v>122</v>
+      </c>
+      <c r="N11" t="s">
+        <v>179</v>
+      </c>
+      <c r="O11" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>211</v>
+      </c>
+      <c r="R11" t="s">
+        <v>179</v>
+      </c>
+      <c r="S11" t="s">
+        <v>216</v>
+      </c>
+      <c r="T11" t="s">
+        <v>218</v>
+      </c>
+      <c r="U11" t="s">
+        <v>227</v>
+      </c>
+      <c r="V11" t="s">
+        <v>237</v>
+      </c>
+      <c r="W11" t="s">
+        <v>248</v>
+      </c>
+      <c r="X11" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>295</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>305</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>314</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>325</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>336</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>340</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>359</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0.3307308523275453</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" t="s">
+        <v>149</v>
+      </c>
+      <c r="K12" t="s">
+        <v>162</v>
+      </c>
+      <c r="L12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M12" t="s">
+        <v>128</v>
+      </c>
+      <c r="N12" t="s">
+        <v>179</v>
+      </c>
+      <c r="O12" t="s">
+        <v>192</v>
+      </c>
+      <c r="P12" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>211</v>
+      </c>
+      <c r="R12" t="s">
+        <v>179</v>
+      </c>
+      <c r="S12" t="s">
+        <v>216</v>
+      </c>
+      <c r="T12" t="s">
+        <v>218</v>
+      </c>
+      <c r="U12" t="s">
+        <v>228</v>
+      </c>
+      <c r="V12" t="s">
+        <v>238</v>
+      </c>
+      <c r="W12" t="s">
+        <v>249</v>
+      </c>
+      <c r="X12" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>279</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>296</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>306</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>315</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>326</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>337</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>340</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>349</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>360</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>0.7925833015825525</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K13" t="s">
+        <v>163</v>
+      </c>
+      <c r="L13" t="s">
+        <v>176</v>
+      </c>
+      <c r="M13" t="s">
+        <v>128</v>
+      </c>
+      <c r="N13" t="s">
+        <v>179</v>
+      </c>
+      <c r="O13" t="s">
+        <v>193</v>
+      </c>
+      <c r="P13" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>211</v>
+      </c>
+      <c r="R13" t="s">
+        <v>179</v>
+      </c>
+      <c r="S13" t="s">
+        <v>216</v>
+      </c>
+      <c r="T13" t="s">
+        <v>218</v>
+      </c>
+      <c r="U13" t="s">
+        <v>229</v>
+      </c>
+      <c r="V13" t="s">
+        <v>239</v>
+      </c>
+      <c r="W13" t="s">
+        <v>250</v>
+      </c>
+      <c r="X13" t="s">
+        <v>260</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>280</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>307</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>316</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>327</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>338</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>340</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>361</v>
+      </c>
+      <c r="AJ13">
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <v>0.7628811949605253</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" t="s">
+        <v>117</v>
+      </c>
+      <c r="H14" t="s">
+        <v>124</v>
+      </c>
+      <c r="I14" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14" t="s">
+        <v>160</v>
+      </c>
+      <c r="L14" t="s">
+        <v>173</v>
+      </c>
+      <c r="M14" t="s">
+        <v>179</v>
+      </c>
+      <c r="N14" t="s">
+        <v>124</v>
+      </c>
+      <c r="O14" t="s">
+        <v>194</v>
+      </c>
+      <c r="P14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" t="s">
+        <v>151</v>
+      </c>
+      <c r="K15" t="s">
+        <v>164</v>
+      </c>
+      <c r="L15" t="s">
+        <v>177</v>
+      </c>
+      <c r="M15" t="s">
+        <v>123</v>
+      </c>
+      <c r="N15" t="s">
+        <v>179</v>
+      </c>
+      <c r="O15" t="s">
+        <v>195</v>
+      </c>
+      <c r="P15" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>211</v>
+      </c>
+      <c r="R15" t="s">
+        <v>179</v>
+      </c>
+      <c r="S15" t="s">
+        <v>216</v>
+      </c>
+      <c r="T15" t="s">
+        <v>218</v>
+      </c>
+      <c r="U15" t="s">
+        <v>230</v>
+      </c>
+      <c r="V15" t="s">
+        <v>240</v>
+      </c>
+      <c r="W15" t="s">
+        <v>246</v>
+      </c>
+      <c r="X15" t="s">
+        <v>261</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>290</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>308</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>317</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>328</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>339</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>340</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>362</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>0.5509156435921251</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -2195,6 +5010,24 @@
     <hyperlink ref="F6" r:id="rId10"/>
     <hyperlink ref="C7" r:id="rId11"/>
     <hyperlink ref="F7" r:id="rId12"/>
+    <hyperlink ref="C8" r:id="rId13"/>
+    <hyperlink ref="F8" r:id="rId14"/>
+    <hyperlink ref="C9" r:id="rId15"/>
+    <hyperlink ref="F9" r:id="rId16"/>
+    <hyperlink ref="C10" r:id="rId17"/>
+    <hyperlink ref="F10" r:id="rId18"/>
+    <hyperlink ref="J10" r:id="rId19"/>
+    <hyperlink ref="C11" r:id="rId20"/>
+    <hyperlink ref="F11" r:id="rId21"/>
+    <hyperlink ref="C12" r:id="rId22"/>
+    <hyperlink ref="F12" r:id="rId23"/>
+    <hyperlink ref="C13" r:id="rId24"/>
+    <hyperlink ref="F13" r:id="rId25"/>
+    <hyperlink ref="C14" r:id="rId26"/>
+    <hyperlink ref="F14" r:id="rId27"/>
+    <hyperlink ref="J14" r:id="rId28"/>
+    <hyperlink ref="C15" r:id="rId29"/>
+    <hyperlink ref="F15" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PARENT_App/data/app_analysis_results.xlsx
+++ b/PARENT_App/data/app_analysis_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="282">
   <si>
     <t>APP_ID</t>
   </si>
@@ -145,6 +145,24 @@
     <t>com.zhiliaoapp.musically</t>
   </si>
   <si>
+    <t>com.deepseek.chat</t>
+  </si>
+  <si>
+    <t>com.whatsapp</t>
+  </si>
+  <si>
+    <t>com.adobe.reader</t>
+  </si>
+  <si>
+    <t>com.snapchat.android</t>
+  </si>
+  <si>
+    <t>com.ss.android.tt.creator</t>
+  </si>
+  <si>
+    <t>com.instapaper.android</t>
+  </si>
+  <si>
     <t>Instagram</t>
   </si>
   <si>
@@ -160,6 +178,24 @@
     <t>TikTok - Videos, Shop &amp; LIVE</t>
   </si>
   <si>
+    <t>DeepSeek - AI Assistant</t>
+  </si>
+  <si>
+    <t>WhatsApp Messenger</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat Reader: Edit PDF</t>
+  </si>
+  <si>
+    <t>Snapchat</t>
+  </si>
+  <si>
+    <t>TikTok Studio</t>
+  </si>
+  <si>
+    <t>Instapaper</t>
+  </si>
+  <si>
     <t>https://play-lh.googleusercontent.com/VRMWkE5p3CkWhJs6nv-9ZsLAs1QOg5ob1_3qg-rckwYW7yp1fMrYZqnEFpk0IoVP4LM</t>
   </si>
   <si>
@@ -175,6 +211,24 @@
     <t>https://play-lh.googleusercontent.com/BmUViDVOKNJe0GYJe22hsr7juFndRVbvr1fGmHGXqHfJjNAXjd26bfuGRQpVrpJ6YbA</t>
   </si>
   <si>
+    <t>https://play-lh.googleusercontent.com/d2zqBFBEymSZKaVg_dRo1gh3hBFn7_Kl9rO74xkDmnJeLgDW0MoJD3cUx0QzZN6jdsg</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/bYtqbOcTYOlgc6gqZ2rwb8lptHuwlNE75zYJu6Bn076-hTmvd96HH-6v7S0YUAAJXoJN</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/BkRfMfIRPR9hUnmIYGDgHHKjow-g18-ouP6B2ko__VnyUHSi1spcc78UtZ4sVUtBH4g</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/KxeSAjPTKliCErbivNiXrd6cTwfbqUJcbSRPe_IBVK_YmwckfMRS1VIHz-5cgT09yMo</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/w3STXz2lqMEQy65UEI9gbFkW8CQMe9xR8EY-2lbyaAVXBNExr221ApEITJfhNbXzHDk</t>
+  </si>
+  <si>
+    <t>https://play-lh.googleusercontent.com/uQElx_kgheNkInfRZl6_iPZ34HLOpt1KMOiVWmcN_PZFRQ66Ug3vDaAS0eymjsok7g</t>
+  </si>
+  <si>
     <t>SOCIAL</t>
   </si>
   <si>
@@ -184,6 +238,15 @@
     <t>TOOLS</t>
   </si>
   <si>
+    <t>PRODUCTIVITY</t>
+  </si>
+  <si>
+    <t>COMMUNICATION</t>
+  </si>
+  <si>
+    <t>NEWS_AND_MAGAZINES</t>
+  </si>
+  <si>
     <t>Teen</t>
   </si>
   <si>
@@ -205,6 +268,21 @@
     <t>https://www.tiktok.com/legal/privacy-policy</t>
   </si>
   <si>
+    <t>https://cdn.deepseek.com/policies/en-US/deepseek-privacy-policy.html</t>
+  </si>
+  <si>
+    <t>https://www.whatsapp.com/legal/privacy-policy</t>
+  </si>
+  <si>
+    <t>http://www.adobe.com/privacy/policy.html</t>
+  </si>
+  <si>
+    <t>http://www.snapchat.com/privacy</t>
+  </si>
+  <si>
+    <t>https://instapaper.com/privacy</t>
+  </si>
+  <si>
     <t>{'Device &amp; app history': ['retrieve running apps'], 'Identity': ['add or remove accounts', 'find accounts on the device', 'read your own contact card'], 'Calendar': ["add or modify calendar events and send email to guests without owners' knowledge"], 'Contacts': ['find accounts on the device', 'read your contacts'], 'Location': ['precise location (GPS and network-based)'], 'SMS': ['receive text messages (SMS)'], 'Phone': ['directly call phone numbers', 'read call log', 'read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['access Bluetooth settings', 'change network connectivity', 'change your audio settings', 'connect and disconnect from Wi-Fi', 'control vibration', 'create accounts and set passwords', 'full network access', 'install shortcuts', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read battery statistics', 'reorder running apps', 'run at startup', 'uninstall shortcuts', 'use accounts on the device', 'view network connections'], 'Uncategorized': ['capture video output', 'change screen orientation', 'read frame buffer', 'receive data from Internet']}</t>
   </si>
   <si>
@@ -220,6 +298,24 @@
     <t>{'Contacts': ['read your contacts'], 'Location': ['approximate location (network-based)'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Other': ['allow Wi-Fi Multicast reception', 'change network connectivity', 'change your audio settings', 'control Near Field Communication', 'control vibration', 'draw over other apps', 'full network access', 'pair with Bluetooth devices', 'prevent device from sleeping', 'reorder running apps', 'set wallpaper', 'view network connections'], 'Uncategorized': ['read Home settings and shortcuts', 'receive data from Internet']}</t>
   </si>
   <si>
+    <t>{'Camera': ['take pictures and videos'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Other': ['Google Play license check', 'change network connectivity', 'connect and disconnect from Wi-Fi', 'full network access', 'view network connections']}</t>
+  </si>
+  <si>
+    <t>{'Device &amp; app history': ['retrieve running apps'], 'Identity': ['add or remove accounts', 'find accounts on the device', 'read your own contact card'], 'Contacts': ['find accounts on the device', 'modify your contacts', 'read your contacts'], 'Location': ['approximate location (network-based)', 'precise location (GPS and network-based)'], 'SMS': ['receive text messages (SMS)', 'send SMS messages'], 'Phone': ['directly call phone numbers', 'read call log', 'read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['access Bluetooth settings', 'change network connectivity', 'change your audio settings', 'connect and disconnect from Wi-Fi', 'control Near Field Communication', 'control vibration', 'create accounts and set passwords', 'draw over other apps', 'full network access', 'install shortcuts', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read Google service configuration', 'read sync settings', 'reorder running apps', 'run at startup', 'send sticky broadcast', 'toggle sync on and off', 'uninstall shortcuts', 'use accounts on the device', 'view network connections'], 'Uncategorized': ['read sync statistics', 'receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Identity': ['add or remove accounts'], 'Contacts': ['read your contacts'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Other': ['change your audio settings', 'control Near Field Communication', 'control vibration', 'create accounts and set passwords', 'full network access', 'prevent device from sleeping', 'run at startup', 'use accounts on the device', 'view network connections'], 'Uncategorized': ['receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Identity': ['find accounts on the device', 'read your own contact card'], 'Contacts': ['find accounts on the device', 'modify your contacts', 'read your contacts'], 'Location': ['precise location (GPS and network-based)'], 'Phone': ['read phone status and identity'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Device ID &amp; call information': ['read phone status and identity'], 'Other': ['access Bluetooth settings', 'change network connectivity', 'change your audio settings', 'connect and disconnect from Wi-Fi', 'control flashlight', 'control vibration', 'create accounts and set passwords', 'full network access', 'pair with Bluetooth devices', 'prevent device from sleeping', 'read sync settings', 'run at startup', 'toggle sync on and off', 'view network connections'], 'Uncategorized': ['read sync statistics', 'receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Contacts': ['read your contacts'], 'Location': ['approximate location (network-based)', 'precise location (GPS and network-based)'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Camera': ['take pictures and videos'], 'Microphone': ['record audio'], 'Wi-Fi connection information': ['view Wi-Fi connections'], 'Other': ['change network connectivity', 'change your audio settings', 'control Near Field Communication', 'control vibration', 'draw over other apps', 'full network access', 'pair with Bluetooth devices', 'prevent device from sleeping', 'reorder running apps', 'set wallpaper', 'view network connections'], 'Uncategorized': ['read Home settings and shortcuts', 'receive data from Internet']}</t>
+  </si>
+  <si>
+    <t>{'Location': ['approximate location (network-based)'], 'Photos/Media/Files': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Storage': ['modify or delete the contents of your USB storage', 'read the contents of your USB storage'], 'Other': ['full network access', 'modify system settings', 'prevent device from sleeping', 'run at startup', 'view network connections'], 'Uncategorized': ['receive data from Internet']}</t>
+  </si>
+  <si>
     <t>['CONTACTS', 'CALENDAR', 'LOCATION', 'SMS', 'PHONE_CALL', 'PERSISTENTID', 'STORAGE', 'CAMERA', 'MICROPHONE']</t>
   </si>
   <si>
@@ -230,6 +326,18 @@
   </si>
   <si>
     <t>['CONTACTS', 'LOCATION', 'STORAGE', 'CAMERA', 'MICROPHONE', 'PERSISTENTID']</t>
+  </si>
+  <si>
+    <t>['CAMERA', 'LOCATION', 'PERSISTENTID']</t>
+  </si>
+  <si>
+    <t>['CONTACTS', 'LOCATION', 'SMS', 'PHONE_CALL', 'PERSISTENTID', 'STORAGE', 'CAMERA', 'MICROPHONE']</t>
+  </si>
+  <si>
+    <t>['CONTACTS', 'STORAGE', 'CAMERA', 'MICROPHONE', 'LOCATION', 'PERSISTENTID']</t>
+  </si>
+  <si>
+    <t>['LOCATION', 'STORAGE', 'PERSISTENTID']</t>
   </si>
   <si>
     <t>👥 CONTACTS: Could share your child’s contacts with others.
@@ -262,6 +370,34 @@
 📁 STORAGE: Could save or read your child’s photos or downloads.
 🎥 CAMERA: Could record your child’s face or surroundings.
 🎙️ MICROPHONE: Could listen to your child talk or play.
+🆔 DEVICE ID: Could track your child across apps or over time.</t>
+  </si>
+  <si>
+    <t>🎥 CAMERA: Could record your child’s face or surroundings.
+📍 LOCATION: Can follow your child’s location.
+🆔 DEVICE ID: Could track your child across apps or over time.</t>
+  </si>
+  <si>
+    <t>👥 CONTACTS: Could share your child’s contacts with others.
+📍 LOCATION: Can follow your child’s location.
+💬 SMS: Could send or read text messages without your knowledge.
+📞 PHONE CALL: Could make calls without your permission.
+🆔 DEVICE ID: Could track your child across apps or over time.
+📁 STORAGE: Could save or read your child’s photos or downloads.
+🎥 CAMERA: Could record your child’s face or surroundings.
+🎙️ MICROPHONE: Could listen to your child talk or play.</t>
+  </si>
+  <si>
+    <t>👥 CONTACTS: Could share your child’s contacts with others.
+📁 STORAGE: Could save or read your child’s photos or downloads.
+🎥 CAMERA: Could record your child’s face or surroundings.
+🎙️ MICROPHONE: Could listen to your child talk or play.
+📍 LOCATION: Can follow your child’s location.
+🆔 DEVICE ID: Could track your child across apps or over time.</t>
+  </si>
+  <si>
+    <t>📍 LOCATION: Can follow your child’s location.
+📁 STORAGE: Could save or read your child’s photos or downloads.
 🆔 DEVICE ID: Could track your child across apps or over time.</t>
   </si>
   <si>
@@ -1009,6 +1145,763 @@
 Mailing Address: TikTok Inc., Attn: Privacy Policy Inquiry, 5800 Bristol Parkway, Suite 100, Culver City, CA 90230</t>
   </si>
   <si>
+    <t>DeepSeek Privacy Policy
+DeepSeek Privacy Policy
+Last Update:  July 4, 2025
+Welcome to DeepSeek!
+Introduction
+This privacy policy (âPrivacy Policyâ) applies to the Personal Data (or other similar terms as defined by applicable data protection law) relating to you (âPersonal Dataâ) that DeepSeek processes in connection with DeepSeek apps, websites, software, and related services (the âServicesâ), that link to or reference this Privacy Policy. The Services enable you to create and interact with chatbots.
+Data Controller: The Services are provided and controlled by Hangzhou DeepSeek Artificial Intelligence Co., Ltd., with its registered address in China (âweâ or âusâ). If you have any questions about how we use your Personal Data, please contact privacy@deepseek.com or click the âContact usâ column on the website.
+Please be informed that the processing rules for Personal Data collected from end users when accessing downstream systems or applications developed by developers using our open platform services are not covered by this privacy policy. The developer operating the application, as the controller of the Personal Data processing activity, should disclose the relevant Personal Data protection policies to the end users. If you would like to learn more about our model mechanism or training methods, please refer to the Model Mechanism and Training Methods of DeepSeek.
+What Personal Data We Collect
+We collect your Personal Data in three ways: Personal Data You Provide, Automatically Collected Personal Data, and Personal Data From Other Sources. More detail is provided below.
+Personal Data You Provide
+When you create an account, input content, contact us directly, or otherwise use the Services, you may provide some or all of the following Personal Data:
+Account Personal Data. We collect Personal Data that you provide when you set up an account, such as your date of birth (where applicable), username (where applicable), email address and/or telephone number, and password.
+User Input. When you use our Services, we may collect your text input, prompt, uploaded files, feedback, chat history, or other content that you provide to our model and Services (âPromptsâ or "Inputs"). We generate responses (âOutputsâ) based on your Inputs.
+Personal Data When You Contact Us. When you contact us, we collect the Personal Data you send us, such as proof of identity or age, contact details, feedback or inquiries about your use of the Services or Personal Data about possible violations of our Terms of Service (our âTermsâ) or other policies.
+Automatically Collected Personal Data
+We automatically collect certain Personal Data from you when you use the Services, including internet or other network activity Personal Data such as your IP address, unique device identifiers, and cookies.
+Device and Network Personal Data. We collect certain device and network connection Personal Data when you access the Services. This Personal Data includes your device model, operating system, IP address, device identifiers and system language. We also collect service-related, diagnostic, and performance Personal Data, including crash reports and performance logs. We automatically assign you a device ID and user ID. Where you log-in from multiple devices, we use Personal Data such as your device ID and user ID to identify your activity across devices to give you a seamless log-in experience and for security purposes.
+Log Personal Data. We collect Personal Data regarding your use of the Services, such as the features you use and the actions you take.
+Location Personal Data. We automatically collect Personal Data about your approximate location based on IP address for security reasons, for example to protect your account by detecting unusual login activity.
+Cookies &amp; Similar Technologies. We may use cookies and similar tracking technologies to operate and provide the Service. For example, we use cookies  for security purposes and to better understand how the Service is used. We will allow you to manage  our use of non-essential cookies where required by law. To learn more about our use of cookies, please see our Cookies Policy.
+Payment Personal Data. When you use paid services for prepayment, we collect your payment order and transaction Personal Data to provide Services such as order placement, payment, customer service, and after-sales support.
+To avoid any doubt, Cookies &amp; Similar Technologies and Payment Personal Data are not applicable to DeepSeek App.
+Personal Data from Other Sources
+We may receive the Personal Data described in this Privacy Policy from other sources, such as:
+Log-in, Sign-up, or Linked Services. Where available, if you choose to sign-up or log-in to the Services using a third-party service such as Apple or Google, or link your account to a third-party service, we may collect Personal Data from the third-party service, such as access token.
+Security Personal Data. We receive Personal Data from our trusted partners, such as security partners, to protect against fraud, abuse, and other security threats to our Services.
+Public Personal Data. We may obtain publicly available Personal Data via online sources  to train our models and provide Services.
+The Services are not designed or intended to process sensitive Personal Data (e.g., personal data revealing racial or ethnic origin, religious beliefs, health, sexuality, citizenship, immigration status, genetic or biometric data, personal data of children, precise geolocation or criminal membership). We do not ask for, and you should not provide sensitive Personal Data to the Services, whether about yourself or other individuals.
+How We Use Your Personal Data
+We use your Personal Data to operate, provide, develop, and improve the Services, including for the following purposes.
+To provide, administer and maintain the Services and to enforce our terms, conditions and policies. Such as creating the accounts, deliver a fast and convenient logging-in experience, enabling you to chat with DeepSeek and provide user support.
+To improve and develop the Services and to train and improve our technology, such as our machine learning models and algorithms. Including by monitoring interactions and usage across your devices, analyzing how people are using it, and training and improving our technology.
+To communicate with you, including to notify you about changes to the  Services, provide customer support to you and send you other service-related messages.
+To promote the safety, security, and stability of the  Services, such as by preventing and detecting abuse, fraud, and illegal activity on the Services and by conducting troubleshooting, data analysis, testing, and research.
+To comply with our legal obligations, or as necessary to perform tasks in the public interest, or to protect the vital interests of our users and other people. This could include providing law enforcement agencies or emergency services with Personal Data in urgent situations to protect health or life.
+PLEASE NOTE: We do not engage in âprofilingâ or otherwise engage in automated processing of Personal Data to make decisions that could have legal or similarly significant impact on you or others.
+How We Share Your Personal Data
+Service Providers
+We engage service providers that help us provide, support, and develop the Services and understand how they are used. We share Personal Data You Provide, Automatically Collected Personal Data, and Personal Data From Other Sources with these service providers as necessary to enable them to provide their services. For example:
+We use communication service providers to send notifications and/or communications to you.
+We integrate third-party APIs to provide search services, and we will share your input to provide these services.
+We use analytics services providers to analyse data.
+We use support and safety monitoring services providers to assist us in ensuring the safety of our Services.
+Pursuant to our instructions, these parties will access, process, or store Personal Data only in the course of performing their duties to us.
+Our Corporate Group
+The Services are supported by certain entities within our corporate group. These entities process the Personal Data You Provide, Automatically Collected Personal Data, and Personal Data from Other Sources for us, as necessary to provide certain functions, such as storage, content delivery, security, research and development, analytics, customer and technical support.
+Other Third Parties
+We share your Personal Data with the following categories of third parties in other limited scenarios as follows:
+Parties to a Corporate Transaction. Your Personal Data may be disclosed to third parties in connection with a corporate transaction, such as a merger, sale of assets or shares, reorganization, financing, change of control, or acquisition of all or a portion of our business.
+Law Enforcement and Parties with Other Legal  Rights. We may access, preserve, and share the Personal Data described in âWhat Personal Data We Collectâ with law enforcement agencies, public authorities, copyright holders, or other third parties if we have good faith belief that it is necessary to:
+comply with applicable law, legal process or government requests, as consistent with internationally recognized standards,
+protect the rights, property, and safety of our users, copyright holders, and others, including protecting life or preventing imminent bodily harm. For example, we may provide Personal Data (such as your IP address) to law enforcement agencies in the event of an emergency where someoneâs life or safety is at risk,
+investigate potential violations of and enforce our Terms, Guidelines, or any other applicable terms, policies, or standards, or
+detect, investigate, prevent, or address misleading activity, copyright infringement, or other illegal activity.
+With Your Consent
+Depending on where you live, we may share Personal Data with the proper authorization or to provide the Services you have requested or authorized. For example, if you choose to log in to our Services using a social network account, or share Personal Data from our Services to a social media service, we will share that Personal Data with those third parties services.
+Third-party content. The Services may contain links to policies, functionality, or content maintained by third parties not controlled by us. We are not responsible for, and make no representations regarding, such policies, functionality, or content or any other practices or operations of such third parties.
+Your Rights
+Depending on where you live and subject to exceptions provided under applicable data protection laws, you may have certain rights with respect to your Personal Data.
+To exercise your rights, you or an authorized agent may submit a request by emailing us at privacy@deepseek.com.
+After we receive your request, we may verify it by requesting information sufficient to confirm your identity or authority to exercise a right on behalf of someone else.
+You may also have the right to appeal requests that we deny by emailing privacy@deepseek.com. If your appeal is unsuccessful and depending on where you live, you may have the right to raise a concern or lodge a complaint with the competent authority.
+We will not discriminate against you for exercising any privacy right you may have.
+Privacy rights that may be available to you include:
+the right to know whether and how we process your Personal Data;
+the right to access your Personal Data;
+the right to correct inaccuracies in your Personal Data;
+the right to delete Personal Data youâve provided to us, or that weâve obtained about you;
+the right to receive a portable copy of Personal Data youâve      provided to us, or that weâve obtained about you, to the extent it is available in a digital format, and where technically feasible, in a format that allows you to transfer your Personal Data to another service, and
+the right to opt-out of the processing of your Personal Data for the purposes of targeted advertising, sale or profiling that could have legal or similarly consequential impact on you.  NOTE WE DO NOT ENGAGE IN TARGETED ADVERTISING, âSELLâ PERSONAL DATA OR USE PERSONAL DATA FOR âPROFILINGâ OR OTHERWISE ENGAGE IN AUTOMATED PROCESSING OF PERSONAL DATA TO MAKE DECISIONS THAT COULD HAVE LEGAL OR SIMILARLY SIGNIFICANT IMPACT ON YOU OR OTHERS.
+Your Choices
+You can control and access some of your Personal Data directly through settings. For example, you can manage your chat history. Should you choose to do so, you may also delete your chat history via your settings.
+If you choose to delete your account, you will not be able to reactivate your account or retrieve any of the content or Personal Data in connection with your account.
+A note about accuracy: Services like DeepSeek generate responses by reading a userâs request and, in response, predicting the words most likely to appear next. In some cases, the words most likely to appear next may not be the most factually accurate.
+For this reason, you should not rely on the factual accuracy of Output from our models. If you notice that Output contains factually inaccurate Personal Data about you and you would like to request a correction or removal of the Personal Data, you can submit these requests through privacy@deepseek.com and we will consider your request based on applicable law and the technical capabilities of our models.
+The Security of Your Personal Data
+The security of your Personal Data is important to us. We maintain commercially reasonable technical, administrative, and physical security measures that are designed to protect your Personal Data from unauthorized access, theft, disclosure, modification, or loss. We regularly review our security measures to consider available new technology and methods. However, no Internet or email transmission is ever fully secure or error free. In particular, emails sent to or from us may not be secure. Therefore, you should take special care in deciding what Personal Data you send to us via the Services or email. In addition, we are not responsible for circumvention of any privacy settings or security measures contained on the Services, or third-party websites.
+How Long Do We Keep Your Personal Data
+We retain Personal Data for as long as necessary to provide our Services and for the other purposes set out in this Privacy Policy. We also retain Personal Data when necessary to comply with contractual and legal obligations, when we have a legitimate business interest to do so (such as improving and developing our Services and enhancing their safety, security and stability), and for the exercise or defense of legal claims.
+The retention periods will be different depending on the amount, type and sensitivity of Personal Data, the purposes for which we use the Personal Data and any legal requirements, etc. For example, when we process your Personal Data to provide you with the Services, we keep this Personal Data for as long as you have an account. This Personal Data includes your account Personal Data, input and payment Personal Data. If you violate any of our terms, policies or guidelines, we may keep your Personal Data as necessary to process the violation.
+When the Personal Data collected is no longer required by us, we and our service providers will perform the necessary procedures for destroying, deleting, erasing, or converting it into an anonymous form as permitted or required under applicable laws.
+Where We Store Your Personal Data
+The Personal Data we collect from you may be stored on a server located outside of the country where you live. To provide you with our services, we directly collect, process and store your Personal Data in People's Republic of China .
+Where required, we will use appropriate safeguards for transferring Personal Data outside of certain countries, including for one or more of the purposes as set out in this Policy, we will do so in accordance with the requirements of applicable data protection laws.
+Personal Data relating to Children
+Our Services are not aimed at children, and we do not knowingly process Personal Data from children. If we notice or receive feedback that we have collected any of their Personal Data from a child, we will investigate, and where appropriate, delete the Personal Data to the extent permitted by applicable law. If you believe that we processed Personal Data about or collected from a child, please contact us at privacy@deepseek.com.
+Privacy Policy Updates
+We may update this Privacy Policy from time to time as required by law. When we update the Privacy Policy, we will notify you by updating the âLast Updatedâ date at the top of the new Privacy Policy, posting the new Privacy Policy, or by providing any other notice required by applicable law. We recommend that you review the Privacy Policy each time you access our Services to stay informed of our privacy practices.
+Contact Us
+Questions, comments and requests regarding this policy should be addressed to privacy@deepseek.com or click âContact usâ column on the website.
+Supplemental  Clause - Jurisdiction-Specific
+European Economic Area (âEEAâ), Switzerland, and UK
+If you are using the Services in the EEA, Switzerland or the UK (the âEuropean Regionâ), the following additional terms apply:
+Legal bases for processing.
+We use your Personal Data only as permitted by law. Our legal bases for processing your Personal Data described in this Privacy Policy are described in the table below.
+Please be aware that we collect your Personal Data for the purposes set out in the table above. You may choose not to provide some of the Personal Data fields, but this may affect the Services you are able to use from us.
+Purpose of processing
+Personal Data categories
+Legal bases
+To provide, administer and maintain the Services and to enforce our terms, conditions and policies. Such as creating the accounts, deliver a fast and convenient logging-in experience, enabling you to chat with DeepSeek and provide user support.
+Account Personal Data
+User Input
+Personal Data When You Contact Us
+Device and Network Personal Data
+Log Personal Data
+Location Personal Data
+Cookies
+Performance of a contract with you when we provide and maintain our services. To take steps that you request prior to signing up for an account to use the Platform.
+Your consent when we ask for it to process your Personal Data for a specific purpose to help you create accounts.
+Legitimate interests. If you are 14 or older but under the age of 18, with a limited ability to enter into an enforceable contract only, where we may be unable to process your Personal Data on the grounds of contractual necessity, we rely on legitimate interests and use the Personal Data we collect to allow you to access and use the Platform.
+To improve and develop the Services and to train and improve our technology, such as our machine learning models and algorithms. Including by monitoring interactions and usage across your devices, analyzing how people are using it, and training and improving our technology.
+Account Personal Data
+User Input
+Personal Data When You Contact Us
+Device and Network Personal Data
+Log Personal Data
+Location Personal Data
+Cookies
+Our legitimate interests to identify and resolve issues with the Platform and to improve the Platform; and to conduct research and protect Personal Data through aggregation or anonymization, consistent with data minimization and privacy by design principles.
+Your consent when we ask for it to process your Personal Data for a specific purpose to provide services.
+To comply with our legal obligations, or as necessary to perform tasks in the public interest, or to protect the vital interests of our users and other people. This could include providing law enforcement agencies or emergency services with Personal Data in urgent situations to protect health or life.
+Account Personal Data
+User Input
+Personal Data When You Contact Us
+Device and Network Personal Data
+Log Personal Data
+Location Personal Data
+Cookies
+Compliance with our legal obligations. This includes situations where we have obligations to take measures to ensure the safety of our users or comply with a valid legal request such as an order from law enforcement agencies or courts; and where we have obligations to comply with applicable law or when we protect our or our affiliatesâ, usersâ, or third partiesâ rights, safety, and property.
+Our legitimate interests to protect our business, employees and users from illegal activities, inappropriate behavior or violations of terms that would be detrimental, and to disclose and share Personal Data with regulators or other government entities.
+To communicate with you, including to notify you about changes to the Platform, provide customer support to you and send you other service-related messages.
+Account Personal Data
+Personal Data When You Contact Us
+Location Personal Data
+Performance of a contract with you when we provide and maintain our services.
+Your consent when we ask for it to process your Personal Data for a specific purpose to communicate with you.
+To promote the safety, security, and stability of the Platform, such as by preventing and detecting abuse, fraud, and illegal activity on the Platform and by conducting troubleshooting, data analysis, testing, and research.
+Account Personal Data
+User Input
+Personal Data When You Contact Us
+Device and Network Personal Data
+Log Personal Data
+Location Personal Data
+Cookies
+Compliance with our legal obligations when we use your Personal Data to comply with applicable law or when we protect our or our affiliatesâ, usersâ, or third partiesâ rights, safety, and property.
+Our legitimate interests to ensure that the Platform is safe and secure.
+Data storage
+Please be aware that our servers are located in the Peopleâs Republic of China. When you access our services, your Personal Data may be processed and stored in our servers in the Peopleâs Republic of China. This may be a direct provision of your Personal Data to us or a transfer that we or a third-party make.
+Your rights
+You have the following rights:
+The right to request free of charge (i) confirmation of whether we process your Personal Data and (ii) access to a copy of the Personal Data retained;
+The right to request proper rectification or erasure of your Personal Data or restriction of the processing of your Personal Data;
+Where processing of your Personal Data is either based on your consent or necessary for the performance of a contract with you and processing is carried out by automated means, the right to receive the Personal Data concerning you in a structured, commonly used and machine-readable format or to have your Personal Data transmitted directly to another company, where technically feasible (data portability);
+Where the processing of your Personal Data is based on your consent, the right to withdraw your consent at any time (withdrawal will not impact the lawfulness of data processing activities that have taken place before such withdrawal);
+The right not to be subject to any automatic individual decisions, including profiling, which produces legal effects on you or similarly significantly affects you unless we have your consent, this is authorised by European Union or Member State law or this is necessary for the performance of a contract;
+The right to object to processing if we are processing your Personal Data on the basis of our legitimate interest unless we can demonstrate compelling legitimate grounds which may override your right. If you object to such processing, we ask you to state the grounds of your objection in order for us to examine the processing of your Personal Data and to balance our legitimate interest in processing and your objection to this processing;
+You have the right to request the restriction of the processing of your Personal Data where (a) you are challenging the accuracy of the Personal Data, (b) the Personal Data has been unlawfully processed, but you are opposing the deletion of that Personal Data, (c) where you need the Personal Data to be retained for the pursuit or defense of a legal claim, or (d) you have objected to the processing and you are awaiting the outcome of that objection request.
+The right to object to processing your Personal Data for direct marketing purposes; and
+The right to lodge complaints before your local data protection authority.
+Before we can respond to a request to exercise one or more of the rights listed above, you may be required to verify your identity or your account details.
+Please send an email to us if you would like to exercise any of your rights at privacy@deepseek.com.
+We value your privacy and your rights as a data subject and have therefore appointed Prighter Group with its local partners as our privacy representative and your point of contact for the following regions:
+-European Union (EU)
+-United Kingdom (UK)
+If you wish to lodge a data subject request, you may also exercise your rights by contacting us at rep_deepseek@prighter.com, with âData Subject Requestâ in the subject line, setting out the details of your rights request.Â To verify the appointment of Prighter as our representative and for further contact details please visitÂ https://app.prighter.com/portal/deepseek.
+powered by
+Prighter
+powered by
+Prighter</t>
+  </si>
+  <si>
+    <t>Privacy Policy
+Skip to contentHome
+Features
+Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI
+Privacy
+Help Center
+Blog
+For Business
+Download
+Download
+Terms &amp; Privacy Policy2025 © WhatsApp LLC
+Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）
+FeaturesMessage privatelyEnd-to-end encryption and privacy controls.
+Stay connectedMessage and call for free* around the world.
+Connect in groupsGroup messaging made easy.
+Express yourselfSay it with stickers, voice, GIFs and more.
+Secure by designLayers of protection to help you stay safe.
+Share your everydayShare photos, videos, voice notes on Status.
+Follow channelsStay updated on topics you care about.
+Do More with
+Meta AIGet help with anything.
+Privacy
+Help Center
+Blog
+For Business
+Apps
+Log inDownload
+WhatsApp Privacy Policy
+Effective January 4, 2021archived versions
+If you live in the European Region, WhatsApp Ireland Limited provides the Services to you under this Terms of Service and Privacy Policy.
+If you live in the UK, WhatsApp LLC provides the Services to you under this Terms of Service  and Privacy Policy.
+WhatsApp Legal Info
+If you live outside the European Region or the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Services to you under this Terms of Service and Privacy Policy.
+Our Privacy Policy ("Privacy Policy") helps explain our data practices, including the information we process to provide our Services.
+For example, our Privacy Policy talks about what information we collect and how this affects you. It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services.
+We are one of the Meta Companies. You can learn more further below in this Privacy Policy about the ways in which we share information across this family of companies.
+This Privacy Policy applies to all of our Services unless specified otherwise.
+Please also read WhatsApp’s Terms of Service ("Terms"), which describe the terms under which you use and we provide our Services.
+Back to top
+Key Updates
+Respect for your privacy is coded into our DNA. Since we started WhatsApp, we’ve built our services with a set of strong privacy principles in mind. In our updated Terms of Service and Privacy Policy you’ll find:
+Additional Information On How We Handle Your Data. Our updated Terms and Privacy Policy provide more information on how we process your data, and our commitment to privacy. For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information.
+Better Communication With Businesses. Many businesses rely on WhatsApp to communicate with their customers and clients. We work with businesses that use Meta or third parties to help store and better manage their communications with you on WhatsApp.
+Making It Easier To Connect. As part of the Meta Companies, WhatsApp partners with Meta to offer experiences and integrations across Meta’s family of apps and products.
+Back to top
+Information We Collect
+WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services.
+The types of information we receive and collect depend on how you use our Services. We require certain information to deliver our Services and without this we will not be able to provide our Services to you. For example, you must provide your mobile phone number to create an account to use our Services.
+Our Services have optional features which, if used by you, require us to collect additional information to provide such features. You will be notified of such collection, as appropriate. If you choose not to provide the information needed to use a feature, you will be unable to use the feature. For example, you cannot share your location with your contacts if you do not permit us to collect your location data from your device. Permissions can be managed through your Settings menu on both Android and iOS devices.
+Information You Provide
+Your Account Information. You must provide your mobile phone number and basic information (including a profile name of your choice) to create a WhatsApp account. If you don’t provide us with this information, you will not be able to create an account to use our Services. You can add other information to your account, such as a profile picture and "about" information.
+Your Messages. We do not retain your messages in the ordinary course of providing our Services to you. Instead, your messages are stored on your device and not typically stored on our servers. Once your messages are delivered, they are deleted from our servers. The following scenarios describe circumstances where we may store your messages in the course of delivering them: Undelivered Messages. If a message cannot be delivered immediately (for example, if the recipient is offline), we keep it in encrypted form on our servers for up to 30 days as we try to deliver it. If a message is still undelivered after 30 days, we delete it.
+Media Forwarding. When a user forwards media within a message, we store that media temporarily in encrypted form on our servers to aid in more efficient delivery of additional forwards.
+We offer end-to-end encryption for our Services. End-to-end encryption means that your messages are encrypted to protect against us and third parties from reading them. Learn more about end-to-end encryption and how businesses communicate with you on WhatsApp.
+Your Connections. You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. If any of your contacts aren’t yet using our Services, we’ll manage this information for you in a way that ensures those contacts cannot be identified by us. Learn more about our contact upload feature here. You can create, join, or get added to groups and broadcast lists, and such groups and lists get associated with your account information. You give your groups a name. You can provide a group profile picture or description.
+Status Information. You may provide us your status if you choose to include one on your account. Learn how to use status on Android, iPhone, or KaiOS.
+Transactions And Payments Data. If you use our payments services, or use our Services meant for purchases or other financial transactions, we process additional information about you, including payment account and transaction information. Payment account and transaction information includes information needed to complete the transaction (for example, information about your payment method, shipping details and transaction amount). If you use our payments services available in your country or territory, our privacy practices are described in the applicable payments privacy policy.
+Customer Support And Other Communications. When you contact us for customer support or otherwise communicate with us, you may provide us with information related to your use of our Services, including copies of your messages, any other information you deem helpful, and how to contact you (e.g., an email address). For example, you may send us an email with information relating to app performance or other issues.
+Automatically Collected Information
+Usage And Log Information. We collect information about your activity on our Services, like service-related, diagnostic, and performance information. This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information.
+Device And Connection Information. We collect device and connection-specific information when you install, access, or use our Services. This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account).
+Location Information. We collect and use precise location information from your device with your permission when you choose to use location-related features, like when you decide to share your location with your contacts or view locations nearby or locations others have shared with you. There are certain settings relating to location-related information which you can find in your device settings or the in-app settings, such as location sharing. Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). We also use your location information for diagnostics and troubleshooting purposes.
+Cookies. We use cookies to operate and provide our Services, including to provide our Services that are web-based, improve your experiences, understand how our Services are being used, and customize them. For example, we use cookies to provide our Services for web and desktop and other web-based services. We may also use cookies to understand which of our Help Center articles are most popular and to show you relevant content related to our Services. Additionally, we may use cookies to remember your choices, like your language preferences, to provide a safer experience, and otherwise to customize our Services for you. Learn more about how we use cookies to provide you our Services.
+Back to top
+Third-Party Information
+Information Others Provide About You. We receive information about you from other users. For example, when other users you know use our Services, they may provide your phone number, name, and other information (like information from their mobile address book) just as you may provide theirs. They may also send you messages, send messages to groups to which you belong, or call you. We require each of these users to have lawful rights to collect, use, and share your information before providing any information to us.
+You should keep in mind that in general any user can capture screenshots of your chats or messages or make recordings of your calls with them and send them to WhatsApp or anyone else, or post them on another platform.
+User Reports. Just as you can report other users, other users or third parties may also choose to report to us your interactions and your messages with them or others on our Services; for example, to report possible violations of our Terms or policies. When a report is made, we collect information on both the reporting user and reported user. To find out more about what happens when a user report is made, please see Advanced Safety and Security Features.
+Businesses On WhatsApp. Businesses you interact with using our Services may provide us with information about their interactions with you. We require each of these businesses to act in accordance with applicable law when providing any information to us.
+When you message with a business on WhatsApp, keep in mind that the content you share may be visible to several people in that business. In addition, some businesses might be working with third-party service providers (which may include Meta) to help manage their communications with their customers. For example, a business may give such third-party service provider access to its communications to send, store, read, manage, or otherwise process them for the business. To understand how a business processes your information, including how it might share your information with third parties or Meta, you should review that business’ privacy policy or contact the business directly.
+Third-Party Service Providers. We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. For example, we work with them to distribute our apps; provide our technical and physical infrastructure, delivery, and other systems; provide engineering support, cybersecurity support, and operational support; supply location, map, and places information; process payments; help us understand how people use our Services; market our Services; help you connect with businesses using our Services; conduct surveys and research for us; ensure safety, security, and integrity; and help with customer service. These companies may provide us with information about you in certain circumstances; for example, app stores may provide us with reports to help us diagnose and fix service issues.
+The "How We Work With Other Meta Companies" section below provides more information about how WhatsApp collects and shares information with the other Meta Companies.
+Third-Party Services. We allow you to use our Services in connection with third-party services and Meta Company Products. If you use our Services with such third-party services or Meta Company Products, we may receive information about you from them; for example, if you use the WhatsApp share button on a news service to share a news article with your WhatsApp contacts, groups, or broadcast lists on our Services, or if you choose to access our Services through a mobile carrier’s or device provider’s promotion of our Services. Please note that when you use third-party services or Meta Company Products, their own terms and privacy policies will govern your use of those services and products.
+Back to top
+How We Use Information
+We use information we have (subject to choices you make and applicable law) to operate, provide, improve, understand, customize, support, and market our Services. Here's how:
+Our Services. We use information we have to operate and provide our Services, including providing customer support; completing purchases or transactions; improving, fixing, and customizing our Services; and connecting our Services with Meta Company Products that you may use. We also use information we have to understand how people use our Services; evaluate and improve our Services; research, develop, and test new services and features; and conduct troubleshooting activities. We also use your information to respond to you when you contact us.
+Safety, Security, And Integrity. Safety, security, and integrity are an integral part of our Services. We use information we have to verify accounts and activity; combat harmful conduct; protect users against bad experiences and spam; and promote safety, security, and integrity on and off our Services, such as by investigating suspicious activity or violations of our Terms and policies, and to ensure our Services are being used legally. Please see the Law, Our Rights and Protection section below for more information.
+Communications About Our Services And The Meta Companies. We use information we have to communicate with you about our Services and let you know about our terms, policies, and other important updates. We may provide you marketing for our Services and those of the Meta Companies.
+No Third-Party Banner Ads. We still do not allow third-party banner ads on our Services. We have no intention to introduce them, but you may see other types of ads in the Updates Tab, home of features like Channels and Status.
+Business Interactions. We enable you and third parties, like businesses, to communicate and interact with each other using our Services, such as Catalogs for businesses on WhatsApp through which you can browse products and services and place orders. Businesses may send you transaction, appointment, and shipping notifications; product and service updates; and marketing. For example, you may receive flight status information for upcoming travel, a receipt for something you purchased, or a notification when a delivery will be made. Messages you receive from a business could include an offer for something that might interest you. We do not want you to have a spammy experience; as with all of your messages, you can manage these communications, and we will honor the choices you make.
+Back to top
+Information You And We Share
+You share your information as you use and communicate through our Services, and we share your information to help us operate, provide, improve, understand, customize, support, and market our Services.
+Send Your Information To Those With Whom You Choose To Communicate. You share your information (including messages) as you use and communicate through our Services.
+Information Associated With Your Account. Your phone number, profile name and photo, "about" information, last seen information, and message receipts are available to anyone who uses our Services, although you can configure your Services settings to manage certain information available to other users, including businesses, with whom you communicate.
+Your Contacts And Others. Users, including businesses, with whom you communicate can store or reshare your information (including your phone number or messages) with others on and off our Services. You can use your Services settings and the “block” feature in our Services to manage who you communicate with on our Services and certain information you share.
+Businesses On WhatsApp. We offer specific services to businesses such as providing them with metrics regarding their use of our Services.
+Third-Party Service Providers. We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. We work with these companies to support our Services, such as to provide technical infrastructure, delivery and other systems; market our Services; conduct surveys and research for us; protect the safety, security, and integrity of users and others; and assist with customer service. When we share information with third-party service providers and other Meta Companies in this capacity, we require them to use your information on our behalf in accordance with our instructions and terms.
+Third-Party Services. When you or others use third-party services or other Meta Company Products that are integrated with our Services, those third-party services may receive information about what you or others share with them. For example, if you use a data backup service integrated with our Services (like iCloud or Google Account), they will receive information you share with them, such as your WhatsApp messages. If you interact with a third-party service or another Meta Company Product linked through our Services, such as when you use the in-app player to play content from a third-party platform, information about you, like your IP address and the fact that you are a WhatsApp user, may be provided to such third party or Meta Company Product. Please note that when you use third-party services or other Meta Company Products, their own terms and privacy policies will govern your use of those services and products.
+Back to top
+How We Work With Other Meta Companies
+As part of the Meta Companies, WhatsApp receives information from, and shares information (see here) with, the other Meta Companies. We may use the information we receive from them, and they may use the information we share with them, to help operate, provide, improve, understand, customize, support, and market our Services and their offerings, including the Meta Company Products. This includes:
+helping improve infrastructure and delivery systems;
+understanding how our Services or theirs are used;
+promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities;
+improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and
+providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. For example, allowing you to connect your Facebook Pay account to pay for things on WhatsApp or enabling you to chat with your friends on other Meta Company Products, such as Portal, by connecting your WhatsApp account.
+Learn more about the other Meta Companies and their privacy practices by reviewing their privacy policies.
+Back to top
+Assignment, Change Of Control, And Transfer
+In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws.
+Back to top
+Managing And Retaining Your Information
+You can access or port your information using our in-app Request Account Info feature (available under Settings &gt; Account). For iPhone users, you can learn how to access, manage, and delete your information through our iPhone Help Center articles. For Android users, you can learn how to access, manage, and delete your information through our Android Help Center articles.
+We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. The storage periods are determined on a case-by-case basis that depends on factors like the nature of the information, why it is collected and processed, relevant legal or operational retention needs, and legal obligations.
+If you would like to further manage, change, limit, or delete your information, you can do that through the following tools:
+Services Settings. You can change your Services settings to manage certain information available to other users. You can manage your contacts, groups, and broadcast lists, or use our “block” feature to manage the users with whom you communicate.
+Changing Your Mobile Phone Number, Profile Name And Picture, And “About” Information. If you change your mobile phone number, you must update it using our in-app change number feature and transfer your account to your new mobile phone number. You can also change your profile name, profile picture, and "about" information at any time.
+Deleting Your WhatsApp Account. You can delete your WhatsApp account at any time (including if you want to revoke your consent to our use of your information pursuant to applicable law) using our in-app delete my account feature. When you delete your WhatsApp account, your undelivered messages are deleted from our servers as well as any of your other information we no longer need to operate and provide our Services. Deleting your account will, for example, delete your account info and profile photo, delete you from all WhatsApp groups, and delete your WhatsApp message history. Be mindful that if you only delete WhatsApp from your device without using our in-app delete my account feature, your information will be stored with us for a longer period. Please remember that when you delete your account, it does not affect your information related to the groups you created or the information other users have relating to you, such as their copy of the messages you sent them.
+You can learn more here about our data deletion and retention practices and about how to delete your account.
+Back to top
+Law, Our Rights, And Protection
+We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm.
+Back to top
+Our Global Operations
+WhatsApp shares information globally, both internally within the Meta Companies and externally with our partners and service providers, and with those with whom you communicate around the world, in accordance with this Privacy Policy. Your information may, for example, be transferred or transmitted to, or stored and processed in, the United States; countries or territories where the Meta Companies’ affiliates and partners, or our service providers are located; or any other country or territory globally where our Services are provided outside of where you live for the purposes as described in this Privacy Policy. WhatsApp uses Meta’s global infrastructure and data centers, including in the United States. These transfers are necessary to provide the global Services set forth in our Terms. Please keep in mind that the countries or territories to which your information is transferred may have different privacy laws and protections than what you have in your home country or territory.
+Back to top
+Updates To Our Policy
+We may amend or update our Privacy Policy. We will provide you notice of amendments to this Privacy Policy, as appropriate, and update the “Effective Date” at the top of this Privacy Policy. Please review our Privacy Policy from time to time.
+Back to top
+Privacy Rights for United States Residents
+You can learn more about the consumer privacy rights that may be available to you, by reviewing the United States Regional Privacy Notice here.
+Back to top
+Contact Us
+If you have questions or issues about our Privacy Policy, please contact us.
+WhatsApp LLC
+Privacy Policy
+1601 Willow Road
+Menlo Park, California 94025
+United States of America
+Back to top
+Download
+Download
+What we do
+FeaturesBlogSecurityFor Business
+Who we are
+About usCareersBrand CenterPrivacy
+Use WhatsApp
+AndroidiPhoneMac/PCWhatsApp Web
+Need help?
+Contact UsHelp CenterAppsSecurity Advisories
+Download
+2025 © WhatsApp LLC
+Terms &amp; Privacy PolicySitemap
+Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）</t>
+  </si>
+  <si>
+    <t>Adobe Privacy Policy
+Adobe Privacy Policy
+Last updated: June 3, 2025
+The Adobe Privacy Policy describes the privacy practices of Adobe’s Services and Software (as defined in our General Terms of Use) and anywhere we display or reference this policy.
+If you are a resident of North America, your relationship is with Adobe Inc. (Adobe U.S.) and the laws of California and the United States apply.
+If you reside outside of North America, your relationship is with Adobe Systems Software Ireland Limited (Adobe Ireland), which is the controller with regard to your personal information collected by Adobe, and the laws of Ireland apply.
+If the content or information that you store in Adobe Services and Software contains personal information of other individuals, you must be legally permitted to disclose the personal information to Adobe.
+Summary of Key Points
+At Adobe we take data privacy seriously. We believe in transparency so you can control your data and make informed choices about how it is used. We are here to support and protect your privacy decisions wherever you use our products and services. Adobe prioritizes your control over the data you store in the cloud in the following ways:
+This policy explains when we process personal information for our legitimate interests. You can ask us to stop processing this information. Learn more about your rights and how you can exercise them.
+This policy also explains when we will first get your consent before processing your personal information, including when doing so is required by law.
+We use your personal information to enable you to register with Adobe and to provide you with our Services and Software, and other products or services that you request. Learn more.
+We provide interactive features that engage with social media sites, such as Facebook. If you use these features, these sites will send us personal information about you. Learn more.
+We use cookies and other technologies to track the use of our Services and Software. To learn about opportunities to choose not to allow cookies, click here. If you are using our website in a browser, this information is also available in our Cookies Policy.
+There are several places within Adobe’s Services and Software that allow you to post comments, upload pictures, or submit content which will be publicly available where you choose to participate in these activities. We also disclose personal information to other companies in the Adobe family and with advertising and sales partners consistent with your choices. We also disclose information with third parties we engage to process personal information on our behalf or when such sharing is required by law, or in certain other situations. Learn more.
+We provide additional information regarding your location specific privacy rights and choices, available in the Location Specific Privacy Rights and Information Notice.
+What does this privacy policy cover?
+What information does Adobe collect about me?
+How does Adobe use the information it collects about me, and what are the legal bases for these uses?
+Does Adobe disclose my personal information to others?
+Is my personal information displayed anywhere within Adobe's apps or websites?
+Is my personal information secure?
+Where does Adobe store my personal information?
+Does Adobe transfer my personal information across national borders?
+What rights do I have regarding my personal information and how can I exercise these?
+What rights do I have in my location?
+Withdrawing consent or otherwise objecting to direct marketing
+How long does Adobe retain my information?
+Can children use Adobe websites and apps?
+Will this privacy policy change?
+Who can I contact with questions or concerns?
+What does this privacy policy cover?
+This privacy policy describes how Adobe (also referred to as "we," "us" or "our") will make use of your information in the context of:
+Adobe websites and web-based services (together referred to as "websites");
+Services that display or include a reference to this policy;
+Adobe’s marketing, sales, and advertising practices;
+The privacy practices of previously acquired companies, unless otherwise noted here.
+This privacy policy applies when (i) Adobe provides products and services directly to an individual (such as when you buy on Adobe.com or units via resellers) or (ii) Adobe collects usage information from employee users of Adobe enterprise customers (unless otherwise directed by an enterprise customer). In (i) and (ii), we are considered the “data controller” because we determine what personal data will be collected and how it will be handled, as detailed and allowed per this policy.
+In contrast, Adobe is considered the “data processor” and not the data controller when enterprise customers such as businesses or educational institutions, use Adobe products and services (e.g., Adobe Experience Cloud) to support their own provision of products and services to individuals since Adobe acts at the direction of these enterprise customers regarding any collection or processing of data on their behalf. This privacy policy does not apply to the data Adobe enterprise customers may collect from individuals or their uses of that data. For questions about any specific organization’s data practices in these scenarios, please contact the organization directly. You can also find more privacy information about Adobe Experience Cloud here.
+In some cases, different or additional privacy and data protection policies and notices apply.
+Some of our products and services have different or extra privacy details to consider. For example, when we acquire a company, their privacy policy and notices apply until such time as Adobe’s privacy practices are implemented. Also, certain products and locations have additional privacy policies and notices that may apply. You can find these, along with other relevant policies, on our Additional Privacy Policies page within the Adobe Privacy Center.
+Please also see the Adobe Terms of Use and any additional Terms of Use or Consumer Product License Agreements that may apply to the Services and Software you are using.
+anchor
+cover
+What information does Adobe collect about me?
+Adobe ID, registration, and customer support
+When you register to use an Adobe Service, create an Adobe ID, purchase a license to our Services and Software, or contact us for support or other offerings, Adobe collects information that identifies you. This includes:
+Identifiers and contact information, such as:
+Name;
+Email address;
+Telephone number;
+Postal or Physical Address;
+Country;
+Commercial and transaction information, such as:
+Payment/billing information (where an app or website is 'paid for');
+Licenses purchased;
+Eligibility information (e.g., student or teacher identification for student and teacher editions of apps);
+Content of and information provided through customer support and other communications (e.g., recorded customer and technical support calls and stored content of your correspondence with us via our website, chat features, phone and video calls, emails, and other channels);
+Types of Services and Software of interest.
+Professional, education or other demographic information, such as:
+Date of birth;
+Company or school name;
+Title;
+Occupation;
+Job function;
+Expertise;
+Company details, such as the size, industry, and other information about the company where a user may work (when the user has provided the company name);
+Analytics or other electronic network activity, such as:
+IP address;
+Browser;
+Mobile Device ID;
+Browser extensions connected to your Adobe accounts.
+Inferred and Third-Party Data
+To help keep our databases current and to provide you the most relevant content and experiences, we may infer or generate information based on the information we collect or combine information provided by you with information from third party sources, in accordance with applicable law. For example, (i) your preferences (e.g., based on your earlier purchases or engagement with our products and services) or (ii) the size, industry, and other information about the company you work for (where you have provided company name) will be obtained from sources including, professional networking sites and information service providers. We may also infer, generate, or collect and receive information from third parties, including partners, data brokers, service providers, aggregators, and from publicly accessible sources, for purposes that include to detect, prevent, or otherwise address fraudulent, deceptive or illegal activity, misuse of our Services and Software, security or technical issues, as well as to protect against harm to the rights, property or safety of Adobe and our employees, our users, children, or the public.
+Adobe Services and Software
+We collect information you provide to us (e.g., when you access and use our Services and Software) or permit us to collect (e.g., as part of a third-party integration). We also collect or generate information about how you access and use our Services and Software, including when you use a desktop or mobile app feature that takes you online (such as a photo syncing feature). Depending on the Services and Software you access and use, this information may be associated with your device or browser or it may be associated with your Adobe account or content. It includes:
+Analytics or other electronic network activity, such as:
+IP address;
+Browser and device information, including browser and device type, settings, unique identifiers, version, language settings, and configuration;
+Webpage that led you to an Adobe website;
+Search terms entered into a search engine which led you to an Adobe website;
+Use and navigation of Services and Software, including how you interact with Adobe websites (collected through cookies and similar technologies, or by Adobe servers when you are logged into the app or website);
+Analysis of your use and navigation of the Services and Software;
+Analysis of your content subject to your opt-out and consent rights.
+Professional, Education or other demographic information, such as:
+Profile information (e.g., account profile, public profile, Behance profile).
+Commercial and transaction information, such as:
+Content that includes personal information which is sent or received using an online feature of Adobe Services and Software, or which is stored on Adobe servers, such as documents, photos, videos, activity logs, direct feedback from you, metadata about your content, user generated requests such as search terms, prompts (e.g., text, images, videos, audio, etc.), inquiries, feedback, and other information you may disclose when you access or use our Services and Software as well as any information the Services and Software returns in response to such requests.
+Sensitive personal information, such as:
+Precise geolocation (e.g., when you add location data about where a picture was taken using your camera or phone's GPS feature);
+Information about your specific accessibility requirements or preferences, such as mobility, visual, auditory, dietary restrictions, or other accommodations (e.g., when you visit our offices);
+Biometric identifiers or information defined under United States laws or other applicable laws (e.g., faceprints and voiceprints, etc.);
+Where required by law, we will seek any required permissions from you prior to any such collection. See the “Adobe acting on your behalf” and “How we analyze your content to deliver features requested by you” sections below for more information.
+The following links provide further information on:
+Adobe product improvement program;
+Usage Data FAQ: Creative Cloud and Document Cloud Apps
+Adobe Genuine Software
+Your privacy choices regarding how we use this information;
+Adobe products and services licensed by educational institutions;
+How Adobe uses cookies and similar technologies; and
+How Adobe analyzes your content using techniques such as machine learning in order to improve our Services and Software, and how to opt out of this.
+Adobe Software activation and automatic updates
+Your device (manufacturer, model, IP address);
+The Adobe Software (version, date of activation, successful and unsuccessful updates);
+Your product serial number (e.g., where this is required before you can start using your product).
+You can learn more about app activation here.
+Adobe emails
+Emails we send you may include a technology (called a web beacon) that collects Analytics or other electronic network activity, such as whether you have received or opened the email, or clicked a link in the email. If you do not want us to collect this information, you can opt out of receiving Adobe marketing emails.
+Adobe social networking pages and social sign-on services
+You can sign into some Adobe Services and Software using a social networking account, such as a Facebook account. Where you give appropriate permissions, we will receive contact and identifier information about you from your social networking account, such as name, country, and basic demographic information.
+Adobe has its own pages on many social networking sites (for example, the Adobe® Photoshop® team’s Facebook page). We will collect information which you have made publicly available on your social networking account, such as name and interests in our products and services, when you interact with our social networking pages. The social networking sites may provide statistics and insights to Adobe which help us understand the types of actions that people take on our pages. Where applicable, Adobe and the social media site(s) have entered into an arrangement which determines our respective responsibilities.
+You can learn more about Adobe’s practices with respect to social networking pages and account sign-on services here.
+Adobe acting on your behalf
+In certain instances, Adobe is acting only on your behalf for personal information collected and processed by our services (for example, for the address book contacts shared by users when entering recipient information). In such cases, Adobe is acting only on your instructions in order to facilitate the Service requested by you, and you will be responsible for the information shared. In these instances, we will inform you through in-app notifications or other in-time communications. If you submit any information relating to other people to us or to our service providers in connection with your use of Adobe apps or websites, you represent that you have the authority to do so and to permit us to use the information in accordance with this policy.
+How we process your content to deliver features requested by you
+Adobe offers certain features that let you edit and organize your photographs, videos, and other types of content using characteristics like face and voice (e.g., you can group similar faces, places, and image characteristics within your collection), and such characteristics may be considered biometric identifiers or biometric information under certain US laws or other applicable privacy laws. When you choose to use these features, Adobe is acting only on your instructions in order to facilitate the service requested by you. These features are off by default and, should you choose to enable them, you can always disable these features. Where we process biometric identifiers or biometric information to deliver a feature requested by you, we delete this information once you turn off the feature, unless otherwise specified in the Software or Services.
+Visiting our Physical Offices
+When you visit an Adobe office, we will collect Identifiers and Contact information such as your name, company name, and email address; and Audio, electronic, visual, or similar information including facial images and voice information such as from CCTV video or voice recordings and photos.
+anchor
+info-collect
+How does Adobe use the information it collects about you, and what are the legal bases for these uses?
+Adobe uses the information we collect about you for the following purposes:
+To fulfill a contract, or take steps linked to a contract: this is relevant where you register to use an Adobe app or website (whether paid, or as a free trial). This includes:
+Providing you with the Adobe Services and Software for which you have registered, and any other services or products that you have requested;
+Administering product or platform skill/knowledge courses and other content, including testing and certifications (as applicable);
+Verifying your identity;
+Processing payments;
+Sending you necessary communications (for example, related to payments or expiration of your subscription); and
+Providing customer service or support.
+As required by Adobe to conduct our business and pursue our legitimate interests:
+Analyzing your content and its characteristics using automated techniques, in the following circumstances:
+Operational Use. To enable the normal running of the Services and Software, our Services and Software will access your content stored locally on your device (“Local Content”) and content that you have uploaded to our servers or create using our cloud-based Services (“Cloud Content”).
+Content Analytics with Cloud Content. Subject to your opt-out rights, including those described here, we may perform analytics with Cloud Content to help us understand how our users are using our Services and Software to allow us to improve your Services and Software experience, provide recommendations to you, and customize your experience. Insights from Content Analytics may be used to inform our marketing to you, subject to your opt-out rights regarding our marketing.
+Analyzing your cloud content and its characteristics using automated techniques or with human review, in the following circumstances:
+Illegal and Abusive Cloud Content. Cloud Content may be automatically scanned to ensure we are not hosting illegal or abusive content, like Child Sexual Abuse Material. Human review may occur when your Cloud Content is flagged or reported as illegal or abusive.
+Public and Shared Cloud Content. All public and shared Cloud Content is subject to review for intellectual property issues and safety issues (for example, violence and nudity). If you choose to share your Cloud Content with others using our Software and Services, we may automatically review this shared Cloud Content to flag abusive behavior (such as spam or phishing). When you make your Cloud Content publicly available, additional human review may occur.
+Providing you with the Adobe Services and Software for which you have registered and any other products and services you have requested;
+Analyzing your use and measuring effectiveness of our Services and Software to better understand how they are being used so we can improve them and engage and retain users;
+Sending you information about Adobe products and services, special offers and similar information, and sharing your information with third parties for their own marketing purposes, where your consent is not required;
+Analyzing your use and navigation of our Services and Software, your profile information, your interaction with our communications (excluding your content), to:
+Detect and prevent fraudulent, deceptive, or, illegal activity, or misuse of our Services and Software;
+Improve our Services and Software, and the user experience, subject to your opt-out and consent rights, including those described here;
+Tailor and customize the Services and Software through marketing communications (learn more);
+Diagnosing problems in our Services and Software;
+Conducting surveys and market research about our customers, their interests, the effectiveness of our marketing campaigns, and customer satisfaction (unless we need consent to undertake such surveys, in which case we will only do this with your permission);
+Investigating and responding to any comments or complaints that you may send us;
+Checking the validity of the sort code, account number, and card number you submit if you use a credit or debit card for payment, in order to prevent payment fraud or other illegal or deceptive payment practices (we use third parties for this – see “Does Adobe disclose my personal information to others?” below);
+Sharing account information registered under a business email address with employers for account migration purposes;
+Combining with other data we may have about how you interacted with our products and services when logged out or logged in, in order to provide a more seamless experience, show you the most relevant content and services, and for marketing purposes, with your consent where required;
+If we merge with or are acquired by another company, sell an Adobe website, app, or business unit, or if all or a substantial portion of our assets are acquired by another company, your information will likely be disclosed to the prospective purchaser, our advisers and any other prospective purchaser's advisers and will be one of the assets that is transferred to the new owner;
+In connection with legal claims, compliance, regulatory and investigative purposes as necessary (including disclosure of information in connection with government agency requests, legal process or litigation).
+Where we process your information based on legitimate interests, you can object to this processing in certain circumstances. In such cases, we will cease processing information unless we have compelling legitimate grounds to continue processing or where it is needed for legal reasons.
+If legitimate interest is not an available legal basis in a particular jurisdiction, we will engage in the processing activities described above on a legal basis that is available in that particular jurisdiction.
+Where required, when you give Adobe your consent or otherwise consistent with your choices:
+Sending you information about Adobe products and services, special offers and similar information, and sharing your information with third parties for their own marketing purposes;
+Placing cookies and using similar technologies in our Services and Software and in email communications, in accordance with our Cookies Policy and the information provided to you when those technologies are used;
+Accessing information stored on your device for the following operational uses:
+Information relating to your use of, and engagement with, Services and Software related to crash reports in order to fix the underlying problem causing the crash;
+Information which you allow us to receive through device-based settings (e.g., photos, location and camera) in order to provide certain functionality within our Services and Software;
+Analyzing your use and navigation of the Services and Software or your content and its characteristics using automated techniques or human review in order to:
+Detect and prevent fraudulent, deceptive, or illegal activity or misuse of the Services and Software;
+Improve our services and the user experience, such as through the Adobe Product Improvement Program as described here;
+Respond to your request (e.g., customer service).
+Allowing you to participate in sweepstakes, contests, and similar promotions and to administer these activities.
+On other occasions where we ask you for consent, we will use the information for the purposes which we explain at that time. Where we rely on consent to process information, you can withdraw your consent to such activities at any time.
+For legal reasons:
+Responding to requests by government or law enforcement authorities conducting an investigation.
+Using or disclosing information as reasonably necessary to detect, prevent, or otherwise address fraud, security, potential deceptive or illegal activities, misuse of Services and Software, or technical issues and software piracy (e.g., to confirm that software is genuine and properly licensed), helping to protect you as well as Adobe.
+Where this processing and these disclosures are not strictly required by law, Adobe may rely on its legitimate interests, where available, and those of third parties described above.
+anchor
+info-use
+Does Adobe disclose my personal information to others?
+Disclosing to other Data Controllers
+We will disclose your personal information within the Adobe family of companies for the purposes identified above (see a list of Adobe entities and our acquired companies).
+We will also disclose your personal information with other third-party data controllers with your consent (where necessary) or to provide any product or service you have requested (e.g., third-party integrations). The types of third parties your information may be disclosed to include: our resellers and other sales and advertising partners, retailers, advertisers, ad agencies, advertising networks and platforms, information service providers, fraud monitoring and prevention providers, and publishers. In some cases, in order to show you more relevant ads, we disclose with social media platforms and other advertising partners, information about actions you take on our websites and apps, such as which pages you visit and which ads you saw. These parties may be joint controllers for this processing. More information is available here.
+Third-party data controllers may also use Adobe products and services to collect and process your personal information. If you are using an email address that is associated with a business domain (e.g., yourname@businessname.com) to access Adobe's Services and Software, or if you were invited to use the Services and Software by a business, we may provide your personal information to that business.
+Disclosing for Fraud Prevention, Safety and Security Purposes
+We will disclose personal information to companies that help us run our business to detect, prevent, or otherwise address fraud, deception, illegal activity, misuse of Adobe Services and Software, and security or technical issues.
+Additionally, we will disclose personal information to companies, organizations, government authorities, or individuals outside of Adobe if we have a good-faith belief that access, use, preservation or disclosure of the information is reasonably necessary to detect, prevent, or protect against such fraudulent, deceptive, or illegal activity, misuse of our Services and Software, or security or technical issues, or where it is reasonably necessary to protect from harm the rights, property or safety of Adobe and our employees, our users, children, or the public as required or permitted by law.
+Disclosing to Data Processors
+We will also disclose your personal information to companies that help us run our business by processing personal information on behalf of Adobe for the purposes identified above. Such companies (including those that may record or store communications) include providers of customer support services, chatbots, session replay partners who provide services which recreate a web or app session showing meaningful insight into a visitor’s experience, providers of analytics technologies that record and analyze your interaction with our websites to help us improve your experience, providers of artificial intelligence technologies that record and analyze your content or communications, payment processing services, fraud monitoring and prevention, detecting and preventing deceptive or illegal activity or misuse of our Services and Software, email, social media, and other marketing platforms and service providers, and hosting services. We require these companies to protect your personal information consistent with this Privacy Policy.
+Other Information Disclosure
+Adobe may also disclose your personal information:
+When you agree to the disclosure;
+When we have a good faith belief that we are required to provide information in response to a subpoena, court order, or other applicable law or legal process (learn more), or to respond to an emergency involving the danger of death or serious bodily harm;
+If we merge with or are acquired by another company, sell an Adobe website, app, or business unit, or if all or a substantial portion of our assets are acquired by another company, your information will likely be disclosed to the prospective purchaser, our advisers and any prospective purchaser's advisers and will be one of the assets that is transferred to the new owner.
+anchor
+info-share
+Is my personal information displayed anywhere on Adobe’s websites or applications?
+There are several places within Adobe’s Services and Software that allow you to post comments, upload pictures, participate in message boards or chats, engage with blogs, share technical information, or submit other content for others to see. Sometimes you can limit who can see what you share, but there are some places where what you share can be seen by the general public or other users of the service. Such information can appear in search engine results or through other publicly available platforms and can be “crawled” or searched by third parties. For example, when users post content on message boards, online chats, blogs, and Community Forums, the information posted by the user will become public. Some online content may remain accessible publicly even after Adobe fulfils a request to delete the poster’s personal information.
+Please be careful when you share your personal information. Do not share anything you wouldn’t want publicly known unless you are sure you are posting it within an app or website that allows you to control who sees what you post. Please note that when you post messages on certain user forums on our websites and app, your email address or name and/or profile photo may be included and displayed with your message. You can find more information about managing your public profile here. To remove content you have shared on our Services and Software, please use the same feature you used to share the content. If another user invites you to participate in shared viewing, editing, or commenting of content, you may be able to delete your contributions, but usually the user who invited you has full control. If you have questions or concerns about this, please contact us.
+anchor
+websites-applications
+Is my personal information secure?
+We work hard to protect your personal information. We employ administrative, technical, and physical security controls where appropriate, such as encryption, 2-step verification, and appropriate contractual confidentiality obligations for employees and contractors.
+anchor
+info-secure
+Where does Adobe store my personal information?
+Your personal information and files are stored on Adobe’s servers and the servers of companies we engage to provide services to us.
+anchor
+info-store
+Does Adobe transfer my personal information across national borders?
+The main locations where we process your personal information are the US and India, but we also transfer personal information to all other countries in which Adobe or its affiliates, providers, and partners operate. We carry out these transfers in compliance with applicable laws – for example, by putting data transfer agreements in place to help protect your personal information.
+Adobe complies with the EU-U.S., UK Extension to the EU-U.S., and Swiss-U.S. Data Privacy Framework. To learn more, see our Cross Border Data Transfers page, or visit the U.S. Department of Commerce’s Data Privacy Framework website.
+As set out above Adobe uses a limited number of third-party service providers to assist us in providing our services to our users and business customers. These third parties may access, process, or store personal data in the course of providing their services. Adobe maintains contracts with these third parties restricting their access, use and disclosure of personal data in compliance with our Data Privacy Framework obligations, including the onward transfer provisions, and Adobe remains liable if they fail to meet those obligations and Adobe is responsible for the event giving rise to the damage).
+The information above applies to Adobe users who are consumers. More information is available for our business customers that want to learn more about Cross-border data transfers.
+anchor
+info-transfer
+What rights do I have regarding my personal information and how can I exercise these rights?
+When provided for by applicable law, you have the right to ask us for a copy of your personal information; to correct, delete or restrict (stop any active) processing of your personal information; and to obtain the personal information you provide to us for a contract or with your consent in a structured, machine readable format, and to ask us to share (port) this information to another controller. You may be entitled to additional rights based on applicable data privacy laws in your jurisdiction.
+In addition, you can object to the processing of your personal information in some c</t>
+  </si>
+  <si>
+    <t>Privacy Policy | Snapchat Privacy
+PrivacyPrivacyPrivacy Center
+Privacy Principles
+Privacy by Product
+Privacy Policy
+Teens on Snapchat
+Snap and Ads
+Privacy Through Security
+Privacy Policy
+Effective: April 7, 2025
+Welcome to Snap Inc.’s Privacy Policy. This Policy explains how we collect and use your data and how you can control your information. Looking for a quick summary on our privacy practices? Check out this page or this video. If you’re looking for specific product privacy information, for example, how we process your Chats and Snaps, take a look at our Privacy by Product page. In addition to these documents, we also show in-app notices that provide you more information about our products and services. And if you’re a Spectacles user you can learn more on how we collect and use your data in the Spectacles Supplemental Privacy Policy.
+Transparency is one of our core values at Snap. We believe there shouldn’t be any surprises about the data we collect and how we use it — that’s why we’re upfront with how we process it. For example, we process your information to provide you a more personalized experience, including to show you content and information that is most relevant to your experience, as well as more relevant advertisements. Understanding your interests and preferences help us provide a better product experience.
+Furthermore, we believe a personalized experience should not come at the expense of your privacy. Just like in real life, there are some moments you want to share privately with your close friends, and others that you want to share publicly. That’s why from day one our philosophy has been to delete content by default and to give Snapchatters control by providing the tools that allow them to decide what happens with their content, like who to share it with or when to save it.
+This Policy covers our Snapchat app as well as our other products, services, and features, such as Bitmoji, Spectacles, and our advertising and commerce initiatives. When you read "Services" in this Policy, we’re talking about all of them. Also, if you see us refer to our "Terms," we mean the Terms of Service that you agree to when you sign up for our Services. Finally, if you see the term "Snapchatter" we are often using that as shorthand for any user of our Services.
+Let’s get started with the controls you have over your information:
+Control Over Your Information
+Control over your information and settings is a core part of Snapchat experience. You can access, update, and delete your information, decide who can contact you, and download your data from within the Snapchat app. Below, we give you more details on the types of settings that are available, link out to our data download tool, and provide instructions on how to delete data or your account.
+We want you to be in control of your information, so we provide you with a range of tools, including:
+Access and update your information. You can access and edit most of your basic account information right in our Services. Just navigate to your settings and you will see the options available to you.
+Delete your information. If you want to delete your account, learn how here. You can also delete some information within our Services, like content you’ve saved to Memories, content you’ve shared with My AI, Spotlight submissions, and more.
+Control who can see your content. We’ve built a number of tools that let you choose who you share your content with. In some cases you may want to share content with your friends, and in other instances you may want to share it with the public. To learn more, go here.
+Control who can contact you. Snapchat is intended for close friends and family, that’s why we’ve built controls that help you decide who can contact you. If you receive unwanted communications, you can always block and report that person. Go here to learn more.
+Change your permissions. In most cases, you can change your permissions at any time. For example,  by default you are findable to others through your phone number and/or email address that you provided. If you no longer want to be findable, you can always change your settings. Or if you provided access to your phone or third party platform contacts to make friending easier, you can change that later on in your app settings. Of course, if you do that, certain features and Services, like finding friends in your contact book, won’t work.
+Opt out of promotional messages. You have the option to opt out or unsubscribe from promotional emails and messages sent by SMS or other messaging platforms. To do so, just follow the instructions in the message like an unsubscribe link or similar functionality.
+Download your data. You can make a request in our Download My Data tool to export a copy of your Snapchat information.
+Object to processing. Depending on where you live and the particular data we are processing, you may have the right to object to our processing of that information. This gets a bit technical, so we’ve explained it in more detail here.
+Set advertising preferences. We try to show you ads that we think will be relevant to your interests, but if you’d like to have a less personalized experience, you can change your advertising settings in the Snapchat app. Learn more here.
+Tracking. If you use an iPhone with iOS 14.5 or above, some specific requirements apply, which we’ve specified here.
+Information We Collect
+This section provides you with details on what information we collect: what you provide to us, what we collect when you use Snapchat, and information we receive from other companies or apps you’ve connected to your Snapchat account. Sometimes, we may also collect additional information, with your permission.
+When you use our Services, such as Snapchat, we collect information you provide to us, generate information when you use our Services, and in some cases receive data from others. Let’s break these down in more detail.
+Information You Provide
+Many of our Services require you to set up an account. To do this, we ask you to provide us with account details (information about you, like your name, username, email address, birthday, and phone number). When you set up your profile, you’ll also provide us with profile details (like your Bitmoji and profile picture). If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history).
+Of course, you’ll also provide us with information you send through or save within our Services, including content and information about that content, and content you share and generate with our AI Features (content, or “Inputs,” including text, images, video, audio, precise location, and engagement, used to generate content and responses, or “Outputs”). We consider some of this information to be private content and communications (like Snaps and Chats with friends, voice and video calls, and content that is saved in My Eyes Only). Or content you share with a particular audience like private &amp; friend stories (My Story set to Friends, Private Stories). On the other end of the spectrum, some of the information you send through or save within our Services may be public content that is accessible to everyone (such as Public Story content, including My Story set to Everyone, Shared Stories, and Community Stories, Spotlight or Snap Map submissions, and Public Profile information). Keep in mind that Snapchatters who view your Snaps, Chats, and any other content, can always screenshot that content, save it, or copy it outside the Snapchat app. So please don’t send messages or share content that you wouldn’t want someone to save or share.
+Lastly, when you contact Support (content and communications shared with Support) or our Safety team, or communicate with us in any other way, including through our research efforts (like responses to surveys, consumer panels, or other research questions) we’ll collect whatever information you provide or that we need to resolve your question.
+Information We Generate When You Use Our Services
+When you use our Services, we collect information about which of those Services you’ve used and how you’ve used them. This helps us better understand the way our community uses our Services so that we can make improvements.
+This includes usage information (information about how you interact with our Services — for example, which Lenses you view and apply, your premium subscriptions, Stories you watch, and how often you interact with other Snapchatters) and content information (information about content you create or provide, your engagement with the camera and creative tools, your interactions with My AI, and metadata — for example, information about the content itself like the date and time it was posted and who viewed it). Content information includes information based on the content of the image, video, or audio — so if you post a Spotlight of a basketball game, we may use that information to show you more content on Spotlight about basketball.
+This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies).
+If you’ve explicitly granted device-level permissions, device information may also include information about your device phonebook (contacts and related information), images and other information from your device’s camera, photos, and microphone (like the ability to take photos, videos, view stored photos and videos, and access the microphone to record audio while recording video), and location information (precise location through methods like GPS signals).
+Data We Receive From Others
+The last category of data we collect is information about you that we may receive from others, such as other users, our affiliates, and third parties. This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines).
+Other Information, With Your Permission
+Additionally, there may be instances when you interact with our Services that we will ask your permission to collect additional information. For example, before accessing your device’s camera roll or your device or third party contact book.
+How We Use Information
+This section explains how we use the information we collect. Among other things, we use the information we collect to provide you with personalized products and Services that we work hard to build and improve. Below, we walk through each purpose for which we use information in detail. If you’d like to see a mapping of the data we collect with the purposes for which we collect it, we have a table here.
+Keep Things Up &amp; Running (i.e., operate, deliver, and maintain our Services)
+We use the information we collect in order to operate, deliver, and maintain our Services. For example, by delivering a Snap you want to send to a friend or, if you share your location on Snap Map, to show you suggestions like places you might like in your neighborhood, content others have posted to the Map, or your friends if they’re sharing their location with you. We also use some of your information to help keep our products up to date, for example to make sure that our Services work with the latest operating systems and devices.
+Personalize Your Experience &amp; Give Context
+We offer personalized Services to Snapchatters. One of the ways we do this is by showing you content that is relevant to you or we think you may enjoy based on the information you share with us. To do so, we use information about you across different areas of the Services in order to add context to your Snapchat experience. For example, we automatically tag content with labels based on the content, your location, or the time of day. So if there's a dog in the photo, it may be searchable in Memories by the term “dog,” show up on the Map at the location where you created the Memory, and inform us that you’re into dogs so we can surface you fun dog videos and dog food ads in other parts of our Services, such as Spotlight.
+Personalization can also help with suggesting friends or recommending a new friend to send a Snap to based on who you Snap with the most. We may show recommended places on the Snap Map, generate stickers, or even generate Snaps and other content using AI, infer your interests based on your content or activity, or customize the content we show you, including ads. For example, if you watch barista content on Spotlight, talk to My AI about your favorite espresso machine, or save a lot of coffee-related Snaps in your Memories, we may highlight coffee shops on the Snap Map when you visit a new city or show you content about coffee that you may find interesting or relevant. Or, if you interact with a lot of music venues we may use that to show you ads for upcoming shows in town. Personalization also includes tailoring your experience based on who you interact with most and what your friends are doing, including showing you content your friends create, like, or enjoy on Spotlight or Place recommendations that are popular with your friends.
+Our goal is to continuously provide you with more relevant and interesting content.
+For example, if you watch a lot of sports content, but skip content with hair and makeup tips, our recommendation algorithms will prioritize sports, but not those makeup tips. You can learn more about how we understand Snapchatter preferences and rank and moderate content here.
+We believe it is critical to also balance the benefits of personalization with our Snapchatters’ expectations of privacy. For example, we may automatically tag the Snaps you save to Memories based on the content within it (e.g., the Snap contained a dog), and then use that tag to personalize your experience, make recommendations, or show you ads (such as showing you Spotlight Snaps containing dogs). We do not use the private content and communications you send to your friends to personalize your experience, make recommendations, or show you ads.
+Provide Relevant Ads
+Another way we provide a personalized Service is through the ads we show. We use your interests and preferences from the information we’ve collected to personalize, target, and measure ads. We think ads are best when they’re relevant. That’s why we try to select the right ads and show them to you at the right time. For example, if you’ve interacted with ads for video games, we will infer that you like video games, and show you similar ads, but those won’t be the only ads you see. Similar to our content strategy, we try to ensure you receive a variety of ads. We also use your information to avoid showing you ads you probably won’t be interested in. For example, if a ticketing site tells us you’ve previously bought tickets for a movie — we can stop showing you ads for it. You can learn about the different types of advertising and your choices about which ads you receive here.
+You can learn more about how we collect, use, and share your information for advertising purposes here.
+A note about information collected by cookies and other technologies: we may use these technologies to collect information when you interact with Services we offer through one of our partners. For example, we may use information collected on an advertiser’s website to show you more relevant ads. Most web browsers are set to accept cookies by default. If you prefer, you can usually remove or reject browser cookies through the settings on your browser or device. Keep in mind, though, that removing or rejecting cookies could affect the availability and functionality of our Services. To learn more about how we and our partners use cookies on our Services and your choices, please check out our Cookie Policy.
+Develop &amp; Improve Features, Algorithms &amp; Machine Learning Models
+Our teams are constantly coming up with new ideas for features and ways to improve our Services. In order to do this, we also develop and improve the algorithms and machine learning models (an expression of an algorithm that combs through significant amounts of data to find patterns or make predictions) that make our features and Services work, including through generative AI features (artificial intelligence capable of generating text, images, or other media, using generative models. Generative AI models learn the patterns and structure of their input training data and then generate new data that has similar characteristics). We use algorithms and machine learning models for personalization, advertising, safety and security, fairness and inclusivity, augmented reality, and to prevent abuse or other Terms of Service violations. For example, our algorithms and machine learning models take into account the conversations Snapchatters are having with My AI to improve the responses from My AI.
+Your information can help us decide what kind of improvements we should make, but we are always focused on privacy — and we don’t want to use more of your personal information than necessary to develop our features and models.
+Analytics
+In order to understand what to build or how to improve our Services, we need to understand trends and demand for our features. For example, we monitor metadata and trends about Group Chat use to help decide whether we should change parts of the feature, like the maximum size of a Group. Studying data from Snapchatters can help us see trends in the ways that people use the Services. This helps inspire us to improve Snapchat on a larger scale. We perform analytics in order to identify, monitor, and analyze trends and usage. Based on this information, we will, among other things, create information about our users to help us understand demand.
+Research
+We conduct research to better understand general consumer interests, trends, and how our Services are used by you and others in our community. This information, along with analytics (as we described above), helps us understand more about our community and about how our Services fit into the lives of those in our community. We also engage in research and development to develop new techniques and technologies (e.g., new machine learning models or hardware, such as Spectacles). The results of our research are sometimes used in features on Snapchat, and we sometimes publish papers about things like overall behaviors and consumer trends (which will only have aggregated data across our user base, and not contain any private information about you specifically).
+Enhance the Safety &amp; Security of Our Services
+We use your information to enhance the safety and security of our Services, verify Snapchatter identity, and prevent fraud or other unauthorized or illegal activity. For example, we provide two-factor authentication to help protect your account and can send you email or text messages if we notice any suspicious activity. We also scan URLs sent on Snapchat to see if that webpage is potentially harmful, and can give you a warning about it.
+Contacting You
+Sometimes we’ll get in touch with you to promote new or existing features. This includes sending Snapchatters communications through Snapchat, email, SMS, or other messaging platforms, where permitted. For example, we may use the Snapchat app, email, SMS, or other messaging platforms to share information about our Services and promotional offers that we think may interest you.
+Other times, we need to communicate with you to provide information, alerts, or to send messages our users ask us to deliver at their request. This may include sending communications through Snapchat, email, SMS, or other messaging platforms, where permitted, to deliver account status updates, security alerts, and Chat or friending reminders; it may also include fulfilling our user’s request to send invites or Snapchat content to non-Snapchatters.
+Support
+When you ask for help, we want to get you support as quickly as possible. In order to provide you, the Snapchatter community, and our business partners with the help needed to resolve issues with our Services, we often need to use the information we have collected to respond.
+Enforce Our Terms &amp; Policies
+We use the data we collect to enforce our Terms and the law. This includes enforcing, investigating, and reporting conduct that violates our Terms, policies, or the law, responding to requests from law enforcement, and complying with legal requirements. For example, when unlawful content is posted on our Services, we may need to enforce our Terms and other policies. In some cases, we may also use or share your information to cooperate with law enforcement requests, escalate safety issues to law enforcement, industry partners, or others, or comply with our legal obligations. Check out our Transparency Report to learn more.
+Other Purposes, With Your Permission
+Additionally, there may be instances when you interact with our Services that we will ask for your permission to use your information in a new, different, or otherwise specific way.
+How We Share Information
+This section explains who we share information with, what that information may include, and the reasons for sharing that information, including when we need to transfer it outside of the country it was collected from.
+Recipients &amp; Reasons for Sharing
+Snapchat. To provide our Services to you and our community, we may share your information with your friends on Snapchat or other Snapchatters. For example, the content you post to Stories, or your status as a premium subscriber, can be viewed by your Friends if you allow them. See the Control Over Your Information section and your Settings for the controls you have over who sees what and when.
+Family Center Participants. When you have enabled Family Center, we share information about the connected teen account to the parent or guardian to provide insight about how the account is used, for example, who your Friends are on Snapchat or which friends you may be sharing your location with. We do not share message content. Learn more.
+Public. Most of the features on Snapchat are private and for Friends only, but we also offer public features that allow you to opt in to showcase your best Snaps to the world, such as Spotlight, Snap Map, or your Public Profile. When you do this, those Snaps may also be discoverable outside of Snapchat, for example on the web. Some information, like your username and Bitmoji, are visible to the public. Learn more.
+Third-Party Apps. Sometimes we provide features that allow you to connect with third-party apps. If you decide to connect your Snapchat account with a third-party app, we will share any additional information you direct us to.
+Service Providers. We share your information with our service providers, who process that information on our behalf. For example, we rely on such Service Providers to facilitate payments, measure and optimize the performance of ads, or protect the services. We do not share private communications with them. We maintain a list of categories of service providers here.
+Business and Integrated Partners. We share your information with business and integrated partners in order to provide the Services. For example, you can use OpenTable within Snapchat to reserve a table. This does not include private communications. We maintain a list of these partners here.
+Anti-Fraud Partners. We share your information, such as device and usage information, with industry partners working to prevent fraud.
+Legal, Safety, and Security Partners. We share your information as necessary for the following legal, safety, and security reasons:
+comply with any valid legal process, governmental request, or applicable law, rule, or regulation.
+investigate, remedy, or enforce potential Terms of Service and Community Guidelines violations.
+protect the rights, property, or safety of us, our users, or others.
+detect and resolve any fraud or security concerns.
+Affiliates. Snap Inc. consists of different subsidiaries owned by us. We may share your information within those internal subsidiaries as needed to carry out our Services.
+For the purposes of a Merger or Acquisition. If we were to sell or negotiate to sell our business to a buyer or possible buyer, we may transfer your information to a successor or affiliate as part of that transaction.
+Integrated Partners
+Our Services may contain content and integrations offered by our integrated partners. Examples include integrations in Lenses, Camera editing tools, to provide Scan results, and third-party developer integrations. Through these integrations, you may be providing information to the integrated partner as well as to Snap. We are not responsible for how those partners collect or use your information. As always, we encourage you to review the privacy policies of every third-party service that you visit or use, including those third parties you interact with through our Services. You can learn more about our integrations in Snapchat here.
+On iOS we use Apple’s TrueDepth camera to improve the quality of Lenses. Note, however, that this information is used in real time — we don’t store this information on our servers or share it with third parties.
+International Data Transfers
+Our Services connect you with your friends around the world. To make that possible, we may collect your personal information from, transfer it to, and store and process it in the United States or other countries outside of where you live. Whenever we share information outside of where you live, we ensure safeguards are in place to protect the data as required by law where you live. If you want to learn more about this, see the Region Specific Information section for more details.
+How Long We Keep Your Information
+In this section we provide you with information on how long we keep your information, why we keep your information, and also highlight how we may need to keep your information to comply with laws, courts, and other obligations.
+As a general rule, we keep information as long as you tell us to, and otherwise as long as we need it to provide our Services, or as required by law. For example, if you store something in Memories, we will keep it as long as you need it, but when you Chat with a friend, our systems are designed to delete Chats you send within 24 hours after your friend reads it (unless you’ve changed your default settings or decide to save it). Whether we retain your data depends on the specific feature, your settings, and how you’re using the Services. Here are some more factors we consider when we decide how long to keep your information:
+If we need the information to operate or provide our Services. For example, we store your basic account details — like your name, phone number, and email address — to maintain your account.
+To do the things you expect from our Services and as we’ve described within this Privacy Policy. For example, we maintain your list of friends until you ask us to delete them since friends are key to expressing yourself. Similarly, we keep your shared list of contacts until you ask us to remove them in our app settings (note: updating your device permissions may not remove the contacts you’ve previously shared with Snapchat). Learn more. Conversely, Snaps and Chats sent in Snapchat will be deleted by default from our servers within 24 hours after we detect they’ve been opened by all recipients or have expired, unless you’ve changed your default settings or decide to save something, in which case we will honor your choices.
+The information itself. For example, we store location information for different lengths of time based on how precise it is and which Services you use. If location information is associated with a Snap — like those saved to Memories or posted to Snap Map or Spotlight — we’ll retain that location as long as we store the Snap. Pro tip: You can see the location data we retain about you by downloading your data.
+How long we need to retain the information to comply with certain legal obligations.
+If we need it for other legitimate purposes, such as to prevent harm, investigate possible violations of our Terms of Service or other policies, investigate reports of abuse, or protect ourselves or others.
+Take a look at our Privacy by Product page and support page for details on the specific retention periods for products.
+Although our systems are designed to delete some of your information automatically, we cannot promise that deletion will take place by a specific time.
+In some cases we need to comply with legal requirements to store your data which stops us from deleting your information. For example, if we receive a notice from a court asking us to keep a copy of your content. Other reasons we may keep a copy of your data are if we get reports of abuse or other Terms or policy violations, or if your account, content created by you, or content created with other Snapchatters is flagged by others or our systems for abuse or other Terms or policy violations. Finally, we may also keep certain information in backup for a limited period of time or as required by law.
+For the latest information about how long we store different types of content, check out our Support Site.
+Region Specific Information
+Depending on where you live, you may have additional rights, this section provides more details on region specific information.
+We do our best to keep our policies as simple as possible, but depending on where you live, you have some additional rights or there may be specific information that you should be aware of. Please take a look at the list below to see if any apply to you!
+Australia
+Brazil
+Canada
+Europe
+Mexico
+South Korea
+Turkey
+United States
+Note: The U.S. State Privacy Notice applies only if you are a resident of certain U.S. states that have implemented state-level privacy laws.
+Some jurisdictions require that we state our legal basis for processing data for particular purposes. You can find that information here.
+Our Audience
+Our Services are directed to individuals 13 years and older.
+Our Services are not directed to children under the age of 13, and you must confirm that you are 13 years or older in order to create an account and use our Services. If we have actual knowledge that you are under the age of 13 (or the minimum age at which a person may use the Services in your state, province, or country without parental consent, if greater), we will stop providing Services to you and delete your account and data.
+In addition, we may also limit how we collect, use, and store some of the information of Snapchatters under 18. In some cases, this means we will be unable to provide certain functionality to people under the age of 18.
+Updates to the Privacy Policy
+We may update our Privacy Policy from time to time, and will give you a heads up if we make any changes we think you should know about.
+We may change this Privacy Policy from time to time. But when we do, we’ll let you know one way or another. Sometimes, we’ll let you know by revising the date at the top of the Privacy Policy that’s available on our website and mobile application. Other times, we may provide you with additional notice (such as adding a st</t>
+  </si>
+  <si>
+    <t>Instapaper
+Privacy
+Terms
+Instapaper
+Create Account
+Sign In
+Help &amp; FAQ
+Apps
+How to Save
+Premium ↗
+Blog ↗
+API
+Press
+Publishers
+Privacy &amp; Terms
+Create Account
+Sign In
+Terms
+Our Commitment To Privacy
+Your privacy is important to us. To better protect your privacy we provide this notice explaining our online information practices and the choices you can make about the way your information is collected and used.
+The Information We Collect
+This notice applies to all information collected or submitted on the Instapaper website and the Instapaper applications and services for iPhone, iPad, Android, Kindle, and other devices and platforms, hereafter referred to as simply Instapaper.
+Instapaper occasionally needs to collect information for convenience, practicality, or technical requirements. This information includes:
+Your chosen username, which may be your email address or name. A username is technically required so you can log in from multiple computers and devices. We encourage you to use your email address to make "forgot password" functionality possible.
+Your chosen password, which is empty by default. A hash of your password is stored in the Instapaper database, and the plain-text password is only used for hash comparison to the stored value.
+The titles, URLs (addresses), and selected text of the pages you save to Instapaper, folder-specific bookmarklets, Instapaper applications, third-party applications using the Instapaper API, and any other means with which to add pages to Instapaper.
+The HTML contents of the pages you save to Instapaper when recognized as a known login-requiring site. This is technically required to generate the Text view and other indexing features for sites that require logins or accounts, such as some major newspaper publishers. When HTML is saved for a page, it is only used within your account and is not revealed via social or sharing features.
+Your Amazon Kindle email address, if you have enabled automatic delivery to your Kindle. This is technically required to send your content to your Kindle.
+Like most Web sites, Instapaper also collects and stores information automatically and through the use of electronic tools that may be transparent to our visitors. For example, we may log the name of your Internet Service Provider, your IP address, and information provided by and about your Internet browser. As we adopt additional technology, we may also gather similar information through other means.
+We may also use "cookie" technology. Among other things, we may use cookies or other tracking technology for the purposes of storing your username and password hash to spare you from having to re-enter that information each time you visit.
+The Way We Use Information
+We use the information you provide to operate Instapaper's features. We do not share this information with outside parties except to the extent necessary to accomplish Instapaper's functionality.
+We use return email addresses to answer the email we receive. Such addresses are not used for any other purpose and are not shared with outside parties.
+We use non-identifying and aggregate information to better design Instapaper, to suggest popular content to users, and to share with advertisers and publishers. For example:
+We may use aggregate information from Instapaper usage to help design new features or services for the product.
+We may tell an advertiser or publisher that X number of people visited a certain area on our website
+We may tell an advertiser or publisher that X number of people bookmarked Z stories from a particular site or topic.
+We may aggregate the most popular stories during limited time periods or from certain websites in order to suggest stories for Instapaper's Editor's Picks or for users who have also saved pages from those websites.
+When information is used in this or a similar manner, we do not disclose anything that could be used to identify the individuals on whom the information is based.
+We may disclose your information in response to subpoenas, court orders, or other legal process, or to establish or exercise our legal rights or to defend against legal claims.
+We may disclose your information when we believe it necessary or desirable in order to investigate, prevent, or take action regarding illegal activities, suspected fraud, situations involving potential threats to the physical safety of any person, violations of our policies, and/or to protect our rights and property.
+In the future, we may sell, buy, merge, or partner with other companies or businesses. In such transactions, user information may be among the transferred assets.
+Publicly Accessible Information
+Some information you share on Instapaper is considered public when you use our social and sharing functionality, including:
+Others can view your most recent Starred articles if they know your username.
+Others can view your Unread, Archive, Starred, or folder contents if you reveal or share their associated RSS-feed URLs.
+External Services
+External services beyond Instapaper's control are integrated with Instapaper where necessary, such as Mailgun for email sending, Crashlytics for crash reporting, ZenDesk for customer support, and Google Analytics for traffic measurement and tracking. Integrations with Google services like Analytics, YouTube, and YouTube API Services are bound to the Google Privacy Policy.
+Instapaper makes reasonable efforts to ensure that all integrated external services are trustworthy and reputable, but Instapaper cannot be held responsible for data collection and usage by such services.
+Our Commitment To Data Security
+To prevent unauthorized access, maintain data accuracy, and ensure the correct use of information, we have put in place appropriate physical, electronic, and managerial procedures to safeguard and secure the information we collect online.
+Please note: To ensure easy account creation, minimal customer errors, and reduced support inquiries, Instapaper accounts initially do not have passwords. If left without a password, anyone can access your account if they know or guess your username. To set or change your password, go to http://www.instapaper.com/user/password.
+Our Commitment To Children's Privacy
+Protecting the privacy of the very young is especially important. For that reason, we never collect or maintain information at our website from those we actually know are under 13, and no part of our website is structured to attract anyone under 13.
+How You Can Access Or Correct Your Information
+You can access all your personally identifiable information that we collect online and maintain by logging into your Instapaper account on the Instapaper website at http://www.instapaper.com/.
+You can correct factual errors in your personally identifiable information by changing or deleting the erroneous information, by deleting your entire Instapaper account at http://www.instapaper.com/user/delete, or by emailing support@instapaper.com.
+To protect your privacy and security, we will also take reasonable steps to verify your identity before granting access or making corrections.
+Deleting Information
+You can delete your entire Instapaper account at any time at http://www.instapaper.com/user/delete. If you delete your account, all account information and saved page data is deleted from the Instapaper service immediately.
+Due to the nature of backups and logs, deleted data may persist in backups and logs until they are deleted.
+Privacy Shield
+Instapaper complies with the EU-U.S. Privacy Shield Framework and the Swiss-U.S. Privacy Shield Framework as set forth by the U.S. Department of Commerce regarding the collection, use, and retention of personal information transferred from the European Union, United Kingdom, and Switzerland to the United States pursuant to the Privacy Shield. Instapaper has certified to the Department of Commerce that it adheres to the Privacy Shield Principles. If there is any conflict between the terms in this privacy policy and the Privacy Shield Principles, the Privacy Shield Principles shall govern. To learn more about the Privacy Shield program, and to view our certification, please visit https://www.privacyshield.gov.
+In compliance with the Privacy Shield Principles, Instapaper commits to resolve complaints about your privacy and our collection or use of your personal information pursuant to the Privacy Shield. EU, UK, and Swiss individuals with inquiries or complaints regarding our Privacy Shield policy should first contact Instapaper at support@instapaper.com.
+Within the scope of this privacy notice, if a privacy complaint or dispute cannot be resolved through Instapaper's internal processes, the Federal Trade Commission has jurisdiction over Instapaper's compliance with the Privacy Shield.
+The Privacy Shield Principles describe Instapaper's accountability for personal data that it subsequently transfers to a third-party agent. Under the Privacy Shield Principles, Instapaper shall remain liable if third party agents process the personal information in a manner inconsistent with the Privacy Shield Principles, unless Instapaper proves it is not responsible for the event giving rise to the damage. If we cannot, we have selected JAMS, an independent dispute resolution provider, to handle unresolved Privacy Shield complaints. If we are unable to resolve your concerns after a good faith effort to address them, you may contact JAMS and submit a Privacy Shield claim. JAMS is a US-based private alternate dispute resolution provider, and we have contracted with JAMS to provide an independent recourse mechanism for any of our users for privacy concerns at no cost to you. You may learn more about the JAMS service or file a claim with JAMS by visiting https://www.jamsadr.com/eu-us-privacy-shield. You do not need to appear in court; you may conduct this dispute resolution process via telephone or video conference.
+Note that Instapaper may be required to release the personal data of EU, UK, and Swiss individuals whose data is pursuant to the Privacy Shield in response to legal requests from public authorities, including to meet national security and law enforcement requirements.
+In certain circumstances, the Privacy Shield Framework provides the right to invoke binding arbitration to resolve complaints not resolved by other means, as described in Annex I to the Privacy Shield Principles.
+In certain circumstances, the Privacy Shield Framework provides the right to invoke binding arbitration to resolve complaints not resolved by other means, as described in Annex I to the Privacy Shield Principles.
+GDPR: Information for EEA Users
+What Rights Do I Have?
+Individuals located in the European Economic Area (EEA) have certain rights in respect of your personal information and Instapaper will provide these capabilities to all our worldwide users, including:
+The right of access to your personal data;
+The right to correct or rectify any inaccurate personal data;
+The right to restrict or oppose processing of personal data;
+The right to erase your personal data; and
+The right to personal data portability.
+Instapaper uses, processes, and stores personal data, including those listed in the "Information We Collect" section, as necessary to perform our contract with you, and based on our legitimate interests in order to provide the Services. We rely on your consent to process personal data to place cookies on your devices. In some cases, Instapaper may process personal data pursuant to legal obligation or to protect your vital interests or those of another person.
+How Can I Exercise my Rights?
+If you're a user based in the EEA, you can:
+Request a personal data report by submitting a request to support@instapaper.com. This report will include the personal data we have about you, provided to you in a structured, commonly used, and portable format. Please note that Instapaper may request additional information from you to verify your identity before we disclose any information.
+Have your personal data corrected or deleted. Some personal data can be updated by you through your Instapaper account settings, or by contacting us at support@instapaper.com. You can also remove your personal data from Instapaper by deleting your account at http://www.instapaper.com/user/delete.
+Complain to a regulator. If you're based in the EEA and think that we haven't complied with data protection laws, you have a right to lodge a complaint with your local supervisory authority.
+If you have other questions or do not have a Instapaper account, please contact us at support@instapaper.com.
+How To Contact Us
+Should you have other questions or concerns about these privacy policies, please email support@instapaper.com. At this time, we only have the ability to receive and send English-language communications.
+Changes To This Policy
+Instapaper reserves the right to change this policy at any time. Please check this page periodically for changes. Your continued use of Instapaper following the posting of changes to this policy will mean you accept those changes. We will notify you before we make material changes to this policy and give you an opportunity to review the revised policy before deciding if you would like to continue to use the Services. You can review previous versions of the policy at https://github.com/Instapaper/privacy.
+Effective Date: January 26th, 2019
+↑   Click &amp; drag up to your Bookmarks Bar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">['Meta Privacy Policy - How Meta collects and uses user data', 'Privacy Policy', 'Search', 'Privacy topics', 'More privacy resources', 'Privacy Policy', 'What is the Privacy Policy and what does it cover?', 'What information do we collect?', 'How do we use your information?', 'How is your information shared on Meta Products or with integrated partners?', 'How do we share information with third parties?', 'How do the Meta Companies work together?', 'How can you manage or delete your information and exercise your rights?', 'How long do we keep your information?', 'How do we transfer information?', 'How do we respond to legal requests, comply with applicable law and prevent harm?', 'How will you know the Policy has changed?', 'Privacy notice for United States residents', 'How to contact Meta with questions', 'Why and how we process your information', 'Other policies and articles', 'Settings', 'Privacy Policy', 'What is the Privacy Policy and what does it cover?', 'Effective June 16, 2025 | View printable version | See previous versions', 'Read the United States Regional Privacy Notice for more details about how we handle Personal Information and how to exercise your rights.', 'Highlights', 'We at Meta want you to understand what information we collect, and how we use and share it. That’s why we encourage you to read our Privacy Policy. This helps you use Meta Products in the way that’s right for you.', 'In the Privacy Policy, we explain how we collect, use, share, retain and transfer information. We also let you know your rights. Each section of this Policy includes helpful examples and simpler language to make our practices easier to understand. We’ve also added links to resources where you can learn more about the privacy topics that interest you.', "It's important to us that you know how to control your privacy, so we also show you where you can manage your information in the settings of the Meta Products you use. You can update these settings to shape your experience.", 'Read the full Policy below.', 'What Products does this Policy cover?', 'Learn more in Privacy Center about managing your privacy', 'What information do we collect?', 'Highlights', "The information we collect and process about you depends on how you use our Products. For example, we collect different information if you sell furniture on Marketplace than if you post a reel on Instagram. When you use our Products, we collect some information about you even if you don't have an account.", "Here's the information we collect:", 'Your activity and information you provide', 'Friends, followers and other connections', 'App, browser and device information', 'Information from partners, vendors and other third parties', 'What if you don’t let us collect certain information?', 'Some information is required for our Products to work. Other information is optional, but without it, the quality of your experience might be affected.', 'Learn more', 'What if the information we collect doesn’t identify individuals?', 'In some cases information is de-identified, aggregated, or anonymized by third parties so that it no longer identifies individuals before it’s made available to us. We use this information as described below without trying to re-identify individuals.', 'Take control', 'Manage the information we collect about you', 'Privacy Center', 'How do we use your information?', 'Highlights', 'We use information we collect to provide a personalized experience to you, including ads, along with the other purposes we explain in detail below.', 'For some of these purposes, we use information across our Products and across your devices. The information we use for these purposes is automatically processed by our systems. But in some cases, we also use manual review to access and review your information.', 'To use less information that’s connected to individual users, in some cases we de-identify or aggregate information or anonymize it so that it no longer identifies you. We use this information in the same ways we use your information as described in this section.', 'Here are the ways we use your information:', 'To provide, personalize and improve our Products', 'We use information we have to provide and improve our Products. This includes personalizing features, content and recommendations, such as your Facebook Feed, Instagram Feed, Stories and ads. We use information with special protections you choose to provide for these purposes, but not to show you ads.', 'Read more about how we use information to provide, personalize and improve our Products:', 'How we show ads and other sponsored or commercial content', 'How we use information to improve our Products', 'How we use location-related information', 'To promote safety, security and integrity', 'We use information we collect to help protect people from harm and provide safe, secure Products.', 'Learn more', 'To provide measurement, analytics and business services', 'Lots of people rely on our Products to run or promote their businesses or share content. We help them measure how well their ads and other content, products and services are working.', 'Learn more', 'To communicate with you', "We communicate with you using information you've given us, like contact information you've entered on your profile.", 'Learn more', 'To research and innovate for social good', 'We use information we have, information from researchers and datasets from publicly available sources, professional groups and non-profit groups to conduct and support research.', 'Learn more', 'More in the Privacy Policy', 'Why and how we process your information', 'How is your information shared on Meta Products or with integrated partners?', 'Highlights', 'On Meta Products', 'Learn more about the different cases when your information can be shared on our Products:', 'People and accounts you share and communicate with', 'Content others share or reshare about you', 'Public content', 'With integrated partners', 'You can choose to connect with integrated partners who use our Products. If you do, these integrated partners receive information about you and your activity.', 'These integrated partners can always access information that’s public on our Products. Learn more about other information they receive and how they handle your information:', 'When you use an integrated partner’s product or service', 'When you interact with someone else’s content on an integrated partner’s product or service', 'How integrated partners handle your information', 'Take control', 'Learn more about audiences', 'Privacy Center', 'Manage apps and websites', 'How do we share information with third parties?', 'Highlights', "We don't sell any of your information to anyone, and we never will. We also require partners and other third parties to follow rules about how they can and cannot use and disclose the information we provide.", 'Here’s more detail about who we share information with:', 'Partners', 'Advertisers and Audience Network publishers', 'Partners who use our analytics services', 'Partners who offer goods or services on our Products and commerce services platforms', 'Integrated partners', 'Vendors', 'Measurement vendors', 'Marketing vendors', 'Service providers', 'Service providers', 'Third parties', 'External researchers', 'AI integrations', 'Other third parties', 'We also share information with other third parties in response to legal requests, to comply with applicable law or to prevent harm. Read the Policy.', 'And if we sell or transfer all or part of our business to someone else, in some cases we’ll give the new owner your information as part of that transaction, but only as the law allows.', 'How do the Meta Companies work together?', 'Highlights', 'We are part of the Meta Companies that provide Meta Company Products. Meta Company Products include all the Meta Products covered by this Policy, plus other products like WhatsApp and more.', 'We share information we collect, infrastructure, systems and technology with the other Meta Companies. Learn more about how we transfer information to other countries.', 'We also process information that we receive about you from other Meta Companies, according to their terms and policies and as permitted by applicable law. In some cases, Meta acts as a service provider for other Meta Companies. We act on their behalf and in accordance with their instructions and terms.', 'Why we share across the Meta Companies', 'Meta Products share information with other Meta Companies:', 'To promote safety, security and integrity and comply with applicable laws', 'To personalize offers, ads and other sponsored or commercial content', 'To develop and provide features and integrations', 'To understand how people use and interact with Meta Company Products', 'See some examples of why we share.', 'More resources', 'Review the privacy policies of the other Meta Companies', 'Facebook Help Center', 'How can you manage or delete your information and exercise your rights?', 'Highlights', 'We offer you a variety of tools to view, manage, download and delete your information below. You can also manage your information by visiting the settings of the Products you use. You may also have other privacy rights under applicable laws.', 'To exercise your rights, visit our Help Centers, your settings for Facebook and Instagram and your device-based settings.', 'Take a privacy checkup', 'Take a privacy checkup', 'Be guided through Facebook privacy settings', 'View and manage your information', 'Access your information', 'Off-Meta activity', 'Ad preferences', 'Manage your data', 'Port, download or delete your information', 'Port your information', 'Download your information', 'Delete your information or account', 'You can learn more about how privacy works on Facebook and on Instagram, and in the Facebook Help Center. If you have questions about this policy, you can contact us as described below. In some countries, you may also be able to contact the Data Protection Officer for Meta Platforms, Inc., and depending on your jurisdiction, you may also contact your local Data Protection Authority (“DPA”) directly.', 'How long do we keep your information?', 'Highlights', 'We keep information as long as we need it to provide our Products, comply with legal obligations or protect our or other’s interests. We decide how long we need information on a case-by-case basis. Here’s what we consider when we decide:', 'If we need it to operate or provide our Products. For example, we need to keep some of your information to maintain your account. Learn more.', 'The feature we use it for, and how that feature works. For example, messages sent using Messenger’s vanish mode are retained for less time than regular messages. Learn more.', 'How long we need to retain the information to comply with certain legal obligations. See some examples.', 'If we need it for other legitimate purposes, such as to prevent harm; investigate possible violations of our terms or policies; promote safety, security and integrity; or protect ourselves, including our rights, property or products', 'In some instances and for specific reasons, we’ll keep information for an extended period of time. Read our Policy about when we may preserve your information.', 'How do we transfer information?', 'Highlights', 'Why is information transferred to other countries?', 'Where is information transferred?', 'How do we safeguard your information?', 'How do we respond to legal requests, comply with applicable law and prevent harm?', 'Highlights', 'We access, preserve, use and share your information:', 'In response to legal requests, like search warrants, court orders, production orders or subpoenas. These requests come from third parties such as civil litigants, law enforcement and other government authorities. Learn more about when we respond to legal requests.', 'In accordance with applicable law', 'To promote the safety, security and integrity of Meta Products, users, employees, property and the public. Learn more.', 'We may access or preserve your information for an extended amount of time. Learn more.', 'How will you know the Policy has changed?', "We'll notify you before we make material changes to this Policy. You’ll have the opportunity to review the revised Policy before you choose to continue using our Products.", 'Privacy notice for United States residents', 'You can learn more about the consumer privacy rights that may be available to you by reviewing the United States Regional Privacy Notice.', 'How to contact Meta with questions', 'You can learn more about how privacy works on Facebook and on Instagram and in the Facebook Help Center. If you have questions about this Policy or have questions, complaints or requests regarding your information, you can contact us as described below.', 'You can contact us online or by mail at:', 'Meta Platforms, Inc.', 'ATTN: Privacy Operations', '1601 Willow Road', 'Menlo Park, CA 94025', 'Why and how we process your information', 'The categories of information we use, and why and how information is processed, are set out below:', 'Why and how we process your information', "Information categories we use (see 'What Information do we collect?' for more information on each information category)", 'The actual information we use depends on your factual circumstances, but could include any of the following:', 'Personalizing the Meta Products (other than ads, see below): Our systems automatically process information we collect and store associated with you and others to assess and understand your interests and your preferences and provide you personalized experiences across the Meta Products in accordance with our terms. This is how we:', 'Personalize features and content (such as your Facebook Feed, Instagram Feed and Stories);', 'Make suggestions for you (such as people you may know, groups or events that you may be interested in or topics that you may want to follow) on and off our products.', 'Learn more about how we use information about you to personalize your experience on and across Meta Products and how we choose the ads that you see.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Metadata about content', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings (like GPS location)', 'Location-related information', 'Information about the network you connect your device to', 'Reports about our products’ performance on your device', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'Providing ads on the Meta Company Products:', 'Our ads system automatically processes information that we’ve collected and stored associated with you. Our ads system uses this information to understand your interests and your preferences and personalize your ads across the Meta Company Products.', 'Our ads system prioritizes what ad to show you based on what audience advertisers want to reach. Then we match the ad to people who might be interested. Learn more about how our ads system works', 'Your activity and information you provide:', 'Age', 'The gender you provide', 'Information about ads we show you and how you engage with those ads', 'App, browser and device information:', 'Location information', 'Device characteristics and device software', 'If you decide to add a WhatsApp account to an Accounts Center with other accounts on Meta Company Products:', 'To associate your accounts on Meta Company Products with your WhatsApp account in the same Accounts Center and share your information with WhatsApp.', 'Note: the list below is about information from Meta. For information that WhatsApp shares with Meta see the WhatsApp Help Center article.', 'Your activity and information you provide', 'Friends, followers and other connections', 'App, browser and device information', 'Providing and improving our Meta Products: The provision of the Meta Products includes collecting, storing, and, where relevant, sharing, profiling, reviewing and curating, and in some instances not only automated processing but also manual (human) reviewing, to:', 'Create and maintain your account and profile,', 'Connect your Meta Products account, including your public profile information, to an integrated partner to sign in or share your information,', 'Facilitate the sharing of content and status,', 'Provide and curate features,', 'Provide messaging services, the ability to make voice and video calls and connect with others,', 'Provide advertising products,', 'Understand and enable creation of content like text, audio, images and videos, including through artificial intelligence technology we provide,', 'Undertake analytics, and', 'Facilitate your purchases and payments on Meta Pay or other Meta checkout experiences.', 'We also use information to develop, research and test improvements to our Products. We use information we have to:', 'See if a product is working correctly,', 'Troubleshoot and fix it when it’s not,', 'Test out new products and features to see if they work,', 'Get feedback on our ideas for products or features, and', 'Conduct surveys and other research about what you like about our Products and brands and what we can do better.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Your public profile information (including your name, username and profile picture)', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Messages you send and receive, including their content, subject to applicable law', 'Metadata about content and messages, subject to applicable law', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make, including truncated credit card information', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Your photo or video selfie if you provide it when you contact us for account support', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'Promoting safety, integrity and security on and across the Meta Products: The Meta Products are designed to research and help ensure the safety, integrity and security of those services and those people who enjoy them, on and off Meta Products. We process information we have associated with you and apply automated processing techniques and, in some instances, conduct manual (human) review to:', 'Verify accounts and activity,', 'Find and address violations of our terms or policies. In some cases, the decisions we make about violations are reviewed by the Oversight Board,', 'Investigate suspicious activity,', 'Detect, prevent and combat harmful or unlawful behavior, such as to review and, in some cases, remove content reported to us,', 'Identify and combat disparities and racial bias against historically marginalized communities,', 'Protect the life, physical or mental health, well-being or integrity of our users or others,', 'Detect and prevent spam, other security matters and other bad experiences,', 'Detect and stop threats to our personnel and property, and', 'Maintain the integrity of our Products.', 'For more information on safety, integrity and security generally on Meta Products, visit the Facebook Security Help Center and Instagram Security Tips.', 'Your activity and information you provide::', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Messages you send and receive, including their content, subject to applicable law', 'Metadata about content and messages, subject to applicable law', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make, including truncated credit card information', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Your photo or video selfie if you provide it when you contact us for account support', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'To communicate with you: We use information you’ve given us (like contact information on your profile) to send you a communication, like an e-mail or in-product notice, for example:', 'We’ll contact you via email or in-product notifications in relation to the Meta Products, product-related issues, research or to let you know about our terms and policies.', 'We also use contact information like your email address to respond when you contact us.', 'Your activity and information you provide:', 'Contact information on your profile and your communications with us', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies.', 'Transferring, storing or processing your information across borders, including from and to the United States and other countries: We share information we collect globally, both internally across our offices and data centers and externally with our partners, third parties and service providers. Because Meta is global, with users, partners, vendors and employees around the world, transfers are necessary:', 'To operate and provide the services described in the terms that apply to the Meta Product(s) you are using. This includes allowing you to share information and connect with your family and friends around the globe; and', 'To fix, analyze and improve our Products.', 'For more information, see the "How do we transfer information?" section of the Meta Privacy Policy.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Metadata about content and messages, subject to applicable law', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make, including truncated credit card information', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Your photo or video selfie if you provide it when you contact us for account support', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users’', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'Processing information subject to special protections under applicable laws that you provide so we can share it with those you choose, to provide, personalize and improve our Products and to undertake analytics.  We’ll collect, store, publish and apply automated, or sometimes manual (human), processing for these purposes.', 'Your activity and information you provide:', 'Any information with special protections that you choose to provide, such as your religious views, your sexual orientation, political views, health, racial or ethnic origin, philosophical beliefs or trade union membership, or as part of surveys you choose to participate in, and where you have given your explicit consent', 'Receiving and using information from third parties to tailor the ads you see:  We’ll use information that advertisers, businesses and other partners provide us about activity off Meta Company Products that we have associated with you to personalize ads that we show you on Meta Products, and on websites, apps and devices that use our advertising services. We receive this information whether or not you’re logged in or have an account on our Products. See the Cookies Policy for more information.', 'Your activity and information you provide:', 'Information and content you provide, such as your name or email address', 'Information from partners, vendors and third parties', 'Sharing your contact, profile or other information with third parties upon your request: The type of third party and categories of information shared depend on the circumstances of what you ask us to share. For example:', 'We share your email (or other contact information) or other information you might choose when you direct us to share it with an advertiser so they can contact you with additional information about a promoted product, and', 'If you choose to integrate other apps, games or websites with Meta Products and log in, we’ll share your information with the app, game or website to log you in.', 'Your activity and information you provide:', 'Information such as your contact or profile information', 'Content you create, like posts or comments', 'Providing measurement, analytics and business services:', 'Our systems automatically, as well as with some manual (human) processing, process information we have collected and stored about you and others. We use this information to:', 'Provide insights and measurement reports to businesses, advertisers and other partners to help them measure the effectiveness and distribution of their or their clients’ ads, content and services, to understand the kinds of people who are seeing their content and ads, and how their content and ads are performing on and off Meta Products, and', 'Provide aggregated user analytics and insights reports that help users, businesses, advertisers and other partners better understand the audiences with whom they may want to connect, as well as the types of people who use their services and how people interact with their content, websites, apps and services.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', 'Identifiers that tell your device apart from other users', 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Sharing of information across the Meta Companies:', 'To provide a seamless, consistent and richer, innovative experience across the Meta Company Products to enable cross app interactions, sharing, viewing and engaging with content, including posts and videos.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Metadata about content', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', "Identifiers that tell your device apart from other users'", 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Business intelligence and analytics:', 'To understand, in aggregate, your usage of and across our Products, to accurately count people and businesses; and', 'To validate metrics directly related to these, in order to inform and improve product direction and development and to adhere to (shareholder/earning) reporting obligations.', 'Your activity and information you provide:', 'Content you create, like posts, comments or audio', 'Content you provide through our camera feature or your camera roll settings, or through our voice-enabled features', 'Metadata about content and messages, subject to applicable law', 'Types of content you view or interact with, and how you interact with it', 'Apps and features you use, and what actions you take in them', 'Purchases or other transactions you make', 'Hashtags you use', 'The time, frequency and duration of your activities on our Products', 'Friends, followers and other connections', 'App, browser and device information:', 'Device characteristics and device software', 'What you’re doing on your device, like whether our app is in the foreground or if your mouse is moving (which can help tell humans from bots)', "Identifiers that tell your device apart from other users'", 'Device signals', 'Information you’ve shared through your device settings', 'Location-related information', 'Information about the network you connect your device to, including your IP address', 'Information from cookies and similar technologies', 'Information from partners, vendors and third parties', 'Identifying you as a Meta Product user and personalizing the ads we show you through Meta Audience Network when you visit other apps:', 'When we show you ads </t>
   </si>
   <si>
@@ -1021,6 +1914,21 @@
     <t>['Privacy Policy | TikTok', 'U.S.', 'Privacy Policy', 'Last updated: Aug 19, 2024', 'This Privacy Policy applies to TikTok services (the â\x80\x9cPlatformâ\x80\x9d), which include TikTok apps, websites, software and related services accessed via any platform or device that link to this Privacy Policy. The Platform is provided and controlled by TikTok Inc. (â\x80\x9cTikTokâ\x80\x9d, â\x80\x9cweâ\x80\x9d or â\x80\x9cusâ\x80\x9d). We are committed to protecting and respecting your privacy. This Privacy Policy explains how we collect, use, share, and otherwise process the personal information of users and other individuals age 13 and over in connection with our Platform. For information about how we collect, use, share, and otherwise process the personal information of users under age 13 (â\x80\x9cChildrenâ\x80\x9d), please refer to our Childrenâ\x80\x99s Privacy Policy. For information about how we collect, use, share, and otherwise process consumer health data as defined under Washingtonâ\x80\x99s My Health My Data Act and other similar state laws, please refer to the Consumer Health Data Privacy Policy.', 'Capitalized terms that are not defined in this Privacy Policy have the meaning given to them in theÂ\xa0Terms of Service.', 'What Information We Collect', 'We may collect information from and about you, including information that you provide, information from other sources, and automatically collected information.', 'Information You Provide', 'When you create an account, upload content, contact us directly, or otherwise use the Platform, you may provide some or all of the following information:', 'Account and profile information, such as name, age, username, password, language, email, phone number, social media account information, and profile image.', 'User-generated content, including comments, photographs, livestreams, audio recordings, videos, text, hashtags, and virtual item videos that you choose to create with or upload to the Platform (â\x80\x9cUser Contentâ\x80\x9d) and the associated metadata, such as when, where, and by whom the content was created. Even if you are not a user, information about you may appear in User Content created or published by users on the Platform. When you create User Content, we may upload or import it to the Platform before you save or post the User Content (also known as pre-uploading), for example, in order to recommend audio options, generate captions, and provide other personalized recommendations. If you apply an effect to your User Content, we may collect a version of your User Content that does not include the effect.', 'Messages, which include information you provide when you compose, send, or receive messages through the Platformâ\x80\x99s messaging functionalities. They include messages you send through our chat functionality when communicating with sellers who sell goods to you, and your use of virtual assistants when purchasing items through the Platform. That information includes the content of the message and information about the message, such as when it was sent, received, or read, and message participants. Please be aware that messages you choose to send to other users of the Platform will be accessible by those users and that we are not responsible for the manner in which those users use or share the messages.', 'Information, including text, images, and videos, found in your deviceâ\x80\x99s clipboard, with your permission. For example, if you choose to initiate information sharing with a third-party platform, or choose to paste content from the clipboard onto the Platform, we access this information stored in your clipboard in order to fulfill your request.', 'Purchase information, including payment card numbers or other third-party payment information (such as PayPal) where required for the purpose of payment, and billing and shipping address. We also collect information that is required for extended warranty purposes and your transaction and purchase history on or through the Platform.', 'Your phone and social network contacts, with your permission. If you choose to find other users through your phone contacts, we will access and collect information such as names, phone numbers, and email addresses, and match that information against existing users of the Platform. If you choose to find other users through your social network contacts, we will collect your public profile information as well as names and profiles of your social network contacts.', 'Your choices and communication preferences.', 'Information to verify an account such as proof of identity or age.Â', 'Information in correspondence you send to us, including when you contact us for support.', 'Information you share through surveys or your participation in challenges, research, promotions, marketing campaigns, events, or contests such as your gender, age, likeness, and preferences.', 'Information From Other Sources', 'We may receive the information described in this Privacy Policy from other sources, such as:', 'If you choose to sign-up or log-in to the Platform using a third-party service such as Facebook, Twitter, Instagram, or Google, or link your TikTok account to a third-party service, we may collect information from the serviceâ\x80\x93for example, your public profile information (such as nickname), email, and contact list.', 'Advertisers, measurement and other partners share information with us about you and the actions you have taken outside of the Platform, such as your activities on other websites and apps or in stores, including the products or services you purchased, online or in person. These partners also share information with us, such as mobile identifiers for advertising, hashed email addresses and phone numbers, and cookie identifiers, which we use to help match you and your actions outside of the Platform with your TikTok account. Some of our advertisers and other partners enable us to collect similar information directly from their websites or apps by integrating our TikTok Advertiser Tools (such as TikTok Pixel).', 'We may obtain information about you from certain affiliated entities within our corporate group, including about your activities on their platform.', 'We may receive information about you from others, including where you are included or mentioned in User Content, direct messages, in a complaint, appeal, request or feedback submitted to us, or if your contact information is provided to us.', 'We may also collect or receive information about you from organizations, businesses, people, and others, including, for example, publicly available sources, government authorities, professional organizations, and charity groups.', 'Automatically Collected Information', 'We automatically collect certain information from you when you use the Platform, including internet or other network activity information such as your IP address, geolocation-related data, unique device identifiers, browsing and search history (including content you have viewed in the Platform), and Cookies.', 'Usage Information. We collect information regarding your use of the Platform and any other User Content that you generate through or upload to our Platform.Â', 'Device Information. We collect certain information about the device you use to access the Platform, such as your IP address, user agent, mobile carrier, time zone settings, identifiers for advertising purposes, model of your device, the device system, network type, device IDs, your screen resolution and operating system, app and file names and types, keystroke patterns or rhythms,Â\xa0battery state, audio settings and connected audio devices. We automatically assign you a device ID and user ID. Where you log-in from multiple devices, we will be able to use information such as your device ID and user ID to identify your activity across devices. We may also associate you with information collected from devices other than those you use to log-in to the Platform.Â', 'Location Data. We collect information about your approximate location, including location information based on your SIM card and/or IP address. In addition, we collect location information (such as tourist attractions, shops, or other points of interest) if you choose to add the location information to your User Content. Current versions of the app do not collect precise or approximate GPS information from U.S. users. If you are still using an older version that allowed for collection of precise or approximate GPS information (last release in August 2020) and you granted us permission to do so, we may collect such information.', 'Image and Audio Information. We may collect information about the videos, images and audio that are a part of your User Content, such as identifying the objects and scenery that appear, the existence and location within an image of face and body features and attributes, the nature of the audio, and the text of the words spoken in your User Content. We may collect this information to enable special video effects, for content moderation, for demographic classification, for content and ad recommendations, and for other non-personally-identifying operations. We may collect biometric identifiers and biometric information as defined under U.S. laws, such as faceprints and voiceprints, from your User Content. Where required by law, we will seek any required permissions from you prior to any such collection. Click here to learn more.', 'Metadata. When you upload or create User Content, you automatically upload certain metadata that is connected to the User Content. Metadata describes other data and provides information about your User Content that will not always be evident to the viewer. For example, in connection with your User Content the metadata can describe how, when, where, and by whom the piece of User Content was created, collected, or modified and how that content is formatted. It also includes information, such as your account name, that enables other users to trace back the User Content to your user account. Additionally, metadata includes data that you choose to provide with your User Content, e.g., any hashtags used to mark keywords to the video and captions.', 'Cookies. We and our service providers and business partners use cookies and other similar technologies (e.g., web beacons, flash cookies, etc.) (â\x80\x9cCookiesâ\x80\x9d) to automatically collect information, measure and analyze how you use the Platform, including which pages you view most often and how you interact with content, enhance your experience using the Platform, improve the Platform, provide you with advertising, and measure the effectiveness of advertisements and other content. We and our partners also use Cookies to promote the Platform on other platforms and websites. Cookies enable the Platform to provide certain features and functionality. Web beacons are very small images or small pieces of data embedded in images, also known as â\x80\x9cpixel tagsâ\x80\x9d or â\x80\x9cclear GIFs,â\x80\x9d that can recognize Cookies, the time and date a page is viewed, a description of the page where the pixel tag is placed, and similar information from your computer or device. To learn how to disable certain Cookies, see the â\x80\x9cYour Choicesâ\x80\x9d section below.', 'We may link your contact or account information with your activity on and off our Platform across all your devices, using your email or other log-in or device information. We may use this information to display advertisements on our Platform tailored to your interests, preferences, and characteristics.', 'We are not responsible for the privacy practices of our service providers and business partners, and the information practices of these service providers and business partners are not covered by this Privacy Policy.', 'We may aggregate or de-identify the information described above. Aggregated or de-identified data is not subject to this Privacy Policy.', 'How We Use Your Information', 'As explained below, we use your information to improve, support and administer the Platform, to allow you to use its functionalities, and to fulfill and enforce our Terms of Service. We may also use your information to, among other things, show you suggestions, promote the Platform, and customize your ad experience.', 'We generally use the Information We Collect:', 'To fulfill requests for products, services, Platform functionality, support and information for internal operations, including troubleshooting, data analysis, testing, research, statistical, and survey purposes and to solicit your feedback.', 'To customize the content you see when you use the Platform. For example, we may provide you with services based on the country settings you have chosen or show you content that is similar to content that you have liked or interacted with.', 'To send promotional materials from us or on behalf of our affiliates and trusted third parties.', 'To improve and develop our Platform and conduct product development.', 'To measure and understand the effectiveness of the advertisements we serve to you and others and to deliver advertising, including targeted advertising, to you on the Platform.', 'To make suggestions and provide a customized ad experience.', 'To support the social functions of the Platform, including to permit you and others to connect with each other (for example, through our Find Friends function), to suggest accounts to you and others, and for you and others to share, download, and otherwise interact with User Content posted through the Platform.', 'To use User Content as part of our advertising and marketing campaigns to promote the Platform.', 'To understand how you use the Platform, including across your devices.', 'To infer additional information about you, such as your age, gender, and interests.', 'To help us detect abuse, fraud, and illegal activity on the Platform.', 'To promote the safety and security of the Platform, including by scanning, analyzing, and reviewing User Content, messages and associated metadata for violations of our Terms of Service, Community Guidelines, or other conditions and policies.', 'To verify your identity in order to use certain features, such as livestream or verified accounts, or when you apply for a Business Account, to ensure that you are old enough to use the Platform (as required by law), or in other instances where verification may be required.', 'To communicate with you, including to notify you about changes in our services.', 'To announce you as a winner of our contests or promotions if permitted by the promotion rule, and to send you any applicable prizes.', 'To enforce our Terms of Service, Community Guidelines, and other conditions and policies.', 'Consistent with your permissions, to provide you with location-based services, such as advertising and other personalized content.', 'To train and improve our technology, such as our machine learning models and algorithms.', 'To combine all the Information We Collect or receive about you for any of the foregoing purposes.', 'To facilitate sales, promotion, and purchases of goods and services and to provide user support.', 'For any other purposes disclosed to you at the time we collect your information or pursuant to your consent.', 'Profiling: We do not engage in profiling which results in legal or similarly significant effects, as defined under applicable law.', 'How We Share Your Information', 'We are committed to maintaining your trust, and while TikTok does not sell your personal information or share your personal information with third parties for purposes of cross-context behavioral advertising where restricted by applicable law, we want you to understand when and with whom we may share the Information We Collect for business purposes.', 'Service Providers and Business Partners', 'We share the categories of personal information listed above with service providers and business partners to help us perform business operations and for business purposes, including research, payment processing and transaction fulfillment, database maintenance, administering contests and special offers, technology services, deliveries, sending communications, advertising and marketing services, analytics, measurement, data storage and hosting, disaster recovery, search engine optimization, and data processing. These service providers and business partners may include:', 'Payment processors and transaction fulfillment providers, who may receive the Information You Provide, Information From Other Sources, and Automatically Collected Information but who do not receive your message data, including, in particular, the following third-party payment providers/processors: PayPal (https://www.paypal.com/us/webapps/mpp/ua/privacy-full) and Stripe (https://stripe.com/en-ie/privacy).', 'Customer and technical support providers, who may receive the Information You Provide, Information From Other Sources, and Automatically Collected Information.', 'Researchers who may receive the Information You Provide, Information From Other Sources, and Automatically Collected Information but would not receive your payment information or message data.', 'Advertising, marketing, and analytics vendors, who may receive the Information You Provide, Information From Other Sources, and Automatically Collected Information but would not receive your payment information or message data.', 'Within Our Corporate Group', 'As a global company, the Platform is supported by certain entities within our corporate group, which are given limited remote access to Information We Collect as necessary to enable them to provide certain important functions. To learn more about how we share information with certain corporate group entities, see here.', 'In Connection with a Sale, Merger, or Other Business Transfer', 'We may share all of the Information We Collect in connection with a substantial corporate transaction, such as the sale of a website, a merger, consolidation, asset sales, or in the unlikely event of bankruptcy.', 'For Legal Reasons', 'We may disclose any of the Information We Collect to respond to subpoenas, court orders, legal process, law enforcement requests, legal claims, or government inquiries, and to protect and defend the rights, interests, safety, and security of the Platform, our affiliates, users, or the public. We may also share any of the Information We Collect to enforce any terms applicable to the Platform, to exercise or defend any legal claims, and comply with any applicable law.Â', 'With Your Consent', 'We may share your information for other purposes pursuant to your consent or at your direction.', 'We partner with third-party services (such as Facebook, Instagram, Twitter, and Google) to offer you a seamless sign-up, log-in, and content-sharing experience. We may share information about you with these third-party services if you choose to use these features. For example, the services may receive information about your activity on the Platform and may notify your connections on the third-party services about your use of the Platform, in accordance with their privacy policies. If you choose to allow a third-party service to access your account, we will share certain information about you with the third party. Depending on the permissions you grant, the third party may be able to obtain your account information and other information you choose to provide.', 'If you choose to engage in public activities on the Platform, you should be aware that any information you share may be read, collected, or used by other users. You should use caution in disclosing personal information while using the Platform. We are not responsible for the information you choose to submit.', 'When you make a purchase from a third party on the Platform, including from a seller selling products through our shopping features, we share the information related to the transaction with that third party and their service providers and transaction fulfillment providers. By making the purchase, you are directing us to share your information in this way. These entities may use the information shared in accordance with their privacy policies.', 'Your Rights', 'You may submit a request to know, access, correct or delete the information we have collected from or about you at https://www.tiktok.com/legal/report/privacy. You may appeal any decision we have made about your request by following the instructions in the communication you receive from us notifying you of our decision. You may also exercise your rights to know, access, correct, delete, or appealby sending your request to the physical address provided in the â\x80\x9cContact Usâ\x80\x9d section below. You can also update your account information directly through your in-app settings, as well as request a copy of your TikTok data or request to deactivate by following the instructions here or delete your account by following the instructions here.', 'You may be entitled, in accordance with applicable law, to submit a request through an authorized agent. To designate an authorized agent to exercise choices on your behalf, please provide evidence that you have given such agent power of attorney or that the agent otherwise has valid written authority to submit requests to exercise rights on your behalf. We will respond to your request consistent with applicable law and subject to proper verification. We will verify your request by asking you to send it from the email address associated with your account or to provide information necessary to verify your account.', 'More information about requests that we received can be found here.Â', 'While some of the information that we collect, use, and disclose may constitute sensitive personal information under applicable state privacy laws, such as information from users under the relevant age threshold, information you disclose in survey responses or in your User Content about your racial or ethnic origin, national origin, religious beliefs, mental or physical health diagnosis, sexual life or sexual orientation, status as transgender or nonbinary, citizenship or immigration status, or financial information, we only process such information in order to provide the Platform and within other exemptions under applicable law. For example, we may process your financial information in order to provide you the goods or services you request from us or your driverâ\x80\x99s license number in order to verify your identity.', 'Your Choices', 'You may be able to control some of the Information We Collect through your device browser settings to refuse or disable Cookies. Because each browser is different, please consult the instructions provided by your browser. Please note that you may need to take additional steps to refuse or disable certain types of Cookies. In addition, your choice to disable Cookies is specific to the particular browser or device that you are using when you disable Cookies, so you may need to separately disable Cookies for each type of browser or device. If you choose to refuse, disable, or delete Cookies, some of the functionality of the Platform may no longer be available to you. Without this information, we are not able to provide you with all of the requested services.', 'You can navigate to "Ads" in your in-app settings to opt-out of targeted advertising based on personal information about your activity on nonaffiliated apps and websites.', 'You may be able to manage third-party advertising preferences for some of the third parties we work with to serve advertising across the Internet by using the choices available atÂ\xa0https://www.networkadvertising.org/managing/opt_out.aspÂ\xa0andÂ\xa0https://www.aboutads.info/choices.', 'Your device may have controls that determine what Information We Collect. For example, you can control whether we can collect your mobile advertising identifier for advertising through settings on your Apple and Android devices.', 'You can opt out of marketing or advertising emails by using the â\x80\x9cunsubscribeâ\x80\x9d link or mechanism noted in marketing or advertising emails.', 'Current versions of the app do not collect precise or approximate GPS information from U.S. users. If you are still using an older version that allowed for collection of precise or approximate GPS information (last release in August 2020) and you granted us permission to do so, you can prevent your device from sharing such information with the Platform at any time through your deviceâ\x80\x99s operating system settings.', 'If you have registered for an account, you may access, review, and update certain personal information that you have provided to us by logging into your account and using available features and functionalities.', 'Some browsers transmit â\x80\x9cdo-not-trackâ\x80\x9d signals to websites. Because of differences in how browsers incorporate and activate this feature, we currently do not take action in response to these signals.', 'Data Security and Retention', 'We use reasonable measures to help protect information from loss, theft, misuse, unauthorized access, disclosure, alteration, or destruction. You should understand that no data storage system or transmission of data over the Internet or any other public network can be guaranteed to be 100 percent secure. Please note that information collected by third parties may not have the same security protections as information you submit to us, and we are not responsible for protecting the security of such information.', 'We retain information for as long as necessary to provide the Platform and for the other purposes set out in this Privacy Policy. We also retain information when necessary to comply with contractual and legal obligations, when we have a legitimate business interest to do so (such as improving and developing the Platform, and enhancing its safety, security and stability), and for the exercise or defense of legal claims.', 'The retention periods are different depending on different criteria, such as the type of information and the purposes for which we use the information. For example, when we process your information such as your profile information to provide you with the Platform, we keep this information for as long as you have an account. If you violate our Terms of Service, Community Guidelines, or other conditions or policies, we may remove your profile immediately, but may keep other information about you to process the violation.', 'TikTok may transmit your data to its servers or data centers outside of the United States for storage and/or processing. Other entities with whom TikTok may share your data as described herein may be located outside of the United States.', 'Children and Teens', 'The privacy of Children is important to us. We provide a separate experience for Children in the United States, in which we collect and process only limited information. For information about how we collect, use, share, and otherwise process the personal information of Children, please refer to our Childrenâ\x80\x99s Privacy Policy.', 'The Platform otherwise is not directed at Children. If we become aware that personal information has been collected on the Platform from a Child, we will delete this information and terminate the Childâ\x80\x99s account. If you believe there is a user who is below the age of 13, please contact us at: https://www.tiktok.com/legal/report/feedback.', "If you are a parent or guardian, our Guardian's Guide contains information and resources to help you understand the Platform and the tools and controls you can use. As a parent or guardian, you can also request the deletion of the account of your underage child or download the account data of your underage child by contacting us at https://www.tiktok.com/legal/report/privacy.", "If you are a parent or guardian, depending on your state of residence, you may have the ability to exercise certain rights over your child's or teen's account. For example, you may request the deletion of their accounts, download account data, or exercise other rights in connection with your child or teen by contacting us at https://www.tiktok.com/legal/report/privacy. We will address these requests in accordance with applicable law.", 'Other Rights', 'Sharing for Direct Marketing Purposes (Shine the Light)', 'If you are a California resident, once a calendar year, you may be entitled to obtain information about personal information that we shared, if any, with other businesses for their own direct marketing uses. To submit a request, contact us at:Â\xa0https://www.tiktok.com/legal/report/privacy.', 'Content Removal for Users Under 18', 'Users of the Platform who are California residents and are under 18 years of age may request and obtain removal of User Content they posted by contacting us at: https://www.tiktok.com/legal/report/privacy. All requests must provide a description of the User Content you want removed and information reasonably sufficient to permit us to locate that User Content. We do not accept California Removal Requests via postal mail, telephone, or facsimile. We may not be able to respond if you do not provide adequate information. Please note that your request does not ensure complete or comprehensive removal of the material. For example, User Content that you have posted may be republished or reposted by another user.', 'Users of the Platform who are Connecticut residents and are under 18 years of age, and parents and guardians of users of the Platform who are Connecticut residents under 16 years of age, may request that we unpublish or delete their own account (for users aged 13 through 17) or their childâ\x80\x99s account (for parents and guardians with teen users under 16) by following the instructions here.', 'Privacy Policy Updates', 'We may update this Privacy Policy from time to time. When we update the Privacy Policy, we will notify you by updating the â\x80\x9cLast Updatedâ\x80\x9d date at the top of the new Privacy Policy, posting the new Privacy Policy, or providing any other notice required by applicable law. We recommend that you review the Privacy Policy each time you visit the Platform to stay informed of our privacy practices.', 'Contact Us', 'Questions, comments and requests regarding this Privacy Policy should be addressed to:', 'Contact us:Â\xa0https://www.tiktok.com/legal/report/privacy', 'Mailing Address: TikTok Inc., Attn: Privacy Policy Inquiry, 5800 Bristol Parkway, Suite 100, Culver City, CA 90230']</t>
   </si>
   <si>
+    <t>['DeepSeek Privacy Policy', 'DeepSeek Privacy Policy', 'Last Update:  July 4, 2025', 'Welcome to DeepSeek!', 'Introduction', 'This privacy policy (â\x80\x9cPrivacy Policyâ\x80\x9d) applies to the Personal Data (or other similar terms as defined by applicable data protection law) relating to you (â\x80\x9cPersonal Dataâ\x80\x9d) that DeepSeek processes in connection with DeepSeek apps, websites, software, and related services (the â\x80\x9cServicesâ\x80\x9d), that link to or reference this Privacy Policy. The Services enable you to create and interact with chatbots.', 'Data Controller: The Services are provided and controlled by Hangzhou DeepSeek Artificial Intelligence Co., Ltd., with its registered address in China (â\x80\x9cweâ\x80\x9d or â\x80\x9cusâ\x80\x9d). If you have any questions about how we use your Personal Data, please contact privacy@deepseek.com or click the â\x80\x9cContact usâ\x80\x9d column on the website.', 'Please be informed that the processing rules for Personal Data collected from end users when accessing downstream systems or applications developed by developers using our open platform services are not covered by this privacy policy. The developer operating the application, as the controller of the Personal Data processing activity, should disclose the relevant Personal Data protection policies to the end users. If you would like to learn more about our model mechanism or training methods, please refer to the Model Mechanism and Training Methods of DeepSeek.', 'What Personal Data We Collect', 'We collect your Personal Data in three ways: Personal Data You Provide, Automatically Collected Personal Data, and Personal Data From Other Sources. More detail is provided below.', 'Personal Data You Provide', 'When you create an account, input content, contact us directly, or otherwise use the Services, you may provide some or all of the following Personal Data:', 'Account Personal Data. We collect Personal Data that you provide when you set up an account, such as your date of birth (where applicable), username (where applicable), email address and/or telephone number, and password.', 'User Input. When you use our Services, we may collect your text input, prompt, uploaded files, feedback, chat history, or other content that you provide to our model and Services (â\x80\x9cPromptsâ\x80\x9d or "Inputs"). We generate responses (â\x80\x9cOutputsâ\x80\x9d) based on your Inputs.', 'Personal Data When You Contact Us. When you contact us, we collect the Personal Data you send us, such as proof of identity or age, contact details, feedback or inquiries about your use of the Services or Personal Data about possible violations of our Terms of Service (our â\x80\x9cTermsâ\x80\x9d) or other policies.', 'Automatically Collected Personal Data', 'We automatically collect certain Personal Data from you when you use the Services, including internet or other network activity Personal Data such as your IP address, unique device identifiers, and cookies.', 'Device and Network Personal Data. We collect certain device and network connection Personal Data when you access the Services. This Personal Data includes your device model, operating system, IP address, device identifiers and system language. We also collect service-related, diagnostic, and performance Personal Data, including crash reports and performance logs. We automatically assign you a device ID and user ID. Where you log-in from multiple devices, we use Personal Data such as your device ID and user ID to identify your activity across devices to give you a seamless log-in experience and for security purposes.', 'Log Personal Data. We collect Personal Data regarding your use of the Services, such as the features you use and the actions you take.', 'Location Personal Data. We automatically collect Personal Data about your approximate location based on IP address for security reasons, for example to protect your account by detecting unusual login activity.', 'Cookies &amp; Similar Technologies. We may use cookies and similar tracking technologies to operate and provide the Service. For example, we use cookies  for security purposes and to better understand how the Service is used. We will allow you to manage  our use of non-essential cookies where required by law. To learn more about our use of cookies, please see our Cookies Policy.', 'Payment Personal Data. When you use paid services for prepayment, we collect your payment order and transaction Personal Data to provide Services such as order placement, payment, customer service, and after-sales support.', 'To avoid any doubt, Cookies &amp; Similar Technologies and Payment Personal Data are not applicable to DeepSeek App.', 'Personal Data from Other Sources', 'We may receive the Personal Data described in this Privacy Policy from other sources, such as:', 'Log-in, Sign-up, or Linked Services. Where available, if you choose to sign-up or log-in to the Services using a third-party service such as Apple or Google, or link your account to a third-party service, we may collect Personal Data from the third-party service, such as access token.', 'Security Personal Data. We receive Personal Data from our trusted partners, such as security partners, to protect against fraud, abuse, and other security threats to our Services.', 'Public Personal Data. We may obtain publicly available Personal Data via online sources  to train our models and provide Services.', 'The Services are not designed or intended to process sensitive Personal Data (e.g., personal data revealing racial or ethnic origin, religious beliefs, health, sexuality, citizenship, immigration status, genetic or biometric data, personal data of children, precise geolocation or criminal membership). We do not ask for, and you should not provide sensitive Personal Data to the Services, whether about yourself or other individuals.', 'How We Use Your Personal Data', 'We use your Personal Data to operate, provide, develop, and improve the Services, including for the following purposes.', 'To provide, administer and maintain the Services and to enforce our terms, conditions and policies. Such as creating the accounts, deliver a fast and convenient logging-in experience, enabling you to chat with DeepSeek and provide user support.', 'To improve and develop the Services and to train and improve our technology, such as our machine learning models and algorithms. Including by monitoring interactions and usage across your devices, analyzing how people are using it, and training and improving our technology.', 'To communicate with you, including to notify you about changes to the  Services, provide customer support to you and send you other service-related messages.', 'To promote the safety, security, and stability of the  Services, such as by preventing and detecting abuse, fraud, and illegal activity on the Services and by conducting troubleshooting, data analysis, testing, and research.', 'To comply with our legal obligations, or as necessary to perform tasks in the public interest, or to protect the vital interests of our users and other people. This could include providing law enforcement agencies or emergency services with Personal Data in urgent situations to protect health or life.', 'PLEASE NOTE: We do not engage in â\x80\x9cprofilingâ\x80\x9d or otherwise engage in automated processing of Personal Data to make decisions that could have legal or similarly significant impact on you or others.', 'How We Share Your Personal Data', 'Service Providers', 'We engage service providers that help us provide, support, and develop the Services and understand how they are used. We share Personal Data You Provide, Automatically Collected Personal Data, and Personal Data From Other Sources with these service providers as necessary to enable them to provide their services. For example:', 'We use communication service providers to send notifications and/or communications to you.', 'We integrate third-party APIs to provide search services, and we will share your input to provide these services.', 'We use analytics services providers to analyse data.', 'We use support and safety monitoring services providers to assist us in ensuring the safety of our Services.', 'Pursuant to our instructions, these parties will access, process, or store Personal Data only in the course of performing their duties to us.', 'Our Corporate Group', 'The Services are supported by certain entities within our corporate group. These entities process the Personal Data You Provide, Automatically Collected Personal Data, and Personal Data from Other Sources for us, as necessary to provide certain functions, such as storage, content delivery, security, research and development, analytics, customer and technical support.', 'Other Third Parties', 'We share your Personal Data with the following categories of third parties in other limited scenarios as follows:', 'Parties to a Corporate Transaction. Your Personal Data may be disclosed to third parties in connection with a corporate transaction, such as a merger, sale of assets or shares, reorganization, financing, change of control, or acquisition of all or a portion of our business.', 'Law Enforcement and Parties with Other Legal  Rights. We may access, preserve, and share the Personal Data described in â\x80\x9cWhat Personal Data We Collectâ\x80\x9d with law enforcement agencies, public authorities, copyright holders, or other third parties if we have good faith belief that it is necessary to:', 'comply with applicable law, legal process or government requests, as consistent with internationally recognized standards,', 'protect the rights, property, and safety of our users, copyright holders, and others, including protecting life or preventing imminent bodily harm. For example, we may provide Personal Data (such as your IP address) to law enforcement agencies in the event of an emergency where someoneâ\x80\x99s life or safety is at risk,', 'investigate potential violations of and enforce our Terms, Guidelines, or any other applicable terms, policies, or standards, or', 'detect, investigate, prevent, or address misleading activity, copyright infringement, or other illegal activity.', 'With Your Consent', 'Depending on where you live, we may share Personal Data with the proper authorization or to provide the Services you have requested or authorized. For example, if you choose to log in to our Services using a social network account, or share Personal Data from our Services to a social media service, we will share that Personal Data with those third parties services.', 'Third-party content. The Services may contain links to policies, functionality, or content maintained by third parties not controlled by us. We are not responsible for, and make no representations regarding, such policies, functionality, or content or any other practices or operations of such third parties.', 'Your Rights', 'Depending on where you live and subject to exceptions provided under applicable data protection laws, you may have certain rights with respect to your Personal Data.', 'To exercise your rights, you or an authorized agent may submit a request by emailing us at privacy@deepseek.com.', 'After we receive your request, we may verify it by requesting information sufficient to confirm your identity or authority to exercise a right on behalf of someone else.', 'You may also have the right to appeal requests that we deny by emailing privacy@deepseek.com. If your appeal is unsuccessful and depending on where you live, you may have the right to raise a concern or lodge a complaint with the competent authority.', 'We will not discriminate against you for exercising any privacy right you may have.', 'Privacy rights that may be available to you include:', 'the right to know whether and how we process your Personal Data;', 'the right to access your Personal Data;', 'the right to correct inaccuracies in your Personal Data;', 'the right to delete Personal Data youâ\x80\x99ve provided to us, or that weâ\x80\x99ve obtained about you;', 'the right to receive a portable copy of Personal Data youâ\x80\x99ve      provided to us, or that weâ\x80\x99ve obtained about you, to the extent it is available in a digital format, and where technically feasible, in a format that allows you to transfer your Personal Data to another service, and', 'the right to opt-out of the processing of your Personal Data for the purposes of targeted advertising, sale or profiling that could have legal or similarly consequential impact on you.  NOTE WE DO NOT ENGAGE IN TARGETED ADVERTISING, â\x80\x9cSELLâ\x80\x9d PERSONAL DATA OR USE PERSONAL DATA FOR â\x80\x9cPROFILINGâ\x80\x9d OR OTHERWISE ENGAGE IN AUTOMATED PROCESSING OF PERSONAL DATA TO MAKE DECISIONS THAT COULD HAVE LEGAL OR SIMILARLY SIGNIFICANT IMPACT ON YOU OR OTHERS.', 'Your Choices', 'You can control and access some of your Personal Data directly through settings. For example, you can manage your chat history. Should you choose to do so, you may also delete your chat history via your settings.', 'If you choose to delete your account, you will not be able to reactivate your account or retrieve any of the content or Personal Data in connection with your account.', 'A note about accuracy: Services like DeepSeek generate responses by reading a userâ\x80\x99s request and, in response, predicting the words most likely to appear next. In some cases, the words most likely to appear next may not be the most factually accurate.', 'For this reason, you should not rely on the factual accuracy of Output from our models. If you notice that Output contains factually inaccurate Personal Data about you and you would like to request a correction or removal of the Personal Data, you can submit these requests through privacy@deepseek.com and we will consider your request based on applicable law and the technical capabilities of our models.', 'The Security of Your Personal Data', 'The security of your Personal Data is important to us. We maintain commercially reasonable technical, administrative, and physical security measures that are designed to protect your Personal Data from unauthorized access, theft, disclosure, modification, or loss. We regularly review our security measures to consider available new technology and methods. However, no Internet or email transmission is ever fully secure or error free. In particular, emails sent to or from us may not be secure. Therefore, you should take special care in deciding what Personal Data you send to us via the Services or email. In addition, we are not responsible for circumvention of any privacy settings or security measures contained on the Services, or third-party websites.', 'How Long Do We Keep Your Personal Data', 'We retain Personal Data for as long as necessary to provide our Services and for the other purposes set out in this Privacy Policy. We also retain Personal Data when necessary to comply with contractual and legal obligations, when we have a legitimate business interest to do so (such as improving and developing our Services and enhancing their safety, security and stability), and for the exercise or defense of legal claims.', 'The retention periods will be different depending on the amount, type and sensitivity of Personal Data, the purposes for which we use the Personal Data and any legal requirements, etc. For example, when we process your Personal Data to provide you with the Services, we keep this Personal Data for as long as you have an account. This Personal Data includes your account Personal Data, input and payment Personal Data. If you violate any of our terms, policies or guidelines, we may keep your Personal Data as necessary to process the violation.', 'When the Personal Data collected is no longer required by us, we and our service providers will perform the necessary procedures for destroying, deleting, erasing, or converting it into an anonymous form as permitted or required under applicable laws.', 'Where We Store Your Personal Data', "The Personal Data we collect from you may be stored on a server located outside of the country where you live. To provide you with our services, we directly collect, process and store your Personal Data in People's Republic of China .", 'Where required, we will use appropriate safeguards for transferring Personal Data outside of certain countries, including for one or more of the purposes as set out in this Policy, we will do so in accordance with the requirements of applicable data protection laws.', 'Personal Data relating to Children', 'Our Services are not aimed at children, and we do not knowingly process Personal Data from children. If we notice or receive feedback that we have collected any of their Personal Data from a child, we will investigate, and where appropriate, delete the Personal Data to the extent permitted by applicable law. If you believe that we processed Personal Data about or collected from a child, please contact us at privacy@deepseek.com.', 'Privacy Policy Updates', 'We may update this Privacy Policy from time to time as required by law. When we update the Privacy Policy, we will notify you by updating the â\x80\x9cLast Updatedâ\x80\x9d date at the top of the new Privacy Policy, posting the new Privacy Policy, or by providing any other notice required by applicable law. We recommend that you review the Privacy Policy each time you access our Services to stay informed of our privacy practices.', 'Contact Us', 'Questions, comments and requests regarding this policy should be addressed to privacy@deepseek.com or click â\x80\x9cContact usâ\x80\x9d column on the website.', 'Supplemental  Clause - Jurisdiction-Specific', 'European Economic Area (â\x80\x9cEEAâ\x80\x9d), Switzerland, and UK', 'If you are using the Services in the EEA, Switzerland or the UK (the â\x80\x9cEuropean Regionâ\x80\x9d), the following additional terms apply:', 'Legal bases for processing.', 'We use your Personal Data only as permitted by law. Our legal bases for processing your Personal Data described in this Privacy Policy are described in the table below.', 'Please be aware that we collect your Personal Data for the purposes set out in the table above. You may choose not to provide some of the Personal Data fields, but this may affect the Services you are able to use from us.', 'Purpose of processing', 'Personal Data categories', 'Legal bases', 'To provide, administer and maintain the Services and to enforce our terms, conditions and policies. Such as creating the accounts, deliver a fast and convenient logging-in experience, enabling you to chat with DeepSeek and provide user support.', 'Account Personal Data', 'User Input', 'Personal Data When You Contact Us', 'Device and Network Personal Data', 'Log Personal Data', 'Location Personal Data', 'Cookies', 'Performance of a contract with you when we provide and maintain our services. To take steps that you request prior to signing up for an account to use the Platform.', 'Your consent when we ask for it to process your Personal Data for a specific purpose to help you create accounts.', 'Legitimate interests. If you are 14 or older but under the age of 18, with a limited ability to enter into an enforceable contract only, where we may be unable to process your Personal Data on the grounds of contractual necessity, we rely on legitimate interests and use the Personal Data we collect to allow you to access and use the Platform.', 'To improve and develop the Services and to train and improve our technology, such as our machine learning models and algorithms. Including by monitoring interactions and usage across your devices, analyzing how people are using it, and training and improving our technology.', 'Account Personal Data', 'User Input', 'Personal Data When You Contact Us', 'Device and Network Personal Data', 'Log Personal Data', 'Location Personal Data', 'Cookies', 'Our legitimate interests to identify and resolve issues with the Platform and to improve the Platform; and to conduct research and protect Personal Data through aggregation or anonymization, consistent with data minimization and privacy by design principles.', 'Your consent when we ask for it to process your Personal Data for a specific purpose to provide services.', 'To comply with our legal obligations, or as necessary to perform tasks in the public interest, or to protect the vital interests of our users and other people. This could include providing law enforcement agencies or emergency services with Personal Data in urgent situations to protect health or life.', 'Account Personal Data', 'User Input', 'Personal Data When You Contact Us', 'Device and Network Personal Data', 'Log Personal Data', 'Location Personal Data', 'Cookies', 'Compliance with our legal obligations. This includes situations where we have obligations to take measures to ensure the safety of our users or comply with a valid legal request such as an order from law enforcement agencies or courts; and where we have obligations to comply with applicable law or when we protect our or our affiliatesâ\x80\x99, usersâ\x80\x99, or third partiesâ\x80\x99 rights, safety, and property.', 'Our legitimate interests to protect our business, employees and users from illegal activities, inappropriate behavior or violations of terms that would be detrimental, and to disclose and share Personal Data with regulators or other government entities.', 'To communicate with you, including to notify you about changes to the Platform, provide customer support to you and send you other service-related messages.', 'Account Personal Data', 'Personal Data When You Contact Us', 'Location Personal Data', 'Performance of a contract with you when we provide and maintain our services.', 'Your consent when we ask for it to process your Personal Data for a specific purpose to communicate with you.', 'To promote the safety, security, and stability of the Platform, such as by preventing and detecting abuse, fraud, and illegal activity on the Platform and by conducting troubleshooting, data analysis, testing, and research.', 'Account Personal Data', 'User Input', 'Personal Data When You Contact Us', 'Device and Network Personal Data', 'Log Personal Data', 'Location Personal Data', 'Cookies', 'Compliance with our legal obligations when we use your Personal Data to comply with applicable law or when we protect our or our affiliatesâ\x80\x99, usersâ\x80\x99, or third partiesâ\x80\x99 rights, safety, and property.', 'Our legitimate interests to ensure that the Platform is safe and secure.', 'Data storage', 'Please be aware that our servers are located in the Peopleâ\x80\x99s Republic of China. When you access our services, your Personal Data may be processed and stored in our servers in the Peopleâ\x80\x99s Republic of China. This may be a direct provision of your Personal Data to us or a transfer that we or a third-party make.', 'Your rights', 'You have the following rights:', 'The right to request free of charge (i) confirmation of whether we process your Personal Data and (ii) access to a copy of the Personal Data retained;', 'The right to request proper rectification or erasure of your Personal Data or restriction of the processing of your Personal Data;', 'Where processing of your Personal Data is either based on your consent or necessary for the performance of a contract with you and processing is carried out by automated means, the right to receive the Personal Data concerning you in a structured, commonly used and machine-readable format or to have your Personal Data transmitted directly to another company, where technically feasible (data portability);', 'Where the processing of your Personal Data is based on your consent, the right to withdraw your consent at any time (withdrawal will not impact the lawfulness of data processing activities that have taken place before such withdrawal);', 'The right not to be subject to any automatic individual decisions, including profiling, which produces legal effects on you or similarly significantly affects you unless we have your consent, this is authorised by European Union or Member State law or this is necessary for the performance of a contract;', 'The right to object to processing if we are processing your Personal Data on the basis of our legitimate interest unless we can demonstrate compelling legitimate grounds which may override your right. If you object to such processing, we ask you to state the grounds of your objection in order for us to examine the processing of your Personal Data and to balance our legitimate interest in processing and your objection to this processing;', 'You have the right to request the restriction of the processing of your Personal Data where (a) you are challenging the accuracy of the Personal Data, (b) the Personal Data has been unlawfully processed, but you are opposing the deletion of that Personal Data, (c) where you need the Personal Data to be retained for the pursuit or defense of a legal claim, or (d) you have objected to the processing and you are awaiting the outcome of that objection request.', 'The right to object to processing your Personal Data for direct marketing purposes; and', 'The right to lodge complaints before your local data protection authority.', 'Before we can respond to a request to exercise one or more of the rights listed above, you may be required to verify your identity or your account details.', 'Please send an email to us if you would like to exercise any of your rights at privacy@deepseek.com.', 'We value your privacy and your rights as a data subject and have therefore appointed Prighter Group with its local partners as our privacy representative and your point of contact for the following regions:', '-European Union (EU)', '-United Kingdom (UK)', 'If you wish to lodge a data subject request, you may also exercise your rights by contacting us at rep_deepseek@prighter.com, with â\x80\x9cData Subject Requestâ\x80\x9d in the subject line, setting out the details of your rights request.Â\xa0To verify the appointment of Prighter as our representative and for further contact details please visitÂ\xa0https://app.prighter.com/portal/deepseek.', 'powered by', 'Prighter', 'powered by', 'Prighter']</t>
+  </si>
+  <si>
+    <t>['Privacy Policy', 'Skip to contentHome', 'Features', 'Message privatelyStay connectedConnect in groupsExpress yourselfSecure by designShare your everydayFollow channels Do more with Meta AI', 'Privacy', 'Help Center', 'Blog', 'For Business', 'Download', 'Download', 'Terms &amp; Privacy Policy2025 © WhatsApp LLC', 'Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）', 'FeaturesMessage privatelyEnd-to-end encryption and privacy controls.', 'Stay connectedMessage and call for free* around the world.', 'Connect in groupsGroup messaging made easy.', 'Express yourselfSay it with stickers, voice, GIFs and more.', 'Secure by designLayers of protection to help you stay safe.', 'Share your everydayShare photos, videos, voice notes on Status.', 'Follow channelsStay updated on topics you care about.', 'Do More with', 'Meta AIGet help with anything.', 'Privacy', 'Help Center', 'Blog', 'For Business', 'Apps', 'Log inDownload', 'WhatsApp Privacy Policy', 'Effective January 4, 2021archived versions', 'If you live in the European Region, WhatsApp Ireland Limited provides the Services to you under this Terms of Service and Privacy Policy.', 'If you live in the UK, WhatsApp LLC provides the Services to you under this Terms of Service  and Privacy Policy.', 'WhatsApp Legal Info', 'If you live outside the European Region or the UK, WhatsApp LLC ("WhatsApp," "our," "we," or "us") provides our Services to you under this Terms of Service and Privacy Policy.', 'Our Privacy Policy ("Privacy Policy") helps explain our data practices, including the information we process to provide our Services.', 'For example, our Privacy Policy talks about what information we collect and how this affects you. It also explains the steps we take to protect your privacy, like building our Services so delivered messages aren’t stored by us and giving you control over who you communicate with on our Services.', 'We are one of the Meta Companies. You can learn more further below in this Privacy Policy about the ways in which we share information across this family of companies.', 'This Privacy Policy applies to all of our Services unless specified otherwise.', 'Please also read WhatsApp’s Terms of Service ("Terms"), which describe the terms under which you use and we provide our Services.', 'Back to top', 'Key Updates', 'Respect for your privacy is coded into our DNA. Since we started WhatsApp, we’ve built our services with a set of strong privacy principles in mind. In our updated Terms of Service and Privacy Policy you’ll find:', 'Additional Information On How We Handle Your Data. Our updated Terms and Privacy Policy provide more information on how we process your data, and our commitment to privacy. For example, we’ve added more information about more recent product features and functionalities, how we process your data for safety, security, and integrity, and added more direct links to user settings, Help Center articles and how you can manage your information.', 'Better Communication With Businesses. Many businesses rely on WhatsApp to communicate with their customers and clients. We work with businesses that use Meta or third parties to help store and better manage their communications with you on WhatsApp.', 'Making It Easier To Connect. As part of the Meta Companies, WhatsApp partners with Meta to offer experiences and integrations across Meta’s family of apps and products.', 'Back to top', 'Information We Collect', 'WhatsApp must receive or collect some information to operate, provide, improve, understand, customize, support, and market our Services, including when you install, access, or use our Services.', 'The types of information we receive and collect depend on how you use our Services. We require certain information to deliver our Services and without this we will not be able to provide our Services to you. For example, you must provide your mobile phone number to create an account to use our Services.', 'Our Services have optional features which, if used by you, require us to collect additional information to provide such features. You will be notified of such collection, as appropriate. If you choose not to provide the information needed to use a feature, you will be unable to use the feature. For example, you cannot share your location with your contacts if you do not permit us to collect your location data from your device. Permissions can be managed through your Settings menu on both Android and iOS devices.', 'Information You Provide', 'Your Account Information. You must provide your mobile phone number and basic information (including a profile name of your choice) to create a WhatsApp account. If you don’t provide us with this information, you will not be able to create an account to use our Services. You can add other information to your account, such as a profile picture and "about" information.', 'Your Messages. We do not retain your messages in the ordinary course of providing our Services to you. Instead, your messages are stored on your device and not typically stored on our servers. Once your messages are delivered, they are deleted from our servers. The following scenarios describe circumstances where we may store your messages in the course of delivering them: Undelivered Messages. If a message cannot be delivered immediately (for example, if the recipient is offline), we keep it in encrypted form on our servers for up to 30 days as we try to deliver it. If a message is still undelivered after 30 days, we delete it.', 'Media Forwarding. When a user forwards media within a message, we store that media temporarily in encrypted form on our servers to aid in more efficient delivery of additional forwards.', 'We offer end-to-end encryption for our Services. End-to-end encryption means that your messages are encrypted to protect against us and third parties from reading them. Learn more about end-to-end encryption and how businesses communicate with you on WhatsApp.', 'Your Connections. You can use the contact upload feature and provide us, if permitted by applicable laws, with the phone numbers in your address book on a regular basis, including those of users of our Services and your other contacts. If any of your contacts aren’t yet using our Services, we’ll manage this information for you in a way that ensures those contacts cannot be identified by us. Learn more about our contact upload feature here. You can create, join, or get added to groups and broadcast lists, and such groups and lists get associated with your account information. You give your groups a name. You can provide a group profile picture or description.', 'Status Information. You may provide us your status if you choose to include one on your account. Learn how to use status on Android, iPhone, or KaiOS.', 'Transactions And Payments Data. If you use our payments services, or use our Services meant for purchases or other financial transactions, we process additional information about you, including payment account and transaction information. Payment account and transaction information includes information needed to complete the transaction (for example, information about your payment method, shipping details and transaction amount). If you use our payments services available in your country or territory, our privacy practices are described in the applicable payments privacy policy.', 'Customer Support And Other Communications. When you contact us for customer support or otherwise communicate with us, you may provide us with information related to your use of our Services, including copies of your messages, any other information you deem helpful, and how to contact you (e.g., an email address). For example, you may send us an email with information relating to app performance or other issues.', 'Automatically Collected Information', 'Usage And Log Information. We collect information about your activity on our Services, like service-related, diagnostic, and performance information. This includes information about your activity (including how you use our Services, your Services settings, how you interact with others using our Services (including when you interact with a business), and the time, frequency, and duration of your activities and interactions), log files, and diagnostic, crash, website, and performance logs and reports. This also includes information about when you registered to use our Services; the features you use like our messaging, calling, Status, groups (including group name, group picture, group description), payments or business features; profile photo, "about" information; whether you are online, when you last used our Services (your "last seen"); and when you last updated your "about" information.', 'Device And Connection Information. We collect device and connection-specific information when you install, access, or use our Services. This includes information such as hardware model, operating system information, battery level, signal strength, app version, browser information, mobile network, connection information (including phone number, mobile operator or ISP), language and time zone, IP address, device operations information, and identifiers (including identifiers unique to Meta Company Products associated with the same device or account).', 'Location Information. We collect and use precise location information from your device with your permission when you choose to use location-related features, like when you decide to share your location with your contacts or view locations nearby or locations others have shared with you. There are certain settings relating to location-related information which you can find in your device settings or the in-app settings, such as location sharing. Even if you do not use our location-related features, we use IP addresses and other information like phone number area codes to estimate your general location (e.g., city and country). We also use your location information for diagnostics and troubleshooting purposes.', 'Cookies. We use cookies to operate and provide our Services, including to provide our Services that are web-based, improve your experiences, understand how our Services are being used, and customize them. For example, we use cookies to provide our Services for web and desktop and other web-based services. We may also use cookies to understand which of our Help Center articles are most popular and to show you relevant content related to our Services. Additionally, we may use cookies to remember your choices, like your language preferences, to provide a safer experience, and otherwise to customize our Services for you. Learn more about how we use cookies to provide you our Services.', 'Back to top', 'Third-Party Information', 'Information Others Provide About You. We receive information about you from other users. For example, when other users you know use our Services, they may provide your phone number, name, and other information (like information from their mobile address book) just as you may provide theirs. They may also send you messages, send messages to groups to which you belong, or call you. We require each of these users to have lawful rights to collect, use, and share your information before providing any information to us.', 'You should keep in mind that in general any user can capture screenshots of your chats or messages or make recordings of your calls with them and send them to WhatsApp or anyone else, or post them on another platform.', 'User Reports. Just as you can report other users, other users or third parties may also choose to report to us your interactions and your messages with them or others on our Services; for example, to report possible violations of our Terms or policies. When a report is made, we collect information on both the reporting user and reported user. To find out more about what happens when a user report is made, please see Advanced Safety and Security Features.', 'Businesses On WhatsApp. Businesses you interact with using our Services may provide us with information about their interactions with you. We require each of these businesses to act in accordance with applicable law when providing any information to us.', 'When you message with a business on WhatsApp, keep in mind that the content you share may be visible to several people in that business. In addition, some businesses might be working with third-party service providers (which may include Meta) to help manage their communications with their customers. For example, a business may give such third-party service provider access to its communications to send, store, read, manage, or otherwise process them for the business. To understand how a business processes your information, including how it might share your information with third parties or Meta, you should review that business’ privacy policy or contact the business directly.', 'Third-Party Service Providers. We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. For example, we work with them to distribute our apps; provide our technical and physical infrastructure, delivery, and other systems; provide engineering support, cybersecurity support, and operational support; supply location, map, and places information; process payments; help us understand how people use our Services; market our Services; help you connect with businesses using our Services; conduct surveys and research for us; ensure safety, security, and integrity; and help with customer service. These companies may provide us with information about you in certain circumstances; for example, app stores may provide us with reports to help us diagnose and fix service issues.', 'The "How We Work With Other Meta Companies" section below provides more information about how WhatsApp collects and shares information with the other Meta Companies.', 'Third-Party Services. We allow you to use our Services in connection with third-party services and Meta Company Products. If you use our Services with such third-party services or Meta Company Products, we may receive information about you from them; for example, if you use the WhatsApp share button on a news service to share a news article with your WhatsApp contacts, groups, or broadcast lists on our Services, or if you choose to access our Services through a mobile carrier’s or device provider’s promotion of our Services. Please note that when you use third-party services or Meta Company Products, their own terms and privacy policies will govern your use of those services and products.', 'Back to top', 'How We Use Information', "We use information we have (subject to choices you make and applicable law) to operate, provide, improve, understand, customize, support, and market our Services. Here's how:", 'Our Services. We use information we have to operate and provide our Services, including providing customer support; completing purchases or transactions; improving, fixing, and customizing our Services; and connecting our Services with Meta Company Products that you may use. We also use information we have to understand how people use our Services; evaluate and improve our Services; research, develop, and test new services and features; and conduct troubleshooting activities. We also use your information to respond to you when you contact us.', 'Safety, Security, And Integrity. Safety, security, and integrity are an integral part of our Services. We use information we have to verify accounts and activity; combat harmful conduct; protect users against bad experiences and spam; and promote safety, security, and integrity on and off our Services, such as by investigating suspicious activity or violations of our Terms and policies, and to ensure our Services are being used legally. Please see the Law, Our Rights and Protection section below for more information.', 'Communications About Our Services And The Meta Companies. We use information we have to communicate with you about our Services and let you know about our terms, policies, and other important updates. We may provide you marketing for our Services and those of the Meta Companies.', 'No Third-Party Banner Ads. We still do not allow third-party banner ads on our Services. We have no intention to introduce them, but you may see other types of ads in the Updates Tab, home of features like Channels and Status.', 'Business Interactions. We enable you and third parties, like businesses, to communicate and interact with each other using our Services, such as Catalogs for businesses on WhatsApp through which you can browse products and services and place orders. Businesses may send you transaction, appointment, and shipping notifications; product and service updates; and marketing. For example, you may receive flight status information for upcoming travel, a receipt for something you purchased, or a notification when a delivery will be made. Messages you receive from a business could include an offer for something that might interest you. We do not want you to have a spammy experience; as with all of your messages, you can manage these communications, and we will honor the choices you make.', 'Back to top', 'Information You And We Share', 'You share your information as you use and communicate through our Services, and we share your information to help us operate, provide, improve, understand, customize, support, and market our Services.', 'Send Your Information To Those With Whom You Choose To Communicate. You share your information (including messages) as you use and communicate through our Services.', 'Information Associated With Your Account. Your phone number, profile name and photo, "about" information, last seen information, and message receipts are available to anyone who uses our Services, although you can configure your Services settings to manage certain information available to other users, including businesses, with whom you communicate.', 'Your Contacts And Others. Users, including businesses, with whom you communicate can store or reshare your information (including your phone number or messages) with others on and off our Services. You can use your Services settings and the “block” feature in our Services to manage who you communicate with on our Services and certain information you share.', 'Businesses On WhatsApp. We offer specific services to businesses such as providing them with metrics regarding their use of our Services.', 'Third-Party Service Providers. We work with third-party service providers and other Meta Companies to help us operate, provide, improve, understand, customize, support, and market our Services. We work with these companies to support our Services, such as to provide technical infrastructure, delivery and other systems; market our Services; conduct surveys and research for us; protect the safety, security, and integrity of users and others; and assist with customer service. When we share information with third-party service providers and other Meta Companies in this capacity, we require them to use your information on our behalf in accordance with our instructions and terms.', 'Third-Party Services. When you or others use third-party services or other Meta Company Products that are integrated with our Services, those third-party services may receive information about what you or others share with them. For example, if you use a data backup service integrated with our Services (like iCloud or Google Account), they will receive information you share with them, such as your WhatsApp messages. If you interact with a third-party service or another Meta Company Product linked through our Services, such as when you use the in-app player to play content from a third-party platform, information about you, like your IP address and the fact that you are a WhatsApp user, may be provided to such third party or Meta Company Product. Please note that when you use third-party services or other Meta Company Products, their own terms and privacy policies will govern your use of those services and products.', 'Back to top', 'How We Work With Other Meta Companies', 'As part of the Meta Companies, WhatsApp receives information from, and shares information (see here) with, the other Meta Companies. We may use the information we receive from them, and they may use the information we share with them, to help operate, provide, improve, understand, customize, support, and market our Services and their offerings, including the Meta Company Products. This includes:', 'helping improve infrastructure and delivery systems;', 'understanding how our Services or theirs are used;', 'promoting safety, security, and integrity across the Meta Company Products, e.g., securing systems and fighting spam, threats, abuse, or infringement activities;', 'improving their services and your experiences using them, such as making suggestions for you (for example, of friends or group connections, or of interesting content), personalizing features and content, helping you complete purchases and transactions, and showing relevant offers and ads across the Meta Company Products; and', 'providing integrations which enable you to connect your WhatsApp experiences with other Meta Company Products. For example, allowing you to connect your Facebook Pay account to pay for things on WhatsApp or enabling you to chat with your friends on other Meta Company Products, such as Portal, by connecting your WhatsApp account.', 'Learn more about the other Meta Companies and their privacy practices by reviewing their privacy policies.', 'Back to top', 'Assignment, Change Of Control, And Transfer', 'In the event that we are involved in a merger, acquisition, restructuring, bankruptcy, or sale of all or some of our assets, we will share your information with the successor entities or new owners in connection with the transaction in accordance with applicable data protection laws.', 'Back to top', 'Managing And Retaining Your Information', 'You can access or port your information using our in-app Request Account Info feature (available under Settings &gt; Account). For iPhone users, you can learn how to access, manage, and delete your information through our iPhone Help Center articles. For Android users, you can learn how to access, manage, and delete your information through our Android Help Center articles.', 'We store information for as long as necessary for the purposes identified in this Privacy Policy, including to provide our Services or for other legitimate purposes, such as complying with legal obligations, enforcing and preventing violations of our Terms, or protecting or defending our rights, property, and users. The storage periods are determined on a case-by-case basis that depends on factors like the nature of the information, why it is collected and processed, relevant legal or operational retention needs, and legal obligations.', 'If you would like to further manage, change, limit, or delete your information, you can do that through the following tools:', 'Services Settings. You can change your Services settings to manage certain information available to other users. You can manage your contacts, groups, and broadcast lists, or use our “block” feature to manage the users with whom you communicate.', 'Changing Your Mobile Phone Number, Profile Name And Picture, And “About” Information. If you change your mobile phone number, you must update it using our in-app change number feature and transfer your account to your new mobile phone number. You can also change your profile name, profile picture, and "about" information at any time.', 'Deleting Your WhatsApp Account. You can delete your WhatsApp account at any time (including if you want to revoke your consent to our use of your information pursuant to applicable law) using our in-app delete my account feature. When you delete your WhatsApp account, your undelivered messages are deleted from our servers as well as any of your other information we no longer need to operate and provide our Services. Deleting your account will, for example, delete your account info and profile photo, delete you from all WhatsApp groups, and delete your WhatsApp message history. Be mindful that if you only delete WhatsApp from your device without using our in-app delete my account feature, your information will be stored with us for a longer period. Please remember that when you delete your account, it does not affect your information related to the groups you created or the information other users have relating to you, such as their copy of the messages you sent them.', 'You can learn more here about our data deletion and retention practices and about how to delete your account.', 'Back to top', 'Law, Our Rights, And Protection', 'We access, preserve, and share your information described in the "Information We Collect" section of this Privacy Policy above if we have a good-faith belief that it is necessary to: (a) respond pursuant to applicable law or regulations, legal process, or government requests; (b) enforce our Terms and any other applicable terms and policies, including for investigations of potential violations; (c) detect, investigate, prevent, or address fraud and other illegal activity or security, and technical issues; or (d) protect the rights, property, and safety of our users, WhatsApp, the other Meta Companies, or others, including to prevent death or imminent bodily harm.', 'Back to top', 'Our Global Operations', 'WhatsApp shares information globally, both internally within the Meta Companies and externally with our partners and service providers, and with those with whom you communicate around the world, in accordance with this Privacy Policy. Your information may, for example, be transferred or transmitted to, or stored and processed in, the United States; countries or territories where the Meta Companies’ affiliates and partners, or our service providers are located; or any other country or territory globally where our Services are provided outside of where you live for the purposes as described in this Privacy Policy. WhatsApp uses Meta’s global infrastructure and data centers, including in the United States. These transfers are necessary to provide the global Services set forth in our Terms. Please keep in mind that the countries or territories to which your information is transferred may have different privacy laws and protections than what you have in your home country or territory.', 'Back to top', 'Updates To Our Policy', 'We may amend or update our Privacy Policy. We will provide you notice of amendments to this Privacy Policy, as appropriate, and update the “Effective Date” at the top of this Privacy Policy. Please review our Privacy Policy from time to time.', 'Back to top', 'Privacy Rights for United States Residents', 'You can learn more about the consumer privacy rights that may be available to you, by reviewing the United States Regional Privacy Notice here.', 'Back to top', 'Contact Us', 'If you have questions or issues about our Privacy Policy, please contact us.', 'WhatsApp LLC', 'Privacy Policy', '1601 Willow Road', 'Menlo Park, California 94025', 'United States of America', 'Back to top', 'Download', 'Download', 'What we do', 'FeaturesBlogSecurityFor Business', 'Who we are', 'About usCareersBrand CenterPrivacy', 'Use WhatsApp', 'AndroidiPhoneMac/PCWhatsApp Web', 'Need help?', 'Contact UsHelp CenterAppsSecurity Advisories', 'Download', '2025 © WhatsApp LLC', 'Terms &amp; Privacy PolicySitemap', 'Englishالعربيةঅসমীয়াবাংলাEspañolFrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）Englishالعربيةঅসমীয়াবাংলাespañolfrançaisગુજરાતીעבריתहिन्दीBahasa Indonesia日本語ಕನ್ನಡ한국어മലയാളംमराठीनेपालीOriyaਪੰਜਾਬੀPortuguês (Brasil)русскийதமிழ்తెలుగుไทยFilipinoTürkçeاردو繁體中文（香港）']</t>
+  </si>
+  <si>
+    <t>['Adobe Privacy Policy', 'Adobe Privacy Policy', 'Last updated: June 3, 2025', 'The Adobe Privacy Policy describes the privacy practices of Adobe’s Services and Software (as defined in our General Terms of Use) and anywhere we display or reference this policy.', 'If you are a resident of North America, your relationship is with Adobe Inc. (Adobe U.S.) and the laws of California and the United States apply.', 'If you reside outside of North America, your relationship is with Adobe Systems Software Ireland Limited (Adobe Ireland), which is the controller with regard to your personal information collected by Adobe, and the laws of Ireland apply.', 'If the content or information that you store in Adobe Services and Software contains personal information of other individuals, you must be legally permitted to disclose the personal information to Adobe.', 'Summary of Key Points', 'At Adobe we take data privacy seriously. We believe in transparency so you can control your data and make informed choices about how it is used. We are here to support and protect your privacy decisions wherever you use our products and services. Adobe prioritizes your control over the data you store in the cloud in the following ways:', 'This policy explains when we process personal information for our legitimate interests. You can ask us to stop processing this information. Learn more about your rights and how you can exercise them.', 'This policy also explains when we will first get your consent before processing your personal information, including when doing so is required by law.', 'We use your personal information to enable you to register with Adobe and to provide you with our Services and Software, and other products or services that you request. Learn more.', 'We provide interactive features that engage with social media sites, such as Facebook. If you use these features, these sites will send us personal information about you. Learn more.', 'We use cookies and other technologies to track the use of our Services and Software. To learn about opportunities to choose not to allow cookies, click here. If you are using our website in a browser, this information is also available in our Cookies Policy.', 'There are several places within Adobe’s Services and Software that allow you to post comments, upload pictures, or submit content which will be publicly available where you choose to participate in these activities. We also disclose personal information to other companies in the Adobe family and with advertising and sales partners consistent with your choices. We also disclose information with third parties we engage to process personal information on our behalf or when such sharing is required by law, or in certain other situations. Learn more.', 'We provide additional information regarding your location specific privacy rights and choices, available in the Location Specific Privacy Rights and Information Notice.', 'What does this privacy policy cover?', 'What information does Adobe collect about me?', 'How does Adobe use the information it collects about me, and what are the legal bases for these uses?', 'Does Adobe disclose my personal information to others?', "Is my personal information displayed anywhere within Adobe's apps or websites?", 'Is my personal information secure?', 'Where does Adobe store my personal information?', 'Does Adobe transfer my personal information across national borders?', 'What rights do I have regarding my personal information and how can I exercise these?', 'What rights do I have in my location?', 'Withdrawing consent or otherwise objecting to direct marketing', 'How long does Adobe retain my information?', 'Can children use Adobe websites and apps?', 'Will this privacy policy change?', 'Who can I contact with questions or concerns?', 'What does this privacy policy cover?', 'This privacy policy describes how Adobe (also referred to as "we," "us" or "our") will make use of your information in the context of:', 'Adobe websites and web-based services (together referred to as "websites");', 'Services that display or include a reference to this policy;', 'Adobe’s marketing, sales, and advertising practices;', 'The privacy practices of previously acquired companies, unless otherwise noted here.', 'This privacy policy applies when (i) Adobe provides products and services directly to an individual (such as when you buy on Adobe.com or units via resellers) or (ii) Adobe collects usage information from employee users of Adobe enterprise customers (unless otherwise directed by an enterprise customer). In (i) and (ii), we are considered the “data controller” because we determine what personal data will be collected and how it will be handled, as detailed and allowed per this policy.', 'In contrast, Adobe is considered the “data processor” and not the data controller when enterprise customers such as businesses or educational institutions, use Adobe products and services (e.g., Adobe Experience Cloud) to support their own provision of products and services to individuals since Adobe acts at the direction of these enterprise customers regarding any collection or processing of data on their behalf. This privacy policy does not apply to the data Adobe enterprise customers may collect from individuals or their uses of that data. For questions about any specific organization’s data practices in these scenarios, please contact the organization directly. You can also find more privacy information about Adobe Experience Cloud here.', 'In some cases, different or additional privacy and data protection policies and notices apply.', 'Some of our products and services have different or extra privacy details to consider. For example, when we acquire a company, their privacy policy and notices apply until such time as Adobe’s privacy practices are implemented. Also, certain products and locations have additional privacy policies and notices that may apply. You can find these, along with other relevant policies, on our Additional Privacy Policies page within the Adobe Privacy Center.', 'Please also see the Adobe Terms of Use and any additional Terms of Use or Consumer Product License Agreements that may apply to the Services and Software you are using.', 'anchor', 'cover', 'What information does Adobe collect about me?', 'Adobe ID, registration, and customer support', 'When you register to use an Adobe Service, create an Adobe ID, purchase a license to our Services and Software, or contact us for support or other offerings, Adobe collects information that identifies you. This includes:', 'Identifiers and contact information, such as:', 'Name;', 'Email address;', 'Telephone number;', 'Postal or Physical Address;', 'Country;', 'Commercial and transaction information, such as:', "Payment/billing information (where an app or website is 'paid for');", 'Licenses purchased;', 'Eligibility information (e.g., student or teacher identification for student and teacher editions of apps);', 'Content of and information provided through customer support and other communications (e.g., recorded customer and technical support calls and stored content of your correspondence with us via our website, chat features, phone and video calls, emails, and other channels);', 'Types of Services and Software of interest.', 'Professional, education or other demographic information, such as:', 'Date of birth;', 'Company or school name;', 'Title;', 'Occupation;', 'Job function;', 'Expertise;', 'Company details, such as the size, industry, and other information about the company where a user may work (when the user has provided the company name);', 'Analytics or other electronic network activity, such as:', 'IP address;', 'Browser;', 'Mobile Device ID;', 'Browser extensions connected to your Adobe accounts.', 'Inferred and Third-Party Data', 'To help keep our databases current and to provide you the most relevant content and experiences, we may infer or generate information based on the information we collect or combine information provided by you with information from third party sources, in accordance with applicable law. For example, (i) your preferences (e.g., based on your earlier purchases or engagement with our products and services) or (ii) the size, industry, and other information about the company you work for (where you have provided company name) will be obtained from sources including, professional networking sites and information service providers. We may also infer, generate, or collect and receive information from third parties, including partners, data brokers, service providers, aggregators, and from publicly accessible sources, for purposes that include to detect, prevent, or otherwise address fraudulent, deceptive or illegal activity, misuse of our Services and Software, security or technical issues, as well as to protect against harm to the rights, property or safety of Adobe and our employees, our users, children, or the public.', 'Adobe Services and Software', 'We collect information you provide to us (e.g., when you access and use our Services and Software) or permit us to collect (e.g., as part of a third-party integration). We also collect or generate information about how you access and use our Services and Software, including when you use a desktop or mobile app feature that takes you online (such as a photo syncing feature). Depending on the Services and Software you access and use, this information may be associated with your device or browser or it may be associated with your Adobe account or content. It includes:', 'Analytics or other electronic network activity, such as:', 'IP address;', 'Browser and device information, including browser and device type, settings, unique identifiers, version, language settings, and configuration;', 'Webpage that led you to an Adobe website;', 'Search terms entered into a search engine which led you to an Adobe website;', 'Use and navigation of Services and Software, including how you interact with Adobe websites (collected through cookies and similar technologies, or by Adobe servers when you are logged into the app or website);', 'Analysis of your use and navigation of the Services and Software;', 'Analysis of your content subject to your opt-out and consent rights.', 'Professional, Education or other demographic information, such as:', 'Profile information (e.g., account profile, public profile, Behance profile).', 'Commercial and transaction information, such as:', 'Content that includes personal information which is sent or received using an online feature of Adobe Services and Software, or which is stored on Adobe servers, such as documents, photos, videos, activity logs, direct feedback from you, metadata about your content, user generated requests such as search terms, prompts (e.g., text, images, videos, audio, etc.), inquiries, feedback, and other information you may disclose when you access or use our Services and Software as well as any information the Services and Software returns in response to such requests.', 'Sensitive personal information, such as:', "Precise geolocation (e.g., when you add location data about where a picture was taken using your camera or phone's GPS feature);", 'Information about your specific accessibility requirements or preferences, such as mobility, visual, auditory, dietary restrictions, or other accommodations (e.g., when you visit our offices);', 'Biometric identifiers or information defined under United States laws or other applicable laws (e.g., faceprints and voiceprints, etc.);', 'Where required by law, we will seek any required permissions from you prior to any such collection. See the “Adobe acting on your behalf” and “How we analyze your content to deliver features requested by you” sections below for more information.', 'The following links provide further information on:', 'Adobe product improvement program;', 'Usage Data FAQ: Creative Cloud and Document Cloud Apps', 'Adobe Genuine Software', 'Your privacy choices regarding how we use this information;', 'Adobe products and services licensed by educational institutions;', 'How Adobe uses cookies and similar technologies; and', 'How Adobe analyzes your content using techniques such as machine learning in order to improve our Services and Software, and how to opt out of this.', 'Adobe Software activation and automatic updates', 'Your device (manufacturer, model, IP address);', 'The Adobe Software (version, date of activation, successful and unsuccessful updates);', 'Your product serial number (e.g., where this is required before you can start using your product).', 'You can learn more about app activation here.', 'Adobe emails', 'Emails we send you may include a technology (called a web beacon) that collects Analytics or other electronic network activity, such as whether you have received or opened the email, or clicked a link in the email. If you do not want us to collect this information, you can opt out of receiving Adobe marketing emails.', 'Adobe social networking pages and social sign-on services', 'You can sign into some Adobe Services and Software using a social networking account, such as a Facebook account. Where you give appropriate permissions, we will receive contact and identifier information about you from your social networking account, such as name, country, and basic demographic information.', 'Adobe has its own pages on many social networking sites (for example, the Adobe® Photoshop® team’s Facebook page). We will collect information which you have made publicly available on your social networking account, such as name and interests in our products and services, when you interact with our social networking pages. The social networking sites may provide statistics and insights to Adobe which help us understand the types of actions that people take on our pages. Where applicable, Adobe and the social media site(s) have entered into an arrangement which determines our respective responsibilities.', 'You can learn more about Adobe’s practices with respect to social networking pages and account sign-on services here.', 'Adobe acting on your behalf', 'In certain instances, Adobe is acting only on your behalf for personal information collected and processed by our services (for example, for the address book contacts shared by users when entering recipient information). In such cases, Adobe is acting only on your instructions in order to facilitate the Service requested by you, and you will be responsible for the information shared. In these instances, we will inform you through in-app notifications or other in-time communications. If you submit any information relating to other people to us or to our service providers in connection with your use of Adobe apps or websites, you represent that you have the authority to do so and to permit us to use the information in accordance with this policy.', 'How we process your content to deliver features requested by you', 'Adobe offers certain features that let you edit and organize your photographs, videos, and other types of content using characteristics like face and voice (e.g., you can group similar faces, places, and image characteristics within your collection), and such characteristics may be considered biometric identifiers or biometric information under certain US laws or other applicable privacy laws. When you choose to use these features, Adobe is acting only on your instructions in order to facilitate the service requested by you. These features are off by default and, should you choose to enable them, you can always disable these features. Where we process biometric identifiers or biometric information to deliver a feature requested by you, we delete this information once you turn off the feature, unless otherwise specified in the Software or Services.', 'Visiting our Physical Offices', 'When you visit an Adobe office, we will collect Identifiers and Contact information such as your name, company name, and email address; and Audio, electronic, visual, or similar information including facial images and voice information such as from CCTV video or voice recordings and photos.', 'anchor', 'info-collect', 'How does Adobe use the information it collects about you, and what are the legal bases for these uses?', 'Adobe uses the information we collect about you for the following purposes:', 'To fulfill a contract, or take steps linked to a contract: this is relevant where you register to use an Adobe app or website (whether paid, or as a free trial). This includes:', 'Providing you with the Adobe Services and Software for which you have registered, and any other services or products that you have requested;', 'Administering product or platform skill/knowledge courses and other content, including testing and certifications (as applicable);', 'Verifying your identity;', 'Processing payments;', 'Sending you necessary communications (for example, related to payments or expiration of your subscription); and', 'Providing customer service or support.', 'As required by Adobe to conduct our business and pursue our legitimate interests:', 'Analyzing your content and its characteristics using automated techniques, in the following circumstances:', 'Operational Use. To enable the normal running of the Services and Software, our Services and Software will access your content stored locally on your device (“Local Content”) and content that you have uploaded to our servers or create using our cloud-based Services (“Cloud Content”).', 'Content Analytics with Cloud Content. Subject to your opt-out rights, including those described here, we may perform analytics with Cloud Content to help us understand how our users are using our Services and Software to allow us to improve your Services and Software experience, provide recommendations to you, and customize your experience. Insights from Content Analytics may be used to inform our marketing to you, subject to your opt-out rights regarding our marketing.', 'Analyzing your cloud content and its characteristics using automated techniques or with human review, in the following circumstances:', 'Illegal and Abusive Cloud Content. Cloud Content may be automatically scanned to ensure we are not hosting illegal or abusive content, like Child Sexual Abuse Material. Human review may occur when your Cloud Content is flagged or reported as illegal or abusive.', 'Public and Shared Cloud Content. All public and shared Cloud Content is subject to review for intellectual property issues and safety issues (for example, violence and nudity). If you choose to share your Cloud Content with others using our Software and Services, we may automatically review this shared Cloud Content to flag abusive behavior (such as spam or phishing). When you make your Cloud Content publicly available, additional human review may occur.', 'Providing you with the Adobe Services and Software for which you have registered and any other products and services you have requested;', 'Analyzing your use and measuring effectiveness of our Services and Software to better understand how they are being used so we can improve them and engage and retain users;', 'Sending you information about Adobe products and services, special offers and similar information, and sharing your information with third parties for their own marketing purposes, where your consent is not required;', 'Analyzing your use and navigation of our Services and Software, your profile information, your interaction with our communications (excluding your content), to:', 'Detect and prevent fraudulent, deceptive, or, illegal activity, or misuse of our Services and Software;', 'Improve our Services and Software, and the user experience, subject to your opt-out and consent rights, including those described here;', 'Tailor and customize the Services and Software through marketing communications (learn more);', 'Diagnosing problems in our Services and Software;', 'Conducting surveys and market research about our customers, their interests, the effectiveness of our marketing campaigns, and customer satisfaction (unless we need consent to undertake such surveys, in which case we will only do this with your permission);', 'Investigating and responding to any comments or complaints that you may send us;', 'Checking the validity of the sort code, account number, and card number you submit if you use a credit or debit card for payment, in order to prevent payment fraud or other illegal or deceptive payment practices (we use third parties for this – see “Does Adobe disclose my personal information to others?” below);', 'Sharing account information registered under a business email address with employers for account migration purposes;', 'Combining with other data we may have about how you interacted with our products and services when logged out or logged in, in order to provide a more seamless experience, show you the most relevant content and services, and for marketing purposes, with your consent where required;', "If we merge with or are acquired by another company, sell an Adobe website, app, or business unit, or if all or a substantial portion of our assets are acquired by another company, your information will likely be disclosed to the prospective purchaser, our advisers and any other prospective purchaser's advisers and will be one of the assets that is transferred to the new owner;", 'In connection with legal claims, compliance, regulatory and investigative purposes as necessary (including disclosure of information in connection with government agency requests, legal process or litigation).', 'Where we process your information based on legitimate interests, you can object to this processing in certain circumstances. In such cases, we will cease processing information unless we have compelling legitimate grounds to continue processing or where it is needed for legal reasons.', 'If legitimate interest is not an available legal basis in a particular jurisdiction, we will engage in the processing activities described above on a legal basis that is available in that particular jurisdiction.', 'Where required, when you give Adobe your consent or otherwise consistent with your choices:', 'Sending you information about Adobe products and services, special offers and similar information, and sharing your information with third parties for their own marketing purposes;', 'Placing cookies and using similar technologies in our Services and Software and in email communications, in accordance with our Cookies Policy and the information provided to you when those technologies are used;', 'Accessing information stored on your device for the following operational uses:', 'Information relating to your use of, and engagement with, Services and Software related to crash reports in order to fix the underlying problem causing the crash;', 'Information which you allow us to receive through device-based settings (e.g., photos, location and camera) in order to provide certain functionality within our Services and Software;', 'Analyzing your use and navigation of the Services and Software or your content and its characteristics using automated techniques or human review in order to:', 'Detect and prevent fraudulent, deceptive, or illegal activity or misuse of the Services and Software;', 'Improve our services and the user experience, such as through the Adobe Product Improvement Program as described here;', 'Respond to your request (e.g., customer service).', 'Allowing you to participate in sweepstakes, contests, and similar promotions and to administer these activities.', 'On other occasions where we ask you for consent, we will use the information for the purposes which we explain at that time. Where we rely on consent to process information, you can withdraw your consent to such activities at any time.', 'For legal reasons:', 'Responding to requests by government or law enforcement authorities conducting an investigation.', 'Using or disclosing information as reasonably necessary to detect, prevent, or otherwise address fraud, security, potential deceptive or illegal activities, misuse of Services and Software, or technical issues and software piracy (e.g., to confirm that software is genuine and properly licensed), helping to protect you as well as Adobe.', 'Where this processing and these disclosures are not strictly required by law, Adobe may rely on its legitimate interests, where available, and those of third parties described above.', 'anchor', 'info-use', 'Does Adobe disclose my personal information to others?', 'Disclosing to other Data Controllers', 'We will disclose your personal information within the Adobe family of companies for the purposes identified above (see a list of Adobe entities and our acquired companies).', 'We will also disclose your personal information with other third-party data controllers with your consent (where necessary) or to provide any product or service you have requested (e.g., third-party integrations). The types of third parties your information may be disclosed to include: our resellers and other sales and advertising partners, retailers, advertisers, ad agencies, advertising networks and platforms, information service providers, fraud monitoring and prevention providers, and publishers. In some cases, in order to show you more relevant ads, we disclose with social media platforms and other advertising partners, information about actions you take on our websites and apps, such as which pages you visit and which ads you saw. These parties may be joint controllers for this processing. More information is available here.', "Third-party data controllers may also use Adobe products and services to collect and process your personal information. If you are using an email address that is associated with a business domain (e.g., yourname@businessname.com) to access Adobe's Services and Software, or if you were invited to use the Services and Software by a business, we may provide your personal information to that business.", 'Disclosing for Fraud Prevention, Safety and Security Purposes', 'We will disclose personal information to companies that help us run our business to detect, prevent, or otherwise address fraud, deception, illegal activity, misuse of Adobe Services and Software, and security or technical issues.', 'Additionally, we will disclose personal information to companies, organizations, government authorities, or individuals outside of Adobe if we have a good-faith belief that access, use, preservation or disclosure of the information is reasonably necessary to detect, prevent, or protect against such fraudulent, deceptive, or illegal activity, misuse of our Services and Software, or security or technical issues, or where it is reasonably necessary to protect from harm the rights, property or safety of Adobe and our employees, our users, children, or the public as required or permitted by law.', 'Disclosing to Data Processors', 'We will also disclose your personal information to companies that help us run our business by processing personal information on behalf of Adobe for the purposes identified above. Such companies (including those that may record or store communications) include providers of customer support services, chatbots, session replay partners who provide services which recreate a web or app session showing meaningful insight into a visitor’s experience, providers of analytics technologies that record and analyze your interaction with our websites to help us improve your experience, providers of artificial intelligence technologies that record and analyze your content or communications, payment processing services, fraud monitoring and prevention, detecting and preventing deceptive or illegal activity or misuse of our Services and Software, email, social media, and other marketing platforms and service providers, and hosting services. We require these companies to protect your personal information consistent with this Privacy Policy.', 'Other Information Disclosure', 'Adobe may also disclose your personal information:', 'When you agree to the disclosure;', 'When we have a good faith belief that we are required to provide information in response to a subpoena, court order, or other applicable law or legal process (learn more), or to respond to an emergency involving the danger of death or serious bodily harm;', "If we merge with or are acquired by another company, sell an Adobe website, app, or business unit, or if all or a substantial portion of our assets are acquired by another company, your information will likely be disclosed to the prospective purchaser, our advisers and any prospective purchaser's advisers and will be one of the assets that is transferred to the new owner.", 'anchor', 'info-share', 'Is my personal information displayed anywhere on Adobe’s websites or applications?', 'There are several places within Adobe’s Services and Software that allow you to post comments, upload pictures, participate in message boards or chats, engage with blogs, share technical information, or submit other content for others to see. Sometimes you can limit who can see what you share, but there are some places where what you share can be seen by the general public or other users of the service. Such information can appear in search engine results or through other publicly available platforms and can be “crawled” or searched by third parties. For example, when users post content on message boards, online chats, blogs, and Community Forums, the information posted by the user will become public. Some online content may remain accessible publicly even after Adobe fulfils a request to delete the poster’s personal information.', 'Please be careful when you share your personal information. Do not share anything you wouldn’t want publicly known unless you are sure you are posting it within an app or website that allows you to control who sees what you post. Please note that when you post messages on certain user forums on our websites and app, your email address or name and/or profile photo may be included and displayed with your message. You can find more information about managing your public profile here. To remove content you have shared on our Services and Software, please use the same feature you used to share the content. If another user invites you to participate in shared viewing, editing, or commenting of content, you may be able to delete your contributions, but usually the user who invited you has full control. If you have questions or concerns about this, please contact us.', 'anchor', 'websites-applications', 'Is my personal information secure?', 'We work hard to protect your personal information. We employ administrative, technical, and physical security controls where appropriate, such as encryption, 2-step verification, and appropriate contractual confidentiality obligations for employees and contractors.', 'anchor', 'info-secure', 'Where does Adobe store my personal information?', 'Your personal information and files are stored on Adobe’s servers and the servers of companies we engage to provide services to us.', 'anchor', 'info-store', 'Does Adobe transfer my personal information across national borders?', 'The main locations where we process your personal information are the US and India, but we also transfer personal information to all other countries in which Adobe or its affiliates, providers, and partners operate. We carry out these transfers in compliance with applicable laws – for example, by putting data transfer agreements in place to help protect your personal information.', 'Adobe complies with the EU-U.S., UK Extension to the EU-U.S., and Swiss-U.S. Data Privacy Framework. To learn more, see our Cross Border Data Transfers page, or visit the U.S. Department of Commerce’s Data Privacy Framework website.', 'As set out above Adobe uses a limited number of third-party service providers to assist us in providing our services to our users and business customers. These third parties may access, process, or store personal data in the course of providing their services. Adobe maintains contracts with these third parties restricting their access, use and disclosure of personal data in compliance with our Data Privacy Framework obligations, including the onward transfer provisions, and Adobe remains liable if they fail to meet those obligations and Adobe is responsible for the event giving rise to the damage).', 'The information above applies to Adobe users who are consumers. More information is available for our business customers that want to learn more about Cross-border data transfers.', 'anchor', 'info-transfer', 'What rights do I have regarding my personal informatio</t>
+  </si>
+  <si>
+    <t>['Privacy Policy | Snapchat Privacy', 'PrivacyPrivacyPrivacy Center', 'Privacy Principles', 'Privacy by Product', 'Privacy Policy', 'Teens on Snapchat', 'Snap and Ads', 'Privacy Through Security', 'Privacy Policy', 'Effective: April 7, 2025', 'Welcome to Snap Inc.’s Privacy Policy. This Policy explains how we collect and use your data and how you can control your information. Looking for a quick summary on our privacy practices? Check out this page or this video. If you’re looking for specific product privacy information, for example, how we process your Chats and Snaps, take a look at our Privacy by Product page. In addition to these documents, we also show in-app notices that provide you more information about our products and services. And if you’re a Spectacles user you can learn more on how we collect and use your data in the Spectacles Supplemental Privacy Policy.', 'Transparency is one of our core values at Snap. We believe there shouldn’t be any surprises about the data we collect and how we use it — that’s why we’re upfront with how we process it. For example, we process your information to provide you a more personalized experience, including to show you content and information that is most relevant to your experience, as well as more relevant advertisements. Understanding your interests and preferences help us provide a better product experience.', 'Furthermore, we believe a personalized experience should not come at the expense of your privacy. Just like in real life, there are some moments you want to share privately with your close friends, and others that you want to share publicly. That’s why from day one our philosophy has been to delete content by default and to give Snapchatters control by providing the tools that allow them to decide what happens with their content, like who to share it with or when to save it.', 'This Policy covers our Snapchat app as well as our other products, services, and features, such as Bitmoji, Spectacles, and our advertising and commerce initiatives. When you read "Services" in this Policy, we’re talking about all of them. Also, if you see us refer to our "Terms," we mean the Terms of Service that you agree to when you sign up for our Services. Finally, if you see the term "Snapchatter" we are often using that as shorthand for any user of our Services.', 'Let’s get started with the controls you have over your information:', 'Control Over Your Information', 'Control over your information and settings is a core part of Snapchat experience. You can access, update, and delete your information, decide who can contact you, and download your data from within the Snapchat app. Below, we give you more details on the types of settings that are available, link out to our data download tool, and provide instructions on how to delete data or your account.', 'We want you to be in control of your information, so we provide you with a range of tools, including:', 'Access and update your information. You can access and edit most of your basic account information right in our Services. Just navigate to your settings and you will see the options available to you.', 'Delete your information. If you want to delete your account, learn how here. You can also delete some information within our Services, like content you’ve saved to Memories, content you’ve shared with My AI, Spotlight submissions, and more.', 'Control who can see your content. We’ve built a number of tools that let you choose who you share your content with. In some cases you may want to share content with your friends, and in other instances you may want to share it with the public. To learn more, go here.', 'Control who can contact you. Snapchat is intended for close friends and family, that’s why we’ve built controls that help you decide who can contact you. If you receive unwanted communications, you can always block and report that person. Go here to learn more.', 'Change your permissions. In most cases, you can change your permissions at any time. For example,  by default you are findable to others through your phone number and/or email address that you provided. If you no longer want to be findable, you can always change your settings. Or if you provided access to your phone or third party platform contacts to make friending easier, you can change that later on in your app settings. Of course, if you do that, certain features and Services, like finding friends in your contact book, won’t work.', 'Opt out of promotional messages. You have the option to opt out or unsubscribe from promotional emails and messages sent by SMS or other messaging platforms. To do so, just follow the instructions in the message like an unsubscribe link or similar functionality.', 'Download your data. You can make a request in our Download My Data tool to export a copy of your Snapchat information.', 'Object to processing. Depending on where you live and the particular data we are processing, you may have the right to object to our processing of that information. This gets a bit technical, so we’ve explained it in more detail here.', 'Set advertising preferences. We try to show you ads that we think will be relevant to your interests, but if you’d like to have a less personalized experience, you can change your advertising settings in the Snapchat app. Learn more here.', 'Tracking. If you use an iPhone with iOS 14.5 or above, some specific requirements apply, which we’ve specified here.', 'Information We Collect', 'This section provides you with details on what information we collect: what you provide to us, what we collect when you use Snapchat, and information we receive from other companies or apps you’ve connected to your Snapchat account. Sometimes, we may also collect additional information, with your permission.', 'When you use our Services, such as Snapchat, we collect information you provide to us, generate information when you use our Services, and in some cases receive data from others. Let’s break these down in more detail.', 'Information You Provide', 'Many of our Services require you to set up an account. To do this, we ask you to provide us with account details (information about you, like your name, username, email address, birthday, and phone number). When you set up your profile, you’ll also provide us with profile details (like your Bitmoji and profile picture). If you use our commerce products to buy something, like those latest sneakers, we may ask you for payment and related information (like your physical address, so we can ship the product to you, payment information, so we can process the payment, and transaction history).', 'Of course, you’ll also provide us with information you send through or save within our Services, including content and information about that content, and content you share and generate with our AI Features (content, or “Inputs,” including text, images, video, audio, precise location, and engagement, used to generate content and responses, or “Outputs”). We consider some of this information to be private content and communications (like Snaps and Chats with friends, voice and video calls, and content that is saved in My Eyes Only). Or content you share with a particular audience like private &amp; friend stories (My Story set to Friends, Private Stories). On the other end of the spectrum, some of the information you send through or save within our Services may be public content that is accessible to everyone (such as Public Story content, including My Story set to Everyone, Shared Stories, and Community Stories, Spotlight or Snap Map submissions, and Public Profile information). Keep in mind that Snapchatters who view your Snaps, Chats, and any other content, can always screenshot that content, save it, or copy it outside the Snapchat app. So please don’t send messages or share content that you wouldn’t want someone to save or share.', 'Lastly, when you contact Support (content and communications shared with Support) or our Safety team, or communicate with us in any other way, including through our research efforts (like responses to surveys, consumer panels, or other research questions) we’ll collect whatever information you provide or that we need to resolve your question.', 'Information We Generate When You Use Our Services', 'When you use our Services, we collect information about which of those Services you’ve used and how you’ve used them. This helps us better understand the way our community uses our Services so that we can make improvements.', 'This includes usage information (information about how you interact with our Services — for example, which Lenses you view and apply, your premium subscriptions, Stories you watch, and how often you interact with other Snapchatters) and content information (information about content you create or provide, your engagement with the camera and creative tools, your interactions with My AI, and metadata — for example, information about the content itself like the date and time it was posted and who viewed it). Content information includes information based on the content of the image, video, or audio — so if you post a Spotlight of a basketball game, we may use that information to show you more content on Spotlight about basketball.', 'This also includes device information (such as your hardware or software, operating system, device memory, advertising identifiers, apps installed, browser type, information from device sensors that measure the motion of your device or compasses and microphones, including whether you have headphones connected, and information about your wireless and mobile connections), location information (IP address), information collected by cookies and similar technologies, depending on your settings, (cookies, pixels (small graphic data that recognize user activity, such as if and how often a user has visited a website), web storage, unique advertising identifiers), and log information (such as details about how you’ve used our Services, access times, pages viewed, IP address, and unique identifiers like cookies).', 'If you’ve explicitly granted device-level permissions, device information may also include information about your device phonebook (contacts and related information), images and other information from your device’s camera, photos, and microphone (like the ability to take photos, videos, view stored photos and videos, and access the microphone to record audio while recording video), and location information (precise location through methods like GPS signals).', 'Data We Receive From Others', 'The last category of data we collect is information about you that we may receive from others, such as other users, our affiliates, and third parties. This includes linked third-party service data (information we get when you link your Snapchat account to another service), data from advertisers (information from advertisers, app developers, publishers, and other third parties to help target or measure the performance of ads), contact info from other Snapchatters or third parties (if another Snapchatter uploads their contact list which includes your information, we may combine that with other information we have about you to better understand who you may want to communicate with. Or, if you provide us with your contact information, we may use that to determine if we can communicate with you in other ways, like SMS, email, or other messaging services), and data relating to potential violations of our Terms (we may receive information from third parties, including website publishers, social network providers, law enforcement, and others, about potential violators of our Terms of Service and Community Guidelines).', 'Other Information, With Your Permission', 'Additionally, there may be instances when you interact with our Services that we will ask your permission to collect additional information. For example, before accessing your device’s camera roll or your device or third party contact book.', 'How We Use Information', 'This section explains how we use the information we collect. Among other things, we use the information we collect to provide you with personalized products and Services that we work hard to build and improve. Below, we walk through each purpose for which we use information in detail. If you’d like to see a mapping of the data we collect with the purposes for which we collect it, we have a table here.', 'Keep Things Up &amp; Running (i.e., operate, deliver, and maintain our Services)', 'We use the information we collect in order to operate, deliver, and maintain our Services. For example, by delivering a Snap you want to send to a friend or, if you share your location on Snap Map, to show you suggestions like places you might like in your neighborhood, content others have posted to the Map, or your friends if they’re sharing their location with you. We also use some of your information to help keep our products up to date, for example to make sure that our Services work with the latest operating systems and devices.', 'Personalize Your Experience &amp; Give Context', "We offer personalized Services to Snapchatters. One of the ways we do this is by showing you content that is relevant to you or we think you may enjoy based on the information you share with us. To do so, we use information about you across different areas of the Services in order to add context to your Snapchat experience. For example, we automatically tag content with labels based on the content, your location, or the time of day. So if there's a dog in the photo, it may be searchable in Memories by the term “dog,” show up on the Map at the location where you created the Memory, and inform us that you’re into dogs so we can surface you fun dog videos and dog food ads in other parts of our Services, such as Spotlight.", 'Personalization can also help with suggesting friends or recommending a new friend to send a Snap to based on who you Snap with the most. We may show recommended places on the Snap Map, generate stickers, or even generate Snaps and other content using AI, infer your interests based on your content or activity, or customize the content we show you, including ads. For example, if you watch barista content on Spotlight, talk to My AI about your favorite espresso machine, or save a lot of coffee-related Snaps in your Memories, we may highlight coffee shops on the Snap Map when you visit a new city or show you content about coffee that you may find interesting or relevant. Or, if you interact with a lot of music venues we may use that to show you ads for upcoming shows in town. Personalization also includes tailoring your experience based on who you interact with most and what your friends are doing, including showing you content your friends create, like, or enjoy on Spotlight or Place recommendations that are popular with your friends.', 'Our goal is to continuously provide you with more relevant and interesting content.', 'For example, if you watch a lot of sports content, but skip content with hair and makeup tips, our recommendation algorithms will prioritize sports, but not those makeup tips. You can learn more about how we understand Snapchatter preferences and rank and moderate content here.', 'We believe it is critical to also balance the benefits of personalization with our Snapchatters’ expectations of privacy. For example, we may automatically tag the Snaps you save to Memories based on the content within it (e.g., the Snap contained a dog), and then use that tag to personalize your experience, make recommendations, or show you ads (such as showing you Spotlight Snaps containing dogs). We do not use the private content and communications you send to your friends to personalize your experience, make recommendations, or show you ads.', 'Provide Relevant Ads', 'Another way we provide a personalized Service is through the ads we show. We use your interests and preferences from the information we’ve collected to personalize, target, and measure ads. We think ads are best when they’re relevant. That’s why we try to select the right ads and show them to you at the right time. For example, if you’ve interacted with ads for video games, we will infer that you like video games, and show you similar ads, but those won’t be the only ads you see. Similar to our content strategy, we try to ensure you receive a variety of ads. We also use your information to avoid showing you ads you probably won’t be interested in. For example, if a ticketing site tells us you’ve previously bought tickets for a movie — we can stop showing you ads for it. You can learn about the different types of advertising and your choices about which ads you receive here.', 'You can learn more about how we collect, use, and share your information for advertising purposes here.', 'A note about information collected by cookies and other technologies: we may use these technologies to collect information when you interact with Services we offer through one of our partners. For example, we may use information collected on an advertiser’s website to show you more relevant ads. Most web browsers are set to accept cookies by default. If you prefer, you can usually remove or reject browser cookies through the settings on your browser or device. Keep in mind, though, that removing or rejecting cookies could affect the availability and functionality of our Services. To learn more about how we and our partners use cookies on our Services and your choices, please check out our Cookie Policy.', 'Develop &amp; Improve Features, Algorithms &amp; Machine Learning Models', 'Our teams are constantly coming up with new ideas for features and ways to improve our Services. In order to do this, we also develop and improve the algorithms and machine learning models (an expression of an algorithm that combs through significant amounts of data to find patterns or make predictions) that make our features and Services work, including through generative AI features (artificial intelligence capable of generating text, images, or other media, using generative models. Generative AI models learn the patterns and structure of their input training data and then generate new data that has similar characteristics). We use algorithms and machine learning models for personalization, advertising, safety and security, fairness and inclusivity, augmented reality, and to prevent abuse or other Terms of Service violations. For example, our algorithms and machine learning models take into account the conversations Snapchatters are having with My AI to improve the responses from My AI.', 'Your information can help us decide what kind of improvements we should make, but we are always focused on privacy — and we don’t want to use more of your personal information than necessary to develop our features and models.', 'Analytics', 'In order to understand what to build or how to improve our Services, we need to understand trends and demand for our features. For example, we monitor metadata and trends about Group Chat use to help decide whether we should change parts of the feature, like the maximum size of a Group. Studying data from Snapchatters can help us see trends in the ways that people use the Services. This helps inspire us to improve Snapchat on a larger scale. We perform analytics in order to identify, monitor, and analyze trends and usage. Based on this information, we will, among other things, create information about our users to help us understand demand.', 'Research', 'We conduct research to better understand general consumer interests, trends, and how our Services are used by you and others in our community. This information, along with analytics (as we described above), helps us understand more about our community and about how our Services fit into the lives of those in our community. We also engage in research and development to develop new techniques and technologies (e.g., new machine learning models or hardware, such as Spectacles). The results of our research are sometimes used in features on Snapchat, and we sometimes publish papers about things like overall behaviors and consumer trends (which will only have aggregated data across our user base, and not contain any private information about you specifically).', 'Enhance the Safety &amp; Security of Our Services', 'We use your information to enhance the safety and security of our Services, verify Snapchatter identity, and prevent fraud or other unauthorized or illegal activity. For example, we provide two-factor authentication to help protect your account and can send you email or text messages if we notice any suspicious activity. We also scan URLs sent on Snapchat to see if that webpage is potentially harmful, and can give you a warning about it.', 'Contacting You', 'Sometimes we’ll get in touch with you to promote new or existing features. This includes sending Snapchatters communications through Snapchat, email, SMS, or other messaging platforms, where permitted. For example, we may use the Snapchat app, email, SMS, or other messaging platforms to share information about our Services and promotional offers that we think may interest you.', 'Other times, we need to communicate with you to provide information, alerts, or to send messages our users ask us to deliver at their request. This may include sending communications through Snapchat, email, SMS, or other messaging platforms, where permitted, to deliver account status updates, security alerts, and Chat or friending reminders; it may also include fulfilling our user’s request to send invites or Snapchat content to non-Snapchatters.', 'Support', 'When you ask for help, we want to get you support as quickly as possible. In order to provide you, the Snapchatter community, and our business partners with the help needed to resolve issues with our Services, we often need to use the information we have collected to respond.', 'Enforce Our Terms &amp; Policies', 'We use the data we collect to enforce our Terms and the law. This includes enforcing, investigating, and reporting conduct that violates our Terms, policies, or the law, responding to requests from law enforcement, and complying with legal requirements. For example, when unlawful content is posted on our Services, we may need to enforce our Terms and other policies. In some cases, we may also use or share your information to cooperate with law enforcement requests, escalate safety issues to law enforcement, industry partners, or others, or comply with our legal obligations. Check out our Transparency Report to learn more.', 'Other Purposes, With Your Permission', 'Additionally, there may be instances when you interact with our Services that we will ask for your permission to use your information in a new, different, or otherwise specific way.', 'How We Share Information', 'This section explains who we share information with, what that information may include, and the reasons for sharing that information, including when we need to transfer it outside of the country it was collected from.', 'Recipients &amp; Reasons for Sharing', 'Snapchat. To provide our Services to you and our community, we may share your information with your friends on Snapchat or other Snapchatters. For example, the content you post to Stories, or your status as a premium subscriber, can be viewed by your Friends if you allow them. See the Control Over Your Information section and your Settings for the controls you have over who sees what and when.', 'Family Center Participants. When you have enabled Family Center, we share information about the connected teen account to the parent or guardian to provide insight about how the account is used, for example, who your Friends are on Snapchat or which friends you may be sharing your location with. We do not share message content. Learn more.', 'Public. Most of the features on Snapchat are private and for Friends only, but we also offer public features that allow you to opt in to showcase your best Snaps to the world, such as Spotlight, Snap Map, or your Public Profile. When you do this, those Snaps may also be discoverable outside of Snapchat, for example on the web. Some information, like your username and Bitmoji, are visible to the public. Learn more.', 'Third-Party Apps. Sometimes we provide features that allow you to connect with third-party apps. If you decide to connect your Snapchat account with a third-party app, we will share any additional information you direct us to.', 'Service Providers. We share your information with our service providers, who process that information on our behalf.\xa0For example, we rely on such Service Providers to facilitate payments, measure and optimize the performance of ads, or protect the services. We do not share private communications with them. We maintain a list of categories of service providers here.', 'Business and Integrated Partners. We share your information with business and integrated partners in order to provide the Services. For example, you can use OpenTable within Snapchat to reserve a table. This does not include private communications. We maintain a list of these partners here.', 'Anti-Fraud Partners. We share your information, such as device and usage information, with industry partners working to prevent fraud.', 'Legal, Safety, and Security Partners. We share your information as necessary for the following legal, safety, and security reasons:', 'comply with any valid legal process, governmental request, or applicable law, rule, or regulation.', 'investigate, remedy, or enforce potential Terms of Service and Community Guidelines violations.', 'protect the rights, property, or safety of us, our users, or others.', 'detect and resolve any fraud or security concerns.', 'Affiliates. Snap Inc. consists of different subsidiaries owned by us.\xa0We may share your information within those internal subsidiaries as needed to carry out our Services.', 'For the purposes of a Merger or Acquisition. If we were to sell or negotiate to sell our business to a buyer or possible buyer, we may transfer your information to a successor or affiliate as part of that transaction.', 'Integrated Partners', 'Our Services may contain content and integrations offered by our integrated partners. Examples include integrations in Lenses, Camera editing tools, to provide Scan results, and third-party developer integrations. Through these integrations, you may be providing information to the integrated partner as well as to Snap. We are not responsible for how those partners collect or use your information. As always, we encourage you to review the privacy policies of every third-party service that you visit or use, including those third parties you interact with through our Services. You can learn more about our integrations in Snapchat here.', 'On iOS we use Apple’s TrueDepth camera to improve the quality of Lenses. Note, however, that this information is used in real time — we don’t store this information on our servers or share it with third parties.', 'International Data Transfers', 'Our Services connect you with your friends around the world. To make that possible, we may collect your personal information from, transfer it to, and store and process it in the United States or other countries outside of where you live. Whenever we share information outside of where you live, we ensure safeguards are in place to protect the data as required by law where you live. If you want to learn more about this, see the Region Specific Information section for more details.', 'How Long We Keep Your Information', 'In this section we provide you with information on how long we keep your information, why we keep your information, and also highlight how we may need to keep your information to comply with laws, courts, and other obligations.', 'As a general rule, we keep information as long as you tell us to, and otherwise as long as we need it to provide our Services, or as required by law. For example, if you store something in Memories, we will keep it as long as you need it, but when you Chat with a friend, our systems are designed to delete Chats you send within 24 hours after your friend reads it (unless you’ve changed your default settings or decide to save it). Whether we retain your data depends on the specific feature, your settings, and how you’re using the Services. Here are some more factors we consider when we decide how long to keep your information:', 'If we need the information to operate or provide our Services. For example, we store your basic account details — like your name, phone number, and email address — to maintain your account.', 'To do the things you expect from our Services and as we’ve described within this Privacy Policy. For example, we maintain your list of friends until you ask us to delete them since friends are key to expressing yourself. Similarly, we keep your shared list of contacts until you ask us to remove them in our app settings (note: updating your device permissions may not remove the contacts you’ve previously shared with Snapchat). Learn more. Conversely, Snaps and Chats sent in Snapchat will be deleted by default from our servers within 24 hours after we detect they’ve been opened by all recipients or have expired, unless you’ve changed your default settings or decide to save something, in which case we will honor your choices.', 'The information itself. For example, we store location information for different lengths of time based on how precise it is and which Services you use. If location information is associated with a Snap — like those saved to Memories or posted to Snap Map or Spotlight — we’ll retain that location as long as we store the Snap. Pro tip: You can see the location data we retain about you by downloading your data.', 'How long we need to retain the information to comply with certain legal obligations.', 'If we need it for other legitimate purposes, such as to prevent harm, investigate possible violations of our Terms of Service or other policies, investigate reports of abuse, or protect ourselves or others.', 'Take a look at our Privacy by Product page and support page for details on the specific retention periods for products.', 'Although our systems are designed to delete some of your information automatically, we cannot promise that deletion will take place by a specific time.', 'In some cases we need to comply with legal requirements to store your data which stops us from deleting your information. For example, if we receive a notice from a court asking us to keep a copy of your content. Other reasons we may keep a copy of your data are if we get reports of abuse or other Terms or policy violations, or if your account, content created by you, or content created with other Snapchatters is flagged by others or our systems for abuse or other Terms or policy violations. Finally, we may also keep certain information in backup for a limited period of time or as required by law.', 'For the latest information about how long we store different types of content, check out our Support Site.', 'Region Specific Information', 'Depending on where you live, you may have additional rights, this section provides more details on region specific information.', 'We do our best to keep our policies as simple as possible, but depending on where you live, you have some additional rights or there may be specific information that you should be aware of. Please take a look at the list below to see if any apply to you!', 'Australia', 'Brazil', 'Canada', 'Europe', 'Mexico', 'South Korea', 'Turkey', 'United States', 'Note: The U.S. State Privacy Notice applies only if you are a resident of certain U.S. states that have implemented state-level privacy laws.', 'Some jurisdictions require that we state our legal basis for processing data for particular purposes. You can find that information here.', 'Our Audience', 'Our Services are directed to individuals 13 years and older.', 'Our Services are not directed to children under the age of 13, and you must confirm that you are 13 years or older in order to create an account and use our Services. If we have actual knowledge that you are under the age of 13 (or the minimum age at which a person may use the Services in your state, province, or country without parental consent, if greater), we will stop providing Services to you and delete your account and data.', 'In addition, we may also limit how we collect, use, and store some of the information of Snapchatters under 18. In some cases, this means we will be unable to provide certain functionality to people under the age of 18.', 'Updates to the Privacy Policy', 'We may update our Privacy Policy from time to time, and will give y</t>
+  </si>
+  <si>
+    <t>['Instapaper', 'Privacy', 'Terms', 'Instapaper', 'Create Account', 'Sign In', 'Help &amp; FAQ', 'Apps', 'How to Save', 'Premium ↗', 'Blog ↗', 'API', 'Press', 'Publishers', 'Privacy &amp; Terms', 'Create Account', 'Sign In', 'Terms', 'Our Commitment To Privacy', 'Your privacy is important to us. To better protect your privacy we provide this notice explaining our online information practices and the choices you can make about the way your information is collected and used.', 'The Information We Collect', 'This notice applies to all information collected or submitted on the Instapaper website and the Instapaper applications and services for iPhone, iPad, Android, Kindle, and other devices and platforms, hereafter referred to as simply Instapaper.', 'Instapaper occasionally needs to collect information for convenience, practicality, or technical requirements. This information includes:', 'Your chosen username, which may be your email address or name. A username is technically required so you can log in from multiple computers and devices. We encourage you to use your email address to make "forgot password" functionality possible.', 'Your chosen password, which is empty by default. A hash of your password is stored in the Instapaper database, and the plain-text password is only used for hash comparison to the stored value.', 'The titles, URLs (addresses), and selected text of the pages you save to Instapaper, folder-specific bookmarklets, Instapaper applications, third-party applications using the Instapaper API, and any other means with which to add pages to Instapaper.', 'The HTML contents of the pages you save to Instapaper when recognized as a known login-requiring site. This is technically required to generate the Text view and other indexing features for sites that require logins or accounts, such as some major newspaper publishers. When HTML is saved for a page, it is only used within your account and is not revealed via social or sharing features.', 'Your Amazon Kindle email address, if you have enabled automatic delivery to your Kindle. This is technically required to send your content to your Kindle.', 'Like most Web sites, Instapaper also collects and stores information automatically and through the use of electronic tools that may be transparent to our visitors. For example, we may log the name of your Internet Service Provider, your IP address, and information provided by and about your Internet browser. As we adopt additional technology, we may also gather similar information through other means.', 'We may also use "cookie" technology. Among other things, we may use cookies or other tracking technology for the purposes of storing your username and password hash to spare you from having to re-enter that information each time you visit.', 'The Way We Use Information', "We use the information you provide to operate Instapaper's features. We do not share this information with outside parties except to the extent necessary to accomplish Instapaper's functionality.", 'We use return email addresses to answer the email we receive. Such addresses are not used for any other purpose and are not shared with outside parties.', 'We use non-identifying and aggregate information to better design Instapaper, to suggest popular content to users, and to share with advertisers and publishers. For example:', 'We may use aggregate information from Instapaper usage to help design new features or services for the product.', 'We may tell an advertiser or publisher that X number of people visited a certain area on our website', 'We may tell an advertiser or publisher that X number of people bookmarked Z stories from a particular site or topic.', "We may aggregate the most popular stories during limited time periods or from certain websites in order to suggest stories for Instapaper's Editor's Picks or for users who have also saved pages from those websites.", 'When information is used in this or a similar manner, we do not disclose anything that could be used to identify the individuals on whom the information is based.', 'We may disclose your information in response to subpoenas, court orders, or other legal process, or to establish or exercise our legal rights or to defend against legal claims.', 'We may disclose your information when we believe it necessary or desirable in order to investigate, prevent, or take action regarding illegal activities, suspected fraud, situations involving potential threats to the physical safety of any person, violations of our policies, and/or to protect our rights and property.', 'In the future, we may sell, buy, merge, or partner with other companies or businesses. In such transactions, user information may be among the transferred assets.', 'Publicly Accessible Information', 'Some information you share on Instapaper is considered public when you use our social and sharing functionality, including:', 'Others can view your most recent Starred articles if they know your username.', 'Others can view your Unread, Archive, Starred, or folder contents if you reveal or share their associated RSS-feed URLs.', 'External Services', "External services beyond Instapaper's control are integrated with Instapaper where necessary, such as Mailgun for email sending, Crashlytics for crash reporting, ZenDesk for customer support, and Google Analytics for traffic measurement and tracking. Integrations with Google services like Analytics, YouTube, and YouTube API Services are bound to the Google Privacy Policy.", 'Instapaper makes reasonable efforts to ensure that all integrated external services are trustworthy and reputable, but Instapaper cannot be held responsible for data collection and usage by such services.', 'Our Commitment To Data Security', 'To prevent unauthorized access, maintain data accuracy, and ensure the correct use of information, we have put in place appropriate physical, electronic, and managerial procedures to safeguard and secure the information we collect online.', 'Please note: To ensure easy account creation, minimal customer errors, and reduced support inquiries, Instapaper accounts initially do not have passwords. If left without a password, anyone can access your account if they know or guess your username. To set or change your password, go to http://www.instapaper.com/user/password.', "Our Commitment To Children's Privacy", 'Protecting the privacy of the very young is especially important. For that reason, we never collect or maintain information at our website from those we actually know are under 13, and no part of our website is structured to attract anyone under 13.', 'How You Can Access Or Correct Your Information', 'You can access all your personally identifiable information that we collect online and maintain by logging into your Instapaper account on the Instapaper website at http://www.instapaper.com/.', 'You can correct factual errors in your personally identifiable information by changing or deleting the erroneous information, by deleting your entire Instapaper account at http://www.instapaper.com/user/delete, or by emailing support@instapaper.com.', 'To protect your privacy and security, we will also take reasonable steps to verify your identity before granting access or making corrections.', 'Deleting Information', 'You can delete your entire Instapaper account at any time at http://www.instapaper.com/user/delete. If you delete your account, all account information and saved page data is deleted from the Instapaper service immediately.', 'Due to the nature of backups and logs, deleted data may persist in backups and logs until they are deleted.', 'Privacy Shield', 'Instapaper complies with the EU-U.S. Privacy Shield Framework and the Swiss-U.S. Privacy Shield Framework as set forth by the U.S. Department of Commerce regarding the collection, use, and retention of personal information transferred from the European Union, United Kingdom, and Switzerland to the United States pursuant to the Privacy Shield. Instapaper has certified to the Department of Commerce that it adheres to the Privacy Shield Principles. If there is any conflict between the terms in this privacy policy and the Privacy Shield Principles, the Privacy Shield Principles shall govern. To learn more about the Privacy Shield program, and to view our certification, please visit https://www.privacyshield.gov.', 'In compliance with the Privacy Shield Principles, Instapaper commits to resolve complaints about your privacy and our collection or use of your personal information pursuant to the Privacy Shield. EU, UK, and Swiss individuals with inquiries or complaints regarding our Privacy Shield policy should first contact Instapaper at support@instapaper.com.', "Within the scope of this privacy notice, if a privacy complaint or dispute cannot be resolved through Instapaper's internal processes, the Federal Trade Commission has jurisdiction over Instapaper's compliance with the Privacy Shield.", "The Privacy Shield Principles describe Instapaper's accountability for personal data that it subsequently transfers to a third-party agent. Under the Privacy Shield Principles, Instapaper shall remain liable if third party agents process the personal information in a manner inconsistent with the Privacy Shield Principles, unless Instapaper proves it is not responsible for the event giving rise to the damage. If we cannot, we have selected JAMS, an independent dispute resolution provider, to handle unresolved Privacy Shield complaints. If we are unable to resolve your concerns after a good faith effort to address them, you may contact JAMS and submit a Privacy Shield claim. JAMS is a US-based private alternate dispute resolution provider, and we have contracted with JAMS to provide an independent recourse mechanism for any of our users for privacy concerns at no cost to you. You may learn more about the JAMS service or file a claim with JAMS by visiting https://www.jamsadr.com/eu-us-privacy-shield. You do not need to appear in court; you may conduct this dispute resolution process via telephone or video conference.", 'Note that Instapaper may be required to release the personal data of EU, UK, and Swiss individuals whose data is pursuant to the Privacy Shield in response to legal requests from public authorities, including to meet national security and law enforcement requirements.', 'In certain circumstances, the Privacy Shield Framework provides the right to invoke binding arbitration to resolve complaints not resolved by other means, as described in Annex I to the Privacy Shield Principles.', 'In certain circumstances, the Privacy Shield Framework provides the right to invoke binding arbitration to resolve complaints not resolved by other means, as described in Annex I to the Privacy Shield Principles.', 'GDPR: Information for EEA Users', 'What Rights Do I Have?', 'Individuals located in the European Economic Area (EEA) have certain rights in respect of your personal information and Instapaper will provide these capabilities to all our worldwide users, including:', 'The right of access to your personal data;', 'The right to correct or rectify any inaccurate personal data;', 'The right to restrict or oppose processing of personal data;', 'The right to erase your personal data; and', 'The right to personal data portability.', 'Instapaper uses, processes, and stores personal data, including those listed in the "Information We Collect" section, as necessary to perform our contract with you, and based on our legitimate interests in order to provide the Services. We rely on your consent to process personal data to place cookies on your devices. In some cases, Instapaper may process personal data pursuant to legal obligation or to protect your vital interests or those of another person.', 'How Can I Exercise my Rights?', "If you're a user based in the EEA, you can:", 'Request a personal data report by submitting a request to support@instapaper.com. This report will include the personal data we have about you, provided to you in a structured, commonly used, and portable format. Please note that Instapaper may request additional information from you to verify your identity before we disclose any information.', 'Have your personal data corrected or deleted. Some personal data can be updated by you through your Instapaper account settings, or by contacting us at support@instapaper.com. You can also remove your personal data from Instapaper by deleting your account at http://www.instapaper.com/user/delete.', "Complain to a regulator. If you're based in the EEA and think that we haven't complied with data protection laws, you have a right to lodge a complaint with your local supervisory authority.", 'If you have other questions or do not have a Instapaper account, please contact us at support@instapaper.com.', 'How To Contact Us', 'Should you have other questions or concerns about these privacy policies, please email support@instapaper.com. At this time, we only have the ability to receive and send English-language communications.', 'Changes To This Policy', 'Instapaper reserves the right to change this policy at any time. Please check this page periodically for changes. Your continued use of Instapaper following the posting of changes to this policy will mean you accept those changes. We will notify you before we make material changes to this policy and give you an opportunity to review the revised policy before deciding if you would like to continue to use the Services. You can review previous versions of the policy at https://github.com/Instapaper/privacy.', 'Effective Date: January 26th, 2019', '↑ \xa0 Click &amp; drag up to your Bookmarks Bar.']</t>
+  </si>
+  <si>
     <t>meta privacy policy meta collect us user data privacy policy search privacy topic privacy resource privacy policy privacy policy cover information collect use information information shared meta product integrated partner share information third party meta company work together manage delete information exercise right long keep information transfer information respond legal request comply applicable law prevent harm know policy changed privacy notice united state resident contact meta question process information policy article setting privacy policy privacy policy cover effective june view printable version see previous version read united state regional privacy notice detail handle personal information exercise right highlight meta want understand information collect use share thats encourage read privacy policy help use meta product way thats right privacy policy explain collect use share retain transfer information also let know right section policy includes helpful example simpler language make practice easier understand weve also added link resource learn privacy topic interest important u know control privacy also show manage information setting meta product use update setting shape experience read full policy product policy cover learn privacy center managing privacy information collect highlight information collect process depends use product example collect different information sell furniture marketplace post reel instagram use product collect information even dont account here information collect activity information provide friend follower connection app browser device information information partner vendor third party dont let u collect certain information information required product work information optional without quality experience might affected learn information collect doesnt identify individual case information deidentified aggregated anonymized third party longer identifies individual made available u use information described without trying reidentify individual take control manage information collect privacy center use information highlight use information collect provide personalized experience including ad along purpose explain detail purpose use information across product across device information use purpose automatically processed system case also use manual review access review information use less information thats connected individual user case deidentify aggregate information anonymize longer identifies use information way use information described section way use information provide personalize improve product use information provide improve product includes personalizing feature content recommendation facebook feed instagram feed story ad use information special protection choose provide purpose show ad read use information provide personalize improve product show ad sponsored commercial content use information improve product use locationrelated information promote safety security integrity use information collect help protect people harm provide safe secure product learn provide measurement analytics business service lot people rely product run promote business share content help measure well ad content product service working learn communicate communicate using information youve given u like contact information youve entered profile learn research innovate social good use information information researcher datasets publicly available source professional group nonprofit group conduct support research learn privacy policy process information information shared meta product integrated partner highlight meta product learn different case information shared product people account share communicate content others share reshare public content integrated partner choose connect integrated partner use product integrated partner receive information activity integrated partner always access information thats public product learn information receive handle information use integrated partner product service interact someone elses content integrated partner product service integrated partner handle information take control learn audience privacy center manage apps website share information third party highlight dont sell information anyone never also require partner third party follow rule use disclose information provide here detail share information partner advertiser audience network publisher partner use analytics service partner offer good service product commerce service platform integrated partner vendor measurement vendor marketing vendor service provider service provider third party external researcher ai integration third party also share information third party response legal request comply applicable law prevent harm read policy sell transfer part business someone else case well give new owner information part transaction law allows meta company work together highlight part meta company provide meta company product meta company product include meta product covered policy plus product like whatsapp share information collect infrastructure system technology meta company learn transfer information country also process information receive meta company according term policy permitted applicable law case meta act service provider meta company act behalf accordance instruction term share across meta company meta product share information meta company promote safety security integrity comply applicable law personalize offer ad sponsored commercial content develop provide feature integration understand people use interact meta company product see example share resource review privacy policy meta company facebook help center manage delete information exercise right highlight offer variety tool view manage download delete information also manage information visiting setting product use may also privacy right applicable law exercise right visit help center setting facebook instagram devicebased setting take privacy checkup take privacy checkup guided facebook privacy setting view manage information access information offmeta activity ad preference manage data port download delete information port information download information delete information account learn privacy work facebook instagram facebook help center question policy contact u described country may also able contact data protection officer meta platform inc depending jurisdiction may also contact local data protection authority dpa directly long keep information highlight keep information long need provide product comply legal obligation protect others interest decide long need information casebycase basis here consider decide need operate provide product example need keep information maintain account learn feature use feature work example message sent using messenger vanish mode retained less time regular message learn long need retain information comply certain legal obligation see example need legitimate purpose prevent harm investigate possible violation term policy promote safety security integrity protect including right property product instance specific reason well keep information extended period time read policy may preserve information transfer information highlight information transferred country information transferred safeguard information respond legal request comply applicable law prevent harm highlight access preserve use share information response legal request like search warrant court order production order subpoena request come third party civil litigant law enforcement government authority learn respond legal request accordance applicable law promote safety security integrity meta product user employee property public learn may access preserve information extended amount time learn know policy changed well notify make material change policy youll opportunity review revised policy choose continue using product privacy notice united state resident learn consumer privacy right may available reviewing united state regional privacy notice contact meta question learn privacy work facebook instagram facebook help center question policy question complaint request regarding information contact u described contact u online mail meta platform inc attn privacy operation willow road menlo park ca process information category information use information processed set process information information category use see information collect information information category actual information use depends factual circumstance could include following personalizing meta product ad see system automatically process information collect store associated others assess understand interest preference provide personalized experience across meta product accordance term personalize feature content facebook feed instagram feed story make suggestion people may know group event may interested topic may want follow product learn use information personalize experience across meta product choose ad see activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting like gps location locationrelated information information network connect device report product performance device information cooky similar technology information partner vendor third party providing ad meta company product ad system automatically process information weve collected stored associated ad system us information understand interest preference personalize ad across meta company product ad system prioritizes ad show based audience advertiser want reach match ad people might interested learn ad system work activity information provide age gender provide information ad show engage ad app browser device information location information device characteristic device software decide add whatsapp account account center account meta company product associate account meta company product whatsapp account account center share information whatsapp note list information meta information whatsapp share meta see whatsapp help center article activity information provide friend follower connection app browser device information providing improving meta product provision meta product includes collecting storing relevant sharing profiling reviewing curating instance automated processing also manual human reviewing create maintain account profile connect meta product account including public profile information integrated partner sign share information facilitate sharing content status provide curate feature provide messaging service ability make voice video call connect others provide advertising product understand enable creation content like text audio image video including artificial intelligence technology provide undertake analytics facilitate purchase payment meta pay meta checkout experience also use information develop research test improvement product use information see product working correctly troubleshoot fix test new product feature see work get feedback idea product feature conduct survey research like product brand better activity information provide content create like post comment audio public profile information including name username profile picture content provide camera feature camera roll setting voiceenabled feature message send receive including content subject applicable law metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make including truncated credit card information hashtags use time frequency duration activity product photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party promoting safety integrity security across meta product meta product designed research help ensure safety integrity security service people enjoy meta product process information associated apply automated processing technique instance conduct manual human review verify account activity find address violation term policy case decision make violation reviewed oversight board investigate suspicious activity detect prevent combat harmful unlawful behavior review case remove content reported u identify combat disparity racial bias historically marginalized community protect life physical mental health wellbeing integrity user others detect prevent spam security matter bad experience detect stop threat personnel property maintain integrity product information safety integrity security generally meta product visit facebook security help center instagram security tip activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature message send receive including content subject applicable law metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make including truncated credit card information hashtags use time frequency duration activity product photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party communicate use information youve given u like contact information profile send communication like email inproduct notice example well contact via email inproduct notification relation meta product productrelated issue research let know term policy also use contact information like email address respond contact u activity information provide contact information profile communication u content create like post comment audio content provide camera feature camera roll setting voiceenabled feature app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology transferring storing processing information across border including united state country share information collect globally internally across office data center externally partner third party service provider meta global user partner vendor employee around world transfer necessary operate provide service described term apply meta product using includes allowing share information connect family friend around globe fix analyze improve product information see transfer information section meta privacy policy activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make including truncated credit card information hashtags use time frequency duration activity product photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party processing information subject special protection applicable law provide share choose provide personalize improve product undertake analytics well collect store publish apply automated sometimes manual human processing purpose activity information provide information special protection choose provide religious view sexual orientation political view health racial ethnic origin philosophical belief trade union membership part survey choose participate given explicit consent receiving using information third party tailor ad see well use information advertiser business partner provide u activity meta company product associated personalize ad show meta product website apps device use advertising service receive information whether youre logged account product see cooky policy information activity information provide information content provide name email address information partner vendor third party sharing contact profile information third party upon request type third party category information shared depend circumstance ask u share example share email contact information information might choose direct u share advertiser contact additional information promoted product choose integrate apps game website meta product log well share information app game website log activity information provide information contact profile information content create like post comment providing measurement analytics business service system automatically well manual human processing process information collected stored others use information provide insight measurement report business advertiser partner help measure effectiveness distribution client ad content service understand kind people seeing content ad content ad performing meta product provide aggregated user analytics insight report help user business advertiser partner better understand audience may want connect well type people use service people interact content website apps service activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology sharing information across meta company provide seamless consistent richer innovative experience across meta company product enable cross app interaction sharing viewing engaging content including post video activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology business intelligence analytics understand aggregate usage across product accurately count people business validate metric directly related order inform improve product direction development adhere shareholderearning reporting obligation activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party identifying meta product user personalizing ad show meta audience network visit apps show ad meta audience network visit apps system automatically process information collected stored others identify meta product user tailor ad see activity information provide information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting information network connect device including ip address information cooky similar technology providing marketing communication depending setting subject applicable law well share marketing communication well collect store information use send marketing communication like email subject applicable law activity information provide information content provide including contact information like email address app browser device information device identifier research innovate social good carry survey use information including researcher collaborate conduct support research innovation topic general social welfare technological advancement public interest health wellbeing example analyze information migration pattern crisis help relief organization get aid right place collect store combine analyze apply automatic processing technique like aggregation information well manual human review share information necessary research innovate social good way support research area like artificial intelligence machine learning learn research program activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party anonymizing information case anonymize information associated activity product use resulting information example provide improve meta product including ad activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content type content view interact interact apps feature use action take purchase transaction make hashtags use time frequency duration activity product friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party sharing information others including law enforcement respond legal request see respond legal request prevent harm promote safety integrity section meta privacy policy information share information law enforcement others category information access preserve use share depend specific circumstance example response legal request compelled law typically include limited information contact detail login information however information process depend purpose could include following response legal request third party civil litigant law enforcement government authority comply applicable law legitimate legal purpose promote safety security integrity meta company meta product user employee property public learn promote safety security integrity activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature metadata content subject applicable law type content view interact interact apps feature use action take purchase transaction make hashtags use photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party processing information law requires obligation disclose information example receive valid legal request certain information search warrant access preserve andor share information regulator law enforcement others way information processed depends specific circumstance see respond legal request prevent harm promote safety integrity section meta privacy policy information law enforcement authority provides information operational guideline law enforcement need follow category information depend specific circumstance mandatory request obligation information necessary comply relevant legal obligation shared otherwise processed example civil matter typically include limited information contact detail login information however depending circumstance could include following activity information provide content create like post comment audio content provide camera feature camera roll setting voiceenabled feature message send receive including content subject applicable law metadata content message subject applicable law type content view interact interact apps feature use action take purchase transaction make including truncated credit card information hashtags use time frequency duration activity product photo video selfie provide contact u account support friend follower connection app browser device information device characteristic device software youre device like whether app foreground mouse moving help tell human bot identifier tell device apart user device signal information youve shared device setting locationrelated information information network connect device including ip address information cooky similar technology information partner vendor third party</t>
   </si>
   <si>
@@ -1033,6 +1941,21 @@
     <t>privacy policy tiktok u privacy policy last updated aug privacy policy applies tiktok service platform include tiktok apps website software related service accessed via platform device link privacy policy platform provided controlled tiktok inc tiktok u committed protecting respecting privacy privacy policy explains collect use share otherwise process personal information user individual age connection platform information collect use share otherwise process personal information user age child please refer childrens privacy policy information collect use share otherwise process consumer health data defined washington health data act similar state law please refer consumer health data privacy policy capitalized term defined privacy policy meaning given term service information collect may collect information including information provide information source automatically collected information information provide create account upload content contact u directly otherwise use platform may provide following information account profile information name age username password language email phone number social medium account information profile image usergenerated content including comment photograph livestreams audio recording video text hashtags virtual item video choose create upload platform user content associated metadata content created even user information may appear user content created published user platform create user content may upload import platform save post user content also known preuploading example order recommend audio option generate caption provide personalized recommendation apply effect user content may collect version user content include effect message include information provide compose send receive message platform messaging functionality include message send chat functionality communicating seller sell good use virtual assistant purchasing item platform information includes content message information message sent received read message participant please aware message choose send user platform accessible user responsible manner user use share message information including text image video found device clipboard permission example choose initiate information sharing thirdparty platform choose paste content clipboard onto platform access information stored clipboard order fulfill request purchase information including payment card number thirdparty payment information paypal required purpose payment billing shipping address also collect information required extended warranty purpose transaction purchase history platform phone social network contact permission choose find user phone contact access collect information name phone number email address match information existing user platform choose find user social network contact collect public profile information well name profile social network contact choice communication preference information verify account proof identity age information correspondence send u including contact u support information share survey participation challenge research promotion marketing campaign event contest gender age likeness preference information source may receive information described privacy policy source choose signup login platform using thirdparty service facebook twitter instagram google link tiktok account thirdparty service may collect information servicefor example public profile information nickname email contact list advertiser measurement partner share information u action taken outside platform activity website apps store including product service purchased online person partner also share information u mobile identifier advertising hashed email address phone number cookie identifier use help match action outside platform tiktok account advertiser partner enable u collect similar information directly website apps integrating tiktok advertiser tool tiktok pixel may obtain information certain affiliated entity within corporate group including activity platform may receive information others including included mentioned user content direct message complaint appeal request feedback submitted u contact information provided u may also collect receive information organization business people others including example publicly available source government authority professional organization charity group automatically collected information automatically collect certain information use platform including internet network activity information ip address geolocationrelated data unique device identifier browsing search history including content viewed platform cooky usage information collect information regarding use platform user content generate upload platform device information collect certain information device use access platform ip address user agent mobile carrier time zone setting identifier advertising purpose model device device system network type device id screen resolution operating system app file name type keystroke pattern rhythm battery state audio setting connected audio device automatically assign device id user id login multiple device able use information device id user id identify activity across device may also associate information collected device use login platform location data collect information approximate location including location information based sim card andor ip address addition collect location information tourist attraction shop point interest choose add location information user content current version app collect precise approximate gps information u user still using older version allowed collection precise approximate gps information last release august granted u permission may collect information image audio information may collect information video image audio part user content identifying object scenery appear existence location within image face body feature attribute nature audio text word spoken user content may collect information enable special video effect content moderation demographic classification content ad recommendation nonpersonallyidentifying operation may collect biometric identifier biometric information defined u law faceprints voiceprint user content required law seek required permission prior collection click learn metadata upload create user content automatically upload certain metadata connected user content metadata describes data provides information user content always evident viewer example connection user content metadata describe piece user content created collected modified content formatted also includes information account name enables user trace back user content user account additionally metadata includes data choose provide user content eg hashtags used mark keywords video caption cooky service provider business partner use cooky similar technology eg web beacon flash cooky etc cooky automatically collect information measure analyze use platform including page view often interact content enhance experience using platform improve platform provide advertising measure effectiveness advertisement content partner also use cooky promote platform platform website cooky enable platform provide certain feature functionality web beacon small image small piece data embedded image also known pixel tag clear gifs recognize cooky time date page viewed description page pixel tag placed similar information computer device learn disable certain cooky see choice section may link contact account information activity platform across device using email login device information may use information display advertisement platform tailored interest preference characteristic responsible privacy practice service provider business partner information practice service provider business partner covered privacy policy may aggregate deidentify information described aggregated deidentified data subject privacy policy use information explained use information improve support administer platform allow use functionality fulfill enforce term service may also use information among thing show suggestion promote platform customize ad experience generally use information collect fulfill request product service platform functionality support information internal operation including troubleshooting data analysis testing research statistical survey purpose solicit feedback customize content see use platform example may provide service based country setting chosen show content similar content liked interacted send promotional material u behalf affiliate trusted third party improve develop platform conduct product development measure understand effectiveness advertisement serve others deliver advertising including targeted advertising platform make suggestion provide customized ad experience support social function platform including permit others connect example find friend function suggest account others others share download otherwise interact user content posted platform use user content part advertising marketing campaign promote platform understand use platform including across device infer additional information age gender interest help u detect abuse fraud illegal activity platform promote safety security platform including scanning analyzing reviewing user content message associated metadata violation term service community guideline condition policy verify identity order use certain feature livestream verified account apply business account ensure old enough use platform required law instance verification may required communicate including notify change service announce winner contest promotion permitted promotion rule send applicable prize enforce term service community guideline condition policy consistent permission provide locationbased service advertising personalized content train improve technology machine learning model algorithm combine information collect receive foregoing purpose facilitate sale promotion purchase good service provide user support purpose disclosed time collect information pursuant consent profiling engage profiling result legal similarly significant effect defined applicable law share information committed maintaining trust tiktok sell personal information share personal information third party purpose crosscontext behavioral advertising restricted applicable law want understand may share information collect business purpose service provider business partner share category personal information listed service provider business partner help u perform business operation business purpose including research payment processing transaction fulfillment database maintenance administering contest special offer technology service delivery sending communication advertising marketing service analytics measurement data storage hosting disaster recovery search engine optimization data processing service provider business partner may include payment processor transaction fulfillment provider may receive information provide information source automatically collected information receive message data including particular following thirdparty payment providersprocessors paypal httpswwwpaypalcomuswebappsmppuaprivacyfull stripe httpsstripecomenieprivacy customer technical support provider may receive information provide information source automatically collected information researcher may receive information provide information source automatically collected information would receive payment information message data advertising marketing analytics vendor may receive information provide information source automatically collected information would receive payment information message data within corporate group global company platform supported certain entity within corporate group given limited remote access information collect necessary enable provide certain important function learn share information certain corporate group entity see connection sale merger business transfer may share information collect connection substantial corporate transaction sale website merger consolidation asset sale unlikely event bankruptcy legal reason may disclose information collect respond subpoena court order legal process law enforcement request legal claim government inquiry protect defend right interest safety security platform affiliate user public may also share information collect enforce term applicable platform exercise defend legal claim comply applicable law consent may share information purpose pursuant consent direction partner thirdparty service facebook instagram twitter google offer seamless signup login contentsharing experience may share information thirdparty service choose use feature example service may receive information activity platform may notify connection thirdparty service use platform accordance privacy policy choose allow thirdparty service access account share certain information third party depending permission grant third party may able obtain account information information choose provide choose engage public activity platform aware information share may read collected used user use caution disclosing personal information using platform responsible information choose submit make purchase third party platform including seller selling product shopping feature share information related transaction third party service provider transaction fulfillment provider making purchase directing u share information way entity may use information shared accordance privacy policy right may submit request know access correct delete information collected httpswwwtiktokcomlegalreportprivacy may appeal decision made request following instruction communication receive u notifying decision may also exercise right know access correct delete appealby sending request physical address provided contact u section also update account information directly inapp setting well request copy tiktok data request deactivate following instruction delete account following instruction may entitled accordance applicable law submit request authorized agent designate authorized agent exercise choice behalf please provide evidence given agent power attorney agent otherwise valid written authority submit request exercise right behalf respond request consistent applicable law subject proper verification verify request asking send email address associated account provide information necessary verify account information request received found information collect use disclose may constitute sensitive personal information applicable state privacy law information user relevant age threshold information disclose survey response user content racial ethnic origin national origin religious belief mental physical health diagnosis sexual life sexual orientation status transgender nonbinary citizenship immigration status financial information process information order provide platform within exemption applicable law example may process financial information order provide good service request u driver license number order verify identity choice may able control information collect device browser setting refuse disable cooky browser different please consult instruction provided browser please note may need take additional step refuse disable certain type cooky addition choice disable cooky specific particular browser device using disable cooky may need separately disable cooky type browser device choose refuse disable delete cooky functionality platform may longer available without information able provide requested service navigate ad inapp setting optout targeted advertising based personal information activity nonaffiliated apps website may able manage thirdparty advertising preference third party work serve advertising across internet using choice available httpswwwnetworkadvertisingorgmanagingoptoutasp httpswwwaboutadsinfochoices device may control determine information collect example control whether collect mobile advertising identifier advertising setting apple android device opt marketing advertising email using unsubscribe link mechanism noted marketing advertising email current version app collect precise approximate gps information u user still using older version allowed collection precise approximate gps information last release august granted u permission prevent device sharing information platform time device operating system setting registered account may access review update certain personal information provided u logging account using available feature functionality browser transmit donottrack signal website difference browser incorporate activate feature currently take action response signal data security retention use reasonable measure help protect information loss theft misuse unauthorized access disclosure alteration destruction understand data storage system transmission data internet public network guaranteed percent secure please note information collected third party may security protection information submit u responsible protecting security information retain information long necessary provide platform purpose set privacy policy also retain information necessary comply contractual legal obligation legitimate business interest improving developing platform enhancing safety security stability exercise defense legal claim retention period different depending different criterion type information purpose use information example process information profile information provide platform keep information long account violate term service community guideline condition policy may remove profile immediately may keep information process violation tiktok may transmit data server data center outside united state storage andor processing entity tiktok may share data described herein may located outside united state child teen privacy child important u provide separate experience child united state collect process limited information information collect use share otherwise process personal information child please refer childrens privacy policy platform otherwise directed child become aware personal information collected platform child delete information terminate child account believe user age please contact u httpswwwtiktokcomlegalreportfeedback parent guardian guardian guide contains information resource help understand platform tool control use parent guardian also request deletion account underage child download account data underage child contacting u httpswwwtiktokcomlegalreportprivacy parent guardian depending state residence may ability exercise certain right child teen account example may request deletion account download account data exercise right connection child teen contacting u httpswwwtiktokcomlegalreportprivacy address request accordance applicable law right sharing direct marketing purpose shine light california resident calendar year may entitled obtain information personal information shared business direct marketing us submit request contact u httpswwwtiktokcomlegalreportprivacy content removal user user platform california resident year age may request obtain removal user content posted contacting u httpswwwtiktokcomlegalreportprivacy request must provide description user content want removed information reasonably sufficient permit u locate user content accept california removal request via postal mail telephone facsimile may able respond provide adequate information please note request ensure complete comprehensive removal material example user content posted may republished reposted another user user platform connecticut resident year age parent guardian user platform connecticut resident year age may request unpublish delete account user aged child account parent guardian teen user following instruction privacy policy update may update privacy policy time time update privacy policy notify updating last updated date top new privacy policy posting new privacy policy providing notice required applicable law recommend review privacy policy time visit platform stay informed privacy practice contact u question comment request regarding privacy policy addressed contact u httpswwwtiktokcomlegalreportprivacy mailing address tiktok inc attn privacy policy inquiry bristol parkway suite culver city ca</t>
   </si>
   <si>
+    <t>deepseek privacy policy deepseek privacy policy last update july welcome deepseek introduction privacy policy privacy policy applies personal data similar term defined applicable data protection law relating personal data deepseek process connection deepseek apps website software related service service link reference privacy policy service enable create interact chatbots data controller service provided controlled hangzhou deepseek artificial intelligence co ltd registered address china u question use personal data please contact privacydeepseekcom click contact u column website please informed processing rule personal data collected end user accessing downstream system application developed developer using open platform service covered privacy policy developer operating application controller personal data processing activity disclose relevant personal data protection policy end user would like learn model mechanism training method please refer model mechanism training method deepseek personal data collect collect personal data three way personal data provide automatically collected personal data personal data source detail provided personal data provide create account input content contact u directly otherwise use service may provide following personal data account personal data collect personal data provide set account date birth applicable username applicable email address andor telephone number password user input use service may collect text input prompt uploaded file feedback chat history content provide model service prompt input generate response output based input personal data contact u contact u collect personal data send u proof identity age contact detail feedback inquiry use service personal data possible violation term service term policy automatically collected personal data automatically collect certain personal data use service including internet network activity personal data ip address unique device identifier cooky device network personal data collect certain device network connection personal data access service personal data includes device model operating system ip address device identifier system language also collect servicerelated diagnostic performance personal data including crash report performance log automatically assign device id user id login multiple device use personal data device id user id identify activity across device give seamless login experience security purpose log personal data collect personal data regarding use service feature use action take location personal data automatically collect personal data approximate location based ip address security reason example protect account detecting unusual login activity cooky similar technology may use cooky similar tracking technology operate provide service example use cooky security purpose better understand service used allow manage use nonessential cooky required law learn use cooky please see cooky policy payment personal data use paid service prepayment collect payment order transaction personal data provide service order placement payment customer service aftersales support avoid doubt cooky similar technology payment personal data applicable deepseek app personal data source may receive personal data described privacy policy source login signup linked service available choose signup login service using thirdparty service apple google link account thirdparty service may collect personal data thirdparty service access token security personal data receive personal data trusted partner security partner protect fraud abuse security threat service public personal data may obtain publicly available personal data via online source train model provide service service designed intended process sensitive personal data eg personal data revealing racial ethnic origin religious belief health sexuality citizenship immigration status genetic biometric data personal data child precise geolocation criminal membership ask provide sensitive personal data service whether individual use personal data use personal data operate provide develop improve service including following purpose provide administer maintain service enforce term condition policy creating account deliver fast convenient loggingin experience enabling chat deepseek provide user support improve develop service train improve technology machine learning model algorithm including monitoring interaction usage across device analyzing people using training improving technology communicate including notify change service provide customer support send servicerelated message promote safety security stability service preventing detecting abuse fraud illegal activity service conducting troubleshooting data analysis testing research comply legal obligation necessary perform task public interest protect vital interest user people could include providing law enforcement agency emergency service personal data urgent situation protect health life please note engage profiling otherwise engage automated processing personal data make decision could legal similarly significant impact others share personal data service provider engage service provider help u provide support develop service understand used share personal data provide automatically collected personal data personal data source service provider necessary enable provide service example use communication service provider send notification andor communication integrate thirdparty apis provide search service share input provide service use analytics service provider analyse data use support safety monitoring service provider assist u ensuring safety service pursuant instruction party access process store personal data course performing duty u corporate group service supported certain entity within corporate group entity process personal data provide automatically collected personal data personal data source u necessary provide certain function storage content delivery security research development analytics customer technical support third party share personal data following category third party limited scenario follows party corporate transaction personal data may disclosed third party connection corporate transaction merger sale asset share reorganization financing change control acquisition portion business law enforcement party legal right may access preserve share personal data described personal data collect law enforcement agency public authority copyright holder third party good faith belief necessary comply applicable law legal process government request consistent internationally recognized standard protect right property safety user copyright holder others including protecting life preventing imminent bodily harm example may provide personal data ip address law enforcement agency event emergency someone life safety risk investigate potential violation enforce term guideline applicable term policy standard detect investigate prevent address misleading activity copyright infringement illegal activity consent depending live may share personal data proper authorization provide service requested authorized example choose log service using social network account share personal data service social medium service share personal data third party service thirdparty content service may contain link policy functionality content maintained third party controlled u responsible make representation regarding policy functionality content practice operation third party right depending live subject exception provided applicable data protection law may certain right respect personal data exercise right authorized agent may submit request emailing u privacydeepseekcom receive request may verify requesting information sufficient confirm identity authority exercise right behalf someone else may also right appeal request deny emailing privacydeepseekcom appeal unsuccessful depending live may right raise concern lodge complaint competent authority discriminate exercising privacy right may privacy right may available include right know whether process personal data right access personal data right correct inaccuracy personal data right delete personal data youve provided u weve obtained right receive portable copy personal data youve provided u weve obtained extent available digital format technically feasible format allows transfer personal data another service right optout processing personal data purpose targeted advertising sale profiling could legal similarly consequential impact note engage targeted advertising sell personal data use personal data profiling otherwise engage automated processing personal data make decision could legal similarly significant impact others choice control access personal data directly setting example manage chat history choose may also delete chat history via setting choose delete account able reactivate account retrieve content personal data connection account note accuracy service like deepseek generate response reading user request response predicting word likely appear next case word likely appear next may factually accurate reason rely factual accuracy output model notice output contains factually inaccurate personal data would like request correction removal personal data submit request privacydeepseekcom consider request based applicable law technical capability model security personal data security personal data important u maintain commercially reasonable technical administrative physical security measure designed protect personal data unauthorized access theft disclosure modification loss regularly review security measure consider available new technology method however internet email transmission ever fully secure error free particular email sent u may secure therefore take special care deciding personal data send u via service email addition responsible circumvention privacy setting security measure contained service thirdparty website long keep personal data retain personal data long necessary provide service purpose set privacy policy also retain personal data necessary comply contractual legal obligation legitimate business interest improving developing service enhancing safety security stability exercise defense legal claim retention period different depending amount type sensitivity personal data purpose use personal data legal requirement etc example process personal data provide service keep personal data long account personal data includes account personal data input payment personal data violate term policy guideline may keep personal data necessary process violation personal data collected longer required u service provider perform necessary procedure destroying deleting erasing converting anonymous form permitted required applicable law store personal data personal data collect may stored server located outside country live provide service directly collect process store personal data people republic china required use appropriate safeguard transferring personal data outside certain country including one purpose set policy accordance requirement applicable data protection law personal data relating child service aimed child knowingly process personal data child notice receive feedback collected personal data child investigate appropriate delete personal data extent permitted applicable law believe processed personal data collected child please contact u privacydeepseekcom privacy policy update may update privacy policy time time required law update privacy policy notify updating last updated date top new privacy policy posting new privacy policy providing notice required applicable law recommend review privacy policy time access service stay informed privacy practice contact u question comment request regarding policy addressed privacydeepseekcom click contact u column website supplemental clause jurisdictionspecific european economic area eea switzerland uk using service eea switzerland uk european region following additional term apply legal base processing use personal data permitted law legal base processing personal data described privacy policy described table please aware collect personal data purpose set table may choose provide personal data field may affect service able use u purpose processing personal data category legal base provide administer maintain service enforce term condition policy creating account deliver fast convenient loggingin experience enabling chat deepseek provide user support account personal data user input personal data contact u device network personal data log personal data location personal data cooky performance contract provide maintain service take step request prior signing account use platform consent ask process personal data specific purpose help create account legitimate interest older age limited ability enter enforceable contract may unable process personal data ground contractual necessity rely legitimate interest use personal data collect allow access use platform improve develop service train improve technology machine learning model algorithm including monitoring interaction usage across device analyzing people using training improving technology account personal data user input personal data contact u device network personal data log personal data location personal data cooky legitimate interest identify resolve issue platform improve platform conduct research protect personal data aggregation anonymization consistent data minimization privacy design principle consent ask process personal data specific purpose provide service comply legal obligation necessary perform task public interest protect vital interest user people could include providing law enforcement agency emergency service personal data urgent situation protect health life account personal data user input personal data contact u device network personal data log personal data location personal data cooky compliance legal obligation includes situation obligation take measure ensure safety user comply valid legal request order law enforcement agency court obligation comply applicable law protect affiliate user third party right safety property legitimate interest protect business employee user illegal activity inappropriate behavior violation term would detrimental disclose share personal data regulator government entity communicate including notify change platform provide customer support send servicerelated message account personal data personal data contact u location personal data performance contract provide maintain service consent ask process personal data specific purpose communicate promote safety security stability platform preventing detecting abuse fraud illegal activity platform conducting troubleshooting data analysis testing research account personal data user input personal data contact u device network personal data log personal data location personal data cooky compliance legal obligation use personal data comply applicable law protect affiliate user third party right safety property legitimate interest ensure platform safe secure data storage please aware server located people republic china access service personal data may processed stored server people republic china may direct provision personal data u transfer thirdparty make right following right right request free charge confirmation whether process personal data ii access copy personal data retained right request proper rectification erasure personal data restriction processing personal data processing personal data either based consent necessary performance contract processing carried automated mean right receive personal data concerning structured commonly used machinereadable format personal data transmitted directly another company technically feasible data portability processing personal data based consent right withdraw consent time withdrawal impact lawfulness data processing activity taken place withdrawal right subject automatic individual decision including profiling produce legal effect similarly significantly affect unless consent authorised european union member state law necessary performance contract right object processing processing personal data basis legitimate interest unless demonstrate compelling legitimate ground may override right object processing ask state ground objection order u examine processing personal data balance legitimate interest processing objection processing right request restriction processing personal data challenging accuracy personal data personal data unlawfully processed opposing deletion personal data need personal data retained pursuit defense legal claim objected processing awaiting outcome objection request right object processing personal data direct marketing purpose right lodge complaint local data protection authority respond request exercise one right listed may required verify identity account detail please send email u would like exercise right privacydeepseekcom value privacy right data subject therefore appointed prighter group local partner privacy representative point contact following region european union eu united kingdom uk wish lodge data subject request may also exercise right contacting u repdeepseekprightercom data subject request subject line setting detail right request verify appointment prighter representative contact detail please visit httpsappprightercomportaldeepseek powered prighter powered prighter</t>
+  </si>
+  <si>
+    <t>privacy policy skip contenthome feature message privatelystay connectedconnect groupsexpress yourselfsecure designshare everydayfollow channel meta ai privacy help center blog business download download term privacy policy whatsapp llc englishespaolfranaisbahasa indonesiaoriyaportugus brasilfilipinotrkeenglishespaolfranaisbahasa indonesiaoriyaportugus brasilfilipinotrke featuresmessage privatelyendtoend encryption privacy control stay connectedmessage call free around world connect groupsgroup messaging made easy express yourselfsay sticker voice gifs secure designlayers protection help stay safe share everydayshare photo video voice note status follow channelsstay updated topic care meta aiget help anything privacy help center blog business apps log indownload whatsapp privacy policy effective january archived version live european region whatsapp ireland limited provides service term service privacy policy live uk whatsapp llc provides service term service privacy policy whatsapp legal info live outside european region uk whatsapp llc whatsapp u provides service term service privacy policy privacy policy privacy policy help explain data practice including information process provide service example privacy policy talk information collect affect also explains step take protect privacy like building service delivered message arent stored u giving control communicate service one meta company learn privacy policy way share information across family company privacy policy applies service unless specified otherwise please also read whatsapps term service term describe term use provide service back top key update respect privacy coded dna since started whatsapp weve built service set strong privacy principle mind updated term service privacy policy youll find additional information handle data updated term privacy policy provide information process data commitment privacy example weve added information recent product feature functionality process data safety security integrity added direct link user setting help center article manage information better communication business many business rely whatsapp communicate customer client work business use meta third party help store better manage communication whatsapp making easier connect part meta company whatsapp partner meta offer experience integration across metas family apps product back top information collect whatsapp must receive collect information operate provide improve understand customize support market service including install access use service type information receive collect depend use service require certain information deliver service without able provide service example must provide mobile phone number create account use service service optional feature used require u collect additional information provide feature notified collection appropriate choose provide information needed use feature unable use feature example share location contact permit u collect location data device permission managed setting menu android io device information provide account information must provide mobile phone number basic information including profile name choice create whatsapp account dont provide u information able create account use service add information account profile picture information message retain message ordinary course providing service instead message stored device typically stored server message delivered deleted server following scenario describe circumstance may store message course delivering undelivered message message delivered immediately example recipient offline keep encrypted form server day try deliver message still undelivered day delete medium forwarding user forward medium within message store medium temporarily encrypted form server aid efficient delivery additional forward offer endtoend encryption service endtoend encryption mean message encrypted protect u third party reading learn endtoend encryption business communicate whatsapp connection use contact upload feature provide u permitted applicable law phone number address book regular basis including user service contact contact arent yet using service well manage information way ensures contact identified u learn contact upload feature create join get added group broadcast list group list get associated account information give group name provide group profile picture description status information may provide u status choose include one account learn use status android iphone kaios transaction payment data use payment service use service meant purchase financial transaction process additional information including payment account transaction information payment account transaction information includes information needed complete transaction example information payment method shipping detail transaction amount use payment service available country territory privacy practice described applicable payment privacy policy customer support communication contact u customer support otherwise communicate u may provide u information related use service including copy message information deem helpful contact eg email address example may send u email information relating app performance issue automatically collected information usage log information collect information activity service like servicerelated diagnostic performance information includes information activity including use service service setting interact others using service including interact business time frequency duration activity interaction log file diagnostic crash website performance log report also includes information registered use service feature use like messaging calling status group including group name group picture group description payment business feature profile photo information whether online last used service last seen last updated information device connection information collect device connectionspecific information install access use service includes information hardware model operating system information battery level signal strength app version browser information mobile network connection information including phone number mobile operator isp language time zone ip address device operation information identifier including identifier unique meta company product associated device account location information collect use precise location information device permission choose use locationrelated feature like decide share location contact view location nearby location others shared certain setting relating locationrelated information find device setting inapp setting location sharing even use locationrelated feature use ip address information like phone number area code estimate general location eg city country also use location information diagnostics troubleshooting purpose cooky use cooky operate provide service including provide service webbased improve experience understand service used customize example use cooky provide service web desktop webbased service may also use cooky understand help center article popular show relevant content related service additionally may use cooky remember choice like language preference provide safer experience otherwise customize service learn use cooky provide service back top thirdparty information information others provide receive information user example user know use service may provide phone number name information like information mobile address book may provide may also send message send message group belong call require user lawful right collect use share information providing information u keep mind general user capture screenshots chat message make recording call send whatsapp anyone else post another platform user report report user user third party may also choose report u interaction message others service example report possible violation term policy report made collect information reporting user reported user find happens user report made please see advanced safety security feature business whatsapp business interact using service may provide u information interaction require business act accordance applicable law providing information u message business whatsapp keep mind content share may visible several people business addition business might working thirdparty service provider may include meta help manage communication customer example business may give thirdparty service provider access communication send store read manage otherwise process business understand business process information including might share information third party meta review business privacy policy contact business directly thirdparty service provider work thirdparty service provider meta company help u operate provide improve understand customize support market service example work distribute apps provide technical physical infrastructure delivery system provide engineering support cybersecurity support operational support supply location map place information process payment help u understand people use service market service help connect business using service conduct survey research u ensure safety security integrity help customer service company may provide u information certain circumstance example app store may provide u report help u diagnose fix service issue work meta company section provides information whatsapp collect share information meta company thirdparty service allow use service connection thirdparty service meta company product use service thirdparty service meta company product may receive information example use whatsapp share button news service share news article whatsapp contact group broadcast list service choose access service mobile carrier device provider promotion service please note use thirdparty service meta company product term privacy policy govern use service product back top use information use information subject choice make applicable law operate provide improve understand customize support market service here service use information operate provide service including providing customer support completing purchase transaction improving fixing customizing service connecting service meta company product may use also use information understand people use service evaluate improve service research develop test new service feature conduct troubleshooting activity also use information respond contact u safety security integrity safety security integrity integral part service use information verify account activity combat harmful conduct protect user bad experience spam promote safety security integrity service investigating suspicious activity violation term policy ensure service used legally please see law right protection section information communication service meta company use information communicate service let know term policy important update may provide marketing service meta company thirdparty banner ad still allow thirdparty banner ad service intention introduce may see type ad update tab home feature like channel status business interaction enable third party like business communicate interact using service catalog business whatsapp browse product service place order business may send transaction appointment shipping notification product service update marketing example may receive flight status information upcoming travel receipt something purchased notification delivery made message receive business could include offer something might interest want spammy experience message manage communication honor choice make back top information share share information use communicate service share information help u operate provide improve understand customize support market service send information choose communicate share information including message use communicate service information associated account phone number profile name photo information last seen information message receipt available anyone us service although configure service setting manage certain information available user including business communicate contact others user including business communicate store reshare information including phone number message others service use service setting block feature service manage communicate service certain information share business whatsapp offer specific service business providing metric regarding use service thirdparty service provider work thirdparty service provider meta company help u operate provide improve understand customize support market service work company support service provide technical infrastructure delivery system market service conduct survey research u protect safety security integrity user others assist customer service share information thirdparty service provider meta company capacity require use information behalf accordance instruction term thirdparty service others use thirdparty service meta company product integrated service thirdparty service may receive information others share example use data backup service integrated service like icloud google account receive information share whatsapp message interact thirdparty service another meta company product linked service use inapp player play content thirdparty platform information like ip address fact whatsapp user may provided third party meta company product please note use thirdparty service meta company product term privacy policy govern use service product back top work meta company part meta company whatsapp receives information share information see meta company may use information receive may use information share help operate provide improve understand customize support market service offering including meta company product includes helping improve infrastructure delivery system understanding service used promoting safety security integrity across meta company product eg securing system fighting spam threat abuse infringement activity improving service experience using making suggestion example friend group connection interesting content personalizing feature content helping complete purchase transaction showing relevant offer ad across meta company product providing integration enable connect whatsapp experience meta company product example allowing connect facebook pay account pay thing whatsapp enabling chat friend meta company product portal connecting whatsapp account learn meta company privacy practice reviewing privacy policy back top assignment change control transfer event involved merger acquisition restructuring bankruptcy sale asset share information successor entity new owner connection transaction accordance applicable data protection law back top managing retaining information access port information using inapp request account info feature available setting account iphone user learn access manage delete information iphone help center article android user learn access manage delete information android help center article store information long necessary purpose identified privacy policy including provide service legitimate purpose complying legal obligation enforcing preventing violation term protecting defending right property user storage period determined casebycase basis depends factor like nature information collected processed relevant legal operational retention need legal obligation would like manage change limit delete information following tool service setting change service setting manage certain information available user manage contact group broadcast list use block feature manage user communicate changing mobile phone number profile name picture information change mobile phone number must update using inapp change number feature transfer account new mobile phone number also change profile name profile picture information time deleting whatsapp account delete whatsapp account time including want revoke consent use information pursuant applicable law using inapp delete account feature delete whatsapp account undelivered message deleted server well information longer need operate provide service deleting account example delete account info profile photo delete whatsapp group delete whatsapp message history mindful delete whatsapp device without using inapp delete account feature information stored u longer period please remember delete account affect information related group created information user relating copy message sent learn data deletion retention practice delete account back top law right protection access preserve share information described information collect section privacy policy goodfaith belief necessary respond pursuant applicable law regulation legal process government request enforce term applicable term policy including investigation potential violation detect investigate prevent address fraud illegal activity security technical issue protect right property safety user whatsapp meta company others including prevent death imminent bodily harm back top global operation whatsapp share information globally internally within meta company externally partner service provider communicate around world accordance privacy policy information may example transferred transmitted stored processed united state country territory meta company affiliate partner service provider located country territory globally service provided outside live purpose described privacy policy whatsapp us metas global infrastructure data center including united state transfer necessary provide global service set forth term please keep mind country territory information transferred may different privacy law protection home country territory back top update policy may amend update privacy policy provide notice amendment privacy policy appropriate update effective date top privacy policy please review privacy policy time time back top privacy right united state resident learn consumer privacy right may available reviewing united state regional privacy notice back top contact u question issue privacy policy please contact u whatsapp llc privacy policy willow road menlo park california united state america back top download download featuresblogsecurityfor business uscareersbrand centerprivacy use whatsapp androidiphonemacpcwhatsapp web need help contact ushelp centerappssecurity advisory download whatsapp llc term privacy policysitemap englishespaolfranaisbahasa indonesiaoriyaportugus brasilfilipinotrkeenglishespaolfranaisbahasa indonesiaoriyaportugus brasilfilipinotrke</t>
+  </si>
+  <si>
+    <t>adobe privacy policy adobe privacy policy last updated june adobe privacy policy describes privacy practice adobe service software defined general term use anywhere display reference policy resident north america relationship adobe inc adobe u law california united state apply reside outside north america relationship adobe system software ireland limited adobe ireland controller regard personal information collected adobe law ireland apply content information store adobe service software contains personal information individual must legally permitted disclose personal information adobe summary key point adobe take data privacy seriously believe transparency control data make informed choice used support protect privacy decision wherever use product service adobe prioritizes control data store cloud following way policy explains process personal information legitimate interest ask u stop processing information learn right exercise policy also explains first get consent processing personal information including required law use personal information enable register adobe provide service software product service request learn provide interactive feature engage social medium site facebook use feature site send u personal information learn use cooky technology track use service software learn opportunity choose allow cooky click using website browser information also available cooky policy several place within adobe service software allow post comment upload picture submit content publicly available choose participate activity also disclose personal information company adobe family advertising sale partner consistent choice also disclose information third party engage process personal information behalf sharing required law certain situation learn provide additional information regarding location specific privacy right choice available location specific privacy right information notice privacy policy cover information adobe collect adobe use information collect legal base us adobe disclose personal information others personal information displayed anywhere within adobe apps website personal information secure adobe store personal information adobe transfer personal information across national border right regarding personal information exercise right location withdrawing consent otherwise objecting direct marketing long adobe retain information child use adobe website apps privacy policy change contact question concern privacy policy cover privacy policy describes adobe also referred u make use information context adobe website webbased service together referred website service display include reference policy adobe marketing sale advertising practice privacy practice previously acquired company unless otherwise noted privacy policy applies adobe provides product service directly individual buy adobecom unit via resellers ii adobe collect usage information employee user adobe enterprise customer unless otherwise directed enterprise customer ii considered data controller determine personal data collected handled detailed allowed per policy contrast adobe considered data processor data controller enterprise customer business educational institution use adobe product service eg adobe experience cloud support provision product service individual since adobe act direction enterprise customer regarding collection processing data behalf privacy policy apply data adobe enterprise customer may collect individual us data question specific organization data practice scenario please contact organization directly also find privacy information adobe experience cloud case different additional privacy data protection policy notice apply product service different extra privacy detail consider example acquire company privacy policy notice apply time adobe privacy practice implemented also certain product location additional privacy policy notice may apply find along relevant policy additional privacy policy page within adobe privacy center please also see adobe term use additional term use consumer product license agreement may apply service software using anchor cover information adobe collect adobe id registration customer support register use adobe service create adobe id purchase license service software contact u support offering adobe collect information identifies includes identifier contact information name email address telephone number postal physical address country commercial transaction information paymentbilling information app website paid license purchased eligibility information eg student teacher identification student teacher edition apps content information provided customer support communication eg recorded customer technical support call stored content correspondence u via website chat feature phone video call email channel type service software interest professional education demographic information date birth company school name title occupation job function expertise company detail size industry information company user may work user provided company name analytics electronic network activity ip address browser mobile device id browser extension connected adobe account inferred thirdparty data help keep database current provide relevant content experience may infer generate information based information collect combine information provided information third party source accordance applicable law example preference eg based earlier purchase engagement product service ii size industry information company work provided company name obtained source including professional networking site information service provider may also infer generate collect receive information third party including partner data broker service provider aggregator publicly accessible source purpose include detect prevent otherwise address fraudulent deceptive illegal activity misuse service software security technical issue well protect harm right property safety adobe employee user child public adobe service software collect information provide u eg access use service software permit u collect eg part thirdparty integration also collect generate information access use service software including use desktop mobile app feature take online photo syncing feature depending service software access use information may associated device browser may associated adobe account content includes analytics electronic network activity ip address browser device information including browser device type setting unique identifier version language setting configuration webpage led adobe website search term entered search engine led adobe website use navigation service software including interact adobe website collected cooky similar technology adobe server logged app website analysis use navigation service software analysis content subject optout consent right professional education demographic information profile information eg account profile public profile behance profile commercial transaction information content includes personal information sent received using online feature adobe service software stored adobe server document photo video activity log direct feedback metadata content user generated request search term prompt eg text image video audio etc inquiry feedback information may disclose access use service software well information service software return response request sensitive personal information precise geolocation eg add location data picture taken using camera phone gps feature information specific accessibility requirement preference mobility visual auditory dietary restriction accommodation eg visit office biometric identifier information defined united state law applicable law eg faceprints voiceprint etc required law seek required permission prior collection see adobe acting behalf analyze content deliver feature requested section information following link provide information adobe product improvement program usage data faq creative cloud document cloud apps adobe genuine software privacy choice regarding use information adobe product service licensed educational institution adobe us cooky similar technology adobe analyzes content using technique machine learning order improve service software opt adobe software activation automatic update device manufacturer model ip address adobe software version date activation successful unsuccessful update product serial number eg required start using product learn app activation adobe email email send may include technology called web beacon collect analytics electronic network activity whether received opened email clicked link email want u collect information opt receiving adobe marketing email adobe social networking page social signon service sign adobe service software using social networking account facebook account give appropriate permission receive contact identifier information social networking account name country basic demographic information adobe page many social networking site example adobe photoshop team facebook page collect information made publicly available social networking account name interest product service interact social networking page social networking site may provide statistic insight adobe help u understand type action people take page applicable adobe social medium site entered arrangement determines respective responsibility learn adobe practice respect social networking page account signon service adobe acting behalf certain instance adobe acting behalf personal information collected processed service example address book contact shared user entering recipient information case adobe acting instruction order facilitate service requested responsible information shared instance inform inapp notification intime communication submit information relating people u service provider connection use adobe apps website represent authority permit u use information accordance policy process content deliver feature requested adobe offer certain feature let edit organize photograph video type content using characteristic like face voice eg group similar face place image characteristic within collection characteristic may considered biometric identifier biometric information certain u law applicable privacy law choose use feature adobe acting instruction order facilitate service requested feature default choose enable always disable feature process biometric identifier biometric information deliver feature requested delete information turn feature unless otherwise specified software service visiting physical office visit adobe office collect identifier contact information name company name email address audio electronic visual similar information including facial image voice information cctv video voice recording photo anchor infocollect adobe use information collect legal base us adobe us information collect following purpose fulfill contract take step linked contract relevant register use adobe app website whether paid free trial includes providing adobe service software registered service product requested administering product platform skillknowledge course content including testing certification applicable verifying identity processing payment sending necessary communication example related payment expiration subscription providing customer service support required adobe conduct business pursue legitimate interest analyzing content characteristic using automated technique following circumstance operational use enable normal running service software service software access content stored locally device local content content uploaded server create using cloudbased service cloud content content analytics cloud content subject optout right including described may perform analytics cloud content help u understand user using service software allow u improve service software experience provide recommendation customize experience insight content analytics may used inform marketing subject optout right regarding marketing analyzing cloud content characteristic using automated technique human review following circumstance illegal abusive cloud content cloud content may automatically scanned ensure hosting illegal abusive content like child sexual abuse material human review may occur cloud content flagged reported illegal abusive public shared cloud content public shared cloud content subject review intellectual property issue safety issue example violence nudity choose share cloud content others using software service may automatically review shared cloud content flag abusive behavior spam phishing make cloud content publicly available additional human review may occur providing adobe service software registered product service requested analyzing use measuring effectiveness service software better understand used improve engage retain user sending information adobe product service special offer similar information sharing information third party marketing purpose consent required analyzing use navigation service software profile information interaction communication excluding content detect prevent fraudulent deceptive illegal activity misuse service software improve service software user experience subject optout consent right including described tailor customize service software marketing communication learn diagnosing problem service software conducting survey market research customer interest effectiveness marketing campaign customer satisfaction unless need consent undertake survey case permission investigating responding comment complaint may send u checking validity sort code account number card number submit use credit debit card payment order prevent payment fraud illegal deceptive payment practice use third party see adobe disclose personal information others sharing account information registered business email address employer account migration purpose combining data may interacted product service logged logged order provide seamless experience show relevant content service marketing purpose consent required merge acquired another company sell adobe website app business unit substantial portion asset acquired another company information likely disclosed prospective purchaser adviser prospective purchaser adviser one asset transferred new owner connection legal claim compliance regulatory investigative purpose necessary including disclosure information connection government agency request legal process litigation process information based legitimate interest object processing certain circumstance case cease processing information unless compelling legitimate ground continue processing needed legal reason legitimate interest available legal basis particular jurisdiction engage processing activity described legal basis available particular jurisdiction required give adobe consent otherwise consistent choice sending information adobe product service special offer similar information sharing information third party marketing purpose placing cooky using similar technology service software email communication accordance cooky policy information provided technology used accessing information stored device following operational us information relating use engagement service software related crash report order fix underlying problem causing crash information allow u receive devicebased setting eg photo location camera order provide certain functionality within service software analyzing use navigation service software content characteristic using automated technique human review order detect prevent fraudulent deceptive illegal activity misuse service software improve service user experience adobe product improvement program described respond request eg customer service allowing participate sweepstakes contest similar promotion administer activity occasion ask consent use information purpose explain time rely consent process information withdraw consent activity time legal reason responding request government law enforcement authority conducting investigation using disclosing information reasonably necessary detect prevent otherwise address fraud security potential deceptive illegal activity misuse service software technical issue software piracy eg confirm software genuine properly licensed helping protect well adobe processing disclosure strictly required law adobe may rely legitimate interest available third party described anchor infouse adobe disclose personal information others disclosing data controller disclose personal information within adobe family company purpose identified see list adobe entity acquired company also disclose personal information thirdparty data controller consent necessary provide product service requested eg thirdparty integration type third party information may disclosed include resellers sale advertising partner retailer advertiser ad agency advertising network platform information service provider fraud monitoring prevention provider publisher case order show relevant ad disclose social medium platform advertising partner information action take website apps page visit ad saw party may joint controller processing information available thirdparty data controller may also use adobe product service collect process personal information using email address associated business domain eg yournamebusinessnamecom access adobe service software invited use service software business may provide personal information business disclosing fraud prevention safety security purpose disclose personal information company help u run business detect prevent otherwise address fraud deception illegal activity misuse adobe service software security technical issue additionally disclose personal information company organization government authority individual outside adobe goodfaith belief access use preservation disclosure information reasonably necessary detect prevent protect fraudulent deceptive illegal activity misuse service software security technical issue reasonably necessary protect harm right property safety adobe employee user child public required permitted law disclosing data processor also disclose personal information company help u run business processing personal information behalf adobe purpose identified company including may record store communication include provider customer support service chatbots session replay partner provide service recreate web app session showing meaningful insight visitor experience provider analytics technology record analyze interaction website help u improve experience provider artificial intelligence technology record analyze content communication payment processing service fraud monitoring prevention detecting preventing deceptive illegal activity misuse service software email social medium marketing platform service provider hosting service require company protect personal information consistent privacy policy information disclosure adobe may also disclose personal information agree disclosure good faith belief required provide information response subpoena court order applicable law legal process learn respond emergency involving danger death serious bodily harm merge acquired another company sell adobe website app business unit substantial portion asset acquired another company information likely disclosed prospective purchaser adviser prospective purchaser adviser one asset transferred new owner anchor infoshare personal information displayed anywhere adobe website application several place within adobe service software allow post comment upload picture participate message board chat engage blog share technical information submit content others see sometimes limit see share place share seen general public user service information appear search engine result publicly available platform crawled searched third party example user post content message board online chat blog community forum information posted user become public online content may remain accessible publicly even adobe fulfils request delete poster personal information please careful share personal information share anything wouldnt want publicly known unless sure posting within app website allows control see post please note post message certain user forum website app email address name andor profile photo may included displayed message find information managing public profile remove content shared service software please use feature used share content another user invite participate shared viewing editing commenting content may able delete contribution usually user invited full control question concern please contact u anchor websitesapplications personal information secure work hard protect personal information employ administrative technical physical security control appropriate encryption step verification appropriate contractual confidentiality obligation employee contractor anchor infosecure adobe store personal information personal information file stored adobe server server company engage provide service u anchor infostore adobe transfer personal information across national border main location process personal information u india also transfer personal information country adobe affiliate provider partner operate carry transfer compliance applicable law example putting data transfer agreement place help protect personal information adobe complies euus uk extension euus swissus data privacy framework learn see cross border data transfer page visit u department commerce data privacy framework website set adobe us limited number thirdparty service provider assist u providing service user business customer third party may access process store personal data course providing service adobe maintains contract third party restricting access use disclosure personal data compliance data privacy framework obligation including onward transfer provision adobe remains liable fail meet obligation adobe responsible event giving rise damage information applies adobe user consumer information available business customer want learn crossborder data transfer anchor infotransfer right regarding personal information exercise right provided applicable law right ask u copy personal information correct delete restrict stop active processing personal information obtain personal information provide u contract consent structured machine readable format ask u share port information another controller may entitled additional right based applicable data privacy law jurisdiction addition object processing personal information circumstance using information direct marketing right may limited example fulfilling request would reveal personal information another person ask u delete information required law keep need defend claim u addition adobe website recognize global privacy control available web browser browser configured send signal adobe opt adobe use advertising cooky browser learn adobe advertising practice privacy choice exercise right including deactivating adobe id account get touch u data protection officer using detail set additionally many service software allow edit personal information accessing account profile similar feature service using likewise delete file photo stored service software logging using deletion function available unresolved concern right report local privacy regulator data protection authority applicable also right lodge complaint adobe ireland lead supervisory authority irish data protection commission asked provide personal information may decline may use web browser operating system control prevent certain type automatic data collection choose provide allow information necessary certain service feature service feature may available fully functional example register adobe create adobe id use adobe service software provision information mandatory relevant information provided able administer adobe account provide service software requested optional information provided may impact ability provide personalized experience tailored content offering anchor right right location addition right see location specific privacy right information notice information anchor californiaconsumer withdrawing consent otherwise objecting direct marketing adobe family company see list adobe entity acquired company company hire help market service software behalf may use information provide information offer related adobe rely consent always able withdraw consent although may legal ground processing information purpose set case able send direct marketing without consent rely legitimate interest absolute right optout direct marketing profiling carry direct marketing time updating preference adobe id profile updating preference specific website app account clicking unsubscribe link bottom marketing email contacting u using detail provided end privacy policy click information choice regarding marketing practice anchor withdrawconsent anchor infoexpcloud long adobe retain information register account create adobe id process keep personal information process behalf long active user service software delete certain personal information collect longer business reason retain additionally personal information need retain even close account comply business legal requirement personal information related contract business transaction retain ten year last interaction u process personal information marketing purpose consent process information ask u stop short period allow u implement request also keep permanent record fact asked u send direct marketing process information respect request future anchor retain child use adobe website apps adobe service software intended child age except limited situation certain product including adobe express creative cloud apps may available child educational purpose direct supervision teacher circumstance adobe authorized collect student data participating school obtained appropriate consent needed adobe direct coppa notice provides information collection use student data adobe service software intended use child certain product specifically prohibit user certain age meet applicable age requirement please use service software age meet applicable age requirement use certain service software adobe make available privacy younger user page provide information privacy practice ageappropriate format anchor child privacy policy change occasionally may update privacy policy document adobe privacy center allow adobe accommodate new technology industry practice regulatory requirement purpose change last updated date top policy revised policy posted page aware information collect use circumstance may disclose encourage periodically review adobe privacy center adobe privacy policy version history page latest information privacy practice certain circumstance example certain material change required applicable privacy law provide notice change required applicable law obtain consent notice may email posting notice change service software mean consistent applicable law anchor policychange contact question concern privacy question concern request please fill privacy inquiry form outside north america also get touch adobe ireland data protection officer dpoadobecom postal mail riverwalk citywest business park dublin ireland practice covered prp certification unresolved privacy data use concern addressed satisfactorily please contact usbased third party dispute resolution provider free charge httpsfeedbackformtrustecomwatchdogrequest believe adobe maintains personal data one service within scope data privacy framework certification may direct inquiry complaint concerning data privacy framework compliance filling privacy inquiry form unresolved privacy data use concern addressed satisfactorily please contact usbased third party dispute resolution provider free charge httpswwwananetcontentshowidaccountabilitydpfconsumers neither adobe dispute resolution provider resolve complaint may possibility engage binding arbitration data privacy framework panel information option please see annex euus data privacy framework principle anchor questionsconcerns home adobe privacy center adobe privacy policy</t>
+  </si>
+  <si>
+    <t>privacy policy snapchat privacy privacyprivacyprivacy center privacy principle privacy product privacy policy teen snapchat snap ad privacy security privacy policy effective april welcome snap inc privacy policy policy explains collect use data control information looking quick summary privacy practice check page video youre looking specific product privacy information example process chat snap take look privacy product page addition document also show inapp notice provide information product service youre spectacle user learn collect use data spectacle supplemental privacy policy transparency one core value snap believe shouldnt surprise data collect use thats upfront process example process information provide personalized experience including show content information relevant experience well relevant advertisement understanding interest preference help u provide better product experience furthermore believe personalized experience come expense privacy like real life moment want share privately close friend others want share publicly thats day one philosophy delete content default give snapchatters control providing tool allow decide happens content like share save policy cover snapchat app well product service feature bitmoji spectacle advertising commerce initiative read service policy talking also see u refer term mean term service agree sign service finally see term snapchatter often using shorthand user service let get started control information control information control information setting core part snapchat experience access update delete information decide contact download data within snapchat app give detail type setting available link data download tool provide instruction delete data account want control information provide range tool including access update information access edit basic account information right service navigate setting see option available delete information want delete account learn also delete information within service like content youve saved memory content youve shared ai spotlight submission control see content weve built number tool let choose share content case may want share content friend instance may want share public learn go control contact snapchat intended close friend family thats weve built control help decide contact receive unwanted communication always block report person go learn change permission case change permission time example default findable others phone number andor email address provided longer want findable always change setting provided access phone third party platform contact make friending easier change later app setting course certain feature service like finding friend contact book wont work opt promotional message option opt unsubscribe promotional email message sent sm messaging platform follow instruction message like unsubscribe link similar functionality download data make request download data tool export copy snapchat information object processing depending live particular data processing may right object processing information get bit technical weve explained detail set advertising preference try show ad think relevant interest youd like less personalized experience change advertising setting snapchat app learn tracking use iphone io specific requirement apply weve specified information collect section provides detail information collect provide u collect use snapchat information receive company apps youve connected snapchat account sometimes may also collect additional information permission use service snapchat collect information provide u generate information use service case receive data others let break detail information provide many service require set account ask provide u account detail information like name username email address birthday phone number set profile youll also provide u profile detail like bitmoji profile picture use commerce product buy something like latest sneaker may ask payment related information like physical address ship product payment information process payment transaction history course youll also provide u information send save within service including content information content content share generate ai feature content input including text image video audio precise location engagement used generate content response output consider information private content communication like snap chat friend voice video call content saved eye content share particular audience like private friend story story set friend private story end spectrum information send save within service may public content accessible everyone public story content including story set everyone shared story community story spotlight snap map submission public profile information keep mind snapchatters view snap chat content always screenshot content save copy outside snapchat app please dont send message share content wouldnt want someone save share lastly contact support content communication shared support safety team communicate u way including research effort like response survey consumer panel research question well collect whatever information provide need resolve question information generate use service use service collect information service youve used youve used help u better understand way community us service make improvement includes usage information information interact service example lens view apply premium subscription story watch often interact snapchatters content information information content create provide engagement camera creative tool interaction ai metadata example information content like date time posted viewed content information includes information based content image video audio post spotlight basketball game may use information show content spotlight basketball also includes device information hardware software operating system device memory advertising identifier apps installed browser type information device sensor measure motion device compass microphone including whether headphone connected information wireless mobile connection location information ip address information collected cooky similar technology depending setting cooky pixel small graphic data recognize user activity often user visited website web storage unique advertising identifier log information detail youve used service access time page viewed ip address unique identifier like cooky youve explicitly granted devicelevel permission device information may also include information device phonebook contact related information image information device camera photo microphone like ability take photo video view stored photo video access microphone record audio recording video location information precise location method like gps signal data receive others last category data collect information may receive others user affiliate third party includes linked thirdparty service data information get link snapchat account another service data advertiser information advertiser app developer publisher third party help target measure performance ad contact info snapchatters third party another snapchatter uploads contact list includes information may combine information better understand may want communicate provide u contact information may use determine communicate way like sm email messaging service data relating potential violation term may receive information third party including website publisher social network provider law enforcement others potential violator term service community guideline information permission additionally may instance interact service ask permission collect additional information example accessing device camera roll device third party contact book use information section explains use information collect among thing use information collect provide personalized product service work hard build improve walk purpose use information detail youd like see mapping data collect purpose collect table keep thing running ie operate deliver maintain service use information collect order operate deliver maintain service example delivering snap want send friend share location snap map show suggestion like place might like neighborhood content others posted map friend theyre sharing location also use information help keep product date example make sure service work latest operating system device personalize experience give context offer personalized service snapchatters one way showing content relevant think may enjoy based information share u use information across different area service order add context snapchat experience example automatically tag content label based content location time day there dog photo may searchable memory term dog show map location created memory inform u youre dog surface fun dog video dog food ad part service spotlight personalization also help suggesting friend recommending new friend send snap based snap may show recommended place snap map generate sticker even generate snap content using ai infer interest based content activity customize content show including ad example watch barista content spotlight talk ai favorite espresso machine save lot coffeerelated snap memory may highlight coffee shop snap map visit new city show content coffee may find interesting relevant interact lot music venue may use show ad upcoming show town personalization also includes tailoring experience based interact friend including showing content friend create like enjoy spotlight place recommendation popular friend goal continuously provide relevant interesting content example watch lot sport content skip content hair makeup tip recommendation algorithm prioritize sport makeup tip learn understand snapchatter preference rank moderate content believe critical also balance benefit personalization snapchatters expectation privacy example may automatically tag snap save memory based content within eg snap contained dog use tag personalize experience make recommendation show ad showing spotlight snap containing dog use private content communication send friend personalize experience make recommendation show ad provide relevant ad another way provide personalized service ad show use interest preference information weve collected personalize target measure ad think ad best theyre relevant thats try select right ad show right time example youve interacted ad video game infer like video game show similar ad wont ad see similar content strategy try ensure receive variety ad also use information avoid showing ad probably wont interested example ticketing site tell u youve previously bought ticket movie stop showing ad learn different type advertising choice ad receive learn collect use share information advertising purpose note information collected cooky technology may use technology collect information interact service offer one partner example may use information collected advertiser website show relevant ad web browser set accept cooky default prefer usually remove reject browser cooky setting browser device keep mind though removing rejecting cooky could affect availability functionality service learn partner use cooky service choice please check cookie policy develop improve feature algorithm machine learning model team constantly coming new idea feature way improve service order also develop improve algorithm machine learning model expression algorithm comb significant amount data find pattern make prediction make feature service work including generative ai feature artificial intelligence capable generating text image medium using generative model generative ai model learn pattern structure input training data generate new data similar characteristic use algorithm machine learning model personalization advertising safety security fairness inclusivity augmented reality prevent abuse term service violation example algorithm machine learning model take account conversation snapchatters ai improve response ai information help u decide kind improvement make always focused privacy dont want use personal information necessary develop feature model analytics order understand build improve service need understand trend demand feature example monitor metadata trend group chat use help decide whether change part feature like maximum size group studying data snapchatters help u see trend way people use service help inspire u improve snapchat larger scale perform analytics order identify monitor analyze trend usage based information among thing create information user help u understand demand research conduct research better understand general consumer interest trend service used others community information along analytics described help u understand community service fit life community also engage research development develop new technique technology eg new machine learning model hardware spectacle result research sometimes used feature snapchat sometimes publish paper thing like overall behavior consumer trend aggregated data across user base contain private information specifically enhance safety security service use information enhance safety security service verify snapchatter identity prevent fraud unauthorized illegal activity example provide twofactor authentication help protect account send email text message notice suspicious activity also scan url sent snapchat see webpage potentially harmful give warning contacting sometimes well get touch promote new existing feature includes sending snapchatters communication snapchat email sm messaging platform permitted example may use snapchat app email sm messaging platform share information service promotional offer think may interest time need communicate provide information alert send message user ask u deliver request may include sending communication snapchat email sm messaging platform permitted deliver account status update security alert chat friending reminder may also include fulfilling user request send invite snapchat content nonsnapchatters support ask help want get support quickly possible order provide snapchatter community business partner help needed resolve issue service often need use information collected respond enforce term policy use data collect enforce term law includes enforcing investigating reporting conduct violates term policy law responding request law enforcement complying legal requirement example unlawful content posted service may need enforce term policy case may also use share information cooperate law enforcement request escalate safety issue law enforcement industry partner others comply legal obligation check transparency report learn purpose permission additionally may instance interact service ask permission use information new different otherwise specific way share information section explains share information information may include reason sharing information including need transfer outside country collected recipient reason sharing snapchat provide service community may share information friend snapchat snapchatters example content post story status premium subscriber viewed friend allow see control information section setting control see family center participant enabled family center share information connected teen account parent guardian provide insight account used example friend snapchat friend may sharing location share message content learn public feature snapchat private friend also offer public feature allow opt showcase best snap world spotlight snap map public profile snap may also discoverable outside snapchat example web information like username bitmoji visible public learn thirdparty apps sometimes provide feature allow connect thirdparty apps decide connect snapchat account thirdparty app share additional information direct u service provider share information service provider process information behalf example rely service provider facilitate payment measure optimize performance ad protect service share private communication maintain list category service provider business integrated partner share information business integrated partner order provide service example use opentable within snapchat reserve table include private communication maintain list partner antifraud partner share information device usage information industry partner working prevent fraud legal safety security partner share information necessary following legal safety security reason comply valid legal process governmental request applicable law rule regulation investigate remedy enforce potential term service community guideline violation protect right property safety u user others detect resolve fraud security concern affiliate snap inc consists different subsidiary owned u may share information within internal subsidiary needed carry service purpose merger acquisition sell negotiate sell business buyer possible buyer may transfer information successor affiliate part transaction integrated partner service may contain content integration offered integrated partner example include integration lens camera editing tool provide scan result thirdparty developer integration integration may providing information integrated partner well snap responsible partner collect use information always encourage review privacy policy every thirdparty service visit use including third party interact service learn integration snapchat io use apple truedepth camera improve quality lens note however information used real time dont store information server share third party international data transfer service connect friend around world make possible may collect personal information transfer store process united state country outside live whenever share information outside live ensure safeguard place protect data required law live want learn see region specific information section detail long keep information section provide information long keep information keep information also highlight may need keep information comply law court obligation general rule keep information long tell u otherwise long need provide service required law example store something memory keep long need chat friend system designed delete chat send within hour friend read unless youve changed default setting decide save whether retain data depends specific feature setting youre using service factor consider decide long keep information need information operate provide service example store basic account detail like name phone number email address maintain account thing expect service weve described within privacy policy example maintain list friend ask u delete since friend key expressing similarly keep shared list contact ask u remove app setting note updating device permission may remove contact youve previously shared snapchat learn conversely snap chat sent snapchat deleted default server within hour detect theyve opened recipient expired unless youve changed default setting decide save something case honor choice information example store location information different length time based precise service use location information associated snap like saved memory posted snap map spotlight well retain location long store snap pro tip see location data retain downloading data long need retain information comply certain legal obligation need legitimate purpose prevent harm investigate possible violation term service policy investigate report abuse protect others take look privacy product page support page detail specific retention period product although system designed delete information automatically promise deletion take place specific time case need comply legal requirement store data stop u deleting information example receive notice court asking u keep copy content reason may keep copy data get report abuse term policy violation account content created content created snapchatters flagged others system abuse term policy violation finally may also keep certain information backup limited period time required law latest information long store different type content check support site region specific information depending live may additional right section provides detail region specific information best keep policy simple possible depending live additional right may specific information aware please take look list see apply australia brazil canada europe mexico south korea turkey united state note u state privacy notice applies resident certain u state implemented statelevel privacy law jurisdiction require state legal basis processing data particular purpose find information audience service directed individual year older service directed child age must confirm year older order create account use service actual knowledge age minimum age person may use service state province country without parental consent greater stop providing service delete account data addition may also limit collect use store information snapchatters case mean unable provide certain functionality people age update privacy policy may update privacy policy time time give head make change think know may change privacy policy time time well let know one way another sometimes well let know revising date top privacy policy thats available website mobile application time may provide additional notice adding statement website homepage providing inapp notification contact u question information wish contact data protection officer dpo contact u companysnap inc career news privacy safety communitysnapchat support spectacle support community guideline advertisingsnapchat ad advertising policy political ad library brand guideline promotion rule legalother term policy law enforcement cookie policy cookie setting report infringement privacy policy term service languageenglish u</t>
+  </si>
+  <si>
+    <t>instapaper privacy term instapaper create account sign help faq apps save premium blog api press publisher privacy term create account sign term commitment privacy privacy important u better protect privacy provide notice explaining online information practice choice make way information collected used information collect notice applies information collected submitted instapaper website instapaper application service iphone ipad android kindle device platform hereafter referred simply instapaper instapaper occasionally need collect information convenience practicality technical requirement information includes chosen username may email address name username technically required log multiple computer device encourage use email address make forgot password functionality possible chosen password empty default hash password stored instapaper database plaintext password used hash comparison stored value title url address selected text page save instapaper folderspecific bookmarklets instapaper application thirdparty application using instapaper api mean add page instapaper html content page save instapaper recognized known loginrequiring site technically required generate text view indexing feature site require logins account major newspaper publisher html saved page used within account revealed via social sharing feature amazon kindle email address enabled automatic delivery kindle technically required send content kindle like web site instapaper also collect store information automatically use electronic tool may transparent visitor example may log name internet service provider ip address information provided internet browser adopt additional technology may also gather similar information mean may also use cookie technology among thing may use cooky tracking technology purpose storing username password hash spare reenter information time visit way use information use information provide operate instapapers feature share information outside party except extent necessary accomplish instapapers functionality use return email address answer email receive address used purpose shared outside party use nonidentifying aggregate information better design instapaper suggest popular content user share advertiser publisher example may use aggregate information instapaper usage help design new feature service product may tell advertiser publisher number people visited certain area website may tell advertiser publisher number people bookmarked story particular site topic may aggregate popular story limited time period certain website order suggest story instapapers editor pick user also saved page website information used similar manner disclose anything could used identify individual information based may disclose information response subpoena court order legal process establish exercise legal right defend legal claim may disclose information believe necessary desirable order investigate prevent take action regarding illegal activity suspected fraud situation involving potential threat physical safety person violation policy andor protect right property future may sell buy merge partner company business transaction user information may among transferred asset publicly accessible information information share instapaper considered public use social sharing functionality including others view recent starred article know username others view unread archive starred folder content reveal share associated rssfeed url external service external service beyond instapapers control integrated instapaper necessary mailgun email sending crashlytics crash reporting zendesk customer support google analytics traffic measurement tracking integration google service like analytics youtube youtube api service bound google privacy policy instapaper make reasonable effort ensure integrated external service trustworthy reputable instapaper held responsible data collection usage service commitment data security prevent unauthorized access maintain data accuracy ensure correct use information put place appropriate physical electronic managerial procedure safeguard secure information collect online please note ensure easy account creation minimal customer error reduced support inquiry instapaper account initially password left without password anyone access account know guess username set change password go httpwwwinstapapercomuserpassword commitment childrens privacy protecting privacy young especially important reason never collect maintain information website actually know part website structured attract anyone access correct information access personally identifiable information collect online maintain logging instapaper account instapaper website httpwwwinstapapercom correct factual error personally identifiable information changing deleting erroneous information deleting entire instapaper account httpwwwinstapapercomuserdelete emailing supportinstapapercom protect privacy security also take reasonable step verify identity granting access making correction deleting information delete entire instapaper account time httpwwwinstapapercomuserdelete delete account account information saved page data deleted instapaper service immediately due nature backup log deleted data may persist backup log deleted privacy shield instapaper complies euus privacy shield framework swissus privacy shield framework set forth u department commerce regarding collection use retention personal information transferred european union united kingdom switzerland united state pursuant privacy shield instapaper certified department commerce adheres privacy shield principle conflict term privacy policy privacy shield principle privacy shield principle shall govern learn privacy shield program view certification please visit httpswwwprivacyshieldgov compliance privacy shield principle instapaper commits resolve complaint privacy collection use personal information pursuant privacy shield eu uk swiss individual inquiry complaint regarding privacy shield policy first contact instapaper supportinstapapercom within scope privacy notice privacy complaint dispute resolved instapapers internal process federal trade commission jurisdiction instapapers compliance privacy shield privacy shield principle describe instapapers accountability personal data subsequently transfer thirdparty agent privacy shield principle instapaper shall remain liable third party agent process personal information manner inconsistent privacy shield principle unless instapaper prof responsible event giving rise damage selected jam independent dispute resolution provider handle unresolved privacy shield complaint unable resolve concern good faith effort address may contact jam submit privacy shield claim jam usbased private alternate dispute resolution provider contracted jam provide independent recourse mechanism user privacy concern cost may learn jam service file claim jam visiting httpswwwjamsadrcomeuusprivacyshield need appear court may conduct dispute resolution process via telephone video conference note instapaper may required release personal data eu uk swiss individual whose data pursuant privacy shield response legal request public authority including meet national security law enforcement requirement certain circumstance privacy shield framework provides right invoke binding arbitration resolve complaint resolved mean described annex privacy shield principle certain circumstance privacy shield framework provides right invoke binding arbitration resolve complaint resolved mean described annex privacy shield principle gdpr information eea user right individual located european economic area eea certain right respect personal information instapaper provide capability worldwide user including right access personal data right correct rectify inaccurate personal data right restrict oppose processing personal data right erase personal data right personal data portability instapaper us process store personal data including listed information collect section necessary perform contract based legitimate interest order provide service rely consent process personal data place cooky device case instapaper may process personal data pursuant legal obligation protect vital interest another person exercise right youre user based eea request personal data report submitting request supportinstapapercom report include personal data provided structured commonly used portable format please note instapaper may request additional information verify identity disclose information personal data corrected deleted personal data updated instapaper account setting contacting u supportinstapapercom also remove personal data instapaper deleting account httpwwwinstapapercomuserdelete complain regulator youre based eea think havent complied data protection law right lodge complaint local supervisory authority question instapaper account please contact u supportinstapapercom contact u question concern privacy policy please email supportinstapapercom time ability receive send englishlanguage communication change policy instapaper reserve right change policy time please check page periodically change continued use instapaper following posting change policy mean accept change notify make material change policy give opportunity review revised policy deciding would like continue use service review previous version policy httpsgithubcominstapaperprivacy effective date january th click drag bookmark bar</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -1048,6 +1971,21 @@
     <t>{'CONTACTS': 85, 'LOCATION': 66, 'STORAGE': 98, 'CAMERA': 18, 'MICROPHONE': 21, 'PERSISTENTID': 135}</t>
   </si>
   <si>
+    <t>{'CAMERA': 13, 'LOCATION': 36, 'PERSISTENTID': 81}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 65, 'LOCATION': 70, 'SMS': 65, 'PHONE_CALL': 92, 'PERSISTENTID': 108, 'STORAGE': 84, 'CAMERA': 17, 'MICROPHONE': 8}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 78, 'STORAGE': 58, 'CAMERA': 32, 'MICROPHONE': 15, 'LOCATION': 52, 'PERSISTENTID': 133}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': 87, 'LOCATION': 61, 'PERSISTENTID': 114, 'STORAGE': 95, 'CAMERA': 105, 'MICROPHONE': 23}</t>
+  </si>
+  <si>
+    <t>{'LOCATION': 21, 'STORAGE': 31, 'PERSISTENTID': 39}</t>
+  </si>
+  <si>
     <t>{'CONTACTS': {'account': 19, 'contact': 25, 'content service': 1, 'cooky': 14, 'friend': 15, 'list': 1, 'purpose': 8, 'social': 4}, 'CALENDAR': {'book': 10, 'contact': 25, 'event': 9, 'including': 30, 'search': 17, 'use information': 22}, 'LOCATION': {'gps': 1, 'identifier': 14, 'including': 30, 'ip': 15, 'ip address': 12, 'location': 15, 'location information': 1}, 'SMS': {'log': 21, 'message': 11, 'receive': 8, 'use service': 1}, 'PHONE_CALL': {'browser': 17, 'call': 9, 'identifier': 14, 'information collect': 15, 'message': 11, 'network': 16, 'receive': 8}, 'PERSISTENTID': {'browser': 17, 'device id': 1, 'id': 124, 'identifier': 14, 'information collect': 15}, 'STORAGE': {'account': 19, 'download': 3, 'file': 9, 'file communication': 1, 'receive': 8, 'share': 49, 'video': 8}, 'CAMERA': {'activity': 37, 'camera': 26, 'photo': 5, 'video': 8}, 'MICROPHONE': {'audio': 14, 'information use': 6, 'video': 8, 'voice': 14}}</t>
   </si>
   <si>
@@ -1058,6 +1996,21 @@
   </si>
   <si>
     <t>{'CONTACTS': {'account': 29, 'contact': 17, 'contact list': 1, 'cooky': 15, 'friend': 1, 'list': 2, 'medium': 1, 'purpose': 13, 'social': 5, 'social medium': 1}, 'LOCATION': {'geolocation': 1, 'gps': 4, 'identifier': 6, 'including': 22, 'ip': 15, 'ip address': 3, 'locate': 2, 'location': 8, 'location data': 1, 'location information': 3, 'track': 1}, 'STORAGE': {'account': 29, 'download': 3, 'file': 8, 'receive': 16, 'save': 1, 'share': 25, 'storage': 3, 'upload': 7, 'video': 6}, 'CAMERA': {'activity': 9, 'appear': 2, 'photo': 1, 'video': 6}, 'MICROPHONE': {'audio': 7, 'audio information': 1, 'information use': 6, 'video': 6, 'voice': 1}, 'PERSISTENTID': {'advertising id': 1, 'browser': 7, 'device id': 4, 'id': 90, 'identifier': 6, 'information collect': 20, 'mobile': 3, 'phone number': 3, 'unique': 1}}</t>
+  </si>
+  <si>
+    <t>{'CAMERA': {'activity': 10, 'appear': 2, 'service like': 1}, 'LOCATION': {'geolocation': 1, 'identifier': 2, 'including': 10, 'ip': 8, 'ip address': 4, 'locate': 2, 'location': 8, 'track': 1}, 'PERSISTENTID': {'application': 2, 'device id': 4, 'id': 71, 'identifier': 2, 'phone number': 1, 'unique': 1}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {'account': 27, 'address book': 2, 'contact': 17, 'cooky': 6, 'friend': 2, 'list': 4, 'medium': 3, 'purpose': 4}, 'LOCATION': {'identifier': 2, 'including': 24, 'ip': 20, 'ip address': 3, 'locate': 1, 'location': 14, 'location data': 1, 'location information': 3, 'map': 2}, 'SMS': {'log': 8, 'message': 29, 'receive': 10, 'use service': 18}, 'PHONE_CALL': {'browser': 1, 'call': 6, 'identifier': 2, 'information collect': 7, 'message': 29, 'mobile': 9, 'network': 1, 'phone': 15, 'phone number': 11, 'receive': 10, 'unique': 1}, 'PERSISTENTID': {'browser': 1, 'id': 77, 'identifier': 2, 'information collect': 7, 'mobile': 9, 'phone number': 11, 'unique': 1}, 'STORAGE': {'account': 27, 'download': 6, 'file': 10, 'receive': 10, 'share': 27, 'storage': 1, 'upload': 2, 'video': 1}, 'CAMERA': {'activity': 8, 'photo': 4, 'profile photo': 2, 'service like': 2, 'video': 1}, 'MICROPHONE': {'information use': 4, 'talk': 1, 'video': 1, 'voice': 2}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {'account': 18, 'address book': 1, 'contact': 12, 'content service': 1, 'cooky': 8, 'list': 2, 'medium': 4, 'purpose': 15, 'social': 13, 'social medium': 4}, 'STORAGE': {'account': 18, 'file': 11, 'receive': 5, 'share': 16, 'upload': 3, 'video': 5}, 'CAMERA': {'activity': 15, 'appear': 1, 'camera': 2, 'photo': 8, 'profile photo': 1, 'video': 5}, 'MICROPHONE': {'audio': 2, 'electronic': 4, 'video': 5, 'voice': 4}, 'LOCATION': {'geolocation': 1, 'gps': 1, 'identifier': 7, 'including': 15, 'ip': 13, 'ip address': 3, 'location': 10, 'location data': 1, 'track': 1}, 'PERSISTENTID': {'application': 2, 'browser': 10, 'collect identifier': 1, 'device id': 1, 'id': 96, 'identifier': 7, 'information collect': 9, 'mobile': 2, 'phone number': 1, 'serial number': 1, 'type setting': 1, 'unique': 1, 'unique identifier': 1}}</t>
+  </si>
+  <si>
+    <t>{'CONTACTS': {'account': 18, 'contact': 17, 'contact list': 1, 'cooky': 8, 'friend': 27, 'list': 6, 'medium': 1, 'phonebook': 1, 'purpose': 7, 'social': 1}, 'LOCATION': {'gps': 1, 'identifier': 3, 'including': 13, 'ip': 13, 'ip address': 2, 'location': 13, 'location data': 1, 'location information': 4, 'map': 9, 'sensor': 1, 'track': 1}, 'PERSISTENTID': {'advertising id': 2, 'application': 1, 'browser': 4, 'id': 86, 'identifier': 3, 'information collect': 9, 'mobile': 2, 'phone number': 3, 'type setting': 1, 'unique': 2, 'unique identifier': 1}, 'STORAGE': {'account': 18, 'download': 5, 'file': 5, 'receive': 9, 'save': 12, 'share': 34, 'storage': 1, 'upload': 1, 'video': 10}, 'CAMERA': {'activity': 4, 'camera': 5, 'photo': 4, 'service like': 2, 'snap': 79, 'take photo': 1, 'video': 10}, 'MICROPHONE': {'audio': 3, 'information use': 3, 'microphone': 3, 'record audio': 1, 'talk': 2, 'video': 10, 'voice': 1}}</t>
+  </si>
+  <si>
+    <t>{'LOCATION': {'including': 4, 'ip': 13, 'ip address': 1, 'locate': 1, 'track': 2}, 'STORAGE': {'account': 16, 'file': 1, 'receive': 2, 'save': 6, 'share': 5, 'video': 1}, 'PERSISTENTID': {'application': 3, 'browser': 1, 'id': 29, 'information collect': 6}}</t>
   </si>
   <si>
     <t>✅ This app clearly explains how it uses your child’s data.
@@ -1081,6 +2034,21 @@
     <t>{'Information Type_Generic personal information': 0.8500409126281738, 'Collection Process_Collected on first-party website/app': 0.9315841794013977, 'Information Type_Contact information': 0.9081942240397135, 'Information Type_User online activities': 0.891263100233945, 'Information Type_Personal identifier': 0.6044059991836548, 'Collection Process_Shared by first party with a third party': 0.8651939809322358, 'Purpose_Analytics or research': 0.8797099471092225, 'Information Type_IP address and device IDs': 0.9947046438852946, 'Information Type_Location': 0.913157323996226, 'Information Type_Computer information': 0.9939739108085632, 'Purpose_Essential service or feature': 0.7210415175982884, 'Information Type_Health, genetic, or biometric data': 0.9143846035003662, 'Purpose_Advertising or marketing': 0.9361460473802354, 'Purpose_Service operation and security': 0.9105730876326561, 'Purpose_Legal requirement': 0.9291104197502136}</t>
   </si>
   <si>
+    <t>{'Information Type_Generic personal information': 0.9235036606373994, 'Collection Process_Collected on first-party website/app': 0.8461252897977829, 'Information Type_Contact information': 0.9767535328865051, 'Information Type_IP address and device IDs': 0.9937131553888321, 'Information Type_Computer information': 0.993837296962738, 'Information Type_User online activities': 0.822649747133255, 'Information Type_Location': 0.9834908545017242, 'Purpose_Service operation and security': 0.9479397495587667, 'Purpose_Analytics or research': 0.9289020725658962, 'Purpose_Essential service or feature': 0.8272640364510673, 'Collection Process_Shared by first party with a third party': 0.896241287390391, 'Information Type_Health, genetic, or biometric data': 0.941914975643158, 'Purpose_Legal requirement': 0.9446798786520958, 'Purpose_Advertising or marketing': 0.9372006058692932}</t>
+  </si>
+  <si>
+    <t>{'Information Type_Contact information': 0.8854578658938408, 'Purpose_Essential service or feature': 0.7709387926494374, 'Purpose_Service operation and security': 0.9291250507036845, 'Information Type_Health, genetic, or biometric data': 0.516525149345398, 'Collection Process_Shared by first party with a third party': 0.7387300804257393, 'Purpose_Analytics or research': 0.887497807542483, 'Collection Process_Collected on first-party website/app': 0.8472914457321167, 'Purpose_Advertising or marketing': 0.9375910758972168, 'Information Type_Location': 0.9841348528862, 'Information Type_User online activities': 0.719200611114502, 'Information Type_Computer information': 0.8451553285121918, 'Information Type_IP address and device IDs': 0.9942948222160339, 'Purpose_Legal requirement': 0.9588719308376312, 'Information Type_Generic personal information': 0.5557473599910736}</t>
+  </si>
+  <si>
+    <t>{'Information Type_Generic personal information': 0.8590632639825344, 'Purpose_Essential service or feature': 0.682478109995524, 'Purpose_Analytics or research': 0.8178578093647957, 'Collection Process_Shared by first party with a third party': 0.6964219212532043, 'Information Type_Location': 0.9799185593922933, 'Purpose_Advertising or marketing': 0.8028789162635803, 'Information Type_User online activities': 0.8997939452528954, 'Collection Process_Collected on first-party website/app': 0.8862740397453308, 'Information Type_Contact information': 0.9425670579075813, 'Information Type_Personal identifier': 0.7156089842319489, 'Purpose_Service operation and security': 0.7983401616414388, 'Information Type_Computer information': 0.9923501014709473, 'Information Type_IP address and device IDs': 0.967140257358551, 'Information Type_Health, genetic, or biometric data': 0.6506217320760092}</t>
+  </si>
+  <si>
+    <t>{'Purpose_Analytics or research': 0.8689473446677712, 'Collection Process_Collected on first-party website/app': 0.8744916915893555, 'Information Type_Contact information': 0.9357475757598877, 'Purpose_Advertising or marketing': 0.8289765053325229, 'Purpose_Essential service or feature': 0.7888849377632141, 'Information Type_User online activities': 0.8891043331887987, 'Information Type_Computer information': 0.8380999445915223, 'Information Type_IP address and device IDs': 0.9943147301673889, 'Information Type_Location': 0.9543438106775284, 'Purpose_Service operation and security': 0.9242209146420161, 'Purpose_Legal requirement': 0.8978159626324972, 'Information Type_Generic personal information': 0.9241885840892792, 'Collection Process_Shared by first party with a third party': 0.8401029573546516}</t>
+  </si>
+  <si>
+    <t>{'Information Type_Contact information': 0.9199002832174301, 'Information Type_IP address and device IDs': 0.9946120977401733, 'Information Type_User online activities': 0.745964248975118, 'Collection Process_Collected on first-party website/app': 0.9835659861564636, 'Collection Process_Shared by first party with a third party': 0.7154817978541056, 'Purpose_Essential service or feature': 0.6130885183811188, 'Purpose_Analytics or research': 0.8153013785680135, 'Purpose_Legal requirement': 0.9048327207565308, 'Purpose_Service operation and security': 0.9416495263576508, 'Information Type_Generic personal information': 0.8611811527184078}</t>
+  </si>
+  <si>
     <t>Legal requirement (Freq: 9, MaxProb: 99%), Analytics or research (Freq: 8, MaxProb: 95%), Service operation and security (Freq: 7, MaxProb: 98%), Shared by first party with a third party (Freq: 6, MaxProb: 95%), Advertising or marketing (Freq: 5, MaxProb: 98%), Essential service or feature (Freq: 4, MaxProb: 87%), Collected on first-party website/app (Freq: 1, MaxProb: 98%), Generic personal information (Freq: 1, MaxProb: 94%), Contact information (Freq: 1, MaxProb: 85%)</t>
   </si>
   <si>
@@ -1088,6 +2056,21 @@
   </si>
   <si>
     <t>User online activities (Freq: 11, MaxProb: 99%), Essential service or feature (Freq: 11, MaxProb: 88%), Analytics or research (Freq: 10, MaxProb: 98%), Advertising or marketing (Freq: 9, MaxProb: 98%), Shared by first party with a third party (Freq: 9, MaxProb: 97%), Contact information (Freq: 8, MaxProb: 98%), Service operation and security (Freq: 7, MaxProb: 99%), Collected on first-party website/app (Freq: 6, MaxProb: 99%), Legal requirement (Freq: 5, MaxProb: 99%), Generic personal information (Freq: 5, MaxProb: 93%), IP address and device IDs (Freq: 3, MaxProb: 99%), Location (Freq: 3, MaxProb: 99%), Computer information (Freq: 1, MaxProb: 99%), Health, genetic, or biometric data (Freq: 1, MaxProb: 91%)</t>
+  </si>
+  <si>
+    <t>Generic personal information (Freq: 46, MaxProb: 94%), Service operation and security (Freq: 15, MaxProb: 99%), Essential service or feature (Freq: 13, MaxProb: 88%), Shared by first party with a third party (Freq: 9, MaxProb: 97%), Legal requirement (Freq: 8, MaxProb: 99%), Analytics or research (Freq: 7, MaxProb: 98%), Collected on first-party website/app (Freq: 6, MaxProb: 99%), IP address and device IDs (Freq: 4, MaxProb: 99%), Location (Freq: 2, MaxProb: 99%), Contact information (Freq: 2, MaxProb: 98%), User online activities (Freq: 2, MaxProb: 96%), Computer information (Freq: 1, MaxProb: 99%), Health, genetic, or biometric data (Freq: 1, MaxProb: 94%), Advertising or marketing (Freq: 1, MaxProb: 94%)</t>
+  </si>
+  <si>
+    <t>Essential service or feature (Freq: 13, MaxProb: 88%), Service operation and security (Freq: 11, MaxProb: 99%), Analytics or research (Freq: 11, MaxProb: 98%), Contact information (Freq: 8, MaxProb: 98%), Advertising or marketing (Freq: 8, MaxProb: 98%), Shared by first party with a third party (Freq: 5, MaxProb: 95%), Collected on first-party website/app (Freq: 4, MaxProb: 96%), IP address and device IDs (Freq: 3, MaxProb: 99%), Location (Freq: 3, MaxProb: 99%), Computer information (Freq: 2, MaxProb: 99%), User online activities (Freq: 2, MaxProb: 99%), Legal requirement (Freq: 2, MaxProb: 98%)</t>
+  </si>
+  <si>
+    <t>Generic personal information (Freq: 13, MaxProb: 95%), User online activities (Freq: 8, MaxProb: 99%), Contact information (Freq: 8, MaxProb: 98%), Analytics or research (Freq: 6, MaxProb: 97%), Essential service or feature (Freq: 6, MaxProb: 88%), Collected on first-party website/app (Freq: 3, MaxProb: 99%), Service operation and security (Freq: 3, MaxProb: 99%), Location (Freq: 3, MaxProb: 99%), IP address and device IDs (Freq: 2, MaxProb: 99%), Computer information (Freq: 2, MaxProb: 99%), Personal identifier (Freq: 2, MaxProb: 95%), Health, genetic, or biometric data (Freq: 1, MaxProb: 85%), Advertising or marketing (Freq: 1, MaxProb: 80%), Shared by first party with a third party (Freq: 1, MaxProb: 70%)</t>
+  </si>
+  <si>
+    <t>Analytics or research (Freq: 16, MaxProb: 98%), Service operation and security (Freq: 12, MaxProb: 99%), Collected on first-party website/app (Freq: 11, MaxProb: 99%), User online activities (Freq: 9, MaxProb: 99%), Essential service or feature (Freq: 9, MaxProb: 88%), Shared by first party with a third party (Freq: 8, MaxProb: 97%), Advertising or marketing (Freq: 7, MaxProb: 98%), Legal requirement (Freq: 5, MaxProb: 99%), Contact information (Freq: 5, MaxProb: 98%), Computer information (Freq: 4, MaxProb: 99%), Location (Freq: 4, MaxProb: 99%), Generic personal information (Freq: 2, MaxProb: 92%), IP address and device IDs (Freq: 1, MaxProb: 99%)</t>
+  </si>
+  <si>
+    <t>Generic personal information (Freq: 12, MaxProb: 94%), Legal requirement (Freq: 4, MaxProb: 99%), Service operation and security (Freq: 4, MaxProb: 98%), Contact information (Freq: 4, MaxProb: 98%), Shared by first party with a third party (Freq: 4, MaxProb: 93%), Analytics or research (Freq: 2, MaxProb: 98%), User online activities (Freq: 2, MaxProb: 85%), IP address and device IDs (Freq: 1, MaxProb: 99%), Collected on first-party website/app (Freq: 1, MaxProb: 98%)</t>
   </si>
   <si>
     <t>This app may collect information such as contact information and other personal information, directly through the app and some of this data may be shared with third parties. 
@@ -1102,6 +2085,22 @@
 Data collected is used for advertising, analytics or research, essential services, legal compliance and security or app functionality.</t>
   </si>
   <si>
+    <t>This app may collect information such as device/computer info, contact information, device ID, location and online activity, directly through the app and some of this data may be shared with third parties. 
+Data collected is used for advertising, analytics or research, essential services, legal compliance and security or app functionality.</t>
+  </si>
+  <si>
+    <t>This app may collect information such as device/computer info, contact information, other personal information, health or biometric data, device ID, location, personal ID and online activity, directly through the app and some of this data may be shared with third parties. 
+Data collected is used for advertising, analytics or research, essential services and security or app functionality.</t>
+  </si>
+  <si>
+    <t>This app may collect information such as device/computer info, contact information, other personal information, device ID, location and online activity, directly through the app and some of this data may be shared with third parties. 
+Data collected is used for advertising, analytics or research, essential services, legal compliance and security or app functionality.</t>
+  </si>
+  <si>
+    <t>This app may collect information such as contact information, other personal information, device ID and online activity, directly through the app and some of this data may be shared with 